--- a/SmartDoc_Master_Implementation_Tracker.xlsx
+++ b/SmartDoc_Master_Implementation_Tracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\speed\Desktop\Claude - ПРОЕКТ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F81385CB-125D-4E8C-9BE1-A3B7EEE798E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8245906-141B-49D4-A760-1D5996054853}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">AI!$A$7:$L$16</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="15" hidden="1">BILLING_PLANS!$A$25:$L$30</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="17" hidden="1">CHANGE_LOG!$A$1:$I$79</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="17" hidden="1">CHANGE_LOG!$A$1:$I$81</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">CRITICAL_FIXES!$A$31:$L$115</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">DOCUMENT_FIDELITY!$A$7:$L$24</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">DOCX_OOXML!$A$7:$L$28</definedName>
@@ -71,12 +71,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3783" uniqueCount="1538">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3794" uniqueCount="1541">
   <si>
     <t>SmartDoc — Master Implementation Tracker</t>
   </si>
   <si>
-    <t>Production-hardening brief. MASTER holds the task data; every number here is a formula. Updated with tools/tracker/tracker.py. Last written 2026-09-27 19:37 (local time).</t>
+    <t>Production-hardening brief. MASTER holds the task data; every number here is a formula. Updated with tools/tracker/tracker.py. Last written 2026-09-27 19:38 (local time).</t>
   </si>
   <si>
     <t>Overall</t>
@@ -1576,2913 +1576,2916 @@
     <t>backend/parsers, export, models</t>
   </si>
   <si>
+    <t>d32c6a6</t>
+  </si>
+  <si>
+    <t>Hidden text (listed here too) is done under DOCX-025.; Part 2 remaining: character scale, kerning, language/noProof, theme font/colour links, effects, emphasis marks - detect, 'kept while unchanged' with the source kept, and export.docx.rewritten_formatting for rewritten blocks.</t>
+  </si>
+  <si>
+    <t>DOCX-014</t>
+  </si>
+  <si>
+    <t>Paragraph formatting</t>
+  </si>
+  <si>
+    <t>Right indent, keep-with-next, keep-lines, page-break-before, widow/orphan, outline level, tabs, borders, shading, direction, contextual spacing.</t>
+  </si>
+  <si>
+    <t>DOCX-015</t>
+  </si>
+  <si>
+    <t>Sections as a first-class concept</t>
+  </si>
+  <si>
+    <t>Breaks (next/continuous/even/odd), orientation, size, margins, columns, header/footer distance, first/even/odd headers, linked-to-previous, page-number restart.</t>
+  </si>
+  <si>
+    <t>tests/test_docx_detect.py::test_a_section_break_breaks_the_page_only_where_word_does</t>
+  </si>
+  <si>
+    <t>backend/models, parsers, export</t>
+  </si>
+  <si>
+    <t>Fixed: a section's w:type describes how THAT section starts (ECMA-376 17.6.22) - the importer used the ending section's own type, so a continuous break became a page break and continuous-&gt;new-page put the break between the wrong sections (probe confirmed). Now the next section's type decides. Per-section differences are reported (FID-002). Remaining: sections as a first-class model concept (orientation/margins/columns/headers per section, page-number restart) and export of several sections.; With DOCX-011 the last section's properties (columns, page numbering, borders, line numbers, vertical alignment, header/footer variants) are kept in Word exports; earlier sections' are still reported lost.; DOCX-028: earlier sections now survive in Word exports while their ending paragraph is unchanged; page setup/header/page-number changes apply to them; a lost one is reported (export.docx.section_lost). Modelling sections is still this task.</t>
+  </si>
+  <si>
+    <t>DOCX-016</t>
+  </si>
+  <si>
+    <t>Numbering engine</t>
+  </si>
+  <si>
+    <t>Decimal/roman/alpha/bullets, custom prefixes/suffixes, start, restart, continuation, multilevel, numId/abstractNum/ilvl, indentation.</t>
+  </si>
+  <si>
+    <t>tests/test_docx_numbering.py</t>
+  </si>
+  <si>
+    <t>Done so far: top-level list number format (decimal/roman/letters), start value (lvl start + lvlOverride/startOverride) and continuation across interrupting paragraphs imported into Element.numbering and written back to Word (per-level formats, startOverride) and PDF; empty numbered items keep counting. Reported, not kept: custom labels ('Чл. 1.', '(a)'), multi-level labels ('1.1'), numbered headings baked into text. Remaining: prefixes/suffixes, multilevel numbering model, restart semantics per level, indentation.</t>
+  </si>
+  <si>
+    <t>AUD-04</t>
+  </si>
+  <si>
+    <t>DOCX-017</t>
+  </si>
+  <si>
+    <t>Table engine</t>
+  </si>
+  <si>
+    <t>No forced header or Table Grid; widths, heights, margins, borders, shading, v-align, nested tables, repeated header rows, table styles.</t>
+  </si>
+  <si>
+    <t>From EDIT-011 (2026-09-27): add per-cell alignment and column widths to the model (the editor's cell align/colwidth, Word tcW/tblGrid, PDF colWidths); until then the editor names them as not kept.</t>
+  </si>
+  <si>
+    <t>DOCX-018</t>
+  </si>
+  <si>
+    <t>Images</t>
+  </si>
+  <si>
+    <t>Alt text exported; crop, rotation, anchor, wrap, position preserved; WEBP converted on export.</t>
+  </si>
+  <si>
+    <t>Alt text + title now exported (docPr descr/title) with DOCX-001; crop, rotation, WEBP still open.</t>
+  </si>
+  <si>
+    <t>DOCX-019</t>
+  </si>
+  <si>
+    <t>Drawings and text boxes preserved</t>
+  </si>
+  <si>
+    <t>Anchored drawings, text boxes, shapes kept even when not editable.</t>
+  </si>
+  <si>
+    <t>DOCX-028: text boxes and drawings in unchanged paragraphs are copied as they are (grouped with their anchor paragraph).</t>
+  </si>
+  <si>
+    <t>DOCX-020</t>
+  </si>
+  <si>
+    <t>Fields</t>
+  </si>
+  <si>
+    <t>Code/result/relationship; header STYLEREF/DATE live; TOC kept; CITATION/BIBLIOGRAPHY sources preserved; no 'Invalid source specified.'</t>
+  </si>
+  <si>
+    <t>backend/parsers, export</t>
+  </si>
+  <si>
+    <t>DOCX-028: field codes in unchanged blocks are copied as they are; a field spanning paragraphs is never copied half (self-contained check).</t>
+  </si>
+  <si>
+    <t>AUD-18</t>
+  </si>
+  <si>
+    <t>DOCX-021</t>
+  </si>
+  <si>
+    <t>Comment threads</t>
+  </si>
+  <si>
+    <t>Replies, resolved state, authors, ranges preserved (commentsExtended, people).</t>
+  </si>
+  <si>
+    <t>AUD-06</t>
+  </si>
+  <si>
+    <t>DOCX-022</t>
+  </si>
+  <si>
+    <t>Tracked changes preserved</t>
+  </si>
+  <si>
+    <t>Not silently accepted; explicit choice.</t>
+  </si>
+  <si>
+    <t>DOCX-028: blocks holding tracked changes are never copied (always written anew, accepted), so this task's explicit choice is still needed.</t>
+  </si>
+  <si>
+    <t>DOCX-023</t>
+  </si>
+  <si>
+    <t>Content controls preserved</t>
+  </si>
+  <si>
+    <t>w:sdt of every kind kept with its properties.</t>
+  </si>
+  <si>
+    <t>DOCX-028: content controls in unchanged blocks are copied with their properties (E2E proves it through the editor); written anew they are unwrapped (reported lossy at import).</t>
+  </si>
+  <si>
+    <t>DOCX-024</t>
+  </si>
+  <si>
+    <t>Real footnotes and endnotes</t>
+  </si>
+  <si>
+    <t>Notes stay notes on export.</t>
+  </si>
+  <si>
+    <t>DOCX-025</t>
+  </si>
+  <si>
+    <t>Hidden text stays hidden</t>
+  </si>
+  <si>
+    <t>Imported hidden text is kept hidden, shown only on request.</t>
+  </si>
+  <si>
+    <t>MarkType.HIDDEN (appended; no existing mark order changes). Importer resolves w:vanish as Word does: run, character style, paragraph style (the default paragraph style when none), docDefaults; webHidden stays visible; an explicit vanish=0 shows text in a hidden style. The detector uses the default paragraph style the same way and names hidden text as kept hidden (DETECTED_PRESERVED, not a content change). Editor: non-inclusive hidden mark (editor/hiddenText.ts; Word's display:none paste stays hidden), hidden by CSS unless .show-hidden; status bar 'Show hidden text (N words)' toggles it and re-paginates; the Structure panel leaves hidden text out of headings. Word export writes w:vanish (copied blocks keep theirs); PDF doesn't print hidden runs, export.pdf.hidden_text names the word count, and the PDF content check compares visible words (document_words(visible_only=True)); Word-side checks count hidden text on both sides. Golden 02-rich-text gained a hidden sentence (editor round trip in Vitest).</t>
+  </si>
+  <si>
+    <t>backend 876 passed/1 skipped (tests/test_hidden_text.py 7: import resolution, default paragraph style, report, upload + content check + editor save, Word export round trip, PDF text + note + check); Vitest 125 (editor/hiddenText.test.tsx 6, golden round trip of 02); Playwright 22 (e2e/hidden-text.spec.ts: hidden until asked, dotted line when shown, vanish in the Word export); tsc + eslint clean</t>
+  </si>
+  <si>
+    <t>backend/parsers, frontend</t>
+  </si>
+  <si>
+    <t>7d1af86</t>
+  </si>
+  <si>
+    <t>DOCX-028: vanish survives in unchanged blocks only; the model still shows hidden text as ordinary text - next task.</t>
+  </si>
+  <si>
+    <t>DOCX-026</t>
+  </si>
+  <si>
+    <t>Hyperlink policy and no silent autolink</t>
+  </si>
+  <si>
+    <t>Plain-text addresses not turned into links by default; file:/UNC reported.</t>
+  </si>
+  <si>
+    <t>tests/test_docx_detect.py::test_unsafe_links_and_spacing_paragraphs_are_reported</t>
+  </si>
+  <si>
+    <t>Done: links to unsafe addresses (javascript:, file:, UNC...) are kept as plain text and reported (docx.link.unsafe); plain-text addresses turned into links are reported (docx.autolink). Remaining: stop autolinking by default (a setting), per the task.</t>
+  </si>
+  <si>
+    <t>AUD-03,AUD-13</t>
+  </si>
+  <si>
+    <t>FMT-004</t>
+  </si>
+  <si>
+    <t>Render-spec defaults respect the source</t>
+  </si>
+  <si>
+    <t>Imported Word styles are not overridden by defaults (headings not forced bold).</t>
+  </si>
+  <si>
+    <t>backend/formatting</t>
+  </si>
+  <si>
+    <t>TEST-020</t>
+  </si>
+  <si>
+    <t>Word-authored fixtures in the repository</t>
+  </si>
+  <si>
+    <t>20 synthetic Word-authored fixtures, scrubbed of identifying metadata.</t>
+  </si>
+  <si>
+    <t>backend/tests/fixtures/word</t>
+  </si>
+  <si>
+    <t>TEST-021</t>
+  </si>
+  <si>
+    <t>Expected-loss manifests in CI</t>
+  </si>
+  <si>
+    <t>expected-loss.json per fixture; CI compares actual vs expected.</t>
+  </si>
+  <si>
+    <t>TEST-022</t>
+  </si>
+  <si>
+    <t>True fidelity test</t>
+  </si>
+  <si>
+    <t>SOURCE -&gt; import -&gt; format -&gt; editor save -&gt; export -&gt; reimport -&gt; compare SOURCE vs RESULT: content, formatting, metadata, structure separately.</t>
+  </si>
+  <si>
+    <t>TEST-023</t>
+  </si>
+  <si>
+    <t>Independent validation</t>
+  </si>
+  <si>
+    <t>OOXML schema validation, Word when available, docx2python; pdftotext/PyMuPDF for PDF.</t>
+  </si>
+  <si>
+    <t>app/export/package_check.py: an independent package check (zip read directly): well-formed parts, content types, relationships resolving, relationship ids used, defined styles/lists/comments. Found a real defect on first run (python-docx's add_comment refers to an undefined CommentReference style; exports now define it). Every golden export passes, fresh and into its original.</t>
+  </si>
+  <si>
+    <t>tests/test_package_check.py (13)</t>
+  </si>
+  <si>
+    <t>The docx skill's XSD validator needs defusedxml (not installed; installing needs a download) - schema-level validation remains open.</t>
+  </si>
+  <si>
+    <t>DOCX-027</t>
+  </si>
+  <si>
+    <t>Importer builds nested blocks</t>
+  </si>
+  <si>
+    <t>Use TableCell.blocks / ListItem.blocks on import: pictures, lists (with bullets) and nested tables inside cells, pictures inside list items - instead of dropping or flattening them.</t>
+  </si>
+  <si>
+    <t>AUD-01,AUD-03,AUD-08</t>
+  </si>
+  <si>
+    <t>DOCX-028</t>
+  </si>
+  <si>
+    <t>Unchanged blocks keep their original XML in Word exports</t>
+  </si>
+  <si>
+    <t>Blocks the user didn't change are written back as their original XML (fields, content controls, run-level formatting the model can't hold, bookmarks), changed ones regenerated; needs block provenance from the importer and fingerprints.</t>
+  </si>
+  <si>
+    <t>Importer records each top-level element's body children (Element.sourceBlocks: list items, drop caps, derived page breaks); an upload with a kept file stamps content+look fingerprints (Element.sourceHash, app/export/provenance.py: own/kind/body/nested resolved styles; page breaks have no look). docx_export._copy_plan groups elements with their children (uncovered children join the group before) and copies a group verbatim when every element is unchanged, together and in original order, children contiguous, XML self-contained (no tracked changes/note refs/altChunk; balanced fields, bookmarks, comment ranges); everything else is written anew. Provenance is server-side (keep_provenance on PUT /content). Page setup now runs after the body: changed size/margins reach every kept section (orientation kept, landscape turned), a changed main header is rewritten where Word shows it (link to previous), page numbers left out/asked for apply to every section. export.docx.section_lost (LOSSY) names sections lost with a changed paragraph; import report: earlier sections' setup/headers kept while unchanged; PDF names them Word-only. All 13 golden documents stamped + exported into their originals: sound packages, content verified (12-complex rewrites only the footnote paragraph and the note, by design).</t>
+  </si>
+  <si>
+    <t>backend 869 passed/1 skipped (tests/test_original_blocks.py 26 incl. 13 golden; test_source_package.py rewritten claims with export proof; test_golden_documents.py 13 files); Vitest 119 (editor round trip of 13-kept-blocks); Playwright 21 (e2e/kept-blocks.spec.ts: edit in the real editor, untouched paragraphs keep content control, double underline, landscape section); tsc + eslint clean</t>
+  </si>
+  <si>
+    <t>c8c2d27</t>
+  </si>
+  <si>
+    <t>Follow-up of DOCX-011 (package-level patch writer).; Known limit: any restyle (template, instruction) changes the body look, so every block but page breaks is written anew; follow-up DOCX-029. Sections survive only with their ending paragraph until DOCX-015 models them.</t>
+  </si>
+  <si>
+    <t>DOCX-029</t>
+  </si>
+  <si>
+    <t>Restyled blocks keep their original XML where nothing conflicts</t>
+  </si>
+  <si>
+    <t>After a template or instruction restyles a kind of block, copy a block's original XML when its paragraph style is the Word style the export rewrites for that kind and its direct formatting (pPr/rPr) sets none of the properties that changed; today any restyle writes every block anew (content controls, double underline etc. then lost, as the import report says).</t>
+  </si>
+  <si>
+    <t>Found while finishing DOCX-028: the look is part of the fingerprint so the export never shows a stale look.</t>
+  </si>
+  <si>
+    <t>FID-007</t>
+  </si>
+  <si>
+    <t>Reports follow the Word copy</t>
+  </si>
+  <si>
+    <t>With the original kept, the import report names what lives in blocks as kept in the Word export while the paragraph is unchanged, and an export that writes such a block anew names what it lost; a copy never brings back a link the app doesn't allow.</t>
+  </si>
+  <si>
+    <t>fidelity/imports.py KEPT_WHILE_UNCHANGED (content controls, text boxes, charts/shapes/SmartArt, objects, picture crop/rotation/floating, drop caps, empty paragraphs, approximated underlines, character scale, text effects, RTL) -&gt; detected_not_editable 'kept while the paragraph isn't changed or restyled'; docx_export._copy_plan returns rewritten groups, _lost_in/_rewritten_losses -&gt; export.docx.rewritten_blocks (LOSSY, count, kinds incl. proofing exclusions); _safe_links keeps groups with unsafe links (relationships or HYPERLINK fields) from being copied; the PDF's Word-only note covers the features.</t>
+  </si>
+  <si>
+    <t>tests/test_copy_reports.py (6): kept while unchanged at import, rewritten losses named (content controls, stretched text), unsafe javascript: link never copied back, PDF word-only; backend 894 passed/1 skipped; Playwright 22</t>
+  </si>
+  <si>
+    <t>Generalises DOCX-028's section handling (export.docx.section_lost) to everything the model doesn't hold inside blocks.</t>
+  </si>
+  <si>
+    <t>SEC-010</t>
+  </si>
+  <si>
+    <t>Malformed DOCX -&gt; safe 4xx</t>
+  </si>
+  <si>
+    <t>XML/zip/structure errors map to invalid_file; fuzz corpus shows no 500.</t>
+  </si>
+  <si>
+    <t>AUD-12</t>
+  </si>
+  <si>
+    <t>SEC-011</t>
+  </si>
+  <si>
+    <t>Malformed PDF -&gt; safe 4xx</t>
+  </si>
+  <si>
+    <t>Verified with a fuzz corpus.</t>
+  </si>
+  <si>
+    <t>SEC-012</t>
+  </si>
+  <si>
+    <t>Image resource limits</t>
+  </si>
+  <si>
+    <t>Compressed and decompressed size, pixel count, width, height, images per document, total bytes, format allowlist; rejected before rasterisation.</t>
+  </si>
+  <si>
+    <t>backend/security</t>
+  </si>
+  <si>
+    <t>AUD-09</t>
+  </si>
+  <si>
+    <t>SEC-013</t>
+  </si>
+  <si>
+    <t>PDF bombs, huge XML, decompression limits</t>
+  </si>
+  <si>
+    <t>Reviewed and tested limits.</t>
+  </si>
+  <si>
+    <t>SEC-014</t>
+  </si>
+  <si>
+    <t>Href policy</t>
+  </si>
+  <si>
+    <t>Server-side scheme allowlist; javascript:/data:/vbscript:/file: never exported as active links.</t>
+  </si>
+  <si>
+    <t>backend/models, export</t>
+  </si>
+  <si>
+    <t>AUD-13</t>
+  </si>
+  <si>
+    <t>SEC-015</t>
+  </si>
+  <si>
+    <t>Field instruction allowlist</t>
+  </si>
+  <si>
+    <t>No DDE/INCLUDETEXT/INCLUDEPICTURE/external fields accepted from clients or exported.</t>
+  </si>
+  <si>
+    <t>SEC-016</t>
+  </si>
+  <si>
+    <t>External relationships policy</t>
+  </si>
+  <si>
+    <t>No arbitrary external targets in exports.</t>
+  </si>
+  <si>
+    <t>SEC-017</t>
+  </si>
+  <si>
+    <t>Malicious SVG</t>
+  </si>
+  <si>
+    <t>Verified refused everywhere.</t>
+  </si>
+  <si>
+    <t>SEC-018</t>
+  </si>
+  <si>
+    <t>Prompt injection / AI output abuse</t>
+  </si>
+  <si>
+    <t>Tests with hostile documents; outputs validated.</t>
+  </si>
+  <si>
+    <t>Hostile-document tests: the document can't close its fence; out-of-bounds answers refused and fall back; an instruction steered by the document deletes nothing (proposals only) and a CSS break-out value is dropped; style-analysis flags on unknown elements dropped (see AI-009).</t>
+  </si>
+  <si>
+    <t>tests/test_prompt_injection.py</t>
+  </si>
+  <si>
+    <t>SEC-019</t>
+  </si>
+  <si>
+    <t>Error envelope audit</t>
+  </si>
+  <si>
+    <t>Every error {code, message, details, request_id}; no stack traces to users.</t>
+  </si>
+  <si>
+    <t>backend/api</t>
+  </si>
+  <si>
+    <t>SEC-020</t>
+  </si>
+  <si>
+    <t>CSP without 'unsafe-inline' scripts</t>
+  </si>
+  <si>
+    <t>Nonce-based CSP for the Next.js app.</t>
+  </si>
+  <si>
+    <t>TEST-030</t>
+  </si>
+  <si>
+    <t>Security regression suite</t>
+  </si>
+  <si>
+    <t>Fuzz corpus, pixel bombs, href/field policy, IDOR, CSRF.</t>
+  </si>
+  <si>
+    <t>SEC-010,SEC-012,SEC-014,SEC-015</t>
+  </si>
+  <si>
+    <t>AUD-09,AUD-12,AUD-13</t>
+  </si>
+  <si>
+    <t>SEC-021</t>
+  </si>
+  <si>
+    <t>Sensitivity-label metadata in the public repository</t>
+  </si>
+  <si>
+    <t>корекции.docx (committed in 5f2bf9e, pushed) carries 8 MSIP_Label_* custom properties incl. the organisation's tenant SiteId (label: Microsoft default 'General' family, no content marking). Options: leave; scrub the file in a new commit (HEAD only); purge from history (force-push).</t>
+  </si>
+  <si>
+    <t>repository history</t>
+  </si>
+  <si>
+    <t>Needs Boril: the choice involves his organisation's label and possibly rewriting pushed history. The tracker tools now strip MSIP labels on every write; the pre-push scan flags them.</t>
+  </si>
+  <si>
+    <t>SEC-022</t>
+  </si>
+  <si>
+    <t>Formatting rule values can't break out of a style</t>
+  </si>
+  <si>
+    <t>A rule value reaches the editor's style attribute, Word and PDF styles as text. The element-style and page-setting endpoints accepted any string (e.g. 'center;background-image:url(...)'), the AI instruction path too (FMT-005): CSS injection into every viewer's editor.</t>
+  </si>
+  <si>
+    <t>app/formatting/values.py: clean_rule_value per property (the StyleSystem's limits: choices, true/false, one safe font name, renderable colours, bounded numbers with known units, header/footer text &lt;=500). Refused with 422 by the element-style and page-setting endpoints (schemas RuleValue); instruction rules and set_style operations with such values dropped (FMT-005), validate_operations refuses them; stored rules no renderer can use are skipped at resolve (engine._usable) so old documents can't carry them either. All 177 default/template rules pass unchanged.</t>
+  </si>
+  <si>
+    <t>tests/test_rule_values.py (34 cases incl. API 422, stored-rule skip, instruction drop)</t>
+  </si>
+  <si>
+    <t>Found 2026-09-27 while mapping editor alignment (EDIT-008); probe confirmed the raw value in resolvedStyles.</t>
+  </si>
+  <si>
+    <t>PERF-001</t>
+  </si>
+  <si>
+    <t>Linear DOCX table export</t>
+  </si>
+  <si>
+    <t>500x8 table under a recorded threshold (baseline 321 s).</t>
+  </si>
+  <si>
+    <t>AUD-10</t>
+  </si>
+  <si>
+    <t>PERF-002</t>
+  </si>
+  <si>
+    <t>Benchmarks recorded</t>
+  </si>
+  <si>
+    <t>Baseline and current measurements in the PERFORMANCE sheet.</t>
+  </si>
+  <si>
+    <t>tests/perf</t>
+  </si>
+  <si>
+    <t>PERF-003</t>
+  </si>
+  <si>
+    <t>Delta autosave</t>
+  </si>
+  <si>
+    <t>Change-aware patches with a threshold strategy; whole document only when needed.</t>
+  </si>
+  <si>
+    <t>frontend/editor, backend/api</t>
+  </si>
+  <si>
+    <t>PERF-004</t>
+  </si>
+  <si>
+    <t>Bounded, compressed version history</t>
+  </si>
+  <si>
+    <t>Editor history separate from persisted versions; compression/deltas; asset references.</t>
+  </si>
+  <si>
+    <t>PERF-005</t>
+  </si>
+  <si>
+    <t>Editor at 5k-12k blocks</t>
+  </si>
+  <si>
+    <t>Typing latency measured and improved.</t>
+  </si>
+  <si>
+    <t>PERF-006</t>
+  </si>
+  <si>
+    <t>JSON without ASCII escaping</t>
+  </si>
+  <si>
+    <t>Document JSON stored and sent as UTF-8.</t>
+  </si>
+  <si>
+    <t>backend/db</t>
+  </si>
+  <si>
+    <t>PERF-007</t>
+  </si>
+  <si>
+    <t>Safe size limits recorded</t>
+  </si>
+  <si>
+    <t>User-facing maximum sizes, job timeouts, resource ceilings documented and enforced.</t>
+  </si>
+  <si>
+    <t>backend/config</t>
+  </si>
+  <si>
+    <t>AUD-09,AUD-10</t>
+  </si>
+  <si>
+    <t>ACCT-001</t>
+  </si>
+  <si>
+    <t>E-mail sender abstraction</t>
+  </si>
+  <si>
+    <t>SMTP provider + development outbox; no secrets in logs.</t>
+  </si>
+  <si>
+    <t>AUD-14</t>
+  </si>
+  <si>
+    <t>ACCT-002</t>
+  </si>
+  <si>
+    <t>Password reset</t>
+  </si>
+  <si>
+    <t>Single-use, expiring, hashed tokens; rate-limited; no account enumeration.</t>
+  </si>
+  <si>
+    <t>backend/api, frontend</t>
+  </si>
+  <si>
+    <t>ACCT-003</t>
+  </si>
+  <si>
+    <t>E-mail verification</t>
+  </si>
+  <si>
+    <t>Verification tokens and state.</t>
+  </si>
+  <si>
+    <t>ACCT-004</t>
+  </si>
+  <si>
+    <t>Password change</t>
+  </si>
+  <si>
+    <t>Current password required; other sessions revoked.</t>
+  </si>
+  <si>
+    <t>ACCT-005</t>
+  </si>
+  <si>
+    <t>Account deletion</t>
+  </si>
+  <si>
+    <t>Cascading policy: documents, versions, assets, exports, sessions, jobs, usage.</t>
+  </si>
+  <si>
+    <t>ACCT-006</t>
+  </si>
+  <si>
+    <t>Session revocation and cleanup</t>
+  </si>
+  <si>
+    <t>Sign out everywhere; expired/revoked session sweep.</t>
+  </si>
+  <si>
+    <t>ACCT-007</t>
+  </si>
+  <si>
+    <t>Suspicious login handling</t>
+  </si>
+  <si>
+    <t>Lockout and notification strategy.</t>
+  </si>
+  <si>
+    <t>PLAN-001</t>
+  </si>
+  <si>
+    <t>Usage units</t>
+  </si>
+  <si>
+    <t>Documents, exports, PDF pages, OCR pages, translation characters, AI operations, storage, batch jobs.</t>
+  </si>
+  <si>
+    <t>backend/billing</t>
+  </si>
+  <si>
+    <t>AUD-11</t>
+  </si>
+  <si>
+    <t>PLAN-002</t>
+  </si>
+  <si>
+    <t>Configurable plan defaults</t>
+  </si>
+  <si>
+    <t>Free/Pro/Business initial hypotheses as configuration, never hardcoded.</t>
+  </si>
+  <si>
+    <t>PLAN-003</t>
+  </si>
+  <si>
+    <t>Atomic entitlement checks</t>
+  </si>
+  <si>
+    <t>Reservation/locking; concurrency test proves limits hold.</t>
+  </si>
+  <si>
+    <t>PLAN-004</t>
+  </si>
+  <si>
+    <t>Stripe flows review</t>
+  </si>
+  <si>
+    <t>Checkout, portal, upgrade, downgrade, cancel, renewal, failed payment, webhook idempotency.</t>
+  </si>
+  <si>
+    <t>PLAN-005</t>
+  </si>
+  <si>
+    <t>Storage metering including history</t>
+  </si>
+  <si>
+    <t>History and autosave growth counted.</t>
+  </si>
+  <si>
+    <t>AUD-11,AUD-16</t>
+  </si>
+  <si>
+    <t>PDF-010</t>
+  </si>
+  <si>
+    <t>Geometry-aware PDF parser</t>
+  </si>
+  <si>
+    <t>Chars, fonts, sizes, colours, lines, rectangles, images, links, annotations, outlines, forms, metadata, rotation, page boxes.</t>
+  </si>
+  <si>
+    <t>backend/parsers/pdf</t>
+  </si>
+  <si>
+    <t>PDF-011</t>
+  </si>
+  <si>
+    <t>Page classifier</t>
+  </si>
+  <si>
+    <t>TEXT / SCANNED / HYBRID per page with evidence.</t>
+  </si>
+  <si>
+    <t>PDF-012</t>
+  </si>
+  <si>
+    <t>PDF inspection report</t>
+  </si>
+  <si>
+    <t>What the parser found, per page.</t>
+  </si>
+  <si>
+    <t>P2E-001</t>
+  </si>
+  <si>
+    <t>Layout primitives where PDF needs them</t>
+  </si>
+  <si>
+    <t>Page, block, bbox, rotation, confidence, provenance.</t>
+  </si>
+  <si>
+    <t>P2E-002</t>
+  </si>
+  <si>
+    <t>Structure reconstruction</t>
+  </si>
+  <si>
+    <t>Reading order, lines, paragraphs, headings, lists, captions, header/footer bands, columns.</t>
+  </si>
+  <si>
+    <t>backend/pdf</t>
+  </si>
+  <si>
+    <t>P2E-003</t>
+  </si>
+  <si>
+    <t>Images with position</t>
+  </si>
+  <si>
+    <t>Extracted images kept with bbox.</t>
+  </si>
+  <si>
+    <t>P2E-004</t>
+  </si>
+  <si>
+    <t>Tables from PDF</t>
+  </si>
+  <si>
+    <t>Ruling lines and alignment.</t>
+  </si>
+  <si>
+    <t>P2E-005</t>
+  </si>
+  <si>
+    <t>Confidence and conversion report</t>
+  </si>
+  <si>
+    <t>Per element confidence; issues reported; never silent removal.</t>
+  </si>
+  <si>
+    <t>P2E-006</t>
+  </si>
+  <si>
+    <t>OCR provider abstraction</t>
+  </si>
+  <si>
+    <t>Interface (text, confidence, bbox, page, language/script); implementation(s); OCR output untrusted.</t>
+  </si>
+  <si>
+    <t>backend/ocr</t>
+  </si>
+  <si>
+    <t>P2E-007</t>
+  </si>
+  <si>
+    <t>Imported-from-PDF version and UX</t>
+  </si>
+  <si>
+    <t>Editable document vs layout-focused choice; confidence shown.</t>
+  </si>
+  <si>
+    <t>frontend, backend</t>
+  </si>
+  <si>
+    <t>P2E-008</t>
+  </si>
+  <si>
+    <t>PDF fixtures and tests</t>
+  </si>
+  <si>
+    <t>Text, scanned, hybrid, tables, columns, multilingual.</t>
+  </si>
+  <si>
+    <t>P2E-020</t>
+  </si>
+  <si>
+    <t>Layout-preserving architecture</t>
+  </si>
+  <si>
+    <t>Frames/anchors model hooks and design doc.</t>
+  </si>
+  <si>
+    <t>docs, backend/models</t>
+  </si>
+  <si>
+    <t>PDF-020</t>
+  </si>
+  <si>
+    <t>PDF page operations service</t>
+  </si>
+  <si>
+    <t>Reorder, rotate, delete, duplicate, extract, split, merge as a separate service.</t>
+  </si>
+  <si>
+    <t>TRAN-001</t>
+  </si>
+  <si>
+    <t>Segments and tag protocol</t>
+  </si>
+  <si>
+    <t>Segments keep element/run ids, marks, placeholders; never one giant string.</t>
+  </si>
+  <si>
+    <t>backend/translation</t>
+  </si>
+  <si>
+    <t>TRAN-002</t>
+  </si>
+  <si>
+    <t>TranslationProvider abstraction</t>
+  </si>
+  <si>
+    <t>AI provider implementation + deterministic test provider.</t>
+  </si>
+  <si>
+    <t>TRAN-003</t>
+  </si>
+  <si>
+    <t>Translation validation</t>
+  </si>
+  <si>
+    <t>Tags, numbers, units, dates, percentages, identifiers, glossary terms.</t>
+  </si>
+  <si>
+    <t>TRAN-004</t>
+  </si>
+  <si>
+    <t>Glossary and terminology lock</t>
+  </si>
+  <si>
+    <t>Source/target term, domain, locked, case-sensitive.</t>
+  </si>
+  <si>
+    <t>backend/translation, db</t>
+  </si>
+  <si>
+    <t>TRAN-005</t>
+  </si>
+  <si>
+    <t>Selection/paragraph/block translation proposals</t>
+  </si>
+  <si>
+    <t>Preview; accept/reject; undo.</t>
+  </si>
+  <si>
+    <t>TRAN-003,REV-001</t>
+  </si>
+  <si>
+    <t>TRAN-006</t>
+  </si>
+  <si>
+    <t>Whole-document translated version</t>
+  </si>
+  <si>
+    <t>Source kept; translated copy linked.</t>
+  </si>
+  <si>
+    <t>TRAN-007</t>
+  </si>
+  <si>
+    <t>Language, script, direction metadata</t>
+  </si>
+  <si>
+    <t>Auto-detect + manual override.</t>
+  </si>
+  <si>
+    <t>TRAN-008</t>
+  </si>
+  <si>
+    <t>Translation UX</t>
+  </si>
+  <si>
+    <t>Toolbar/context Translate, target language, preview, accept/reject; 'AI-assisted translation - review required'.</t>
+  </si>
+  <si>
+    <t>TRAN-009</t>
+  </si>
+  <si>
+    <t>Translation metering</t>
+  </si>
+  <si>
+    <t>Translation characters as a usage unit.</t>
+  </si>
+  <si>
+    <t>TRAN-010</t>
+  </si>
+  <si>
+    <t>Translation tests</t>
+  </si>
+  <si>
+    <t>Formatting preservation, validation, versions.</t>
+  </si>
+  <si>
+    <t>FONT-001</t>
+  </si>
+  <si>
+    <t>Font catalogue with Unicode coverage</t>
+  </si>
+  <si>
+    <t>fontTools cmap coverage per script, metrics, embeddability.</t>
+  </si>
+  <si>
+    <t>backend/fonts</t>
+  </si>
+  <si>
+    <t>AUD-17</t>
+  </si>
+  <si>
+    <t>FONT-002</t>
+  </si>
+  <si>
+    <t>FontResolver</t>
+  </si>
+  <si>
+    <t>Script segmentation, coverage, fallback chain, embedding, RTL; deterministic first, AI suggestion validated.</t>
+  </si>
+  <si>
+    <t>FONT-003</t>
+  </si>
+  <si>
+    <t>Multilingual PDF rendering</t>
+  </si>
+  <si>
+    <t>Shaping for Arabic/Hebrew/Devanagari, bidi, CJK fonts, emoji handled gracefully.</t>
+  </si>
+  <si>
+    <t>FONT-004</t>
+  </si>
+  <si>
+    <t>DOCX per-script fonts</t>
+  </si>
+  <si>
+    <t>w:rFonts ascii/hAnsi/eastAsia/cs, w:lang, rtl/bidi.</t>
+  </si>
+  <si>
+    <t>FONT-005</t>
+  </si>
+  <si>
+    <t>Editor fallback stacks</t>
+  </si>
+  <si>
+    <t>CSS stacks from the resolver.</t>
+  </si>
+  <si>
+    <t>FONT-006</t>
+  </si>
+  <si>
+    <t>Multilingual tests</t>
+  </si>
+  <si>
+    <t>Script matrix x editor/DOCX/PDF with pdftotext and rendering.</t>
+  </si>
+  <si>
+    <t>FMT-001</t>
+  </si>
+  <si>
+    <t>Style extraction completeness</t>
+  </si>
+  <si>
+    <t>Page setup, margins, fonts, headings, lists, tables, captions, headers/footers, spacing, numbering, colours.</t>
+  </si>
+  <si>
+    <t>FMT-002</t>
+  </si>
+  <si>
+    <t>Semantic mapping validated</t>
+  </si>
+  <si>
+    <t>AI classifies/maps, engine applies; validation.</t>
+  </si>
+  <si>
+    <t>FMT-003</t>
+  </si>
+  <si>
+    <t>Before/after for Format by Example</t>
+  </si>
+  <si>
+    <t>Preview before saving a template.</t>
+  </si>
+  <si>
+    <t>FMT-005</t>
+  </si>
+  <si>
+    <t>Rule value validation</t>
+  </si>
+  <si>
+    <t>Instruction-path values validated before reaching CSS/export.</t>
+  </si>
+  <si>
+    <t>Instruction rules and set_style operations go through values.clean_rule_value: invalid ones dropped, normalised values stored (see SEC-022).</t>
+  </si>
+  <si>
+    <t>tests/test_rule_values.py::test_instructions_cannot_carry_such_values</t>
+  </si>
+  <si>
+    <t>HLTH-001</t>
+  </si>
+  <si>
+    <t>Health 2.0 checks</t>
+  </si>
+  <si>
+    <t>Alt text, hidden text, mixed language, unsupported features, section inconsistency, broken lists, empty paragraphs, layout anomalies, duplicated formatting, broken links.</t>
+  </si>
+  <si>
+    <t>HLTH-002</t>
+  </si>
+  <si>
+    <t>Deterministic fixes with preview</t>
+  </si>
+  <si>
+    <t>Fix proposals through the change model.</t>
+  </si>
+  <si>
+    <t>HLTH-003</t>
+  </si>
+  <si>
+    <t>AI explanations only</t>
+  </si>
+  <si>
+    <t>AI explains issues; never scores.</t>
+  </si>
+  <si>
+    <t>REV-002</t>
+  </si>
+  <si>
+    <t>Review Changes UI</t>
+  </si>
+  <si>
+    <t>Categories FORMAT/STRUCTURE/CONTENT/METADATA/PRESERVATION/TRANSLATION.</t>
+  </si>
+  <si>
+    <t>REV-003</t>
+  </si>
+  <si>
+    <t>Content changes need acceptance</t>
+  </si>
+  <si>
+    <t>Enforced server-side.</t>
+  </si>
+  <si>
+    <t>backend</t>
+  </si>
+  <si>
+    <t>REV-004</t>
+  </si>
+  <si>
+    <t>Repair</t>
+  </si>
+  <si>
+    <t>Detected issue, proposed fix, preview, apply.</t>
+  </si>
+  <si>
+    <t>REV-005</t>
+  </si>
+  <si>
+    <t>Clean copy</t>
+  </si>
+  <si>
+    <t>Explicit: remove comments, accept tracked changes, remove hidden text, remove metadata, normalise formatting.</t>
+  </si>
+  <si>
+    <t>FEAT-001</t>
+  </si>
+  <si>
+    <t>Batch formatting</t>
+  </si>
+  <si>
+    <t>One template/reference over many documents as jobs.</t>
+  </si>
+  <si>
+    <t>backend/jobs</t>
+  </si>
+  <si>
+    <t>FEAT-002</t>
+  </si>
+  <si>
+    <t>Batch export</t>
+  </si>
+  <si>
+    <t>Many documents to a zip.</t>
+  </si>
+  <si>
+    <t>FEAT-003</t>
+  </si>
+  <si>
+    <t>Batch translation</t>
+  </si>
+  <si>
+    <t>After the translation MVP.</t>
+  </si>
+  <si>
+    <t>FEAT-010</t>
+  </si>
+  <si>
+    <t>Accessibility checker</t>
+  </si>
+  <si>
+    <t>Heading hierarchy, alt text, link labels, table headers, reading order, language, contrast.</t>
+  </si>
+  <si>
+    <t>FEAT-011</t>
+  </si>
+  <si>
+    <t>App accessibility fixes</t>
+  </si>
+  <si>
+    <t>Zero serious axe violations on main pages and the editor.</t>
+  </si>
+  <si>
+    <t>JOB-001</t>
+  </si>
+  <si>
+    <t>Job safety</t>
+  </si>
+  <si>
+    <t>idempotency_key, retry_count, timeout, cancellation, stuck detection, backoff, dead-letter.</t>
+  </si>
+  <si>
+    <t>STOR-001</t>
+  </si>
+  <si>
+    <t>Storage retention and deletion</t>
+  </si>
+  <si>
+    <t>Source files, exports, OCR artifacts: retention, deletion, access control, content types, size limits.</t>
+  </si>
+  <si>
+    <t>OBS-001</t>
+  </si>
+  <si>
+    <t>Metrics</t>
+  </si>
+  <si>
+    <t>Latency, failure rate, job/AI/export metrics without content.</t>
+  </si>
+  <si>
+    <t>AUD-15</t>
+  </si>
+  <si>
+    <t>OBS-002</t>
+  </si>
+  <si>
+    <t>Operation and job IDs in logs</t>
+  </si>
+  <si>
+    <t>Request, operation and job IDs everywhere.</t>
+  </si>
+  <si>
+    <t>OBS-003</t>
+  </si>
+  <si>
+    <t>Operations data</t>
+  </si>
+  <si>
+    <t>Failed jobs, processing failures, usage spikes, AI/export failures, storage, abuse - minimal admin API.</t>
+  </si>
+  <si>
+    <t>INFRA-010</t>
+  </si>
+  <si>
+    <t>Deployment verified</t>
+  </si>
+  <si>
+    <t>Docker images build and start; Postgres, Redis, storage, worker, frontend, backend.</t>
+  </si>
+  <si>
+    <t>docker, CI</t>
+  </si>
+  <si>
+    <t>INFRA-011</t>
+  </si>
+  <si>
+    <t>CI gates</t>
+  </si>
+  <si>
+    <t>Backend, frontend, E2E, lint, typecheck, build, migrations, security audit, document fidelity tests.</t>
+  </si>
+  <si>
+    <t>.github/workflows</t>
+  </si>
+  <si>
+    <t>AUD-15,AUD-20</t>
+  </si>
+  <si>
+    <t>TEST-040</t>
+  </si>
+  <si>
+    <t>Playwright workflow coverage</t>
+  </si>
+  <si>
+    <t>The 24 workflows of the brief.</t>
+  </si>
+  <si>
+    <t>TEST-041</t>
+  </si>
+  <si>
+    <t>Performance gates</t>
+  </si>
+  <si>
+    <t>Regression thresholds relative to baseline.</t>
+  </si>
+  <si>
+    <t>TEST-043</t>
+  </si>
+  <si>
+    <t>Browser matrix</t>
+  </si>
+  <si>
+    <t>Chromium, Firefox, WebKit.</t>
+  </si>
+  <si>
+    <t>TEST-006</t>
+  </si>
+  <si>
+    <t>E2E backend removes its temp directory</t>
+  </si>
+  <si>
+    <t>scripts/e2e_server.py leaves %TEMP%/smartdoc-e2e-* behind after every Playwright run (10 found on 2026-09-27).</t>
+  </si>
+  <si>
+    <t>backend/scripts/e2e_server.py</t>
+  </si>
+  <si>
+    <t>DOCS-010</t>
+  </si>
+  <si>
+    <t>final-production-readiness.md</t>
+  </si>
+  <si>
+    <t>The 16-section final report.</t>
+  </si>
+  <si>
+    <t>DOCS-011</t>
+  </si>
+  <si>
+    <t>Documentation tree</t>
+  </si>
+  <si>
+    <t>docs/{architecture,document-model,docx,pdf,translation,ai,formatting,security,testing,deployment,billing,operations}.</t>
+  </si>
+  <si>
+    <t>Started with Phase 1: docs/document-model, docs/architecture/fidelity.md, docs/docx, docs/formatting, docs/security, docs/testing (each grounded in the code and tests of Phases 0-1). Remaining folders (pdf, translation, ai, deployment, billing, operations) as their phases land.; docs/ai/README.md added with Phase 2.</t>
+  </si>
+  <si>
+    <t>CRITICAL_FIXES — Audit findings and P0 tasks</t>
+  </si>
+  <si>
+    <t>The 20 findings of the 2026-09-26 audit (current known risks) with fix progress, then every P0 task. Report: https://claude.ai/artifact/WKskiyexTDLAHe1BfjvWR1 — a finding is RESOLVED when every linked fix task is DONE.</t>
+  </si>
+  <si>
+    <t>Findings</t>
+  </si>
+  <si>
+    <t>Resolved</t>
+  </si>
+  <si>
+    <t>Open</t>
+  </si>
+  <si>
+    <t>P0 tasks</t>
+  </si>
+  <si>
+    <t>P0 done</t>
+  </si>
+  <si>
+    <t>Audit findings (current known risks)</t>
+  </si>
+  <si>
+    <t>Finding ID</t>
+  </si>
+  <si>
+    <t>Progress</t>
+  </si>
+  <si>
+    <t>Finding</t>
+  </si>
+  <si>
+    <t>Fix Tasks</t>
+  </si>
+  <si>
+    <t>Active</t>
+  </si>
+  <si>
+    <t>Blocked/Failed</t>
+  </si>
+  <si>
+    <t>Editor save can discard nested blocks (lists, pictures, code, quotes inside cells/items)</t>
+  </si>
+  <si>
+    <t>EDIT-001,EDIT-002,EDIT-003,EDIT-005,EDIT-006</t>
+  </si>
+  <si>
+    <t>AI fidelity check misses omissions, negation removal, number changes, inserted text</t>
+  </si>
+  <si>
+    <t>AI-001,AI-002,AI-003,AI-004</t>
+  </si>
+  <si>
+    <t>Fixed in Phase 2 (AI-001..004): AI structure answers are checked token by token; any omission, negation removal, number/unit/date change, insertion, reordering, duplication or punctuation change is refused.</t>
+  </si>
+  <si>
+    <t>Import/export silently changes hidden text, numbering, section headers, metadata, alt text, structure</t>
+  </si>
+  <si>
+    <t>FID-002,DOCX-011,DOCX-013,DOCX-015,DOCX-025</t>
+  </si>
+  <si>
+    <t>List numbering changes ('Чл. 1.' -&gt; '1.', '(a)' -&gt; 'a.', start values)</t>
+  </si>
+  <si>
+    <t>Partly fixed in 622d9c1: list format/start/continuation kept; custom labels ('Чл. 1.', '(a)') and multi-level labels reported, not kept yet (DOCX-016).</t>
+  </si>
+  <si>
+    <t>AI instruction operations can delete/insert/move content without preview</t>
+  </si>
+  <si>
+    <t>AI-005,AI-006,AI-007,REV-003</t>
+  </si>
+  <si>
+    <t>Fixed in Phase 2 (AI-005..AI-007): an instruction's insert/delete/move is a proposal the user sees and accepts or rejects; nothing is deleted silently.</t>
+  </si>
+  <si>
+    <t>Content controls, metadata, comment threads, sensitivity information lost</t>
+  </si>
+  <si>
+    <t>DOCX-012,DOCX-021,DOCX-023</t>
+  </si>
+  <si>
+    <t>Image fidelity gaps: alt text, crop, rotation, formats</t>
+  </si>
+  <si>
+    <t>Table export changes header state, borders, alignment, widths, geometry</t>
+  </si>
+  <si>
+    <t>Large images cause huge memory consumption</t>
+  </si>
+  <si>
+    <t>SEC-012,SEC-013</t>
+  </si>
+  <si>
+    <t>Large tables have a performance problem</t>
+  </si>
+  <si>
+    <t>Plan limits have a concurrency race</t>
+  </si>
+  <si>
+    <t>Malformed DOCX leads to HTTP 500</t>
+  </si>
+  <si>
+    <t>SEC-010,SEC-019</t>
+  </si>
+  <si>
+    <t>Dangerous href/field instructions must be filtered</t>
+  </si>
+  <si>
+    <t>SEC-014,SEC-015,SEC-016</t>
+  </si>
+  <si>
+    <t>Account essentials missing: reset, verification, change, deletion</t>
+  </si>
+  <si>
+    <t>ACCT-002,ACCT-003,ACCT-004,ACCT-005</t>
+  </si>
+  <si>
+    <t>Operations/monitoring must be confirmed</t>
+  </si>
+  <si>
+    <t>OBS-001,OBS-002,INFRA-010</t>
+  </si>
+  <si>
+    <t>Whole-document autosave must be optimised</t>
+  </si>
+  <si>
+    <t>PERF-003,PERF-004</t>
+  </si>
+  <si>
+    <t>PDF multilingual rendering must be reliable</t>
+  </si>
+  <si>
+    <t>FONT-003,FONT-006</t>
+  </si>
+  <si>
+    <t>Export metadata must be correct</t>
+  </si>
+  <si>
+    <t>DOCX-012,DOCX-020</t>
+  </si>
+  <si>
+    <t>Partly fixed in 622d9c1: Word exports carry the source file's core properties (author, dates, subject...) instead of 'python-docx'/2013; fields remain (DOCX-020).</t>
+  </si>
+  <si>
+    <t>AUD-19</t>
+  </si>
+  <si>
+    <t>Canonical model must represent more than paragraphs + runs + simple tables</t>
+  </si>
+  <si>
+    <t>CORE-001,DOCX-015,DOCX-016,DOCX-017</t>
+  </si>
+  <si>
+    <t>Tests can miss import-side data loss (model-relative comparison)</t>
+  </si>
+  <si>
+    <t>TEST-020,TEST-021,TEST-022</t>
+  </si>
+  <si>
+    <t>P0 tasks (live from MASTER)</t>
+  </si>
+  <si>
+    <t>DOCUMENT_FIDELITY — Content preservation</t>
+  </si>
+  <si>
+    <t>Canonical model, fidelity reports, capability matrix, change/review model. Categories: CORE, FIDELITY, REVIEW. Rows are formulas over MASTER — change task data in MASTER or with tools/tracker/tracker.py.</t>
+  </si>
+  <si>
+    <t>Tasks (live from MASTER)</t>
+  </si>
+  <si>
+    <t>DOCX_OOXML — DOCX / OOXML preservation</t>
+  </si>
+  <si>
+    <t>Import and export fidelity for Word documents. Categories: DOCX. Rows are formulas over MASTER — change task data in MASTER or with tools/tracker/tracker.py.</t>
+  </si>
+  <si>
+    <t>PDF — PDF engine</t>
+  </si>
+  <si>
+    <t>PDF export and PDF parsing. Categories: PDF. Rows are formulas over MASTER — change task data in MASTER or with tools/tracker/tracker.py.</t>
+  </si>
+  <si>
+    <t>EDITOR — Editor integrity</t>
+  </si>
+  <si>
+    <t>Tiptap mapping and save integrity. Categories: EDITOR. Rows are formulas over MASTER — change task data in MASTER or with tools/tracker/tracker.py.</t>
+  </si>
+  <si>
+    <t>FORMATTING — Formatting and Document Health</t>
+  </si>
+  <si>
+    <t>Formatting engine, Format by Example, Document Health. Categories: FORMATTING, HEALTH. Rows are formulas over MASTER — change task data in MASTER or with tools/tracker/tracker.py.</t>
+  </si>
+  <si>
+    <t>AI — AI fidelity</t>
+  </si>
+  <si>
+    <t>Fidelity checks, proposals and review, budgets. Categories: AI. Rows are formulas over MASTER — change task data in MASTER or with tools/tracker/tracker.py.</t>
+  </si>
+  <si>
+    <t>SECURITY — Security and accounts</t>
+  </si>
+  <si>
+    <t>Security hardening and account essentials. Categories: SECURITY, ACCOUNT. Rows are formulas over MASTER — change task data in MASTER or with tools/tracker/tracker.py.</t>
+  </si>
+  <si>
+    <t>PERFORMANCE — Performance</t>
+  </si>
+  <si>
+    <t>Measured results — brief §80-81: measure, then set regression thresholds relative to the baseline (no invented SLOs)</t>
+  </si>
+  <si>
+    <t>Bench ID</t>
+  </si>
+  <si>
+    <t>Metric</t>
+  </si>
+  <si>
+    <t>Unit</t>
+  </si>
+  <si>
+    <t>Scenario</t>
+  </si>
+  <si>
+    <t>Baseline</t>
+  </si>
+  <si>
+    <t>Baseline Source</t>
+  </si>
+  <si>
+    <t>Current</t>
+  </si>
+  <si>
+    <t>Measured On</t>
+  </si>
+  <si>
+    <t>Threshold</t>
+  </si>
+  <si>
+    <t>BENCH-001</t>
+  </si>
+  <si>
+    <t>duration</t>
+  </si>
+  <si>
+    <t>s</t>
+  </si>
+  <si>
+    <t>DOCX export: table 500x8 (4,000 cells)</t>
+  </si>
+  <si>
+    <t>audit perf_table.py (400 cells 3.8 s; 1,600 cells 53.7 s; quadratic)</t>
+  </si>
+  <si>
+    <t>BENCH-002</t>
+  </si>
+  <si>
+    <t>PDF export: table 500x8</t>
+  </si>
+  <si>
+    <t>audit perf_table.py (linear)</t>
+  </si>
+  <si>
+    <t>BENCH-003</t>
+  </si>
+  <si>
+    <t>Import: 300-page text DOCX (1,650 elements)</t>
+  </si>
+  <si>
+    <t>audit perf_backend.py</t>
+  </si>
+  <si>
+    <t>BENCH-004</t>
+  </si>
+  <si>
+    <t>DOCX export: 300-page text document</t>
+  </si>
+  <si>
+    <t>BENCH-005</t>
+  </si>
+  <si>
+    <t>PDF export: 300-page text document</t>
+  </si>
+  <si>
+    <t>BENCH-006</t>
+  </si>
+  <si>
+    <t>memory growth</t>
+  </si>
+  <si>
+    <t>MB</t>
+  </si>
+  <si>
+    <t>PDF export: 39 KB DOCX holding a 12000x12000 PNG</t>
+  </si>
+  <si>
+    <t>audit pixel_bomb.py (14000x14000 crashes the export)</t>
+  </si>
+  <si>
+    <t>BENCH-007</t>
+  </si>
+  <si>
+    <t>PDF export: 4 JPEG images 2400x1800</t>
+  </si>
+  <si>
+    <t>audit perf_backend.py (6.3 s)</t>
+  </si>
+  <si>
+    <t>BENCH-008</t>
+  </si>
+  <si>
+    <t>Editor: type 20 characters at 12,196 elements (1M-character paste)</t>
+  </si>
+  <si>
+    <t>audit perf_browser.js (~470 ms per key)</t>
+  </si>
+  <si>
+    <t>BENCH-009</t>
+  </si>
+  <si>
+    <t>Editor: type 20 characters, 300-page document</t>
+  </si>
+  <si>
+    <t>audit perf_browser.js</t>
+  </si>
+  <si>
+    <t>BENCH-010</t>
+  </si>
+  <si>
+    <t>request size</t>
+  </si>
+  <si>
+    <t>Autosave request: 300-page document</t>
+  </si>
+  <si>
+    <t>audit perf_browser.js (whole elements list per save)</t>
+  </si>
+  <si>
+    <t>BENCH-011</t>
+  </si>
+  <si>
+    <t>Autosave request: 1M-character paste</t>
+  </si>
+  <si>
+    <t>BENCH-012</t>
+  </si>
+  <si>
+    <t>storage</t>
+  </si>
+  <si>
+    <t>Stored history: one 300-page document, 50 steps</t>
+  </si>
+  <si>
+    <t>audit (2.8 MB per full copy; 7.2 MB when the JSON is ASCII-escaped)</t>
+  </si>
+  <si>
+    <t>BENCH-013</t>
+  </si>
+  <si>
+    <t>Paste: 2M characters (the cap)</t>
+  </si>
+  <si>
+    <t>audit perf_backend.py (17.5k elements, 7.1 MB JSON)</t>
+  </si>
+  <si>
+    <t>Performance tasks (live from MASTER)</t>
+  </si>
+  <si>
+    <t>TESTING — Testing</t>
+  </si>
+  <si>
+    <t>Test runs (oldest first)</t>
+  </si>
+  <si>
+    <t>Run ID</t>
+  </si>
+  <si>
+    <t>Command</t>
+  </si>
+  <si>
+    <t>Passed</t>
+  </si>
+  <si>
+    <t>Skipped</t>
+  </si>
+  <si>
+    <t>Date</t>
+  </si>
+  <si>
+    <t>Duration (s)</t>
+  </si>
+  <si>
+    <t>RUN-0001</t>
+  </si>
+  <si>
+    <t>backend-pytest</t>
+  </si>
+  <si>
+    <t>PASS</t>
+  </si>
+  <si>
+    <t>cd backend &amp;&amp; venv/Scripts/python -m pytest -q -p no:cacheprovider</t>
+  </si>
+  <si>
+    <t>Skip: optional real-Word check (SMARTDOC_REAL_DOCX unset). 1 DeprecationWarning (starlette/anyio). Audit measured 93% line coverage on 2026-09-26.</t>
+  </si>
+  <si>
+    <t>ea69829</t>
+  </si>
+  <si>
+    <t>RUN-0002</t>
+  </si>
+  <si>
+    <t>frontend-lint</t>
+  </si>
+  <si>
+    <t>cd frontend &amp;&amp; npm run lint</t>
+  </si>
+  <si>
+    <t>eslint: 0 problems</t>
+  </si>
+  <si>
+    <t>RUN-0003</t>
+  </si>
+  <si>
+    <t>frontend-tsc</t>
+  </si>
+  <si>
+    <t>cd frontend &amp;&amp; npx tsc --noEmit</t>
+  </si>
+  <si>
+    <t>0 type errors</t>
+  </si>
+  <si>
+    <t>RUN-0004</t>
+  </si>
+  <si>
+    <t>frontend-vitest</t>
+  </si>
+  <si>
+    <t>cd frontend &amp;&amp; npm test</t>
+  </si>
+  <si>
+    <t>6 test files</t>
+  </si>
+  <si>
+    <t>RUN-0005</t>
+  </si>
+  <si>
+    <t>frontend-build</t>
+  </si>
+  <si>
+    <t>cd frontend &amp;&amp; npm run build</t>
+  </si>
+  <si>
+    <t>Next.js production build, 11 routes</t>
+  </si>
+  <si>
+    <t>RUN-0006</t>
+  </si>
+  <si>
+    <t>e2e-playwright</t>
+  </si>
+  <si>
+    <t>cd frontend &amp;&amp; npm run test:e2e</t>
+  </si>
+  <si>
+    <t>Edge; throwaway backend on SQLite (:8100) + production build (:3100). 16 workflows in 5 spec files; the brief asks for 24 (TEST-040). Leaves %TEMP%/smartdoc-e2e-* dirs behind (TEST-006).</t>
+  </si>
+  <si>
+    <t>RUN-0007</t>
+  </si>
+  <si>
+    <t>migrations</t>
+  </si>
+  <si>
+    <t>alembic upgrade head &amp;&amp; alembic check &amp;&amp; alembic downgrade base &amp;&amp; alembic upgrade head (scratch SQLite); alembic upgrade head --sql (PostgreSQL dialect)</t>
+  </si>
+  <si>
+    <t>head 85211092fe4c; 'No new upgrade operations detected'; offline SQL: 14 tables at head, RLS enabled on every table</t>
+  </si>
+  <si>
+    <t>RUN-0008</t>
+  </si>
+  <si>
+    <t>supabase</t>
+  </si>
+  <si>
+    <t>Supabase MCP: list_migrations, get_advisors security+performance, list_tables (project edmmjmsynjziahwtjuke)</t>
+  </si>
+  <si>
+    <t>8/8 migrations applied; 14 tables, RLS on all; advisors only INFO: 14x rls_enabled_no_policy (by design: the API connects as owner, PostgREST roles see nothing), 8x unused_index (low traffic)</t>
+  </si>
+  <si>
+    <t>RUN-0009</t>
+  </si>
+  <si>
+    <t>pip-audit</t>
+  </si>
+  <si>
+    <t>uvx pip-audit --disable-pip -r backend/requirements.lock; same for requirements-dev.lock</t>
+  </si>
+  <si>
+    <t>No known vulnerabilities in either lock file</t>
+  </si>
+  <si>
+    <t>RUN-0010</t>
+  </si>
+  <si>
+    <t>npm-audit</t>
+  </si>
+  <si>
+    <t>cd frontend &amp;&amp; npm audit; npm audit --omit=dev</t>
+  </si>
+  <si>
+    <t>0 vulnerabilities across 633 dependencies</t>
+  </si>
+  <si>
+    <t>RUN-0011</t>
+  </si>
+  <si>
+    <t>docker-compose</t>
+  </si>
+  <si>
+    <t>PARTIAL</t>
+  </si>
+  <si>
+    <t>docker compose config --quiet</t>
+  </si>
+  <si>
+    <t>compose file valid (8 services: postgres, redis, minio, minio-bucket, migrate, worker, backend, frontend); images NOT built: Docker daemon not running on this machine (CI builds them on main)</t>
+  </si>
+  <si>
+    <t>RUN-0012</t>
+  </si>
+  <si>
+    <t>Phase 1 editor integrity: +16 tests (nesting model, nested API/exports, health links)</t>
+  </si>
+  <si>
+    <t>RUN-0013</t>
+  </si>
+  <si>
+    <t>cd frontend &amp;&amp; npx vitest run</t>
+  </si>
+  <si>
+    <t>+31: nestedBlocks.test.ts (28), useAutoSave.test.tsx (3); tsc and eslint clean</t>
+  </si>
+  <si>
+    <t>RUN-0014</t>
+  </si>
+  <si>
+    <t>cd frontend &amp;&amp; npx playwright test</t>
+  </si>
+  <si>
+    <t>+1: e2e/nested.spec.ts (paste, autosave, reload)</t>
+  </si>
+  <si>
+    <t>RUN-0015</t>
+  </si>
+  <si>
+    <t>+29 test_fidelity_report.py</t>
+  </si>
+  <si>
+    <t>RUN-0016</t>
+  </si>
+  <si>
+    <t>+3 FidelityPanel.test.tsx</t>
+  </si>
+  <si>
+    <t>RUN-0017</t>
+  </si>
+  <si>
+    <t>+fidelity.spec.ts; nested.spec.ts made deterministic (focus check, Ctrl+End) after one run pasted at the document start</t>
+  </si>
+  <si>
+    <t>RUN-0018</t>
+  </si>
+  <si>
+    <t>+6 test_export_fidelity.py</t>
+  </si>
+  <si>
+    <t>RUN-0019</t>
+  </si>
+  <si>
+    <t>+4 ExportResult.test.tsx</t>
+  </si>
+  <si>
+    <t>RUN-0020</t>
+  </si>
+  <si>
+    <t>export test checks the export's content message</t>
+  </si>
+  <si>
+    <t>RUN-0021</t>
+  </si>
+  <si>
+    <t>+6 test_capabilities.py</t>
+  </si>
+  <si>
+    <t>RUN-0022</t>
+  </si>
+  <si>
+    <t>venv/Scripts/python -m pytest -q</t>
+  </si>
+  <si>
+    <t>after FID-002 detections + section break fix</t>
+  </si>
+  <si>
+    <t>RUN-0023</t>
+  </si>
+  <si>
+    <t>npx vitest run</t>
+  </si>
+  <si>
+    <t>tsc --noEmit and eslint clean too</t>
+  </si>
+  <si>
+    <t>RUN-0024</t>
+  </si>
+  <si>
+    <t>rule values (SEC-022) + editor direct styles</t>
+  </si>
+  <si>
+    <t>RUN-0025</t>
+  </si>
+  <si>
+    <t>tsc + eslint clean</t>
+  </si>
+  <si>
+    <t>RUN-0026</t>
+  </si>
+  <si>
+    <t>e2e</t>
+  </si>
+  <si>
+    <t>npx playwright test</t>
+  </si>
+  <si>
+    <t>incl. e2e/direct-formatting.spec.ts</t>
+  </si>
+  <si>
+    <t>RUN-0027</t>
+  </si>
+  <si>
+    <t>Phase 1 gate: link titles, mark order, Markdown pictures/rules</t>
+  </si>
+  <si>
+    <t>RUN-0028</t>
+  </si>
+  <si>
+    <t>Phase 1 gate; tsc + eslint clean</t>
+  </si>
+  <si>
+    <t>RUN-0029</t>
+  </si>
+  <si>
+    <t>Phase 1 gate</t>
+  </si>
+  <si>
+    <t>RUN-0030</t>
+  </si>
+  <si>
+    <t>AI fidelity check (AI-001..004)</t>
+  </si>
+  <si>
+    <t>RUN-0031</t>
+  </si>
+  <si>
+    <t>AI proposals</t>
+  </si>
+  <si>
+    <t>RUN-0032</t>
+  </si>
+  <si>
+    <t>RUN-0033</t>
+  </si>
+  <si>
+    <t>incl. e2e/proposals.spec.ts</t>
+  </si>
+  <si>
+    <t>RUN-0034</t>
+  </si>
+  <si>
+    <t>AI budget</t>
+  </si>
+  <si>
+    <t>RUN-0035</t>
+  </si>
+  <si>
+    <t>prompt-injection review</t>
+  </si>
+  <si>
+    <t>RUN-0036</t>
+  </si>
+  <si>
+    <t>Phase 2 gate</t>
+  </si>
+  <si>
+    <t>RUN-0037</t>
+  </si>
+  <si>
+    <t>RUN-0038</t>
+  </si>
+  <si>
+    <t>source package + patch writer</t>
+  </si>
+  <si>
+    <t>RUN-0039</t>
+  </si>
+  <si>
+    <t>after the patch writer</t>
+  </si>
+  <si>
+    <t>RUN-0040</t>
+  </si>
+  <si>
+    <t>backend pytest</t>
+  </si>
+  <si>
+    <t>DOCX-028: test_original_blocks.py (26), golden set of 13</t>
+  </si>
+  <si>
+    <t>7f22bf9</t>
+  </si>
+  <si>
+    <t>RUN-0041</t>
+  </si>
+  <si>
+    <t>frontend vitest</t>
+  </si>
+  <si>
+    <t>editor round trip includes 13-kept-blocks</t>
+  </si>
+  <si>
+    <t>RUN-0042</t>
+  </si>
+  <si>
+    <t>playwright</t>
+  </si>
+  <si>
+    <t>new e2e/kept-blocks.spec.ts</t>
+  </si>
+  <si>
+    <t>RUN-0043</t>
+  </si>
+  <si>
+    <t>tsc + eslint</t>
+  </si>
+  <si>
+    <t>cd frontend &amp;&amp; npx tsc --noEmit &amp;&amp; npx eslint .</t>
+  </si>
+  <si>
+    <t>0 type errors, 0 lint problems</t>
+  </si>
+  <si>
+    <t>RUN-0044</t>
+  </si>
+  <si>
+    <t>DOCX-025: tests/test_hidden_text.py (7)</t>
+  </si>
+  <si>
+    <t>fada4d7</t>
+  </si>
+  <si>
+    <t>RUN-0045</t>
+  </si>
+  <si>
+    <t>editor/hiddenText.test.tsx (6)</t>
+  </si>
+  <si>
+    <t>RUN-0046</t>
+  </si>
+  <si>
+    <t>new e2e/hidden-text.spec.ts</t>
+  </si>
+  <si>
+    <t>RUN-0047</t>
+  </si>
+  <si>
+    <t>RUN-0048</t>
+  </si>
+  <si>
+    <t>DOCX-013 part 1: tests/test_character_formatting.py (12)</t>
+  </si>
+  <si>
+    <t>c51b1bf</t>
+  </si>
+  <si>
+    <t>RUN-0049</t>
+  </si>
+  <si>
+    <t>editor/characterFormatting.test.ts (3)</t>
+  </si>
+  <si>
+    <t>RUN-0050</t>
+  </si>
+  <si>
+    <t>after DOCX-013 part 1</t>
+  </si>
+  <si>
+    <t>RUN-0051</t>
+  </si>
+  <si>
+    <t>RUN-0052</t>
+  </si>
+  <si>
+    <t>DOCX-013 part 2 + FID-007: tests/test_copy_reports.py (6)</t>
+  </si>
+  <si>
+    <t>309f9d6</t>
+  </si>
+  <si>
+    <t>RUN-0053</t>
+  </si>
+  <si>
+    <t>characterFormatting.test.ts (4)</t>
+  </si>
+  <si>
+    <t>RUN-0054</t>
+  </si>
+  <si>
+    <t>after DOCX-013 part 2</t>
+  </si>
+  <si>
+    <t>RUN-0055</t>
+  </si>
+  <si>
+    <t>Testing tasks (live from MASTER)</t>
+  </si>
+  <si>
+    <t>PRODUCT_FEATURES — Product features</t>
+  </si>
+  <si>
+    <t>Feature backlog — brief §61-62</t>
+  </si>
+  <si>
+    <t>Feature</t>
+  </si>
+  <si>
+    <t>Bucket</t>
+  </si>
+  <si>
+    <t>Linked Tasks</t>
+  </si>
+  <si>
+    <t>Linked Done</t>
+  </si>
+  <si>
+    <t>Linked Total</t>
+  </si>
+  <si>
+    <t>Document integrity</t>
+  </si>
+  <si>
+    <t>NOW</t>
+  </si>
+  <si>
+    <t>EDIT-001,EDIT-005,FID-002</t>
+  </si>
+  <si>
+    <t>Brief 62: NOW #1</t>
+  </si>
+  <si>
+    <t>Fidelity</t>
+  </si>
+  <si>
+    <t>DOCX-011,TEST-022</t>
+  </si>
+  <si>
+    <t>Brief 62: NOW #2</t>
+  </si>
+  <si>
+    <t>Security</t>
+  </si>
+  <si>
+    <t>SEC-010,SEC-012,SEC-014</t>
+  </si>
+  <si>
+    <t>Brief 62: NOW #3</t>
+  </si>
+  <si>
+    <t>Performance</t>
+  </si>
+  <si>
+    <t>PERF-001,PERF-003,PERF-004</t>
+  </si>
+  <si>
+    <t>Brief 62: NOW #4</t>
+  </si>
+  <si>
+    <t>PDF -&gt; editable</t>
+  </si>
+  <si>
+    <t>P2E-002,P2E-005</t>
+  </si>
+  <si>
+    <t>Brief 62: NOW #5</t>
+  </si>
+  <si>
+    <t>TRAN-001,TRAN-006</t>
+  </si>
+  <si>
+    <t>Brief 62: NOW #6</t>
+  </si>
+  <si>
+    <t>FONT-002,FONT-003</t>
+  </si>
+  <si>
+    <t>Brief 62: NOW #7</t>
+  </si>
+  <si>
+    <t>Review Changes</t>
+  </si>
+  <si>
+    <t>REV-001,REV-002</t>
+  </si>
+  <si>
+    <t>Brief 62: NOW #8</t>
+  </si>
+  <si>
+    <t>HLTH-001,HLTH-002</t>
+  </si>
+  <si>
+    <t>Brief 62: NOW #9</t>
+  </si>
+  <si>
+    <t>FMT-001,FMT-002,FMT-003</t>
+  </si>
+  <si>
+    <t>Brief 62: NOW #10</t>
+  </si>
+  <si>
+    <t>OCR</t>
+  </si>
+  <si>
+    <t>Part of PDF -&gt; editable (brief 43)</t>
+  </si>
+  <si>
+    <t>Multilingual support</t>
+  </si>
+  <si>
+    <t>TRAN-007,FONT-003</t>
+  </si>
+  <si>
+    <t>Part of translation + FontResolver</t>
+  </si>
+  <si>
+    <t>RTL</t>
+  </si>
+  <si>
+    <t>FONT-003,FONT-004</t>
+  </si>
+  <si>
+    <t>Part of FontResolver</t>
+  </si>
+  <si>
+    <t>CJK</t>
+  </si>
+  <si>
+    <t>Glossary</t>
+  </si>
+  <si>
+    <t>Part of translation MVP (brief 49)</t>
+  </si>
+  <si>
+    <t>Terminology lock</t>
+  </si>
+  <si>
+    <t>Citation preservation</t>
+  </si>
+  <si>
+    <t>Preservation is fidelity work; a citation editor is LATER</t>
+  </si>
+  <si>
+    <t>Bibliography preservation</t>
+  </si>
+  <si>
+    <t>Preservation is fidelity work</t>
+  </si>
+  <si>
+    <t>Content controls</t>
+  </si>
+  <si>
+    <t>Preserve now; editing content controls NEXT</t>
+  </si>
+  <si>
+    <t>Custom fields</t>
+  </si>
+  <si>
+    <t>Preserve custom properties and fields now; an editor NEXT</t>
+  </si>
+  <si>
+    <t>Document compare</t>
+  </si>
+  <si>
+    <t>NEXT</t>
+  </si>
+  <si>
+    <t>Brief 62: NEXT</t>
+  </si>
+  <si>
+    <t>Version compare</t>
+  </si>
+  <si>
+    <t>Brief 62: NEXT (batch processing)</t>
+  </si>
+  <si>
+    <t>After the translation MVP</t>
+  </si>
+  <si>
+    <t>Table repair</t>
+  </si>
+  <si>
+    <t>List repair</t>
+  </si>
+  <si>
+    <t>Brief 62: NEXT (accessibility)</t>
+  </si>
+  <si>
+    <t>Heading hierarchy checker</t>
+  </si>
+  <si>
+    <t>Link checker</t>
+  </si>
+  <si>
+    <t>Alt-text checker</t>
+  </si>
+  <si>
+    <t>HLTH-001,FEAT-010</t>
+  </si>
+  <si>
+    <t>Metadata editor</t>
+  </si>
+  <si>
+    <t>Global style replacement</t>
+  </si>
+  <si>
+    <t>Find/replace with formatting</t>
+  </si>
+  <si>
+    <t>Tracked change cleanup</t>
+  </si>
+  <si>
+    <t>Template extraction</t>
+  </si>
+  <si>
+    <t>Document-to-template</t>
+  </si>
+  <si>
+    <t>Template matching</t>
+  </si>
+  <si>
+    <t>Advanced template sharing</t>
+  </si>
+  <si>
+    <t>Teams</t>
+  </si>
+  <si>
+    <t>Translation memory</t>
+  </si>
+  <si>
+    <t>PDF merge/split</t>
+  </si>
+  <si>
+    <t>Page reorder</t>
+  </si>
+  <si>
+    <t>Page rotate</t>
+  </si>
+  <si>
+    <t>Page delete</t>
+  </si>
+  <si>
+    <t>Page extract</t>
+  </si>
+  <si>
+    <t>Merge documents</t>
+  </si>
+  <si>
+    <t>LATER</t>
+  </si>
+  <si>
+    <t>Split documents</t>
+  </si>
+  <si>
+    <t>Watermark</t>
+  </si>
+  <si>
+    <t>Forms (advanced)</t>
+  </si>
+  <si>
+    <t>Brief 62: LATER</t>
+  </si>
+  <si>
+    <t>SmartArt editing</t>
+  </si>
+  <si>
+    <t>Brief 62: LATER; SmartArt is preserved, not edited</t>
+  </si>
+  <si>
+    <t>OLE</t>
+  </si>
+  <si>
+    <t>Brief 62: LATER; OLE objects preserved, not edited</t>
+  </si>
+  <si>
+    <t>Full tracked-change editor</t>
+  </si>
+  <si>
+    <t>Advanced citation manager</t>
+  </si>
+  <si>
+    <t>Advanced drawing editor</t>
+  </si>
+  <si>
+    <t>Layout-preserving PDF editing (frames/anchors)</t>
+  </si>
+  <si>
+    <t>ARCHITECTURE_ONLY</t>
+  </si>
+  <si>
+    <t>Phase 9: architecture and hooks only</t>
+  </si>
+  <si>
+    <t>Product tasks (live from MASTER)</t>
+  </si>
+  <si>
+    <t>TRANSLATION — Translation and fonts</t>
+  </si>
+  <si>
+    <t>Translation MVP and FontResolver. Categories: TRANSLATION, FONT. Rows are formulas over MASTER — change task data in MASTER or with tools/tracker/tracker.py.</t>
+  </si>
+  <si>
+    <t>PDF_TO_EDITABLE — PDF to editable</t>
+  </si>
+  <si>
+    <t>PDF to editable document conversion. Categories: P2E. Rows are formulas over MASTER — change task data in MASTER or with tools/tracker/tracker.py.</t>
+  </si>
+  <si>
+    <t>BILLING_PLANS — Plans and billing</t>
+  </si>
+  <si>
+    <t>Initial plan hypothesis — brief §64: configurable defaults, not final prices; confirm against measured AI and infrastructure cost. Blue = input.</t>
+  </si>
+  <si>
+    <t>Usage unit / feature</t>
+  </si>
+  <si>
+    <t>FREE</t>
+  </si>
+  <si>
+    <t>PRO</t>
+  </si>
+  <si>
+    <t>BUSINESS</t>
+  </si>
+  <si>
+    <t>Documents / month</t>
+  </si>
+  <si>
+    <t>BUSINESS: per workspace</t>
+  </si>
+  <si>
+    <t>PDF conversion pages / month</t>
+  </si>
+  <si>
+    <t>OCR pages / month</t>
+  </si>
+  <si>
+    <t>Translation characters / month</t>
+  </si>
+  <si>
+    <t>AI operations / month</t>
+  </si>
+  <si>
+    <t>Exports / month</t>
+  </si>
+  <si>
+    <t>high</t>
+  </si>
+  <si>
+    <t>BUSINESS: 'high export limits', no number given</t>
+  </si>
+  <si>
+    <t>Templates</t>
+  </si>
+  <si>
+    <t>basic</t>
+  </si>
+  <si>
+    <t>custom</t>
+  </si>
+  <si>
+    <t>shared</t>
+  </si>
+  <si>
+    <t>Formatting</t>
+  </si>
+  <si>
+    <t>Format by Example</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>Advanced Document Health</t>
+  </si>
+  <si>
+    <t>yes</t>
+  </si>
+  <si>
+    <t>Version history</t>
+  </si>
+  <si>
+    <t>no</t>
+  </si>
+  <si>
+    <t>reasonable limits</t>
+  </si>
+  <si>
+    <t>Team workspace</t>
+  </si>
+  <si>
+    <t>Priority processing</t>
+  </si>
+  <si>
+    <t>Advanced controls</t>
+  </si>
+  <si>
+    <t>Billing and plan tasks (live from MASTER)</t>
+  </si>
+  <si>
+    <t>INFRA — Infrastructure</t>
+  </si>
+  <si>
+    <t>Tracker, jobs, storage, observability, deployment, documentation. Categories: INFRA, JOBS, STORAGE, OBSERVABILITY, DOCS. Rows are formulas over MASTER — change task data in MASTER or with tools/tracker/tracker.py.</t>
+  </si>
+  <si>
+    <t>Timestamp</t>
+  </si>
+  <si>
+    <t>Task ID</t>
+  </si>
+  <si>
+    <t>Change</t>
+  </si>
+  <si>
+    <t>Files</t>
+  </si>
+  <si>
+    <t>Created SmartDoc_Master_Implementation_Tracker.xlsx from the 2026-09-26 audit findings and the brief's phases: 151 tasks, 20 findings, 15 release gates.</t>
+  </si>
+  <si>
+    <t>tools/tracker/tracker.py, tools/tracker/seed.py</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>Built the Excel control centre: MASTER with 151 stable-ID tasks from the audit findings and the brief's 19 phases, CRITICAL_FIXES (20 findings -&gt; fix tasks, live status), 14 category views, DASHBOARD (totals, completion/verified %, phase %, category %, P0/P1 remaining), CHANGE_LOG, SESSION_STATE, RELEASE_GATES GATE-001..015. Formulas verified in Excel against independently computed values.</t>
+  </si>
+  <si>
+    <t>tools/tracker/*, SmartDoc_Master_Implementation_Tracker.xlsx, .gitignore</t>
+  </si>
+  <si>
+    <t>Resume reminder set with the platform scheduler; it fired and resumed the work. It only fires while this session is open and idle, which is recorded in AI-CONTINUATION.md.</t>
+  </si>
+  <si>
+    <t>Created the checkpoint system: AI-CONTINUATION.md with CURRENT STATE / LAST VERIFIED / WHAT WAS CHANGED / WHAT PASSED / WHAT FAILED / WHAT REMAINS / NEXT ACTION / IMPORTANT WARNINGS, session-state.json mirrored into SESSION_STATE by tracker.py state, and the brief saved verbatim for future sessions.</t>
+  </si>
+  <si>
+    <t>docs/AI-CONTINUATION.md, docs/session-state.json, docs/implementation-brief.md</t>
+  </si>
+  <si>
+    <t>Baseline backend suite: 643 passed, 1 skipped (optional real-Word check), 0 failed in 88 s on ea69829. Recorded as RUN-0001.</t>
+  </si>
+  <si>
+    <t>Baseline frontend: eslint clean, tsc clean, Vitest 46 passed in 6 files, production build succeeded. Recorded as RUN-0002..RUN-0005.</t>
+  </si>
+  <si>
+    <t>Baseline E2E: 16 Playwright workflows passed against the throwaway stack (SQLite backend :8100, production build :3100). The brief's 24-workflow target is TEST-040; temp-dir leak logged as TEST-006.</t>
+  </si>
+  <si>
+    <t>Baseline database: alembic head 85211092fe4c, check reports no drift, full down/up cycle clean; PostgreSQL offline SQL builds 14 tables with RLS; Supabase has all 8 migrations and only INFO-level advisor notices.</t>
+  </si>
+  <si>
+    <t>Baseline dependency audit: pip-audit finds no known vulnerabilities in requirements.lock or requirements-dev.lock; npm audit reports 0 vulnerabilities (production and dev).</t>
+  </si>
+  <si>
+    <t>Baseline infrastructure inspected: compose file valid with 8 services, arq worker and in-process job backends, local and S3 storage providers. Docker images were not built (daemon not running) - left to INFRA-010.</t>
+  </si>
+  <si>
+    <t>Baseline fixtures: the repository's 12 golden DOCX are generated by python-docx (not Word-authored) plus one PDF; the audit's 17 Word-authored fixtures still live outside the repo and move in with TEST-020.</t>
+  </si>
+  <si>
+    <t>Wrote docs/architecture/current-baseline.md: stack versions, the 11 baseline checks with commands and results, the migration chain and live database state, fixture inventory, audit performance figures, and what the baseline could not verify (Docker images, real AI model, Stripe, e-mail, hosting).</t>
+  </si>
+  <si>
+    <t>INFRA-001, INFRA-002, INFRA-003, TEST-001, TEST-002, TEST-003, TEST-004, TEST-005, SEC-001, INFRA-004, DOCS-001</t>
+  </si>
+  <si>
+    <t>Phase 0 committed (4da4ecb, pushed to feature/smartdoc-production-hardening): tracker, checkpoint system and measured baseline. All 11 phase-0 tasks DONE; no production code changed.</t>
+  </si>
+  <si>
+    <t>see commit 4da4ecb</t>
+  </si>
+  <si>
+    <t>Model now holds blocks nested inside table cells, list items and quotes as Elements (authoritative when set; inline keeps plain text), plus list numbering start/format; nesting capped at 8 levels (422 beyond). schemaVersion stays 1: the fields are additive.</t>
+  </si>
+  <si>
+    <t>backend/app/models/document.py, backend/tests/test_document_nesting.py</t>
+  </si>
+  <si>
+    <t>Regenerated the OpenAPI schema and the frontend's generated types for the nested-block and numbering fields; the contract test and the type check pass.</t>
+  </si>
+  <si>
+    <t>frontend/types/generated/*, frontend/types/document.ts</t>
+  </si>
+  <si>
+    <t>Backend readers now see nested blocks: pasted pictures inside cells/list items/quotes are validated and moved to asset storage like top-level ones (security and quota), exports fetch their assets, and the links health check covers list items, cells and nested blocks.</t>
+  </si>
+  <si>
+    <t>backend/app/services/image_assets.py, backend/app/services/document_service.py, backend/app/formatting/health.py</t>
+  </si>
+  <si>
+    <t>Word export renders nested blocks in cells, list items and quotes in reading order (verified by text order), numbers lists from their start in their format, and writes pictures' alt text.</t>
+  </si>
+  <si>
+    <t>backend/app/export/docx_export.py</t>
+  </si>
+  <si>
+    <t>PDF export renders nested blocks and list numbering (start/format); nested numbered levels now use the same a./i. sequence as the Word export instead of 1. everywhere.</t>
+  </si>
+  <si>
+    <t>backend/app/export/pdf_export.py</t>
+  </si>
+  <si>
+    <t>The editor mapping is total over the schema (tested against getSchema(editorExtensions)); anything unknown stops the save with a visible 'Not saved' message instead of being dropped, and the last saved version stays untouched.</t>
+  </si>
+  <si>
+    <t>frontend/editor/*</t>
+  </si>
+  <si>
+    <t>frontend/editor/nestedBlocks.test.ts (7 refusal cases); frontend/editor/useAutoSave.test.tsx (3)</t>
+  </si>
+  <si>
+    <t>Playwright pastes rich HTML (lists, code and a picture in table cells; a list in a quote; code in a list item; a list starting at 3 in letters), waits for autosave and reloads: everything is still there and no 'Not saved' appears.</t>
+  </si>
+  <si>
+    <t>frontend/e2e/nested.spec.ts</t>
+  </si>
+  <si>
+    <t>CORE-001, CORE-002, CORE-003, EDIT-001, EDIT-002, EDIT-003, EDIT-004, EDIT-005, EDIT-006, DOCX-001, PDF-001</t>
+  </si>
+  <si>
+    <t>Committed phase-01a-editor-integrity (1fe27a9, pushed): nested blocks in cells, list items and quotes survive the editor, the backend and both exports; unknown content stops the save visibly. AUD-01 fix tasks all DONE.</t>
+  </si>
+  <si>
+    <t>Import now produces a Document Fidelity Report: the importer's notes as items (feature, policy, count, content lost) plus an independent content check - the source's words (DOCX XML read separately from the importer, Markdown by what it renders, PDF extracted text) against the document's, in order. 'Verified' only when identical; differences listed with context (missing/added/changed/moved).</t>
+  </si>
+  <si>
+    <t>backend/app/fidelity/*, backend/app/models/document.py, backend/app/services/ingestion_service.py</t>
+  </si>
+  <si>
+    <t>Every importer note now carries a stable feature key and a brief-§90 policy class; review count and content-loss count are derived from them.</t>
+  </si>
+  <si>
+    <t>The editor shows the import's verdict in the status bar and a Проверка panel: content verified / differs (with word-level differences) / body complete but some content left out, then each item by policy. Browser check with a05 caught and fixed a misleading 'No content changes' when header text had been left out.</t>
+  </si>
+  <si>
+    <t>frontend/editor/panels/FidelityPanel.tsx, frontend/editor/EditorStatusBar.tsx, frontend/editor/DocumentEditorShell.tsx</t>
+  </si>
+  <si>
+    <t>FID-001, FID-004, FID-005, INFRA-005</t>
+  </si>
+  <si>
+    <t>Committed phase-01b-fidelity-report (8a330be, pushed): import fidelity report with policy classes and an independent word-level content check, shown in the editor; throwaway preview scripts.</t>
+  </si>
+  <si>
+    <t>Exports now report what they approximate or leave out (missing pictures, WebP a Word file can't hold, tables restyled for Word-sourced documents, edited kept fragments, page breaks in PDF tables, PDF comments/equations/fields/internal links, scripts the PDF can't lay out, alt text) and re-read the file: a Word export must hold exactly the document's words, a PDF every word in order (its own list numbers and page headers allowed). Shown under the Download button; the job result carries it.</t>
+  </si>
+  <si>
+    <t>Committed phase-01c-export-report (e55412f, pushed): export fidelity report with read-back content check, shown in the Export menu.</t>
+  </si>
+  <si>
+    <t>Added the machine-readable capability matrix (brief §91): 67 document features with import/edit/export/round-trip support and the policy the fidelity report uses, served at GET /api/v1/capabilities. Tests tie it to the code both ways, require a test for every clean round trip and a task for every unreported gap; writing it exposed unreported gaps now tracked (EDIT-012, DOCX-027).</t>
+  </si>
+  <si>
+    <t>backend/app/capabilities.py, backend/app/api/capabilities.py, backend/app/main.py, backend/tests/test_capabilities.py, frontend/types/generated/*</t>
+  </si>
+  <si>
+    <t>Committed phase-01d-capability-matrix (fcf30d7, pushed).</t>
+  </si>
+  <si>
+    <t>FID-002: import report now names empty spacing paragraphs, unsafe link addresses and per-section differences (page setup, odd/even breaks, page numbering, borders, line numbers, vertical alignment); matrix rows docx.empty_paragraphs + docx.sections updated</t>
+  </si>
+  <si>
+    <t>backend/app/fidelity/docx_detect.py, backend/app/fidelity/imports.py, backend/app/parsers/docx.py, backend/app/parsers/docx_inline.py, backend/app/capabilities.py, backend/tests/test_docx_detect.py</t>
+  </si>
+  <si>
+    <t>DOCX-015: section breaks break the page only where Word does (next section's w:type decides); continuous breaks no longer become page breaks</t>
+  </si>
+  <si>
+    <t>DOCX-016: list number formats, start values and continuation round-trip; custom and multi-level labels reported</t>
+  </si>
+  <si>
+    <t>DOCX-012: Word core properties round-trip; custom properties and sensitivity labels reported without values</t>
+  </si>
+  <si>
+    <t>tests/test_docx_detect.py::test_the_files_own_properties_go_back_into_word_not_the_templates, tests/test_docx_detect.py::test_metadata_that_is_not_kept_is_reported_without_its_values</t>
+  </si>
+  <si>
+    <t>DOCX-026: unsafe link addresses reported instead of silently dropped</t>
+  </si>
+  <si>
+    <t>Golden JSON export is deterministic (uuid5 ids by order, fixed timestamps) so a regenerated fixture only differs where the importer's output did</t>
+  </si>
+  <si>
+    <t>backend/scripts/export_golden_json.py, frontend/tests/fixtures/golden/*.json</t>
+  </si>
+  <si>
+    <t>two consecutive exports byte-identical; tests/test_golden_documents.py::test_the_frontend_golden_json_is_current</t>
+  </si>
+  <si>
+    <t>FID-002 committed and pushed (phase-01e-import-detections)</t>
+  </si>
+  <si>
+    <t>SEC-022: formatting rule values validated at every entry and at resolve; CSS break-out via element style/page settings/instructions closed</t>
+  </si>
+  <si>
+    <t>backend/app/formatting/values.py, backend/app/formatting/engine.py, backend/app/schemas/formatting.py, backend/app/schemas/document.py, backend/app/ai/instruction_extraction.py, backend/tests/test_rule_values.py</t>
+  </si>
+  <si>
+    <t>FMT-005: instruction-path rule values validated before reaching CSS/export (with SEC-022)</t>
+  </si>
+  <si>
+    <t>EDIT-008: pasted/shortcut alignment saved as the element's own style and kept on split; paste into an empty paragraph keeps the pasted paragraphs' attributes</t>
+  </si>
+  <si>
+    <t>frontend/editor/tiptapToDocument.ts, frontend/editor/documentToTiptap.ts, frontend/editor/useAutoSave.ts, frontend/editor/pasteIntoEmptyBlock.ts, frontend/editor/extensions.ts, frontend/services/api/documents.ts, backend/app/schemas/document.py, backend/app/formatting/engine.py, backend/app/services/document_service.py, backend/app/api/documents.py</t>
+  </si>
+  <si>
+    <t>EDIT-009: pasted picture size kept as the picture's width share</t>
+  </si>
+  <si>
+    <t>EDIT-012: values outside the model named in the status bar and the Проверка panel</t>
+  </si>
+  <si>
+    <t>EDIT-011: cell alignment from pasted cells kept per column; differing cells and column widths reported</t>
+  </si>
+  <si>
+    <t>EDIT-008, EDIT-009, EDIT-012, SEC-022, FMT-005</t>
+  </si>
+  <si>
+    <t>Committed and pushed phase-01f-editor-direct-formatting</t>
+  </si>
+  <si>
+    <t>EDIT-010: link titles kept from Word/Markdown through the editor back into Word</t>
+  </si>
+  <si>
+    <t>backend/app/models/document.py, backend/app/parsers/docx_inline.py, backend/app/parsers/docx.py, backend/app/export/docx_export.py, backend/app/parsers/markdown.py, frontend/editor/tiptapToDocument.ts, frontend/editor/documentToTiptap.ts</t>
+  </si>
+  <si>
+    <t>FID-006: Markdown pictures named as left out (content), thematic breaks kept as rules</t>
+  </si>
+  <si>
+    <t>backend/app/parsers/markdown.py, backend/app/capabilities.py, backend/tests/test_capabilities.py, backend/tests/test_markdown_parser.py</t>
+  </si>
+  <si>
+    <t>EDIT-011: cell alignment/widths the model can't hold are named; keeping them moves to DOCX-017</t>
+  </si>
+  <si>
+    <t>EDIT-007: marks in one canonical order (MarkType) on both sides; opening a document saves nothing</t>
+  </si>
+  <si>
+    <t>backend/app/models/document.py, frontend/editor/tiptapToDocument.ts</t>
+  </si>
+  <si>
+    <t>TEST-010: nested-structure regression suite consolidated and verified</t>
+  </si>
+  <si>
+    <t>EDIT-008, EDIT-010, FID-006</t>
+  </si>
+  <si>
+    <t>Phase 1 browser check in the throwaway stack: Markdown doc with a picture -&gt; 'Body text complete, some content left out · 1 to review' (picture named with its description), '---' imported as a rule; pasted centred line + 160px picture + hsl colour + titled link at the end -&gt; status 'Saved · 1 formatting change not kept', Проверка 'While editing' lists the colour; after reload: line centred, picture width 24.9%, link title kept, notice gone</t>
+  </si>
+  <si>
+    <t>manual browser check (throwaway stack, fresh SQLite)</t>
+  </si>
+  <si>
+    <t>DOCS-011: documentation tree started for Phase 1 (document model, fidelity, docx, formatting, security, testing)</t>
+  </si>
+  <si>
+    <t>EDIT-007, EDIT-010, EDIT-011, FID-006, TEST-010, DOCS-011</t>
+  </si>
+  <si>
+    <t>Committed and pushed phase-01g-phase-1-complete; Phase 1 complete</t>
+  </si>
+  <si>
+    <t>AI-001: order/count/token/numeric/punctuation-aware comparator for AI output, with classified differences</t>
+  </si>
+  <si>
+    <t>backend/app/fidelity/text_check.py, backend/tests/test_ai_fidelity.py</t>
+  </si>
+  <si>
+    <t>AI-002: numbers and units protected; changed_numbers for cross-language checks</t>
+  </si>
+  <si>
+    <t>AI-003: structure analysis refuses answers that alter the text, per piece, logging without content</t>
+  </si>
+  <si>
+    <t>backend/app/ai/structure_analysis.py</t>
+  </si>
+  <si>
+    <t>AI-004: adversarial fidelity tests for every alteration the brief names</t>
+  </si>
+  <si>
+    <t>AI-001, AI-002, AI-003, AI-004</t>
+  </si>
+  <si>
+    <t>Committed and pushed phase-02a-ai-fidelity-check</t>
+  </si>
+  <si>
+    <t>AI-005: AI operations classified FORMAT/STRUCTURE/CONTENT; per-element instruction styles no longer dropped by the formatting pass</t>
+  </si>
+  <si>
+    <t>backend/app/formatting/proposals.py, backend/app/services/document_service.py</t>
+  </si>
+  <si>
+    <t>REV-001: change model with categories, used for proposals</t>
+  </si>
+  <si>
+    <t>backend/app/models/document.py, frontend/types/document.ts</t>
+  </si>
+  <si>
+    <t>AI-006: PLAN-&gt;VALIDATE-&gt;PREVIEW-&gt;ACCEPT-&gt;APPLY for AI content changes</t>
+  </si>
+  <si>
+    <t>backend/app/formatting/proposals.py, backend/app/services/document_service.py, backend/app/api/documents.py, backend/app/jobs/runner.py, backend/app/schemas/document.py, backend/app/schemas/jobs.py</t>
+  </si>
+  <si>
+    <t>AI-007: proposal review UI with accept/reject, E2E verified</t>
+  </si>
+  <si>
+    <t>frontend/editor/panels/ProposalsList.tsx, frontend/editor/panels/InstructionsPanel.tsx, frontend/editor/EditorStatusBar.tsx, frontend/editor/useFormatting.ts, frontend/services/api/documents.ts, frontend/services/api/jobs.ts, backend/scripts/e2e_ai.py, backend/scripts/e2e_server.py</t>
+  </si>
+  <si>
+    <t>AI-005, REV-001, AI-006, AI-007</t>
+  </si>
+  <si>
+    <t>Committed and pushed phase-02b-ai-proposals</t>
+  </si>
+  <si>
+    <t>AI-008: per-job/per-request AI call and time budget; no unbounded retries</t>
+  </si>
+  <si>
+    <t>backend/app/ai/budget.py, backend/app/config.py, backend/app/jobs/runner.py, backend/app/api/deps.py, backend/app/ai/structure_analysis.py</t>
+  </si>
+  <si>
+    <t>Committed and pushed phase-02c-ai-budget</t>
+  </si>
+  <si>
+    <t>AI-009: prompt-injection review; AI answer fields bounded; hostile-document tests</t>
+  </si>
+  <si>
+    <t>backend/app/ai/schemas.py, backend/app/ai/structure_analysis.py, backend/tests/test_prompt_injection.py</t>
+  </si>
+  <si>
+    <t>SEC-018: prompt injection / AI output abuse covered by AI-009's tests</t>
+  </si>
+  <si>
+    <t>AI-001, AI-005, AI-007, AI-009</t>
+  </si>
+  <si>
+    <t>Phase 2 gate: backend 817 passed/1 skipped, Vitest 117, Playwright 20; browser check in the throwaway stack - 'make the title red and delete “This draft paragraph”': title red at once, the paragraph kept and shown under Changes to review (struck through, with the instruction), notice + '1 AI change to review'; Accept removed it, reload kept it removed with nothing pending</t>
+  </si>
+  <si>
+    <t>full suites + manual browser check</t>
+  </si>
+  <si>
+    <t>DOCX-010: original Word package kept as an immutable, checksummed asset</t>
+  </si>
+  <si>
+    <t>backend/app/models/document.py, backend/app/services/document_service.py</t>
+  </si>
+  <si>
+    <t>DOCX-011: Word exports written into the original package; import report reflects what they keep</t>
+  </si>
+  <si>
+    <t>backend/app/export/docx_export.py, backend/app/fidelity/imports.py, backend/app/fidelity/docx_source.py, backend/app/fidelity/docx_detect.py, backend/app/fidelity/exports.py, backend/app/jobs/runner.py, backend/app/api/documents.py, backend/app/capabilities.py</t>
+  </si>
+  <si>
+    <t>TEST-023: independent package validation of every Word export</t>
+  </si>
+  <si>
+    <t>backend/app/export/package_check.py, backend/tests/test_package_check.py</t>
+  </si>
+  <si>
+    <t>DOCX-012: metadata preserved (core in the model, app/custom/labels via the original package)</t>
+  </si>
+  <si>
+    <t>DOCX-028: unchanged blocks keep their original XML in Word exports; server-side provenance; earlier sections follow page setup, header and page-number changes; lost sections reported; golden 13-kept-blocks + E2E.</t>
+  </si>
+  <si>
+    <t>backend/app/export/provenance.py, backend/app/export/docx_export.py, backend/app/parsers/docx.py, backend/app/models/document.py, backend/app/services/document_service.py, backend/app/fidelity/imports.py, backend/app/fidelity/exports.py, backend/app/capabilities.py, frontend/editor/tiptapToDocument.ts, frontend/e2e/kept-blocks.spec.ts, docs/docx/README.md</t>
+  </si>
+  <si>
+    <t>DOCX-028 committed and pushed as c8c2d27 (phase-03b-original-blocks).</t>
+  </si>
+  <si>
+    <t>DOCX-025: Word's hidden text stays hidden - hidden mark with Word's style resolution, editor shows it only on request, vanish in Word exports, left out of PDF with a note, consistent content checks.</t>
+  </si>
+  <si>
+    <t>backend/app/models/document.py, backend/app/parsers/docx_inline.py, backend/app/parsers/docx_styles.py, backend/app/parsers/docx.py, backend/app/fidelity/docx_detect.py, backend/app/fidelity/content.py, backend/app/fidelity/exports.py, backend/app/export/docx_export.py, backend/app/export/pdf_export.py, frontend/editor/hiddenText.ts, frontend/editor/EditorStatusBar.tsx, frontend/editor/DocumentEditorShell.tsx, frontend/app/globals.css</t>
+  </si>
+  <si>
+    <t>DOCX-025 committed and pushed as 7d1af86 (phase-03c-hidden-text).</t>
+  </si>
+  <si>
+    <t>DOCX-013 part 1: underline and strike styles, capitals, small capitals, spacing and raised/lowered text kept through import, editor, Word and PDF; paragraph-style formatting turned off by a run fixed.</t>
+  </si>
+  <si>
+    <t>backend/app/models/document.py, backend/app/parsers/docx_inline.py, backend/app/parsers/docx_styles.py, backend/app/parsers/docx.py, backend/app/export/docx_export.py, backend/app/export/pdf_export.py, backend/app/fidelity/*, frontend/editor/characterFormatting.ts, frontend/editor/tiptapToDocument.ts</t>
+  </si>
+  <si>
+    <t>backend 888 passed/1 skipped (tests/test_character_formatting.py 12); Vitest 128 (editor/characterFormatting.test.ts 3, golden round trip of 02); Playwright 22; tsc + eslint clean</t>
+  </si>
+  <si>
+    <t>DOCX-013 part 1 committed and pushed as 6619159 (phase-03d-character-formatting); part 2 next.</t>
+  </si>
+  <si>
     <t>6619159</t>
   </si>
   <si>
-    <t>Hidden text (listed here too) is done under DOCX-025.; Part 2 remaining: character scale, kerning, language/noProof, theme font/colour links, effects, emphasis marks - detect, 'kept while unchanged' with the source kept, and export.docx.rewritten_formatting for rewritten blocks.</t>
-  </si>
-  <si>
-    <t>DOCX-014</t>
-  </si>
-  <si>
-    <t>Paragraph formatting</t>
-  </si>
-  <si>
-    <t>Right indent, keep-with-next, keep-lines, page-break-before, widow/orphan, outline level, tabs, borders, shading, direction, contextual spacing.</t>
-  </si>
-  <si>
-    <t>DOCX-015</t>
-  </si>
-  <si>
-    <t>Sections as a first-class concept</t>
-  </si>
-  <si>
-    <t>Breaks (next/continuous/even/odd), orientation, size, margins, columns, header/footer distance, first/even/odd headers, linked-to-previous, page-number restart.</t>
-  </si>
-  <si>
-    <t>tests/test_docx_detect.py::test_a_section_break_breaks_the_page_only_where_word_does</t>
-  </si>
-  <si>
-    <t>backend/models, parsers, export</t>
-  </si>
-  <si>
-    <t>Fixed: a section's w:type describes how THAT section starts (ECMA-376 17.6.22) - the importer used the ending section's own type, so a continuous break became a page break and continuous-&gt;new-page put the break between the wrong sections (probe confirmed). Now the next section's type decides. Per-section differences are reported (FID-002). Remaining: sections as a first-class model concept (orientation/margins/columns/headers per section, page-number restart) and export of several sections.; With DOCX-011 the last section's properties (columns, page numbering, borders, line numbers, vertical alignment, header/footer variants) are kept in Word exports; earlier sections' are still reported lost.; DOCX-028: earlier sections now survive in Word exports while their ending paragraph is unchanged; page setup/header/page-number changes apply to them; a lost one is reported (export.docx.section_lost). Modelling sections is still this task.</t>
-  </si>
-  <si>
-    <t>DOCX-016</t>
-  </si>
-  <si>
-    <t>Numbering engine</t>
-  </si>
-  <si>
-    <t>Decimal/roman/alpha/bullets, custom prefixes/suffixes, start, restart, continuation, multilevel, numId/abstractNum/ilvl, indentation.</t>
-  </si>
-  <si>
-    <t>tests/test_docx_numbering.py</t>
-  </si>
-  <si>
-    <t>Done so far: top-level list number format (decimal/roman/letters), start value (lvl start + lvlOverride/startOverride) and continuation across interrupting paragraphs imported into Element.numbering and written back to Word (per-level formats, startOverride) and PDF; empty numbered items keep counting. Reported, not kept: custom labels ('Чл. 1.', '(a)'), multi-level labels ('1.1'), numbered headings baked into text. Remaining: prefixes/suffixes, multilevel numbering model, restart semantics per level, indentation.</t>
-  </si>
-  <si>
-    <t>AUD-04</t>
-  </si>
-  <si>
-    <t>DOCX-017</t>
-  </si>
-  <si>
-    <t>Table engine</t>
-  </si>
-  <si>
-    <t>No forced header or Table Grid; widths, heights, margins, borders, shading, v-align, nested tables, repeated header rows, table styles.</t>
-  </si>
-  <si>
-    <t>From EDIT-011 (2026-09-27): add per-cell alignment and column widths to the model (the editor's cell align/colwidth, Word tcW/tblGrid, PDF colWidths); until then the editor names them as not kept.</t>
-  </si>
-  <si>
-    <t>DOCX-018</t>
-  </si>
-  <si>
-    <t>Images</t>
-  </si>
-  <si>
-    <t>Alt text exported; crop, rotation, anchor, wrap, position preserved; WEBP converted on export.</t>
-  </si>
-  <si>
-    <t>Alt text + title now exported (docPr descr/title) with DOCX-001; crop, rotation, WEBP still open.</t>
-  </si>
-  <si>
-    <t>DOCX-019</t>
-  </si>
-  <si>
-    <t>Drawings and text boxes preserved</t>
-  </si>
-  <si>
-    <t>Anchored drawings, text boxes, shapes kept even when not editable.</t>
-  </si>
-  <si>
-    <t>DOCX-028: text boxes and drawings in unchanged paragraphs are copied as they are (grouped with their anchor paragraph).</t>
-  </si>
-  <si>
-    <t>DOCX-020</t>
-  </si>
-  <si>
-    <t>Fields</t>
-  </si>
-  <si>
-    <t>Code/result/relationship; header STYLEREF/DATE live; TOC kept; CITATION/BIBLIOGRAPHY sources preserved; no 'Invalid source specified.'</t>
-  </si>
-  <si>
-    <t>backend/parsers, export</t>
-  </si>
-  <si>
-    <t>DOCX-028: field codes in unchanged blocks are copied as they are; a field spanning paragraphs is never copied half (self-contained check).</t>
-  </si>
-  <si>
-    <t>AUD-18</t>
-  </si>
-  <si>
-    <t>DOCX-021</t>
-  </si>
-  <si>
-    <t>Comment threads</t>
-  </si>
-  <si>
-    <t>Replies, resolved state, authors, ranges preserved (commentsExtended, people).</t>
-  </si>
-  <si>
-    <t>AUD-06</t>
-  </si>
-  <si>
-    <t>DOCX-022</t>
-  </si>
-  <si>
-    <t>Tracked changes preserved</t>
-  </si>
-  <si>
-    <t>Not silently accepted; explicit choice.</t>
-  </si>
-  <si>
-    <t>DOCX-028: blocks holding tracked changes are never copied (always written anew, accepted), so this task's explicit choice is still needed.</t>
-  </si>
-  <si>
-    <t>DOCX-023</t>
-  </si>
-  <si>
-    <t>Content controls preserved</t>
-  </si>
-  <si>
-    <t>w:sdt of every kind kept with its properties.</t>
-  </si>
-  <si>
-    <t>DOCX-028: content controls in unchanged blocks are copied with their properties (E2E proves it through the editor); written anew they are unwrapped (reported lossy at import).</t>
-  </si>
-  <si>
-    <t>DOCX-024</t>
-  </si>
-  <si>
-    <t>Real footnotes and endnotes</t>
-  </si>
-  <si>
-    <t>Notes stay notes on export.</t>
-  </si>
-  <si>
-    <t>DOCX-025</t>
-  </si>
-  <si>
-    <t>Hidden text stays hidden</t>
-  </si>
-  <si>
-    <t>Imported hidden text is kept hidden, shown only on request.</t>
-  </si>
-  <si>
-    <t>MarkType.HIDDEN (appended; no existing mark order changes). Importer resolves w:vanish as Word does: run, character style, paragraph style (the default paragraph style when none), docDefaults; webHidden stays visible; an explicit vanish=0 shows text in a hidden style. The detector uses the default paragraph style the same way and names hidden text as kept hidden (DETECTED_PRESERVED, not a content change). Editor: non-inclusive hidden mark (editor/hiddenText.ts; Word's display:none paste stays hidden), hidden by CSS unless .show-hidden; status bar 'Show hidden text (N words)' toggles it and re-paginates; the Structure panel leaves hidden text out of headings. Word export writes w:vanish (copied blocks keep theirs); PDF doesn't print hidden runs, export.pdf.hidden_text names the word count, and the PDF content check compares visible words (document_words(visible_only=True)); Word-side checks count hidden text on both sides. Golden 02-rich-text gained a hidden sentence (editor round trip in Vitest).</t>
-  </si>
-  <si>
-    <t>backend 876 passed/1 skipped (tests/test_hidden_text.py 7: import resolution, default paragraph style, report, upload + content check + editor save, Word export round trip, PDF text + note + check); Vitest 125 (editor/hiddenText.test.tsx 6, golden round trip of 02); Playwright 22 (e2e/hidden-text.spec.ts: hidden until asked, dotted line when shown, vanish in the Word export); tsc + eslint clean</t>
-  </si>
-  <si>
-    <t>backend/parsers, frontend</t>
-  </si>
-  <si>
-    <t>7d1af86</t>
-  </si>
-  <si>
-    <t>DOCX-028: vanish survives in unchanged blocks only; the model still shows hidden text as ordinary text - next task.</t>
-  </si>
-  <si>
-    <t>DOCX-026</t>
-  </si>
-  <si>
-    <t>Hyperlink policy and no silent autolink</t>
-  </si>
-  <si>
-    <t>Plain-text addresses not turned into links by default; file:/UNC reported.</t>
-  </si>
-  <si>
-    <t>tests/test_docx_detect.py::test_unsafe_links_and_spacing_paragraphs_are_reported</t>
-  </si>
-  <si>
-    <t>Done: links to unsafe addresses (javascript:, file:, UNC...) are kept as plain text and reported (docx.link.unsafe); plain-text addresses turned into links are reported (docx.autolink). Remaining: stop autolinking by default (a setting), per the task.</t>
-  </si>
-  <si>
-    <t>AUD-03,AUD-13</t>
-  </si>
-  <si>
-    <t>FMT-004</t>
-  </si>
-  <si>
-    <t>Render-spec defaults respect the source</t>
-  </si>
-  <si>
-    <t>Imported Word styles are not overridden by defaults (headings not forced bold).</t>
-  </si>
-  <si>
-    <t>backend/formatting</t>
-  </si>
-  <si>
-    <t>TEST-020</t>
-  </si>
-  <si>
-    <t>Word-authored fixtures in the repository</t>
-  </si>
-  <si>
-    <t>20 synthetic Word-authored fixtures, scrubbed of identifying metadata.</t>
-  </si>
-  <si>
-    <t>backend/tests/fixtures/word</t>
-  </si>
-  <si>
-    <t>TEST-021</t>
-  </si>
-  <si>
-    <t>Expected-loss manifests in CI</t>
-  </si>
-  <si>
-    <t>expected-loss.json per fixture; CI compares actual vs expected.</t>
-  </si>
-  <si>
-    <t>TEST-022</t>
-  </si>
-  <si>
-    <t>True fidelity test</t>
-  </si>
-  <si>
-    <t>SOURCE -&gt; import -&gt; format -&gt; editor save -&gt; export -&gt; reimport -&gt; compare SOURCE vs RESULT: content, formatting, metadata, structure separately.</t>
-  </si>
-  <si>
-    <t>TEST-023</t>
-  </si>
-  <si>
-    <t>Independent validation</t>
-  </si>
-  <si>
-    <t>OOXML schema validation, Word when available, docx2python; pdftotext/PyMuPDF for PDF.</t>
-  </si>
-  <si>
-    <t>app/export/package_check.py: an independent package check (zip read directly): well-formed parts, content types, relationships resolving, relationship ids used, defined styles/lists/comments. Found a real defect on first run (python-docx's add_comment refers to an undefined CommentReference style; exports now define it). Every golden export passes, fresh and into its original.</t>
-  </si>
-  <si>
-    <t>tests/test_package_check.py (13)</t>
-  </si>
-  <si>
-    <t>The docx skill's XSD validator needs defusedxml (not installed; installing needs a download) - schema-level validation remains open.</t>
-  </si>
-  <si>
-    <t>DOCX-027</t>
-  </si>
-  <si>
-    <t>Importer builds nested blocks</t>
-  </si>
-  <si>
-    <t>Use TableCell.blocks / ListItem.blocks on import: pictures, lists (with bullets) and nested tables inside cells, pictures inside list items - instead of dropping or flattening them.</t>
-  </si>
-  <si>
-    <t>AUD-01,AUD-03,AUD-08</t>
-  </si>
-  <si>
-    <t>DOCX-028</t>
-  </si>
-  <si>
-    <t>Unchanged blocks keep their original XML in Word exports</t>
-  </si>
-  <si>
-    <t>Blocks the user didn't change are written back as their original XML (fields, content controls, run-level formatting the model can't hold, bookmarks), changed ones regenerated; needs block provenance from the importer and fingerprints.</t>
-  </si>
-  <si>
-    <t>Importer records each top-level element's body children (Element.sourceBlocks: list items, drop caps, derived page breaks); an upload with a kept file stamps content+look fingerprints (Element.sourceHash, app/export/provenance.py: own/kind/body/nested resolved styles; page breaks have no look). docx_export._copy_plan groups elements with their children (uncovered children join the group before) and copies a group verbatim when every element is unchanged, together and in original order, children contiguous, XML self-contained (no tracked changes/note refs/altChunk; balanced fields, bookmarks, comment ranges); everything else is written anew. Provenance is server-side (keep_provenance on PUT /content). Page setup now runs after the body: changed size/margins reach every kept section (orientation kept, landscape turned), a changed main header is rewritten where Word shows it (link to previous), page numbers left out/asked for apply to every section. export.docx.section_lost (LOSSY) names sections lost with a changed paragraph; import report: earlier sections' setup/headers kept while unchanged; PDF names them Word-only. All 13 golden documents stamped + exported into their originals: sound packages, content verified (12-complex rewrites only the footnote paragraph and the note, by design).</t>
-  </si>
-  <si>
-    <t>backend 869 passed/1 skipped (tests/test_original_blocks.py 26 incl. 13 golden; test_source_package.py rewritten claims with export proof; test_golden_documents.py 13 files); Vitest 119 (editor round trip of 13-kept-blocks); Playwright 21 (e2e/kept-blocks.spec.ts: edit in the real editor, untouched paragraphs keep content control, double underline, landscape section); tsc + eslint clean</t>
-  </si>
-  <si>
-    <t>c8c2d27</t>
-  </si>
-  <si>
-    <t>Follow-up of DOCX-011 (package-level patch writer).; Known limit: any restyle (template, instruction) changes the body look, so every block but page breaks is written anew; follow-up DOCX-029. Sections survive only with their ending paragraph until DOCX-015 models them.</t>
-  </si>
-  <si>
-    <t>DOCX-029</t>
-  </si>
-  <si>
-    <t>Restyled blocks keep their original XML where nothing conflicts</t>
-  </si>
-  <si>
-    <t>After a template or instruction restyles a kind of block, copy a block's original XML when its paragraph style is the Word style the export rewrites for that kind and its direct formatting (pPr/rPr) sets none of the properties that changed; today any restyle writes every block anew (content controls, double underline etc. then lost, as the import report says).</t>
-  </si>
-  <si>
-    <t>Found while finishing DOCX-028: the look is part of the fingerprint so the export never shows a stale look.</t>
-  </si>
-  <si>
-    <t>FID-007</t>
-  </si>
-  <si>
-    <t>Reports follow the Word copy</t>
-  </si>
-  <si>
-    <t>With the original kept, the import report names what lives in blocks as kept in the Word export while the paragraph is unchanged, and an export that writes such a block anew names what it lost; a copy never brings back a link the app doesn't allow.</t>
-  </si>
-  <si>
-    <t>fidelity/imports.py KEPT_WHILE_UNCHANGED (content controls, text boxes, charts/shapes/SmartArt, objects, picture crop/rotation/floating, drop caps, empty paragraphs, approximated underlines, character scale, text effects, RTL) -&gt; detected_not_editable 'kept while the paragraph isn't changed or restyled'; docx_export._copy_plan returns rewritten groups, _lost_in/_rewritten_losses -&gt; export.docx.rewritten_blocks (LOSSY, count, kinds incl. proofing exclusions); _safe_links keeps groups with unsafe links (relationships or HYPERLINK fields) from being copied; the PDF's Word-only note covers the features.</t>
-  </si>
-  <si>
-    <t>tests/test_copy_reports.py (6): kept while unchanged at import, rewritten losses named (content controls, stretched text), unsafe javascript: link never copied back, PDF word-only; backend 894 passed/1 skipped; Playwright 22</t>
-  </si>
-  <si>
-    <t>Generalises DOCX-028's section handling (export.docx.section_lost) to everything the model doesn't hold inside blocks.</t>
-  </si>
-  <si>
-    <t>SEC-010</t>
-  </si>
-  <si>
-    <t>Malformed DOCX -&gt; safe 4xx</t>
-  </si>
-  <si>
-    <t>XML/zip/structure errors map to invalid_file; fuzz corpus shows no 500.</t>
-  </si>
-  <si>
-    <t>AUD-12</t>
-  </si>
-  <si>
-    <t>SEC-011</t>
-  </si>
-  <si>
-    <t>Malformed PDF -&gt; safe 4xx</t>
-  </si>
-  <si>
-    <t>Verified with a fuzz corpus.</t>
-  </si>
-  <si>
-    <t>SEC-012</t>
-  </si>
-  <si>
-    <t>Image resource limits</t>
-  </si>
-  <si>
-    <t>Compressed and decompressed size, pixel count, width, height, images per document, total bytes, format allowlist; rejected before rasterisation.</t>
-  </si>
-  <si>
-    <t>backend/security</t>
-  </si>
-  <si>
-    <t>AUD-09</t>
-  </si>
-  <si>
-    <t>SEC-013</t>
-  </si>
-  <si>
-    <t>PDF bombs, huge XML, decompression limits</t>
-  </si>
-  <si>
-    <t>Reviewed and tested limits.</t>
-  </si>
-  <si>
-    <t>SEC-014</t>
-  </si>
-  <si>
-    <t>Href policy</t>
-  </si>
-  <si>
-    <t>Server-side scheme allowlist; javascript:/data:/vbscript:/file: never exported as active links.</t>
-  </si>
-  <si>
-    <t>backend/models, export</t>
-  </si>
-  <si>
-    <t>AUD-13</t>
-  </si>
-  <si>
-    <t>SEC-015</t>
-  </si>
-  <si>
-    <t>Field instruction allowlist</t>
-  </si>
-  <si>
-    <t>No DDE/INCLUDETEXT/INCLUDEPICTURE/external fields accepted from clients or exported.</t>
-  </si>
-  <si>
-    <t>SEC-016</t>
-  </si>
-  <si>
-    <t>External relationships policy</t>
-  </si>
-  <si>
-    <t>No arbitrary external targets in exports.</t>
-  </si>
-  <si>
-    <t>SEC-017</t>
-  </si>
-  <si>
-    <t>Malicious SVG</t>
-  </si>
-  <si>
-    <t>Verified refused everywhere.</t>
-  </si>
-  <si>
-    <t>SEC-018</t>
-  </si>
-  <si>
-    <t>Prompt injection / AI output abuse</t>
-  </si>
-  <si>
-    <t>Tests with hostile documents; outputs validated.</t>
-  </si>
-  <si>
-    <t>Hostile-document tests: the document can't close its fence; out-of-bounds answers refused and fall back; an instruction steered by the document deletes nothing (proposals only) and a CSS break-out value is dropped; style-analysis flags on unknown elements dropped (see AI-009).</t>
-  </si>
-  <si>
-    <t>tests/test_prompt_injection.py</t>
-  </si>
-  <si>
-    <t>SEC-019</t>
-  </si>
-  <si>
-    <t>Error envelope audit</t>
-  </si>
-  <si>
-    <t>Every error {code, message, details, request_id}; no stack traces to users.</t>
-  </si>
-  <si>
-    <t>backend/api</t>
-  </si>
-  <si>
-    <t>SEC-020</t>
-  </si>
-  <si>
-    <t>CSP without 'unsafe-inline' scripts</t>
-  </si>
-  <si>
-    <t>Nonce-based CSP for the Next.js app.</t>
-  </si>
-  <si>
-    <t>TEST-030</t>
-  </si>
-  <si>
-    <t>Security regression suite</t>
-  </si>
-  <si>
-    <t>Fuzz corpus, pixel bombs, href/field policy, IDOR, CSRF.</t>
-  </si>
-  <si>
-    <t>SEC-010,SEC-012,SEC-014,SEC-015</t>
-  </si>
-  <si>
-    <t>AUD-09,AUD-12,AUD-13</t>
-  </si>
-  <si>
-    <t>SEC-021</t>
-  </si>
-  <si>
-    <t>Sensitivity-label metadata in the public repository</t>
-  </si>
-  <si>
-    <t>корекции.docx (committed in 5f2bf9e, pushed) carries 8 MSIP_Label_* custom properties incl. the organisation's tenant SiteId (label: Microsoft default 'General' family, no content marking). Options: leave; scrub the file in a new commit (HEAD only); purge from history (force-push).</t>
-  </si>
-  <si>
-    <t>repository history</t>
-  </si>
-  <si>
-    <t>Needs Boril: the choice involves his organisation's label and possibly rewriting pushed history. The tracker tools now strip MSIP labels on every write; the pre-push scan flags them.</t>
-  </si>
-  <si>
-    <t>SEC-022</t>
-  </si>
-  <si>
-    <t>Formatting rule values can't break out of a style</t>
-  </si>
-  <si>
-    <t>A rule value reaches the editor's style attribute, Word and PDF styles as text. The element-style and page-setting endpoints accepted any string (e.g. 'center;background-image:url(...)'), the AI instruction path too (FMT-005): CSS injection into every viewer's editor.</t>
-  </si>
-  <si>
-    <t>app/formatting/values.py: clean_rule_value per property (the StyleSystem's limits: choices, true/false, one safe font name, renderable colours, bounded numbers with known units, header/footer text &lt;=500). Refused with 422 by the element-style and page-setting endpoints (schemas RuleValue); instruction rules and set_style operations with such values dropped (FMT-005), validate_operations refuses them; stored rules no renderer can use are skipped at resolve (engine._usable) so old documents can't carry them either. All 177 default/template rules pass unchanged.</t>
-  </si>
-  <si>
-    <t>tests/test_rule_values.py (34 cases incl. API 422, stored-rule skip, instruction drop)</t>
-  </si>
-  <si>
-    <t>Found 2026-09-27 while mapping editor alignment (EDIT-008); probe confirmed the raw value in resolvedStyles.</t>
-  </si>
-  <si>
-    <t>PERF-001</t>
-  </si>
-  <si>
-    <t>Linear DOCX table export</t>
-  </si>
-  <si>
-    <t>500x8 table under a recorded threshold (baseline 321 s).</t>
-  </si>
-  <si>
-    <t>AUD-10</t>
-  </si>
-  <si>
-    <t>PERF-002</t>
-  </si>
-  <si>
-    <t>Benchmarks recorded</t>
-  </si>
-  <si>
-    <t>Baseline and current measurements in the PERFORMANCE sheet.</t>
-  </si>
-  <si>
-    <t>tests/perf</t>
-  </si>
-  <si>
-    <t>PERF-003</t>
-  </si>
-  <si>
-    <t>Delta autosave</t>
-  </si>
-  <si>
-    <t>Change-aware patches with a threshold strategy; whole document only when needed.</t>
-  </si>
-  <si>
-    <t>frontend/editor, backend/api</t>
-  </si>
-  <si>
-    <t>PERF-004</t>
-  </si>
-  <si>
-    <t>Bounded, compressed version history</t>
-  </si>
-  <si>
-    <t>Editor history separate from persisted versions; compression/deltas; asset references.</t>
-  </si>
-  <si>
-    <t>PERF-005</t>
-  </si>
-  <si>
-    <t>Editor at 5k-12k blocks</t>
-  </si>
-  <si>
-    <t>Typing latency measured and improved.</t>
-  </si>
-  <si>
-    <t>PERF-006</t>
-  </si>
-  <si>
-    <t>JSON without ASCII escaping</t>
-  </si>
-  <si>
-    <t>Document JSON stored and sent as UTF-8.</t>
-  </si>
-  <si>
-    <t>backend/db</t>
-  </si>
-  <si>
-    <t>PERF-007</t>
-  </si>
-  <si>
-    <t>Safe size limits recorded</t>
-  </si>
-  <si>
-    <t>User-facing maximum sizes, job timeouts, resource ceilings documented and enforced.</t>
-  </si>
-  <si>
-    <t>backend/config</t>
-  </si>
-  <si>
-    <t>AUD-09,AUD-10</t>
-  </si>
-  <si>
-    <t>ACCT-001</t>
-  </si>
-  <si>
-    <t>E-mail sender abstraction</t>
-  </si>
-  <si>
-    <t>SMTP provider + development outbox; no secrets in logs.</t>
-  </si>
-  <si>
-    <t>AUD-14</t>
-  </si>
-  <si>
-    <t>ACCT-002</t>
-  </si>
-  <si>
-    <t>Password reset</t>
-  </si>
-  <si>
-    <t>Single-use, expiring, hashed tokens; rate-limited; no account enumeration.</t>
-  </si>
-  <si>
-    <t>backend/api, frontend</t>
-  </si>
-  <si>
-    <t>ACCT-003</t>
-  </si>
-  <si>
-    <t>E-mail verification</t>
-  </si>
-  <si>
-    <t>Verification tokens and state.</t>
-  </si>
-  <si>
-    <t>ACCT-004</t>
-  </si>
-  <si>
-    <t>Password change</t>
-  </si>
-  <si>
-    <t>Current password required; other sessions revoked.</t>
-  </si>
-  <si>
-    <t>ACCT-005</t>
-  </si>
-  <si>
-    <t>Account deletion</t>
-  </si>
-  <si>
-    <t>Cascading policy: documents, versions, assets, exports, sessions, jobs, usage.</t>
-  </si>
-  <si>
-    <t>ACCT-006</t>
-  </si>
-  <si>
-    <t>Session revocation and cleanup</t>
-  </si>
-  <si>
-    <t>Sign out everywhere; expired/revoked session sweep.</t>
-  </si>
-  <si>
-    <t>ACCT-007</t>
-  </si>
-  <si>
-    <t>Suspicious login handling</t>
-  </si>
-  <si>
-    <t>Lockout and notification strategy.</t>
-  </si>
-  <si>
-    <t>PLAN-001</t>
-  </si>
-  <si>
-    <t>Usage units</t>
-  </si>
-  <si>
-    <t>Documents, exports, PDF pages, OCR pages, translation characters, AI operations, storage, batch jobs.</t>
-  </si>
-  <si>
-    <t>backend/billing</t>
-  </si>
-  <si>
-    <t>AUD-11</t>
-  </si>
-  <si>
-    <t>PLAN-002</t>
-  </si>
-  <si>
-    <t>Configurable plan defaults</t>
-  </si>
-  <si>
-    <t>Free/Pro/Business initial hypotheses as configuration, never hardcoded.</t>
-  </si>
-  <si>
-    <t>PLAN-003</t>
-  </si>
-  <si>
-    <t>Atomic entitlement checks</t>
-  </si>
-  <si>
-    <t>Reservation/locking; concurrency test proves limits hold.</t>
-  </si>
-  <si>
-    <t>PLAN-004</t>
-  </si>
-  <si>
-    <t>Stripe flows review</t>
-  </si>
-  <si>
-    <t>Checkout, portal, upgrade, downgrade, cancel, renewal, failed payment, webhook idempotency.</t>
-  </si>
-  <si>
-    <t>PLAN-005</t>
-  </si>
-  <si>
-    <t>Storage metering including history</t>
-  </si>
-  <si>
-    <t>History and autosave growth counted.</t>
-  </si>
-  <si>
-    <t>AUD-11,AUD-16</t>
-  </si>
-  <si>
-    <t>PDF-010</t>
-  </si>
-  <si>
-    <t>Geometry-aware PDF parser</t>
-  </si>
-  <si>
-    <t>Chars, fonts, sizes, colours, lines, rectangles, images, links, annotations, outlines, forms, metadata, rotation, page boxes.</t>
-  </si>
-  <si>
-    <t>backend/parsers/pdf</t>
-  </si>
-  <si>
-    <t>PDF-011</t>
-  </si>
-  <si>
-    <t>Page classifier</t>
-  </si>
-  <si>
-    <t>TEXT / SCANNED / HYBRID per page with evidence.</t>
-  </si>
-  <si>
-    <t>PDF-012</t>
-  </si>
-  <si>
-    <t>PDF inspection report</t>
-  </si>
-  <si>
-    <t>What the parser found, per page.</t>
-  </si>
-  <si>
-    <t>P2E-001</t>
-  </si>
-  <si>
-    <t>Layout primitives where PDF needs them</t>
-  </si>
-  <si>
-    <t>Page, block, bbox, rotation, confidence, provenance.</t>
-  </si>
-  <si>
-    <t>P2E-002</t>
-  </si>
-  <si>
-    <t>Structure reconstruction</t>
-  </si>
-  <si>
-    <t>Reading order, lines, paragraphs, headings, lists, captions, header/footer bands, columns.</t>
-  </si>
-  <si>
-    <t>backend/pdf</t>
-  </si>
-  <si>
-    <t>P2E-003</t>
-  </si>
-  <si>
-    <t>Images with position</t>
-  </si>
-  <si>
-    <t>Extracted images kept with bbox.</t>
-  </si>
-  <si>
-    <t>P2E-004</t>
-  </si>
-  <si>
-    <t>Tables from PDF</t>
-  </si>
-  <si>
-    <t>Ruling lines and alignment.</t>
-  </si>
-  <si>
-    <t>P2E-005</t>
-  </si>
-  <si>
-    <t>Confidence and conversion report</t>
-  </si>
-  <si>
-    <t>Per element confidence; issues reported; never silent removal.</t>
-  </si>
-  <si>
-    <t>P2E-006</t>
-  </si>
-  <si>
-    <t>OCR provider abstraction</t>
-  </si>
-  <si>
-    <t>Interface (text, confidence, bbox, page, language/script); implementation(s); OCR output untrusted.</t>
-  </si>
-  <si>
-    <t>backend/ocr</t>
-  </si>
-  <si>
-    <t>P2E-007</t>
-  </si>
-  <si>
-    <t>Imported-from-PDF version and UX</t>
-  </si>
-  <si>
-    <t>Editable document vs layout-focused choice; confidence shown.</t>
-  </si>
-  <si>
-    <t>frontend, backend</t>
-  </si>
-  <si>
-    <t>P2E-008</t>
-  </si>
-  <si>
-    <t>PDF fixtures and tests</t>
-  </si>
-  <si>
-    <t>Text, scanned, hybrid, tables, columns, multilingual.</t>
-  </si>
-  <si>
-    <t>P2E-020</t>
-  </si>
-  <si>
-    <t>Layout-preserving architecture</t>
-  </si>
-  <si>
-    <t>Frames/anchors model hooks and design doc.</t>
-  </si>
-  <si>
-    <t>docs, backend/models</t>
-  </si>
-  <si>
-    <t>PDF-020</t>
-  </si>
-  <si>
-    <t>PDF page operations service</t>
-  </si>
-  <si>
-    <t>Reorder, rotate, delete, duplicate, extract, split, merge as a separate service.</t>
-  </si>
-  <si>
-    <t>TRAN-001</t>
-  </si>
-  <si>
-    <t>Segments and tag protocol</t>
-  </si>
-  <si>
-    <t>Segments keep element/run ids, marks, placeholders; never one giant string.</t>
-  </si>
-  <si>
-    <t>backend/translation</t>
-  </si>
-  <si>
-    <t>TRAN-002</t>
-  </si>
-  <si>
-    <t>TranslationProvider abstraction</t>
-  </si>
-  <si>
-    <t>AI provider implementation + deterministic test provider.</t>
-  </si>
-  <si>
-    <t>TRAN-003</t>
-  </si>
-  <si>
-    <t>Translation validation</t>
-  </si>
-  <si>
-    <t>Tags, numbers, units, dates, percentages, identifiers, glossary terms.</t>
-  </si>
-  <si>
-    <t>TRAN-004</t>
-  </si>
-  <si>
-    <t>Glossary and terminology lock</t>
-  </si>
-  <si>
-    <t>Source/target term, domain, locked, case-sensitive.</t>
-  </si>
-  <si>
-    <t>backend/translation, db</t>
-  </si>
-  <si>
-    <t>TRAN-005</t>
-  </si>
-  <si>
-    <t>Selection/paragraph/block translation proposals</t>
-  </si>
-  <si>
-    <t>Preview; accept/reject; undo.</t>
-  </si>
-  <si>
-    <t>TRAN-003,REV-001</t>
-  </si>
-  <si>
-    <t>TRAN-006</t>
-  </si>
-  <si>
-    <t>Whole-document translated version</t>
-  </si>
-  <si>
-    <t>Source kept; translated copy linked.</t>
-  </si>
-  <si>
-    <t>TRAN-007</t>
-  </si>
-  <si>
-    <t>Language, script, direction metadata</t>
-  </si>
-  <si>
-    <t>Auto-detect + manual override.</t>
-  </si>
-  <si>
-    <t>TRAN-008</t>
-  </si>
-  <si>
-    <t>Translation UX</t>
-  </si>
-  <si>
-    <t>Toolbar/context Translate, target language, preview, accept/reject; 'AI-assisted translation - review required'.</t>
-  </si>
-  <si>
-    <t>TRAN-009</t>
-  </si>
-  <si>
-    <t>Translation metering</t>
-  </si>
-  <si>
-    <t>Translation characters as a usage unit.</t>
-  </si>
-  <si>
-    <t>TRAN-010</t>
-  </si>
-  <si>
-    <t>Translation tests</t>
-  </si>
-  <si>
-    <t>Formatting preservation, validation, versions.</t>
-  </si>
-  <si>
-    <t>FONT-001</t>
-  </si>
-  <si>
-    <t>Font catalogue with Unicode coverage</t>
-  </si>
-  <si>
-    <t>fontTools cmap coverage per script, metrics, embeddability.</t>
-  </si>
-  <si>
-    <t>backend/fonts</t>
-  </si>
-  <si>
-    <t>AUD-17</t>
-  </si>
-  <si>
-    <t>FONT-002</t>
-  </si>
-  <si>
-    <t>FontResolver</t>
-  </si>
-  <si>
-    <t>Script segmentation, coverage, fallback chain, embedding, RTL; deterministic first, AI suggestion validated.</t>
-  </si>
-  <si>
-    <t>FONT-003</t>
-  </si>
-  <si>
-    <t>Multilingual PDF rendering</t>
-  </si>
-  <si>
-    <t>Shaping for Arabic/Hebrew/Devanagari, bidi, CJK fonts, emoji handled gracefully.</t>
-  </si>
-  <si>
-    <t>FONT-004</t>
-  </si>
-  <si>
-    <t>DOCX per-script fonts</t>
-  </si>
-  <si>
-    <t>w:rFonts ascii/hAnsi/eastAsia/cs, w:lang, rtl/bidi.</t>
-  </si>
-  <si>
-    <t>FONT-005</t>
-  </si>
-  <si>
-    <t>Editor fallback stacks</t>
-  </si>
-  <si>
-    <t>CSS stacks from the resolver.</t>
-  </si>
-  <si>
-    <t>FONT-006</t>
-  </si>
-  <si>
-    <t>Multilingual tests</t>
-  </si>
-  <si>
-    <t>Script matrix x editor/DOCX/PDF with pdftotext and rendering.</t>
-  </si>
-  <si>
-    <t>FMT-001</t>
-  </si>
-  <si>
-    <t>Style extraction completeness</t>
-  </si>
-  <si>
-    <t>Page setup, margins, fonts, headings, lists, tables, captions, headers/footers, spacing, numbering, colours.</t>
-  </si>
-  <si>
-    <t>FMT-002</t>
-  </si>
-  <si>
-    <t>Semantic mapping validated</t>
-  </si>
-  <si>
-    <t>AI classifies/maps, engine applies; validation.</t>
-  </si>
-  <si>
-    <t>FMT-003</t>
-  </si>
-  <si>
-    <t>Before/after for Format by Example</t>
-  </si>
-  <si>
-    <t>Preview before saving a template.</t>
-  </si>
-  <si>
-    <t>FMT-005</t>
-  </si>
-  <si>
-    <t>Rule value validation</t>
-  </si>
-  <si>
-    <t>Instruction-path values validated before reaching CSS/export.</t>
-  </si>
-  <si>
-    <t>Instruction rules and set_style operations go through values.clean_rule_value: invalid ones dropped, normalised values stored (see SEC-022).</t>
-  </si>
-  <si>
-    <t>tests/test_rule_values.py::test_instructions_cannot_carry_such_values</t>
-  </si>
-  <si>
-    <t>HLTH-001</t>
-  </si>
-  <si>
-    <t>Health 2.0 checks</t>
-  </si>
-  <si>
-    <t>Alt text, hidden text, mixed language, unsupported features, section inconsistency, broken lists, empty paragraphs, layout anomalies, duplicated formatting, broken links.</t>
-  </si>
-  <si>
-    <t>HLTH-002</t>
-  </si>
-  <si>
-    <t>Deterministic fixes with preview</t>
-  </si>
-  <si>
-    <t>Fix proposals through the change model.</t>
-  </si>
-  <si>
-    <t>HLTH-003</t>
-  </si>
-  <si>
-    <t>AI explanations only</t>
-  </si>
-  <si>
-    <t>AI explains issues; never scores.</t>
-  </si>
-  <si>
-    <t>REV-002</t>
-  </si>
-  <si>
-    <t>Review Changes UI</t>
-  </si>
-  <si>
-    <t>Categories FORMAT/STRUCTURE/CONTENT/METADATA/PRESERVATION/TRANSLATION.</t>
-  </si>
-  <si>
-    <t>REV-003</t>
-  </si>
-  <si>
-    <t>Content changes need acceptance</t>
-  </si>
-  <si>
-    <t>Enforced server-side.</t>
-  </si>
-  <si>
-    <t>backend</t>
-  </si>
-  <si>
-    <t>REV-004</t>
-  </si>
-  <si>
-    <t>Repair</t>
-  </si>
-  <si>
-    <t>Detected issue, proposed fix, preview, apply.</t>
-  </si>
-  <si>
-    <t>REV-005</t>
-  </si>
-  <si>
-    <t>Clean copy</t>
-  </si>
-  <si>
-    <t>Explicit: remove comments, accept tracked changes, remove hidden text, remove metadata, normalise formatting.</t>
-  </si>
-  <si>
-    <t>FEAT-001</t>
-  </si>
-  <si>
-    <t>Batch formatting</t>
-  </si>
-  <si>
-    <t>One template/reference over many documents as jobs.</t>
-  </si>
-  <si>
-    <t>backend/jobs</t>
-  </si>
-  <si>
-    <t>FEAT-002</t>
-  </si>
-  <si>
-    <t>Batch export</t>
-  </si>
-  <si>
-    <t>Many documents to a zip.</t>
-  </si>
-  <si>
-    <t>FEAT-003</t>
-  </si>
-  <si>
-    <t>Batch translation</t>
-  </si>
-  <si>
-    <t>After the translation MVP.</t>
-  </si>
-  <si>
-    <t>FEAT-010</t>
-  </si>
-  <si>
-    <t>Accessibility checker</t>
-  </si>
-  <si>
-    <t>Heading hierarchy, alt text, link labels, table headers, reading order, language, contrast.</t>
-  </si>
-  <si>
-    <t>FEAT-011</t>
-  </si>
-  <si>
-    <t>App accessibility fixes</t>
-  </si>
-  <si>
-    <t>Zero serious axe violations on main pages and the editor.</t>
-  </si>
-  <si>
-    <t>JOB-001</t>
-  </si>
-  <si>
-    <t>Job safety</t>
-  </si>
-  <si>
-    <t>idempotency_key, retry_count, timeout, cancellation, stuck detection, backoff, dead-letter.</t>
-  </si>
-  <si>
-    <t>STOR-001</t>
-  </si>
-  <si>
-    <t>Storage retention and deletion</t>
-  </si>
-  <si>
-    <t>Source files, exports, OCR artifacts: retention, deletion, access control, content types, size limits.</t>
-  </si>
-  <si>
-    <t>OBS-001</t>
-  </si>
-  <si>
-    <t>Metrics</t>
-  </si>
-  <si>
-    <t>Latency, failure rate, job/AI/export metrics without content.</t>
-  </si>
-  <si>
-    <t>AUD-15</t>
-  </si>
-  <si>
-    <t>OBS-002</t>
-  </si>
-  <si>
-    <t>Operation and job IDs in logs</t>
-  </si>
-  <si>
-    <t>Request, operation and job IDs everywhere.</t>
-  </si>
-  <si>
-    <t>OBS-003</t>
-  </si>
-  <si>
-    <t>Operations data</t>
-  </si>
-  <si>
-    <t>Failed jobs, processing failures, usage spikes, AI/export failures, storage, abuse - minimal admin API.</t>
-  </si>
-  <si>
-    <t>INFRA-010</t>
-  </si>
-  <si>
-    <t>Deployment verified</t>
-  </si>
-  <si>
-    <t>Docker images build and start; Postgres, Redis, storage, worker, frontend, backend.</t>
-  </si>
-  <si>
-    <t>docker, CI</t>
-  </si>
-  <si>
-    <t>INFRA-011</t>
-  </si>
-  <si>
-    <t>CI gates</t>
-  </si>
-  <si>
-    <t>Backend, frontend, E2E, lint, typecheck, build, migrations, security audit, document fidelity tests.</t>
-  </si>
-  <si>
-    <t>.github/workflows</t>
-  </si>
-  <si>
-    <t>AUD-15,AUD-20</t>
-  </si>
-  <si>
-    <t>TEST-040</t>
-  </si>
-  <si>
-    <t>Playwright workflow coverage</t>
-  </si>
-  <si>
-    <t>The 24 workflows of the brief.</t>
-  </si>
-  <si>
-    <t>TEST-041</t>
-  </si>
-  <si>
-    <t>Performance gates</t>
-  </si>
-  <si>
-    <t>Regression thresholds relative to baseline.</t>
-  </si>
-  <si>
-    <t>TEST-043</t>
-  </si>
-  <si>
-    <t>Browser matrix</t>
-  </si>
-  <si>
-    <t>Chromium, Firefox, WebKit.</t>
-  </si>
-  <si>
-    <t>TEST-006</t>
-  </si>
-  <si>
-    <t>E2E backend removes its temp directory</t>
-  </si>
-  <si>
-    <t>scripts/e2e_server.py leaves %TEMP%/smartdoc-e2e-* behind after every Playwright run (10 found on 2026-09-27).</t>
-  </si>
-  <si>
-    <t>backend/scripts/e2e_server.py</t>
-  </si>
-  <si>
-    <t>DOCS-010</t>
-  </si>
-  <si>
-    <t>final-production-readiness.md</t>
-  </si>
-  <si>
-    <t>The 16-section final report.</t>
-  </si>
-  <si>
-    <t>DOCS-011</t>
-  </si>
-  <si>
-    <t>Documentation tree</t>
-  </si>
-  <si>
-    <t>docs/{architecture,document-model,docx,pdf,translation,ai,formatting,security,testing,deployment,billing,operations}.</t>
-  </si>
-  <si>
-    <t>Started with Phase 1: docs/document-model, docs/architecture/fidelity.md, docs/docx, docs/formatting, docs/security, docs/testing (each grounded in the code and tests of Phases 0-1). Remaining folders (pdf, translation, ai, deployment, billing, operations) as their phases land.; docs/ai/README.md added with Phase 2.</t>
-  </si>
-  <si>
-    <t>CRITICAL_FIXES — Audit findings and P0 tasks</t>
-  </si>
-  <si>
-    <t>The 20 findings of the 2026-09-26 audit (current known risks) with fix progress, then every P0 task. Report: https://claude.ai/artifact/WKskiyexTDLAHe1BfjvWR1 — a finding is RESOLVED when every linked fix task is DONE.</t>
-  </si>
-  <si>
-    <t>Findings</t>
-  </si>
-  <si>
-    <t>Resolved</t>
-  </si>
-  <si>
-    <t>Open</t>
-  </si>
-  <si>
-    <t>P0 tasks</t>
-  </si>
-  <si>
-    <t>P0 done</t>
-  </si>
-  <si>
-    <t>Audit findings (current known risks)</t>
-  </si>
-  <si>
-    <t>Finding ID</t>
-  </si>
-  <si>
-    <t>Progress</t>
-  </si>
-  <si>
-    <t>Finding</t>
-  </si>
-  <si>
-    <t>Fix Tasks</t>
-  </si>
-  <si>
-    <t>Active</t>
-  </si>
-  <si>
-    <t>Blocked/Failed</t>
-  </si>
-  <si>
-    <t>Editor save can discard nested blocks (lists, pictures, code, quotes inside cells/items)</t>
-  </si>
-  <si>
-    <t>EDIT-001,EDIT-002,EDIT-003,EDIT-005,EDIT-006</t>
-  </si>
-  <si>
-    <t>AI fidelity check misses omissions, negation removal, number changes, inserted text</t>
-  </si>
-  <si>
-    <t>AI-001,AI-002,AI-003,AI-004</t>
-  </si>
-  <si>
-    <t>Fixed in Phase 2 (AI-001..004): AI structure answers are checked token by token; any omission, negation removal, number/unit/date change, insertion, reordering, duplication or punctuation change is refused.</t>
-  </si>
-  <si>
-    <t>Import/export silently changes hidden text, numbering, section headers, metadata, alt text, structure</t>
-  </si>
-  <si>
-    <t>FID-002,DOCX-011,DOCX-013,DOCX-015,DOCX-025</t>
-  </si>
-  <si>
-    <t>List numbering changes ('Чл. 1.' -&gt; '1.', '(a)' -&gt; 'a.', start values)</t>
-  </si>
-  <si>
-    <t>Partly fixed in 622d9c1: list format/start/continuation kept; custom labels ('Чл. 1.', '(a)') and multi-level labels reported, not kept yet (DOCX-016).</t>
-  </si>
-  <si>
-    <t>AI instruction operations can delete/insert/move content without preview</t>
-  </si>
-  <si>
-    <t>AI-005,AI-006,AI-007,REV-003</t>
-  </si>
-  <si>
-    <t>Fixed in Phase 2 (AI-005..AI-007): an instruction's insert/delete/move is a proposal the user sees and accepts or rejects; nothing is deleted silently.</t>
-  </si>
-  <si>
-    <t>Content controls, metadata, comment threads, sensitivity information lost</t>
-  </si>
-  <si>
-    <t>DOCX-012,DOCX-021,DOCX-023</t>
-  </si>
-  <si>
-    <t>Image fidelity gaps: alt text, crop, rotation, formats</t>
-  </si>
-  <si>
-    <t>Table export changes header state, borders, alignment, widths, geometry</t>
-  </si>
-  <si>
-    <t>Large images cause huge memory consumption</t>
-  </si>
-  <si>
-    <t>SEC-012,SEC-013</t>
-  </si>
-  <si>
-    <t>Large tables have a performance problem</t>
-  </si>
-  <si>
-    <t>Plan limits have a concurrency race</t>
-  </si>
-  <si>
-    <t>Malformed DOCX leads to HTTP 500</t>
-  </si>
-  <si>
-    <t>SEC-010,SEC-019</t>
-  </si>
-  <si>
-    <t>Dangerous href/field instructions must be filtered</t>
-  </si>
-  <si>
-    <t>SEC-014,SEC-015,SEC-016</t>
-  </si>
-  <si>
-    <t>Account essentials missing: reset, verification, change, deletion</t>
-  </si>
-  <si>
-    <t>ACCT-002,ACCT-003,ACCT-004,ACCT-005</t>
-  </si>
-  <si>
-    <t>Operations/monitoring must be confirmed</t>
-  </si>
-  <si>
-    <t>OBS-001,OBS-002,INFRA-010</t>
-  </si>
-  <si>
-    <t>Whole-document autosave must be optimised</t>
-  </si>
-  <si>
-    <t>PERF-003,PERF-004</t>
-  </si>
-  <si>
-    <t>PDF multilingual rendering must be reliable</t>
-  </si>
-  <si>
-    <t>FONT-003,FONT-006</t>
-  </si>
-  <si>
-    <t>Export metadata must be correct</t>
-  </si>
-  <si>
-    <t>DOCX-012,DOCX-020</t>
-  </si>
-  <si>
-    <t>Partly fixed in 622d9c1: Word exports carry the source file's core properties (author, dates, subject...) instead of 'python-docx'/2013; fields remain (DOCX-020).</t>
-  </si>
-  <si>
-    <t>AUD-19</t>
-  </si>
-  <si>
-    <t>Canonical model must represent more than paragraphs + runs + simple tables</t>
-  </si>
-  <si>
-    <t>CORE-001,DOCX-015,DOCX-016,DOCX-017</t>
-  </si>
-  <si>
-    <t>Tests can miss import-side data loss (model-relative comparison)</t>
-  </si>
-  <si>
-    <t>TEST-020,TEST-021,TEST-022</t>
-  </si>
-  <si>
-    <t>P0 tasks (live from MASTER)</t>
-  </si>
-  <si>
-    <t>DOCUMENT_FIDELITY — Content preservation</t>
-  </si>
-  <si>
-    <t>Canonical model, fidelity reports, capability matrix, change/review model. Categories: CORE, FIDELITY, REVIEW. Rows are formulas over MASTER — change task data in MASTER or with tools/tracker/tracker.py.</t>
-  </si>
-  <si>
-    <t>Tasks (live from MASTER)</t>
-  </si>
-  <si>
-    <t>DOCX_OOXML — DOCX / OOXML preservation</t>
-  </si>
-  <si>
-    <t>Import and export fidelity for Word documents. Categories: DOCX. Rows are formulas over MASTER — change task data in MASTER or with tools/tracker/tracker.py.</t>
-  </si>
-  <si>
-    <t>PDF — PDF engine</t>
-  </si>
-  <si>
-    <t>PDF export and PDF parsing. Categories: PDF. Rows are formulas over MASTER — change task data in MASTER or with tools/tracker/tracker.py.</t>
-  </si>
-  <si>
-    <t>EDITOR — Editor integrity</t>
-  </si>
-  <si>
-    <t>Tiptap mapping and save integrity. Categories: EDITOR. Rows are formulas over MASTER — change task data in MASTER or with tools/tracker/tracker.py.</t>
-  </si>
-  <si>
-    <t>FORMATTING — Formatting and Document Health</t>
-  </si>
-  <si>
-    <t>Formatting engine, Format by Example, Document Health. Categories: FORMATTING, HEALTH. Rows are formulas over MASTER — change task data in MASTER or with tools/tracker/tracker.py.</t>
-  </si>
-  <si>
-    <t>AI — AI fidelity</t>
-  </si>
-  <si>
-    <t>Fidelity checks, proposals and review, budgets. Categories: AI. Rows are formulas over MASTER — change task data in MASTER or with tools/tracker/tracker.py.</t>
-  </si>
-  <si>
-    <t>SECURITY — Security and accounts</t>
-  </si>
-  <si>
-    <t>Security hardening and account essentials. Categories: SECURITY, ACCOUNT. Rows are formulas over MASTER — change task data in MASTER or with tools/tracker/tracker.py.</t>
-  </si>
-  <si>
-    <t>PERFORMANCE — Performance</t>
-  </si>
-  <si>
-    <t>Measured results — brief §80-81: measure, then set regression thresholds relative to the baseline (no invented SLOs)</t>
-  </si>
-  <si>
-    <t>Bench ID</t>
-  </si>
-  <si>
-    <t>Metric</t>
-  </si>
-  <si>
-    <t>Unit</t>
-  </si>
-  <si>
-    <t>Scenario</t>
-  </si>
-  <si>
-    <t>Baseline</t>
-  </si>
-  <si>
-    <t>Baseline Source</t>
-  </si>
-  <si>
-    <t>Current</t>
-  </si>
-  <si>
-    <t>Measured On</t>
-  </si>
-  <si>
-    <t>Threshold</t>
-  </si>
-  <si>
-    <t>BENCH-001</t>
-  </si>
-  <si>
-    <t>duration</t>
-  </si>
-  <si>
-    <t>s</t>
-  </si>
-  <si>
-    <t>DOCX export: table 500x8 (4,000 cells)</t>
-  </si>
-  <si>
-    <t>audit perf_table.py (400 cells 3.8 s; 1,600 cells 53.7 s; quadratic)</t>
-  </si>
-  <si>
-    <t>BENCH-002</t>
-  </si>
-  <si>
-    <t>PDF export: table 500x8</t>
-  </si>
-  <si>
-    <t>audit perf_table.py (linear)</t>
-  </si>
-  <si>
-    <t>BENCH-003</t>
-  </si>
-  <si>
-    <t>Import: 300-page text DOCX (1,650 elements)</t>
-  </si>
-  <si>
-    <t>audit perf_backend.py</t>
-  </si>
-  <si>
-    <t>BENCH-004</t>
-  </si>
-  <si>
-    <t>DOCX export: 300-page text document</t>
-  </si>
-  <si>
-    <t>BENCH-005</t>
-  </si>
-  <si>
-    <t>PDF export: 300-page text document</t>
-  </si>
-  <si>
-    <t>BENCH-006</t>
-  </si>
-  <si>
-    <t>memory growth</t>
-  </si>
-  <si>
-    <t>MB</t>
-  </si>
-  <si>
-    <t>PDF export: 39 KB DOCX holding a 12000x12000 PNG</t>
-  </si>
-  <si>
-    <t>audit pixel_bomb.py (14000x14000 crashes the export)</t>
-  </si>
-  <si>
-    <t>BENCH-007</t>
-  </si>
-  <si>
-    <t>PDF export: 4 JPEG images 2400x1800</t>
-  </si>
-  <si>
-    <t>audit perf_backend.py (6.3 s)</t>
-  </si>
-  <si>
-    <t>BENCH-008</t>
-  </si>
-  <si>
-    <t>Editor: type 20 characters at 12,196 elements (1M-character paste)</t>
-  </si>
-  <si>
-    <t>audit perf_browser.js (~470 ms per key)</t>
-  </si>
-  <si>
-    <t>BENCH-009</t>
-  </si>
-  <si>
-    <t>Editor: type 20 characters, 300-page document</t>
-  </si>
-  <si>
-    <t>audit perf_browser.js</t>
-  </si>
-  <si>
-    <t>BENCH-010</t>
-  </si>
-  <si>
-    <t>request size</t>
-  </si>
-  <si>
-    <t>Autosave request: 300-page document</t>
-  </si>
-  <si>
-    <t>audit perf_browser.js (whole elements list per save)</t>
-  </si>
-  <si>
-    <t>BENCH-011</t>
-  </si>
-  <si>
-    <t>Autosave request: 1M-character paste</t>
-  </si>
-  <si>
-    <t>BENCH-012</t>
-  </si>
-  <si>
-    <t>storage</t>
-  </si>
-  <si>
-    <t>Stored history: one 300-page document, 50 steps</t>
-  </si>
-  <si>
-    <t>audit (2.8 MB per full copy; 7.2 MB when the JSON is ASCII-escaped)</t>
-  </si>
-  <si>
-    <t>BENCH-013</t>
-  </si>
-  <si>
-    <t>Paste: 2M characters (the cap)</t>
-  </si>
-  <si>
-    <t>audit perf_backend.py (17.5k elements, 7.1 MB JSON)</t>
-  </si>
-  <si>
-    <t>Performance tasks (live from MASTER)</t>
-  </si>
-  <si>
-    <t>TESTING — Testing</t>
-  </si>
-  <si>
-    <t>Test runs (oldest first)</t>
-  </si>
-  <si>
-    <t>Run ID</t>
-  </si>
-  <si>
-    <t>Command</t>
-  </si>
-  <si>
-    <t>Passed</t>
-  </si>
-  <si>
-    <t>Skipped</t>
-  </si>
-  <si>
-    <t>Date</t>
-  </si>
-  <si>
-    <t>Duration (s)</t>
-  </si>
-  <si>
-    <t>RUN-0001</t>
-  </si>
-  <si>
-    <t>backend-pytest</t>
-  </si>
-  <si>
-    <t>PASS</t>
-  </si>
-  <si>
-    <t>cd backend &amp;&amp; venv/Scripts/python -m pytest -q -p no:cacheprovider</t>
-  </si>
-  <si>
-    <t>Skip: optional real-Word check (SMARTDOC_REAL_DOCX unset). 1 DeprecationWarning (starlette/anyio). Audit measured 93% line coverage on 2026-09-26.</t>
-  </si>
-  <si>
-    <t>ea69829</t>
-  </si>
-  <si>
-    <t>RUN-0002</t>
-  </si>
-  <si>
-    <t>frontend-lint</t>
-  </si>
-  <si>
-    <t>cd frontend &amp;&amp; npm run lint</t>
-  </si>
-  <si>
-    <t>eslint: 0 problems</t>
-  </si>
-  <si>
-    <t>RUN-0003</t>
-  </si>
-  <si>
-    <t>frontend-tsc</t>
-  </si>
-  <si>
-    <t>cd frontend &amp;&amp; npx tsc --noEmit</t>
-  </si>
-  <si>
-    <t>0 type errors</t>
-  </si>
-  <si>
-    <t>RUN-0004</t>
-  </si>
-  <si>
-    <t>frontend-vitest</t>
-  </si>
-  <si>
-    <t>cd frontend &amp;&amp; npm test</t>
-  </si>
-  <si>
-    <t>6 test files</t>
-  </si>
-  <si>
-    <t>RUN-0005</t>
-  </si>
-  <si>
-    <t>frontend-build</t>
-  </si>
-  <si>
-    <t>cd frontend &amp;&amp; npm run build</t>
-  </si>
-  <si>
-    <t>Next.js production build, 11 routes</t>
-  </si>
-  <si>
-    <t>RUN-0006</t>
-  </si>
-  <si>
-    <t>e2e-playwright</t>
-  </si>
-  <si>
-    <t>cd frontend &amp;&amp; npm run test:e2e</t>
-  </si>
-  <si>
-    <t>Edge; throwaway backend on SQLite (:8100) + production build (:3100). 16 workflows in 5 spec files; the brief asks for 24 (TEST-040). Leaves %TEMP%/smartdoc-e2e-* dirs behind (TEST-006).</t>
-  </si>
-  <si>
-    <t>RUN-0007</t>
-  </si>
-  <si>
-    <t>migrations</t>
-  </si>
-  <si>
-    <t>alembic upgrade head &amp;&amp; alembic check &amp;&amp; alembic downgrade base &amp;&amp; alembic upgrade head (scratch SQLite); alembic upgrade head --sql (PostgreSQL dialect)</t>
-  </si>
-  <si>
-    <t>head 85211092fe4c; 'No new upgrade operations detected'; offline SQL: 14 tables at head, RLS enabled on every table</t>
-  </si>
-  <si>
-    <t>RUN-0008</t>
-  </si>
-  <si>
-    <t>supabase</t>
-  </si>
-  <si>
-    <t>Supabase MCP: list_migrations, get_advisors security+performance, list_tables (project edmmjmsynjziahwtjuke)</t>
-  </si>
-  <si>
-    <t>8/8 migrations applied; 14 tables, RLS on all; advisors only INFO: 14x rls_enabled_no_policy (by design: the API connects as owner, PostgREST roles see nothing), 8x unused_index (low traffic)</t>
-  </si>
-  <si>
-    <t>RUN-0009</t>
-  </si>
-  <si>
-    <t>pip-audit</t>
-  </si>
-  <si>
-    <t>uvx pip-audit --disable-pip -r backend/requirements.lock; same for requirements-dev.lock</t>
-  </si>
-  <si>
-    <t>No known vulnerabilities in either lock file</t>
-  </si>
-  <si>
-    <t>RUN-0010</t>
-  </si>
-  <si>
-    <t>npm-audit</t>
-  </si>
-  <si>
-    <t>cd frontend &amp;&amp; npm audit; npm audit --omit=dev</t>
-  </si>
-  <si>
-    <t>0 vulnerabilities across 633 dependencies</t>
-  </si>
-  <si>
-    <t>RUN-0011</t>
-  </si>
-  <si>
-    <t>docker-compose</t>
-  </si>
-  <si>
-    <t>PARTIAL</t>
-  </si>
-  <si>
-    <t>docker compose config --quiet</t>
-  </si>
-  <si>
-    <t>compose file valid (8 services: postgres, redis, minio, minio-bucket, migrate, worker, backend, frontend); images NOT built: Docker daemon not running on this machine (CI builds them on main)</t>
-  </si>
-  <si>
-    <t>RUN-0012</t>
-  </si>
-  <si>
-    <t>Phase 1 editor integrity: +16 tests (nesting model, nested API/exports, health links)</t>
-  </si>
-  <si>
-    <t>RUN-0013</t>
-  </si>
-  <si>
-    <t>cd frontend &amp;&amp; npx vitest run</t>
-  </si>
-  <si>
-    <t>+31: nestedBlocks.test.ts (28), useAutoSave.test.tsx (3); tsc and eslint clean</t>
-  </si>
-  <si>
-    <t>RUN-0014</t>
-  </si>
-  <si>
-    <t>cd frontend &amp;&amp; npx playwright test</t>
-  </si>
-  <si>
-    <t>+1: e2e/nested.spec.ts (paste, autosave, reload)</t>
-  </si>
-  <si>
-    <t>RUN-0015</t>
-  </si>
-  <si>
-    <t>+29 test_fidelity_report.py</t>
-  </si>
-  <si>
-    <t>RUN-0016</t>
-  </si>
-  <si>
-    <t>+3 FidelityPanel.test.tsx</t>
-  </si>
-  <si>
-    <t>RUN-0017</t>
-  </si>
-  <si>
-    <t>+fidelity.spec.ts; nested.spec.ts made deterministic (focus check, Ctrl+End) after one run pasted at the document start</t>
-  </si>
-  <si>
-    <t>RUN-0018</t>
-  </si>
-  <si>
-    <t>+6 test_export_fidelity.py</t>
-  </si>
-  <si>
-    <t>RUN-0019</t>
-  </si>
-  <si>
-    <t>+4 ExportResult.test.tsx</t>
-  </si>
-  <si>
-    <t>RUN-0020</t>
-  </si>
-  <si>
-    <t>export test checks the export's content message</t>
-  </si>
-  <si>
-    <t>RUN-0021</t>
-  </si>
-  <si>
-    <t>+6 test_capabilities.py</t>
-  </si>
-  <si>
-    <t>RUN-0022</t>
-  </si>
-  <si>
-    <t>venv/Scripts/python -m pytest -q</t>
-  </si>
-  <si>
-    <t>after FID-002 detections + section break fix</t>
-  </si>
-  <si>
-    <t>RUN-0023</t>
-  </si>
-  <si>
-    <t>npx vitest run</t>
-  </si>
-  <si>
-    <t>tsc --noEmit and eslint clean too</t>
-  </si>
-  <si>
-    <t>RUN-0024</t>
-  </si>
-  <si>
-    <t>rule values (SEC-022) + editor direct styles</t>
-  </si>
-  <si>
-    <t>RUN-0025</t>
-  </si>
-  <si>
-    <t>tsc + eslint clean</t>
-  </si>
-  <si>
-    <t>RUN-0026</t>
-  </si>
-  <si>
-    <t>e2e</t>
-  </si>
-  <si>
-    <t>npx playwright test</t>
-  </si>
-  <si>
-    <t>incl. e2e/direct-formatting.spec.ts</t>
-  </si>
-  <si>
-    <t>RUN-0027</t>
-  </si>
-  <si>
-    <t>Phase 1 gate: link titles, mark order, Markdown pictures/rules</t>
-  </si>
-  <si>
-    <t>RUN-0028</t>
-  </si>
-  <si>
-    <t>Phase 1 gate; tsc + eslint clean</t>
-  </si>
-  <si>
-    <t>RUN-0029</t>
-  </si>
-  <si>
-    <t>Phase 1 gate</t>
-  </si>
-  <si>
-    <t>RUN-0030</t>
-  </si>
-  <si>
-    <t>AI fidelity check (AI-001..004)</t>
-  </si>
-  <si>
-    <t>RUN-0031</t>
-  </si>
-  <si>
-    <t>AI proposals</t>
-  </si>
-  <si>
-    <t>RUN-0032</t>
-  </si>
-  <si>
-    <t>RUN-0033</t>
-  </si>
-  <si>
-    <t>incl. e2e/proposals.spec.ts</t>
-  </si>
-  <si>
-    <t>RUN-0034</t>
-  </si>
-  <si>
-    <t>AI budget</t>
-  </si>
-  <si>
-    <t>RUN-0035</t>
-  </si>
-  <si>
-    <t>prompt-injection review</t>
-  </si>
-  <si>
-    <t>RUN-0036</t>
-  </si>
-  <si>
-    <t>Phase 2 gate</t>
-  </si>
-  <si>
-    <t>RUN-0037</t>
-  </si>
-  <si>
-    <t>RUN-0038</t>
-  </si>
-  <si>
-    <t>source package + patch writer</t>
-  </si>
-  <si>
-    <t>RUN-0039</t>
-  </si>
-  <si>
-    <t>after the patch writer</t>
-  </si>
-  <si>
-    <t>RUN-0040</t>
-  </si>
-  <si>
-    <t>backend pytest</t>
-  </si>
-  <si>
-    <t>DOCX-028: test_original_blocks.py (26), golden set of 13</t>
-  </si>
-  <si>
-    <t>7f22bf9</t>
-  </si>
-  <si>
-    <t>RUN-0041</t>
-  </si>
-  <si>
-    <t>frontend vitest</t>
-  </si>
-  <si>
-    <t>editor round trip includes 13-kept-blocks</t>
-  </si>
-  <si>
-    <t>RUN-0042</t>
-  </si>
-  <si>
-    <t>playwright</t>
-  </si>
-  <si>
-    <t>new e2e/kept-blocks.spec.ts</t>
-  </si>
-  <si>
-    <t>RUN-0043</t>
-  </si>
-  <si>
-    <t>tsc + eslint</t>
-  </si>
-  <si>
-    <t>cd frontend &amp;&amp; npx tsc --noEmit &amp;&amp; npx eslint .</t>
-  </si>
-  <si>
-    <t>0 type errors, 0 lint problems</t>
-  </si>
-  <si>
-    <t>RUN-0044</t>
-  </si>
-  <si>
-    <t>DOCX-025: tests/test_hidden_text.py (7)</t>
-  </si>
-  <si>
-    <t>fada4d7</t>
-  </si>
-  <si>
-    <t>RUN-0045</t>
-  </si>
-  <si>
-    <t>editor/hiddenText.test.tsx (6)</t>
-  </si>
-  <si>
-    <t>RUN-0046</t>
-  </si>
-  <si>
-    <t>new e2e/hidden-text.spec.ts</t>
-  </si>
-  <si>
-    <t>RUN-0047</t>
-  </si>
-  <si>
-    <t>RUN-0048</t>
-  </si>
-  <si>
-    <t>DOCX-013 part 1: tests/test_character_formatting.py (12)</t>
-  </si>
-  <si>
-    <t>c51b1bf</t>
-  </si>
-  <si>
-    <t>RUN-0049</t>
-  </si>
-  <si>
-    <t>editor/characterFormatting.test.ts (3)</t>
-  </si>
-  <si>
-    <t>RUN-0050</t>
-  </si>
-  <si>
-    <t>after DOCX-013 part 1</t>
-  </si>
-  <si>
-    <t>RUN-0051</t>
-  </si>
-  <si>
-    <t>RUN-0052</t>
-  </si>
-  <si>
-    <t>DOCX-013 part 2 + FID-007: tests/test_copy_reports.py (6)</t>
-  </si>
-  <si>
-    <t>309f9d6</t>
-  </si>
-  <si>
-    <t>RUN-0053</t>
-  </si>
-  <si>
-    <t>characterFormatting.test.ts (4)</t>
-  </si>
-  <si>
-    <t>RUN-0054</t>
-  </si>
-  <si>
-    <t>after DOCX-013 part 2</t>
-  </si>
-  <si>
-    <t>RUN-0055</t>
-  </si>
-  <si>
-    <t>Testing tasks (live from MASTER)</t>
-  </si>
-  <si>
-    <t>PRODUCT_FEATURES — Product features</t>
-  </si>
-  <si>
-    <t>Feature backlog — brief §61-62</t>
-  </si>
-  <si>
-    <t>Feature</t>
-  </si>
-  <si>
-    <t>Bucket</t>
-  </si>
-  <si>
-    <t>Linked Tasks</t>
-  </si>
-  <si>
-    <t>Linked Done</t>
-  </si>
-  <si>
-    <t>Linked Total</t>
-  </si>
-  <si>
-    <t>Document integrity</t>
-  </si>
-  <si>
-    <t>NOW</t>
-  </si>
-  <si>
-    <t>EDIT-001,EDIT-005,FID-002</t>
-  </si>
-  <si>
-    <t>Brief 62: NOW #1</t>
-  </si>
-  <si>
-    <t>Fidelity</t>
-  </si>
-  <si>
-    <t>DOCX-011,TEST-022</t>
-  </si>
-  <si>
-    <t>Brief 62: NOW #2</t>
-  </si>
-  <si>
-    <t>Security</t>
-  </si>
-  <si>
-    <t>SEC-010,SEC-012,SEC-014</t>
-  </si>
-  <si>
-    <t>Brief 62: NOW #3</t>
-  </si>
-  <si>
-    <t>Performance</t>
-  </si>
-  <si>
-    <t>PERF-001,PERF-003,PERF-004</t>
-  </si>
-  <si>
-    <t>Brief 62: NOW #4</t>
-  </si>
-  <si>
-    <t>PDF -&gt; editable</t>
-  </si>
-  <si>
-    <t>P2E-002,P2E-005</t>
-  </si>
-  <si>
-    <t>Brief 62: NOW #5</t>
-  </si>
-  <si>
-    <t>TRAN-001,TRAN-006</t>
-  </si>
-  <si>
-    <t>Brief 62: NOW #6</t>
-  </si>
-  <si>
-    <t>FONT-002,FONT-003</t>
-  </si>
-  <si>
-    <t>Brief 62: NOW #7</t>
-  </si>
-  <si>
-    <t>Review Changes</t>
-  </si>
-  <si>
-    <t>REV-001,REV-002</t>
-  </si>
-  <si>
-    <t>Brief 62: NOW #8</t>
-  </si>
-  <si>
-    <t>HLTH-001,HLTH-002</t>
-  </si>
-  <si>
-    <t>Brief 62: NOW #9</t>
-  </si>
-  <si>
-    <t>FMT-001,FMT-002,FMT-003</t>
-  </si>
-  <si>
-    <t>Brief 62: NOW #10</t>
-  </si>
-  <si>
-    <t>OCR</t>
-  </si>
-  <si>
-    <t>Part of PDF -&gt; editable (brief 43)</t>
-  </si>
-  <si>
-    <t>Multilingual support</t>
-  </si>
-  <si>
-    <t>TRAN-007,FONT-003</t>
-  </si>
-  <si>
-    <t>Part of translation + FontResolver</t>
-  </si>
-  <si>
-    <t>RTL</t>
-  </si>
-  <si>
-    <t>FONT-003,FONT-004</t>
-  </si>
-  <si>
-    <t>Part of FontResolver</t>
-  </si>
-  <si>
-    <t>CJK</t>
-  </si>
-  <si>
-    <t>Glossary</t>
-  </si>
-  <si>
-    <t>Part of translation MVP (brief 49)</t>
-  </si>
-  <si>
-    <t>Terminology lock</t>
-  </si>
-  <si>
-    <t>Citation preservation</t>
-  </si>
-  <si>
-    <t>Preservation is fidelity work; a citation editor is LATER</t>
-  </si>
-  <si>
-    <t>Bibliography preservation</t>
-  </si>
-  <si>
-    <t>Preservation is fidelity work</t>
-  </si>
-  <si>
-    <t>Content controls</t>
-  </si>
-  <si>
-    <t>Preserve now; editing content controls NEXT</t>
-  </si>
-  <si>
-    <t>Custom fields</t>
-  </si>
-  <si>
-    <t>Preserve custom properties and fields now; an editor NEXT</t>
-  </si>
-  <si>
-    <t>Document compare</t>
-  </si>
-  <si>
-    <t>NEXT</t>
-  </si>
-  <si>
-    <t>Brief 62: NEXT</t>
-  </si>
-  <si>
-    <t>Version compare</t>
-  </si>
-  <si>
-    <t>Brief 62: NEXT (batch processing)</t>
-  </si>
-  <si>
-    <t>After the translation MVP</t>
-  </si>
-  <si>
-    <t>Table repair</t>
-  </si>
-  <si>
-    <t>List repair</t>
-  </si>
-  <si>
-    <t>Brief 62: NEXT (accessibility)</t>
-  </si>
-  <si>
-    <t>Heading hierarchy checker</t>
-  </si>
-  <si>
-    <t>Link checker</t>
-  </si>
-  <si>
-    <t>Alt-text checker</t>
-  </si>
-  <si>
-    <t>HLTH-001,FEAT-010</t>
-  </si>
-  <si>
-    <t>Metadata editor</t>
-  </si>
-  <si>
-    <t>Global style replacement</t>
-  </si>
-  <si>
-    <t>Find/replace with formatting</t>
-  </si>
-  <si>
-    <t>Tracked change cleanup</t>
-  </si>
-  <si>
-    <t>Template extraction</t>
-  </si>
-  <si>
-    <t>Document-to-template</t>
-  </si>
-  <si>
-    <t>Template matching</t>
-  </si>
-  <si>
-    <t>Advanced template sharing</t>
-  </si>
-  <si>
-    <t>Teams</t>
-  </si>
-  <si>
-    <t>Translation memory</t>
-  </si>
-  <si>
-    <t>PDF merge/split</t>
-  </si>
-  <si>
-    <t>Page reorder</t>
-  </si>
-  <si>
-    <t>Page rotate</t>
-  </si>
-  <si>
-    <t>Page delete</t>
-  </si>
-  <si>
-    <t>Page extract</t>
-  </si>
-  <si>
-    <t>Merge documents</t>
-  </si>
-  <si>
-    <t>LATER</t>
-  </si>
-  <si>
-    <t>Split documents</t>
-  </si>
-  <si>
-    <t>Watermark</t>
-  </si>
-  <si>
-    <t>Forms (advanced)</t>
-  </si>
-  <si>
-    <t>Brief 62: LATER</t>
-  </si>
-  <si>
-    <t>SmartArt editing</t>
-  </si>
-  <si>
-    <t>Brief 62: LATER; SmartArt is preserved, not edited</t>
-  </si>
-  <si>
-    <t>OLE</t>
-  </si>
-  <si>
-    <t>Brief 62: LATER; OLE objects preserved, not edited</t>
-  </si>
-  <si>
-    <t>Full tracked-change editor</t>
-  </si>
-  <si>
-    <t>Advanced citation manager</t>
-  </si>
-  <si>
-    <t>Advanced drawing editor</t>
-  </si>
-  <si>
-    <t>Layout-preserving PDF editing (frames/anchors)</t>
-  </si>
-  <si>
-    <t>ARCHITECTURE_ONLY</t>
-  </si>
-  <si>
-    <t>Phase 9: architecture and hooks only</t>
-  </si>
-  <si>
-    <t>Product tasks (live from MASTER)</t>
-  </si>
-  <si>
-    <t>TRANSLATION — Translation and fonts</t>
-  </si>
-  <si>
-    <t>Translation MVP and FontResolver. Categories: TRANSLATION, FONT. Rows are formulas over MASTER — change task data in MASTER or with tools/tracker/tracker.py.</t>
-  </si>
-  <si>
-    <t>PDF_TO_EDITABLE — PDF to editable</t>
-  </si>
-  <si>
-    <t>PDF to editable document conversion. Categories: P2E. Rows are formulas over MASTER — change task data in MASTER or with tools/tracker/tracker.py.</t>
-  </si>
-  <si>
-    <t>BILLING_PLANS — Plans and billing</t>
-  </si>
-  <si>
-    <t>Initial plan hypothesis — brief §64: configurable defaults, not final prices; confirm against measured AI and infrastructure cost. Blue = input.</t>
-  </si>
-  <si>
-    <t>Usage unit / feature</t>
-  </si>
-  <si>
-    <t>FREE</t>
-  </si>
-  <si>
-    <t>PRO</t>
-  </si>
-  <si>
-    <t>BUSINESS</t>
-  </si>
-  <si>
-    <t>Documents / month</t>
-  </si>
-  <si>
-    <t>BUSINESS: per workspace</t>
-  </si>
-  <si>
-    <t>PDF conversion pages / month</t>
-  </si>
-  <si>
-    <t>OCR pages / month</t>
-  </si>
-  <si>
-    <t>Translation characters / month</t>
-  </si>
-  <si>
-    <t>AI operations / month</t>
-  </si>
-  <si>
-    <t>Exports / month</t>
-  </si>
-  <si>
-    <t>high</t>
-  </si>
-  <si>
-    <t>BUSINESS: 'high export limits', no number given</t>
-  </si>
-  <si>
-    <t>Templates</t>
-  </si>
-  <si>
-    <t>basic</t>
-  </si>
-  <si>
-    <t>custom</t>
-  </si>
-  <si>
-    <t>shared</t>
-  </si>
-  <si>
-    <t>Formatting</t>
-  </si>
-  <si>
-    <t>Format by Example</t>
-  </si>
-  <si>
-    <t>-</t>
-  </si>
-  <si>
-    <t>Advanced Document Health</t>
-  </si>
-  <si>
-    <t>yes</t>
-  </si>
-  <si>
-    <t>Version history</t>
-  </si>
-  <si>
-    <t>no</t>
-  </si>
-  <si>
-    <t>reasonable limits</t>
-  </si>
-  <si>
-    <t>Team workspace</t>
-  </si>
-  <si>
-    <t>Priority processing</t>
-  </si>
-  <si>
-    <t>Advanced controls</t>
-  </si>
-  <si>
-    <t>Billing and plan tasks (live from MASTER)</t>
-  </si>
-  <si>
-    <t>INFRA — Infrastructure</t>
-  </si>
-  <si>
-    <t>Tracker, jobs, storage, observability, deployment, documentation. Categories: INFRA, JOBS, STORAGE, OBSERVABILITY, DOCS. Rows are formulas over MASTER — change task data in MASTER or with tools/tracker/tracker.py.</t>
-  </si>
-  <si>
-    <t>Timestamp</t>
-  </si>
-  <si>
-    <t>Task ID</t>
-  </si>
-  <si>
-    <t>Change</t>
-  </si>
-  <si>
-    <t>Files</t>
-  </si>
-  <si>
-    <t>Created SmartDoc_Master_Implementation_Tracker.xlsx from the 2026-09-26 audit findings and the brief's phases: 151 tasks, 20 findings, 15 release gates.</t>
-  </si>
-  <si>
-    <t>tools/tracker/tracker.py, tools/tracker/seed.py</t>
-  </si>
-  <si>
-    <t>N/A</t>
-  </si>
-  <si>
-    <t>Built the Excel control centre: MASTER with 151 stable-ID tasks from the audit findings and the brief's 19 phases, CRITICAL_FIXES (20 findings -&gt; fix tasks, live status), 14 category views, DASHBOARD (totals, completion/verified %, phase %, category %, P0/P1 remaining), CHANGE_LOG, SESSION_STATE, RELEASE_GATES GATE-001..015. Formulas verified in Excel against independently computed values.</t>
-  </si>
-  <si>
-    <t>tools/tracker/*, SmartDoc_Master_Implementation_Tracker.xlsx, .gitignore</t>
-  </si>
-  <si>
-    <t>Resume reminder set with the platform scheduler; it fired and resumed the work. It only fires while this session is open and idle, which is recorded in AI-CONTINUATION.md.</t>
-  </si>
-  <si>
-    <t>Created the checkpoint system: AI-CONTINUATION.md with CURRENT STATE / LAST VERIFIED / WHAT WAS CHANGED / WHAT PASSED / WHAT FAILED / WHAT REMAINS / NEXT ACTION / IMPORTANT WARNINGS, session-state.json mirrored into SESSION_STATE by tracker.py state, and the brief saved verbatim for future sessions.</t>
-  </si>
-  <si>
-    <t>docs/AI-CONTINUATION.md, docs/session-state.json, docs/implementation-brief.md</t>
-  </si>
-  <si>
-    <t>Baseline backend suite: 643 passed, 1 skipped (optional real-Word check), 0 failed in 88 s on ea69829. Recorded as RUN-0001.</t>
-  </si>
-  <si>
-    <t>Baseline frontend: eslint clean, tsc clean, Vitest 46 passed in 6 files, production build succeeded. Recorded as RUN-0002..RUN-0005.</t>
-  </si>
-  <si>
-    <t>Baseline E2E: 16 Playwright workflows passed against the throwaway stack (SQLite backend :8100, production build :3100). The brief's 24-workflow target is TEST-040; temp-dir leak logged as TEST-006.</t>
-  </si>
-  <si>
-    <t>Baseline database: alembic head 85211092fe4c, check reports no drift, full down/up cycle clean; PostgreSQL offline SQL builds 14 tables with RLS; Supabase has all 8 migrations and only INFO-level advisor notices.</t>
-  </si>
-  <si>
-    <t>Baseline dependency audit: pip-audit finds no known vulnerabilities in requirements.lock or requirements-dev.lock; npm audit reports 0 vulnerabilities (production and dev).</t>
-  </si>
-  <si>
-    <t>Baseline infrastructure inspected: compose file valid with 8 services, arq worker and in-process job backends, local and S3 storage providers. Docker images were not built (daemon not running) - left to INFRA-010.</t>
-  </si>
-  <si>
-    <t>Baseline fixtures: the repository's 12 golden DOCX are generated by python-docx (not Word-authored) plus one PDF; the audit's 17 Word-authored fixtures still live outside the repo and move in with TEST-020.</t>
-  </si>
-  <si>
-    <t>Wrote docs/architecture/current-baseline.md: stack versions, the 11 baseline checks with commands and results, the migration chain and live database state, fixture inventory, audit performance figures, and what the baseline could not verify (Docker images, real AI model, Stripe, e-mail, hosting).</t>
-  </si>
-  <si>
-    <t>INFRA-001, INFRA-002, INFRA-003, TEST-001, TEST-002, TEST-003, TEST-004, TEST-005, SEC-001, INFRA-004, DOCS-001</t>
-  </si>
-  <si>
-    <t>Phase 0 committed (4da4ecb, pushed to feature/smartdoc-production-hardening): tracker, checkpoint system and measured baseline. All 11 phase-0 tasks DONE; no production code changed.</t>
-  </si>
-  <si>
-    <t>see commit 4da4ecb</t>
-  </si>
-  <si>
-    <t>Model now holds blocks nested inside table cells, list items and quotes as Elements (authoritative when set; inline keeps plain text), plus list numbering start/format; nesting capped at 8 levels (422 beyond). schemaVersion stays 1: the fields are additive.</t>
-  </si>
-  <si>
-    <t>backend/app/models/document.py, backend/tests/test_document_nesting.py</t>
-  </si>
-  <si>
-    <t>Regenerated the OpenAPI schema and the frontend's generated types for the nested-block and numbering fields; the contract test and the type check pass.</t>
-  </si>
-  <si>
-    <t>frontend/types/generated/*, frontend/types/document.ts</t>
-  </si>
-  <si>
-    <t>Backend readers now see nested blocks: pasted pictures inside cells/list items/quotes are validated and moved to asset storage like top-level ones (security and quota), exports fetch their assets, and the links health check covers list items, cells and nested blocks.</t>
-  </si>
-  <si>
-    <t>backend/app/services/image_assets.py, backend/app/services/document_service.py, backend/app/formatting/health.py</t>
-  </si>
-  <si>
-    <t>Word export renders nested blocks in cells, list items and quotes in reading order (verified by text order), numbers lists from their start in their format, and writes pictures' alt text.</t>
-  </si>
-  <si>
-    <t>backend/app/export/docx_export.py</t>
-  </si>
-  <si>
-    <t>PDF export renders nested blocks and list numbering (start/format); nested numbered levels now use the same a./i. sequence as the Word export instead of 1. everywhere.</t>
-  </si>
-  <si>
-    <t>backend/app/export/pdf_export.py</t>
-  </si>
-  <si>
-    <t>The editor mapping is total over the schema (tested against getSchema(editorExtensions)); anything unknown stops the save with a visible 'Not saved' message instead of being dropped, and the last saved version stays untouched.</t>
-  </si>
-  <si>
-    <t>frontend/editor/*</t>
-  </si>
-  <si>
-    <t>frontend/editor/nestedBlocks.test.ts (7 refusal cases); frontend/editor/useAutoSave.test.tsx (3)</t>
-  </si>
-  <si>
-    <t>Playwright pastes rich HTML (lists, code and a picture in table cells; a list in a quote; code in a list item; a list starting at 3 in letters), waits for autosave and reloads: everything is still there and no 'Not saved' appears.</t>
-  </si>
-  <si>
-    <t>frontend/e2e/nested.spec.ts</t>
-  </si>
-  <si>
-    <t>CORE-001, CORE-002, CORE-003, EDIT-001, EDIT-002, EDIT-003, EDIT-004, EDIT-005, EDIT-006, DOCX-001, PDF-001</t>
-  </si>
-  <si>
-    <t>Committed phase-01a-editor-integrity (1fe27a9, pushed): nested blocks in cells, list items and quotes survive the editor, the backend and both exports; unknown content stops the save visibly. AUD-01 fix tasks all DONE.</t>
-  </si>
-  <si>
-    <t>Import now produces a Document Fidelity Report: the importer's notes as items (feature, policy, count, content lost) plus an independent content check - the source's words (DOCX XML read separately from the importer, Markdown by what it renders, PDF extracted text) against the document's, in order. 'Verified' only when identical; differences listed with context (missing/added/changed/moved).</t>
-  </si>
-  <si>
-    <t>backend/app/fidelity/*, backend/app/models/document.py, backend/app/services/ingestion_service.py</t>
-  </si>
-  <si>
-    <t>Every importer note now carries a stable feature key and a brief-§90 policy class; review count and content-loss count are derived from them.</t>
-  </si>
-  <si>
-    <t>The editor shows the import's verdict in the status bar and a Проверка panel: content verified / differs (with word-level differences) / body complete but some content left out, then each item by policy. Browser check with a05 caught and fixed a misleading 'No content changes' when header text had been left out.</t>
-  </si>
-  <si>
-    <t>frontend/editor/panels/FidelityPanel.tsx, frontend/editor/EditorStatusBar.tsx, frontend/editor/DocumentEditorShell.tsx</t>
-  </si>
-  <si>
-    <t>FID-001, FID-004, FID-005, INFRA-005</t>
-  </si>
-  <si>
-    <t>Committed phase-01b-fidelity-report (8a330be, pushed): import fidelity report with policy classes and an independent word-level content check, shown in the editor; throwaway preview scripts.</t>
-  </si>
-  <si>
-    <t>Exports now report what they approximate or leave out (missing pictures, WebP a Word file can't hold, tables restyled for Word-sourced documents, edited kept fragments, page breaks in PDF tables, PDF comments/equations/fields/internal links, scripts the PDF can't lay out, alt text) and re-read the file: a Word export must hold exactly the document's words, a PDF every word in order (its own list numbers and page headers allowed). Shown under the Download button; the job result carries it.</t>
-  </si>
-  <si>
-    <t>Committed phase-01c-export-report (e55412f, pushed): export fidelity report with read-back content check, shown in the Export menu.</t>
-  </si>
-  <si>
-    <t>Added the machine-readable capability matrix (brief §91): 67 document features with import/edit/export/round-trip support and the policy the fidelity report uses, served at GET /api/v1/capabilities. Tests tie it to the code both ways, require a test for every clean round trip and a task for every unreported gap; writing it exposed unreported gaps now tracked (EDIT-012, DOCX-027).</t>
-  </si>
-  <si>
-    <t>backend/app/capabilities.py, backend/app/api/capabilities.py, backend/app/main.py, backend/tests/test_capabilities.py, frontend/types/generated/*</t>
-  </si>
-  <si>
-    <t>Committed phase-01d-capability-matrix (fcf30d7, pushed).</t>
-  </si>
-  <si>
-    <t>FID-002: import report now names empty spacing paragraphs, unsafe link addresses and per-section differences (page setup, odd/even breaks, page numbering, borders, line numbers, vertical alignment); matrix rows docx.empty_paragraphs + docx.sections updated</t>
-  </si>
-  <si>
-    <t>backend/app/fidelity/docx_detect.py, backend/app/fidelity/imports.py, backend/app/parsers/docx.py, backend/app/parsers/docx_inline.py, backend/app/capabilities.py, backend/tests/test_docx_detect.py</t>
-  </si>
-  <si>
-    <t>DOCX-015: section breaks break the page only where Word does (next section's w:type decides); continuous breaks no longer become page breaks</t>
-  </si>
-  <si>
-    <t>DOCX-016: list number formats, start values and continuation round-trip; custom and multi-level labels reported</t>
-  </si>
-  <si>
-    <t>DOCX-012: Word core properties round-trip; custom properties and sensitivity labels reported without values</t>
-  </si>
-  <si>
-    <t>tests/test_docx_detect.py::test_the_files_own_properties_go_back_into_word_not_the_templates, tests/test_docx_detect.py::test_metadata_that_is_not_kept_is_reported_without_its_values</t>
-  </si>
-  <si>
-    <t>DOCX-026: unsafe link addresses reported instead of silently dropped</t>
-  </si>
-  <si>
-    <t>Golden JSON export is deterministic (uuid5 ids by order, fixed timestamps) so a regenerated fixture only differs where the importer's output did</t>
-  </si>
-  <si>
-    <t>backend/scripts/export_golden_json.py, frontend/tests/fixtures/golden/*.json</t>
-  </si>
-  <si>
-    <t>two consecutive exports byte-identical; tests/test_golden_documents.py::test_the_frontend_golden_json_is_current</t>
-  </si>
-  <si>
-    <t>FID-002 committed and pushed (phase-01e-import-detections)</t>
-  </si>
-  <si>
-    <t>SEC-022: formatting rule values validated at every entry and at resolve; CSS break-out via element style/page settings/instructions closed</t>
-  </si>
-  <si>
-    <t>backend/app/formatting/values.py, backend/app/formatting/engine.py, backend/app/schemas/formatting.py, backend/app/schemas/document.py, backend/app/ai/instruction_extraction.py, backend/tests/test_rule_values.py</t>
-  </si>
-  <si>
-    <t>FMT-005: instruction-path rule values validated before reaching CSS/export (with SEC-022)</t>
-  </si>
-  <si>
-    <t>EDIT-008: pasted/shortcut alignment saved as the element's own style and kept on split; paste into an empty paragraph keeps the pasted paragraphs' attributes</t>
-  </si>
-  <si>
-    <t>frontend/editor/tiptapToDocument.ts, frontend/editor/documentToTiptap.ts, frontend/editor/useAutoSave.ts, frontend/editor/pasteIntoEmptyBlock.ts, frontend/editor/extensions.ts, frontend/services/api/documents.ts, backend/app/schemas/document.py, backend/app/formatting/engine.py, backend/app/services/document_service.py, backend/app/api/documents.py</t>
-  </si>
-  <si>
-    <t>EDIT-009: pasted picture size kept as the picture's width share</t>
-  </si>
-  <si>
-    <t>EDIT-012: values outside the model named in the status bar and the Проверка panel</t>
-  </si>
-  <si>
-    <t>EDIT-011: cell alignment from pasted cells kept per column; differing cells and column widths reported</t>
-  </si>
-  <si>
-    <t>EDIT-008, EDIT-009, EDIT-012, SEC-022, FMT-005</t>
-  </si>
-  <si>
-    <t>Committed and pushed phase-01f-editor-direct-formatting</t>
-  </si>
-  <si>
-    <t>EDIT-010: link titles kept from Word/Markdown through the editor back into Word</t>
-  </si>
-  <si>
-    <t>backend/app/models/document.py, backend/app/parsers/docx_inline.py, backend/app/parsers/docx.py, backend/app/export/docx_export.py, backend/app/parsers/markdown.py, frontend/editor/tiptapToDocument.ts, frontend/editor/documentToTiptap.ts</t>
-  </si>
-  <si>
-    <t>FID-006: Markdown pictures named as left out (content), thematic breaks kept as rules</t>
-  </si>
-  <si>
-    <t>backend/app/parsers/markdown.py, backend/app/capabilities.py, backend/tests/test_capabilities.py, backend/tests/test_markdown_parser.py</t>
-  </si>
-  <si>
-    <t>EDIT-011: cell alignment/widths the model can't hold are named; keeping them moves to DOCX-017</t>
-  </si>
-  <si>
-    <t>EDIT-007: marks in one canonical order (MarkType) on both sides; opening a document saves nothing</t>
-  </si>
-  <si>
-    <t>backend/app/models/document.py, frontend/editor/tiptapToDocument.ts</t>
-  </si>
-  <si>
-    <t>TEST-010: nested-structure regression suite consolidated and verified</t>
-  </si>
-  <si>
-    <t>EDIT-008, EDIT-010, FID-006</t>
-  </si>
-  <si>
-    <t>Phase 1 browser check in the throwaway stack: Markdown doc with a picture -&gt; 'Body text complete, some content left out · 1 to review' (picture named with its description), '---' imported as a rule; pasted centred line + 160px picture + hsl colour + titled link at the end -&gt; status 'Saved · 1 formatting change not kept', Проверка 'While editing' lists the colour; after reload: line centred, picture width 24.9%, link title kept, notice gone</t>
-  </si>
-  <si>
-    <t>manual browser check (throwaway stack, fresh SQLite)</t>
-  </si>
-  <si>
-    <t>DOCS-011: documentation tree started for Phase 1 (document model, fidelity, docx, formatting, security, testing)</t>
-  </si>
-  <si>
-    <t>EDIT-007, EDIT-010, EDIT-011, FID-006, TEST-010, DOCS-011</t>
-  </si>
-  <si>
-    <t>Committed and pushed phase-01g-phase-1-complete; Phase 1 complete</t>
-  </si>
-  <si>
-    <t>AI-001: order/count/token/numeric/punctuation-aware comparator for AI output, with classified differences</t>
-  </si>
-  <si>
-    <t>backend/app/fidelity/text_check.py, backend/tests/test_ai_fidelity.py</t>
-  </si>
-  <si>
-    <t>AI-002: numbers and units protected; changed_numbers for cross-language checks</t>
-  </si>
-  <si>
-    <t>AI-003: structure analysis refuses answers that alter the text, per piece, logging without content</t>
-  </si>
-  <si>
-    <t>backend/app/ai/structure_analysis.py</t>
-  </si>
-  <si>
-    <t>AI-004: adversarial fidelity tests for every alteration the brief names</t>
-  </si>
-  <si>
-    <t>AI-001, AI-002, AI-003, AI-004</t>
-  </si>
-  <si>
-    <t>Committed and pushed phase-02a-ai-fidelity-check</t>
-  </si>
-  <si>
-    <t>AI-005: AI operations classified FORMAT/STRUCTURE/CONTENT; per-element instruction styles no longer dropped by the formatting pass</t>
-  </si>
-  <si>
-    <t>backend/app/formatting/proposals.py, backend/app/services/document_service.py</t>
-  </si>
-  <si>
-    <t>REV-001: change model with categories, used for proposals</t>
-  </si>
-  <si>
-    <t>backend/app/models/document.py, frontend/types/document.ts</t>
-  </si>
-  <si>
-    <t>AI-006: PLAN-&gt;VALIDATE-&gt;PREVIEW-&gt;ACCEPT-&gt;APPLY for AI content changes</t>
-  </si>
-  <si>
-    <t>backend/app/formatting/proposals.py, backend/app/services/document_service.py, backend/app/api/documents.py, backend/app/jobs/runner.py, backend/app/schemas/document.py, backend/app/schemas/jobs.py</t>
-  </si>
-  <si>
-    <t>AI-007: proposal review UI with accept/reject, E2E verified</t>
-  </si>
-  <si>
-    <t>frontend/editor/panels/ProposalsList.tsx, frontend/editor/panels/InstructionsPanel.tsx, frontend/editor/EditorStatusBar.tsx, frontend/editor/useFormatting.ts, frontend/services/api/documents.ts, frontend/services/api/jobs.ts, backend/scripts/e2e_ai.py, backend/scripts/e2e_server.py</t>
-  </si>
-  <si>
-    <t>AI-005, REV-001, AI-006, AI-007</t>
-  </si>
-  <si>
-    <t>Committed and pushed phase-02b-ai-proposals</t>
-  </si>
-  <si>
-    <t>AI-008: per-job/per-request AI call and time budget; no unbounded retries</t>
-  </si>
-  <si>
-    <t>backend/app/ai/budget.py, backend/app/config.py, backend/app/jobs/runner.py, backend/app/api/deps.py, backend/app/ai/structure_analysis.py</t>
-  </si>
-  <si>
-    <t>Committed and pushed phase-02c-ai-budget</t>
-  </si>
-  <si>
-    <t>AI-009: prompt-injection review; AI answer fields bounded; hostile-document tests</t>
-  </si>
-  <si>
-    <t>backend/app/ai/schemas.py, backend/app/ai/structure_analysis.py, backend/tests/test_prompt_injection.py</t>
-  </si>
-  <si>
-    <t>SEC-018: prompt injection / AI output abuse covered by AI-009's tests</t>
-  </si>
-  <si>
-    <t>AI-001, AI-005, AI-007, AI-009</t>
-  </si>
-  <si>
-    <t>Phase 2 gate: backend 817 passed/1 skipped, Vitest 117, Playwright 20; browser check in the throwaway stack - 'make the title red and delete “This draft paragraph”': title red at once, the paragraph kept and shown under Changes to review (struck through, with the instruction), notice + '1 AI change to review'; Accept removed it, reload kept it removed with nothing pending</t>
-  </si>
-  <si>
-    <t>full suites + manual browser check</t>
-  </si>
-  <si>
-    <t>DOCX-010: original Word package kept as an immutable, checksummed asset</t>
-  </si>
-  <si>
-    <t>backend/app/models/document.py, backend/app/services/document_service.py</t>
-  </si>
-  <si>
-    <t>DOCX-011: Word exports written into the original package; import report reflects what they keep</t>
-  </si>
-  <si>
-    <t>backend/app/export/docx_export.py, backend/app/fidelity/imports.py, backend/app/fidelity/docx_source.py, backend/app/fidelity/docx_detect.py, backend/app/fidelity/exports.py, backend/app/jobs/runner.py, backend/app/api/documents.py, backend/app/capabilities.py</t>
-  </si>
-  <si>
-    <t>TEST-023: independent package validation of every Word export</t>
-  </si>
-  <si>
-    <t>backend/app/export/package_check.py, backend/tests/test_package_check.py</t>
-  </si>
-  <si>
-    <t>DOCX-012: metadata preserved (core in the model, app/custom/labels via the original package)</t>
-  </si>
-  <si>
-    <t>DOCX-028: unchanged blocks keep their original XML in Word exports; server-side provenance; earlier sections follow page setup, header and page-number changes; lost sections reported; golden 13-kept-blocks + E2E.</t>
-  </si>
-  <si>
-    <t>backend/app/export/provenance.py, backend/app/export/docx_export.py, backend/app/parsers/docx.py, backend/app/models/document.py, backend/app/services/document_service.py, backend/app/fidelity/imports.py, backend/app/fidelity/exports.py, backend/app/capabilities.py, frontend/editor/tiptapToDocument.ts, frontend/e2e/kept-blocks.spec.ts, docs/docx/README.md</t>
-  </si>
-  <si>
-    <t>DOCX-028 committed and pushed as c8c2d27 (phase-03b-original-blocks).</t>
-  </si>
-  <si>
-    <t>DOCX-025: Word's hidden text stays hidden - hidden mark with Word's style resolution, editor shows it only on request, vanish in Word exports, left out of PDF with a note, consistent content checks.</t>
-  </si>
-  <si>
-    <t>backend/app/models/document.py, backend/app/parsers/docx_inline.py, backend/app/parsers/docx_styles.py, backend/app/parsers/docx.py, backend/app/fidelity/docx_detect.py, backend/app/fidelity/content.py, backend/app/fidelity/exports.py, backend/app/export/docx_export.py, backend/app/export/pdf_export.py, frontend/editor/hiddenText.ts, frontend/editor/EditorStatusBar.tsx, frontend/editor/DocumentEditorShell.tsx, frontend/app/globals.css</t>
-  </si>
-  <si>
-    <t>DOCX-025 committed and pushed as 7d1af86 (phase-03c-hidden-text).</t>
-  </si>
-  <si>
-    <t>DOCX-013 part 1: underline and strike styles, capitals, small capitals, spacing and raised/lowered text kept through import, editor, Word and PDF; paragraph-style formatting turned off by a run fixed.</t>
-  </si>
-  <si>
-    <t>backend/app/models/document.py, backend/app/parsers/docx_inline.py, backend/app/parsers/docx_styles.py, backend/app/parsers/docx.py, backend/app/export/docx_export.py, backend/app/export/pdf_export.py, backend/app/fidelity/*, frontend/editor/characterFormatting.ts, frontend/editor/tiptapToDocument.ts</t>
-  </si>
-  <si>
-    <t>backend 888 passed/1 skipped (tests/test_character_formatting.py 12); Vitest 128 (editor/characterFormatting.test.ts 3, golden round trip of 02); Playwright 22; tsc + eslint clean</t>
-  </si>
-  <si>
-    <t>DOCX-013 part 1 committed and pushed as 6619159 (phase-03d-character-formatting); part 2 next.</t>
-  </si>
-  <si>
     <t>FID-007: reports follow the Word copy - kept while unchanged at import, rewritten losses named at export, unsafe links never copied back.</t>
   </si>
   <si>
@@ -4495,6 +4498,12 @@
     <t>backend/app/models/document.py, backend/app/parsers/docx_inline.py, backend/app/fidelity/docx_detect.py, frontend/editor/characterFormatting.ts</t>
   </si>
   <si>
+    <t>DOCX-013 done: part 1 6619159, part 2 d32c6a6 (phase-03e-copy-reports).</t>
+  </si>
+  <si>
+    <t>FID-007 committed and pushed as d32c6a6.</t>
+  </si>
+  <si>
     <t>SESSION_STATE — Where the work stands</t>
   </si>
   <si>
@@ -4528,7 +4537,7 @@
     <t>Current Commit</t>
   </si>
   <si>
-    <t>309f9d6 (+ uncommitted changes)</t>
+    <t>d32c6a6 (+ uncommitted changes)</t>
   </si>
   <si>
     <t>backend 894 passed, 1 skipped; vitest 129; e2e 22; tsc; eslint</t>
@@ -4549,7 +4558,7 @@
     <t>cd backend &amp;&amp; venv/Scripts/python -m pytest -q tests/test_docx_fidelity.py tests/test_golden_documents.py</t>
   </si>
   <si>
-    <t>2026-09-27T19:37:21+03:00</t>
+    <t>2026-09-27T19:38:07+03:00</t>
   </si>
   <si>
     <t>Resume Instructions</t>
@@ -9077,7 +9086,7 @@
       </c>
       <c r="B6" s="7">
         <f>COUNTIF(MASTER!$G$2:$G$2000,"DONE")</f>
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C6" s="8" t="s">
         <v>8</v>
@@ -9208,7 +9217,7 @@
       </c>
       <c r="B13" s="7">
         <f>B5-B6</f>
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C13" s="8" t="s">
         <v>28</v>
@@ -9227,7 +9236,7 @@
       </c>
       <c r="B14" s="9">
         <f>IF(B5=0,0,B6/B5)</f>
-        <v>0.33939393939393941</v>
+        <v>0.3515151515151515</v>
       </c>
       <c r="C14" s="8" t="s">
         <v>31</v>
@@ -9256,7 +9265,7 @@
       </c>
       <c r="F15" s="1" t="str">
         <f>IF(SESSION_STATE!$B$17="","",SESSION_STATE!$B$17)</f>
-        <v>2026-09-27T19:37:21+03:00</v>
+        <v>2026-09-27T19:38:07+03:00</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
@@ -9265,7 +9274,7 @@
       </c>
       <c r="B16" s="7">
         <f>COUNTIFS(MASTER!$F$2:$F$2000,"P0",MASTER!$G$2:$G$2000,"&lt;&gt;DONE")</f>
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C16" s="8" t="s">
         <v>37</v>
@@ -9277,7 +9286,7 @@
       </c>
       <c r="B17" s="7">
         <f>COUNTIFS(MASTER!$F$2:$F$2000,"P1",MASTER!$G$2:$G$2000,"&lt;&gt;DONE")</f>
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C17" s="8" t="s">
         <v>39</v>
@@ -9482,7 +9491,7 @@
       </c>
       <c r="H22" s="13">
         <f>COUNTIFS(MASTER!$B$2:$B$2000,$E22,MASTER!$G$2:$G$2000,"DONE")</f>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I22" s="13">
         <f>COUNTIFS(MASTER!$B$2:$B$2000,$E22,MASTER!$G$2:$G$2000,"VERIFIED")+H22</f>
@@ -9502,7 +9511,7 @@
       </c>
       <c r="M22" s="14">
         <f t="shared" si="0"/>
-        <v>0.23076923076923078</v>
+        <v>0.30769230769230771</v>
       </c>
       <c r="N22" s="14">
         <f t="shared" si="1"/>
@@ -9814,7 +9823,7 @@
       </c>
       <c r="B29" s="13">
         <f>COUNTIF(MASTER!$G$2:$G$2000,A29)</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C29" s="12" t="s">
         <v>76</v>
@@ -9864,7 +9873,7 @@
       </c>
       <c r="B30" s="13">
         <f>COUNTIF(MASTER!$G$2:$G$2000,A30)</f>
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C30" s="12" t="s">
         <v>79</v>
@@ -10394,7 +10403,7 @@
       </c>
       <c r="H42" s="13">
         <f>COUNTIFS(MASTER!$C$2:$C$2000,$E42,MASTER!$G$2:$G$2000,"DONE")</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I42" s="13">
         <f>COUNTIFS(MASTER!$C$2:$C$2000,$E42,MASTER!$G$2:$G$2000,"VERIFIED")+H42</f>
@@ -10414,7 +10423,7 @@
       </c>
       <c r="M42" s="14">
         <f t="shared" si="2"/>
-        <v>0.8571428571428571</v>
+        <v>1</v>
       </c>
       <c r="N42" s="14">
         <f t="shared" si="3"/>
@@ -10477,7 +10486,7 @@
       </c>
       <c r="H44" s="13">
         <f>COUNTIFS(MASTER!$C$2:$C$2000,$E44,MASTER!$G$2:$G$2000,"DONE")</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I44" s="13">
         <f>COUNTIFS(MASTER!$C$2:$C$2000,$E44,MASTER!$G$2:$G$2000,"VERIFIED")+H44</f>
@@ -10497,7 +10506,7 @@
       </c>
       <c r="M44" s="14">
         <f t="shared" si="2"/>
-        <v>0.2857142857142857</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="N44" s="14">
         <f t="shared" si="3"/>
@@ -21580,7 +21589,7 @@
     <tabColor rgb="FF7F7F7F"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I79"/>
+  <dimension ref="A1:I81"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17" customWidth="1"/>
@@ -23461,7 +23470,7 @@
         <v>1059</v>
       </c>
       <c r="H77" s="12" t="s">
-        <v>501</v>
+        <v>1470</v>
       </c>
       <c r="I77" s="18"/>
     </row>
@@ -23476,10 +23485,10 @@
         <v>3</v>
       </c>
       <c r="D78" s="18" t="s">
-        <v>1470</v>
+        <v>1471</v>
       </c>
       <c r="E78" s="18" t="s">
-        <v>1471</v>
+        <v>1472</v>
       </c>
       <c r="F78" s="18" t="s">
         <v>604</v>
@@ -23501,10 +23510,10 @@
         <v>3</v>
       </c>
       <c r="D79" s="18" t="s">
-        <v>1472</v>
+        <v>1473</v>
       </c>
       <c r="E79" s="18" t="s">
-        <v>1473</v>
+        <v>1474</v>
       </c>
       <c r="F79" s="18" t="s">
         <v>499</v>
@@ -23513,12 +23522,62 @@
         <v>1059</v>
       </c>
       <c r="H79" s="12" t="s">
+        <v>1470</v>
+      </c>
+      <c r="I79" s="18"/>
+    </row>
+    <row r="80" spans="1:9" ht="102" x14ac:dyDescent="0.25">
+      <c r="A80" s="19">
+        <v>46292.818067129629</v>
+      </c>
+      <c r="B80" s="12" t="s">
+        <v>495</v>
+      </c>
+      <c r="C80" s="12">
+        <v>3</v>
+      </c>
+      <c r="D80" s="18" t="s">
+        <v>1475</v>
+      </c>
+      <c r="E80" s="18"/>
+      <c r="F80" s="18" t="s">
+        <v>499</v>
+      </c>
+      <c r="G80" s="12" t="s">
+        <v>1059</v>
+      </c>
+      <c r="H80" s="12" t="s">
         <v>501</v>
       </c>
-      <c r="I79" s="18"/>
+      <c r="I80" s="18"/>
+    </row>
+    <row r="81" spans="1:9" ht="76.5" x14ac:dyDescent="0.25">
+      <c r="A81" s="19">
+        <v>46292.818101851852</v>
+      </c>
+      <c r="B81" s="12" t="s">
+        <v>600</v>
+      </c>
+      <c r="C81" s="12">
+        <v>3</v>
+      </c>
+      <c r="D81" s="18" t="s">
+        <v>1476</v>
+      </c>
+      <c r="E81" s="18"/>
+      <c r="F81" s="18" t="s">
+        <v>604</v>
+      </c>
+      <c r="G81" s="12" t="s">
+        <v>1059</v>
+      </c>
+      <c r="H81" s="12" t="s">
+        <v>501</v>
+      </c>
+      <c r="I81" s="18"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I79" xr:uid="{00000000-0009-0000-0000-000011000000}"/>
+  <autoFilter ref="A1:I81" xr:uid="{00000000-0009-0000-0000-000011000000}"/>
   <conditionalFormatting sqref="G2:G5000">
     <cfRule type="cellIs" dxfId="4" priority="1" operator="equal">
       <formula>"PASS"</formula>
@@ -23555,7 +23614,7 @@
   <sheetData>
     <row r="1" spans="1:2" ht="20.25" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
-        <v>1474</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -23565,15 +23624,15 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>1475</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="10" t="s">
-        <v>1476</v>
+        <v>1479</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>1477</v>
+        <v>1480</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -23581,7 +23640,7 @@
         <v>6</v>
       </c>
       <c r="B5" s="18" t="s">
-        <v>1478</v>
+        <v>1481</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="25.5" x14ac:dyDescent="0.25">
@@ -23589,7 +23648,7 @@
         <v>9</v>
       </c>
       <c r="B6" s="18" t="s">
-        <v>1479</v>
+        <v>1482</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="25.5" x14ac:dyDescent="0.25">
@@ -23597,7 +23656,7 @@
         <v>12</v>
       </c>
       <c r="B7" s="18" t="s">
-        <v>1480</v>
+        <v>1483</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="25.5" x14ac:dyDescent="0.25">
@@ -23605,23 +23664,23 @@
         <v>15</v>
       </c>
       <c r="B8" s="18" t="s">
-        <v>1481</v>
+        <v>1484</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>1482</v>
+        <v>1485</v>
       </c>
       <c r="B9" s="18" t="s">
-        <v>1483</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
-        <v>1484</v>
+        <v>1487</v>
       </c>
       <c r="B10" s="18" t="s">
-        <v>1485</v>
+        <v>1488</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
@@ -23629,7 +23688,7 @@
         <v>26</v>
       </c>
       <c r="B11" s="18" t="s">
-        <v>1486</v>
+        <v>1489</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
@@ -23637,7 +23696,7 @@
         <v>29</v>
       </c>
       <c r="B12" s="18" t="s">
-        <v>1487</v>
+        <v>1490</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="25.5" x14ac:dyDescent="0.25">
@@ -23645,7 +23704,7 @@
         <v>32</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>1488</v>
+        <v>1491</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="25.5" x14ac:dyDescent="0.25">
@@ -23653,7 +23712,7 @@
         <v>18</v>
       </c>
       <c r="B14" s="18" t="s">
-        <v>1489</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
@@ -23661,7 +23720,7 @@
         <v>21</v>
       </c>
       <c r="B15" s="18" t="s">
-        <v>1490</v>
+        <v>1493</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
@@ -23669,7 +23728,7 @@
         <v>24</v>
       </c>
       <c r="B16" s="18" t="s">
-        <v>1491</v>
+        <v>1494</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
@@ -23677,29 +23736,29 @@
         <v>35</v>
       </c>
       <c r="B17" s="18" t="s">
-        <v>1492</v>
+        <v>1495</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
-        <v>1493</v>
+        <v>1496</v>
       </c>
       <c r="B18" s="18" t="s">
-        <v>1494</v>
+        <v>1497</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="6" t="s">
-        <v>1495</v>
+        <v>1498</v>
       </c>
       <c r="B19" s="18" t="str">
         <f>"Tasks "&amp;DASHBOARD!B5&amp;" · done "&amp;DASHBOARD!B6&amp;" · verified "&amp;DASHBOARD!B7&amp;" · in progress "&amp;DASHBOARD!B8&amp;" · blocked "&amp;DASHBOARD!B9&amp;" · failed "&amp;DASHBOARD!B10&amp;" · P0 open "&amp;DASHBOARD!B16&amp;" · P1 open "&amp;DASHBOARD!B17</f>
-        <v>Tasks 165 · done 56 · verified 58 · in progress 5 · blocked 1 · failed 0 · P0 open 47 · P1 open 44</v>
+        <v>Tasks 165 · done 58 · verified 58 · in progress 5 · blocked 1 · failed 0 · P0 open 46 · P1 open 43</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
-        <v>1496</v>
+        <v>1499</v>
       </c>
       <c r="B20" s="18" t="s">
         <v>1329</v>
@@ -23707,7 +23766,7 @@
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" s="6" t="s">
-        <v>1497</v>
+        <v>1500</v>
       </c>
       <c r="B21" s="18" t="s">
         <v>1331</v>
@@ -26603,7 +26662,7 @@
         <v>180</v>
       </c>
       <c r="G53" s="12" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="H53" s="18" t="s">
         <v>498</v>
@@ -26623,9 +26682,11 @@
       <c r="M53" s="19">
         <v>46292.807187500002</v>
       </c>
-      <c r="N53" s="19"/>
+      <c r="N53" s="19">
+        <v>46292.818067129629</v>
+      </c>
       <c r="O53" s="19">
-        <v>46292.817407407398</v>
+        <v>46292.818067129629</v>
       </c>
       <c r="P53" s="12" t="s">
         <v>501</v>
@@ -27635,7 +27696,7 @@
         <v>195</v>
       </c>
       <c r="G75" s="12" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="H75" s="18" t="s">
         <v>603</v>
@@ -27653,11 +27714,15 @@
       <c r="M75" s="19">
         <v>46292.817372685182</v>
       </c>
-      <c r="N75" s="19"/>
+      <c r="N75" s="19">
+        <v>46292.818101851852</v>
+      </c>
       <c r="O75" s="19">
-        <v>46292.817372685182</v>
-      </c>
-      <c r="P75" s="12"/>
+        <v>46292.818101851852</v>
+      </c>
+      <c r="P75" s="12" t="s">
+        <v>501</v>
+      </c>
       <c r="Q75" s="18" t="s">
         <v>605</v>
       </c>
@@ -31518,7 +31583,7 @@
   <sheetData>
     <row r="1" spans="1:9" ht="20.25" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
-        <v>1498</v>
+        <v>1501</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
@@ -31528,16 +31593,16 @@
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
-        <v>1499</v>
+        <v>1502</v>
       </c>
       <c r="B3" s="6" t="s">
         <v>1059</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>1500</v>
+        <v>1503</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>1501</v>
+        <v>1504</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
@@ -31560,10 +31625,10 @@
     </row>
     <row r="6" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>1502</v>
+        <v>1505</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>1503</v>
+        <v>1506</v>
       </c>
       <c r="C6" s="10" t="s">
         <v>57</v>
@@ -31589,16 +31654,16 @@
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="15" t="s">
+        <v>1507</v>
+      </c>
+      <c r="B7" s="18" t="s">
+        <v>1508</v>
+      </c>
+      <c r="C7" s="12" t="s">
         <v>1504</v>
       </c>
-      <c r="B7" s="18" t="s">
-        <v>1505</v>
-      </c>
-      <c r="C7" s="12" t="s">
-        <v>1501</v>
-      </c>
       <c r="D7" s="18" t="s">
-        <v>1506</v>
+        <v>1509</v>
       </c>
       <c r="E7" s="16">
         <f>SUMPRODUCT(ISNUMBER(SEARCH(","&amp;MASTER!$A$2:$A$2000&amp;",",","&amp;SUBSTITUTE($D7," ","")&amp;","))*((MASTER!$G$2:$G$2000="DONE")))</f>
@@ -31614,13 +31679,13 @@
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="15" t="s">
-        <v>1507</v>
+        <v>1510</v>
       </c>
       <c r="B8" s="18" t="s">
-        <v>1508</v>
+        <v>1511</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>1501</v>
+        <v>1504</v>
       </c>
       <c r="D8" s="18" t="s">
         <v>647</v>
@@ -31639,16 +31704,16 @@
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="15" t="s">
-        <v>1509</v>
+        <v>1512</v>
       </c>
       <c r="B9" s="18" t="s">
-        <v>1510</v>
+        <v>1513</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>1501</v>
+        <v>1504</v>
       </c>
       <c r="D9" s="18" t="s">
-        <v>1511</v>
+        <v>1514</v>
       </c>
       <c r="E9" s="16">
         <f>SUMPRODUCT(ISNUMBER(SEARCH(","&amp;MASTER!$A$2:$A$2000&amp;",",","&amp;SUBSTITUTE($D9," ","")&amp;","))*((MASTER!$G$2:$G$2000="DONE")))</f>
@@ -31664,13 +31729,13 @@
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="15" t="s">
-        <v>1512</v>
+        <v>1515</v>
       </c>
       <c r="B10" s="18" t="s">
-        <v>1513</v>
+        <v>1516</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>1501</v>
+        <v>1504</v>
       </c>
       <c r="D10" s="18" t="s">
         <v>721</v>
@@ -31689,16 +31754,16 @@
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="15" t="s">
-        <v>1514</v>
+        <v>1517</v>
       </c>
       <c r="B11" s="18" t="s">
-        <v>1515</v>
+        <v>1518</v>
       </c>
       <c r="C11" s="12" t="s">
-        <v>1501</v>
+        <v>1504</v>
       </c>
       <c r="D11" s="18" t="s">
-        <v>1516</v>
+        <v>1519</v>
       </c>
       <c r="E11" s="16">
         <f>SUMPRODUCT(ISNUMBER(SEARCH(","&amp;MASTER!$A$2:$A$2000&amp;",",","&amp;SUBSTITUTE($D11," ","")&amp;","))*((MASTER!$G$2:$G$2000="DONE")))</f>
@@ -31714,13 +31779,13 @@
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="15" t="s">
-        <v>1517</v>
+        <v>1520</v>
       </c>
       <c r="B12" s="18" t="s">
-        <v>1518</v>
+        <v>1521</v>
       </c>
       <c r="C12" s="12" t="s">
-        <v>1501</v>
+        <v>1504</v>
       </c>
       <c r="D12" s="18" t="s">
         <v>579</v>
@@ -31739,13 +31804,13 @@
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="15" t="s">
-        <v>1519</v>
+        <v>1522</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>1520</v>
+        <v>1523</v>
       </c>
       <c r="C13" s="12" t="s">
-        <v>1501</v>
+        <v>1504</v>
       </c>
       <c r="D13" s="18" t="s">
         <v>579</v>
@@ -31764,13 +31829,13 @@
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="15" t="s">
-        <v>1521</v>
+        <v>1524</v>
       </c>
       <c r="B14" s="18" t="s">
-        <v>1522</v>
+        <v>1525</v>
       </c>
       <c r="C14" s="12" t="s">
-        <v>1501</v>
+        <v>1504</v>
       </c>
       <c r="D14" s="18" t="s">
         <v>825</v>
@@ -31789,13 +31854,13 @@
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="15" t="s">
-        <v>1523</v>
+        <v>1526</v>
       </c>
       <c r="B15" s="18" t="s">
-        <v>1524</v>
+        <v>1527</v>
       </c>
       <c r="C15" s="12" t="s">
-        <v>1501</v>
+        <v>1504</v>
       </c>
       <c r="D15" s="18" t="s">
         <v>754</v>
@@ -31814,13 +31879,13 @@
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" s="15" t="s">
-        <v>1525</v>
+        <v>1528</v>
       </c>
       <c r="B16" s="18" t="s">
-        <v>1526</v>
+        <v>1529</v>
       </c>
       <c r="C16" s="12" t="s">
-        <v>1501</v>
+        <v>1504</v>
       </c>
       <c r="D16" s="18" t="s">
         <v>805</v>
@@ -31839,13 +31904,13 @@
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" s="15" t="s">
-        <v>1527</v>
+        <v>1530</v>
       </c>
       <c r="B17" s="18" t="s">
-        <v>1528</v>
+        <v>1531</v>
       </c>
       <c r="C17" s="12" t="s">
-        <v>1501</v>
+        <v>1504</v>
       </c>
       <c r="D17" s="18" t="s">
         <v>793</v>
@@ -31864,13 +31929,13 @@
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" s="15" t="s">
-        <v>1529</v>
+        <v>1532</v>
       </c>
       <c r="B18" s="18" t="s">
-        <v>1530</v>
+        <v>1533</v>
       </c>
       <c r="C18" s="12" t="s">
-        <v>1501</v>
+        <v>1504</v>
       </c>
       <c r="D18" s="18" t="s">
         <v>905</v>
@@ -31889,13 +31954,13 @@
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" s="15" t="s">
-        <v>1531</v>
+        <v>1534</v>
       </c>
       <c r="B19" s="18" t="s">
-        <v>1532</v>
+        <v>1535</v>
       </c>
       <c r="C19" s="12" t="s">
-        <v>1501</v>
+        <v>1504</v>
       </c>
       <c r="D19" s="18" t="s">
         <v>217</v>
@@ -31914,16 +31979,16 @@
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" s="15" t="s">
-        <v>1533</v>
+        <v>1536</v>
       </c>
       <c r="B20" s="18" t="s">
-        <v>1534</v>
+        <v>1537</v>
       </c>
       <c r="C20" s="12" t="s">
-        <v>1501</v>
+        <v>1504</v>
       </c>
       <c r="D20" s="18" t="s">
-        <v>1535</v>
+        <v>1538</v>
       </c>
       <c r="E20" s="16">
         <f>SUMPRODUCT(ISNUMBER(SEARCH(","&amp;MASTER!$A$2:$A$2000&amp;",",","&amp;SUBSTITUTE($D20," ","")&amp;","))*((MASTER!$G$2:$G$2000="DONE")))</f>
@@ -31939,13 +32004,13 @@
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" s="15" t="s">
-        <v>1536</v>
+        <v>1539</v>
       </c>
       <c r="B21" s="18" t="s">
-        <v>1537</v>
+        <v>1540</v>
       </c>
       <c r="C21" s="12" t="s">
-        <v>1501</v>
+        <v>1504</v>
       </c>
       <c r="D21" s="18" t="s">
         <v>886</v>
@@ -32066,11 +32131,11 @@
       </c>
       <c r="G4" s="7">
         <f>COUNTIFS(MASTER!$F$2:$F$2000,"P0",MASTER!$G$2:$G$2000,"DONE")</f>
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H4" s="7">
         <f>F4-G4</f>
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -32194,7 +32259,7 @@
       </c>
       <c r="C10" s="14">
         <f t="shared" si="1"/>
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="D10" s="18" t="s">
         <v>944</v>
@@ -32205,14 +32270,14 @@
       </c>
       <c r="F10" s="16">
         <f>SUMPRODUCT(ISNUMBER(SEARCH(","&amp;MASTER!$A$2:$A$2000&amp;",",","&amp;SUBSTITUTE($G10," ","")&amp;","))*((MASTER!$G$2:$G$2000="DONE")))</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G10" s="18" t="s">
         <v>945</v>
       </c>
       <c r="H10" s="16">
         <f>SUMPRODUCT(ISNUMBER(SEARCH(","&amp;MASTER!$A$2:$A$2000&amp;",",","&amp;SUBSTITUTE($G10," ","")&amp;","))*((MASTER!$G$2:$G$2000="IN_PROGRESS")+(MASTER!$G$2:$G$2000="IMPLEMENTED")+(MASTER!$G$2:$G$2000="TESTING")+(MASTER!$G$2:$G$2000="VERIFIED")))</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I10" s="16">
         <f>SUMPRODUCT(ISNUMBER(SEARCH(","&amp;MASTER!$A$2:$A$2000&amp;",",","&amp;SUBSTITUTE($G10," ","")&amp;","))*((MASTER!$G$2:$G$2000="BLOCKED")+(MASTER!$G$2:$G$2000="FAILED")))</f>
@@ -34618,7 +34683,7 @@
       </c>
       <c r="F67" s="12" t="str">
         <f>IFERROR(INDEX(MASTER!$G$2:$G$2000,MATCH($A67,MASTER!$A$2:$A$2000,0))&amp;"","NOT IN MASTER")</f>
-        <v>VERIFIED</v>
+        <v>DONE</v>
       </c>
       <c r="G67" s="12" t="str">
         <f>IFERROR(INDEX(MASTER!$H$2:$H$2000,MATCH($A67,MASTER!$A$2:$A$2000,0))&amp;"","")</f>
@@ -34630,11 +34695,11 @@
       </c>
       <c r="I67" s="19">
         <f>IFERROR(IF(INDEX(MASTER!$O$2:$O$2000,MATCH($A67,MASTER!$A$2:$A$2000,0))="","",INDEX(MASTER!$O$2:$O$2000,MATCH($A67,MASTER!$A$2:$A$2000,0))),"")</f>
-        <v>46292.817407407398</v>
+        <v>46292.818067129629</v>
       </c>
       <c r="J67" s="12" t="str">
         <f>IFERROR(INDEX(MASTER!$P$2:$P$2000,MATCH($A67,MASTER!$A$2:$A$2000,0))&amp;"","")</f>
-        <v>6619159</v>
+        <v>d32c6a6</v>
       </c>
       <c r="K67" s="12" t="str">
         <f>IFERROR(INDEX(MASTER!$Q$2:$Q$2000,MATCH($A67,MASTER!$A$2:$A$2000,0))&amp;"","")</f>
@@ -37156,7 +37221,7 @@
       </c>
       <c r="B4" s="7">
         <f>COUNTIFS(MASTER!$C$2:$C$2000,"CORE",MASTER!$G$2:$G$2000,"DONE")+COUNTIFS(MASTER!$C$2:$C$2000,"FIDELITY",MASTER!$G$2:$G$2000,"DONE")+COUNTIFS(MASTER!$C$2:$C$2000,"REVIEW",MASTER!$G$2:$G$2000,"DONE")</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C4" s="7">
         <f>COUNTIFS(MASTER!$C$2:$C$2000,"CORE",MASTER!$G$2:$G$2000,"VERIFIED")+COUNTIFS(MASTER!$C$2:$C$2000,"FIDELITY",MASTER!$G$2:$G$2000,"VERIFIED")+COUNTIFS(MASTER!$C$2:$C$2000,"REVIEW",MASTER!$G$2:$G$2000,"VERIFIED")+B4</f>
@@ -37176,7 +37241,7 @@
       </c>
       <c r="G4" s="9">
         <f>IF(A4=0,0,B4/A4)</f>
-        <v>0.6470588235294118</v>
+        <v>0.70588235294117652</v>
       </c>
       <c r="H4" s="9">
         <f>IF(A4=0,0,C4/A4)</f>
@@ -37836,7 +37901,7 @@
       </c>
       <c r="F20" s="12" t="str">
         <f>IFERROR(INDEX(MASTER!$G$2:$G$2000,MATCH($A20,MASTER!$A$2:$A$2000,0))&amp;"","NOT IN MASTER")</f>
-        <v>VERIFIED</v>
+        <v>DONE</v>
       </c>
       <c r="G20" s="12" t="str">
         <f>IFERROR(INDEX(MASTER!$H$2:$H$2000,MATCH($A20,MASTER!$A$2:$A$2000,0))&amp;"","")</f>
@@ -37848,11 +37913,11 @@
       </c>
       <c r="I20" s="19">
         <f>IFERROR(IF(INDEX(MASTER!$O$2:$O$2000,MATCH($A20,MASTER!$A$2:$A$2000,0))="","",INDEX(MASTER!$O$2:$O$2000,MATCH($A20,MASTER!$A$2:$A$2000,0))),"")</f>
-        <v>46292.817372685182</v>
+        <v>46292.818101851852</v>
       </c>
       <c r="J20" s="12" t="str">
         <f>IFERROR(INDEX(MASTER!$P$2:$P$2000,MATCH($A20,MASTER!$A$2:$A$2000,0))&amp;"","")</f>
-        <v/>
+        <v>d32c6a6</v>
       </c>
       <c r="K20" s="12" t="str">
         <f>IFERROR(INDEX(MASTER!$Q$2:$Q$2000,MATCH($A20,MASTER!$A$2:$A$2000,0))&amp;"","")</f>
@@ -38195,7 +38260,7 @@
       </c>
       <c r="B4" s="7">
         <f>COUNTIFS(MASTER!$C$2:$C$2000,"DOCX",MASTER!$G$2:$G$2000,"DONE")</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C4" s="7">
         <f>COUNTIFS(MASTER!$C$2:$C$2000,"DOCX",MASTER!$G$2:$G$2000,"VERIFIED")+B4</f>
@@ -38215,7 +38280,7 @@
       </c>
       <c r="G4" s="9">
         <f>IF(A4=0,0,B4/A4)</f>
-        <v>0.2857142857142857</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="H4" s="9">
         <f>IF(A4=0,0,C4/A4)</f>
@@ -38483,7 +38548,7 @@
       </c>
       <c r="F12" s="12" t="str">
         <f>IFERROR(INDEX(MASTER!$G$2:$G$2000,MATCH($A12,MASTER!$A$2:$A$2000,0))&amp;"","NOT IN MASTER")</f>
-        <v>VERIFIED</v>
+        <v>DONE</v>
       </c>
       <c r="G12" s="12" t="str">
         <f>IFERROR(INDEX(MASTER!$H$2:$H$2000,MATCH($A12,MASTER!$A$2:$A$2000,0))&amp;"","")</f>
@@ -38495,11 +38560,11 @@
       </c>
       <c r="I12" s="19">
         <f>IFERROR(IF(INDEX(MASTER!$O$2:$O$2000,MATCH($A12,MASTER!$A$2:$A$2000,0))="","",INDEX(MASTER!$O$2:$O$2000,MATCH($A12,MASTER!$A$2:$A$2000,0))),"")</f>
-        <v>46292.817407407398</v>
+        <v>46292.818067129629</v>
       </c>
       <c r="J12" s="12" t="str">
         <f>IFERROR(INDEX(MASTER!$P$2:$P$2000,MATCH($A12,MASTER!$A$2:$A$2000,0))&amp;"","")</f>
-        <v>6619159</v>
+        <v>d32c6a6</v>
       </c>
       <c r="K12" s="12" t="str">
         <f>IFERROR(INDEX(MASTER!$Q$2:$Q$2000,MATCH($A12,MASTER!$A$2:$A$2000,0))&amp;"","")</f>

--- a/SmartDoc_Master_Implementation_Tracker.xlsx
+++ b/SmartDoc_Master_Implementation_Tracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\speed\Desktop\Claude - ПРОЕКТ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9057D13-E49D-4F2F-B090-FBC5A0A9CF49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{769333EE-422A-4024-8CED-1A2534D60C36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">AI!$A$7:$L$16</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="15" hidden="1">BILLING_PLANS!$A$25:$L$30</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="17" hidden="1">CHANGE_LOG!$A$1:$I$84</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="17" hidden="1">CHANGE_LOG!$A$1:$I$85</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">CRITICAL_FIXES!$A$31:$L$115</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">DOCUMENT_FIDELITY!$A$7:$L$24</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">DOCX_OOXML!$A$7:$L$28</definedName>
@@ -71,7 +71,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3862" uniqueCount="1565">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3867" uniqueCount="1567">
   <si>
     <t>SmartDoc — Master Implementation Tracker</t>
   </si>
@@ -1597,2985 +1597,2991 @@
     <t>backend 903 passed/1 skipped (tests/test_paragraph_formatting.py 9); Vitest 129; Playwright 22; tsc + eslint clean; tests/test_paragraph_formatting.py (19 in all); backend 913 passed/1 skipped; Vitest 129; Playwright 22</t>
   </si>
   <si>
+    <t>c158722</t>
+  </si>
+  <si>
+    <t>Part 2 remaining: paragraph borders (model + exports) and tab stops (detect, keep while unchanged, name when lost).</t>
+  </si>
+  <si>
+    <t>DOCX-015</t>
+  </si>
+  <si>
+    <t>Sections as a first-class concept</t>
+  </si>
+  <si>
+    <t>Breaks (next/continuous/even/odd), orientation, size, margins, columns, header/footer distance, first/even/odd headers, linked-to-previous, page-number restart.</t>
+  </si>
+  <si>
+    <t>tests/test_docx_detect.py::test_a_section_break_breaks_the_page_only_where_word_does</t>
+  </si>
+  <si>
+    <t>backend/models, parsers, export</t>
+  </si>
+  <si>
+    <t>Fixed: a section's w:type describes how THAT section starts (ECMA-376 17.6.22) - the importer used the ending section's own type, so a continuous break became a page break and continuous-&gt;new-page put the break between the wrong sections (probe confirmed). Now the next section's type decides. Per-section differences are reported (FID-002). Remaining: sections as a first-class model concept (orientation/margins/columns/headers per section, page-number restart) and export of several sections.; With DOCX-011 the last section's properties (columns, page numbering, borders, line numbers, vertical alignment, header/footer variants) are kept in Word exports; earlier sections' are still reported lost.; DOCX-028: earlier sections now survive in Word exports while their ending paragraph is unchanged; page setup/header/page-number changes apply to them; a lost one is reported (export.docx.section_lost). Modelling sections is still this task.</t>
+  </si>
+  <si>
+    <t>DOCX-016</t>
+  </si>
+  <si>
+    <t>Numbering engine</t>
+  </si>
+  <si>
+    <t>Decimal/roman/alpha/bullets, custom prefixes/suffixes, start, restart, continuation, multilevel, numId/abstractNum/ilvl, indentation.</t>
+  </si>
+  <si>
+    <t>tests/test_docx_numbering.py</t>
+  </si>
+  <si>
+    <t>Done so far: top-level list number format (decimal/roman/letters), start value (lvl start + lvlOverride/startOverride) and continuation across interrupting paragraphs imported into Element.numbering and written back to Word (per-level formats, startOverride) and PDF; empty numbered items keep counting. Reported, not kept: custom labels ('Чл. 1.', '(a)'), multi-level labels ('1.1'), numbered headings baked into text. Remaining: prefixes/suffixes, multilevel numbering model, restart semantics per level, indentation.</t>
+  </si>
+  <si>
+    <t>AUD-04</t>
+  </si>
+  <si>
+    <t>DOCX-017</t>
+  </si>
+  <si>
+    <t>Table engine</t>
+  </si>
+  <si>
+    <t>No forced header or Table Grid; widths, heights, margins, borders, shading, v-align, nested tables, repeated header rows, table styles.</t>
+  </si>
+  <si>
+    <t>From EDIT-011 (2026-09-27): add per-cell alignment and column widths to the model (the editor's cell align/colwidth, Word tcW/tblGrid, PDF colWidths); until then the editor names them as not kept.</t>
+  </si>
+  <si>
+    <t>DOCX-018</t>
+  </si>
+  <si>
+    <t>Images</t>
+  </si>
+  <si>
+    <t>Alt text exported; crop, rotation, anchor, wrap, position preserved; WEBP converted on export.</t>
+  </si>
+  <si>
+    <t>Alt text + title now exported (docPr descr/title) with DOCX-001; crop, rotation, WEBP still open.</t>
+  </si>
+  <si>
+    <t>DOCX-019</t>
+  </si>
+  <si>
+    <t>Drawings and text boxes preserved</t>
+  </si>
+  <si>
+    <t>Anchored drawings, text boxes, shapes kept even when not editable.</t>
+  </si>
+  <si>
+    <t>DOCX-028: text boxes and drawings in unchanged paragraphs are copied as they are (grouped with their anchor paragraph).</t>
+  </si>
+  <si>
+    <t>DOCX-020</t>
+  </si>
+  <si>
+    <t>Fields</t>
+  </si>
+  <si>
+    <t>Code/result/relationship; header STYLEREF/DATE live; TOC kept; CITATION/BIBLIOGRAPHY sources preserved; no 'Invalid source specified.'</t>
+  </si>
+  <si>
+    <t>backend/parsers, export</t>
+  </si>
+  <si>
+    <t>DOCX-028: field codes in unchanged blocks are copied as they are; a field spanning paragraphs is never copied half (self-contained check).</t>
+  </si>
+  <si>
+    <t>AUD-18</t>
+  </si>
+  <si>
+    <t>DOCX-021</t>
+  </si>
+  <si>
+    <t>Comment threads</t>
+  </si>
+  <si>
+    <t>Replies, resolved state, authors, ranges preserved (commentsExtended, people).</t>
+  </si>
+  <si>
+    <t>AUD-06</t>
+  </si>
+  <si>
+    <t>DOCX-022</t>
+  </si>
+  <si>
+    <t>Tracked changes preserved</t>
+  </si>
+  <si>
+    <t>Not silently accepted; explicit choice.</t>
+  </si>
+  <si>
+    <t>DOCX-028: blocks holding tracked changes are never copied (always written anew, accepted), so this task's explicit choice is still needed.</t>
+  </si>
+  <si>
+    <t>DOCX-023</t>
+  </si>
+  <si>
+    <t>Content controls preserved</t>
+  </si>
+  <si>
+    <t>w:sdt of every kind kept with its properties.</t>
+  </si>
+  <si>
+    <t>DOCX-028: content controls in unchanged blocks are copied with their properties (E2E proves it through the editor); written anew they are unwrapped (reported lossy at import).</t>
+  </si>
+  <si>
+    <t>DOCX-024</t>
+  </si>
+  <si>
+    <t>Real footnotes and endnotes</t>
+  </si>
+  <si>
+    <t>Notes stay notes on export.</t>
+  </si>
+  <si>
+    <t>DOCX-025</t>
+  </si>
+  <si>
+    <t>Hidden text stays hidden</t>
+  </si>
+  <si>
+    <t>Imported hidden text is kept hidden, shown only on request.</t>
+  </si>
+  <si>
+    <t>MarkType.HIDDEN (appended; no existing mark order changes). Importer resolves w:vanish as Word does: run, character style, paragraph style (the default paragraph style when none), docDefaults; webHidden stays visible; an explicit vanish=0 shows text in a hidden style. The detector uses the default paragraph style the same way and names hidden text as kept hidden (DETECTED_PRESERVED, not a content change). Editor: non-inclusive hidden mark (editor/hiddenText.ts; Word's display:none paste stays hidden), hidden by CSS unless .show-hidden; status bar 'Show hidden text (N words)' toggles it and re-paginates; the Structure panel leaves hidden text out of headings. Word export writes w:vanish (copied blocks keep theirs); PDF doesn't print hidden runs, export.pdf.hidden_text names the word count, and the PDF content check compares visible words (document_words(visible_only=True)); Word-side checks count hidden text on both sides. Golden 02-rich-text gained a hidden sentence (editor round trip in Vitest).</t>
+  </si>
+  <si>
+    <t>backend 876 passed/1 skipped (tests/test_hidden_text.py 7: import resolution, default paragraph style, report, upload + content check + editor save, Word export round trip, PDF text + note + check); Vitest 125 (editor/hiddenText.test.tsx 6, golden round trip of 02); Playwright 22 (e2e/hidden-text.spec.ts: hidden until asked, dotted line when shown, vanish in the Word export); tsc + eslint clean</t>
+  </si>
+  <si>
+    <t>backend/parsers, frontend</t>
+  </si>
+  <si>
+    <t>7d1af86</t>
+  </si>
+  <si>
+    <t>DOCX-028: vanish survives in unchanged blocks only; the model still shows hidden text as ordinary text - next task.</t>
+  </si>
+  <si>
+    <t>DOCX-026</t>
+  </si>
+  <si>
+    <t>Hyperlink policy and no silent autolink</t>
+  </si>
+  <si>
+    <t>Plain-text addresses not turned into links by default; file:/UNC reported.</t>
+  </si>
+  <si>
+    <t>tests/test_docx_detect.py::test_unsafe_links_and_spacing_paragraphs_are_reported</t>
+  </si>
+  <si>
+    <t>Done: links to unsafe addresses (javascript:, file:, UNC...) are kept as plain text and reported (docx.link.unsafe); plain-text addresses turned into links are reported (docx.autolink). Remaining: stop autolinking by default (a setting), per the task.</t>
+  </si>
+  <si>
+    <t>AUD-03,AUD-13</t>
+  </si>
+  <si>
+    <t>FMT-004</t>
+  </si>
+  <si>
+    <t>Render-spec defaults respect the source</t>
+  </si>
+  <si>
+    <t>Imported Word styles are not overridden by defaults (headings not forced bold).</t>
+  </si>
+  <si>
+    <t>backend/formatting</t>
+  </si>
+  <si>
+    <t>TEST-020</t>
+  </si>
+  <si>
+    <t>Word-authored fixtures in the repository</t>
+  </si>
+  <si>
+    <t>20 synthetic Word-authored fixtures, scrubbed of identifying metadata.</t>
+  </si>
+  <si>
+    <t>backend/tests/fixtures/word</t>
+  </si>
+  <si>
+    <t>TEST-021</t>
+  </si>
+  <si>
+    <t>Expected-loss manifests in CI</t>
+  </si>
+  <si>
+    <t>expected-loss.json per fixture; CI compares actual vs expected.</t>
+  </si>
+  <si>
+    <t>TEST-022</t>
+  </si>
+  <si>
+    <t>True fidelity test</t>
+  </si>
+  <si>
+    <t>SOURCE -&gt; import -&gt; format -&gt; editor save -&gt; export -&gt; reimport -&gt; compare SOURCE vs RESULT: content, formatting, metadata, structure separately.</t>
+  </si>
+  <si>
+    <t>TEST-023</t>
+  </si>
+  <si>
+    <t>Independent validation</t>
+  </si>
+  <si>
+    <t>OOXML schema validation, Word when available, docx2python; pdftotext/PyMuPDF for PDF.</t>
+  </si>
+  <si>
+    <t>app/export/package_check.py: an independent package check (zip read directly): well-formed parts, content types, relationships resolving, relationship ids used, defined styles/lists/comments. Found a real defect on first run (python-docx's add_comment refers to an undefined CommentReference style; exports now define it). Every golden export passes, fresh and into its original.</t>
+  </si>
+  <si>
+    <t>tests/test_package_check.py (13)</t>
+  </si>
+  <si>
+    <t>The docx skill's XSD validator needs defusedxml (not installed; installing needs a download) - schema-level validation remains open.</t>
+  </si>
+  <si>
+    <t>DOCX-027</t>
+  </si>
+  <si>
+    <t>Importer builds nested blocks</t>
+  </si>
+  <si>
+    <t>Use TableCell.blocks / ListItem.blocks on import: pictures, lists (with bullets) and nested tables inside cells, pictures inside list items - instead of dropping or flattening them.</t>
+  </si>
+  <si>
+    <t>AUD-01,AUD-03,AUD-08</t>
+  </si>
+  <si>
+    <t>DOCX-028</t>
+  </si>
+  <si>
+    <t>Unchanged blocks keep their original XML in Word exports</t>
+  </si>
+  <si>
+    <t>Blocks the user didn't change are written back as their original XML (fields, content controls, run-level formatting the model can't hold, bookmarks), changed ones regenerated; needs block provenance from the importer and fingerprints.</t>
+  </si>
+  <si>
+    <t>Importer records each top-level element's body children (Element.sourceBlocks: list items, drop caps, derived page breaks); an upload with a kept file stamps content+look fingerprints (Element.sourceHash, app/export/provenance.py: own/kind/body/nested resolved styles; page breaks have no look). docx_export._copy_plan groups elements with their children (uncovered children join the group before) and copies a group verbatim when every element is unchanged, together and in original order, children contiguous, XML self-contained (no tracked changes/note refs/altChunk; balanced fields, bookmarks, comment ranges); everything else is written anew. Provenance is server-side (keep_provenance on PUT /content). Page setup now runs after the body: changed size/margins reach every kept section (orientation kept, landscape turned), a changed main header is rewritten where Word shows it (link to previous), page numbers left out/asked for apply to every section. export.docx.section_lost (LOSSY) names sections lost with a changed paragraph; import report: earlier sections' setup/headers kept while unchanged; PDF names them Word-only. All 13 golden documents stamped + exported into their originals: sound packages, content verified (12-complex rewrites only the footnote paragraph and the note, by design).</t>
+  </si>
+  <si>
+    <t>backend 869 passed/1 skipped (tests/test_original_blocks.py 26 incl. 13 golden; test_source_package.py rewritten claims with export proof; test_golden_documents.py 13 files); Vitest 119 (editor round trip of 13-kept-blocks); Playwright 21 (e2e/kept-blocks.spec.ts: edit in the real editor, untouched paragraphs keep content control, double underline, landscape section); tsc + eslint clean</t>
+  </si>
+  <si>
+    <t>c8c2d27</t>
+  </si>
+  <si>
+    <t>Follow-up of DOCX-011 (package-level patch writer).; Known limit: any restyle (template, instruction) changes the body look, so every block but page breaks is written anew; follow-up DOCX-029. Sections survive only with their ending paragraph until DOCX-015 models them.</t>
+  </si>
+  <si>
+    <t>DOCX-029</t>
+  </si>
+  <si>
+    <t>Restyled blocks keep their original XML where nothing conflicts</t>
+  </si>
+  <si>
+    <t>After a template or instruction restyles a kind of block, copy a block's original XML when its paragraph style is the Word style the export rewrites for that kind and its direct formatting (pPr/rPr) sets none of the properties that changed; today any restyle writes every block anew (content controls, double underline etc. then lost, as the import report says).</t>
+  </si>
+  <si>
+    <t>Found while finishing DOCX-028: the look is part of the fingerprint so the export never shows a stale look.</t>
+  </si>
+  <si>
+    <t>FID-007</t>
+  </si>
+  <si>
+    <t>Reports follow the Word copy</t>
+  </si>
+  <si>
+    <t>With the original kept, the import report names what lives in blocks as kept in the Word export while the paragraph is unchanged, and an export that writes such a block anew names what it lost; a copy never brings back a link the app doesn't allow.</t>
+  </si>
+  <si>
+    <t>fidelity/imports.py KEPT_WHILE_UNCHANGED (content controls, text boxes, charts/shapes/SmartArt, objects, picture crop/rotation/floating, drop caps, empty paragraphs, approximated underlines, character scale, text effects, RTL) -&gt; detected_not_editable 'kept while the paragraph isn't changed or restyled'; docx_export._copy_plan returns rewritten groups, _lost_in/_rewritten_losses -&gt; export.docx.rewritten_blocks (LOSSY, count, kinds incl. proofing exclusions); _safe_links keeps groups with unsafe links (relationships or HYPERLINK fields) from being copied; the PDF's Word-only note covers the features.</t>
+  </si>
+  <si>
+    <t>tests/test_copy_reports.py (6): kept while unchanged at import, rewritten losses named (content controls, stretched text), unsafe javascript: link never copied back, PDF word-only; backend 894 passed/1 skipped; Playwright 22</t>
+  </si>
+  <si>
+    <t>Generalises DOCX-028's section handling (export.docx.section_lost) to everything the model doesn't hold inside blocks.</t>
+  </si>
+  <si>
+    <t>SEC-010</t>
+  </si>
+  <si>
+    <t>Malformed DOCX -&gt; safe 4xx</t>
+  </si>
+  <si>
+    <t>XML/zip/structure errors map to invalid_file; fuzz corpus shows no 500.</t>
+  </si>
+  <si>
+    <t>AUD-12</t>
+  </si>
+  <si>
+    <t>SEC-011</t>
+  </si>
+  <si>
+    <t>Malformed PDF -&gt; safe 4xx</t>
+  </si>
+  <si>
+    <t>Verified with a fuzz corpus.</t>
+  </si>
+  <si>
+    <t>SEC-012</t>
+  </si>
+  <si>
+    <t>Image resource limits</t>
+  </si>
+  <si>
+    <t>Compressed and decompressed size, pixel count, width, height, images per document, total bytes, format allowlist; rejected before rasterisation.</t>
+  </si>
+  <si>
+    <t>backend/security</t>
+  </si>
+  <si>
+    <t>AUD-09</t>
+  </si>
+  <si>
+    <t>SEC-013</t>
+  </si>
+  <si>
+    <t>PDF bombs, huge XML, decompression limits</t>
+  </si>
+  <si>
+    <t>Reviewed and tested limits.</t>
+  </si>
+  <si>
+    <t>SEC-014</t>
+  </si>
+  <si>
+    <t>Href policy</t>
+  </si>
+  <si>
+    <t>Server-side scheme allowlist; javascript:/data:/vbscript:/file: never exported as active links.</t>
+  </si>
+  <si>
+    <t>backend/models, export</t>
+  </si>
+  <si>
+    <t>AUD-13</t>
+  </si>
+  <si>
+    <t>SEC-015</t>
+  </si>
+  <si>
+    <t>Field instruction allowlist</t>
+  </si>
+  <si>
+    <t>No DDE/INCLUDETEXT/INCLUDEPICTURE/external fields accepted from clients or exported.</t>
+  </si>
+  <si>
+    <t>SEC-016</t>
+  </si>
+  <si>
+    <t>External relationships policy</t>
+  </si>
+  <si>
+    <t>No arbitrary external targets in exports.</t>
+  </si>
+  <si>
+    <t>SEC-017</t>
+  </si>
+  <si>
+    <t>Malicious SVG</t>
+  </si>
+  <si>
+    <t>Verified refused everywhere.</t>
+  </si>
+  <si>
+    <t>SEC-018</t>
+  </si>
+  <si>
+    <t>Prompt injection / AI output abuse</t>
+  </si>
+  <si>
+    <t>Tests with hostile documents; outputs validated.</t>
+  </si>
+  <si>
+    <t>Hostile-document tests: the document can't close its fence; out-of-bounds answers refused and fall back; an instruction steered by the document deletes nothing (proposals only) and a CSS break-out value is dropped; style-analysis flags on unknown elements dropped (see AI-009).</t>
+  </si>
+  <si>
+    <t>tests/test_prompt_injection.py</t>
+  </si>
+  <si>
+    <t>SEC-019</t>
+  </si>
+  <si>
+    <t>Error envelope audit</t>
+  </si>
+  <si>
+    <t>Every error {code, message, details, request_id}; no stack traces to users.</t>
+  </si>
+  <si>
+    <t>backend/api</t>
+  </si>
+  <si>
+    <t>SEC-020</t>
+  </si>
+  <si>
+    <t>CSP without 'unsafe-inline' scripts</t>
+  </si>
+  <si>
+    <t>Nonce-based CSP for the Next.js app.</t>
+  </si>
+  <si>
+    <t>TEST-030</t>
+  </si>
+  <si>
+    <t>Security regression suite</t>
+  </si>
+  <si>
+    <t>Fuzz corpus, pixel bombs, href/field policy, IDOR, CSRF.</t>
+  </si>
+  <si>
+    <t>SEC-010,SEC-012,SEC-014,SEC-015</t>
+  </si>
+  <si>
+    <t>AUD-09,AUD-12,AUD-13</t>
+  </si>
+  <si>
+    <t>SEC-021</t>
+  </si>
+  <si>
+    <t>Sensitivity-label metadata in the public repository</t>
+  </si>
+  <si>
+    <t>корекции.docx (committed in 5f2bf9e, pushed) carries 8 MSIP_Label_* custom properties incl. the organisation's tenant SiteId (label: Microsoft default 'General' family, no content marking). Options: leave; scrub the file in a new commit (HEAD only); purge from history (force-push).</t>
+  </si>
+  <si>
+    <t>repository history</t>
+  </si>
+  <si>
+    <t>Needs Boril: the choice involves his organisation's label and possibly rewriting pushed history. The tracker tools now strip MSIP labels on every write; the pre-push scan flags them.</t>
+  </si>
+  <si>
+    <t>SEC-022</t>
+  </si>
+  <si>
+    <t>Formatting rule values can't break out of a style</t>
+  </si>
+  <si>
+    <t>A rule value reaches the editor's style attribute, Word and PDF styles as text. The element-style and page-setting endpoints accepted any string (e.g. 'center;background-image:url(...)'), the AI instruction path too (FMT-005): CSS injection into every viewer's editor.</t>
+  </si>
+  <si>
+    <t>app/formatting/values.py: clean_rule_value per property (the StyleSystem's limits: choices, true/false, one safe font name, renderable colours, bounded numbers with known units, header/footer text &lt;=500). Refused with 422 by the element-style and page-setting endpoints (schemas RuleValue); instruction rules and set_style operations with such values dropped (FMT-005), validate_operations refuses them; stored rules no renderer can use are skipped at resolve (engine._usable) so old documents can't carry them either. All 177 default/template rules pass unchanged.</t>
+  </si>
+  <si>
+    <t>tests/test_rule_values.py (34 cases incl. API 422, stored-rule skip, instruction drop)</t>
+  </si>
+  <si>
+    <t>Found 2026-09-27 while mapping editor alignment (EDIT-008); probe confirmed the raw value in resolvedStyles.</t>
+  </si>
+  <si>
+    <t>PERF-001</t>
+  </si>
+  <si>
+    <t>Linear DOCX table export</t>
+  </si>
+  <si>
+    <t>500x8 table under a recorded threshold (baseline 321 s).</t>
+  </si>
+  <si>
+    <t>AUD-10</t>
+  </si>
+  <si>
+    <t>PERF-002</t>
+  </si>
+  <si>
+    <t>Benchmarks recorded</t>
+  </si>
+  <si>
+    <t>Baseline and current measurements in the PERFORMANCE sheet.</t>
+  </si>
+  <si>
+    <t>tests/perf</t>
+  </si>
+  <si>
+    <t>PERF-003</t>
+  </si>
+  <si>
+    <t>Delta autosave</t>
+  </si>
+  <si>
+    <t>Change-aware patches with a threshold strategy; whole document only when needed.</t>
+  </si>
+  <si>
+    <t>frontend/editor, backend/api</t>
+  </si>
+  <si>
+    <t>PERF-004</t>
+  </si>
+  <si>
+    <t>Bounded, compressed version history</t>
+  </si>
+  <si>
+    <t>Editor history separate from persisted versions; compression/deltas; asset references.</t>
+  </si>
+  <si>
+    <t>PERF-005</t>
+  </si>
+  <si>
+    <t>Editor at 5k-12k blocks</t>
+  </si>
+  <si>
+    <t>Typing latency measured and improved.</t>
+  </si>
+  <si>
+    <t>PERF-006</t>
+  </si>
+  <si>
+    <t>JSON without ASCII escaping</t>
+  </si>
+  <si>
+    <t>Document JSON stored and sent as UTF-8.</t>
+  </si>
+  <si>
+    <t>backend/db</t>
+  </si>
+  <si>
+    <t>PERF-007</t>
+  </si>
+  <si>
+    <t>Safe size limits recorded</t>
+  </si>
+  <si>
+    <t>User-facing maximum sizes, job timeouts, resource ceilings documented and enforced.</t>
+  </si>
+  <si>
+    <t>backend/config</t>
+  </si>
+  <si>
+    <t>AUD-09,AUD-10</t>
+  </si>
+  <si>
+    <t>ACCT-001</t>
+  </si>
+  <si>
+    <t>E-mail sender abstraction</t>
+  </si>
+  <si>
+    <t>SMTP provider + development outbox; no secrets in logs.</t>
+  </si>
+  <si>
+    <t>AUD-14</t>
+  </si>
+  <si>
+    <t>ACCT-002</t>
+  </si>
+  <si>
+    <t>Password reset</t>
+  </si>
+  <si>
+    <t>Single-use, expiring, hashed tokens; rate-limited; no account enumeration.</t>
+  </si>
+  <si>
+    <t>backend/api, frontend</t>
+  </si>
+  <si>
+    <t>ACCT-003</t>
+  </si>
+  <si>
+    <t>E-mail verification</t>
+  </si>
+  <si>
+    <t>Verification tokens and state.</t>
+  </si>
+  <si>
+    <t>ACCT-004</t>
+  </si>
+  <si>
+    <t>Password change</t>
+  </si>
+  <si>
+    <t>Current password required; other sessions revoked.</t>
+  </si>
+  <si>
+    <t>ACCT-005</t>
+  </si>
+  <si>
+    <t>Account deletion</t>
+  </si>
+  <si>
+    <t>Cascading policy: documents, versions, assets, exports, sessions, jobs, usage.</t>
+  </si>
+  <si>
+    <t>ACCT-006</t>
+  </si>
+  <si>
+    <t>Session revocation and cleanup</t>
+  </si>
+  <si>
+    <t>Sign out everywhere; expired/revoked session sweep.</t>
+  </si>
+  <si>
+    <t>ACCT-007</t>
+  </si>
+  <si>
+    <t>Suspicious login handling</t>
+  </si>
+  <si>
+    <t>Lockout and notification strategy.</t>
+  </si>
+  <si>
+    <t>PLAN-001</t>
+  </si>
+  <si>
+    <t>Usage units</t>
+  </si>
+  <si>
+    <t>Documents, exports, PDF pages, OCR pages, translation characters, AI operations, storage, batch jobs.</t>
+  </si>
+  <si>
+    <t>backend/billing</t>
+  </si>
+  <si>
+    <t>AUD-11</t>
+  </si>
+  <si>
+    <t>PLAN-002</t>
+  </si>
+  <si>
+    <t>Configurable plan defaults</t>
+  </si>
+  <si>
+    <t>Free/Pro/Business initial hypotheses as configuration, never hardcoded.</t>
+  </si>
+  <si>
+    <t>PLAN-003</t>
+  </si>
+  <si>
+    <t>Atomic entitlement checks</t>
+  </si>
+  <si>
+    <t>Reservation/locking; concurrency test proves limits hold.</t>
+  </si>
+  <si>
+    <t>PLAN-004</t>
+  </si>
+  <si>
+    <t>Stripe flows review</t>
+  </si>
+  <si>
+    <t>Checkout, portal, upgrade, downgrade, cancel, renewal, failed payment, webhook idempotency.</t>
+  </si>
+  <si>
+    <t>PLAN-005</t>
+  </si>
+  <si>
+    <t>Storage metering including history</t>
+  </si>
+  <si>
+    <t>History and autosave growth counted.</t>
+  </si>
+  <si>
+    <t>AUD-11,AUD-16</t>
+  </si>
+  <si>
+    <t>PDF-010</t>
+  </si>
+  <si>
+    <t>Geometry-aware PDF parser</t>
+  </si>
+  <si>
+    <t>Chars, fonts, sizes, colours, lines, rectangles, images, links, annotations, outlines, forms, metadata, rotation, page boxes.</t>
+  </si>
+  <si>
+    <t>backend/parsers/pdf</t>
+  </si>
+  <si>
+    <t>PDF-011</t>
+  </si>
+  <si>
+    <t>Page classifier</t>
+  </si>
+  <si>
+    <t>TEXT / SCANNED / HYBRID per page with evidence.</t>
+  </si>
+  <si>
+    <t>PDF-012</t>
+  </si>
+  <si>
+    <t>PDF inspection report</t>
+  </si>
+  <si>
+    <t>What the parser found, per page.</t>
+  </si>
+  <si>
+    <t>P2E-001</t>
+  </si>
+  <si>
+    <t>Layout primitives where PDF needs them</t>
+  </si>
+  <si>
+    <t>Page, block, bbox, rotation, confidence, provenance.</t>
+  </si>
+  <si>
+    <t>P2E-002</t>
+  </si>
+  <si>
+    <t>Structure reconstruction</t>
+  </si>
+  <si>
+    <t>Reading order, lines, paragraphs, headings, lists, captions, header/footer bands, columns.</t>
+  </si>
+  <si>
+    <t>backend/pdf</t>
+  </si>
+  <si>
+    <t>P2E-003</t>
+  </si>
+  <si>
+    <t>Images with position</t>
+  </si>
+  <si>
+    <t>Extracted images kept with bbox.</t>
+  </si>
+  <si>
+    <t>P2E-004</t>
+  </si>
+  <si>
+    <t>Tables from PDF</t>
+  </si>
+  <si>
+    <t>Ruling lines and alignment.</t>
+  </si>
+  <si>
+    <t>P2E-005</t>
+  </si>
+  <si>
+    <t>Confidence and conversion report</t>
+  </si>
+  <si>
+    <t>Per element confidence; issues reported; never silent removal.</t>
+  </si>
+  <si>
+    <t>P2E-006</t>
+  </si>
+  <si>
+    <t>OCR provider abstraction</t>
+  </si>
+  <si>
+    <t>Interface (text, confidence, bbox, page, language/script); implementation(s); OCR output untrusted.</t>
+  </si>
+  <si>
+    <t>backend/ocr</t>
+  </si>
+  <si>
+    <t>P2E-007</t>
+  </si>
+  <si>
+    <t>Imported-from-PDF version and UX</t>
+  </si>
+  <si>
+    <t>Editable document vs layout-focused choice; confidence shown.</t>
+  </si>
+  <si>
+    <t>frontend, backend</t>
+  </si>
+  <si>
+    <t>P2E-008</t>
+  </si>
+  <si>
+    <t>PDF fixtures and tests</t>
+  </si>
+  <si>
+    <t>Text, scanned, hybrid, tables, columns, multilingual.</t>
+  </si>
+  <si>
+    <t>P2E-020</t>
+  </si>
+  <si>
+    <t>Layout-preserving architecture</t>
+  </si>
+  <si>
+    <t>Frames/anchors model hooks and design doc.</t>
+  </si>
+  <si>
+    <t>docs, backend/models</t>
+  </si>
+  <si>
+    <t>PDF-020</t>
+  </si>
+  <si>
+    <t>PDF page operations service</t>
+  </si>
+  <si>
+    <t>Reorder, rotate, delete, duplicate, extract, split, merge as a separate service.</t>
+  </si>
+  <si>
+    <t>TRAN-001</t>
+  </si>
+  <si>
+    <t>Segments and tag protocol</t>
+  </si>
+  <si>
+    <t>Segments keep element/run ids, marks, placeholders; never one giant string.</t>
+  </si>
+  <si>
+    <t>backend/translation</t>
+  </si>
+  <si>
+    <t>TRAN-002</t>
+  </si>
+  <si>
+    <t>TranslationProvider abstraction</t>
+  </si>
+  <si>
+    <t>AI provider implementation + deterministic test provider.</t>
+  </si>
+  <si>
+    <t>TRAN-003</t>
+  </si>
+  <si>
+    <t>Translation validation</t>
+  </si>
+  <si>
+    <t>Tags, numbers, units, dates, percentages, identifiers, glossary terms.</t>
+  </si>
+  <si>
+    <t>TRAN-004</t>
+  </si>
+  <si>
+    <t>Glossary and terminology lock</t>
+  </si>
+  <si>
+    <t>Source/target term, domain, locked, case-sensitive.</t>
+  </si>
+  <si>
+    <t>backend/translation, db</t>
+  </si>
+  <si>
+    <t>TRAN-005</t>
+  </si>
+  <si>
+    <t>Selection/paragraph/block translation proposals</t>
+  </si>
+  <si>
+    <t>Preview; accept/reject; undo.</t>
+  </si>
+  <si>
+    <t>TRAN-003,REV-001</t>
+  </si>
+  <si>
+    <t>TRAN-006</t>
+  </si>
+  <si>
+    <t>Whole-document translated version</t>
+  </si>
+  <si>
+    <t>Source kept; translated copy linked.</t>
+  </si>
+  <si>
+    <t>TRAN-007</t>
+  </si>
+  <si>
+    <t>Language, script, direction metadata</t>
+  </si>
+  <si>
+    <t>Auto-detect + manual override.</t>
+  </si>
+  <si>
+    <t>TRAN-008</t>
+  </si>
+  <si>
+    <t>Translation UX</t>
+  </si>
+  <si>
+    <t>Toolbar/context Translate, target language, preview, accept/reject; 'AI-assisted translation - review required'.</t>
+  </si>
+  <si>
+    <t>TRAN-009</t>
+  </si>
+  <si>
+    <t>Translation metering</t>
+  </si>
+  <si>
+    <t>Translation characters as a usage unit.</t>
+  </si>
+  <si>
+    <t>TRAN-010</t>
+  </si>
+  <si>
+    <t>Translation tests</t>
+  </si>
+  <si>
+    <t>Formatting preservation, validation, versions.</t>
+  </si>
+  <si>
+    <t>FONT-001</t>
+  </si>
+  <si>
+    <t>Font catalogue with Unicode coverage</t>
+  </si>
+  <si>
+    <t>fontTools cmap coverage per script, metrics, embeddability.</t>
+  </si>
+  <si>
+    <t>backend/fonts</t>
+  </si>
+  <si>
+    <t>AUD-17</t>
+  </si>
+  <si>
+    <t>FONT-002</t>
+  </si>
+  <si>
+    <t>FontResolver</t>
+  </si>
+  <si>
+    <t>Script segmentation, coverage, fallback chain, embedding, RTL; deterministic first, AI suggestion validated.</t>
+  </si>
+  <si>
+    <t>FONT-003</t>
+  </si>
+  <si>
+    <t>Multilingual PDF rendering</t>
+  </si>
+  <si>
+    <t>Shaping for Arabic/Hebrew/Devanagari, bidi, CJK fonts, emoji handled gracefully.</t>
+  </si>
+  <si>
+    <t>FONT-004</t>
+  </si>
+  <si>
+    <t>DOCX per-script fonts</t>
+  </si>
+  <si>
+    <t>w:rFonts ascii/hAnsi/eastAsia/cs, w:lang, rtl/bidi.</t>
+  </si>
+  <si>
+    <t>FONT-005</t>
+  </si>
+  <si>
+    <t>Editor fallback stacks</t>
+  </si>
+  <si>
+    <t>CSS stacks from the resolver.</t>
+  </si>
+  <si>
+    <t>FONT-006</t>
+  </si>
+  <si>
+    <t>Multilingual tests</t>
+  </si>
+  <si>
+    <t>Script matrix x editor/DOCX/PDF with pdftotext and rendering.</t>
+  </si>
+  <si>
+    <t>FMT-001</t>
+  </si>
+  <si>
+    <t>Style extraction completeness</t>
+  </si>
+  <si>
+    <t>Page setup, margins, fonts, headings, lists, tables, captions, headers/footers, spacing, numbering, colours.</t>
+  </si>
+  <si>
+    <t>FMT-002</t>
+  </si>
+  <si>
+    <t>Semantic mapping validated</t>
+  </si>
+  <si>
+    <t>AI classifies/maps, engine applies; validation.</t>
+  </si>
+  <si>
+    <t>FMT-003</t>
+  </si>
+  <si>
+    <t>Before/after for Format by Example</t>
+  </si>
+  <si>
+    <t>Preview before saving a template.</t>
+  </si>
+  <si>
+    <t>FMT-005</t>
+  </si>
+  <si>
+    <t>Rule value validation</t>
+  </si>
+  <si>
+    <t>Instruction-path values validated before reaching CSS/export.</t>
+  </si>
+  <si>
+    <t>Instruction rules and set_style operations go through values.clean_rule_value: invalid ones dropped, normalised values stored (see SEC-022).</t>
+  </si>
+  <si>
+    <t>tests/test_rule_values.py::test_instructions_cannot_carry_such_values</t>
+  </si>
+  <si>
+    <t>HLTH-001</t>
+  </si>
+  <si>
+    <t>Health 2.0 checks</t>
+  </si>
+  <si>
+    <t>Alt text, hidden text, mixed language, unsupported features, section inconsistency, broken lists, empty paragraphs, layout anomalies, duplicated formatting, broken links.</t>
+  </si>
+  <si>
+    <t>HLTH-002</t>
+  </si>
+  <si>
+    <t>Deterministic fixes with preview</t>
+  </si>
+  <si>
+    <t>Fix proposals through the change model.</t>
+  </si>
+  <si>
+    <t>HLTH-003</t>
+  </si>
+  <si>
+    <t>AI explanations only</t>
+  </si>
+  <si>
+    <t>AI explains issues; never scores.</t>
+  </si>
+  <si>
+    <t>REV-002</t>
+  </si>
+  <si>
+    <t>Review Changes UI</t>
+  </si>
+  <si>
+    <t>Categories FORMAT/STRUCTURE/CONTENT/METADATA/PRESERVATION/TRANSLATION.</t>
+  </si>
+  <si>
+    <t>REV-003</t>
+  </si>
+  <si>
+    <t>Content changes need acceptance</t>
+  </si>
+  <si>
+    <t>Enforced server-side.</t>
+  </si>
+  <si>
+    <t>backend</t>
+  </si>
+  <si>
+    <t>REV-004</t>
+  </si>
+  <si>
+    <t>Repair</t>
+  </si>
+  <si>
+    <t>Detected issue, proposed fix, preview, apply.</t>
+  </si>
+  <si>
+    <t>REV-005</t>
+  </si>
+  <si>
+    <t>Clean copy</t>
+  </si>
+  <si>
+    <t>Explicit: remove comments, accept tracked changes, remove hidden text, remove metadata, normalise formatting.</t>
+  </si>
+  <si>
+    <t>FEAT-001</t>
+  </si>
+  <si>
+    <t>Batch formatting</t>
+  </si>
+  <si>
+    <t>One template/reference over many documents as jobs.</t>
+  </si>
+  <si>
+    <t>backend/jobs</t>
+  </si>
+  <si>
+    <t>FEAT-002</t>
+  </si>
+  <si>
+    <t>Batch export</t>
+  </si>
+  <si>
+    <t>Many documents to a zip.</t>
+  </si>
+  <si>
+    <t>FEAT-003</t>
+  </si>
+  <si>
+    <t>Batch translation</t>
+  </si>
+  <si>
+    <t>After the translation MVP.</t>
+  </si>
+  <si>
+    <t>FEAT-010</t>
+  </si>
+  <si>
+    <t>Accessibility checker</t>
+  </si>
+  <si>
+    <t>Heading hierarchy, alt text, link labels, table headers, reading order, language, contrast.</t>
+  </si>
+  <si>
+    <t>FEAT-011</t>
+  </si>
+  <si>
+    <t>App accessibility fixes</t>
+  </si>
+  <si>
+    <t>Zero serious axe violations on main pages and the editor.</t>
+  </si>
+  <si>
+    <t>JOB-001</t>
+  </si>
+  <si>
+    <t>Job safety</t>
+  </si>
+  <si>
+    <t>idempotency_key, retry_count, timeout, cancellation, stuck detection, backoff, dead-letter.</t>
+  </si>
+  <si>
+    <t>STOR-001</t>
+  </si>
+  <si>
+    <t>Storage retention and deletion</t>
+  </si>
+  <si>
+    <t>Source files, exports, OCR artifacts: retention, deletion, access control, content types, size limits.</t>
+  </si>
+  <si>
+    <t>OBS-001</t>
+  </si>
+  <si>
+    <t>Metrics</t>
+  </si>
+  <si>
+    <t>Latency, failure rate, job/AI/export metrics without content.</t>
+  </si>
+  <si>
+    <t>AUD-15</t>
+  </si>
+  <si>
+    <t>OBS-002</t>
+  </si>
+  <si>
+    <t>Operation and job IDs in logs</t>
+  </si>
+  <si>
+    <t>Request, operation and job IDs everywhere.</t>
+  </si>
+  <si>
+    <t>OBS-003</t>
+  </si>
+  <si>
+    <t>Operations data</t>
+  </si>
+  <si>
+    <t>Failed jobs, processing failures, usage spikes, AI/export failures, storage, abuse - minimal admin API.</t>
+  </si>
+  <si>
+    <t>INFRA-010</t>
+  </si>
+  <si>
+    <t>Deployment verified</t>
+  </si>
+  <si>
+    <t>Docker images build and start; Postgres, Redis, storage, worker, frontend, backend.</t>
+  </si>
+  <si>
+    <t>docker, CI</t>
+  </si>
+  <si>
+    <t>INFRA-011</t>
+  </si>
+  <si>
+    <t>CI gates</t>
+  </si>
+  <si>
+    <t>Backend, frontend, E2E, lint, typecheck, build, migrations, security audit, document fidelity tests.</t>
+  </si>
+  <si>
+    <t>.github/workflows</t>
+  </si>
+  <si>
+    <t>AUD-15,AUD-20</t>
+  </si>
+  <si>
+    <t>TEST-040</t>
+  </si>
+  <si>
+    <t>Playwright workflow coverage</t>
+  </si>
+  <si>
+    <t>The 24 workflows of the brief.</t>
+  </si>
+  <si>
+    <t>TEST-041</t>
+  </si>
+  <si>
+    <t>Performance gates</t>
+  </si>
+  <si>
+    <t>Regression thresholds relative to baseline.</t>
+  </si>
+  <si>
+    <t>TEST-043</t>
+  </si>
+  <si>
+    <t>Browser matrix</t>
+  </si>
+  <si>
+    <t>Chromium, Firefox, WebKit.</t>
+  </si>
+  <si>
+    <t>TEST-006</t>
+  </si>
+  <si>
+    <t>E2E backend removes its temp directory</t>
+  </si>
+  <si>
+    <t>scripts/e2e_server.py leaves %TEMP%/smartdoc-e2e-* behind after every Playwright run (10 found on 2026-09-27).</t>
+  </si>
+  <si>
+    <t>backend/scripts/e2e_server.py</t>
+  </si>
+  <si>
+    <t>DOCS-010</t>
+  </si>
+  <si>
+    <t>final-production-readiness.md</t>
+  </si>
+  <si>
+    <t>The 16-section final report.</t>
+  </si>
+  <si>
+    <t>DOCS-011</t>
+  </si>
+  <si>
+    <t>Documentation tree</t>
+  </si>
+  <si>
+    <t>docs/{architecture,document-model,docx,pdf,translation,ai,formatting,security,testing,deployment,billing,operations}.</t>
+  </si>
+  <si>
+    <t>Started with Phase 1: docs/document-model, docs/architecture/fidelity.md, docs/docx, docs/formatting, docs/security, docs/testing (each grounded in the code and tests of Phases 0-1). Remaining folders (pdf, translation, ai, deployment, billing, operations) as their phases land.; docs/ai/README.md added with Phase 2.</t>
+  </si>
+  <si>
+    <t>CRITICAL_FIXES — Audit findings and P0 tasks</t>
+  </si>
+  <si>
+    <t>The 20 findings of the 2026-09-26 audit (current known risks) with fix progress, then every P0 task. Report: https://claude.ai/artifact/WKskiyexTDLAHe1BfjvWR1 — a finding is RESOLVED when every linked fix task is DONE.</t>
+  </si>
+  <si>
+    <t>Findings</t>
+  </si>
+  <si>
+    <t>Resolved</t>
+  </si>
+  <si>
+    <t>Open</t>
+  </si>
+  <si>
+    <t>P0 tasks</t>
+  </si>
+  <si>
+    <t>P0 done</t>
+  </si>
+  <si>
+    <t>Audit findings (current known risks)</t>
+  </si>
+  <si>
+    <t>Finding ID</t>
+  </si>
+  <si>
+    <t>Progress</t>
+  </si>
+  <si>
+    <t>Finding</t>
+  </si>
+  <si>
+    <t>Fix Tasks</t>
+  </si>
+  <si>
+    <t>Active</t>
+  </si>
+  <si>
+    <t>Blocked/Failed</t>
+  </si>
+  <si>
+    <t>Editor save can discard nested blocks (lists, pictures, code, quotes inside cells/items)</t>
+  </si>
+  <si>
+    <t>EDIT-001,EDIT-002,EDIT-003,EDIT-005,EDIT-006</t>
+  </si>
+  <si>
+    <t>AI fidelity check misses omissions, negation removal, number changes, inserted text</t>
+  </si>
+  <si>
+    <t>AI-001,AI-002,AI-003,AI-004</t>
+  </si>
+  <si>
+    <t>Fixed in Phase 2 (AI-001..004): AI structure answers are checked token by token; any omission, negation removal, number/unit/date change, insertion, reordering, duplication or punctuation change is refused.</t>
+  </si>
+  <si>
+    <t>Import/export silently changes hidden text, numbering, section headers, metadata, alt text, structure</t>
+  </si>
+  <si>
+    <t>FID-002,DOCX-011,DOCX-013,DOCX-015,DOCX-025</t>
+  </si>
+  <si>
+    <t>List numbering changes ('Чл. 1.' -&gt; '1.', '(a)' -&gt; 'a.', start values)</t>
+  </si>
+  <si>
+    <t>Partly fixed in 622d9c1: list format/start/continuation kept; custom labels ('Чл. 1.', '(a)') and multi-level labels reported, not kept yet (DOCX-016).</t>
+  </si>
+  <si>
+    <t>AI instruction operations can delete/insert/move content without preview</t>
+  </si>
+  <si>
+    <t>AI-005,AI-006,AI-007,REV-003</t>
+  </si>
+  <si>
+    <t>Fixed in Phase 2 (AI-005..AI-007): an instruction's insert/delete/move is a proposal the user sees and accepts or rejects; nothing is deleted silently.</t>
+  </si>
+  <si>
+    <t>Content controls, metadata, comment threads, sensitivity information lost</t>
+  </si>
+  <si>
+    <t>DOCX-012,DOCX-021,DOCX-023</t>
+  </si>
+  <si>
+    <t>Image fidelity gaps: alt text, crop, rotation, formats</t>
+  </si>
+  <si>
+    <t>Table export changes header state, borders, alignment, widths, geometry</t>
+  </si>
+  <si>
+    <t>Large images cause huge memory consumption</t>
+  </si>
+  <si>
+    <t>SEC-012,SEC-013</t>
+  </si>
+  <si>
+    <t>Large tables have a performance problem</t>
+  </si>
+  <si>
+    <t>Plan limits have a concurrency race</t>
+  </si>
+  <si>
+    <t>Malformed DOCX leads to HTTP 500</t>
+  </si>
+  <si>
+    <t>SEC-010,SEC-019</t>
+  </si>
+  <si>
+    <t>Dangerous href/field instructions must be filtered</t>
+  </si>
+  <si>
+    <t>SEC-014,SEC-015,SEC-016</t>
+  </si>
+  <si>
+    <t>Account essentials missing: reset, verification, change, deletion</t>
+  </si>
+  <si>
+    <t>ACCT-002,ACCT-003,ACCT-004,ACCT-005</t>
+  </si>
+  <si>
+    <t>Operations/monitoring must be confirmed</t>
+  </si>
+  <si>
+    <t>OBS-001,OBS-002,INFRA-010</t>
+  </si>
+  <si>
+    <t>Whole-document autosave must be optimised</t>
+  </si>
+  <si>
+    <t>PERF-003,PERF-004</t>
+  </si>
+  <si>
+    <t>PDF multilingual rendering must be reliable</t>
+  </si>
+  <si>
+    <t>FONT-003,FONT-006</t>
+  </si>
+  <si>
+    <t>Export metadata must be correct</t>
+  </si>
+  <si>
+    <t>DOCX-012,DOCX-020</t>
+  </si>
+  <si>
+    <t>Partly fixed in 622d9c1: Word exports carry the source file's core properties (author, dates, subject...) instead of 'python-docx'/2013; fields remain (DOCX-020).</t>
+  </si>
+  <si>
+    <t>AUD-19</t>
+  </si>
+  <si>
+    <t>Canonical model must represent more than paragraphs + runs + simple tables</t>
+  </si>
+  <si>
+    <t>CORE-001,DOCX-015,DOCX-016,DOCX-017</t>
+  </si>
+  <si>
+    <t>Tests can miss import-side data loss (model-relative comparison)</t>
+  </si>
+  <si>
+    <t>TEST-020,TEST-021,TEST-022</t>
+  </si>
+  <si>
+    <t>P0 tasks (live from MASTER)</t>
+  </si>
+  <si>
+    <t>DOCUMENT_FIDELITY — Content preservation</t>
+  </si>
+  <si>
+    <t>Canonical model, fidelity reports, capability matrix, change/review model. Categories: CORE, FIDELITY, REVIEW. Rows are formulas over MASTER — change task data in MASTER or with tools/tracker/tracker.py.</t>
+  </si>
+  <si>
+    <t>Tasks (live from MASTER)</t>
+  </si>
+  <si>
+    <t>DOCX_OOXML — DOCX / OOXML preservation</t>
+  </si>
+  <si>
+    <t>Import and export fidelity for Word documents. Categories: DOCX. Rows are formulas over MASTER — change task data in MASTER or with tools/tracker/tracker.py.</t>
+  </si>
+  <si>
+    <t>PDF — PDF engine</t>
+  </si>
+  <si>
+    <t>PDF export and PDF parsing. Categories: PDF. Rows are formulas over MASTER — change task data in MASTER or with tools/tracker/tracker.py.</t>
+  </si>
+  <si>
+    <t>EDITOR — Editor integrity</t>
+  </si>
+  <si>
+    <t>Tiptap mapping and save integrity. Categories: EDITOR. Rows are formulas over MASTER — change task data in MASTER or with tools/tracker/tracker.py.</t>
+  </si>
+  <si>
+    <t>FORMATTING — Formatting and Document Health</t>
+  </si>
+  <si>
+    <t>Formatting engine, Format by Example, Document Health. Categories: FORMATTING, HEALTH. Rows are formulas over MASTER — change task data in MASTER or with tools/tracker/tracker.py.</t>
+  </si>
+  <si>
+    <t>AI — AI fidelity</t>
+  </si>
+  <si>
+    <t>Fidelity checks, proposals and review, budgets. Categories: AI. Rows are formulas over MASTER — change task data in MASTER or with tools/tracker/tracker.py.</t>
+  </si>
+  <si>
+    <t>SECURITY — Security and accounts</t>
+  </si>
+  <si>
+    <t>Security hardening and account essentials. Categories: SECURITY, ACCOUNT. Rows are formulas over MASTER — change task data in MASTER or with tools/tracker/tracker.py.</t>
+  </si>
+  <si>
+    <t>PERFORMANCE — Performance</t>
+  </si>
+  <si>
+    <t>Measured results — brief §80-81: measure, then set regression thresholds relative to the baseline (no invented SLOs)</t>
+  </si>
+  <si>
+    <t>Bench ID</t>
+  </si>
+  <si>
+    <t>Metric</t>
+  </si>
+  <si>
+    <t>Unit</t>
+  </si>
+  <si>
+    <t>Scenario</t>
+  </si>
+  <si>
+    <t>Baseline</t>
+  </si>
+  <si>
+    <t>Baseline Source</t>
+  </si>
+  <si>
+    <t>Current</t>
+  </si>
+  <si>
+    <t>Measured On</t>
+  </si>
+  <si>
+    <t>Threshold</t>
+  </si>
+  <si>
+    <t>BENCH-001</t>
+  </si>
+  <si>
+    <t>duration</t>
+  </si>
+  <si>
+    <t>s</t>
+  </si>
+  <si>
+    <t>DOCX export: table 500x8 (4,000 cells)</t>
+  </si>
+  <si>
+    <t>audit perf_table.py (400 cells 3.8 s; 1,600 cells 53.7 s; quadratic)</t>
+  </si>
+  <si>
+    <t>BENCH-002</t>
+  </si>
+  <si>
+    <t>PDF export: table 500x8</t>
+  </si>
+  <si>
+    <t>audit perf_table.py (linear)</t>
+  </si>
+  <si>
+    <t>BENCH-003</t>
+  </si>
+  <si>
+    <t>Import: 300-page text DOCX (1,650 elements)</t>
+  </si>
+  <si>
+    <t>audit perf_backend.py</t>
+  </si>
+  <si>
+    <t>BENCH-004</t>
+  </si>
+  <si>
+    <t>DOCX export: 300-page text document</t>
+  </si>
+  <si>
+    <t>BENCH-005</t>
+  </si>
+  <si>
+    <t>PDF export: 300-page text document</t>
+  </si>
+  <si>
+    <t>BENCH-006</t>
+  </si>
+  <si>
+    <t>memory growth</t>
+  </si>
+  <si>
+    <t>MB</t>
+  </si>
+  <si>
+    <t>PDF export: 39 KB DOCX holding a 12000x12000 PNG</t>
+  </si>
+  <si>
+    <t>audit pixel_bomb.py (14000x14000 crashes the export)</t>
+  </si>
+  <si>
+    <t>BENCH-007</t>
+  </si>
+  <si>
+    <t>PDF export: 4 JPEG images 2400x1800</t>
+  </si>
+  <si>
+    <t>audit perf_backend.py (6.3 s)</t>
+  </si>
+  <si>
+    <t>BENCH-008</t>
+  </si>
+  <si>
+    <t>Editor: type 20 characters at 12,196 elements (1M-character paste)</t>
+  </si>
+  <si>
+    <t>audit perf_browser.js (~470 ms per key)</t>
+  </si>
+  <si>
+    <t>BENCH-009</t>
+  </si>
+  <si>
+    <t>Editor: type 20 characters, 300-page document</t>
+  </si>
+  <si>
+    <t>audit perf_browser.js</t>
+  </si>
+  <si>
+    <t>BENCH-010</t>
+  </si>
+  <si>
+    <t>request size</t>
+  </si>
+  <si>
+    <t>Autosave request: 300-page document</t>
+  </si>
+  <si>
+    <t>audit perf_browser.js (whole elements list per save)</t>
+  </si>
+  <si>
+    <t>BENCH-011</t>
+  </si>
+  <si>
+    <t>Autosave request: 1M-character paste</t>
+  </si>
+  <si>
+    <t>BENCH-012</t>
+  </si>
+  <si>
+    <t>storage</t>
+  </si>
+  <si>
+    <t>Stored history: one 300-page document, 50 steps</t>
+  </si>
+  <si>
+    <t>audit (2.8 MB per full copy; 7.2 MB when the JSON is ASCII-escaped)</t>
+  </si>
+  <si>
+    <t>BENCH-013</t>
+  </si>
+  <si>
+    <t>Paste: 2M characters (the cap)</t>
+  </si>
+  <si>
+    <t>audit perf_backend.py (17.5k elements, 7.1 MB JSON)</t>
+  </si>
+  <si>
+    <t>Performance tasks (live from MASTER)</t>
+  </si>
+  <si>
+    <t>TESTING — Testing</t>
+  </si>
+  <si>
+    <t>Test runs (oldest first)</t>
+  </si>
+  <si>
+    <t>Run ID</t>
+  </si>
+  <si>
+    <t>Command</t>
+  </si>
+  <si>
+    <t>Passed</t>
+  </si>
+  <si>
+    <t>Skipped</t>
+  </si>
+  <si>
+    <t>Date</t>
+  </si>
+  <si>
+    <t>Duration (s)</t>
+  </si>
+  <si>
+    <t>RUN-0001</t>
+  </si>
+  <si>
+    <t>backend-pytest</t>
+  </si>
+  <si>
+    <t>PASS</t>
+  </si>
+  <si>
+    <t>cd backend &amp;&amp; venv/Scripts/python -m pytest -q -p no:cacheprovider</t>
+  </si>
+  <si>
+    <t>Skip: optional real-Word check (SMARTDOC_REAL_DOCX unset). 1 DeprecationWarning (starlette/anyio). Audit measured 93% line coverage on 2026-09-26.</t>
+  </si>
+  <si>
+    <t>ea69829</t>
+  </si>
+  <si>
+    <t>RUN-0002</t>
+  </si>
+  <si>
+    <t>frontend-lint</t>
+  </si>
+  <si>
+    <t>cd frontend &amp;&amp; npm run lint</t>
+  </si>
+  <si>
+    <t>eslint: 0 problems</t>
+  </si>
+  <si>
+    <t>RUN-0003</t>
+  </si>
+  <si>
+    <t>frontend-tsc</t>
+  </si>
+  <si>
+    <t>cd frontend &amp;&amp; npx tsc --noEmit</t>
+  </si>
+  <si>
+    <t>0 type errors</t>
+  </si>
+  <si>
+    <t>RUN-0004</t>
+  </si>
+  <si>
+    <t>frontend-vitest</t>
+  </si>
+  <si>
+    <t>cd frontend &amp;&amp; npm test</t>
+  </si>
+  <si>
+    <t>6 test files</t>
+  </si>
+  <si>
+    <t>RUN-0005</t>
+  </si>
+  <si>
+    <t>frontend-build</t>
+  </si>
+  <si>
+    <t>cd frontend &amp;&amp; npm run build</t>
+  </si>
+  <si>
+    <t>Next.js production build, 11 routes</t>
+  </si>
+  <si>
+    <t>RUN-0006</t>
+  </si>
+  <si>
+    <t>e2e-playwright</t>
+  </si>
+  <si>
+    <t>cd frontend &amp;&amp; npm run test:e2e</t>
+  </si>
+  <si>
+    <t>Edge; throwaway backend on SQLite (:8100) + production build (:3100). 16 workflows in 5 spec files; the brief asks for 24 (TEST-040). Leaves %TEMP%/smartdoc-e2e-* dirs behind (TEST-006).</t>
+  </si>
+  <si>
+    <t>RUN-0007</t>
+  </si>
+  <si>
+    <t>migrations</t>
+  </si>
+  <si>
+    <t>alembic upgrade head &amp;&amp; alembic check &amp;&amp; alembic downgrade base &amp;&amp; alembic upgrade head (scratch SQLite); alembic upgrade head --sql (PostgreSQL dialect)</t>
+  </si>
+  <si>
+    <t>head 85211092fe4c; 'No new upgrade operations detected'; offline SQL: 14 tables at head, RLS enabled on every table</t>
+  </si>
+  <si>
+    <t>RUN-0008</t>
+  </si>
+  <si>
+    <t>supabase</t>
+  </si>
+  <si>
+    <t>Supabase MCP: list_migrations, get_advisors security+performance, list_tables (project edmmjmsynjziahwtjuke)</t>
+  </si>
+  <si>
+    <t>8/8 migrations applied; 14 tables, RLS on all; advisors only INFO: 14x rls_enabled_no_policy (by design: the API connects as owner, PostgREST roles see nothing), 8x unused_index (low traffic)</t>
+  </si>
+  <si>
+    <t>RUN-0009</t>
+  </si>
+  <si>
+    <t>pip-audit</t>
+  </si>
+  <si>
+    <t>uvx pip-audit --disable-pip -r backend/requirements.lock; same for requirements-dev.lock</t>
+  </si>
+  <si>
+    <t>No known vulnerabilities in either lock file</t>
+  </si>
+  <si>
+    <t>RUN-0010</t>
+  </si>
+  <si>
+    <t>npm-audit</t>
+  </si>
+  <si>
+    <t>cd frontend &amp;&amp; npm audit; npm audit --omit=dev</t>
+  </si>
+  <si>
+    <t>0 vulnerabilities across 633 dependencies</t>
+  </si>
+  <si>
+    <t>RUN-0011</t>
+  </si>
+  <si>
+    <t>docker-compose</t>
+  </si>
+  <si>
+    <t>PARTIAL</t>
+  </si>
+  <si>
+    <t>docker compose config --quiet</t>
+  </si>
+  <si>
+    <t>compose file valid (8 services: postgres, redis, minio, minio-bucket, migrate, worker, backend, frontend); images NOT built: Docker daemon not running on this machine (CI builds them on main)</t>
+  </si>
+  <si>
+    <t>RUN-0012</t>
+  </si>
+  <si>
+    <t>Phase 1 editor integrity: +16 tests (nesting model, nested API/exports, health links)</t>
+  </si>
+  <si>
+    <t>RUN-0013</t>
+  </si>
+  <si>
+    <t>cd frontend &amp;&amp; npx vitest run</t>
+  </si>
+  <si>
+    <t>+31: nestedBlocks.test.ts (28), useAutoSave.test.tsx (3); tsc and eslint clean</t>
+  </si>
+  <si>
+    <t>RUN-0014</t>
+  </si>
+  <si>
+    <t>cd frontend &amp;&amp; npx playwright test</t>
+  </si>
+  <si>
+    <t>+1: e2e/nested.spec.ts (paste, autosave, reload)</t>
+  </si>
+  <si>
+    <t>RUN-0015</t>
+  </si>
+  <si>
+    <t>+29 test_fidelity_report.py</t>
+  </si>
+  <si>
+    <t>RUN-0016</t>
+  </si>
+  <si>
+    <t>+3 FidelityPanel.test.tsx</t>
+  </si>
+  <si>
+    <t>RUN-0017</t>
+  </si>
+  <si>
+    <t>+fidelity.spec.ts; nested.spec.ts made deterministic (focus check, Ctrl+End) after one run pasted at the document start</t>
+  </si>
+  <si>
+    <t>RUN-0018</t>
+  </si>
+  <si>
+    <t>+6 test_export_fidelity.py</t>
+  </si>
+  <si>
+    <t>RUN-0019</t>
+  </si>
+  <si>
+    <t>+4 ExportResult.test.tsx</t>
+  </si>
+  <si>
+    <t>RUN-0020</t>
+  </si>
+  <si>
+    <t>export test checks the export's content message</t>
+  </si>
+  <si>
+    <t>RUN-0021</t>
+  </si>
+  <si>
+    <t>+6 test_capabilities.py</t>
+  </si>
+  <si>
+    <t>RUN-0022</t>
+  </si>
+  <si>
+    <t>venv/Scripts/python -m pytest -q</t>
+  </si>
+  <si>
+    <t>after FID-002 detections + section break fix</t>
+  </si>
+  <si>
+    <t>RUN-0023</t>
+  </si>
+  <si>
+    <t>npx vitest run</t>
+  </si>
+  <si>
+    <t>tsc --noEmit and eslint clean too</t>
+  </si>
+  <si>
+    <t>RUN-0024</t>
+  </si>
+  <si>
+    <t>rule values (SEC-022) + editor direct styles</t>
+  </si>
+  <si>
+    <t>RUN-0025</t>
+  </si>
+  <si>
+    <t>tsc + eslint clean</t>
+  </si>
+  <si>
+    <t>RUN-0026</t>
+  </si>
+  <si>
+    <t>e2e</t>
+  </si>
+  <si>
+    <t>npx playwright test</t>
+  </si>
+  <si>
+    <t>incl. e2e/direct-formatting.spec.ts</t>
+  </si>
+  <si>
+    <t>RUN-0027</t>
+  </si>
+  <si>
+    <t>Phase 1 gate: link titles, mark order, Markdown pictures/rules</t>
+  </si>
+  <si>
+    <t>RUN-0028</t>
+  </si>
+  <si>
+    <t>Phase 1 gate; tsc + eslint clean</t>
+  </si>
+  <si>
+    <t>RUN-0029</t>
+  </si>
+  <si>
+    <t>Phase 1 gate</t>
+  </si>
+  <si>
+    <t>RUN-0030</t>
+  </si>
+  <si>
+    <t>AI fidelity check (AI-001..004)</t>
+  </si>
+  <si>
+    <t>RUN-0031</t>
+  </si>
+  <si>
+    <t>AI proposals</t>
+  </si>
+  <si>
+    <t>RUN-0032</t>
+  </si>
+  <si>
+    <t>RUN-0033</t>
+  </si>
+  <si>
+    <t>incl. e2e/proposals.spec.ts</t>
+  </si>
+  <si>
+    <t>RUN-0034</t>
+  </si>
+  <si>
+    <t>AI budget</t>
+  </si>
+  <si>
+    <t>RUN-0035</t>
+  </si>
+  <si>
+    <t>prompt-injection review</t>
+  </si>
+  <si>
+    <t>RUN-0036</t>
+  </si>
+  <si>
+    <t>Phase 2 gate</t>
+  </si>
+  <si>
+    <t>RUN-0037</t>
+  </si>
+  <si>
+    <t>RUN-0038</t>
+  </si>
+  <si>
+    <t>source package + patch writer</t>
+  </si>
+  <si>
+    <t>RUN-0039</t>
+  </si>
+  <si>
+    <t>after the patch writer</t>
+  </si>
+  <si>
+    <t>RUN-0040</t>
+  </si>
+  <si>
+    <t>backend pytest</t>
+  </si>
+  <si>
+    <t>DOCX-028: test_original_blocks.py (26), golden set of 13</t>
+  </si>
+  <si>
+    <t>7f22bf9</t>
+  </si>
+  <si>
+    <t>RUN-0041</t>
+  </si>
+  <si>
+    <t>frontend vitest</t>
+  </si>
+  <si>
+    <t>editor round trip includes 13-kept-blocks</t>
+  </si>
+  <si>
+    <t>RUN-0042</t>
+  </si>
+  <si>
+    <t>playwright</t>
+  </si>
+  <si>
+    <t>new e2e/kept-blocks.spec.ts</t>
+  </si>
+  <si>
+    <t>RUN-0043</t>
+  </si>
+  <si>
+    <t>tsc + eslint</t>
+  </si>
+  <si>
+    <t>cd frontend &amp;&amp; npx tsc --noEmit &amp;&amp; npx eslint .</t>
+  </si>
+  <si>
+    <t>0 type errors, 0 lint problems</t>
+  </si>
+  <si>
+    <t>RUN-0044</t>
+  </si>
+  <si>
+    <t>DOCX-025: tests/test_hidden_text.py (7)</t>
+  </si>
+  <si>
+    <t>fada4d7</t>
+  </si>
+  <si>
+    <t>RUN-0045</t>
+  </si>
+  <si>
+    <t>editor/hiddenText.test.tsx (6)</t>
+  </si>
+  <si>
+    <t>RUN-0046</t>
+  </si>
+  <si>
+    <t>new e2e/hidden-text.spec.ts</t>
+  </si>
+  <si>
+    <t>RUN-0047</t>
+  </si>
+  <si>
+    <t>RUN-0048</t>
+  </si>
+  <si>
+    <t>DOCX-013 part 1: tests/test_character_formatting.py (12)</t>
+  </si>
+  <si>
+    <t>c51b1bf</t>
+  </si>
+  <si>
+    <t>RUN-0049</t>
+  </si>
+  <si>
+    <t>editor/characterFormatting.test.ts (3)</t>
+  </si>
+  <si>
+    <t>RUN-0050</t>
+  </si>
+  <si>
+    <t>after DOCX-013 part 1</t>
+  </si>
+  <si>
+    <t>RUN-0051</t>
+  </si>
+  <si>
+    <t>RUN-0052</t>
+  </si>
+  <si>
+    <t>DOCX-013 part 2 + FID-007: tests/test_copy_reports.py (6)</t>
+  </si>
+  <si>
+    <t>309f9d6</t>
+  </si>
+  <si>
+    <t>RUN-0053</t>
+  </si>
+  <si>
+    <t>characterFormatting.test.ts (4)</t>
+  </si>
+  <si>
+    <t>RUN-0054</t>
+  </si>
+  <si>
+    <t>after DOCX-013 part 2</t>
+  </si>
+  <si>
+    <t>RUN-0055</t>
+  </si>
+  <si>
+    <t>RUN-0056</t>
+  </si>
+  <si>
+    <t>DOCX-014 part 1: tests/test_paragraph_formatting.py (9)</t>
+  </si>
+  <si>
+    <t>597275a</t>
+  </si>
+  <si>
+    <t>RUN-0057</t>
+  </si>
+  <si>
+    <t>after DOCX-014 part 1</t>
+  </si>
+  <si>
+    <t>RUN-0058</t>
+  </si>
+  <si>
+    <t>RUN-0059</t>
+  </si>
+  <si>
+    <t>RUN-0060</t>
+  </si>
+  <si>
+    <t>DOCX-014 part 2: tests/test_paragraph_formatting.py (19)</t>
+  </si>
+  <si>
+    <t>9f1c5b4</t>
+  </si>
+  <si>
+    <t>RUN-0061</t>
+  </si>
+  <si>
+    <t>after DOCX-014 part 2</t>
+  </si>
+  <si>
+    <t>RUN-0062</t>
+  </si>
+  <si>
+    <t>RUN-0063</t>
+  </si>
+  <si>
+    <t>Testing tasks (live from MASTER)</t>
+  </si>
+  <si>
+    <t>PRODUCT_FEATURES — Product features</t>
+  </si>
+  <si>
+    <t>Feature backlog — brief §61-62</t>
+  </si>
+  <si>
+    <t>Feature</t>
+  </si>
+  <si>
+    <t>Bucket</t>
+  </si>
+  <si>
+    <t>Linked Tasks</t>
+  </si>
+  <si>
+    <t>Linked Done</t>
+  </si>
+  <si>
+    <t>Linked Total</t>
+  </si>
+  <si>
+    <t>Document integrity</t>
+  </si>
+  <si>
+    <t>NOW</t>
+  </si>
+  <si>
+    <t>EDIT-001,EDIT-005,FID-002</t>
+  </si>
+  <si>
+    <t>Brief 62: NOW #1</t>
+  </si>
+  <si>
+    <t>Fidelity</t>
+  </si>
+  <si>
+    <t>DOCX-011,TEST-022</t>
+  </si>
+  <si>
+    <t>Brief 62: NOW #2</t>
+  </si>
+  <si>
+    <t>Security</t>
+  </si>
+  <si>
+    <t>SEC-010,SEC-012,SEC-014</t>
+  </si>
+  <si>
+    <t>Brief 62: NOW #3</t>
+  </si>
+  <si>
+    <t>Performance</t>
+  </si>
+  <si>
+    <t>PERF-001,PERF-003,PERF-004</t>
+  </si>
+  <si>
+    <t>Brief 62: NOW #4</t>
+  </si>
+  <si>
+    <t>PDF -&gt; editable</t>
+  </si>
+  <si>
+    <t>P2E-002,P2E-005</t>
+  </si>
+  <si>
+    <t>Brief 62: NOW #5</t>
+  </si>
+  <si>
+    <t>TRAN-001,TRAN-006</t>
+  </si>
+  <si>
+    <t>Brief 62: NOW #6</t>
+  </si>
+  <si>
+    <t>FONT-002,FONT-003</t>
+  </si>
+  <si>
+    <t>Brief 62: NOW #7</t>
+  </si>
+  <si>
+    <t>Review Changes</t>
+  </si>
+  <si>
+    <t>REV-001,REV-002</t>
+  </si>
+  <si>
+    <t>Brief 62: NOW #8</t>
+  </si>
+  <si>
+    <t>HLTH-001,HLTH-002</t>
+  </si>
+  <si>
+    <t>Brief 62: NOW #9</t>
+  </si>
+  <si>
+    <t>FMT-001,FMT-002,FMT-003</t>
+  </si>
+  <si>
+    <t>Brief 62: NOW #10</t>
+  </si>
+  <si>
+    <t>OCR</t>
+  </si>
+  <si>
+    <t>Part of PDF -&gt; editable (brief 43)</t>
+  </si>
+  <si>
+    <t>Multilingual support</t>
+  </si>
+  <si>
+    <t>TRAN-007,FONT-003</t>
+  </si>
+  <si>
+    <t>Part of translation + FontResolver</t>
+  </si>
+  <si>
+    <t>RTL</t>
+  </si>
+  <si>
+    <t>FONT-003,FONT-004</t>
+  </si>
+  <si>
+    <t>Part of FontResolver</t>
+  </si>
+  <si>
+    <t>CJK</t>
+  </si>
+  <si>
+    <t>Glossary</t>
+  </si>
+  <si>
+    <t>Part of translation MVP (brief 49)</t>
+  </si>
+  <si>
+    <t>Terminology lock</t>
+  </si>
+  <si>
+    <t>Citation preservation</t>
+  </si>
+  <si>
+    <t>Preservation is fidelity work; a citation editor is LATER</t>
+  </si>
+  <si>
+    <t>Bibliography preservation</t>
+  </si>
+  <si>
+    <t>Preservation is fidelity work</t>
+  </si>
+  <si>
+    <t>Content controls</t>
+  </si>
+  <si>
+    <t>Preserve now; editing content controls NEXT</t>
+  </si>
+  <si>
+    <t>Custom fields</t>
+  </si>
+  <si>
+    <t>Preserve custom properties and fields now; an editor NEXT</t>
+  </si>
+  <si>
+    <t>Document compare</t>
+  </si>
+  <si>
+    <t>NEXT</t>
+  </si>
+  <si>
+    <t>Brief 62: NEXT</t>
+  </si>
+  <si>
+    <t>Version compare</t>
+  </si>
+  <si>
+    <t>Brief 62: NEXT (batch processing)</t>
+  </si>
+  <si>
+    <t>After the translation MVP</t>
+  </si>
+  <si>
+    <t>Table repair</t>
+  </si>
+  <si>
+    <t>List repair</t>
+  </si>
+  <si>
+    <t>Brief 62: NEXT (accessibility)</t>
+  </si>
+  <si>
+    <t>Heading hierarchy checker</t>
+  </si>
+  <si>
+    <t>Link checker</t>
+  </si>
+  <si>
+    <t>Alt-text checker</t>
+  </si>
+  <si>
+    <t>HLTH-001,FEAT-010</t>
+  </si>
+  <si>
+    <t>Metadata editor</t>
+  </si>
+  <si>
+    <t>Global style replacement</t>
+  </si>
+  <si>
+    <t>Find/replace with formatting</t>
+  </si>
+  <si>
+    <t>Tracked change cleanup</t>
+  </si>
+  <si>
+    <t>Template extraction</t>
+  </si>
+  <si>
+    <t>Document-to-template</t>
+  </si>
+  <si>
+    <t>Template matching</t>
+  </si>
+  <si>
+    <t>Advanced template sharing</t>
+  </si>
+  <si>
+    <t>Teams</t>
+  </si>
+  <si>
+    <t>Translation memory</t>
+  </si>
+  <si>
+    <t>PDF merge/split</t>
+  </si>
+  <si>
+    <t>Page reorder</t>
+  </si>
+  <si>
+    <t>Page rotate</t>
+  </si>
+  <si>
+    <t>Page delete</t>
+  </si>
+  <si>
+    <t>Page extract</t>
+  </si>
+  <si>
+    <t>Merge documents</t>
+  </si>
+  <si>
+    <t>LATER</t>
+  </si>
+  <si>
+    <t>Split documents</t>
+  </si>
+  <si>
+    <t>Watermark</t>
+  </si>
+  <si>
+    <t>Forms (advanced)</t>
+  </si>
+  <si>
+    <t>Brief 62: LATER</t>
+  </si>
+  <si>
+    <t>SmartArt editing</t>
+  </si>
+  <si>
+    <t>Brief 62: LATER; SmartArt is preserved, not edited</t>
+  </si>
+  <si>
+    <t>OLE</t>
+  </si>
+  <si>
+    <t>Brief 62: LATER; OLE objects preserved, not edited</t>
+  </si>
+  <si>
+    <t>Full tracked-change editor</t>
+  </si>
+  <si>
+    <t>Advanced citation manager</t>
+  </si>
+  <si>
+    <t>Advanced drawing editor</t>
+  </si>
+  <si>
+    <t>Layout-preserving PDF editing (frames/anchors)</t>
+  </si>
+  <si>
+    <t>ARCHITECTURE_ONLY</t>
+  </si>
+  <si>
+    <t>Phase 9: architecture and hooks only</t>
+  </si>
+  <si>
+    <t>Product tasks (live from MASTER)</t>
+  </si>
+  <si>
+    <t>TRANSLATION — Translation and fonts</t>
+  </si>
+  <si>
+    <t>Translation MVP and FontResolver. Categories: TRANSLATION, FONT. Rows are formulas over MASTER — change task data in MASTER or with tools/tracker/tracker.py.</t>
+  </si>
+  <si>
+    <t>PDF_TO_EDITABLE — PDF to editable</t>
+  </si>
+  <si>
+    <t>PDF to editable document conversion. Categories: P2E. Rows are formulas over MASTER — change task data in MASTER or with tools/tracker/tracker.py.</t>
+  </si>
+  <si>
+    <t>BILLING_PLANS — Plans and billing</t>
+  </si>
+  <si>
+    <t>Initial plan hypothesis — brief §64: configurable defaults, not final prices; confirm against measured AI and infrastructure cost. Blue = input.</t>
+  </si>
+  <si>
+    <t>Usage unit / feature</t>
+  </si>
+  <si>
+    <t>FREE</t>
+  </si>
+  <si>
+    <t>PRO</t>
+  </si>
+  <si>
+    <t>BUSINESS</t>
+  </si>
+  <si>
+    <t>Documents / month</t>
+  </si>
+  <si>
+    <t>BUSINESS: per workspace</t>
+  </si>
+  <si>
+    <t>PDF conversion pages / month</t>
+  </si>
+  <si>
+    <t>OCR pages / month</t>
+  </si>
+  <si>
+    <t>Translation characters / month</t>
+  </si>
+  <si>
+    <t>AI operations / month</t>
+  </si>
+  <si>
+    <t>Exports / month</t>
+  </si>
+  <si>
+    <t>high</t>
+  </si>
+  <si>
+    <t>BUSINESS: 'high export limits', no number given</t>
+  </si>
+  <si>
+    <t>Templates</t>
+  </si>
+  <si>
+    <t>basic</t>
+  </si>
+  <si>
+    <t>custom</t>
+  </si>
+  <si>
+    <t>shared</t>
+  </si>
+  <si>
+    <t>Formatting</t>
+  </si>
+  <si>
+    <t>Format by Example</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>Advanced Document Health</t>
+  </si>
+  <si>
+    <t>yes</t>
+  </si>
+  <si>
+    <t>Version history</t>
+  </si>
+  <si>
+    <t>no</t>
+  </si>
+  <si>
+    <t>reasonable limits</t>
+  </si>
+  <si>
+    <t>Team workspace</t>
+  </si>
+  <si>
+    <t>Priority processing</t>
+  </si>
+  <si>
+    <t>Advanced controls</t>
+  </si>
+  <si>
+    <t>Billing and plan tasks (live from MASTER)</t>
+  </si>
+  <si>
+    <t>INFRA — Infrastructure</t>
+  </si>
+  <si>
+    <t>Tracker, jobs, storage, observability, deployment, documentation. Categories: INFRA, JOBS, STORAGE, OBSERVABILITY, DOCS. Rows are formulas over MASTER — change task data in MASTER or with tools/tracker/tracker.py.</t>
+  </si>
+  <si>
+    <t>Timestamp</t>
+  </si>
+  <si>
+    <t>Task ID</t>
+  </si>
+  <si>
+    <t>Change</t>
+  </si>
+  <si>
+    <t>Files</t>
+  </si>
+  <si>
+    <t>Created SmartDoc_Master_Implementation_Tracker.xlsx from the 2026-09-26 audit findings and the brief's phases: 151 tasks, 20 findings, 15 release gates.</t>
+  </si>
+  <si>
+    <t>tools/tracker/tracker.py, tools/tracker/seed.py</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>Built the Excel control centre: MASTER with 151 stable-ID tasks from the audit findings and the brief's 19 phases, CRITICAL_FIXES (20 findings -&gt; fix tasks, live status), 14 category views, DASHBOARD (totals, completion/verified %, phase %, category %, P0/P1 remaining), CHANGE_LOG, SESSION_STATE, RELEASE_GATES GATE-001..015. Formulas verified in Excel against independently computed values.</t>
+  </si>
+  <si>
+    <t>tools/tracker/*, SmartDoc_Master_Implementation_Tracker.xlsx, .gitignore</t>
+  </si>
+  <si>
+    <t>Resume reminder set with the platform scheduler; it fired and resumed the work. It only fires while this session is open and idle, which is recorded in AI-CONTINUATION.md.</t>
+  </si>
+  <si>
+    <t>Created the checkpoint system: AI-CONTINUATION.md with CURRENT STATE / LAST VERIFIED / WHAT WAS CHANGED / WHAT PASSED / WHAT FAILED / WHAT REMAINS / NEXT ACTION / IMPORTANT WARNINGS, session-state.json mirrored into SESSION_STATE by tracker.py state, and the brief saved verbatim for future sessions.</t>
+  </si>
+  <si>
+    <t>docs/AI-CONTINUATION.md, docs/session-state.json, docs/implementation-brief.md</t>
+  </si>
+  <si>
+    <t>Baseline backend suite: 643 passed, 1 skipped (optional real-Word check), 0 failed in 88 s on ea69829. Recorded as RUN-0001.</t>
+  </si>
+  <si>
+    <t>Baseline frontend: eslint clean, tsc clean, Vitest 46 passed in 6 files, production build succeeded. Recorded as RUN-0002..RUN-0005.</t>
+  </si>
+  <si>
+    <t>Baseline E2E: 16 Playwright workflows passed against the throwaway stack (SQLite backend :8100, production build :3100). The brief's 24-workflow target is TEST-040; temp-dir leak logged as TEST-006.</t>
+  </si>
+  <si>
+    <t>Baseline database: alembic head 85211092fe4c, check reports no drift, full down/up cycle clean; PostgreSQL offline SQL builds 14 tables with RLS; Supabase has all 8 migrations and only INFO-level advisor notices.</t>
+  </si>
+  <si>
+    <t>Baseline dependency audit: pip-audit finds no known vulnerabilities in requirements.lock or requirements-dev.lock; npm audit reports 0 vulnerabilities (production and dev).</t>
+  </si>
+  <si>
+    <t>Baseline infrastructure inspected: compose file valid with 8 services, arq worker and in-process job backends, local and S3 storage providers. Docker images were not built (daemon not running) - left to INFRA-010.</t>
+  </si>
+  <si>
+    <t>Baseline fixtures: the repository's 12 golden DOCX are generated by python-docx (not Word-authored) plus one PDF; the audit's 17 Word-authored fixtures still live outside the repo and move in with TEST-020.</t>
+  </si>
+  <si>
+    <t>Wrote docs/architecture/current-baseline.md: stack versions, the 11 baseline checks with commands and results, the migration chain and live database state, fixture inventory, audit performance figures, and what the baseline could not verify (Docker images, real AI model, Stripe, e-mail, hosting).</t>
+  </si>
+  <si>
+    <t>INFRA-001, INFRA-002, INFRA-003, TEST-001, TEST-002, TEST-003, TEST-004, TEST-005, SEC-001, INFRA-004, DOCS-001</t>
+  </si>
+  <si>
+    <t>Phase 0 committed (4da4ecb, pushed to feature/smartdoc-production-hardening): tracker, checkpoint system and measured baseline. All 11 phase-0 tasks DONE; no production code changed.</t>
+  </si>
+  <si>
+    <t>see commit 4da4ecb</t>
+  </si>
+  <si>
+    <t>Model now holds blocks nested inside table cells, list items and quotes as Elements (authoritative when set; inline keeps plain text), plus list numbering start/format; nesting capped at 8 levels (422 beyond). schemaVersion stays 1: the fields are additive.</t>
+  </si>
+  <si>
+    <t>backend/app/models/document.py, backend/tests/test_document_nesting.py</t>
+  </si>
+  <si>
+    <t>Regenerated the OpenAPI schema and the frontend's generated types for the nested-block and numbering fields; the contract test and the type check pass.</t>
+  </si>
+  <si>
+    <t>frontend/types/generated/*, frontend/types/document.ts</t>
+  </si>
+  <si>
+    <t>Backend readers now see nested blocks: pasted pictures inside cells/list items/quotes are validated and moved to asset storage like top-level ones (security and quota), exports fetch their assets, and the links health check covers list items, cells and nested blocks.</t>
+  </si>
+  <si>
+    <t>backend/app/services/image_assets.py, backend/app/services/document_service.py, backend/app/formatting/health.py</t>
+  </si>
+  <si>
+    <t>Word export renders nested blocks in cells, list items and quotes in reading order (verified by text order), numbers lists from their start in their format, and writes pictures' alt text.</t>
+  </si>
+  <si>
+    <t>backend/app/export/docx_export.py</t>
+  </si>
+  <si>
+    <t>PDF export renders nested blocks and list numbering (start/format); nested numbered levels now use the same a./i. sequence as the Word export instead of 1. everywhere.</t>
+  </si>
+  <si>
+    <t>backend/app/export/pdf_export.py</t>
+  </si>
+  <si>
+    <t>The editor mapping is total over the schema (tested against getSchema(editorExtensions)); anything unknown stops the save with a visible 'Not saved' message instead of being dropped, and the last saved version stays untouched.</t>
+  </si>
+  <si>
+    <t>frontend/editor/*</t>
+  </si>
+  <si>
+    <t>frontend/editor/nestedBlocks.test.ts (7 refusal cases); frontend/editor/useAutoSave.test.tsx (3)</t>
+  </si>
+  <si>
+    <t>Playwright pastes rich HTML (lists, code and a picture in table cells; a list in a quote; code in a list item; a list starting at 3 in letters), waits for autosave and reloads: everything is still there and no 'Not saved' appears.</t>
+  </si>
+  <si>
+    <t>frontend/e2e/nested.spec.ts</t>
+  </si>
+  <si>
+    <t>CORE-001, CORE-002, CORE-003, EDIT-001, EDIT-002, EDIT-003, EDIT-004, EDIT-005, EDIT-006, DOCX-001, PDF-001</t>
+  </si>
+  <si>
+    <t>Committed phase-01a-editor-integrity (1fe27a9, pushed): nested blocks in cells, list items and quotes survive the editor, the backend and both exports; unknown content stops the save visibly. AUD-01 fix tasks all DONE.</t>
+  </si>
+  <si>
+    <t>Import now produces a Document Fidelity Report: the importer's notes as items (feature, policy, count, content lost) plus an independent content check - the source's words (DOCX XML read separately from the importer, Markdown by what it renders, PDF extracted text) against the document's, in order. 'Verified' only when identical; differences listed with context (missing/added/changed/moved).</t>
+  </si>
+  <si>
+    <t>backend/app/fidelity/*, backend/app/models/document.py, backend/app/services/ingestion_service.py</t>
+  </si>
+  <si>
+    <t>Every importer note now carries a stable feature key and a brief-§90 policy class; review count and content-loss count are derived from them.</t>
+  </si>
+  <si>
+    <t>The editor shows the import's verdict in the status bar and a Проверка panel: content verified / differs (with word-level differences) / body complete but some content left out, then each item by policy. Browser check with a05 caught and fixed a misleading 'No content changes' when header text had been left out.</t>
+  </si>
+  <si>
+    <t>frontend/editor/panels/FidelityPanel.tsx, frontend/editor/EditorStatusBar.tsx, frontend/editor/DocumentEditorShell.tsx</t>
+  </si>
+  <si>
+    <t>FID-001, FID-004, FID-005, INFRA-005</t>
+  </si>
+  <si>
+    <t>Committed phase-01b-fidelity-report (8a330be, pushed): import fidelity report with policy classes and an independent word-level content check, shown in the editor; throwaway preview scripts.</t>
+  </si>
+  <si>
+    <t>Exports now report what they approximate or leave out (missing pictures, WebP a Word file can't hold, tables restyled for Word-sourced documents, edited kept fragments, page breaks in PDF tables, PDF comments/equations/fields/internal links, scripts the PDF can't lay out, alt text) and re-read the file: a Word export must hold exactly the document's words, a PDF every word in order (its own list numbers and page headers allowed). Shown under the Download button; the job result carries it.</t>
+  </si>
+  <si>
+    <t>Committed phase-01c-export-report (e55412f, pushed): export fidelity report with read-back content check, shown in the Export menu.</t>
+  </si>
+  <si>
+    <t>Added the machine-readable capability matrix (brief §91): 67 document features with import/edit/export/round-trip support and the policy the fidelity report uses, served at GET /api/v1/capabilities. Tests tie it to the code both ways, require a test for every clean round trip and a task for every unreported gap; writing it exposed unreported gaps now tracked (EDIT-012, DOCX-027).</t>
+  </si>
+  <si>
+    <t>backend/app/capabilities.py, backend/app/api/capabilities.py, backend/app/main.py, backend/tests/test_capabilities.py, frontend/types/generated/*</t>
+  </si>
+  <si>
+    <t>Committed phase-01d-capability-matrix (fcf30d7, pushed).</t>
+  </si>
+  <si>
+    <t>FID-002: import report now names empty spacing paragraphs, unsafe link addresses and per-section differences (page setup, odd/even breaks, page numbering, borders, line numbers, vertical alignment); matrix rows docx.empty_paragraphs + docx.sections updated</t>
+  </si>
+  <si>
+    <t>backend/app/fidelity/docx_detect.py, backend/app/fidelity/imports.py, backend/app/parsers/docx.py, backend/app/parsers/docx_inline.py, backend/app/capabilities.py, backend/tests/test_docx_detect.py</t>
+  </si>
+  <si>
+    <t>DOCX-015: section breaks break the page only where Word does (next section's w:type decides); continuous breaks no longer become page breaks</t>
+  </si>
+  <si>
+    <t>DOCX-016: list number formats, start values and continuation round-trip; custom and multi-level labels reported</t>
+  </si>
+  <si>
+    <t>DOCX-012: Word core properties round-trip; custom properties and sensitivity labels reported without values</t>
+  </si>
+  <si>
+    <t>tests/test_docx_detect.py::test_the_files_own_properties_go_back_into_word_not_the_templates, tests/test_docx_detect.py::test_metadata_that_is_not_kept_is_reported_without_its_values</t>
+  </si>
+  <si>
+    <t>DOCX-026: unsafe link addresses reported instead of silently dropped</t>
+  </si>
+  <si>
+    <t>Golden JSON export is deterministic (uuid5 ids by order, fixed timestamps) so a regenerated fixture only differs where the importer's output did</t>
+  </si>
+  <si>
+    <t>backend/scripts/export_golden_json.py, frontend/tests/fixtures/golden/*.json</t>
+  </si>
+  <si>
+    <t>two consecutive exports byte-identical; tests/test_golden_documents.py::test_the_frontend_golden_json_is_current</t>
+  </si>
+  <si>
+    <t>FID-002 committed and pushed (phase-01e-import-detections)</t>
+  </si>
+  <si>
+    <t>SEC-022: formatting rule values validated at every entry and at resolve; CSS break-out via element style/page settings/instructions closed</t>
+  </si>
+  <si>
+    <t>backend/app/formatting/values.py, backend/app/formatting/engine.py, backend/app/schemas/formatting.py, backend/app/schemas/document.py, backend/app/ai/instruction_extraction.py, backend/tests/test_rule_values.py</t>
+  </si>
+  <si>
+    <t>FMT-005: instruction-path rule values validated before reaching CSS/export (with SEC-022)</t>
+  </si>
+  <si>
+    <t>EDIT-008: pasted/shortcut alignment saved as the element's own style and kept on split; paste into an empty paragraph keeps the pasted paragraphs' attributes</t>
+  </si>
+  <si>
+    <t>frontend/editor/tiptapToDocument.ts, frontend/editor/documentToTiptap.ts, frontend/editor/useAutoSave.ts, frontend/editor/pasteIntoEmptyBlock.ts, frontend/editor/extensions.ts, frontend/services/api/documents.ts, backend/app/schemas/document.py, backend/app/formatting/engine.py, backend/app/services/document_service.py, backend/app/api/documents.py</t>
+  </si>
+  <si>
+    <t>EDIT-009: pasted picture size kept as the picture's width share</t>
+  </si>
+  <si>
+    <t>EDIT-012: values outside the model named in the status bar and the Проверка panel</t>
+  </si>
+  <si>
+    <t>EDIT-011: cell alignment from pasted cells kept per column; differing cells and column widths reported</t>
+  </si>
+  <si>
+    <t>EDIT-008, EDIT-009, EDIT-012, SEC-022, FMT-005</t>
+  </si>
+  <si>
+    <t>Committed and pushed phase-01f-editor-direct-formatting</t>
+  </si>
+  <si>
+    <t>EDIT-010: link titles kept from Word/Markdown through the editor back into Word</t>
+  </si>
+  <si>
+    <t>backend/app/models/document.py, backend/app/parsers/docx_inline.py, backend/app/parsers/docx.py, backend/app/export/docx_export.py, backend/app/parsers/markdown.py, frontend/editor/tiptapToDocument.ts, frontend/editor/documentToTiptap.ts</t>
+  </si>
+  <si>
+    <t>FID-006: Markdown pictures named as left out (content), thematic breaks kept as rules</t>
+  </si>
+  <si>
+    <t>backend/app/parsers/markdown.py, backend/app/capabilities.py, backend/tests/test_capabilities.py, backend/tests/test_markdown_parser.py</t>
+  </si>
+  <si>
+    <t>EDIT-011: cell alignment/widths the model can't hold are named; keeping them moves to DOCX-017</t>
+  </si>
+  <si>
+    <t>EDIT-007: marks in one canonical order (MarkType) on both sides; opening a document saves nothing</t>
+  </si>
+  <si>
+    <t>backend/app/models/document.py, frontend/editor/tiptapToDocument.ts</t>
+  </si>
+  <si>
+    <t>TEST-010: nested-structure regression suite consolidated and verified</t>
+  </si>
+  <si>
+    <t>EDIT-008, EDIT-010, FID-006</t>
+  </si>
+  <si>
+    <t>Phase 1 browser check in the throwaway stack: Markdown doc with a picture -&gt; 'Body text complete, some content left out · 1 to review' (picture named with its description), '---' imported as a rule; pasted centred line + 160px picture + hsl colour + titled link at the end -&gt; status 'Saved · 1 formatting change not kept', Проверка 'While editing' lists the colour; after reload: line centred, picture width 24.9%, link title kept, notice gone</t>
+  </si>
+  <si>
+    <t>manual browser check (throwaway stack, fresh SQLite)</t>
+  </si>
+  <si>
+    <t>DOCS-011: documentation tree started for Phase 1 (document model, fidelity, docx, formatting, security, testing)</t>
+  </si>
+  <si>
+    <t>EDIT-007, EDIT-010, EDIT-011, FID-006, TEST-010, DOCS-011</t>
+  </si>
+  <si>
+    <t>Committed and pushed phase-01g-phase-1-complete; Phase 1 complete</t>
+  </si>
+  <si>
+    <t>AI-001: order/count/token/numeric/punctuation-aware comparator for AI output, with classified differences</t>
+  </si>
+  <si>
+    <t>backend/app/fidelity/text_check.py, backend/tests/test_ai_fidelity.py</t>
+  </si>
+  <si>
+    <t>AI-002: numbers and units protected; changed_numbers for cross-language checks</t>
+  </si>
+  <si>
+    <t>AI-003: structure analysis refuses answers that alter the text, per piece, logging without content</t>
+  </si>
+  <si>
+    <t>backend/app/ai/structure_analysis.py</t>
+  </si>
+  <si>
+    <t>AI-004: adversarial fidelity tests for every alteration the brief names</t>
+  </si>
+  <si>
+    <t>AI-001, AI-002, AI-003, AI-004</t>
+  </si>
+  <si>
+    <t>Committed and pushed phase-02a-ai-fidelity-check</t>
+  </si>
+  <si>
+    <t>AI-005: AI operations classified FORMAT/STRUCTURE/CONTENT; per-element instruction styles no longer dropped by the formatting pass</t>
+  </si>
+  <si>
+    <t>backend/app/formatting/proposals.py, backend/app/services/document_service.py</t>
+  </si>
+  <si>
+    <t>REV-001: change model with categories, used for proposals</t>
+  </si>
+  <si>
+    <t>backend/app/models/document.py, frontend/types/document.ts</t>
+  </si>
+  <si>
+    <t>AI-006: PLAN-&gt;VALIDATE-&gt;PREVIEW-&gt;ACCEPT-&gt;APPLY for AI content changes</t>
+  </si>
+  <si>
+    <t>backend/app/formatting/proposals.py, backend/app/services/document_service.py, backend/app/api/documents.py, backend/app/jobs/runner.py, backend/app/schemas/document.py, backend/app/schemas/jobs.py</t>
+  </si>
+  <si>
+    <t>AI-007: proposal review UI with accept/reject, E2E verified</t>
+  </si>
+  <si>
+    <t>frontend/editor/panels/ProposalsList.tsx, frontend/editor/panels/InstructionsPanel.tsx, frontend/editor/EditorStatusBar.tsx, frontend/editor/useFormatting.ts, frontend/services/api/documents.ts, frontend/services/api/jobs.ts, backend/scripts/e2e_ai.py, backend/scripts/e2e_server.py</t>
+  </si>
+  <si>
+    <t>AI-005, REV-001, AI-006, AI-007</t>
+  </si>
+  <si>
+    <t>Committed and pushed phase-02b-ai-proposals</t>
+  </si>
+  <si>
+    <t>AI-008: per-job/per-request AI call and time budget; no unbounded retries</t>
+  </si>
+  <si>
+    <t>backend/app/ai/budget.py, backend/app/config.py, backend/app/jobs/runner.py, backend/app/api/deps.py, backend/app/ai/structure_analysis.py</t>
+  </si>
+  <si>
+    <t>Committed and pushed phase-02c-ai-budget</t>
+  </si>
+  <si>
+    <t>AI-009: prompt-injection review; AI answer fields bounded; hostile-document tests</t>
+  </si>
+  <si>
+    <t>backend/app/ai/schemas.py, backend/app/ai/structure_analysis.py, backend/tests/test_prompt_injection.py</t>
+  </si>
+  <si>
+    <t>SEC-018: prompt injection / AI output abuse covered by AI-009's tests</t>
+  </si>
+  <si>
+    <t>AI-001, AI-005, AI-007, AI-009</t>
+  </si>
+  <si>
+    <t>Phase 2 gate: backend 817 passed/1 skipped, Vitest 117, Playwright 20; browser check in the throwaway stack - 'make the title red and delete “This draft paragraph”': title red at once, the paragraph kept and shown under Changes to review (struck through, with the instruction), notice + '1 AI change to review'; Accept removed it, reload kept it removed with nothing pending</t>
+  </si>
+  <si>
+    <t>full suites + manual browser check</t>
+  </si>
+  <si>
+    <t>DOCX-010: original Word package kept as an immutable, checksummed asset</t>
+  </si>
+  <si>
+    <t>backend/app/models/document.py, backend/app/services/document_service.py</t>
+  </si>
+  <si>
+    <t>DOCX-011: Word exports written into the original package; import report reflects what they keep</t>
+  </si>
+  <si>
+    <t>backend/app/export/docx_export.py, backend/app/fidelity/imports.py, backend/app/fidelity/docx_source.py, backend/app/fidelity/docx_detect.py, backend/app/fidelity/exports.py, backend/app/jobs/runner.py, backend/app/api/documents.py, backend/app/capabilities.py</t>
+  </si>
+  <si>
+    <t>TEST-023: independent package validation of every Word export</t>
+  </si>
+  <si>
+    <t>backend/app/export/package_check.py, backend/tests/test_package_check.py</t>
+  </si>
+  <si>
+    <t>DOCX-012: metadata preserved (core in the model, app/custom/labels via the original package)</t>
+  </si>
+  <si>
+    <t>DOCX-028: unchanged blocks keep their original XML in Word exports; server-side provenance; earlier sections follow page setup, header and page-number changes; lost sections reported; golden 13-kept-blocks + E2E.</t>
+  </si>
+  <si>
+    <t>backend/app/export/provenance.py, backend/app/export/docx_export.py, backend/app/parsers/docx.py, backend/app/models/document.py, backend/app/services/document_service.py, backend/app/fidelity/imports.py, backend/app/fidelity/exports.py, backend/app/capabilities.py, frontend/editor/tiptapToDocument.ts, frontend/e2e/kept-blocks.spec.ts, docs/docx/README.md</t>
+  </si>
+  <si>
+    <t>DOCX-028 committed and pushed as c8c2d27 (phase-03b-original-blocks).</t>
+  </si>
+  <si>
+    <t>DOCX-025: Word's hidden text stays hidden - hidden mark with Word's style resolution, editor shows it only on request, vanish in Word exports, left out of PDF with a note, consistent content checks.</t>
+  </si>
+  <si>
+    <t>backend/app/models/document.py, backend/app/parsers/docx_inline.py, backend/app/parsers/docx_styles.py, backend/app/parsers/docx.py, backend/app/fidelity/docx_detect.py, backend/app/fidelity/content.py, backend/app/fidelity/exports.py, backend/app/export/docx_export.py, backend/app/export/pdf_export.py, frontend/editor/hiddenText.ts, frontend/editor/EditorStatusBar.tsx, frontend/editor/DocumentEditorShell.tsx, frontend/app/globals.css</t>
+  </si>
+  <si>
+    <t>DOCX-025 committed and pushed as 7d1af86 (phase-03c-hidden-text).</t>
+  </si>
+  <si>
+    <t>DOCX-013 part 1: underline and strike styles, capitals, small capitals, spacing and raised/lowered text kept through import, editor, Word and PDF; paragraph-style formatting turned off by a run fixed.</t>
+  </si>
+  <si>
+    <t>backend/app/models/document.py, backend/app/parsers/docx_inline.py, backend/app/parsers/docx_styles.py, backend/app/parsers/docx.py, backend/app/export/docx_export.py, backend/app/export/pdf_export.py, backend/app/fidelity/*, frontend/editor/characterFormatting.ts, frontend/editor/tiptapToDocument.ts</t>
+  </si>
+  <si>
+    <t>backend 888 passed/1 skipped (tests/test_character_formatting.py 12); Vitest 128 (editor/characterFormatting.test.ts 3, golden round trip of 02); Playwright 22; tsc + eslint clean</t>
+  </si>
+  <si>
+    <t>DOCX-013 part 1 committed and pushed as 6619159 (phase-03d-character-formatting); part 2 next.</t>
+  </si>
+  <si>
+    <t>6619159</t>
+  </si>
+  <si>
+    <t>FID-007: reports follow the Word copy - kept while unchanged at import, rewritten losses named at export, unsafe links never copied back.</t>
+  </si>
+  <si>
+    <t>backend/app/fidelity/imports.py, backend/app/export/docx_export.py, backend/tests/test_copy_reports.py</t>
+  </si>
+  <si>
+    <t>DOCX-013 part 2: language kept; scale and effects named and kept while unchanged; brief §22 list is now supported, preserved or explicitly named.</t>
+  </si>
+  <si>
+    <t>backend/app/models/document.py, backend/app/parsers/docx_inline.py, backend/app/fidelity/docx_detect.py, frontend/editor/characterFormatting.ts</t>
+  </si>
+  <si>
+    <t>DOCX-013 done: part 1 6619159, part 2 d32c6a6 (phase-03e-copy-reports).</t>
+  </si>
+  <si>
+    <t>FID-007 committed and pushed as d32c6a6.</t>
+  </si>
+  <si>
+    <t>DOCX-014 part 1: right indent, shading, pagination controls, contextual spacing and direction kept through import, CSS, Word and PDF.</t>
+  </si>
+  <si>
+    <t>backend/app/models/document.py, backend/app/formatting/*, backend/app/parsers/docx_styles.py, backend/app/parsers/docx.py, backend/app/export/docx_export.py, backend/app/export/pdf_export.py</t>
+  </si>
+  <si>
+    <t>backend 903 passed/1 skipped (tests/test_paragraph_formatting.py 9); Vitest 129; Playwright 22; tsc + eslint clean</t>
+  </si>
+  <si>
+    <t>DOCX-014 part 1 committed and pushed as eade93e (phase-03f-paragraph-formatting); part 2 next.</t>
+  </si>
+  <si>
     <t>eade93e</t>
   </si>
   <si>
-    <t>Part 2 remaining: paragraph borders (model + exports) and tab stops (detect, keep while unchanged, name when lost).</t>
-  </si>
-  <si>
-    <t>DOCX-015</t>
-  </si>
-  <si>
-    <t>Sections as a first-class concept</t>
-  </si>
-  <si>
-    <t>Breaks (next/continuous/even/odd), orientation, size, margins, columns, header/footer distance, first/even/odd headers, linked-to-previous, page-number restart.</t>
-  </si>
-  <si>
-    <t>tests/test_docx_detect.py::test_a_section_break_breaks_the_page_only_where_word_does</t>
-  </si>
-  <si>
-    <t>backend/models, parsers, export</t>
-  </si>
-  <si>
-    <t>Fixed: a section's w:type describes how THAT section starts (ECMA-376 17.6.22) - the importer used the ending section's own type, so a continuous break became a page break and continuous-&gt;new-page put the break between the wrong sections (probe confirmed). Now the next section's type decides. Per-section differences are reported (FID-002). Remaining: sections as a first-class model concept (orientation/margins/columns/headers per section, page-number restart) and export of several sections.; With DOCX-011 the last section's properties (columns, page numbering, borders, line numbers, vertical alignment, header/footer variants) are kept in Word exports; earlier sections' are still reported lost.; DOCX-028: earlier sections now survive in Word exports while their ending paragraph is unchanged; page setup/header/page-number changes apply to them; a lost one is reported (export.docx.section_lost). Modelling sections is still this task.</t>
-  </si>
-  <si>
-    <t>DOCX-016</t>
-  </si>
-  <si>
-    <t>Numbering engine</t>
-  </si>
-  <si>
-    <t>Decimal/roman/alpha/bullets, custom prefixes/suffixes, start, restart, continuation, multilevel, numId/abstractNum/ilvl, indentation.</t>
-  </si>
-  <si>
-    <t>tests/test_docx_numbering.py</t>
-  </si>
-  <si>
-    <t>Done so far: top-level list number format (decimal/roman/letters), start value (lvl start + lvlOverride/startOverride) and continuation across interrupting paragraphs imported into Element.numbering and written back to Word (per-level formats, startOverride) and PDF; empty numbered items keep counting. Reported, not kept: custom labels ('Чл. 1.', '(a)'), multi-level labels ('1.1'), numbered headings baked into text. Remaining: prefixes/suffixes, multilevel numbering model, restart semantics per level, indentation.</t>
-  </si>
-  <si>
-    <t>AUD-04</t>
-  </si>
-  <si>
-    <t>DOCX-017</t>
-  </si>
-  <si>
-    <t>Table engine</t>
-  </si>
-  <si>
-    <t>No forced header or Table Grid; widths, heights, margins, borders, shading, v-align, nested tables, repeated header rows, table styles.</t>
-  </si>
-  <si>
-    <t>From EDIT-011 (2026-09-27): add per-cell alignment and column widths to the model (the editor's cell align/colwidth, Word tcW/tblGrid, PDF colWidths); until then the editor names them as not kept.</t>
-  </si>
-  <si>
-    <t>DOCX-018</t>
-  </si>
-  <si>
-    <t>Images</t>
-  </si>
-  <si>
-    <t>Alt text exported; crop, rotation, anchor, wrap, position preserved; WEBP converted on export.</t>
-  </si>
-  <si>
-    <t>Alt text + title now exported (docPr descr/title) with DOCX-001; crop, rotation, WEBP still open.</t>
-  </si>
-  <si>
-    <t>DOCX-019</t>
-  </si>
-  <si>
-    <t>Drawings and text boxes preserved</t>
-  </si>
-  <si>
-    <t>Anchored drawings, text boxes, shapes kept even when not editable.</t>
-  </si>
-  <si>
-    <t>DOCX-028: text boxes and drawings in unchanged paragraphs are copied as they are (grouped with their anchor paragraph).</t>
-  </si>
-  <si>
-    <t>DOCX-020</t>
-  </si>
-  <si>
-    <t>Fields</t>
-  </si>
-  <si>
-    <t>Code/result/relationship; header STYLEREF/DATE live; TOC kept; CITATION/BIBLIOGRAPHY sources preserved; no 'Invalid source specified.'</t>
-  </si>
-  <si>
-    <t>backend/parsers, export</t>
-  </si>
-  <si>
-    <t>DOCX-028: field codes in unchanged blocks are copied as they are; a field spanning paragraphs is never copied half (self-contained check).</t>
-  </si>
-  <si>
-    <t>AUD-18</t>
-  </si>
-  <si>
-    <t>DOCX-021</t>
-  </si>
-  <si>
-    <t>Comment threads</t>
-  </si>
-  <si>
-    <t>Replies, resolved state, authors, ranges preserved (commentsExtended, people).</t>
-  </si>
-  <si>
-    <t>AUD-06</t>
-  </si>
-  <si>
-    <t>DOCX-022</t>
-  </si>
-  <si>
-    <t>Tracked changes preserved</t>
-  </si>
-  <si>
-    <t>Not silently accepted; explicit choice.</t>
-  </si>
-  <si>
-    <t>DOCX-028: blocks holding tracked changes are never copied (always written anew, accepted), so this task's explicit choice is still needed.</t>
-  </si>
-  <si>
-    <t>DOCX-023</t>
-  </si>
-  <si>
-    <t>Content controls preserved</t>
-  </si>
-  <si>
-    <t>w:sdt of every kind kept with its properties.</t>
-  </si>
-  <si>
-    <t>DOCX-028: content controls in unchanged blocks are copied with their properties (E2E proves it through the editor); written anew they are unwrapped (reported lossy at import).</t>
-  </si>
-  <si>
-    <t>DOCX-024</t>
-  </si>
-  <si>
-    <t>Real footnotes and endnotes</t>
-  </si>
-  <si>
-    <t>Notes stay notes on export.</t>
-  </si>
-  <si>
-    <t>DOCX-025</t>
-  </si>
-  <si>
-    <t>Hidden text stays hidden</t>
-  </si>
-  <si>
-    <t>Imported hidden text is kept hidden, shown only on request.</t>
-  </si>
-  <si>
-    <t>MarkType.HIDDEN (appended; no existing mark order changes). Importer resolves w:vanish as Word does: run, character style, paragraph style (the default paragraph style when none), docDefaults; webHidden stays visible; an explicit vanish=0 shows text in a hidden style. The detector uses the default paragraph style the same way and names hidden text as kept hidden (DETECTED_PRESERVED, not a content change). Editor: non-inclusive hidden mark (editor/hiddenText.ts; Word's display:none paste stays hidden), hidden by CSS unless .show-hidden; status bar 'Show hidden text (N words)' toggles it and re-paginates; the Structure panel leaves hidden text out of headings. Word export writes w:vanish (copied blocks keep theirs); PDF doesn't print hidden runs, export.pdf.hidden_text names the word count, and the PDF content check compares visible words (document_words(visible_only=True)); Word-side checks count hidden text on both sides. Golden 02-rich-text gained a hidden sentence (editor round trip in Vitest).</t>
-  </si>
-  <si>
-    <t>backend 876 passed/1 skipped (tests/test_hidden_text.py 7: import resolution, default paragraph style, report, upload + content check + editor save, Word export round trip, PDF text + note + check); Vitest 125 (editor/hiddenText.test.tsx 6, golden round trip of 02); Playwright 22 (e2e/hidden-text.spec.ts: hidden until asked, dotted line when shown, vanish in the Word export); tsc + eslint clean</t>
-  </si>
-  <si>
-    <t>backend/parsers, frontend</t>
-  </si>
-  <si>
-    <t>7d1af86</t>
-  </si>
-  <si>
-    <t>DOCX-028: vanish survives in unchanged blocks only; the model still shows hidden text as ordinary text - next task.</t>
-  </si>
-  <si>
-    <t>DOCX-026</t>
-  </si>
-  <si>
-    <t>Hyperlink policy and no silent autolink</t>
-  </si>
-  <si>
-    <t>Plain-text addresses not turned into links by default; file:/UNC reported.</t>
-  </si>
-  <si>
-    <t>tests/test_docx_detect.py::test_unsafe_links_and_spacing_paragraphs_are_reported</t>
-  </si>
-  <si>
-    <t>Done: links to unsafe addresses (javascript:, file:, UNC...) are kept as plain text and reported (docx.link.unsafe); plain-text addresses turned into links are reported (docx.autolink). Remaining: stop autolinking by default (a setting), per the task.</t>
-  </si>
-  <si>
-    <t>AUD-03,AUD-13</t>
-  </si>
-  <si>
-    <t>FMT-004</t>
-  </si>
-  <si>
-    <t>Render-spec defaults respect the source</t>
-  </si>
-  <si>
-    <t>Imported Word styles are not overridden by defaults (headings not forced bold).</t>
-  </si>
-  <si>
-    <t>backend/formatting</t>
-  </si>
-  <si>
-    <t>TEST-020</t>
-  </si>
-  <si>
-    <t>Word-authored fixtures in the repository</t>
-  </si>
-  <si>
-    <t>20 synthetic Word-authored fixtures, scrubbed of identifying metadata.</t>
-  </si>
-  <si>
-    <t>backend/tests/fixtures/word</t>
-  </si>
-  <si>
-    <t>TEST-021</t>
-  </si>
-  <si>
-    <t>Expected-loss manifests in CI</t>
-  </si>
-  <si>
-    <t>expected-loss.json per fixture; CI compares actual vs expected.</t>
-  </si>
-  <si>
-    <t>TEST-022</t>
-  </si>
-  <si>
-    <t>True fidelity test</t>
-  </si>
-  <si>
-    <t>SOURCE -&gt; import -&gt; format -&gt; editor save -&gt; export -&gt; reimport -&gt; compare SOURCE vs RESULT: content, formatting, metadata, structure separately.</t>
-  </si>
-  <si>
-    <t>TEST-023</t>
-  </si>
-  <si>
-    <t>Independent validation</t>
-  </si>
-  <si>
-    <t>OOXML schema validation, Word when available, docx2python; pdftotext/PyMuPDF for PDF.</t>
-  </si>
-  <si>
-    <t>app/export/package_check.py: an independent package check (zip read directly): well-formed parts, content types, relationships resolving, relationship ids used, defined styles/lists/comments. Found a real defect on first run (python-docx's add_comment refers to an undefined CommentReference style; exports now define it). Every golden export passes, fresh and into its original.</t>
-  </si>
-  <si>
-    <t>tests/test_package_check.py (13)</t>
-  </si>
-  <si>
-    <t>The docx skill's XSD validator needs defusedxml (not installed; installing needs a download) - schema-level validation remains open.</t>
-  </si>
-  <si>
-    <t>DOCX-027</t>
-  </si>
-  <si>
-    <t>Importer builds nested blocks</t>
-  </si>
-  <si>
-    <t>Use TableCell.blocks / ListItem.blocks on import: pictures, lists (with bullets) and nested tables inside cells, pictures inside list items - instead of dropping or flattening them.</t>
-  </si>
-  <si>
-    <t>AUD-01,AUD-03,AUD-08</t>
-  </si>
-  <si>
-    <t>DOCX-028</t>
-  </si>
-  <si>
-    <t>Unchanged blocks keep their original XML in Word exports</t>
-  </si>
-  <si>
-    <t>Blocks the user didn't change are written back as their original XML (fields, content controls, run-level formatting the model can't hold, bookmarks), changed ones regenerated; needs block provenance from the importer and fingerprints.</t>
-  </si>
-  <si>
-    <t>Importer records each top-level element's body children (Element.sourceBlocks: list items, drop caps, derived page breaks); an upload with a kept file stamps content+look fingerprints (Element.sourceHash, app/export/provenance.py: own/kind/body/nested resolved styles; page breaks have no look). docx_export._copy_plan groups elements with their children (uncovered children join the group before) and copies a group verbatim when every element is unchanged, together and in original order, children contiguous, XML self-contained (no tracked changes/note refs/altChunk; balanced fields, bookmarks, comment ranges); everything else is written anew. Provenance is server-side (keep_provenance on PUT /content). Page setup now runs after the body: changed size/margins reach every kept section (orientation kept, landscape turned), a changed main header is rewritten where Word shows it (link to previous), page numbers left out/asked for apply to every section. export.docx.section_lost (LOSSY) names sections lost with a changed paragraph; import report: earlier sections' setup/headers kept while unchanged; PDF names them Word-only. All 13 golden documents stamped + exported into their originals: sound packages, content verified (12-complex rewrites only the footnote paragraph and the note, by design).</t>
-  </si>
-  <si>
-    <t>backend 869 passed/1 skipped (tests/test_original_blocks.py 26 incl. 13 golden; test_source_package.py rewritten claims with export proof; test_golden_documents.py 13 files); Vitest 119 (editor round trip of 13-kept-blocks); Playwright 21 (e2e/kept-blocks.spec.ts: edit in the real editor, untouched paragraphs keep content control, double underline, landscape section); tsc + eslint clean</t>
-  </si>
-  <si>
-    <t>c8c2d27</t>
-  </si>
-  <si>
-    <t>Follow-up of DOCX-011 (package-level patch writer).; Known limit: any restyle (template, instruction) changes the body look, so every block but page breaks is written anew; follow-up DOCX-029. Sections survive only with their ending paragraph until DOCX-015 models them.</t>
-  </si>
-  <si>
-    <t>DOCX-029</t>
-  </si>
-  <si>
-    <t>Restyled blocks keep their original XML where nothing conflicts</t>
-  </si>
-  <si>
-    <t>After a template or instruction restyles a kind of block, copy a block's original XML when its paragraph style is the Word style the export rewrites for that kind and its direct formatting (pPr/rPr) sets none of the properties that changed; today any restyle writes every block anew (content controls, double underline etc. then lost, as the import report says).</t>
-  </si>
-  <si>
-    <t>Found while finishing DOCX-028: the look is part of the fingerprint so the export never shows a stale look.</t>
-  </si>
-  <si>
-    <t>FID-007</t>
-  </si>
-  <si>
-    <t>Reports follow the Word copy</t>
-  </si>
-  <si>
-    <t>With the original kept, the import report names what lives in blocks as kept in the Word export while the paragraph is unchanged, and an export that writes such a block anew names what it lost; a copy never brings back a link the app doesn't allow.</t>
-  </si>
-  <si>
-    <t>fidelity/imports.py KEPT_WHILE_UNCHANGED (content controls, text boxes, charts/shapes/SmartArt, objects, picture crop/rotation/floating, drop caps, empty paragraphs, approximated underlines, character scale, text effects, RTL) -&gt; detected_not_editable 'kept while the paragraph isn't changed or restyled'; docx_export._copy_plan returns rewritten groups, _lost_in/_rewritten_losses -&gt; export.docx.rewritten_blocks (LOSSY, count, kinds incl. proofing exclusions); _safe_links keeps groups with unsafe links (relationships or HYPERLINK fields) from being copied; the PDF's Word-only note covers the features.</t>
-  </si>
-  <si>
-    <t>tests/test_copy_reports.py (6): kept while unchanged at import, rewritten losses named (content controls, stretched text), unsafe javascript: link never copied back, PDF word-only; backend 894 passed/1 skipped; Playwright 22</t>
-  </si>
-  <si>
-    <t>Generalises DOCX-028's section handling (export.docx.section_lost) to everything the model doesn't hold inside blocks.</t>
-  </si>
-  <si>
-    <t>SEC-010</t>
-  </si>
-  <si>
-    <t>Malformed DOCX -&gt; safe 4xx</t>
-  </si>
-  <si>
-    <t>XML/zip/structure errors map to invalid_file; fuzz corpus shows no 500.</t>
-  </si>
-  <si>
-    <t>AUD-12</t>
-  </si>
-  <si>
-    <t>SEC-011</t>
-  </si>
-  <si>
-    <t>Malformed PDF -&gt; safe 4xx</t>
-  </si>
-  <si>
-    <t>Verified with a fuzz corpus.</t>
-  </si>
-  <si>
-    <t>SEC-012</t>
-  </si>
-  <si>
-    <t>Image resource limits</t>
-  </si>
-  <si>
-    <t>Compressed and decompressed size, pixel count, width, height, images per document, total bytes, format allowlist; rejected before rasterisation.</t>
-  </si>
-  <si>
-    <t>backend/security</t>
-  </si>
-  <si>
-    <t>AUD-09</t>
-  </si>
-  <si>
-    <t>SEC-013</t>
-  </si>
-  <si>
-    <t>PDF bombs, huge XML, decompression limits</t>
-  </si>
-  <si>
-    <t>Reviewed and tested limits.</t>
-  </si>
-  <si>
-    <t>SEC-014</t>
-  </si>
-  <si>
-    <t>Href policy</t>
-  </si>
-  <si>
-    <t>Server-side scheme allowlist; javascript:/data:/vbscript:/file: never exported as active links.</t>
-  </si>
-  <si>
-    <t>backend/models, export</t>
-  </si>
-  <si>
-    <t>AUD-13</t>
-  </si>
-  <si>
-    <t>SEC-015</t>
-  </si>
-  <si>
-    <t>Field instruction allowlist</t>
-  </si>
-  <si>
-    <t>No DDE/INCLUDETEXT/INCLUDEPICTURE/external fields accepted from clients or exported.</t>
-  </si>
-  <si>
-    <t>SEC-016</t>
-  </si>
-  <si>
-    <t>External relationships policy</t>
-  </si>
-  <si>
-    <t>No arbitrary external targets in exports.</t>
-  </si>
-  <si>
-    <t>SEC-017</t>
-  </si>
-  <si>
-    <t>Malicious SVG</t>
-  </si>
-  <si>
-    <t>Verified refused everywhere.</t>
-  </si>
-  <si>
-    <t>SEC-018</t>
-  </si>
-  <si>
-    <t>Prompt injection / AI output abuse</t>
-  </si>
-  <si>
-    <t>Tests with hostile documents; outputs validated.</t>
-  </si>
-  <si>
-    <t>Hostile-document tests: the document can't close its fence; out-of-bounds answers refused and fall back; an instruction steered by the document deletes nothing (proposals only) and a CSS break-out value is dropped; style-analysis flags on unknown elements dropped (see AI-009).</t>
-  </si>
-  <si>
-    <t>tests/test_prompt_injection.py</t>
-  </si>
-  <si>
-    <t>SEC-019</t>
-  </si>
-  <si>
-    <t>Error envelope audit</t>
-  </si>
-  <si>
-    <t>Every error {code, message, details, request_id}; no stack traces to users.</t>
-  </si>
-  <si>
-    <t>backend/api</t>
-  </si>
-  <si>
-    <t>SEC-020</t>
-  </si>
-  <si>
-    <t>CSP without 'unsafe-inline' scripts</t>
-  </si>
-  <si>
-    <t>Nonce-based CSP for the Next.js app.</t>
-  </si>
-  <si>
-    <t>TEST-030</t>
-  </si>
-  <si>
-    <t>Security regression suite</t>
-  </si>
-  <si>
-    <t>Fuzz corpus, pixel bombs, href/field policy, IDOR, CSRF.</t>
-  </si>
-  <si>
-    <t>SEC-010,SEC-012,SEC-014,SEC-015</t>
-  </si>
-  <si>
-    <t>AUD-09,AUD-12,AUD-13</t>
-  </si>
-  <si>
-    <t>SEC-021</t>
-  </si>
-  <si>
-    <t>Sensitivity-label metadata in the public repository</t>
-  </si>
-  <si>
-    <t>корекции.docx (committed in 5f2bf9e, pushed) carries 8 MSIP_Label_* custom properties incl. the organisation's tenant SiteId (label: Microsoft default 'General' family, no content marking). Options: leave; scrub the file in a new commit (HEAD only); purge from history (force-push).</t>
-  </si>
-  <si>
-    <t>repository history</t>
-  </si>
-  <si>
-    <t>Needs Boril: the choice involves his organisation's label and possibly rewriting pushed history. The tracker tools now strip MSIP labels on every write; the pre-push scan flags them.</t>
-  </si>
-  <si>
-    <t>SEC-022</t>
-  </si>
-  <si>
-    <t>Formatting rule values can't break out of a style</t>
-  </si>
-  <si>
-    <t>A rule value reaches the editor's style attribute, Word and PDF styles as text. The element-style and page-setting endpoints accepted any string (e.g. 'center;background-image:url(...)'), the AI instruction path too (FMT-005): CSS injection into every viewer's editor.</t>
-  </si>
-  <si>
-    <t>app/formatting/values.py: clean_rule_value per property (the StyleSystem's limits: choices, true/false, one safe font name, renderable colours, bounded numbers with known units, header/footer text &lt;=500). Refused with 422 by the element-style and page-setting endpoints (schemas RuleValue); instruction rules and set_style operations with such values dropped (FMT-005), validate_operations refuses them; stored rules no renderer can use are skipped at resolve (engine._usable) so old documents can't carry them either. All 177 default/template rules pass unchanged.</t>
-  </si>
-  <si>
-    <t>tests/test_rule_values.py (34 cases incl. API 422, stored-rule skip, instruction drop)</t>
-  </si>
-  <si>
-    <t>Found 2026-09-27 while mapping editor alignment (EDIT-008); probe confirmed the raw value in resolvedStyles.</t>
-  </si>
-  <si>
-    <t>PERF-001</t>
-  </si>
-  <si>
-    <t>Linear DOCX table export</t>
-  </si>
-  <si>
-    <t>500x8 table under a recorded threshold (baseline 321 s).</t>
-  </si>
-  <si>
-    <t>AUD-10</t>
-  </si>
-  <si>
-    <t>PERF-002</t>
-  </si>
-  <si>
-    <t>Benchmarks recorded</t>
-  </si>
-  <si>
-    <t>Baseline and current measurements in the PERFORMANCE sheet.</t>
-  </si>
-  <si>
-    <t>tests/perf</t>
-  </si>
-  <si>
-    <t>PERF-003</t>
-  </si>
-  <si>
-    <t>Delta autosave</t>
-  </si>
-  <si>
-    <t>Change-aware patches with a threshold strategy; whole document only when needed.</t>
-  </si>
-  <si>
-    <t>frontend/editor, backend/api</t>
-  </si>
-  <si>
-    <t>PERF-004</t>
-  </si>
-  <si>
-    <t>Bounded, compressed version history</t>
-  </si>
-  <si>
-    <t>Editor history separate from persisted versions; compression/deltas; asset references.</t>
-  </si>
-  <si>
-    <t>PERF-005</t>
-  </si>
-  <si>
-    <t>Editor at 5k-12k blocks</t>
-  </si>
-  <si>
-    <t>Typing latency measured and improved.</t>
-  </si>
-  <si>
-    <t>PERF-006</t>
-  </si>
-  <si>
-    <t>JSON without ASCII escaping</t>
-  </si>
-  <si>
-    <t>Document JSON stored and sent as UTF-8.</t>
-  </si>
-  <si>
-    <t>backend/db</t>
-  </si>
-  <si>
-    <t>PERF-007</t>
-  </si>
-  <si>
-    <t>Safe size limits recorded</t>
-  </si>
-  <si>
-    <t>User-facing maximum sizes, job timeouts, resource ceilings documented and enforced.</t>
-  </si>
-  <si>
-    <t>backend/config</t>
-  </si>
-  <si>
-    <t>AUD-09,AUD-10</t>
-  </si>
-  <si>
-    <t>ACCT-001</t>
-  </si>
-  <si>
-    <t>E-mail sender abstraction</t>
-  </si>
-  <si>
-    <t>SMTP provider + development outbox; no secrets in logs.</t>
-  </si>
-  <si>
-    <t>AUD-14</t>
-  </si>
-  <si>
-    <t>ACCT-002</t>
-  </si>
-  <si>
-    <t>Password reset</t>
-  </si>
-  <si>
-    <t>Single-use, expiring, hashed tokens; rate-limited; no account enumeration.</t>
-  </si>
-  <si>
-    <t>backend/api, frontend</t>
-  </si>
-  <si>
-    <t>ACCT-003</t>
-  </si>
-  <si>
-    <t>E-mail verification</t>
-  </si>
-  <si>
-    <t>Verification tokens and state.</t>
-  </si>
-  <si>
-    <t>ACCT-004</t>
-  </si>
-  <si>
-    <t>Password change</t>
-  </si>
-  <si>
-    <t>Current password required; other sessions revoked.</t>
-  </si>
-  <si>
-    <t>ACCT-005</t>
-  </si>
-  <si>
-    <t>Account deletion</t>
-  </si>
-  <si>
-    <t>Cascading policy: documents, versions, assets, exports, sessions, jobs, usage.</t>
-  </si>
-  <si>
-    <t>ACCT-006</t>
-  </si>
-  <si>
-    <t>Session revocation and cleanup</t>
-  </si>
-  <si>
-    <t>Sign out everywhere; expired/revoked session sweep.</t>
-  </si>
-  <si>
-    <t>ACCT-007</t>
-  </si>
-  <si>
-    <t>Suspicious login handling</t>
-  </si>
-  <si>
-    <t>Lockout and notification strategy.</t>
-  </si>
-  <si>
-    <t>PLAN-001</t>
-  </si>
-  <si>
-    <t>Usage units</t>
-  </si>
-  <si>
-    <t>Documents, exports, PDF pages, OCR pages, translation characters, AI operations, storage, batch jobs.</t>
-  </si>
-  <si>
-    <t>backend/billing</t>
-  </si>
-  <si>
-    <t>AUD-11</t>
-  </si>
-  <si>
-    <t>PLAN-002</t>
-  </si>
-  <si>
-    <t>Configurable plan defaults</t>
-  </si>
-  <si>
-    <t>Free/Pro/Business initial hypotheses as configuration, never hardcoded.</t>
-  </si>
-  <si>
-    <t>PLAN-003</t>
-  </si>
-  <si>
-    <t>Atomic entitlement checks</t>
-  </si>
-  <si>
-    <t>Reservation/locking; concurrency test proves limits hold.</t>
-  </si>
-  <si>
-    <t>PLAN-004</t>
-  </si>
-  <si>
-    <t>Stripe flows review</t>
-  </si>
-  <si>
-    <t>Checkout, portal, upgrade, downgrade, cancel, renewal, failed payment, webhook idempotency.</t>
-  </si>
-  <si>
-    <t>PLAN-005</t>
-  </si>
-  <si>
-    <t>Storage metering including history</t>
-  </si>
-  <si>
-    <t>History and autosave growth counted.</t>
-  </si>
-  <si>
-    <t>AUD-11,AUD-16</t>
-  </si>
-  <si>
-    <t>PDF-010</t>
-  </si>
-  <si>
-    <t>Geometry-aware PDF parser</t>
-  </si>
-  <si>
-    <t>Chars, fonts, sizes, colours, lines, rectangles, images, links, annotations, outlines, forms, metadata, rotation, page boxes.</t>
-  </si>
-  <si>
-    <t>backend/parsers/pdf</t>
-  </si>
-  <si>
-    <t>PDF-011</t>
-  </si>
-  <si>
-    <t>Page classifier</t>
-  </si>
-  <si>
-    <t>TEXT / SCANNED / HYBRID per page with evidence.</t>
-  </si>
-  <si>
-    <t>PDF-012</t>
-  </si>
-  <si>
-    <t>PDF inspection report</t>
-  </si>
-  <si>
-    <t>What the parser found, per page.</t>
-  </si>
-  <si>
-    <t>P2E-001</t>
-  </si>
-  <si>
-    <t>Layout primitives where PDF needs them</t>
-  </si>
-  <si>
-    <t>Page, block, bbox, rotation, confidence, provenance.</t>
-  </si>
-  <si>
-    <t>P2E-002</t>
-  </si>
-  <si>
-    <t>Structure reconstruction</t>
-  </si>
-  <si>
-    <t>Reading order, lines, paragraphs, headings, lists, captions, header/footer bands, columns.</t>
-  </si>
-  <si>
-    <t>backend/pdf</t>
-  </si>
-  <si>
-    <t>P2E-003</t>
-  </si>
-  <si>
-    <t>Images with position</t>
-  </si>
-  <si>
-    <t>Extracted images kept with bbox.</t>
-  </si>
-  <si>
-    <t>P2E-004</t>
-  </si>
-  <si>
-    <t>Tables from PDF</t>
-  </si>
-  <si>
-    <t>Ruling lines and alignment.</t>
-  </si>
-  <si>
-    <t>P2E-005</t>
-  </si>
-  <si>
-    <t>Confidence and conversion report</t>
-  </si>
-  <si>
-    <t>Per element confidence; issues reported; never silent removal.</t>
-  </si>
-  <si>
-    <t>P2E-006</t>
-  </si>
-  <si>
-    <t>OCR provider abstraction</t>
-  </si>
-  <si>
-    <t>Interface (text, confidence, bbox, page, language/script); implementation(s); OCR output untrusted.</t>
-  </si>
-  <si>
-    <t>backend/ocr</t>
-  </si>
-  <si>
-    <t>P2E-007</t>
-  </si>
-  <si>
-    <t>Imported-from-PDF version and UX</t>
-  </si>
-  <si>
-    <t>Editable document vs layout-focused choice; confidence shown.</t>
-  </si>
-  <si>
-    <t>frontend, backend</t>
-  </si>
-  <si>
-    <t>P2E-008</t>
-  </si>
-  <si>
-    <t>PDF fixtures and tests</t>
-  </si>
-  <si>
-    <t>Text, scanned, hybrid, tables, columns, multilingual.</t>
-  </si>
-  <si>
-    <t>P2E-020</t>
-  </si>
-  <si>
-    <t>Layout-preserving architecture</t>
-  </si>
-  <si>
-    <t>Frames/anchors model hooks and design doc.</t>
-  </si>
-  <si>
-    <t>docs, backend/models</t>
-  </si>
-  <si>
-    <t>PDF-020</t>
-  </si>
-  <si>
-    <t>PDF page operations service</t>
-  </si>
-  <si>
-    <t>Reorder, rotate, delete, duplicate, extract, split, merge as a separate service.</t>
-  </si>
-  <si>
-    <t>TRAN-001</t>
-  </si>
-  <si>
-    <t>Segments and tag protocol</t>
-  </si>
-  <si>
-    <t>Segments keep element/run ids, marks, placeholders; never one giant string.</t>
-  </si>
-  <si>
-    <t>backend/translation</t>
-  </si>
-  <si>
-    <t>TRAN-002</t>
-  </si>
-  <si>
-    <t>TranslationProvider abstraction</t>
-  </si>
-  <si>
-    <t>AI provider implementation + deterministic test provider.</t>
-  </si>
-  <si>
-    <t>TRAN-003</t>
-  </si>
-  <si>
-    <t>Translation validation</t>
-  </si>
-  <si>
-    <t>Tags, numbers, units, dates, percentages, identifiers, glossary terms.</t>
-  </si>
-  <si>
-    <t>TRAN-004</t>
-  </si>
-  <si>
-    <t>Glossary and terminology lock</t>
-  </si>
-  <si>
-    <t>Source/target term, domain, locked, case-sensitive.</t>
-  </si>
-  <si>
-    <t>backend/translation, db</t>
-  </si>
-  <si>
-    <t>TRAN-005</t>
-  </si>
-  <si>
-    <t>Selection/paragraph/block translation proposals</t>
-  </si>
-  <si>
-    <t>Preview; accept/reject; undo.</t>
-  </si>
-  <si>
-    <t>TRAN-003,REV-001</t>
-  </si>
-  <si>
-    <t>TRAN-006</t>
-  </si>
-  <si>
-    <t>Whole-document translated version</t>
-  </si>
-  <si>
-    <t>Source kept; translated copy linked.</t>
-  </si>
-  <si>
-    <t>TRAN-007</t>
-  </si>
-  <si>
-    <t>Language, script, direction metadata</t>
-  </si>
-  <si>
-    <t>Auto-detect + manual override.</t>
-  </si>
-  <si>
-    <t>TRAN-008</t>
-  </si>
-  <si>
-    <t>Translation UX</t>
-  </si>
-  <si>
-    <t>Toolbar/context Translate, target language, preview, accept/reject; 'AI-assisted translation - review required'.</t>
-  </si>
-  <si>
-    <t>TRAN-009</t>
-  </si>
-  <si>
-    <t>Translation metering</t>
-  </si>
-  <si>
-    <t>Translation characters as a usage unit.</t>
-  </si>
-  <si>
-    <t>TRAN-010</t>
-  </si>
-  <si>
-    <t>Translation tests</t>
-  </si>
-  <si>
-    <t>Formatting preservation, validation, versions.</t>
-  </si>
-  <si>
-    <t>FONT-001</t>
-  </si>
-  <si>
-    <t>Font catalogue with Unicode coverage</t>
-  </si>
-  <si>
-    <t>fontTools cmap coverage per script, metrics, embeddability.</t>
-  </si>
-  <si>
-    <t>backend/fonts</t>
-  </si>
-  <si>
-    <t>AUD-17</t>
-  </si>
-  <si>
-    <t>FONT-002</t>
-  </si>
-  <si>
-    <t>FontResolver</t>
-  </si>
-  <si>
-    <t>Script segmentation, coverage, fallback chain, embedding, RTL; deterministic first, AI suggestion validated.</t>
-  </si>
-  <si>
-    <t>FONT-003</t>
-  </si>
-  <si>
-    <t>Multilingual PDF rendering</t>
-  </si>
-  <si>
-    <t>Shaping for Arabic/Hebrew/Devanagari, bidi, CJK fonts, emoji handled gracefully.</t>
-  </si>
-  <si>
-    <t>FONT-004</t>
-  </si>
-  <si>
-    <t>DOCX per-script fonts</t>
-  </si>
-  <si>
-    <t>w:rFonts ascii/hAnsi/eastAsia/cs, w:lang, rtl/bidi.</t>
-  </si>
-  <si>
-    <t>FONT-005</t>
-  </si>
-  <si>
-    <t>Editor fallback stacks</t>
-  </si>
-  <si>
-    <t>CSS stacks from the resolver.</t>
-  </si>
-  <si>
-    <t>FONT-006</t>
-  </si>
-  <si>
-    <t>Multilingual tests</t>
-  </si>
-  <si>
-    <t>Script matrix x editor/DOCX/PDF with pdftotext and rendering.</t>
-  </si>
-  <si>
-    <t>FMT-001</t>
-  </si>
-  <si>
-    <t>Style extraction completeness</t>
-  </si>
-  <si>
-    <t>Page setup, margins, fonts, headings, lists, tables, captions, headers/footers, spacing, numbering, colours.</t>
-  </si>
-  <si>
-    <t>FMT-002</t>
-  </si>
-  <si>
-    <t>Semantic mapping validated</t>
-  </si>
-  <si>
-    <t>AI classifies/maps, engine applies; validation.</t>
-  </si>
-  <si>
-    <t>FMT-003</t>
-  </si>
-  <si>
-    <t>Before/after for Format by Example</t>
-  </si>
-  <si>
-    <t>Preview before saving a template.</t>
-  </si>
-  <si>
-    <t>FMT-005</t>
-  </si>
-  <si>
-    <t>Rule value validation</t>
-  </si>
-  <si>
-    <t>Instruction-path values validated before reaching CSS/export.</t>
-  </si>
-  <si>
-    <t>Instruction rules and set_style operations go through values.clean_rule_value: invalid ones dropped, normalised values stored (see SEC-022).</t>
-  </si>
-  <si>
-    <t>tests/test_rule_values.py::test_instructions_cannot_carry_such_values</t>
-  </si>
-  <si>
-    <t>HLTH-001</t>
-  </si>
-  <si>
-    <t>Health 2.0 checks</t>
-  </si>
-  <si>
-    <t>Alt text, hidden text, mixed language, unsupported features, section inconsistency, broken lists, empty paragraphs, layout anomalies, duplicated formatting, broken links.</t>
-  </si>
-  <si>
-    <t>HLTH-002</t>
-  </si>
-  <si>
-    <t>Deterministic fixes with preview</t>
-  </si>
-  <si>
-    <t>Fix proposals through the change model.</t>
-  </si>
-  <si>
-    <t>HLTH-003</t>
-  </si>
-  <si>
-    <t>AI explanations only</t>
-  </si>
-  <si>
-    <t>AI explains issues; never scores.</t>
-  </si>
-  <si>
-    <t>REV-002</t>
-  </si>
-  <si>
-    <t>Review Changes UI</t>
-  </si>
-  <si>
-    <t>Categories FORMAT/STRUCTURE/CONTENT/METADATA/PRESERVATION/TRANSLATION.</t>
-  </si>
-  <si>
-    <t>REV-003</t>
-  </si>
-  <si>
-    <t>Content changes need acceptance</t>
-  </si>
-  <si>
-    <t>Enforced server-side.</t>
-  </si>
-  <si>
-    <t>backend</t>
-  </si>
-  <si>
-    <t>REV-004</t>
-  </si>
-  <si>
-    <t>Repair</t>
-  </si>
-  <si>
-    <t>Detected issue, proposed fix, preview, apply.</t>
-  </si>
-  <si>
-    <t>REV-005</t>
-  </si>
-  <si>
-    <t>Clean copy</t>
-  </si>
-  <si>
-    <t>Explicit: remove comments, accept tracked changes, remove hidden text, remove metadata, normalise formatting.</t>
-  </si>
-  <si>
-    <t>FEAT-001</t>
-  </si>
-  <si>
-    <t>Batch formatting</t>
-  </si>
-  <si>
-    <t>One template/reference over many documents as jobs.</t>
-  </si>
-  <si>
-    <t>backend/jobs</t>
-  </si>
-  <si>
-    <t>FEAT-002</t>
-  </si>
-  <si>
-    <t>Batch export</t>
-  </si>
-  <si>
-    <t>Many documents to a zip.</t>
-  </si>
-  <si>
-    <t>FEAT-003</t>
-  </si>
-  <si>
-    <t>Batch translation</t>
-  </si>
-  <si>
-    <t>After the translation MVP.</t>
-  </si>
-  <si>
-    <t>FEAT-010</t>
-  </si>
-  <si>
-    <t>Accessibility checker</t>
-  </si>
-  <si>
-    <t>Heading hierarchy, alt text, link labels, table headers, reading order, language, contrast.</t>
-  </si>
-  <si>
-    <t>FEAT-011</t>
-  </si>
-  <si>
-    <t>App accessibility fixes</t>
-  </si>
-  <si>
-    <t>Zero serious axe violations on main pages and the editor.</t>
-  </si>
-  <si>
-    <t>JOB-001</t>
-  </si>
-  <si>
-    <t>Job safety</t>
-  </si>
-  <si>
-    <t>idempotency_key, retry_count, timeout, cancellation, stuck detection, backoff, dead-letter.</t>
-  </si>
-  <si>
-    <t>STOR-001</t>
-  </si>
-  <si>
-    <t>Storage retention and deletion</t>
-  </si>
-  <si>
-    <t>Source files, exports, OCR artifacts: retention, deletion, access control, content types, size limits.</t>
-  </si>
-  <si>
-    <t>OBS-001</t>
-  </si>
-  <si>
-    <t>Metrics</t>
-  </si>
-  <si>
-    <t>Latency, failure rate, job/AI/export metrics without content.</t>
-  </si>
-  <si>
-    <t>AUD-15</t>
-  </si>
-  <si>
-    <t>OBS-002</t>
-  </si>
-  <si>
-    <t>Operation and job IDs in logs</t>
-  </si>
-  <si>
-    <t>Request, operation and job IDs everywhere.</t>
-  </si>
-  <si>
-    <t>OBS-003</t>
-  </si>
-  <si>
-    <t>Operations data</t>
-  </si>
-  <si>
-    <t>Failed jobs, processing failures, usage spikes, AI/export failures, storage, abuse - minimal admin API.</t>
-  </si>
-  <si>
-    <t>INFRA-010</t>
-  </si>
-  <si>
-    <t>Deployment verified</t>
-  </si>
-  <si>
-    <t>Docker images build and start; Postgres, Redis, storage, worker, frontend, backend.</t>
-  </si>
-  <si>
-    <t>docker, CI</t>
-  </si>
-  <si>
-    <t>INFRA-011</t>
-  </si>
-  <si>
-    <t>CI gates</t>
-  </si>
-  <si>
-    <t>Backend, frontend, E2E, lint, typecheck, build, migrations, security audit, document fidelity tests.</t>
-  </si>
-  <si>
-    <t>.github/workflows</t>
-  </si>
-  <si>
-    <t>AUD-15,AUD-20</t>
-  </si>
-  <si>
-    <t>TEST-040</t>
-  </si>
-  <si>
-    <t>Playwright workflow coverage</t>
-  </si>
-  <si>
-    <t>The 24 workflows of the brief.</t>
-  </si>
-  <si>
-    <t>TEST-041</t>
-  </si>
-  <si>
-    <t>Performance gates</t>
-  </si>
-  <si>
-    <t>Regression thresholds relative to baseline.</t>
-  </si>
-  <si>
-    <t>TEST-043</t>
-  </si>
-  <si>
-    <t>Browser matrix</t>
-  </si>
-  <si>
-    <t>Chromium, Firefox, WebKit.</t>
-  </si>
-  <si>
-    <t>TEST-006</t>
-  </si>
-  <si>
-    <t>E2E backend removes its temp directory</t>
-  </si>
-  <si>
-    <t>scripts/e2e_server.py leaves %TEMP%/smartdoc-e2e-* behind after every Playwright run (10 found on 2026-09-27).</t>
-  </si>
-  <si>
-    <t>backend/scripts/e2e_server.py</t>
-  </si>
-  <si>
-    <t>DOCS-010</t>
-  </si>
-  <si>
-    <t>final-production-readiness.md</t>
-  </si>
-  <si>
-    <t>The 16-section final report.</t>
-  </si>
-  <si>
-    <t>DOCS-011</t>
-  </si>
-  <si>
-    <t>Documentation tree</t>
-  </si>
-  <si>
-    <t>docs/{architecture,document-model,docx,pdf,translation,ai,formatting,security,testing,deployment,billing,operations}.</t>
-  </si>
-  <si>
-    <t>Started with Phase 1: docs/document-model, docs/architecture/fidelity.md, docs/docx, docs/formatting, docs/security, docs/testing (each grounded in the code and tests of Phases 0-1). Remaining folders (pdf, translation, ai, deployment, billing, operations) as their phases land.; docs/ai/README.md added with Phase 2.</t>
-  </si>
-  <si>
-    <t>CRITICAL_FIXES — Audit findings and P0 tasks</t>
-  </si>
-  <si>
-    <t>The 20 findings of the 2026-09-26 audit (current known risks) with fix progress, then every P0 task. Report: https://claude.ai/artifact/WKskiyexTDLAHe1BfjvWR1 — a finding is RESOLVED when every linked fix task is DONE.</t>
-  </si>
-  <si>
-    <t>Findings</t>
-  </si>
-  <si>
-    <t>Resolved</t>
-  </si>
-  <si>
-    <t>Open</t>
-  </si>
-  <si>
-    <t>P0 tasks</t>
-  </si>
-  <si>
-    <t>P0 done</t>
-  </si>
-  <si>
-    <t>Audit findings (current known risks)</t>
-  </si>
-  <si>
-    <t>Finding ID</t>
-  </si>
-  <si>
-    <t>Progress</t>
-  </si>
-  <si>
-    <t>Finding</t>
-  </si>
-  <si>
-    <t>Fix Tasks</t>
-  </si>
-  <si>
-    <t>Active</t>
-  </si>
-  <si>
-    <t>Blocked/Failed</t>
-  </si>
-  <si>
-    <t>Editor save can discard nested blocks (lists, pictures, code, quotes inside cells/items)</t>
-  </si>
-  <si>
-    <t>EDIT-001,EDIT-002,EDIT-003,EDIT-005,EDIT-006</t>
-  </si>
-  <si>
-    <t>AI fidelity check misses omissions, negation removal, number changes, inserted text</t>
-  </si>
-  <si>
-    <t>AI-001,AI-002,AI-003,AI-004</t>
-  </si>
-  <si>
-    <t>Fixed in Phase 2 (AI-001..004): AI structure answers are checked token by token; any omission, negation removal, number/unit/date change, insertion, reordering, duplication or punctuation change is refused.</t>
-  </si>
-  <si>
-    <t>Import/export silently changes hidden text, numbering, section headers, metadata, alt text, structure</t>
-  </si>
-  <si>
-    <t>FID-002,DOCX-011,DOCX-013,DOCX-015,DOCX-025</t>
-  </si>
-  <si>
-    <t>List numbering changes ('Чл. 1.' -&gt; '1.', '(a)' -&gt; 'a.', start values)</t>
-  </si>
-  <si>
-    <t>Partly fixed in 622d9c1: list format/start/continuation kept; custom labels ('Чл. 1.', '(a)') and multi-level labels reported, not kept yet (DOCX-016).</t>
-  </si>
-  <si>
-    <t>AI instruction operations can delete/insert/move content without preview</t>
-  </si>
-  <si>
-    <t>AI-005,AI-006,AI-007,REV-003</t>
-  </si>
-  <si>
-    <t>Fixed in Phase 2 (AI-005..AI-007): an instruction's insert/delete/move is a proposal the user sees and accepts or rejects; nothing is deleted silently.</t>
-  </si>
-  <si>
-    <t>Content controls, metadata, comment threads, sensitivity information lost</t>
-  </si>
-  <si>
-    <t>DOCX-012,DOCX-021,DOCX-023</t>
-  </si>
-  <si>
-    <t>Image fidelity gaps: alt text, crop, rotation, formats</t>
-  </si>
-  <si>
-    <t>Table export changes header state, borders, alignment, widths, geometry</t>
-  </si>
-  <si>
-    <t>Large images cause huge memory consumption</t>
-  </si>
-  <si>
-    <t>SEC-012,SEC-013</t>
-  </si>
-  <si>
-    <t>Large tables have a performance problem</t>
-  </si>
-  <si>
-    <t>Plan limits have a concurrency race</t>
-  </si>
-  <si>
-    <t>Malformed DOCX leads to HTTP 500</t>
-  </si>
-  <si>
-    <t>SEC-010,SEC-019</t>
-  </si>
-  <si>
-    <t>Dangerous href/field instructions must be filtered</t>
-  </si>
-  <si>
-    <t>SEC-014,SEC-015,SEC-016</t>
-  </si>
-  <si>
-    <t>Account essentials missing: reset, verification, change, deletion</t>
-  </si>
-  <si>
-    <t>ACCT-002,ACCT-003,ACCT-004,ACCT-005</t>
-  </si>
-  <si>
-    <t>Operations/monitoring must be confirmed</t>
-  </si>
-  <si>
-    <t>OBS-001,OBS-002,INFRA-010</t>
-  </si>
-  <si>
-    <t>Whole-document autosave must be optimised</t>
-  </si>
-  <si>
-    <t>PERF-003,PERF-004</t>
-  </si>
-  <si>
-    <t>PDF multilingual rendering must be reliable</t>
-  </si>
-  <si>
-    <t>FONT-003,FONT-006</t>
-  </si>
-  <si>
-    <t>Export metadata must be correct</t>
-  </si>
-  <si>
-    <t>DOCX-012,DOCX-020</t>
-  </si>
-  <si>
-    <t>Partly fixed in 622d9c1: Word exports carry the source file's core properties (author, dates, subject...) instead of 'python-docx'/2013; fields remain (DOCX-020).</t>
-  </si>
-  <si>
-    <t>AUD-19</t>
-  </si>
-  <si>
-    <t>Canonical model must represent more than paragraphs + runs + simple tables</t>
-  </si>
-  <si>
-    <t>CORE-001,DOCX-015,DOCX-016,DOCX-017</t>
-  </si>
-  <si>
-    <t>Tests can miss import-side data loss (model-relative comparison)</t>
-  </si>
-  <si>
-    <t>TEST-020,TEST-021,TEST-022</t>
-  </si>
-  <si>
-    <t>P0 tasks (live from MASTER)</t>
-  </si>
-  <si>
-    <t>DOCUMENT_FIDELITY — Content preservation</t>
-  </si>
-  <si>
-    <t>Canonical model, fidelity reports, capability matrix, change/review model. Categories: CORE, FIDELITY, REVIEW. Rows are formulas over MASTER — change task data in MASTER or with tools/tracker/tracker.py.</t>
-  </si>
-  <si>
-    <t>Tasks (live from MASTER)</t>
-  </si>
-  <si>
-    <t>DOCX_OOXML — DOCX / OOXML preservation</t>
-  </si>
-  <si>
-    <t>Import and export fidelity for Word documents. Categories: DOCX. Rows are formulas over MASTER — change task data in MASTER or with tools/tracker/tracker.py.</t>
-  </si>
-  <si>
-    <t>PDF — PDF engine</t>
-  </si>
-  <si>
-    <t>PDF export and PDF parsing. Categories: PDF. Rows are formulas over MASTER — change task data in MASTER or with tools/tracker/tracker.py.</t>
-  </si>
-  <si>
-    <t>EDITOR — Editor integrity</t>
-  </si>
-  <si>
-    <t>Tiptap mapping and save integrity. Categories: EDITOR. Rows are formulas over MASTER — change task data in MASTER or with tools/tracker/tracker.py.</t>
-  </si>
-  <si>
-    <t>FORMATTING — Formatting and Document Health</t>
-  </si>
-  <si>
-    <t>Formatting engine, Format by Example, Document Health. Categories: FORMATTING, HEALTH. Rows are formulas over MASTER — change task data in MASTER or with tools/tracker/tracker.py.</t>
-  </si>
-  <si>
-    <t>AI — AI fidelity</t>
-  </si>
-  <si>
-    <t>Fidelity checks, proposals and review, budgets. Categories: AI. Rows are formulas over MASTER — change task data in MASTER or with tools/tracker/tracker.py.</t>
-  </si>
-  <si>
-    <t>SECURITY — Security and accounts</t>
-  </si>
-  <si>
-    <t>Security hardening and account essentials. Categories: SECURITY, ACCOUNT. Rows are formulas over MASTER — change task data in MASTER or with tools/tracker/tracker.py.</t>
-  </si>
-  <si>
-    <t>PERFORMANCE — Performance</t>
-  </si>
-  <si>
-    <t>Measured results — brief §80-81: measure, then set regression thresholds relative to the baseline (no invented SLOs)</t>
-  </si>
-  <si>
-    <t>Bench ID</t>
-  </si>
-  <si>
-    <t>Metric</t>
-  </si>
-  <si>
-    <t>Unit</t>
-  </si>
-  <si>
-    <t>Scenario</t>
-  </si>
-  <si>
-    <t>Baseline</t>
-  </si>
-  <si>
-    <t>Baseline Source</t>
-  </si>
-  <si>
-    <t>Current</t>
-  </si>
-  <si>
-    <t>Measured On</t>
-  </si>
-  <si>
-    <t>Threshold</t>
-  </si>
-  <si>
-    <t>BENCH-001</t>
-  </si>
-  <si>
-    <t>duration</t>
-  </si>
-  <si>
-    <t>s</t>
-  </si>
-  <si>
-    <t>DOCX export: table 500x8 (4,000 cells)</t>
-  </si>
-  <si>
-    <t>audit perf_table.py (400 cells 3.8 s; 1,600 cells 53.7 s; quadratic)</t>
-  </si>
-  <si>
-    <t>BENCH-002</t>
-  </si>
-  <si>
-    <t>PDF export: table 500x8</t>
-  </si>
-  <si>
-    <t>audit perf_table.py (linear)</t>
-  </si>
-  <si>
-    <t>BENCH-003</t>
-  </si>
-  <si>
-    <t>Import: 300-page text DOCX (1,650 elements)</t>
-  </si>
-  <si>
-    <t>audit perf_backend.py</t>
-  </si>
-  <si>
-    <t>BENCH-004</t>
-  </si>
-  <si>
-    <t>DOCX export: 300-page text document</t>
-  </si>
-  <si>
-    <t>BENCH-005</t>
-  </si>
-  <si>
-    <t>PDF export: 300-page text document</t>
-  </si>
-  <si>
-    <t>BENCH-006</t>
-  </si>
-  <si>
-    <t>memory growth</t>
-  </si>
-  <si>
-    <t>MB</t>
-  </si>
-  <si>
-    <t>PDF export: 39 KB DOCX holding a 12000x12000 PNG</t>
-  </si>
-  <si>
-    <t>audit pixel_bomb.py (14000x14000 crashes the export)</t>
-  </si>
-  <si>
-    <t>BENCH-007</t>
-  </si>
-  <si>
-    <t>PDF export: 4 JPEG images 2400x1800</t>
-  </si>
-  <si>
-    <t>audit perf_backend.py (6.3 s)</t>
-  </si>
-  <si>
-    <t>BENCH-008</t>
-  </si>
-  <si>
-    <t>Editor: type 20 characters at 12,196 elements (1M-character paste)</t>
-  </si>
-  <si>
-    <t>audit perf_browser.js (~470 ms per key)</t>
-  </si>
-  <si>
-    <t>BENCH-009</t>
-  </si>
-  <si>
-    <t>Editor: type 20 characters, 300-page document</t>
-  </si>
-  <si>
-    <t>audit perf_browser.js</t>
-  </si>
-  <si>
-    <t>BENCH-010</t>
-  </si>
-  <si>
-    <t>request size</t>
-  </si>
-  <si>
-    <t>Autosave request: 300-page document</t>
-  </si>
-  <si>
-    <t>audit perf_browser.js (whole elements list per save)</t>
-  </si>
-  <si>
-    <t>BENCH-011</t>
-  </si>
-  <si>
-    <t>Autosave request: 1M-character paste</t>
-  </si>
-  <si>
-    <t>BENCH-012</t>
-  </si>
-  <si>
-    <t>storage</t>
-  </si>
-  <si>
-    <t>Stored history: one 300-page document, 50 steps</t>
-  </si>
-  <si>
-    <t>audit (2.8 MB per full copy; 7.2 MB when the JSON is ASCII-escaped)</t>
-  </si>
-  <si>
-    <t>BENCH-013</t>
-  </si>
-  <si>
-    <t>Paste: 2M characters (the cap)</t>
-  </si>
-  <si>
-    <t>audit perf_backend.py (17.5k elements, 7.1 MB JSON)</t>
-  </si>
-  <si>
-    <t>Performance tasks (live from MASTER)</t>
-  </si>
-  <si>
-    <t>TESTING — Testing</t>
-  </si>
-  <si>
-    <t>Test runs (oldest first)</t>
-  </si>
-  <si>
-    <t>Run ID</t>
-  </si>
-  <si>
-    <t>Command</t>
-  </si>
-  <si>
-    <t>Passed</t>
-  </si>
-  <si>
-    <t>Skipped</t>
-  </si>
-  <si>
-    <t>Date</t>
-  </si>
-  <si>
-    <t>Duration (s)</t>
-  </si>
-  <si>
-    <t>RUN-0001</t>
-  </si>
-  <si>
-    <t>backend-pytest</t>
-  </si>
-  <si>
-    <t>PASS</t>
-  </si>
-  <si>
-    <t>cd backend &amp;&amp; venv/Scripts/python -m pytest -q -p no:cacheprovider</t>
-  </si>
-  <si>
-    <t>Skip: optional real-Word check (SMARTDOC_REAL_DOCX unset). 1 DeprecationWarning (starlette/anyio). Audit measured 93% line coverage on 2026-09-26.</t>
-  </si>
-  <si>
-    <t>ea69829</t>
-  </si>
-  <si>
-    <t>RUN-0002</t>
-  </si>
-  <si>
-    <t>frontend-lint</t>
-  </si>
-  <si>
-    <t>cd frontend &amp;&amp; npm run lint</t>
-  </si>
-  <si>
-    <t>eslint: 0 problems</t>
-  </si>
-  <si>
-    <t>RUN-0003</t>
-  </si>
-  <si>
-    <t>frontend-tsc</t>
-  </si>
-  <si>
-    <t>cd frontend &amp;&amp; npx tsc --noEmit</t>
-  </si>
-  <si>
-    <t>0 type errors</t>
-  </si>
-  <si>
-    <t>RUN-0004</t>
-  </si>
-  <si>
-    <t>frontend-vitest</t>
-  </si>
-  <si>
-    <t>cd frontend &amp;&amp; npm test</t>
-  </si>
-  <si>
-    <t>6 test files</t>
-  </si>
-  <si>
-    <t>RUN-0005</t>
-  </si>
-  <si>
-    <t>frontend-build</t>
-  </si>
-  <si>
-    <t>cd frontend &amp;&amp; npm run build</t>
-  </si>
-  <si>
-    <t>Next.js production build, 11 routes</t>
-  </si>
-  <si>
-    <t>RUN-0006</t>
-  </si>
-  <si>
-    <t>e2e-playwright</t>
-  </si>
-  <si>
-    <t>cd frontend &amp;&amp; npm run test:e2e</t>
-  </si>
-  <si>
-    <t>Edge; throwaway backend on SQLite (:8100) + production build (:3100). 16 workflows in 5 spec files; the brief asks for 24 (TEST-040). Leaves %TEMP%/smartdoc-e2e-* dirs behind (TEST-006).</t>
-  </si>
-  <si>
-    <t>RUN-0007</t>
-  </si>
-  <si>
-    <t>migrations</t>
-  </si>
-  <si>
-    <t>alembic upgrade head &amp;&amp; alembic check &amp;&amp; alembic downgrade base &amp;&amp; alembic upgrade head (scratch SQLite); alembic upgrade head --sql (PostgreSQL dialect)</t>
-  </si>
-  <si>
-    <t>head 85211092fe4c; 'No new upgrade operations detected'; offline SQL: 14 tables at head, RLS enabled on every table</t>
-  </si>
-  <si>
-    <t>RUN-0008</t>
-  </si>
-  <si>
-    <t>supabase</t>
-  </si>
-  <si>
-    <t>Supabase MCP: list_migrations, get_advisors security+performance, list_tables (project edmmjmsynjziahwtjuke)</t>
-  </si>
-  <si>
-    <t>8/8 migrations applied; 14 tables, RLS on all; advisors only INFO: 14x rls_enabled_no_policy (by design: the API connects as owner, PostgREST roles see nothing), 8x unused_index (low traffic)</t>
-  </si>
-  <si>
-    <t>RUN-0009</t>
-  </si>
-  <si>
-    <t>pip-audit</t>
-  </si>
-  <si>
-    <t>uvx pip-audit --disable-pip -r backend/requirements.lock; same for requirements-dev.lock</t>
-  </si>
-  <si>
-    <t>No known vulnerabilities in either lock file</t>
-  </si>
-  <si>
-    <t>RUN-0010</t>
-  </si>
-  <si>
-    <t>npm-audit</t>
-  </si>
-  <si>
-    <t>cd frontend &amp;&amp; npm audit; npm audit --omit=dev</t>
-  </si>
-  <si>
-    <t>0 vulnerabilities across 633 dependencies</t>
-  </si>
-  <si>
-    <t>RUN-0011</t>
-  </si>
-  <si>
-    <t>docker-compose</t>
-  </si>
-  <si>
-    <t>PARTIAL</t>
-  </si>
-  <si>
-    <t>docker compose config --quiet</t>
-  </si>
-  <si>
-    <t>compose file valid (8 services: postgres, redis, minio, minio-bucket, migrate, worker, backend, frontend); images NOT built: Docker daemon not running on this machine (CI builds them on main)</t>
-  </si>
-  <si>
-    <t>RUN-0012</t>
-  </si>
-  <si>
-    <t>Phase 1 editor integrity: +16 tests (nesting model, nested API/exports, health links)</t>
-  </si>
-  <si>
-    <t>RUN-0013</t>
-  </si>
-  <si>
-    <t>cd frontend &amp;&amp; npx vitest run</t>
-  </si>
-  <si>
-    <t>+31: nestedBlocks.test.ts (28), useAutoSave.test.tsx (3); tsc and eslint clean</t>
-  </si>
-  <si>
-    <t>RUN-0014</t>
-  </si>
-  <si>
-    <t>cd frontend &amp;&amp; npx playwright test</t>
-  </si>
-  <si>
-    <t>+1: e2e/nested.spec.ts (paste, autosave, reload)</t>
-  </si>
-  <si>
-    <t>RUN-0015</t>
-  </si>
-  <si>
-    <t>+29 test_fidelity_report.py</t>
-  </si>
-  <si>
-    <t>RUN-0016</t>
-  </si>
-  <si>
-    <t>+3 FidelityPanel.test.tsx</t>
-  </si>
-  <si>
-    <t>RUN-0017</t>
-  </si>
-  <si>
-    <t>+fidelity.spec.ts; nested.spec.ts made deterministic (focus check, Ctrl+End) after one run pasted at the document start</t>
-  </si>
-  <si>
-    <t>RUN-0018</t>
-  </si>
-  <si>
-    <t>+6 test_export_fidelity.py</t>
-  </si>
-  <si>
-    <t>RUN-0019</t>
-  </si>
-  <si>
-    <t>+4 ExportResult.test.tsx</t>
-  </si>
-  <si>
-    <t>RUN-0020</t>
-  </si>
-  <si>
-    <t>export test checks the export's content message</t>
-  </si>
-  <si>
-    <t>RUN-0021</t>
-  </si>
-  <si>
-    <t>+6 test_capabilities.py</t>
-  </si>
-  <si>
-    <t>RUN-0022</t>
-  </si>
-  <si>
-    <t>venv/Scripts/python -m pytest -q</t>
-  </si>
-  <si>
-    <t>after FID-002 detections + section break fix</t>
-  </si>
-  <si>
-    <t>RUN-0023</t>
-  </si>
-  <si>
-    <t>npx vitest run</t>
-  </si>
-  <si>
-    <t>tsc --noEmit and eslint clean too</t>
-  </si>
-  <si>
-    <t>RUN-0024</t>
-  </si>
-  <si>
-    <t>rule values (SEC-022) + editor direct styles</t>
-  </si>
-  <si>
-    <t>RUN-0025</t>
-  </si>
-  <si>
-    <t>tsc + eslint clean</t>
-  </si>
-  <si>
-    <t>RUN-0026</t>
-  </si>
-  <si>
-    <t>e2e</t>
-  </si>
-  <si>
-    <t>npx playwright test</t>
-  </si>
-  <si>
-    <t>incl. e2e/direct-formatting.spec.ts</t>
-  </si>
-  <si>
-    <t>RUN-0027</t>
-  </si>
-  <si>
-    <t>Phase 1 gate: link titles, mark order, Markdown pictures/rules</t>
-  </si>
-  <si>
-    <t>RUN-0028</t>
-  </si>
-  <si>
-    <t>Phase 1 gate; tsc + eslint clean</t>
-  </si>
-  <si>
-    <t>RUN-0029</t>
-  </si>
-  <si>
-    <t>Phase 1 gate</t>
-  </si>
-  <si>
-    <t>RUN-0030</t>
-  </si>
-  <si>
-    <t>AI fidelity check (AI-001..004)</t>
-  </si>
-  <si>
-    <t>RUN-0031</t>
-  </si>
-  <si>
-    <t>AI proposals</t>
-  </si>
-  <si>
-    <t>RUN-0032</t>
-  </si>
-  <si>
-    <t>RUN-0033</t>
-  </si>
-  <si>
-    <t>incl. e2e/proposals.spec.ts</t>
-  </si>
-  <si>
-    <t>RUN-0034</t>
-  </si>
-  <si>
-    <t>AI budget</t>
-  </si>
-  <si>
-    <t>RUN-0035</t>
-  </si>
-  <si>
-    <t>prompt-injection review</t>
-  </si>
-  <si>
-    <t>RUN-0036</t>
-  </si>
-  <si>
-    <t>Phase 2 gate</t>
-  </si>
-  <si>
-    <t>RUN-0037</t>
-  </si>
-  <si>
-    <t>RUN-0038</t>
-  </si>
-  <si>
-    <t>source package + patch writer</t>
-  </si>
-  <si>
-    <t>RUN-0039</t>
-  </si>
-  <si>
-    <t>after the patch writer</t>
-  </si>
-  <si>
-    <t>RUN-0040</t>
-  </si>
-  <si>
-    <t>backend pytest</t>
-  </si>
-  <si>
-    <t>DOCX-028: test_original_blocks.py (26), golden set of 13</t>
-  </si>
-  <si>
-    <t>7f22bf9</t>
-  </si>
-  <si>
-    <t>RUN-0041</t>
-  </si>
-  <si>
-    <t>frontend vitest</t>
-  </si>
-  <si>
-    <t>editor round trip includes 13-kept-blocks</t>
-  </si>
-  <si>
-    <t>RUN-0042</t>
-  </si>
-  <si>
-    <t>playwright</t>
-  </si>
-  <si>
-    <t>new e2e/kept-blocks.spec.ts</t>
-  </si>
-  <si>
-    <t>RUN-0043</t>
-  </si>
-  <si>
-    <t>tsc + eslint</t>
-  </si>
-  <si>
-    <t>cd frontend &amp;&amp; npx tsc --noEmit &amp;&amp; npx eslint .</t>
-  </si>
-  <si>
-    <t>0 type errors, 0 lint problems</t>
-  </si>
-  <si>
-    <t>RUN-0044</t>
-  </si>
-  <si>
-    <t>DOCX-025: tests/test_hidden_text.py (7)</t>
-  </si>
-  <si>
-    <t>fada4d7</t>
-  </si>
-  <si>
-    <t>RUN-0045</t>
-  </si>
-  <si>
-    <t>editor/hiddenText.test.tsx (6)</t>
-  </si>
-  <si>
-    <t>RUN-0046</t>
-  </si>
-  <si>
-    <t>new e2e/hidden-text.spec.ts</t>
-  </si>
-  <si>
-    <t>RUN-0047</t>
-  </si>
-  <si>
-    <t>RUN-0048</t>
-  </si>
-  <si>
-    <t>DOCX-013 part 1: tests/test_character_formatting.py (12)</t>
-  </si>
-  <si>
-    <t>c51b1bf</t>
-  </si>
-  <si>
-    <t>RUN-0049</t>
-  </si>
-  <si>
-    <t>editor/characterFormatting.test.ts (3)</t>
-  </si>
-  <si>
-    <t>RUN-0050</t>
-  </si>
-  <si>
-    <t>after DOCX-013 part 1</t>
-  </si>
-  <si>
-    <t>RUN-0051</t>
-  </si>
-  <si>
-    <t>RUN-0052</t>
-  </si>
-  <si>
-    <t>DOCX-013 part 2 + FID-007: tests/test_copy_reports.py (6)</t>
-  </si>
-  <si>
-    <t>309f9d6</t>
-  </si>
-  <si>
-    <t>RUN-0053</t>
-  </si>
-  <si>
-    <t>characterFormatting.test.ts (4)</t>
-  </si>
-  <si>
-    <t>RUN-0054</t>
-  </si>
-  <si>
-    <t>after DOCX-013 part 2</t>
-  </si>
-  <si>
-    <t>RUN-0055</t>
-  </si>
-  <si>
-    <t>RUN-0056</t>
-  </si>
-  <si>
-    <t>DOCX-014 part 1: tests/test_paragraph_formatting.py (9)</t>
-  </si>
-  <si>
-    <t>597275a</t>
-  </si>
-  <si>
-    <t>RUN-0057</t>
-  </si>
-  <si>
-    <t>after DOCX-014 part 1</t>
-  </si>
-  <si>
-    <t>RUN-0058</t>
-  </si>
-  <si>
-    <t>RUN-0059</t>
-  </si>
-  <si>
-    <t>RUN-0060</t>
-  </si>
-  <si>
-    <t>DOCX-014 part 2: tests/test_paragraph_formatting.py (19)</t>
-  </si>
-  <si>
-    <t>9f1c5b4</t>
-  </si>
-  <si>
-    <t>RUN-0061</t>
-  </si>
-  <si>
-    <t>after DOCX-014 part 2</t>
-  </si>
-  <si>
-    <t>RUN-0062</t>
-  </si>
-  <si>
-    <t>RUN-0063</t>
-  </si>
-  <si>
-    <t>Testing tasks (live from MASTER)</t>
-  </si>
-  <si>
-    <t>PRODUCT_FEATURES — Product features</t>
-  </si>
-  <si>
-    <t>Feature backlog — brief §61-62</t>
-  </si>
-  <si>
-    <t>Feature</t>
-  </si>
-  <si>
-    <t>Bucket</t>
-  </si>
-  <si>
-    <t>Linked Tasks</t>
-  </si>
-  <si>
-    <t>Linked Done</t>
-  </si>
-  <si>
-    <t>Linked Total</t>
-  </si>
-  <si>
-    <t>Document integrity</t>
-  </si>
-  <si>
-    <t>NOW</t>
-  </si>
-  <si>
-    <t>EDIT-001,EDIT-005,FID-002</t>
-  </si>
-  <si>
-    <t>Brief 62: NOW #1</t>
-  </si>
-  <si>
-    <t>Fidelity</t>
-  </si>
-  <si>
-    <t>DOCX-011,TEST-022</t>
-  </si>
-  <si>
-    <t>Brief 62: NOW #2</t>
-  </si>
-  <si>
-    <t>Security</t>
-  </si>
-  <si>
-    <t>SEC-010,SEC-012,SEC-014</t>
-  </si>
-  <si>
-    <t>Brief 62: NOW #3</t>
-  </si>
-  <si>
-    <t>Performance</t>
-  </si>
-  <si>
-    <t>PERF-001,PERF-003,PERF-004</t>
-  </si>
-  <si>
-    <t>Brief 62: NOW #4</t>
-  </si>
-  <si>
-    <t>PDF -&gt; editable</t>
-  </si>
-  <si>
-    <t>P2E-002,P2E-005</t>
-  </si>
-  <si>
-    <t>Brief 62: NOW #5</t>
-  </si>
-  <si>
-    <t>TRAN-001,TRAN-006</t>
-  </si>
-  <si>
-    <t>Brief 62: NOW #6</t>
-  </si>
-  <si>
-    <t>FONT-002,FONT-003</t>
-  </si>
-  <si>
-    <t>Brief 62: NOW #7</t>
-  </si>
-  <si>
-    <t>Review Changes</t>
-  </si>
-  <si>
-    <t>REV-001,REV-002</t>
-  </si>
-  <si>
-    <t>Brief 62: NOW #8</t>
-  </si>
-  <si>
-    <t>HLTH-001,HLTH-002</t>
-  </si>
-  <si>
-    <t>Brief 62: NOW #9</t>
-  </si>
-  <si>
-    <t>FMT-001,FMT-002,FMT-003</t>
-  </si>
-  <si>
-    <t>Brief 62: NOW #10</t>
-  </si>
-  <si>
-    <t>OCR</t>
-  </si>
-  <si>
-    <t>Part of PDF -&gt; editable (brief 43)</t>
-  </si>
-  <si>
-    <t>Multilingual support</t>
-  </si>
-  <si>
-    <t>TRAN-007,FONT-003</t>
-  </si>
-  <si>
-    <t>Part of translation + FontResolver</t>
-  </si>
-  <si>
-    <t>RTL</t>
-  </si>
-  <si>
-    <t>FONT-003,FONT-004</t>
-  </si>
-  <si>
-    <t>Part of FontResolver</t>
-  </si>
-  <si>
-    <t>CJK</t>
-  </si>
-  <si>
-    <t>Glossary</t>
-  </si>
-  <si>
-    <t>Part of translation MVP (brief 49)</t>
-  </si>
-  <si>
-    <t>Terminology lock</t>
-  </si>
-  <si>
-    <t>Citation preservation</t>
-  </si>
-  <si>
-    <t>Preservation is fidelity work; a citation editor is LATER</t>
-  </si>
-  <si>
-    <t>Bibliography preservation</t>
-  </si>
-  <si>
-    <t>Preservation is fidelity work</t>
-  </si>
-  <si>
-    <t>Content controls</t>
-  </si>
-  <si>
-    <t>Preserve now; editing content controls NEXT</t>
-  </si>
-  <si>
-    <t>Custom fields</t>
-  </si>
-  <si>
-    <t>Preserve custom properties and fields now; an editor NEXT</t>
-  </si>
-  <si>
-    <t>Document compare</t>
-  </si>
-  <si>
-    <t>NEXT</t>
-  </si>
-  <si>
-    <t>Brief 62: NEXT</t>
-  </si>
-  <si>
-    <t>Version compare</t>
-  </si>
-  <si>
-    <t>Brief 62: NEXT (batch processing)</t>
-  </si>
-  <si>
-    <t>After the translation MVP</t>
-  </si>
-  <si>
-    <t>Table repair</t>
-  </si>
-  <si>
-    <t>List repair</t>
-  </si>
-  <si>
-    <t>Brief 62: NEXT (accessibility)</t>
-  </si>
-  <si>
-    <t>Heading hierarchy checker</t>
-  </si>
-  <si>
-    <t>Link checker</t>
-  </si>
-  <si>
-    <t>Alt-text checker</t>
-  </si>
-  <si>
-    <t>HLTH-001,FEAT-010</t>
-  </si>
-  <si>
-    <t>Metadata editor</t>
-  </si>
-  <si>
-    <t>Global style replacement</t>
-  </si>
-  <si>
-    <t>Find/replace with formatting</t>
-  </si>
-  <si>
-    <t>Tracked change cleanup</t>
-  </si>
-  <si>
-    <t>Template extraction</t>
-  </si>
-  <si>
-    <t>Document-to-template</t>
-  </si>
-  <si>
-    <t>Template matching</t>
-  </si>
-  <si>
-    <t>Advanced template sharing</t>
-  </si>
-  <si>
-    <t>Teams</t>
-  </si>
-  <si>
-    <t>Translation memory</t>
-  </si>
-  <si>
-    <t>PDF merge/split</t>
-  </si>
-  <si>
-    <t>Page reorder</t>
-  </si>
-  <si>
-    <t>Page rotate</t>
-  </si>
-  <si>
-    <t>Page delete</t>
-  </si>
-  <si>
-    <t>Page extract</t>
-  </si>
-  <si>
-    <t>Merge documents</t>
-  </si>
-  <si>
-    <t>LATER</t>
-  </si>
-  <si>
-    <t>Split documents</t>
-  </si>
-  <si>
-    <t>Watermark</t>
-  </si>
-  <si>
-    <t>Forms (advanced)</t>
-  </si>
-  <si>
-    <t>Brief 62: LATER</t>
-  </si>
-  <si>
-    <t>SmartArt editing</t>
-  </si>
-  <si>
-    <t>Brief 62: LATER; SmartArt is preserved, not edited</t>
-  </si>
-  <si>
-    <t>OLE</t>
-  </si>
-  <si>
-    <t>Brief 62: LATER; OLE objects preserved, not edited</t>
-  </si>
-  <si>
-    <t>Full tracked-change editor</t>
-  </si>
-  <si>
-    <t>Advanced citation manager</t>
-  </si>
-  <si>
-    <t>Advanced drawing editor</t>
-  </si>
-  <si>
-    <t>Layout-preserving PDF editing (frames/anchors)</t>
-  </si>
-  <si>
-    <t>ARCHITECTURE_ONLY</t>
-  </si>
-  <si>
-    <t>Phase 9: architecture and hooks only</t>
-  </si>
-  <si>
-    <t>Product tasks (live from MASTER)</t>
-  </si>
-  <si>
-    <t>TRANSLATION — Translation and fonts</t>
-  </si>
-  <si>
-    <t>Translation MVP and FontResolver. Categories: TRANSLATION, FONT. Rows are formulas over MASTER — change task data in MASTER or with tools/tracker/tracker.py.</t>
-  </si>
-  <si>
-    <t>PDF_TO_EDITABLE — PDF to editable</t>
-  </si>
-  <si>
-    <t>PDF to editable document conversion. Categories: P2E. Rows are formulas over MASTER — change task data in MASTER or with tools/tracker/tracker.py.</t>
-  </si>
-  <si>
-    <t>BILLING_PLANS — Plans and billing</t>
-  </si>
-  <si>
-    <t>Initial plan hypothesis — brief §64: configurable defaults, not final prices; confirm against measured AI and infrastructure cost. Blue = input.</t>
-  </si>
-  <si>
-    <t>Usage unit / feature</t>
-  </si>
-  <si>
-    <t>FREE</t>
-  </si>
-  <si>
-    <t>PRO</t>
-  </si>
-  <si>
-    <t>BUSINESS</t>
-  </si>
-  <si>
-    <t>Documents / month</t>
-  </si>
-  <si>
-    <t>BUSINESS: per workspace</t>
-  </si>
-  <si>
-    <t>PDF conversion pages / month</t>
-  </si>
-  <si>
-    <t>OCR pages / month</t>
-  </si>
-  <si>
-    <t>Translation characters / month</t>
-  </si>
-  <si>
-    <t>AI operations / month</t>
-  </si>
-  <si>
-    <t>Exports / month</t>
-  </si>
-  <si>
-    <t>high</t>
-  </si>
-  <si>
-    <t>BUSINESS: 'high export limits', no number given</t>
-  </si>
-  <si>
-    <t>Templates</t>
-  </si>
-  <si>
-    <t>basic</t>
-  </si>
-  <si>
-    <t>custom</t>
-  </si>
-  <si>
-    <t>shared</t>
-  </si>
-  <si>
-    <t>Formatting</t>
-  </si>
-  <si>
-    <t>Format by Example</t>
-  </si>
-  <si>
-    <t>-</t>
-  </si>
-  <si>
-    <t>Advanced Document Health</t>
-  </si>
-  <si>
-    <t>yes</t>
-  </si>
-  <si>
-    <t>Version history</t>
-  </si>
-  <si>
-    <t>no</t>
-  </si>
-  <si>
-    <t>reasonable limits</t>
-  </si>
-  <si>
-    <t>Team workspace</t>
-  </si>
-  <si>
-    <t>Priority processing</t>
-  </si>
-  <si>
-    <t>Advanced controls</t>
-  </si>
-  <si>
-    <t>Billing and plan tasks (live from MASTER)</t>
-  </si>
-  <si>
-    <t>INFRA — Infrastructure</t>
-  </si>
-  <si>
-    <t>Tracker, jobs, storage, observability, deployment, documentation. Categories: INFRA, JOBS, STORAGE, OBSERVABILITY, DOCS. Rows are formulas over MASTER — change task data in MASTER or with tools/tracker/tracker.py.</t>
-  </si>
-  <si>
-    <t>Timestamp</t>
-  </si>
-  <si>
-    <t>Task ID</t>
-  </si>
-  <si>
-    <t>Change</t>
-  </si>
-  <si>
-    <t>Files</t>
-  </si>
-  <si>
-    <t>Created SmartDoc_Master_Implementation_Tracker.xlsx from the 2026-09-26 audit findings and the brief's phases: 151 tasks, 20 findings, 15 release gates.</t>
-  </si>
-  <si>
-    <t>tools/tracker/tracker.py, tools/tracker/seed.py</t>
-  </si>
-  <si>
-    <t>N/A</t>
-  </si>
-  <si>
-    <t>Built the Excel control centre: MASTER with 151 stable-ID tasks from the audit findings and the brief's 19 phases, CRITICAL_FIXES (20 findings -&gt; fix tasks, live status), 14 category views, DASHBOARD (totals, completion/verified %, phase %, category %, P0/P1 remaining), CHANGE_LOG, SESSION_STATE, RELEASE_GATES GATE-001..015. Formulas verified in Excel against independently computed values.</t>
-  </si>
-  <si>
-    <t>tools/tracker/*, SmartDoc_Master_Implementation_Tracker.xlsx, .gitignore</t>
-  </si>
-  <si>
-    <t>Resume reminder set with the platform scheduler; it fired and resumed the work. It only fires while this session is open and idle, which is recorded in AI-CONTINUATION.md.</t>
-  </si>
-  <si>
-    <t>Created the checkpoint system: AI-CONTINUATION.md with CURRENT STATE / LAST VERIFIED / WHAT WAS CHANGED / WHAT PASSED / WHAT FAILED / WHAT REMAINS / NEXT ACTION / IMPORTANT WARNINGS, session-state.json mirrored into SESSION_STATE by tracker.py state, and the brief saved verbatim for future sessions.</t>
-  </si>
-  <si>
-    <t>docs/AI-CONTINUATION.md, docs/session-state.json, docs/implementation-brief.md</t>
-  </si>
-  <si>
-    <t>Baseline backend suite: 643 passed, 1 skipped (optional real-Word check), 0 failed in 88 s on ea69829. Recorded as RUN-0001.</t>
-  </si>
-  <si>
-    <t>Baseline frontend: eslint clean, tsc clean, Vitest 46 passed in 6 files, production build succeeded. Recorded as RUN-0002..RUN-0005.</t>
-  </si>
-  <si>
-    <t>Baseline E2E: 16 Playwright workflows passed against the throwaway stack (SQLite backend :8100, production build :3100). The brief's 24-workflow target is TEST-040; temp-dir leak logged as TEST-006.</t>
-  </si>
-  <si>
-    <t>Baseline database: alembic head 85211092fe4c, check reports no drift, full down/up cycle clean; PostgreSQL offline SQL builds 14 tables with RLS; Supabase has all 8 migrations and only INFO-level advisor notices.</t>
-  </si>
-  <si>
-    <t>Baseline dependency audit: pip-audit finds no known vulnerabilities in requirements.lock or requirements-dev.lock; npm audit reports 0 vulnerabilities (production and dev).</t>
-  </si>
-  <si>
-    <t>Baseline infrastructure inspected: compose file valid with 8 services, arq worker and in-process job backends, local and S3 storage providers. Docker images were not built (daemon not running) - left to INFRA-010.</t>
-  </si>
-  <si>
-    <t>Baseline fixtures: the repository's 12 golden DOCX are generated by python-docx (not Word-authored) plus one PDF; the audit's 17 Word-authored fixtures still live outside the repo and move in with TEST-020.</t>
-  </si>
-  <si>
-    <t>Wrote docs/architecture/current-baseline.md: stack versions, the 11 baseline checks with commands and results, the migration chain and live database state, fixture inventory, audit performance figures, and what the baseline could not verify (Docker images, real AI model, Stripe, e-mail, hosting).</t>
-  </si>
-  <si>
-    <t>INFRA-001, INFRA-002, INFRA-003, TEST-001, TEST-002, TEST-003, TEST-004, TEST-005, SEC-001, INFRA-004, DOCS-001</t>
-  </si>
-  <si>
-    <t>Phase 0 committed (4da4ecb, pushed to feature/smartdoc-production-hardening): tracker, checkpoint system and measured baseline. All 11 phase-0 tasks DONE; no production code changed.</t>
-  </si>
-  <si>
-    <t>see commit 4da4ecb</t>
-  </si>
-  <si>
-    <t>Model now holds blocks nested inside table cells, list items and quotes as Elements (authoritative when set; inline keeps plain text), plus list numbering start/format; nesting capped at 8 levels (422 beyond). schemaVersion stays 1: the fields are additive.</t>
-  </si>
-  <si>
-    <t>backend/app/models/document.py, backend/tests/test_document_nesting.py</t>
-  </si>
-  <si>
-    <t>Regenerated the OpenAPI schema and the frontend's generated types for the nested-block and numbering fields; the contract test and the type check pass.</t>
-  </si>
-  <si>
-    <t>frontend/types/generated/*, frontend/types/document.ts</t>
-  </si>
-  <si>
-    <t>Backend readers now see nested blocks: pasted pictures inside cells/list items/quotes are validated and moved to asset storage like top-level ones (security and quota), exports fetch their assets, and the links health check covers list items, cells and nested blocks.</t>
-  </si>
-  <si>
-    <t>backend/app/services/image_assets.py, backend/app/services/document_service.py, backend/app/formatting/health.py</t>
-  </si>
-  <si>
-    <t>Word export renders nested blocks in cells, list items and quotes in reading order (verified by text order), numbers lists from their start in their format, and writes pictures' alt text.</t>
-  </si>
-  <si>
-    <t>backend/app/export/docx_export.py</t>
-  </si>
-  <si>
-    <t>PDF export renders nested blocks and list numbering (start/format); nested numbered levels now use the same a./i. sequence as the Word export instead of 1. everywhere.</t>
-  </si>
-  <si>
-    <t>backend/app/export/pdf_export.py</t>
-  </si>
-  <si>
-    <t>The editor mapping is total over the schema (tested against getSchema(editorExtensions)); anything unknown stops the save with a visible 'Not saved' message instead of being dropped, and the last saved version stays untouched.</t>
-  </si>
-  <si>
-    <t>frontend/editor/*</t>
-  </si>
-  <si>
-    <t>frontend/editor/nestedBlocks.test.ts (7 refusal cases); frontend/editor/useAutoSave.test.tsx (3)</t>
-  </si>
-  <si>
-    <t>Playwright pastes rich HTML (lists, code and a picture in table cells; a list in a quote; code in a list item; a list starting at 3 in letters), waits for autosave and reloads: everything is still there and no 'Not saved' appears.</t>
-  </si>
-  <si>
-    <t>frontend/e2e/nested.spec.ts</t>
-  </si>
-  <si>
-    <t>CORE-001, CORE-002, CORE-003, EDIT-001, EDIT-002, EDIT-003, EDIT-004, EDIT-005, EDIT-006, DOCX-001, PDF-001</t>
-  </si>
-  <si>
-    <t>Committed phase-01a-editor-integrity (1fe27a9, pushed): nested blocks in cells, list items and quotes survive the editor, the backend and both exports; unknown content stops the save visibly. AUD-01 fix tasks all DONE.</t>
-  </si>
-  <si>
-    <t>Import now produces a Document Fidelity Report: the importer's notes as items (feature, policy, count, content lost) plus an independent content check - the source's words (DOCX XML read separately from the importer, Markdown by what it renders, PDF extracted text) against the document's, in order. 'Verified' only when identical; differences listed with context (missing/added/changed/moved).</t>
-  </si>
-  <si>
-    <t>backend/app/fidelity/*, backend/app/models/document.py, backend/app/services/ingestion_service.py</t>
-  </si>
-  <si>
-    <t>Every importer note now carries a stable feature key and a brief-§90 policy class; review count and content-loss count are derived from them.</t>
-  </si>
-  <si>
-    <t>The editor shows the import's verdict in the status bar and a Проверка panel: content verified / differs (with word-level differences) / body complete but some content left out, then each item by policy. Browser check with a05 caught and fixed a misleading 'No content changes' when header text had been left out.</t>
-  </si>
-  <si>
-    <t>frontend/editor/panels/FidelityPanel.tsx, frontend/editor/EditorStatusBar.tsx, frontend/editor/DocumentEditorShell.tsx</t>
-  </si>
-  <si>
-    <t>FID-001, FID-004, FID-005, INFRA-005</t>
-  </si>
-  <si>
-    <t>Committed phase-01b-fidelity-report (8a330be, pushed): import fidelity report with policy classes and an independent word-level content check, shown in the editor; throwaway preview scripts.</t>
-  </si>
-  <si>
-    <t>Exports now report what they approximate or leave out (missing pictures, WebP a Word file can't hold, tables restyled for Word-sourced documents, edited kept fragments, page breaks in PDF tables, PDF comments/equations/fields/internal links, scripts the PDF can't lay out, alt text) and re-read the file: a Word export must hold exactly the document's words, a PDF every word in order (its own list numbers and page headers allowed). Shown under the Download button; the job result carries it.</t>
-  </si>
-  <si>
-    <t>Committed phase-01c-export-report (e55412f, pushed): export fidelity report with read-back content check, shown in the Export menu.</t>
-  </si>
-  <si>
-    <t>Added the machine-readable capability matrix (brief §91): 67 document features with import/edit/export/round-trip support and the policy the fidelity report uses, served at GET /api/v1/capabilities. Tests tie it to the code both ways, require a test for every clean round trip and a task for every unreported gap; writing it exposed unreported gaps now tracked (EDIT-012, DOCX-027).</t>
-  </si>
-  <si>
-    <t>backend/app/capabilities.py, backend/app/api/capabilities.py, backend/app/main.py, backend/tests/test_capabilities.py, frontend/types/generated/*</t>
-  </si>
-  <si>
-    <t>Committed phase-01d-capability-matrix (fcf30d7, pushed).</t>
-  </si>
-  <si>
-    <t>FID-002: import report now names empty spacing paragraphs, unsafe link addresses and per-section differences (page setup, odd/even breaks, page numbering, borders, line numbers, vertical alignment); matrix rows docx.empty_paragraphs + docx.sections updated</t>
-  </si>
-  <si>
-    <t>backend/app/fidelity/docx_detect.py, backend/app/fidelity/imports.py, backend/app/parsers/docx.py, backend/app/parsers/docx_inline.py, backend/app/capabilities.py, backend/tests/test_docx_detect.py</t>
-  </si>
-  <si>
-    <t>DOCX-015: section breaks break the page only where Word does (next section's w:type decides); continuous breaks no longer become page breaks</t>
-  </si>
-  <si>
-    <t>DOCX-016: list number formats, start values and continuation round-trip; custom and multi-level labels reported</t>
-  </si>
-  <si>
-    <t>DOCX-012: Word core properties round-trip; custom properties and sensitivity labels reported without values</t>
-  </si>
-  <si>
-    <t>tests/test_docx_detect.py::test_the_files_own_properties_go_back_into_word_not_the_templates, tests/test_docx_detect.py::test_metadata_that_is_not_kept_is_reported_without_its_values</t>
-  </si>
-  <si>
-    <t>DOCX-026: unsafe link addresses reported instead of silently dropped</t>
-  </si>
-  <si>
-    <t>Golden JSON export is deterministic (uuid5 ids by order, fixed timestamps) so a regenerated fixture only differs where the importer's output did</t>
-  </si>
-  <si>
-    <t>backend/scripts/export_golden_json.py, frontend/tests/fixtures/golden/*.json</t>
-  </si>
-  <si>
-    <t>two consecutive exports byte-identical; tests/test_golden_documents.py::test_the_frontend_golden_json_is_current</t>
-  </si>
-  <si>
-    <t>FID-002 committed and pushed (phase-01e-import-detections)</t>
-  </si>
-  <si>
-    <t>SEC-022: formatting rule values validated at every entry and at resolve; CSS break-out via element style/page settings/instructions closed</t>
-  </si>
-  <si>
-    <t>backend/app/formatting/values.py, backend/app/formatting/engine.py, backend/app/schemas/formatting.py, backend/app/schemas/document.py, backend/app/ai/instruction_extraction.py, backend/tests/test_rule_values.py</t>
-  </si>
-  <si>
-    <t>FMT-005: instruction-path rule values validated before reaching CSS/export (with SEC-022)</t>
-  </si>
-  <si>
-    <t>EDIT-008: pasted/shortcut alignment saved as the element's own style and kept on split; paste into an empty paragraph keeps the pasted paragraphs' attributes</t>
-  </si>
-  <si>
-    <t>frontend/editor/tiptapToDocument.ts, frontend/editor/documentToTiptap.ts, frontend/editor/useAutoSave.ts, frontend/editor/pasteIntoEmptyBlock.ts, frontend/editor/extensions.ts, frontend/services/api/documents.ts, backend/app/schemas/document.py, backend/app/formatting/engine.py, backend/app/services/document_service.py, backend/app/api/documents.py</t>
-  </si>
-  <si>
-    <t>EDIT-009: pasted picture size kept as the picture's width share</t>
-  </si>
-  <si>
-    <t>EDIT-012: values outside the model named in the status bar and the Проверка panel</t>
-  </si>
-  <si>
-    <t>EDIT-011: cell alignment from pasted cells kept per column; differing cells and column widths reported</t>
-  </si>
-  <si>
-    <t>EDIT-008, EDIT-009, EDIT-012, SEC-022, FMT-005</t>
-  </si>
-  <si>
-    <t>Committed and pushed phase-01f-editor-direct-formatting</t>
-  </si>
-  <si>
-    <t>EDIT-010: link titles kept from Word/Markdown through the editor back into Word</t>
-  </si>
-  <si>
-    <t>backend/app/models/document.py, backend/app/parsers/docx_inline.py, backend/app/parsers/docx.py, backend/app/export/docx_export.py, backend/app/parsers/markdown.py, frontend/editor/tiptapToDocument.ts, frontend/editor/documentToTiptap.ts</t>
-  </si>
-  <si>
-    <t>FID-006: Markdown pictures named as left out (content), thematic breaks kept as rules</t>
-  </si>
-  <si>
-    <t>backend/app/parsers/markdown.py, backend/app/capabilities.py, backend/tests/test_capabilities.py, backend/tests/test_markdown_parser.py</t>
-  </si>
-  <si>
-    <t>EDIT-011: cell alignment/widths the model can't hold are named; keeping them moves to DOCX-017</t>
-  </si>
-  <si>
-    <t>EDIT-007: marks in one canonical order (MarkType) on both sides; opening a document saves nothing</t>
-  </si>
-  <si>
-    <t>backend/app/models/document.py, frontend/editor/tiptapToDocument.ts</t>
-  </si>
-  <si>
-    <t>TEST-010: nested-structure regression suite consolidated and verified</t>
-  </si>
-  <si>
-    <t>EDIT-008, EDIT-010, FID-006</t>
-  </si>
-  <si>
-    <t>Phase 1 browser check in the throwaway stack: Markdown doc with a picture -&gt; 'Body text complete, some content left out · 1 to review' (picture named with its description), '---' imported as a rule; pasted centred line + 160px picture + hsl colour + titled link at the end -&gt; status 'Saved · 1 formatting change not kept', Проверка 'While editing' lists the colour; after reload: line centred, picture width 24.9%, link title kept, notice gone</t>
-  </si>
-  <si>
-    <t>manual browser check (throwaway stack, fresh SQLite)</t>
-  </si>
-  <si>
-    <t>DOCS-011: documentation tree started for Phase 1 (document model, fidelity, docx, formatting, security, testing)</t>
-  </si>
-  <si>
-    <t>EDIT-007, EDIT-010, EDIT-011, FID-006, TEST-010, DOCS-011</t>
-  </si>
-  <si>
-    <t>Committed and pushed phase-01g-phase-1-complete; Phase 1 complete</t>
-  </si>
-  <si>
-    <t>AI-001: order/count/token/numeric/punctuation-aware comparator for AI output, with classified differences</t>
-  </si>
-  <si>
-    <t>backend/app/fidelity/text_check.py, backend/tests/test_ai_fidelity.py</t>
-  </si>
-  <si>
-    <t>AI-002: numbers and units protected; changed_numbers for cross-language checks</t>
-  </si>
-  <si>
-    <t>AI-003: structure analysis refuses answers that alter the text, per piece, logging without content</t>
-  </si>
-  <si>
-    <t>backend/app/ai/structure_analysis.py</t>
-  </si>
-  <si>
-    <t>AI-004: adversarial fidelity tests for every alteration the brief names</t>
-  </si>
-  <si>
-    <t>AI-001, AI-002, AI-003, AI-004</t>
-  </si>
-  <si>
-    <t>Committed and pushed phase-02a-ai-fidelity-check</t>
-  </si>
-  <si>
-    <t>AI-005: AI operations classified FORMAT/STRUCTURE/CONTENT; per-element instruction styles no longer dropped by the formatting pass</t>
-  </si>
-  <si>
-    <t>backend/app/formatting/proposals.py, backend/app/services/document_service.py</t>
-  </si>
-  <si>
-    <t>REV-001: change model with categories, used for proposals</t>
-  </si>
-  <si>
-    <t>backend/app/models/document.py, frontend/types/document.ts</t>
-  </si>
-  <si>
-    <t>AI-006: PLAN-&gt;VALIDATE-&gt;PREVIEW-&gt;ACCEPT-&gt;APPLY for AI content changes</t>
-  </si>
-  <si>
-    <t>backend/app/formatting/proposals.py, backend/app/services/document_service.py, backend/app/api/documents.py, backend/app/jobs/runner.py, backend/app/schemas/document.py, backend/app/schemas/jobs.py</t>
-  </si>
-  <si>
-    <t>AI-007: proposal review UI with accept/reject, E2E verified</t>
-  </si>
-  <si>
-    <t>frontend/editor/panels/ProposalsList.tsx, frontend/editor/panels/InstructionsPanel.tsx, frontend/editor/EditorStatusBar.tsx, frontend/editor/useFormatting.ts, frontend/services/api/documents.ts, frontend/services/api/jobs.ts, backend/scripts/e2e_ai.py, backend/scripts/e2e_server.py</t>
-  </si>
-  <si>
-    <t>AI-005, REV-001, AI-006, AI-007</t>
-  </si>
-  <si>
-    <t>Committed and pushed phase-02b-ai-proposals</t>
-  </si>
-  <si>
-    <t>AI-008: per-job/per-request AI call and time budget; no unbounded retries</t>
-  </si>
-  <si>
-    <t>backend/app/ai/budget.py, backend/app/config.py, backend/app/jobs/runner.py, backend/app/api/deps.py, backend/app/ai/structure_analysis.py</t>
-  </si>
-  <si>
-    <t>Committed and pushed phase-02c-ai-budget</t>
-  </si>
-  <si>
-    <t>AI-009: prompt-injection review; AI answer fields bounded; hostile-document tests</t>
-  </si>
-  <si>
-    <t>backend/app/ai/schemas.py, backend/app/ai/structure_analysis.py, backend/tests/test_prompt_injection.py</t>
-  </si>
-  <si>
-    <t>SEC-018: prompt injection / AI output abuse covered by AI-009's tests</t>
-  </si>
-  <si>
-    <t>AI-001, AI-005, AI-007, AI-009</t>
-  </si>
-  <si>
-    <t>Phase 2 gate: backend 817 passed/1 skipped, Vitest 117, Playwright 20; browser check in the throwaway stack - 'make the title red and delete “This draft paragraph”': title red at once, the paragraph kept and shown under Changes to review (struck through, with the instruction), notice + '1 AI change to review'; Accept removed it, reload kept it removed with nothing pending</t>
-  </si>
-  <si>
-    <t>full suites + manual browser check</t>
-  </si>
-  <si>
-    <t>DOCX-010: original Word package kept as an immutable, checksummed asset</t>
-  </si>
-  <si>
-    <t>backend/app/models/document.py, backend/app/services/document_service.py</t>
-  </si>
-  <si>
-    <t>DOCX-011: Word exports written into the original package; import report reflects what they keep</t>
-  </si>
-  <si>
-    <t>backend/app/export/docx_export.py, backend/app/fidelity/imports.py, backend/app/fidelity/docx_source.py, backend/app/fidelity/docx_detect.py, backend/app/fidelity/exports.py, backend/app/jobs/runner.py, backend/app/api/documents.py, backend/app/capabilities.py</t>
-  </si>
-  <si>
-    <t>TEST-023: independent package validation of every Word export</t>
-  </si>
-  <si>
-    <t>backend/app/export/package_check.py, backend/tests/test_package_check.py</t>
-  </si>
-  <si>
-    <t>DOCX-012: metadata preserved (core in the model, app/custom/labels via the original package)</t>
-  </si>
-  <si>
-    <t>DOCX-028: unchanged blocks keep their original XML in Word exports; server-side provenance; earlier sections follow page setup, header and page-number changes; lost sections reported; golden 13-kept-blocks + E2E.</t>
-  </si>
-  <si>
-    <t>backend/app/export/provenance.py, backend/app/export/docx_export.py, backend/app/parsers/docx.py, backend/app/models/document.py, backend/app/services/document_service.py, backend/app/fidelity/imports.py, backend/app/fidelity/exports.py, backend/app/capabilities.py, frontend/editor/tiptapToDocument.ts, frontend/e2e/kept-blocks.spec.ts, docs/docx/README.md</t>
-  </si>
-  <si>
-    <t>DOCX-028 committed and pushed as c8c2d27 (phase-03b-original-blocks).</t>
-  </si>
-  <si>
-    <t>DOCX-025: Word's hidden text stays hidden - hidden mark with Word's style resolution, editor shows it only on request, vanish in Word exports, left out of PDF with a note, consistent content checks.</t>
-  </si>
-  <si>
-    <t>backend/app/models/document.py, backend/app/parsers/docx_inline.py, backend/app/parsers/docx_styles.py, backend/app/parsers/docx.py, backend/app/fidelity/docx_detect.py, backend/app/fidelity/content.py, backend/app/fidelity/exports.py, backend/app/export/docx_export.py, backend/app/export/pdf_export.py, frontend/editor/hiddenText.ts, frontend/editor/EditorStatusBar.tsx, frontend/editor/DocumentEditorShell.tsx, frontend/app/globals.css</t>
-  </si>
-  <si>
-    <t>DOCX-025 committed and pushed as 7d1af86 (phase-03c-hidden-text).</t>
-  </si>
-  <si>
-    <t>DOCX-013 part 1: underline and strike styles, capitals, small capitals, spacing and raised/lowered text kept through import, editor, Word and PDF; paragraph-style formatting turned off by a run fixed.</t>
-  </si>
-  <si>
-    <t>backend/app/models/document.py, backend/app/parsers/docx_inline.py, backend/app/parsers/docx_styles.py, backend/app/parsers/docx.py, backend/app/export/docx_export.py, backend/app/export/pdf_export.py, backend/app/fidelity/*, frontend/editor/characterFormatting.ts, frontend/editor/tiptapToDocument.ts</t>
-  </si>
-  <si>
-    <t>backend 888 passed/1 skipped (tests/test_character_formatting.py 12); Vitest 128 (editor/characterFormatting.test.ts 3, golden round trip of 02); Playwright 22; tsc + eslint clean</t>
-  </si>
-  <si>
-    <t>DOCX-013 part 1 committed and pushed as 6619159 (phase-03d-character-formatting); part 2 next.</t>
-  </si>
-  <si>
-    <t>6619159</t>
-  </si>
-  <si>
-    <t>FID-007: reports follow the Word copy - kept while unchanged at import, rewritten losses named at export, unsafe links never copied back.</t>
-  </si>
-  <si>
-    <t>backend/app/fidelity/imports.py, backend/app/export/docx_export.py, backend/tests/test_copy_reports.py</t>
-  </si>
-  <si>
-    <t>DOCX-013 part 2: language kept; scale and effects named and kept while unchanged; brief §22 list is now supported, preserved or explicitly named.</t>
-  </si>
-  <si>
-    <t>backend/app/models/document.py, backend/app/parsers/docx_inline.py, backend/app/fidelity/docx_detect.py, frontend/editor/characterFormatting.ts</t>
-  </si>
-  <si>
-    <t>DOCX-013 done: part 1 6619159, part 2 d32c6a6 (phase-03e-copy-reports).</t>
-  </si>
-  <si>
-    <t>FID-007 committed and pushed as d32c6a6.</t>
-  </si>
-  <si>
-    <t>DOCX-014 part 1: right indent, shading, pagination controls, contextual spacing and direction kept through import, CSS, Word and PDF.</t>
-  </si>
-  <si>
-    <t>backend/app/models/document.py, backend/app/formatting/*, backend/app/parsers/docx_styles.py, backend/app/parsers/docx.py, backend/app/export/docx_export.py, backend/app/export/pdf_export.py</t>
-  </si>
-  <si>
-    <t>backend 903 passed/1 skipped (tests/test_paragraph_formatting.py 9); Vitest 129; Playwright 22; tsc + eslint clean</t>
-  </si>
-  <si>
-    <t>DOCX-014 part 1 committed and pushed as eade93e (phase-03f-paragraph-formatting); part 2 next.</t>
-  </si>
-  <si>
     <t>DOCX-014 part 2: paragraph borders and tab stops kept through import, CSS, Word and PDF; what the PDF and editor can't draw is named.</t>
   </si>
   <si>
     <t>backend/app/formatting/values.py, backend/app/parsers/docx_styles.py, backend/app/export/docx_export.py, backend/app/export/pdf_export.py, backend/tests/test_paragraph_formatting.py</t>
   </si>
   <si>
+    <t>DOCX-014 done: part 1 eade93e, part 2 c158722 (phase-03g-borders-tab-stops).</t>
+  </si>
+  <si>
     <t>SESSION_STATE — Where the work stands</t>
   </si>
   <si>
@@ -4609,7 +4615,7 @@
     <t>Current Commit</t>
   </si>
   <si>
-    <t>9f1c5b4 (+ uncommitted changes)</t>
+    <t>c158722 (+ uncommitted changes)</t>
   </si>
   <si>
     <t>backend 913 passed, 1 skipped; vitest 129; e2e 22; tsc; eslint</t>
@@ -4630,7 +4636,7 @@
     <t>cd backend &amp;&amp; venv/Scripts/python -m pytest -q tests/test_original_blocks.py tests/test_source_package.py tests/test_docx_detect.py</t>
   </si>
   <si>
-    <t>2026-09-27T20:01:11+03:00</t>
+    <t>2026-09-27T20:01:47+03:00</t>
   </si>
   <si>
     <t>Resume Instructions</t>
@@ -9158,7 +9164,7 @@
       </c>
       <c r="B6" s="7">
         <f>COUNTIF(MASTER!$G$2:$G$2000,"DONE")</f>
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C6" s="8" t="s">
         <v>8</v>
@@ -9289,7 +9295,7 @@
       </c>
       <c r="B13" s="7">
         <f>B5-B6</f>
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C13" s="8" t="s">
         <v>28</v>
@@ -9308,7 +9314,7 @@
       </c>
       <c r="B14" s="9">
         <f>IF(B5=0,0,B6/B5)</f>
-        <v>0.3515151515151515</v>
+        <v>0.3575757575757576</v>
       </c>
       <c r="C14" s="8" t="s">
         <v>31</v>
@@ -9337,7 +9343,7 @@
       </c>
       <c r="F15" s="1" t="str">
         <f>IF(SESSION_STATE!$B$17="","",SESSION_STATE!$B$17)</f>
-        <v>2026-09-27T20:01:11+03:00</v>
+        <v>2026-09-27T20:01:47+03:00</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
@@ -9358,7 +9364,7 @@
       </c>
       <c r="B17" s="7">
         <f>COUNTIFS(MASTER!$F$2:$F$2000,"P1",MASTER!$G$2:$G$2000,"&lt;&gt;DONE")</f>
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C17" s="8" t="s">
         <v>39</v>
@@ -9563,7 +9569,7 @@
       </c>
       <c r="H22" s="13">
         <f>COUNTIFS(MASTER!$B$2:$B$2000,$E22,MASTER!$G$2:$G$2000,"DONE")</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I22" s="13">
         <f>COUNTIFS(MASTER!$B$2:$B$2000,$E22,MASTER!$G$2:$G$2000,"VERIFIED")+H22</f>
@@ -9583,7 +9589,7 @@
       </c>
       <c r="M22" s="14">
         <f t="shared" si="0"/>
-        <v>0.30769230769230771</v>
+        <v>0.34615384615384615</v>
       </c>
       <c r="N22" s="14">
         <f t="shared" si="1"/>
@@ -9895,7 +9901,7 @@
       </c>
       <c r="B29" s="13">
         <f>COUNTIF(MASTER!$G$2:$G$2000,A29)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C29" s="12" t="s">
         <v>76</v>
@@ -9945,7 +9951,7 @@
       </c>
       <c r="B30" s="13">
         <f>COUNTIF(MASTER!$G$2:$G$2000,A30)</f>
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C30" s="12" t="s">
         <v>79</v>
@@ -10558,7 +10564,7 @@
       </c>
       <c r="H44" s="13">
         <f>COUNTIFS(MASTER!$C$2:$C$2000,$E44,MASTER!$G$2:$G$2000,"DONE")</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I44" s="13">
         <f>COUNTIFS(MASTER!$C$2:$C$2000,$E44,MASTER!$G$2:$G$2000,"VERIFIED")+H44</f>
@@ -10578,7 +10584,7 @@
       </c>
       <c r="M44" s="14">
         <f t="shared" si="2"/>
-        <v>0.33333333333333331</v>
+        <v>0.38095238095238093</v>
       </c>
       <c r="N44" s="14">
         <f t="shared" si="3"/>
@@ -21933,7 +21939,7 @@
     <tabColor rgb="FF7F7F7F"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I84"/>
+  <dimension ref="A1:I85"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17" customWidth="1"/>
@@ -23966,7 +23972,7 @@
         <v>1063</v>
       </c>
       <c r="H83" s="12" t="s">
-        <v>508</v>
+        <v>1499</v>
       </c>
       <c r="I83" s="18"/>
     </row>
@@ -23981,10 +23987,10 @@
         <v>3</v>
       </c>
       <c r="D84" s="18" t="s">
-        <v>1499</v>
+        <v>1500</v>
       </c>
       <c r="E84" s="18" t="s">
-        <v>1500</v>
+        <v>1501</v>
       </c>
       <c r="F84" s="18" t="s">
         <v>507</v>
@@ -23993,12 +23999,37 @@
         <v>1063</v>
       </c>
       <c r="H84" s="12" t="s">
+        <v>1499</v>
+      </c>
+      <c r="I84" s="18"/>
+    </row>
+    <row r="85" spans="1:9" ht="76.5" x14ac:dyDescent="0.25">
+      <c r="A85" s="19">
+        <v>46292.834537037037</v>
+      </c>
+      <c r="B85" s="12" t="s">
+        <v>503</v>
+      </c>
+      <c r="C85" s="12">
+        <v>3</v>
+      </c>
+      <c r="D85" s="18" t="s">
+        <v>1502</v>
+      </c>
+      <c r="E85" s="18"/>
+      <c r="F85" s="18" t="s">
+        <v>507</v>
+      </c>
+      <c r="G85" s="12" t="s">
+        <v>1063</v>
+      </c>
+      <c r="H85" s="12" t="s">
         <v>508</v>
       </c>
-      <c r="I84" s="18"/>
+      <c r="I85" s="18"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I84" xr:uid="{00000000-0009-0000-0000-000011000000}"/>
+  <autoFilter ref="A1:I85" xr:uid="{00000000-0009-0000-0000-000011000000}"/>
   <conditionalFormatting sqref="G2:G5000">
     <cfRule type="cellIs" dxfId="4" priority="1" operator="equal">
       <formula>"PASS"</formula>
@@ -24035,7 +24066,7 @@
   <sheetData>
     <row r="1" spans="1:2" ht="20.25" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
-        <v>1501</v>
+        <v>1503</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -24045,15 +24076,15 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>1502</v>
+        <v>1504</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="10" t="s">
-        <v>1503</v>
+        <v>1505</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>1504</v>
+        <v>1506</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -24061,7 +24092,7 @@
         <v>6</v>
       </c>
       <c r="B5" s="18" t="s">
-        <v>1505</v>
+        <v>1507</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="25.5" x14ac:dyDescent="0.25">
@@ -24069,7 +24100,7 @@
         <v>9</v>
       </c>
       <c r="B6" s="18" t="s">
-        <v>1506</v>
+        <v>1508</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="25.5" x14ac:dyDescent="0.25">
@@ -24077,7 +24108,7 @@
         <v>12</v>
       </c>
       <c r="B7" s="18" t="s">
-        <v>1507</v>
+        <v>1509</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="25.5" x14ac:dyDescent="0.25">
@@ -24085,23 +24116,23 @@
         <v>15</v>
       </c>
       <c r="B8" s="18" t="s">
-        <v>1508</v>
+        <v>1510</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>1509</v>
+        <v>1511</v>
       </c>
       <c r="B9" s="18" t="s">
-        <v>1510</v>
+        <v>1512</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
-        <v>1511</v>
+        <v>1513</v>
       </c>
       <c r="B10" s="18" t="s">
-        <v>1512</v>
+        <v>1514</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
@@ -24109,7 +24140,7 @@
         <v>26</v>
       </c>
       <c r="B11" s="18" t="s">
-        <v>1513</v>
+        <v>1515</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
@@ -24117,7 +24148,7 @@
         <v>29</v>
       </c>
       <c r="B12" s="18" t="s">
-        <v>1514</v>
+        <v>1516</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="25.5" x14ac:dyDescent="0.25">
@@ -24125,7 +24156,7 @@
         <v>32</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>1515</v>
+        <v>1517</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="25.5" x14ac:dyDescent="0.25">
@@ -24133,7 +24164,7 @@
         <v>18</v>
       </c>
       <c r="B14" s="18" t="s">
-        <v>1516</v>
+        <v>1518</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="25.5" x14ac:dyDescent="0.25">
@@ -24141,7 +24172,7 @@
         <v>21</v>
       </c>
       <c r="B15" s="18" t="s">
-        <v>1517</v>
+        <v>1519</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
@@ -24149,7 +24180,7 @@
         <v>24</v>
       </c>
       <c r="B16" s="18" t="s">
-        <v>1518</v>
+        <v>1520</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
@@ -24157,29 +24188,29 @@
         <v>35</v>
       </c>
       <c r="B17" s="18" t="s">
-        <v>1519</v>
+        <v>1521</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
-        <v>1520</v>
+        <v>1522</v>
       </c>
       <c r="B18" s="18" t="s">
-        <v>1521</v>
+        <v>1523</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="6" t="s">
-        <v>1522</v>
+        <v>1524</v>
       </c>
       <c r="B19" s="18" t="str">
         <f>"Tasks "&amp;DASHBOARD!B5&amp;" · done "&amp;DASHBOARD!B6&amp;" · verified "&amp;DASHBOARD!B7&amp;" · in progress "&amp;DASHBOARD!B8&amp;" · blocked "&amp;DASHBOARD!B9&amp;" · failed "&amp;DASHBOARD!B10&amp;" · P0 open "&amp;DASHBOARD!B16&amp;" · P1 open "&amp;DASHBOARD!B17</f>
-        <v>Tasks 165 · done 58 · verified 59 · in progress 5 · blocked 1 · failed 0 · P0 open 46 · P1 open 43</v>
+        <v>Tasks 165 · done 59 · verified 59 · in progress 5 · blocked 1 · failed 0 · P0 open 46 · P1 open 42</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
-        <v>1523</v>
+        <v>1525</v>
       </c>
       <c r="B20" s="18" t="s">
         <v>1347</v>
@@ -24187,7 +24218,7 @@
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" s="6" t="s">
-        <v>1524</v>
+        <v>1526</v>
       </c>
       <c r="B21" s="18" t="s">
         <v>1349</v>
@@ -27140,7 +27171,7 @@
         <v>195</v>
       </c>
       <c r="G54" s="12" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="H54" s="18" t="s">
         <v>506</v>
@@ -27160,9 +27191,11 @@
       <c r="M54" s="19">
         <v>46292.826909722222</v>
       </c>
-      <c r="N54" s="19"/>
+      <c r="N54" s="19">
+        <v>46292.834537037037</v>
+      </c>
       <c r="O54" s="19">
-        <v>46292.833958333344</v>
+        <v>46292.834537037037</v>
       </c>
       <c r="P54" s="12" t="s">
         <v>508</v>
@@ -32016,7 +32049,7 @@
   <sheetData>
     <row r="1" spans="1:9" ht="20.25" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
-        <v>1525</v>
+        <v>1527</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
@@ -32026,16 +32059,16 @@
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
-        <v>1526</v>
+        <v>1528</v>
       </c>
       <c r="B3" s="6" t="s">
         <v>1063</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>1527</v>
+        <v>1529</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>1528</v>
+        <v>1530</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
@@ -32058,10 +32091,10 @@
     </row>
     <row r="6" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>1529</v>
+        <v>1531</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>1530</v>
+        <v>1532</v>
       </c>
       <c r="C6" s="10" t="s">
         <v>57</v>
@@ -32087,16 +32120,16 @@
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="15" t="s">
-        <v>1531</v>
+        <v>1533</v>
       </c>
       <c r="B7" s="18" t="s">
-        <v>1532</v>
+        <v>1534</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>1528</v>
+        <v>1530</v>
       </c>
       <c r="D7" s="18" t="s">
-        <v>1533</v>
+        <v>1535</v>
       </c>
       <c r="E7" s="16">
         <f>SUMPRODUCT(ISNUMBER(SEARCH(","&amp;MASTER!$A$2:$A$2000&amp;",",","&amp;SUBSTITUTE($D7," ","")&amp;","))*((MASTER!$G$2:$G$2000="DONE")))</f>
@@ -32112,13 +32145,13 @@
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="15" t="s">
-        <v>1534</v>
+        <v>1536</v>
       </c>
       <c r="B8" s="18" t="s">
-        <v>1535</v>
+        <v>1537</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>1528</v>
+        <v>1530</v>
       </c>
       <c r="D8" s="18" t="s">
         <v>651</v>
@@ -32137,16 +32170,16 @@
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="15" t="s">
-        <v>1536</v>
+        <v>1538</v>
       </c>
       <c r="B9" s="18" t="s">
-        <v>1537</v>
+        <v>1539</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>1528</v>
+        <v>1530</v>
       </c>
       <c r="D9" s="18" t="s">
-        <v>1538</v>
+        <v>1540</v>
       </c>
       <c r="E9" s="16">
         <f>SUMPRODUCT(ISNUMBER(SEARCH(","&amp;MASTER!$A$2:$A$2000&amp;",",","&amp;SUBSTITUTE($D9," ","")&amp;","))*((MASTER!$G$2:$G$2000="DONE")))</f>
@@ -32162,13 +32195,13 @@
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="15" t="s">
-        <v>1539</v>
+        <v>1541</v>
       </c>
       <c r="B10" s="18" t="s">
-        <v>1540</v>
+        <v>1542</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>1528</v>
+        <v>1530</v>
       </c>
       <c r="D10" s="18" t="s">
         <v>725</v>
@@ -32187,16 +32220,16 @@
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="15" t="s">
-        <v>1541</v>
+        <v>1543</v>
       </c>
       <c r="B11" s="18" t="s">
-        <v>1542</v>
+        <v>1544</v>
       </c>
       <c r="C11" s="12" t="s">
-        <v>1528</v>
+        <v>1530</v>
       </c>
       <c r="D11" s="18" t="s">
-        <v>1543</v>
+        <v>1545</v>
       </c>
       <c r="E11" s="16">
         <f>SUMPRODUCT(ISNUMBER(SEARCH(","&amp;MASTER!$A$2:$A$2000&amp;",",","&amp;SUBSTITUTE($D11," ","")&amp;","))*((MASTER!$G$2:$G$2000="DONE")))</f>
@@ -32212,13 +32245,13 @@
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="15" t="s">
-        <v>1544</v>
+        <v>1546</v>
       </c>
       <c r="B12" s="18" t="s">
-        <v>1545</v>
+        <v>1547</v>
       </c>
       <c r="C12" s="12" t="s">
-        <v>1528</v>
+        <v>1530</v>
       </c>
       <c r="D12" s="18" t="s">
         <v>583</v>
@@ -32237,13 +32270,13 @@
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="15" t="s">
-        <v>1546</v>
+        <v>1548</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>1547</v>
+        <v>1549</v>
       </c>
       <c r="C13" s="12" t="s">
-        <v>1528</v>
+        <v>1530</v>
       </c>
       <c r="D13" s="18" t="s">
         <v>583</v>
@@ -32262,13 +32295,13 @@
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="15" t="s">
-        <v>1548</v>
+        <v>1550</v>
       </c>
       <c r="B14" s="18" t="s">
-        <v>1549</v>
+        <v>1551</v>
       </c>
       <c r="C14" s="12" t="s">
-        <v>1528</v>
+        <v>1530</v>
       </c>
       <c r="D14" s="18" t="s">
         <v>829</v>
@@ -32287,13 +32320,13 @@
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="15" t="s">
-        <v>1550</v>
+        <v>1552</v>
       </c>
       <c r="B15" s="18" t="s">
-        <v>1551</v>
+        <v>1553</v>
       </c>
       <c r="C15" s="12" t="s">
-        <v>1528</v>
+        <v>1530</v>
       </c>
       <c r="D15" s="18" t="s">
         <v>758</v>
@@ -32312,13 +32345,13 @@
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" s="15" t="s">
-        <v>1552</v>
+        <v>1554</v>
       </c>
       <c r="B16" s="18" t="s">
-        <v>1553</v>
+        <v>1555</v>
       </c>
       <c r="C16" s="12" t="s">
-        <v>1528</v>
+        <v>1530</v>
       </c>
       <c r="D16" s="18" t="s">
         <v>809</v>
@@ -32337,13 +32370,13 @@
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" s="15" t="s">
-        <v>1554</v>
+        <v>1556</v>
       </c>
       <c r="B17" s="18" t="s">
-        <v>1555</v>
+        <v>1557</v>
       </c>
       <c r="C17" s="12" t="s">
-        <v>1528</v>
+        <v>1530</v>
       </c>
       <c r="D17" s="18" t="s">
         <v>797</v>
@@ -32362,13 +32395,13 @@
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" s="15" t="s">
-        <v>1556</v>
+        <v>1558</v>
       </c>
       <c r="B18" s="18" t="s">
-        <v>1557</v>
+        <v>1559</v>
       </c>
       <c r="C18" s="12" t="s">
-        <v>1528</v>
+        <v>1530</v>
       </c>
       <c r="D18" s="18" t="s">
         <v>909</v>
@@ -32387,13 +32420,13 @@
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" s="15" t="s">
-        <v>1558</v>
+        <v>1560</v>
       </c>
       <c r="B19" s="18" t="s">
-        <v>1559</v>
+        <v>1561</v>
       </c>
       <c r="C19" s="12" t="s">
-        <v>1528</v>
+        <v>1530</v>
       </c>
       <c r="D19" s="18" t="s">
         <v>217</v>
@@ -32412,16 +32445,16 @@
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" s="15" t="s">
-        <v>1560</v>
+        <v>1562</v>
       </c>
       <c r="B20" s="18" t="s">
-        <v>1561</v>
+        <v>1563</v>
       </c>
       <c r="C20" s="12" t="s">
-        <v>1528</v>
+        <v>1530</v>
       </c>
       <c r="D20" s="18" t="s">
-        <v>1562</v>
+        <v>1564</v>
       </c>
       <c r="E20" s="16">
         <f>SUMPRODUCT(ISNUMBER(SEARCH(","&amp;MASTER!$A$2:$A$2000&amp;",",","&amp;SUBSTITUTE($D20," ","")&amp;","))*((MASTER!$G$2:$G$2000="DONE")))</f>
@@ -32437,13 +32470,13 @@
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" s="15" t="s">
-        <v>1563</v>
+        <v>1565</v>
       </c>
       <c r="B21" s="18" t="s">
-        <v>1564</v>
+        <v>1566</v>
       </c>
       <c r="C21" s="12" t="s">
-        <v>1528</v>
+        <v>1530</v>
       </c>
       <c r="D21" s="18" t="s">
         <v>890</v>
@@ -38693,7 +38726,7 @@
       </c>
       <c r="B4" s="7">
         <f>COUNTIFS(MASTER!$C$2:$C$2000,"DOCX",MASTER!$G$2:$G$2000,"DONE")</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C4" s="7">
         <f>COUNTIFS(MASTER!$C$2:$C$2000,"DOCX",MASTER!$G$2:$G$2000,"VERIFIED")+B4</f>
@@ -38713,7 +38746,7 @@
       </c>
       <c r="G4" s="9">
         <f>IF(A4=0,0,B4/A4)</f>
-        <v>0.33333333333333331</v>
+        <v>0.38095238095238093</v>
       </c>
       <c r="H4" s="9">
         <f>IF(A4=0,0,C4/A4)</f>
@@ -39030,7 +39063,7 @@
       </c>
       <c r="F13" s="12" t="str">
         <f>IFERROR(INDEX(MASTER!$G$2:$G$2000,MATCH($A13,MASTER!$A$2:$A$2000,0))&amp;"","NOT IN MASTER")</f>
-        <v>VERIFIED</v>
+        <v>DONE</v>
       </c>
       <c r="G13" s="12" t="str">
         <f>IFERROR(INDEX(MASTER!$H$2:$H$2000,MATCH($A13,MASTER!$A$2:$A$2000,0))&amp;"","")</f>
@@ -39042,11 +39075,11 @@
       </c>
       <c r="I13" s="19">
         <f>IFERROR(IF(INDEX(MASTER!$O$2:$O$2000,MATCH($A13,MASTER!$A$2:$A$2000,0))="","",INDEX(MASTER!$O$2:$O$2000,MATCH($A13,MASTER!$A$2:$A$2000,0))),"")</f>
-        <v>46292.833958333344</v>
+        <v>46292.834537037037</v>
       </c>
       <c r="J13" s="12" t="str">
         <f>IFERROR(INDEX(MASTER!$P$2:$P$2000,MATCH($A13,MASTER!$A$2:$A$2000,0))&amp;"","")</f>
-        <v>eade93e</v>
+        <v>c158722</v>
       </c>
       <c r="K13" s="12" t="str">
         <f>IFERROR(INDEX(MASTER!$Q$2:$Q$2000,MATCH($A13,MASTER!$A$2:$A$2000,0))&amp;"","")</f>

--- a/SmartDoc_Master_Implementation_Tracker.xlsx
+++ b/SmartDoc_Master_Implementation_Tracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\speed\Desktop\Claude - ПРОЕКТ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA5ABFF4-A455-41D9-9C4B-8DB5F9C09841}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58858500-CB45-4D6D-B387-A2089CE8FB4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">AI!$A$7:$L$16</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="15" hidden="1">BILLING_PLANS!$A$25:$L$30</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="17" hidden="1">CHANGE_LOG!$A$1:$I$88</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="17" hidden="1">CHANGE_LOG!$A$1:$I$89</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">CRITICAL_FIXES!$A$31:$L$115</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">DOCUMENT_FIDELITY!$A$7:$L$24</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">DOCX_OOXML!$A$7:$L$28</definedName>
@@ -71,12 +71,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3933" uniqueCount="1591">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3938" uniqueCount="1593">
   <si>
     <t>SmartDoc — Master Implementation Tracker</t>
   </si>
   <si>
-    <t>Production-hardening brief. MASTER holds the task data; every number here is a formula. Updated with tools/tracker/tracker.py. Last written 2026-09-27 23:32 (local time).</t>
+    <t>Production-hardening brief. MASTER holds the task data; every number here is a formula. Updated with tools/tracker/tracker.py. Last written 2026-09-27 23:33 (local time).</t>
   </si>
   <si>
     <t>Overall</t>
@@ -1621,3039 +1621,3045 @@
     <t>backend/models, parsers, export</t>
   </si>
   <si>
+    <t>35c6771</t>
+  </si>
+  <si>
+    <t>Fixed: a section's w:type describes how THAT section starts (ECMA-376 17.6.22) - the importer used the ending section's own type, so a continuous break became a page break and continuous-&gt;new-page put the break between the wrong sections (probe confirmed). Now the next section's type decides. Per-section differences are reported (FID-002). Remaining: sections as a first-class model concept (orientation/margins/columns/headers per section, page-number restart) and export of several sections.; With DOCX-011 the last section's properties (columns, page numbering, borders, line numbers, vertical alignment, header/footer variants) are kept in Word exports; earlier sections' are still reported lost.; DOCX-028: earlier sections now survive in Word exports while their ending paragraph is unchanged; page setup/header/page-number changes apply to them; a lost one is reported (export.docx.section_lost). Modelling sections is still this task.</t>
+  </si>
+  <si>
+    <t>DOCX-016</t>
+  </si>
+  <si>
+    <t>Numbering engine</t>
+  </si>
+  <si>
+    <t>Decimal/roman/alpha/bullets, custom prefixes/suffixes, start, restart, continuation, multilevel, numId/abstractNum/ilvl, indentation.</t>
+  </si>
+  <si>
+    <t>tests/test_docx_numbering.py</t>
+  </si>
+  <si>
+    <t>Done so far: top-level list number format (decimal/roman/letters), start value (lvl start + lvlOverride/startOverride) and continuation across interrupting paragraphs imported into Element.numbering and written back to Word (per-level formats, startOverride) and PDF; empty numbered items keep counting. Reported, not kept: custom labels ('Чл. 1.', '(a)'), multi-level labels ('1.1'), numbered headings baked into text. Remaining: prefixes/suffixes, multilevel numbering model, restart semantics per level, indentation.</t>
+  </si>
+  <si>
+    <t>AUD-04</t>
+  </si>
+  <si>
+    <t>DOCX-017</t>
+  </si>
+  <si>
+    <t>Table engine</t>
+  </si>
+  <si>
+    <t>No forced header or Table Grid; widths, heights, margins, borders, shading, v-align, nested tables, repeated header rows, table styles.</t>
+  </si>
+  <si>
+    <t>From EDIT-011 (2026-09-27): add per-cell alignment and column widths to the model (the editor's cell align/colwidth, Word tcW/tblGrid, PDF colWidths); until then the editor names them as not kept.</t>
+  </si>
+  <si>
+    <t>DOCX-018</t>
+  </si>
+  <si>
+    <t>Images</t>
+  </si>
+  <si>
+    <t>Alt text exported; crop, rotation, anchor, wrap, position preserved; WEBP converted on export.</t>
+  </si>
+  <si>
+    <t>Alt text + title now exported (docPr descr/title) with DOCX-001; crop, rotation, WEBP still open.</t>
+  </si>
+  <si>
+    <t>DOCX-019</t>
+  </si>
+  <si>
+    <t>Drawings and text boxes preserved</t>
+  </si>
+  <si>
+    <t>Anchored drawings, text boxes, shapes kept even when not editable.</t>
+  </si>
+  <si>
+    <t>DOCX-028: text boxes and drawings in unchanged paragraphs are copied as they are (grouped with their anchor paragraph).</t>
+  </si>
+  <si>
+    <t>DOCX-020</t>
+  </si>
+  <si>
+    <t>Fields</t>
+  </si>
+  <si>
+    <t>Code/result/relationship; header STYLEREF/DATE live; TOC kept; CITATION/BIBLIOGRAPHY sources preserved; no 'Invalid source specified.'</t>
+  </si>
+  <si>
+    <t>backend/parsers, export</t>
+  </si>
+  <si>
+    <t>DOCX-028: field codes in unchanged blocks are copied as they are; a field spanning paragraphs is never copied half (self-contained check).</t>
+  </si>
+  <si>
+    <t>AUD-18</t>
+  </si>
+  <si>
+    <t>DOCX-021</t>
+  </si>
+  <si>
+    <t>Comment threads</t>
+  </si>
+  <si>
+    <t>Replies, resolved state, authors, ranges preserved (commentsExtended, people).</t>
+  </si>
+  <si>
+    <t>AUD-06</t>
+  </si>
+  <si>
+    <t>DOCX-022</t>
+  </si>
+  <si>
+    <t>Tracked changes preserved</t>
+  </si>
+  <si>
+    <t>Not silently accepted; explicit choice.</t>
+  </si>
+  <si>
+    <t>DOCX-028: blocks holding tracked changes are never copied (always written anew, accepted), so this task's explicit choice is still needed.</t>
+  </si>
+  <si>
+    <t>DOCX-023</t>
+  </si>
+  <si>
+    <t>Content controls preserved</t>
+  </si>
+  <si>
+    <t>w:sdt of every kind kept with its properties.</t>
+  </si>
+  <si>
+    <t>DOCX-028: content controls in unchanged blocks are copied with their properties (E2E proves it through the editor); written anew they are unwrapped (reported lossy at import).</t>
+  </si>
+  <si>
+    <t>DOCX-024</t>
+  </si>
+  <si>
+    <t>Real footnotes and endnotes</t>
+  </si>
+  <si>
+    <t>Notes stay notes on export.</t>
+  </si>
+  <si>
+    <t>DOCX-025</t>
+  </si>
+  <si>
+    <t>Hidden text stays hidden</t>
+  </si>
+  <si>
+    <t>Imported hidden text is kept hidden, shown only on request.</t>
+  </si>
+  <si>
+    <t>MarkType.HIDDEN (appended; no existing mark order changes). Importer resolves w:vanish as Word does: run, character style, paragraph style (the default paragraph style when none), docDefaults; webHidden stays visible; an explicit vanish=0 shows text in a hidden style. The detector uses the default paragraph style the same way and names hidden text as kept hidden (DETECTED_PRESERVED, not a content change). Editor: non-inclusive hidden mark (editor/hiddenText.ts; Word's display:none paste stays hidden), hidden by CSS unless .show-hidden; status bar 'Show hidden text (N words)' toggles it and re-paginates; the Structure panel leaves hidden text out of headings. Word export writes w:vanish (copied blocks keep theirs); PDF doesn't print hidden runs, export.pdf.hidden_text names the word count, and the PDF content check compares visible words (document_words(visible_only=True)); Word-side checks count hidden text on both sides. Golden 02-rich-text gained a hidden sentence (editor round trip in Vitest).</t>
+  </si>
+  <si>
+    <t>backend 876 passed/1 skipped (tests/test_hidden_text.py 7: import resolution, default paragraph style, report, upload + content check + editor save, Word export round trip, PDF text + note + check); Vitest 125 (editor/hiddenText.test.tsx 6, golden round trip of 02); Playwright 22 (e2e/hidden-text.spec.ts: hidden until asked, dotted line when shown, vanish in the Word export); tsc + eslint clean</t>
+  </si>
+  <si>
+    <t>backend/parsers, frontend</t>
+  </si>
+  <si>
+    <t>7d1af86</t>
+  </si>
+  <si>
+    <t>DOCX-028: vanish survives in unchanged blocks only; the model still shows hidden text as ordinary text - next task.</t>
+  </si>
+  <si>
+    <t>DOCX-026</t>
+  </si>
+  <si>
+    <t>Hyperlink policy and no silent autolink</t>
+  </si>
+  <si>
+    <t>Plain-text addresses not turned into links by default; file:/UNC reported.</t>
+  </si>
+  <si>
+    <t>tests/test_docx_detect.py::test_unsafe_links_and_spacing_paragraphs_are_reported</t>
+  </si>
+  <si>
+    <t>Done: links to unsafe addresses (javascript:, file:, UNC...) are kept as plain text and reported (docx.link.unsafe); plain-text addresses turned into links are reported (docx.autolink). Remaining: stop autolinking by default (a setting), per the task.</t>
+  </si>
+  <si>
+    <t>AUD-03,AUD-13</t>
+  </si>
+  <si>
+    <t>FMT-004</t>
+  </si>
+  <si>
+    <t>Render-spec defaults respect the source</t>
+  </si>
+  <si>
+    <t>Imported Word styles are not overridden by defaults (headings not forced bold).</t>
+  </si>
+  <si>
+    <t>backend/formatting</t>
+  </si>
+  <si>
+    <t>TEST-020</t>
+  </si>
+  <si>
+    <t>Word-authored fixtures in the repository</t>
+  </si>
+  <si>
+    <t>20 synthetic Word-authored fixtures, scrubbed of identifying metadata.</t>
+  </si>
+  <si>
+    <t>backend/tests/fixtures/word</t>
+  </si>
+  <si>
+    <t>TEST-021</t>
+  </si>
+  <si>
+    <t>Expected-loss manifests in CI</t>
+  </si>
+  <si>
+    <t>expected-loss.json per fixture; CI compares actual vs expected.</t>
+  </si>
+  <si>
+    <t>TEST-022</t>
+  </si>
+  <si>
+    <t>True fidelity test</t>
+  </si>
+  <si>
+    <t>SOURCE -&gt; import -&gt; format -&gt; editor save -&gt; export -&gt; reimport -&gt; compare SOURCE vs RESULT: content, formatting, metadata, structure separately.</t>
+  </si>
+  <si>
+    <t>TEST-023</t>
+  </si>
+  <si>
+    <t>Independent validation</t>
+  </si>
+  <si>
+    <t>OOXML schema validation, Word when available, docx2python; pdftotext/PyMuPDF for PDF.</t>
+  </si>
+  <si>
+    <t>app/export/package_check.py: an independent package check (zip read directly): well-formed parts, content types, relationships resolving, relationship ids used, defined styles/lists/comments. Found a real defect on first run (python-docx's add_comment refers to an undefined CommentReference style; exports now define it). Every golden export passes, fresh and into its original.</t>
+  </si>
+  <si>
+    <t>tests/test_package_check.py (13)</t>
+  </si>
+  <si>
+    <t>The docx skill's XSD validator needs defusedxml (not installed; installing needs a download) - schema-level validation remains open.</t>
+  </si>
+  <si>
+    <t>DOCX-027</t>
+  </si>
+  <si>
+    <t>Importer builds nested blocks</t>
+  </si>
+  <si>
+    <t>Use TableCell.blocks / ListItem.blocks on import: pictures, lists (with bullets) and nested tables inside cells, pictures inside list items - instead of dropping or flattening them.</t>
+  </si>
+  <si>
+    <t>AUD-01,AUD-03,AUD-08</t>
+  </si>
+  <si>
+    <t>DOCX-028</t>
+  </si>
+  <si>
+    <t>Unchanged blocks keep their original XML in Word exports</t>
+  </si>
+  <si>
+    <t>Blocks the user didn't change are written back as their original XML (fields, content controls, run-level formatting the model can't hold, bookmarks), changed ones regenerated; needs block provenance from the importer and fingerprints.</t>
+  </si>
+  <si>
+    <t>Importer records each top-level element's body children (Element.sourceBlocks: list items, drop caps, derived page breaks); an upload with a kept file stamps content+look fingerprints (Element.sourceHash, app/export/provenance.py: own/kind/body/nested resolved styles; page breaks have no look). docx_export._copy_plan groups elements with their children (uncovered children join the group before) and copies a group verbatim when every element is unchanged, together and in original order, children contiguous, XML self-contained (no tracked changes/note refs/altChunk; balanced fields, bookmarks, comment ranges); everything else is written anew. Provenance is server-side (keep_provenance on PUT /content). Page setup now runs after the body: changed size/margins reach every kept section (orientation kept, landscape turned), a changed main header is rewritten where Word shows it (link to previous), page numbers left out/asked for apply to every section. export.docx.section_lost (LOSSY) names sections lost with a changed paragraph; import report: earlier sections' setup/headers kept while unchanged; PDF names them Word-only. All 13 golden documents stamped + exported into their originals: sound packages, content verified (12-complex rewrites only the footnote paragraph and the note, by design).</t>
+  </si>
+  <si>
+    <t>backend 869 passed/1 skipped (tests/test_original_blocks.py 26 incl. 13 golden; test_source_package.py rewritten claims with export proof; test_golden_documents.py 13 files); Vitest 119 (editor round trip of 13-kept-blocks); Playwright 21 (e2e/kept-blocks.spec.ts: edit in the real editor, untouched paragraphs keep content control, double underline, landscape section); tsc + eslint clean</t>
+  </si>
+  <si>
+    <t>c8c2d27</t>
+  </si>
+  <si>
+    <t>Follow-up of DOCX-011 (package-level patch writer).; Known limit: any restyle (template, instruction) changes the body look, so every block but page breaks is written anew; follow-up DOCX-029. Sections survive only with their ending paragraph until DOCX-015 models them.</t>
+  </si>
+  <si>
+    <t>DOCX-029</t>
+  </si>
+  <si>
+    <t>Restyled blocks keep their original XML where nothing conflicts</t>
+  </si>
+  <si>
+    <t>After a template or instruction restyles a kind of block, copy a block's original XML when its paragraph style is the Word style the export rewrites for that kind and its direct formatting (pPr/rPr) sets none of the properties that changed; today any restyle writes every block anew (content controls, double underline etc. then lost, as the import report says).</t>
+  </si>
+  <si>
+    <t>Found while finishing DOCX-028: the look is part of the fingerprint so the export never shows a stale look.</t>
+  </si>
+  <si>
+    <t>FID-007</t>
+  </si>
+  <si>
+    <t>Reports follow the Word copy</t>
+  </si>
+  <si>
+    <t>With the original kept, the import report names what lives in blocks as kept in the Word export while the paragraph is unchanged, and an export that writes such a block anew names what it lost; a copy never brings back a link the app doesn't allow.</t>
+  </si>
+  <si>
+    <t>fidelity/imports.py KEPT_WHILE_UNCHANGED (content controls, text boxes, charts/shapes/SmartArt, objects, picture crop/rotation/floating, drop caps, empty paragraphs, approximated underlines, character scale, text effects, RTL) -&gt; detected_not_editable 'kept while the paragraph isn't changed or restyled'; docx_export._copy_plan returns rewritten groups, _lost_in/_rewritten_losses -&gt; export.docx.rewritten_blocks (LOSSY, count, kinds incl. proofing exclusions); _safe_links keeps groups with unsafe links (relationships or HYPERLINK fields) from being copied; the PDF's Word-only note covers the features.</t>
+  </si>
+  <si>
+    <t>tests/test_copy_reports.py (6): kept while unchanged at import, rewritten losses named (content controls, stretched text), unsafe javascript: link never copied back, PDF word-only; backend 894 passed/1 skipped; Playwright 22</t>
+  </si>
+  <si>
+    <t>Generalises DOCX-028's section handling (export.docx.section_lost) to everything the model doesn't hold inside blocks.</t>
+  </si>
+  <si>
+    <t>SEC-010</t>
+  </si>
+  <si>
+    <t>Malformed DOCX -&gt; safe 4xx</t>
+  </si>
+  <si>
+    <t>XML/zip/structure errors map to invalid_file; fuzz corpus shows no 500.</t>
+  </si>
+  <si>
+    <t>AUD-12</t>
+  </si>
+  <si>
+    <t>SEC-011</t>
+  </si>
+  <si>
+    <t>Malformed PDF -&gt; safe 4xx</t>
+  </si>
+  <si>
+    <t>Verified with a fuzz corpus.</t>
+  </si>
+  <si>
+    <t>SEC-012</t>
+  </si>
+  <si>
+    <t>Image resource limits</t>
+  </si>
+  <si>
+    <t>Compressed and decompressed size, pixel count, width, height, images per document, total bytes, format allowlist; rejected before rasterisation.</t>
+  </si>
+  <si>
+    <t>backend/security</t>
+  </si>
+  <si>
+    <t>AUD-09</t>
+  </si>
+  <si>
+    <t>SEC-013</t>
+  </si>
+  <si>
+    <t>PDF bombs, huge XML, decompression limits</t>
+  </si>
+  <si>
+    <t>Reviewed and tested limits.</t>
+  </si>
+  <si>
+    <t>SEC-014</t>
+  </si>
+  <si>
+    <t>Href policy</t>
+  </si>
+  <si>
+    <t>Server-side scheme allowlist; javascript:/data:/vbscript:/file: never exported as active links.</t>
+  </si>
+  <si>
+    <t>backend/models, export</t>
+  </si>
+  <si>
+    <t>AUD-13</t>
+  </si>
+  <si>
+    <t>SEC-015</t>
+  </si>
+  <si>
+    <t>Field instruction allowlist</t>
+  </si>
+  <si>
+    <t>No DDE/INCLUDETEXT/INCLUDEPICTURE/external fields accepted from clients or exported.</t>
+  </si>
+  <si>
+    <t>SEC-016</t>
+  </si>
+  <si>
+    <t>External relationships policy</t>
+  </si>
+  <si>
+    <t>No arbitrary external targets in exports.</t>
+  </si>
+  <si>
+    <t>SEC-017</t>
+  </si>
+  <si>
+    <t>Malicious SVG</t>
+  </si>
+  <si>
+    <t>Verified refused everywhere.</t>
+  </si>
+  <si>
+    <t>SEC-018</t>
+  </si>
+  <si>
+    <t>Prompt injection / AI output abuse</t>
+  </si>
+  <si>
+    <t>Tests with hostile documents; outputs validated.</t>
+  </si>
+  <si>
+    <t>Hostile-document tests: the document can't close its fence; out-of-bounds answers refused and fall back; an instruction steered by the document deletes nothing (proposals only) and a CSS break-out value is dropped; style-analysis flags on unknown elements dropped (see AI-009).</t>
+  </si>
+  <si>
+    <t>tests/test_prompt_injection.py</t>
+  </si>
+  <si>
+    <t>SEC-019</t>
+  </si>
+  <si>
+    <t>Error envelope audit</t>
+  </si>
+  <si>
+    <t>Every error {code, message, details, request_id}; no stack traces to users.</t>
+  </si>
+  <si>
+    <t>backend/api</t>
+  </si>
+  <si>
+    <t>SEC-020</t>
+  </si>
+  <si>
+    <t>CSP without 'unsafe-inline' scripts</t>
+  </si>
+  <si>
+    <t>Nonce-based CSP for the Next.js app.</t>
+  </si>
+  <si>
+    <t>TEST-030</t>
+  </si>
+  <si>
+    <t>Security regression suite</t>
+  </si>
+  <si>
+    <t>Fuzz corpus, pixel bombs, href/field policy, IDOR, CSRF.</t>
+  </si>
+  <si>
+    <t>SEC-010,SEC-012,SEC-014,SEC-015</t>
+  </si>
+  <si>
+    <t>AUD-09,AUD-12,AUD-13</t>
+  </si>
+  <si>
+    <t>SEC-021</t>
+  </si>
+  <si>
+    <t>Sensitivity-label metadata in the public repository</t>
+  </si>
+  <si>
+    <t>корекции.docx (committed in 5f2bf9e, pushed) carries 8 MSIP_Label_* custom properties incl. the organisation's tenant SiteId (label: Microsoft default 'General' family, no content marking). Options: leave; scrub the file in a new commit (HEAD only); purge from history (force-push).</t>
+  </si>
+  <si>
+    <t>repository history</t>
+  </si>
+  <si>
+    <t>Needs Boril: the choice involves his organisation's label and possibly rewriting pushed history. The tracker tools now strip MSIP labels on every write; the pre-push scan flags them.</t>
+  </si>
+  <si>
+    <t>SEC-022</t>
+  </si>
+  <si>
+    <t>Formatting rule values can't break out of a style</t>
+  </si>
+  <si>
+    <t>A rule value reaches the editor's style attribute, Word and PDF styles as text. The element-style and page-setting endpoints accepted any string (e.g. 'center;background-image:url(...)'), the AI instruction path too (FMT-005): CSS injection into every viewer's editor.</t>
+  </si>
+  <si>
+    <t>app/formatting/values.py: clean_rule_value per property (the StyleSystem's limits: choices, true/false, one safe font name, renderable colours, bounded numbers with known units, header/footer text &lt;=500). Refused with 422 by the element-style and page-setting endpoints (schemas RuleValue); instruction rules and set_style operations with such values dropped (FMT-005), validate_operations refuses them; stored rules no renderer can use are skipped at resolve (engine._usable) so old documents can't carry them either. All 177 default/template rules pass unchanged.</t>
+  </si>
+  <si>
+    <t>tests/test_rule_values.py (34 cases incl. API 422, stored-rule skip, instruction drop)</t>
+  </si>
+  <si>
+    <t>Found 2026-09-27 while mapping editor alignment (EDIT-008); probe confirmed the raw value in resolvedStyles.</t>
+  </si>
+  <si>
+    <t>PERF-001</t>
+  </si>
+  <si>
+    <t>Linear DOCX table export</t>
+  </si>
+  <si>
+    <t>500x8 table under a recorded threshold (baseline 321 s).</t>
+  </si>
+  <si>
+    <t>AUD-10</t>
+  </si>
+  <si>
+    <t>PERF-002</t>
+  </si>
+  <si>
+    <t>Benchmarks recorded</t>
+  </si>
+  <si>
+    <t>Baseline and current measurements in the PERFORMANCE sheet.</t>
+  </si>
+  <si>
+    <t>tests/perf</t>
+  </si>
+  <si>
+    <t>PERF-003</t>
+  </si>
+  <si>
+    <t>Delta autosave</t>
+  </si>
+  <si>
+    <t>Change-aware patches with a threshold strategy; whole document only when needed.</t>
+  </si>
+  <si>
+    <t>frontend/editor, backend/api</t>
+  </si>
+  <si>
+    <t>PERF-004</t>
+  </si>
+  <si>
+    <t>Bounded, compressed version history</t>
+  </si>
+  <si>
+    <t>Editor history separate from persisted versions; compression/deltas; asset references.</t>
+  </si>
+  <si>
+    <t>PERF-005</t>
+  </si>
+  <si>
+    <t>Editor at 5k-12k blocks</t>
+  </si>
+  <si>
+    <t>Typing latency measured and improved.</t>
+  </si>
+  <si>
+    <t>PERF-006</t>
+  </si>
+  <si>
+    <t>JSON without ASCII escaping</t>
+  </si>
+  <si>
+    <t>Document JSON stored and sent as UTF-8.</t>
+  </si>
+  <si>
+    <t>backend/db</t>
+  </si>
+  <si>
+    <t>PERF-007</t>
+  </si>
+  <si>
+    <t>Safe size limits recorded</t>
+  </si>
+  <si>
+    <t>User-facing maximum sizes, job timeouts, resource ceilings documented and enforced.</t>
+  </si>
+  <si>
+    <t>backend/config</t>
+  </si>
+  <si>
+    <t>AUD-09,AUD-10</t>
+  </si>
+  <si>
+    <t>ACCT-001</t>
+  </si>
+  <si>
+    <t>E-mail sender abstraction</t>
+  </si>
+  <si>
+    <t>SMTP provider + development outbox; no secrets in logs.</t>
+  </si>
+  <si>
+    <t>AUD-14</t>
+  </si>
+  <si>
+    <t>ACCT-002</t>
+  </si>
+  <si>
+    <t>Password reset</t>
+  </si>
+  <si>
+    <t>Single-use, expiring, hashed tokens; rate-limited; no account enumeration.</t>
+  </si>
+  <si>
+    <t>backend/api, frontend</t>
+  </si>
+  <si>
+    <t>ACCT-003</t>
+  </si>
+  <si>
+    <t>E-mail verification</t>
+  </si>
+  <si>
+    <t>Verification tokens and state.</t>
+  </si>
+  <si>
+    <t>ACCT-004</t>
+  </si>
+  <si>
+    <t>Password change</t>
+  </si>
+  <si>
+    <t>Current password required; other sessions revoked.</t>
+  </si>
+  <si>
+    <t>ACCT-005</t>
+  </si>
+  <si>
+    <t>Account deletion</t>
+  </si>
+  <si>
+    <t>Cascading policy: documents, versions, assets, exports, sessions, jobs, usage.</t>
+  </si>
+  <si>
+    <t>ACCT-006</t>
+  </si>
+  <si>
+    <t>Session revocation and cleanup</t>
+  </si>
+  <si>
+    <t>Sign out everywhere; expired/revoked session sweep.</t>
+  </si>
+  <si>
+    <t>ACCT-007</t>
+  </si>
+  <si>
+    <t>Suspicious login handling</t>
+  </si>
+  <si>
+    <t>Lockout and notification strategy.</t>
+  </si>
+  <si>
+    <t>PLAN-001</t>
+  </si>
+  <si>
+    <t>Usage units</t>
+  </si>
+  <si>
+    <t>Documents, exports, PDF pages, OCR pages, translation characters, AI operations, storage, batch jobs.</t>
+  </si>
+  <si>
+    <t>backend/billing</t>
+  </si>
+  <si>
+    <t>AUD-11</t>
+  </si>
+  <si>
+    <t>PLAN-002</t>
+  </si>
+  <si>
+    <t>Configurable plan defaults</t>
+  </si>
+  <si>
+    <t>Free/Pro/Business initial hypotheses as configuration, never hardcoded.</t>
+  </si>
+  <si>
+    <t>PLAN-003</t>
+  </si>
+  <si>
+    <t>Atomic entitlement checks</t>
+  </si>
+  <si>
+    <t>Reservation/locking; concurrency test proves limits hold.</t>
+  </si>
+  <si>
+    <t>PLAN-004</t>
+  </si>
+  <si>
+    <t>Stripe flows review</t>
+  </si>
+  <si>
+    <t>Checkout, portal, upgrade, downgrade, cancel, renewal, failed payment, webhook idempotency.</t>
+  </si>
+  <si>
+    <t>PLAN-005</t>
+  </si>
+  <si>
+    <t>Storage metering including history</t>
+  </si>
+  <si>
+    <t>History and autosave growth counted.</t>
+  </si>
+  <si>
+    <t>AUD-11,AUD-16</t>
+  </si>
+  <si>
+    <t>PDF-010</t>
+  </si>
+  <si>
+    <t>Geometry-aware PDF parser</t>
+  </si>
+  <si>
+    <t>Chars, fonts, sizes, colours, lines, rectangles, images, links, annotations, outlines, forms, metadata, rotation, page boxes.</t>
+  </si>
+  <si>
+    <t>backend/parsers/pdf</t>
+  </si>
+  <si>
+    <t>PDF-011</t>
+  </si>
+  <si>
+    <t>Page classifier</t>
+  </si>
+  <si>
+    <t>TEXT / SCANNED / HYBRID per page with evidence.</t>
+  </si>
+  <si>
+    <t>PDF-012</t>
+  </si>
+  <si>
+    <t>PDF inspection report</t>
+  </si>
+  <si>
+    <t>What the parser found, per page.</t>
+  </si>
+  <si>
+    <t>P2E-001</t>
+  </si>
+  <si>
+    <t>Layout primitives where PDF needs them</t>
+  </si>
+  <si>
+    <t>Page, block, bbox, rotation, confidence, provenance.</t>
+  </si>
+  <si>
+    <t>P2E-002</t>
+  </si>
+  <si>
+    <t>Structure reconstruction</t>
+  </si>
+  <si>
+    <t>Reading order, lines, paragraphs, headings, lists, captions, header/footer bands, columns.</t>
+  </si>
+  <si>
+    <t>backend/pdf</t>
+  </si>
+  <si>
+    <t>P2E-003</t>
+  </si>
+  <si>
+    <t>Images with position</t>
+  </si>
+  <si>
+    <t>Extracted images kept with bbox.</t>
+  </si>
+  <si>
+    <t>P2E-004</t>
+  </si>
+  <si>
+    <t>Tables from PDF</t>
+  </si>
+  <si>
+    <t>Ruling lines and alignment.</t>
+  </si>
+  <si>
+    <t>P2E-005</t>
+  </si>
+  <si>
+    <t>Confidence and conversion report</t>
+  </si>
+  <si>
+    <t>Per element confidence; issues reported; never silent removal.</t>
+  </si>
+  <si>
+    <t>P2E-006</t>
+  </si>
+  <si>
+    <t>OCR provider abstraction</t>
+  </si>
+  <si>
+    <t>Interface (text, confidence, bbox, page, language/script); implementation(s); OCR output untrusted.</t>
+  </si>
+  <si>
+    <t>backend/ocr</t>
+  </si>
+  <si>
+    <t>P2E-007</t>
+  </si>
+  <si>
+    <t>Imported-from-PDF version and UX</t>
+  </si>
+  <si>
+    <t>Editable document vs layout-focused choice; confidence shown.</t>
+  </si>
+  <si>
+    <t>frontend, backend</t>
+  </si>
+  <si>
+    <t>P2E-008</t>
+  </si>
+  <si>
+    <t>PDF fixtures and tests</t>
+  </si>
+  <si>
+    <t>Text, scanned, hybrid, tables, columns, multilingual.</t>
+  </si>
+  <si>
+    <t>P2E-020</t>
+  </si>
+  <si>
+    <t>Layout-preserving architecture</t>
+  </si>
+  <si>
+    <t>Frames/anchors model hooks and design doc.</t>
+  </si>
+  <si>
+    <t>docs, backend/models</t>
+  </si>
+  <si>
+    <t>PDF-020</t>
+  </si>
+  <si>
+    <t>PDF page operations service</t>
+  </si>
+  <si>
+    <t>Reorder, rotate, delete, duplicate, extract, split, merge as a separate service.</t>
+  </si>
+  <si>
+    <t>TRAN-001</t>
+  </si>
+  <si>
+    <t>Segments and tag protocol</t>
+  </si>
+  <si>
+    <t>Segments keep element/run ids, marks, placeholders; never one giant string.</t>
+  </si>
+  <si>
+    <t>backend/translation</t>
+  </si>
+  <si>
+    <t>TRAN-002</t>
+  </si>
+  <si>
+    <t>TranslationProvider abstraction</t>
+  </si>
+  <si>
+    <t>AI provider implementation + deterministic test provider.</t>
+  </si>
+  <si>
+    <t>TRAN-003</t>
+  </si>
+  <si>
+    <t>Translation validation</t>
+  </si>
+  <si>
+    <t>Tags, numbers, units, dates, percentages, identifiers, glossary terms.</t>
+  </si>
+  <si>
+    <t>TRAN-004</t>
+  </si>
+  <si>
+    <t>Glossary and terminology lock</t>
+  </si>
+  <si>
+    <t>Source/target term, domain, locked, case-sensitive.</t>
+  </si>
+  <si>
+    <t>backend/translation, db</t>
+  </si>
+  <si>
+    <t>TRAN-005</t>
+  </si>
+  <si>
+    <t>Selection/paragraph/block translation proposals</t>
+  </si>
+  <si>
+    <t>Preview; accept/reject; undo.</t>
+  </si>
+  <si>
+    <t>TRAN-003,REV-001</t>
+  </si>
+  <si>
+    <t>TRAN-006</t>
+  </si>
+  <si>
+    <t>Whole-document translated version</t>
+  </si>
+  <si>
+    <t>Source kept; translated copy linked.</t>
+  </si>
+  <si>
+    <t>TRAN-007</t>
+  </si>
+  <si>
+    <t>Language, script, direction metadata</t>
+  </si>
+  <si>
+    <t>Auto-detect + manual override.</t>
+  </si>
+  <si>
+    <t>TRAN-008</t>
+  </si>
+  <si>
+    <t>Translation UX</t>
+  </si>
+  <si>
+    <t>Toolbar/context Translate, target language, preview, accept/reject; 'AI-assisted translation - review required'.</t>
+  </si>
+  <si>
+    <t>TRAN-009</t>
+  </si>
+  <si>
+    <t>Translation metering</t>
+  </si>
+  <si>
+    <t>Translation characters as a usage unit.</t>
+  </si>
+  <si>
+    <t>TRAN-010</t>
+  </si>
+  <si>
+    <t>Translation tests</t>
+  </si>
+  <si>
+    <t>Formatting preservation, validation, versions.</t>
+  </si>
+  <si>
+    <t>FONT-001</t>
+  </si>
+  <si>
+    <t>Font catalogue with Unicode coverage</t>
+  </si>
+  <si>
+    <t>fontTools cmap coverage per script, metrics, embeddability.</t>
+  </si>
+  <si>
+    <t>backend/fonts</t>
+  </si>
+  <si>
+    <t>AUD-17</t>
+  </si>
+  <si>
+    <t>FONT-002</t>
+  </si>
+  <si>
+    <t>FontResolver</t>
+  </si>
+  <si>
+    <t>Script segmentation, coverage, fallback chain, embedding, RTL; deterministic first, AI suggestion validated.</t>
+  </si>
+  <si>
+    <t>FONT-003</t>
+  </si>
+  <si>
+    <t>Multilingual PDF rendering</t>
+  </si>
+  <si>
+    <t>Shaping for Arabic/Hebrew/Devanagari, bidi, CJK fonts, emoji handled gracefully.</t>
+  </si>
+  <si>
+    <t>FONT-004</t>
+  </si>
+  <si>
+    <t>DOCX per-script fonts</t>
+  </si>
+  <si>
+    <t>w:rFonts ascii/hAnsi/eastAsia/cs, w:lang, rtl/bidi.</t>
+  </si>
+  <si>
+    <t>FONT-005</t>
+  </si>
+  <si>
+    <t>Editor fallback stacks</t>
+  </si>
+  <si>
+    <t>CSS stacks from the resolver.</t>
+  </si>
+  <si>
+    <t>FONT-006</t>
+  </si>
+  <si>
+    <t>Multilingual tests</t>
+  </si>
+  <si>
+    <t>Script matrix x editor/DOCX/PDF with pdftotext and rendering.</t>
+  </si>
+  <si>
+    <t>FMT-001</t>
+  </si>
+  <si>
+    <t>Style extraction completeness</t>
+  </si>
+  <si>
+    <t>Page setup, margins, fonts, headings, lists, tables, captions, headers/footers, spacing, numbering, colours.</t>
+  </si>
+  <si>
+    <t>FMT-002</t>
+  </si>
+  <si>
+    <t>Semantic mapping validated</t>
+  </si>
+  <si>
+    <t>AI classifies/maps, engine applies; validation.</t>
+  </si>
+  <si>
+    <t>FMT-003</t>
+  </si>
+  <si>
+    <t>Before/after for Format by Example</t>
+  </si>
+  <si>
+    <t>Preview before saving a template.</t>
+  </si>
+  <si>
+    <t>FMT-005</t>
+  </si>
+  <si>
+    <t>Rule value validation</t>
+  </si>
+  <si>
+    <t>Instruction-path values validated before reaching CSS/export.</t>
+  </si>
+  <si>
+    <t>Instruction rules and set_style operations go through values.clean_rule_value: invalid ones dropped, normalised values stored (see SEC-022).</t>
+  </si>
+  <si>
+    <t>tests/test_rule_values.py::test_instructions_cannot_carry_such_values</t>
+  </si>
+  <si>
+    <t>HLTH-001</t>
+  </si>
+  <si>
+    <t>Health 2.0 checks</t>
+  </si>
+  <si>
+    <t>Alt text, hidden text, mixed language, unsupported features, section inconsistency, broken lists, empty paragraphs, layout anomalies, duplicated formatting, broken links.</t>
+  </si>
+  <si>
+    <t>HLTH-002</t>
+  </si>
+  <si>
+    <t>Deterministic fixes with preview</t>
+  </si>
+  <si>
+    <t>Fix proposals through the change model.</t>
+  </si>
+  <si>
+    <t>HLTH-003</t>
+  </si>
+  <si>
+    <t>AI explanations only</t>
+  </si>
+  <si>
+    <t>AI explains issues; never scores.</t>
+  </si>
+  <si>
+    <t>REV-002</t>
+  </si>
+  <si>
+    <t>Review Changes UI</t>
+  </si>
+  <si>
+    <t>Categories FORMAT/STRUCTURE/CONTENT/METADATA/PRESERVATION/TRANSLATION.</t>
+  </si>
+  <si>
+    <t>REV-003</t>
+  </si>
+  <si>
+    <t>Content changes need acceptance</t>
+  </si>
+  <si>
+    <t>Enforced server-side.</t>
+  </si>
+  <si>
+    <t>backend</t>
+  </si>
+  <si>
+    <t>REV-004</t>
+  </si>
+  <si>
+    <t>Repair</t>
+  </si>
+  <si>
+    <t>Detected issue, proposed fix, preview, apply.</t>
+  </si>
+  <si>
+    <t>REV-005</t>
+  </si>
+  <si>
+    <t>Clean copy</t>
+  </si>
+  <si>
+    <t>Explicit: remove comments, accept tracked changes, remove hidden text, remove metadata, normalise formatting.</t>
+  </si>
+  <si>
+    <t>FEAT-001</t>
+  </si>
+  <si>
+    <t>Batch formatting</t>
+  </si>
+  <si>
+    <t>One template/reference over many documents as jobs.</t>
+  </si>
+  <si>
+    <t>backend/jobs</t>
+  </si>
+  <si>
+    <t>FEAT-002</t>
+  </si>
+  <si>
+    <t>Batch export</t>
+  </si>
+  <si>
+    <t>Many documents to a zip.</t>
+  </si>
+  <si>
+    <t>FEAT-003</t>
+  </si>
+  <si>
+    <t>Batch translation</t>
+  </si>
+  <si>
+    <t>After the translation MVP.</t>
+  </si>
+  <si>
+    <t>FEAT-010</t>
+  </si>
+  <si>
+    <t>Accessibility checker</t>
+  </si>
+  <si>
+    <t>Heading hierarchy, alt text, link labels, table headers, reading order, language, contrast.</t>
+  </si>
+  <si>
+    <t>FEAT-011</t>
+  </si>
+  <si>
+    <t>App accessibility fixes</t>
+  </si>
+  <si>
+    <t>Zero serious axe violations on main pages and the editor.</t>
+  </si>
+  <si>
+    <t>JOB-001</t>
+  </si>
+  <si>
+    <t>Job safety</t>
+  </si>
+  <si>
+    <t>idempotency_key, retry_count, timeout, cancellation, stuck detection, backoff, dead-letter.</t>
+  </si>
+  <si>
+    <t>STOR-001</t>
+  </si>
+  <si>
+    <t>Storage retention and deletion</t>
+  </si>
+  <si>
+    <t>Source files, exports, OCR artifacts: retention, deletion, access control, content types, size limits.</t>
+  </si>
+  <si>
+    <t>OBS-001</t>
+  </si>
+  <si>
+    <t>Metrics</t>
+  </si>
+  <si>
+    <t>Latency, failure rate, job/AI/export metrics without content.</t>
+  </si>
+  <si>
+    <t>AUD-15</t>
+  </si>
+  <si>
+    <t>OBS-002</t>
+  </si>
+  <si>
+    <t>Operation and job IDs in logs</t>
+  </si>
+  <si>
+    <t>Request, operation and job IDs everywhere.</t>
+  </si>
+  <si>
+    <t>OBS-003</t>
+  </si>
+  <si>
+    <t>Operations data</t>
+  </si>
+  <si>
+    <t>Failed jobs, processing failures, usage spikes, AI/export failures, storage, abuse - minimal admin API.</t>
+  </si>
+  <si>
+    <t>INFRA-010</t>
+  </si>
+  <si>
+    <t>Deployment verified</t>
+  </si>
+  <si>
+    <t>Docker images build and start; Postgres, Redis, storage, worker, frontend, backend.</t>
+  </si>
+  <si>
+    <t>docker, CI</t>
+  </si>
+  <si>
+    <t>INFRA-011</t>
+  </si>
+  <si>
+    <t>CI gates</t>
+  </si>
+  <si>
+    <t>Backend, frontend, E2E, lint, typecheck, build, migrations, security audit, document fidelity tests.</t>
+  </si>
+  <si>
+    <t>.github/workflows</t>
+  </si>
+  <si>
+    <t>AUD-15,AUD-20</t>
+  </si>
+  <si>
+    <t>TEST-040</t>
+  </si>
+  <si>
+    <t>Playwright workflow coverage</t>
+  </si>
+  <si>
+    <t>The 24 workflows of the brief.</t>
+  </si>
+  <si>
+    <t>TEST-041</t>
+  </si>
+  <si>
+    <t>Performance gates</t>
+  </si>
+  <si>
+    <t>Regression thresholds relative to baseline.</t>
+  </si>
+  <si>
+    <t>TEST-043</t>
+  </si>
+  <si>
+    <t>Browser matrix</t>
+  </si>
+  <si>
+    <t>Chromium, Firefox, WebKit.</t>
+  </si>
+  <si>
+    <t>TEST-006</t>
+  </si>
+  <si>
+    <t>E2E backend removes its temp directory</t>
+  </si>
+  <si>
+    <t>scripts/e2e_server.py leaves %TEMP%/smartdoc-e2e-* behind after every Playwright run (10 found on 2026-09-27).</t>
+  </si>
+  <si>
+    <t>backend/scripts/e2e_server.py</t>
+  </si>
+  <si>
+    <t>DOCS-010</t>
+  </si>
+  <si>
+    <t>final-production-readiness.md</t>
+  </si>
+  <si>
+    <t>The 16-section final report.</t>
+  </si>
+  <si>
+    <t>DOCS-011</t>
+  </si>
+  <si>
+    <t>Documentation tree</t>
+  </si>
+  <si>
+    <t>docs/{architecture,document-model,docx,pdf,translation,ai,formatting,security,testing,deployment,billing,operations}.</t>
+  </si>
+  <si>
+    <t>Started with Phase 1: docs/document-model, docs/architecture/fidelity.md, docs/docx, docs/formatting, docs/security, docs/testing (each grounded in the code and tests of Phases 0-1). Remaining folders (pdf, translation, ai, deployment, billing, operations) as their phases land.; docs/ai/README.md added with Phase 2.</t>
+  </si>
+  <si>
+    <t>CRITICAL_FIXES — Audit findings and P0 tasks</t>
+  </si>
+  <si>
+    <t>The 20 findings of the 2026-09-26 audit (current known risks) with fix progress, then every P0 task. Report: https://claude.ai/artifact/WKskiyexTDLAHe1BfjvWR1 — a finding is RESOLVED when every linked fix task is DONE.</t>
+  </si>
+  <si>
+    <t>Findings</t>
+  </si>
+  <si>
+    <t>Resolved</t>
+  </si>
+  <si>
+    <t>Open</t>
+  </si>
+  <si>
+    <t>P0 tasks</t>
+  </si>
+  <si>
+    <t>P0 done</t>
+  </si>
+  <si>
+    <t>Audit findings (current known risks)</t>
+  </si>
+  <si>
+    <t>Finding ID</t>
+  </si>
+  <si>
+    <t>Progress</t>
+  </si>
+  <si>
+    <t>Finding</t>
+  </si>
+  <si>
+    <t>Fix Tasks</t>
+  </si>
+  <si>
+    <t>Active</t>
+  </si>
+  <si>
+    <t>Blocked/Failed</t>
+  </si>
+  <si>
+    <t>Editor save can discard nested blocks (lists, pictures, code, quotes inside cells/items)</t>
+  </si>
+  <si>
+    <t>EDIT-001,EDIT-002,EDIT-003,EDIT-005,EDIT-006</t>
+  </si>
+  <si>
+    <t>AI fidelity check misses omissions, negation removal, number changes, inserted text</t>
+  </si>
+  <si>
+    <t>AI-001,AI-002,AI-003,AI-004</t>
+  </si>
+  <si>
+    <t>Fixed in Phase 2 (AI-001..004): AI structure answers are checked token by token; any omission, negation removal, number/unit/date change, insertion, reordering, duplication or punctuation change is refused.</t>
+  </si>
+  <si>
+    <t>Import/export silently changes hidden text, numbering, section headers, metadata, alt text, structure</t>
+  </si>
+  <si>
+    <t>FID-002,DOCX-011,DOCX-013,DOCX-015,DOCX-025</t>
+  </si>
+  <si>
+    <t>List numbering changes ('Чл. 1.' -&gt; '1.', '(a)' -&gt; 'a.', start values)</t>
+  </si>
+  <si>
+    <t>Partly fixed in 622d9c1: list format/start/continuation kept; custom labels ('Чл. 1.', '(a)') and multi-level labels reported, not kept yet (DOCX-016).</t>
+  </si>
+  <si>
+    <t>AI instruction operations can delete/insert/move content without preview</t>
+  </si>
+  <si>
+    <t>AI-005,AI-006,AI-007,REV-003</t>
+  </si>
+  <si>
+    <t>Fixed in Phase 2 (AI-005..AI-007): an instruction's insert/delete/move is a proposal the user sees and accepts or rejects; nothing is deleted silently.</t>
+  </si>
+  <si>
+    <t>Content controls, metadata, comment threads, sensitivity information lost</t>
+  </si>
+  <si>
+    <t>DOCX-012,DOCX-021,DOCX-023</t>
+  </si>
+  <si>
+    <t>Image fidelity gaps: alt text, crop, rotation, formats</t>
+  </si>
+  <si>
+    <t>Table export changes header state, borders, alignment, widths, geometry</t>
+  </si>
+  <si>
+    <t>Large images cause huge memory consumption</t>
+  </si>
+  <si>
+    <t>SEC-012,SEC-013</t>
+  </si>
+  <si>
+    <t>Large tables have a performance problem</t>
+  </si>
+  <si>
+    <t>Plan limits have a concurrency race</t>
+  </si>
+  <si>
+    <t>Malformed DOCX leads to HTTP 500</t>
+  </si>
+  <si>
+    <t>SEC-010,SEC-019</t>
+  </si>
+  <si>
+    <t>Dangerous href/field instructions must be filtered</t>
+  </si>
+  <si>
+    <t>SEC-014,SEC-015,SEC-016</t>
+  </si>
+  <si>
+    <t>Account essentials missing: reset, verification, change, deletion</t>
+  </si>
+  <si>
+    <t>ACCT-002,ACCT-003,ACCT-004,ACCT-005</t>
+  </si>
+  <si>
+    <t>Operations/monitoring must be confirmed</t>
+  </si>
+  <si>
+    <t>OBS-001,OBS-002,INFRA-010</t>
+  </si>
+  <si>
+    <t>Whole-document autosave must be optimised</t>
+  </si>
+  <si>
+    <t>PERF-003,PERF-004</t>
+  </si>
+  <si>
+    <t>PDF multilingual rendering must be reliable</t>
+  </si>
+  <si>
+    <t>FONT-003,FONT-006</t>
+  </si>
+  <si>
+    <t>Export metadata must be correct</t>
+  </si>
+  <si>
+    <t>DOCX-012,DOCX-020</t>
+  </si>
+  <si>
+    <t>Partly fixed in 622d9c1: Word exports carry the source file's core properties (author, dates, subject...) instead of 'python-docx'/2013; fields remain (DOCX-020).</t>
+  </si>
+  <si>
+    <t>AUD-19</t>
+  </si>
+  <si>
+    <t>Canonical model must represent more than paragraphs + runs + simple tables</t>
+  </si>
+  <si>
+    <t>CORE-001,DOCX-015,DOCX-016,DOCX-017</t>
+  </si>
+  <si>
+    <t>Tests can miss import-side data loss (model-relative comparison)</t>
+  </si>
+  <si>
+    <t>TEST-020,TEST-021,TEST-022</t>
+  </si>
+  <si>
+    <t>P0 tasks (live from MASTER)</t>
+  </si>
+  <si>
+    <t>DOCUMENT_FIDELITY — Content preservation</t>
+  </si>
+  <si>
+    <t>Canonical model, fidelity reports, capability matrix, change/review model. Categories: CORE, FIDELITY, REVIEW. Rows are formulas over MASTER — change task data in MASTER or with tools/tracker/tracker.py.</t>
+  </si>
+  <si>
+    <t>Tasks (live from MASTER)</t>
+  </si>
+  <si>
+    <t>DOCX_OOXML — DOCX / OOXML preservation</t>
+  </si>
+  <si>
+    <t>Import and export fidelity for Word documents. Categories: DOCX. Rows are formulas over MASTER — change task data in MASTER or with tools/tracker/tracker.py.</t>
+  </si>
+  <si>
+    <t>PDF — PDF engine</t>
+  </si>
+  <si>
+    <t>PDF export and PDF parsing. Categories: PDF. Rows are formulas over MASTER — change task data in MASTER or with tools/tracker/tracker.py.</t>
+  </si>
+  <si>
+    <t>EDITOR — Editor integrity</t>
+  </si>
+  <si>
+    <t>Tiptap mapping and save integrity. Categories: EDITOR. Rows are formulas over MASTER — change task data in MASTER or with tools/tracker/tracker.py.</t>
+  </si>
+  <si>
+    <t>FORMATTING — Formatting and Document Health</t>
+  </si>
+  <si>
+    <t>Formatting engine, Format by Example, Document Health. Categories: FORMATTING, HEALTH. Rows are formulas over MASTER — change task data in MASTER or with tools/tracker/tracker.py.</t>
+  </si>
+  <si>
+    <t>AI — AI fidelity</t>
+  </si>
+  <si>
+    <t>Fidelity checks, proposals and review, budgets. Categories: AI. Rows are formulas over MASTER — change task data in MASTER or with tools/tracker/tracker.py.</t>
+  </si>
+  <si>
+    <t>SECURITY — Security and accounts</t>
+  </si>
+  <si>
+    <t>Security hardening and account essentials. Categories: SECURITY, ACCOUNT. Rows are formulas over MASTER — change task data in MASTER or with tools/tracker/tracker.py.</t>
+  </si>
+  <si>
+    <t>PERFORMANCE — Performance</t>
+  </si>
+  <si>
+    <t>Measured results — brief §80-81: measure, then set regression thresholds relative to the baseline (no invented SLOs)</t>
+  </si>
+  <si>
+    <t>Bench ID</t>
+  </si>
+  <si>
+    <t>Metric</t>
+  </si>
+  <si>
+    <t>Unit</t>
+  </si>
+  <si>
+    <t>Scenario</t>
+  </si>
+  <si>
+    <t>Baseline</t>
+  </si>
+  <si>
+    <t>Baseline Source</t>
+  </si>
+  <si>
+    <t>Current</t>
+  </si>
+  <si>
+    <t>Measured On</t>
+  </si>
+  <si>
+    <t>Threshold</t>
+  </si>
+  <si>
+    <t>BENCH-001</t>
+  </si>
+  <si>
+    <t>duration</t>
+  </si>
+  <si>
+    <t>s</t>
+  </si>
+  <si>
+    <t>DOCX export: table 500x8 (4,000 cells)</t>
+  </si>
+  <si>
+    <t>audit perf_table.py (400 cells 3.8 s; 1,600 cells 53.7 s; quadratic)</t>
+  </si>
+  <si>
+    <t>BENCH-002</t>
+  </si>
+  <si>
+    <t>PDF export: table 500x8</t>
+  </si>
+  <si>
+    <t>audit perf_table.py (linear)</t>
+  </si>
+  <si>
+    <t>BENCH-003</t>
+  </si>
+  <si>
+    <t>Import: 300-page text DOCX (1,650 elements)</t>
+  </si>
+  <si>
+    <t>audit perf_backend.py</t>
+  </si>
+  <si>
+    <t>BENCH-004</t>
+  </si>
+  <si>
+    <t>DOCX export: 300-page text document</t>
+  </si>
+  <si>
+    <t>BENCH-005</t>
+  </si>
+  <si>
+    <t>PDF export: 300-page text document</t>
+  </si>
+  <si>
+    <t>BENCH-006</t>
+  </si>
+  <si>
+    <t>memory growth</t>
+  </si>
+  <si>
+    <t>MB</t>
+  </si>
+  <si>
+    <t>PDF export: 39 KB DOCX holding a 12000x12000 PNG</t>
+  </si>
+  <si>
+    <t>audit pixel_bomb.py (14000x14000 crashes the export)</t>
+  </si>
+  <si>
+    <t>BENCH-007</t>
+  </si>
+  <si>
+    <t>PDF export: 4 JPEG images 2400x1800</t>
+  </si>
+  <si>
+    <t>audit perf_backend.py (6.3 s)</t>
+  </si>
+  <si>
+    <t>BENCH-008</t>
+  </si>
+  <si>
+    <t>Editor: type 20 characters at 12,196 elements (1M-character paste)</t>
+  </si>
+  <si>
+    <t>audit perf_browser.js (~470 ms per key)</t>
+  </si>
+  <si>
+    <t>BENCH-009</t>
+  </si>
+  <si>
+    <t>Editor: type 20 characters, 300-page document</t>
+  </si>
+  <si>
+    <t>audit perf_browser.js</t>
+  </si>
+  <si>
+    <t>BENCH-010</t>
+  </si>
+  <si>
+    <t>request size</t>
+  </si>
+  <si>
+    <t>Autosave request: 300-page document</t>
+  </si>
+  <si>
+    <t>audit perf_browser.js (whole elements list per save)</t>
+  </si>
+  <si>
+    <t>BENCH-011</t>
+  </si>
+  <si>
+    <t>Autosave request: 1M-character paste</t>
+  </si>
+  <si>
+    <t>BENCH-012</t>
+  </si>
+  <si>
+    <t>storage</t>
+  </si>
+  <si>
+    <t>Stored history: one 300-page document, 50 steps</t>
+  </si>
+  <si>
+    <t>audit (2.8 MB per full copy; 7.2 MB when the JSON is ASCII-escaped)</t>
+  </si>
+  <si>
+    <t>BENCH-013</t>
+  </si>
+  <si>
+    <t>Paste: 2M characters (the cap)</t>
+  </si>
+  <si>
+    <t>audit perf_backend.py (17.5k elements, 7.1 MB JSON)</t>
+  </si>
+  <si>
+    <t>Performance tasks (live from MASTER)</t>
+  </si>
+  <si>
+    <t>TESTING — Testing</t>
+  </si>
+  <si>
+    <t>Test runs (oldest first)</t>
+  </si>
+  <si>
+    <t>Run ID</t>
+  </si>
+  <si>
+    <t>Command</t>
+  </si>
+  <si>
+    <t>Passed</t>
+  </si>
+  <si>
+    <t>Skipped</t>
+  </si>
+  <si>
+    <t>Date</t>
+  </si>
+  <si>
+    <t>Duration (s)</t>
+  </si>
+  <si>
+    <t>RUN-0001</t>
+  </si>
+  <si>
+    <t>backend-pytest</t>
+  </si>
+  <si>
+    <t>PASS</t>
+  </si>
+  <si>
+    <t>cd backend &amp;&amp; venv/Scripts/python -m pytest -q -p no:cacheprovider</t>
+  </si>
+  <si>
+    <t>Skip: optional real-Word check (SMARTDOC_REAL_DOCX unset). 1 DeprecationWarning (starlette/anyio). Audit measured 93% line coverage on 2026-09-26.</t>
+  </si>
+  <si>
+    <t>ea69829</t>
+  </si>
+  <si>
+    <t>RUN-0002</t>
+  </si>
+  <si>
+    <t>frontend-lint</t>
+  </si>
+  <si>
+    <t>cd frontend &amp;&amp; npm run lint</t>
+  </si>
+  <si>
+    <t>eslint: 0 problems</t>
+  </si>
+  <si>
+    <t>RUN-0003</t>
+  </si>
+  <si>
+    <t>frontend-tsc</t>
+  </si>
+  <si>
+    <t>cd frontend &amp;&amp; npx tsc --noEmit</t>
+  </si>
+  <si>
+    <t>0 type errors</t>
+  </si>
+  <si>
+    <t>RUN-0004</t>
+  </si>
+  <si>
+    <t>frontend-vitest</t>
+  </si>
+  <si>
+    <t>cd frontend &amp;&amp; npm test</t>
+  </si>
+  <si>
+    <t>6 test files</t>
+  </si>
+  <si>
+    <t>RUN-0005</t>
+  </si>
+  <si>
+    <t>frontend-build</t>
+  </si>
+  <si>
+    <t>cd frontend &amp;&amp; npm run build</t>
+  </si>
+  <si>
+    <t>Next.js production build, 11 routes</t>
+  </si>
+  <si>
+    <t>RUN-0006</t>
+  </si>
+  <si>
+    <t>e2e-playwright</t>
+  </si>
+  <si>
+    <t>cd frontend &amp;&amp; npm run test:e2e</t>
+  </si>
+  <si>
+    <t>Edge; throwaway backend on SQLite (:8100) + production build (:3100). 16 workflows in 5 spec files; the brief asks for 24 (TEST-040). Leaves %TEMP%/smartdoc-e2e-* dirs behind (TEST-006).</t>
+  </si>
+  <si>
+    <t>RUN-0007</t>
+  </si>
+  <si>
+    <t>migrations</t>
+  </si>
+  <si>
+    <t>alembic upgrade head &amp;&amp; alembic check &amp;&amp; alembic downgrade base &amp;&amp; alembic upgrade head (scratch SQLite); alembic upgrade head --sql (PostgreSQL dialect)</t>
+  </si>
+  <si>
+    <t>head 85211092fe4c; 'No new upgrade operations detected'; offline SQL: 14 tables at head, RLS enabled on every table</t>
+  </si>
+  <si>
+    <t>RUN-0008</t>
+  </si>
+  <si>
+    <t>supabase</t>
+  </si>
+  <si>
+    <t>Supabase MCP: list_migrations, get_advisors security+performance, list_tables (project edmmjmsynjziahwtjuke)</t>
+  </si>
+  <si>
+    <t>8/8 migrations applied; 14 tables, RLS on all; advisors only INFO: 14x rls_enabled_no_policy (by design: the API connects as owner, PostgREST roles see nothing), 8x unused_index (low traffic)</t>
+  </si>
+  <si>
+    <t>RUN-0009</t>
+  </si>
+  <si>
+    <t>pip-audit</t>
+  </si>
+  <si>
+    <t>uvx pip-audit --disable-pip -r backend/requirements.lock; same for requirements-dev.lock</t>
+  </si>
+  <si>
+    <t>No known vulnerabilities in either lock file</t>
+  </si>
+  <si>
+    <t>RUN-0010</t>
+  </si>
+  <si>
+    <t>npm-audit</t>
+  </si>
+  <si>
+    <t>cd frontend &amp;&amp; npm audit; npm audit --omit=dev</t>
+  </si>
+  <si>
+    <t>0 vulnerabilities across 633 dependencies</t>
+  </si>
+  <si>
+    <t>RUN-0011</t>
+  </si>
+  <si>
+    <t>docker-compose</t>
+  </si>
+  <si>
+    <t>PARTIAL</t>
+  </si>
+  <si>
+    <t>docker compose config --quiet</t>
+  </si>
+  <si>
+    <t>compose file valid (8 services: postgres, redis, minio, minio-bucket, migrate, worker, backend, frontend); images NOT built: Docker daemon not running on this machine (CI builds them on main)</t>
+  </si>
+  <si>
+    <t>RUN-0012</t>
+  </si>
+  <si>
+    <t>Phase 1 editor integrity: +16 tests (nesting model, nested API/exports, health links)</t>
+  </si>
+  <si>
+    <t>RUN-0013</t>
+  </si>
+  <si>
+    <t>cd frontend &amp;&amp; npx vitest run</t>
+  </si>
+  <si>
+    <t>+31: nestedBlocks.test.ts (28), useAutoSave.test.tsx (3); tsc and eslint clean</t>
+  </si>
+  <si>
+    <t>RUN-0014</t>
+  </si>
+  <si>
+    <t>cd frontend &amp;&amp; npx playwright test</t>
+  </si>
+  <si>
+    <t>+1: e2e/nested.spec.ts (paste, autosave, reload)</t>
+  </si>
+  <si>
+    <t>RUN-0015</t>
+  </si>
+  <si>
+    <t>+29 test_fidelity_report.py</t>
+  </si>
+  <si>
+    <t>RUN-0016</t>
+  </si>
+  <si>
+    <t>+3 FidelityPanel.test.tsx</t>
+  </si>
+  <si>
+    <t>RUN-0017</t>
+  </si>
+  <si>
+    <t>+fidelity.spec.ts; nested.spec.ts made deterministic (focus check, Ctrl+End) after one run pasted at the document start</t>
+  </si>
+  <si>
+    <t>RUN-0018</t>
+  </si>
+  <si>
+    <t>+6 test_export_fidelity.py</t>
+  </si>
+  <si>
+    <t>RUN-0019</t>
+  </si>
+  <si>
+    <t>+4 ExportResult.test.tsx</t>
+  </si>
+  <si>
+    <t>RUN-0020</t>
+  </si>
+  <si>
+    <t>export test checks the export's content message</t>
+  </si>
+  <si>
+    <t>RUN-0021</t>
+  </si>
+  <si>
+    <t>+6 test_capabilities.py</t>
+  </si>
+  <si>
+    <t>RUN-0022</t>
+  </si>
+  <si>
+    <t>venv/Scripts/python -m pytest -q</t>
+  </si>
+  <si>
+    <t>after FID-002 detections + section break fix</t>
+  </si>
+  <si>
+    <t>RUN-0023</t>
+  </si>
+  <si>
+    <t>npx vitest run</t>
+  </si>
+  <si>
+    <t>tsc --noEmit and eslint clean too</t>
+  </si>
+  <si>
+    <t>RUN-0024</t>
+  </si>
+  <si>
+    <t>rule values (SEC-022) + editor direct styles</t>
+  </si>
+  <si>
+    <t>RUN-0025</t>
+  </si>
+  <si>
+    <t>tsc + eslint clean</t>
+  </si>
+  <si>
+    <t>RUN-0026</t>
+  </si>
+  <si>
+    <t>e2e</t>
+  </si>
+  <si>
+    <t>npx playwright test</t>
+  </si>
+  <si>
+    <t>incl. e2e/direct-formatting.spec.ts</t>
+  </si>
+  <si>
+    <t>RUN-0027</t>
+  </si>
+  <si>
+    <t>Phase 1 gate: link titles, mark order, Markdown pictures/rules</t>
+  </si>
+  <si>
+    <t>RUN-0028</t>
+  </si>
+  <si>
+    <t>Phase 1 gate; tsc + eslint clean</t>
+  </si>
+  <si>
+    <t>RUN-0029</t>
+  </si>
+  <si>
+    <t>Phase 1 gate</t>
+  </si>
+  <si>
+    <t>RUN-0030</t>
+  </si>
+  <si>
+    <t>AI fidelity check (AI-001..004)</t>
+  </si>
+  <si>
+    <t>RUN-0031</t>
+  </si>
+  <si>
+    <t>AI proposals</t>
+  </si>
+  <si>
+    <t>RUN-0032</t>
+  </si>
+  <si>
+    <t>RUN-0033</t>
+  </si>
+  <si>
+    <t>incl. e2e/proposals.spec.ts</t>
+  </si>
+  <si>
+    <t>RUN-0034</t>
+  </si>
+  <si>
+    <t>AI budget</t>
+  </si>
+  <si>
+    <t>RUN-0035</t>
+  </si>
+  <si>
+    <t>prompt-injection review</t>
+  </si>
+  <si>
+    <t>RUN-0036</t>
+  </si>
+  <si>
+    <t>Phase 2 gate</t>
+  </si>
+  <si>
+    <t>RUN-0037</t>
+  </si>
+  <si>
+    <t>RUN-0038</t>
+  </si>
+  <si>
+    <t>source package + patch writer</t>
+  </si>
+  <si>
+    <t>RUN-0039</t>
+  </si>
+  <si>
+    <t>after the patch writer</t>
+  </si>
+  <si>
+    <t>RUN-0040</t>
+  </si>
+  <si>
+    <t>backend pytest</t>
+  </si>
+  <si>
+    <t>DOCX-028: test_original_blocks.py (26), golden set of 13</t>
+  </si>
+  <si>
+    <t>7f22bf9</t>
+  </si>
+  <si>
+    <t>RUN-0041</t>
+  </si>
+  <si>
+    <t>frontend vitest</t>
+  </si>
+  <si>
+    <t>editor round trip includes 13-kept-blocks</t>
+  </si>
+  <si>
+    <t>RUN-0042</t>
+  </si>
+  <si>
+    <t>playwright</t>
+  </si>
+  <si>
+    <t>new e2e/kept-blocks.spec.ts</t>
+  </si>
+  <si>
+    <t>RUN-0043</t>
+  </si>
+  <si>
+    <t>tsc + eslint</t>
+  </si>
+  <si>
+    <t>cd frontend &amp;&amp; npx tsc --noEmit &amp;&amp; npx eslint .</t>
+  </si>
+  <si>
+    <t>0 type errors, 0 lint problems</t>
+  </si>
+  <si>
+    <t>RUN-0044</t>
+  </si>
+  <si>
+    <t>DOCX-025: tests/test_hidden_text.py (7)</t>
+  </si>
+  <si>
+    <t>fada4d7</t>
+  </si>
+  <si>
+    <t>RUN-0045</t>
+  </si>
+  <si>
+    <t>editor/hiddenText.test.tsx (6)</t>
+  </si>
+  <si>
+    <t>RUN-0046</t>
+  </si>
+  <si>
+    <t>new e2e/hidden-text.spec.ts</t>
+  </si>
+  <si>
+    <t>RUN-0047</t>
+  </si>
+  <si>
+    <t>RUN-0048</t>
+  </si>
+  <si>
+    <t>DOCX-013 part 1: tests/test_character_formatting.py (12)</t>
+  </si>
+  <si>
+    <t>c51b1bf</t>
+  </si>
+  <si>
+    <t>RUN-0049</t>
+  </si>
+  <si>
+    <t>editor/characterFormatting.test.ts (3)</t>
+  </si>
+  <si>
+    <t>RUN-0050</t>
+  </si>
+  <si>
+    <t>after DOCX-013 part 1</t>
+  </si>
+  <si>
+    <t>RUN-0051</t>
+  </si>
+  <si>
+    <t>RUN-0052</t>
+  </si>
+  <si>
+    <t>DOCX-013 part 2 + FID-007: tests/test_copy_reports.py (6)</t>
+  </si>
+  <si>
+    <t>309f9d6</t>
+  </si>
+  <si>
+    <t>RUN-0053</t>
+  </si>
+  <si>
+    <t>characterFormatting.test.ts (4)</t>
+  </si>
+  <si>
+    <t>RUN-0054</t>
+  </si>
+  <si>
+    <t>after DOCX-013 part 2</t>
+  </si>
+  <si>
+    <t>RUN-0055</t>
+  </si>
+  <si>
+    <t>RUN-0056</t>
+  </si>
+  <si>
+    <t>DOCX-014 part 1: tests/test_paragraph_formatting.py (9)</t>
+  </si>
+  <si>
+    <t>597275a</t>
+  </si>
+  <si>
+    <t>RUN-0057</t>
+  </si>
+  <si>
+    <t>after DOCX-014 part 1</t>
+  </si>
+  <si>
+    <t>RUN-0058</t>
+  </si>
+  <si>
+    <t>RUN-0059</t>
+  </si>
+  <si>
+    <t>RUN-0060</t>
+  </si>
+  <si>
+    <t>DOCX-014 part 2: tests/test_paragraph_formatting.py (19)</t>
+  </si>
+  <si>
+    <t>9f1c5b4</t>
+  </si>
+  <si>
+    <t>RUN-0061</t>
+  </si>
+  <si>
+    <t>after DOCX-014 part 2</t>
+  </si>
+  <si>
+    <t>RUN-0062</t>
+  </si>
+  <si>
+    <t>RUN-0063</t>
+  </si>
+  <si>
+    <t>RUN-0064</t>
+  </si>
+  <si>
+    <t>DOCX-015 part 1a: tests/test_sections.py (6)</t>
+  </si>
+  <si>
+    <t>49d54e5</t>
+  </si>
+  <si>
+    <t>RUN-0065</t>
+  </si>
+  <si>
+    <t>sectionBreak.test.ts (3)</t>
+  </si>
+  <si>
+    <t>RUN-0066</t>
+  </si>
+  <si>
+    <t>after DOCX-015 part 1a</t>
+  </si>
+  <si>
+    <t>RUN-0067</t>
+  </si>
+  <si>
+    <t>RUN-0068</t>
+  </si>
+  <si>
+    <t>DOCX-015 part 1b: tests/test_sections.py (7)</t>
+  </si>
+  <si>
+    <t>cb75ebd</t>
+  </si>
+  <si>
+    <t>RUN-0069</t>
+  </si>
+  <si>
+    <t>after DOCX-015 part 1b</t>
+  </si>
+  <si>
+    <t>RUN-0070</t>
+  </si>
+  <si>
+    <t>RUN-0071</t>
+  </si>
+  <si>
+    <t>Testing tasks (live from MASTER)</t>
+  </si>
+  <si>
+    <t>PRODUCT_FEATURES — Product features</t>
+  </si>
+  <si>
+    <t>Feature backlog — brief §61-62</t>
+  </si>
+  <si>
+    <t>Feature</t>
+  </si>
+  <si>
+    <t>Bucket</t>
+  </si>
+  <si>
+    <t>Linked Tasks</t>
+  </si>
+  <si>
+    <t>Linked Done</t>
+  </si>
+  <si>
+    <t>Linked Total</t>
+  </si>
+  <si>
+    <t>Document integrity</t>
+  </si>
+  <si>
+    <t>NOW</t>
+  </si>
+  <si>
+    <t>EDIT-001,EDIT-005,FID-002</t>
+  </si>
+  <si>
+    <t>Brief 62: NOW #1</t>
+  </si>
+  <si>
+    <t>Fidelity</t>
+  </si>
+  <si>
+    <t>DOCX-011,TEST-022</t>
+  </si>
+  <si>
+    <t>Brief 62: NOW #2</t>
+  </si>
+  <si>
+    <t>Security</t>
+  </si>
+  <si>
+    <t>SEC-010,SEC-012,SEC-014</t>
+  </si>
+  <si>
+    <t>Brief 62: NOW #3</t>
+  </si>
+  <si>
+    <t>Performance</t>
+  </si>
+  <si>
+    <t>PERF-001,PERF-003,PERF-004</t>
+  </si>
+  <si>
+    <t>Brief 62: NOW #4</t>
+  </si>
+  <si>
+    <t>PDF -&gt; editable</t>
+  </si>
+  <si>
+    <t>P2E-002,P2E-005</t>
+  </si>
+  <si>
+    <t>Brief 62: NOW #5</t>
+  </si>
+  <si>
+    <t>TRAN-001,TRAN-006</t>
+  </si>
+  <si>
+    <t>Brief 62: NOW #6</t>
+  </si>
+  <si>
+    <t>FONT-002,FONT-003</t>
+  </si>
+  <si>
+    <t>Brief 62: NOW #7</t>
+  </si>
+  <si>
+    <t>Review Changes</t>
+  </si>
+  <si>
+    <t>REV-001,REV-002</t>
+  </si>
+  <si>
+    <t>Brief 62: NOW #8</t>
+  </si>
+  <si>
+    <t>HLTH-001,HLTH-002</t>
+  </si>
+  <si>
+    <t>Brief 62: NOW #9</t>
+  </si>
+  <si>
+    <t>FMT-001,FMT-002,FMT-003</t>
+  </si>
+  <si>
+    <t>Brief 62: NOW #10</t>
+  </si>
+  <si>
+    <t>OCR</t>
+  </si>
+  <si>
+    <t>Part of PDF -&gt; editable (brief 43)</t>
+  </si>
+  <si>
+    <t>Multilingual support</t>
+  </si>
+  <si>
+    <t>TRAN-007,FONT-003</t>
+  </si>
+  <si>
+    <t>Part of translation + FontResolver</t>
+  </si>
+  <si>
+    <t>RTL</t>
+  </si>
+  <si>
+    <t>FONT-003,FONT-004</t>
+  </si>
+  <si>
+    <t>Part of FontResolver</t>
+  </si>
+  <si>
+    <t>CJK</t>
+  </si>
+  <si>
+    <t>Glossary</t>
+  </si>
+  <si>
+    <t>Part of translation MVP (brief 49)</t>
+  </si>
+  <si>
+    <t>Terminology lock</t>
+  </si>
+  <si>
+    <t>Citation preservation</t>
+  </si>
+  <si>
+    <t>Preservation is fidelity work; a citation editor is LATER</t>
+  </si>
+  <si>
+    <t>Bibliography preservation</t>
+  </si>
+  <si>
+    <t>Preservation is fidelity work</t>
+  </si>
+  <si>
+    <t>Content controls</t>
+  </si>
+  <si>
+    <t>Preserve now; editing content controls NEXT</t>
+  </si>
+  <si>
+    <t>Custom fields</t>
+  </si>
+  <si>
+    <t>Preserve custom properties and fields now; an editor NEXT</t>
+  </si>
+  <si>
+    <t>Document compare</t>
+  </si>
+  <si>
+    <t>NEXT</t>
+  </si>
+  <si>
+    <t>Brief 62: NEXT</t>
+  </si>
+  <si>
+    <t>Version compare</t>
+  </si>
+  <si>
+    <t>Brief 62: NEXT (batch processing)</t>
+  </si>
+  <si>
+    <t>After the translation MVP</t>
+  </si>
+  <si>
+    <t>Table repair</t>
+  </si>
+  <si>
+    <t>List repair</t>
+  </si>
+  <si>
+    <t>Brief 62: NEXT (accessibility)</t>
+  </si>
+  <si>
+    <t>Heading hierarchy checker</t>
+  </si>
+  <si>
+    <t>Link checker</t>
+  </si>
+  <si>
+    <t>Alt-text checker</t>
+  </si>
+  <si>
+    <t>HLTH-001,FEAT-010</t>
+  </si>
+  <si>
+    <t>Metadata editor</t>
+  </si>
+  <si>
+    <t>Global style replacement</t>
+  </si>
+  <si>
+    <t>Find/replace with formatting</t>
+  </si>
+  <si>
+    <t>Tracked change cleanup</t>
+  </si>
+  <si>
+    <t>Template extraction</t>
+  </si>
+  <si>
+    <t>Document-to-template</t>
+  </si>
+  <si>
+    <t>Template matching</t>
+  </si>
+  <si>
+    <t>Advanced template sharing</t>
+  </si>
+  <si>
+    <t>Teams</t>
+  </si>
+  <si>
+    <t>Translation memory</t>
+  </si>
+  <si>
+    <t>PDF merge/split</t>
+  </si>
+  <si>
+    <t>Page reorder</t>
+  </si>
+  <si>
+    <t>Page rotate</t>
+  </si>
+  <si>
+    <t>Page delete</t>
+  </si>
+  <si>
+    <t>Page extract</t>
+  </si>
+  <si>
+    <t>Merge documents</t>
+  </si>
+  <si>
+    <t>LATER</t>
+  </si>
+  <si>
+    <t>Split documents</t>
+  </si>
+  <si>
+    <t>Watermark</t>
+  </si>
+  <si>
+    <t>Forms (advanced)</t>
+  </si>
+  <si>
+    <t>Brief 62: LATER</t>
+  </si>
+  <si>
+    <t>SmartArt editing</t>
+  </si>
+  <si>
+    <t>Brief 62: LATER; SmartArt is preserved, not edited</t>
+  </si>
+  <si>
+    <t>OLE</t>
+  </si>
+  <si>
+    <t>Brief 62: LATER; OLE objects preserved, not edited</t>
+  </si>
+  <si>
+    <t>Full tracked-change editor</t>
+  </si>
+  <si>
+    <t>Advanced citation manager</t>
+  </si>
+  <si>
+    <t>Advanced drawing editor</t>
+  </si>
+  <si>
+    <t>Layout-preserving PDF editing (frames/anchors)</t>
+  </si>
+  <si>
+    <t>ARCHITECTURE_ONLY</t>
+  </si>
+  <si>
+    <t>Phase 9: architecture and hooks only</t>
+  </si>
+  <si>
+    <t>Product tasks (live from MASTER)</t>
+  </si>
+  <si>
+    <t>TRANSLATION — Translation and fonts</t>
+  </si>
+  <si>
+    <t>Translation MVP and FontResolver. Categories: TRANSLATION, FONT. Rows are formulas over MASTER — change task data in MASTER or with tools/tracker/tracker.py.</t>
+  </si>
+  <si>
+    <t>PDF_TO_EDITABLE — PDF to editable</t>
+  </si>
+  <si>
+    <t>PDF to editable document conversion. Categories: P2E. Rows are formulas over MASTER — change task data in MASTER or with tools/tracker/tracker.py.</t>
+  </si>
+  <si>
+    <t>BILLING_PLANS — Plans and billing</t>
+  </si>
+  <si>
+    <t>Initial plan hypothesis — brief §64: configurable defaults, not final prices; confirm against measured AI and infrastructure cost. Blue = input.</t>
+  </si>
+  <si>
+    <t>Usage unit / feature</t>
+  </si>
+  <si>
+    <t>FREE</t>
+  </si>
+  <si>
+    <t>PRO</t>
+  </si>
+  <si>
+    <t>BUSINESS</t>
+  </si>
+  <si>
+    <t>Documents / month</t>
+  </si>
+  <si>
+    <t>BUSINESS: per workspace</t>
+  </si>
+  <si>
+    <t>PDF conversion pages / month</t>
+  </si>
+  <si>
+    <t>OCR pages / month</t>
+  </si>
+  <si>
+    <t>Translation characters / month</t>
+  </si>
+  <si>
+    <t>AI operations / month</t>
+  </si>
+  <si>
+    <t>Exports / month</t>
+  </si>
+  <si>
+    <t>high</t>
+  </si>
+  <si>
+    <t>BUSINESS: 'high export limits', no number given</t>
+  </si>
+  <si>
+    <t>Templates</t>
+  </si>
+  <si>
+    <t>basic</t>
+  </si>
+  <si>
+    <t>custom</t>
+  </si>
+  <si>
+    <t>shared</t>
+  </si>
+  <si>
+    <t>Formatting</t>
+  </si>
+  <si>
+    <t>Format by Example</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>Advanced Document Health</t>
+  </si>
+  <si>
+    <t>yes</t>
+  </si>
+  <si>
+    <t>Version history</t>
+  </si>
+  <si>
+    <t>no</t>
+  </si>
+  <si>
+    <t>reasonable limits</t>
+  </si>
+  <si>
+    <t>Team workspace</t>
+  </si>
+  <si>
+    <t>Priority processing</t>
+  </si>
+  <si>
+    <t>Advanced controls</t>
+  </si>
+  <si>
+    <t>Billing and plan tasks (live from MASTER)</t>
+  </si>
+  <si>
+    <t>INFRA — Infrastructure</t>
+  </si>
+  <si>
+    <t>Tracker, jobs, storage, observability, deployment, documentation. Categories: INFRA, JOBS, STORAGE, OBSERVABILITY, DOCS. Rows are formulas over MASTER — change task data in MASTER or with tools/tracker/tracker.py.</t>
+  </si>
+  <si>
+    <t>Timestamp</t>
+  </si>
+  <si>
+    <t>Task ID</t>
+  </si>
+  <si>
+    <t>Change</t>
+  </si>
+  <si>
+    <t>Files</t>
+  </si>
+  <si>
+    <t>Created SmartDoc_Master_Implementation_Tracker.xlsx from the 2026-09-26 audit findings and the brief's phases: 151 tasks, 20 findings, 15 release gates.</t>
+  </si>
+  <si>
+    <t>tools/tracker/tracker.py, tools/tracker/seed.py</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>Built the Excel control centre: MASTER with 151 stable-ID tasks from the audit findings and the brief's 19 phases, CRITICAL_FIXES (20 findings -&gt; fix tasks, live status), 14 category views, DASHBOARD (totals, completion/verified %, phase %, category %, P0/P1 remaining), CHANGE_LOG, SESSION_STATE, RELEASE_GATES GATE-001..015. Formulas verified in Excel against independently computed values.</t>
+  </si>
+  <si>
+    <t>tools/tracker/*, SmartDoc_Master_Implementation_Tracker.xlsx, .gitignore</t>
+  </si>
+  <si>
+    <t>Resume reminder set with the platform scheduler; it fired and resumed the work. It only fires while this session is open and idle, which is recorded in AI-CONTINUATION.md.</t>
+  </si>
+  <si>
+    <t>Created the checkpoint system: AI-CONTINUATION.md with CURRENT STATE / LAST VERIFIED / WHAT WAS CHANGED / WHAT PASSED / WHAT FAILED / WHAT REMAINS / NEXT ACTION / IMPORTANT WARNINGS, session-state.json mirrored into SESSION_STATE by tracker.py state, and the brief saved verbatim for future sessions.</t>
+  </si>
+  <si>
+    <t>docs/AI-CONTINUATION.md, docs/session-state.json, docs/implementation-brief.md</t>
+  </si>
+  <si>
+    <t>Baseline backend suite: 643 passed, 1 skipped (optional real-Word check), 0 failed in 88 s on ea69829. Recorded as RUN-0001.</t>
+  </si>
+  <si>
+    <t>Baseline frontend: eslint clean, tsc clean, Vitest 46 passed in 6 files, production build succeeded. Recorded as RUN-0002..RUN-0005.</t>
+  </si>
+  <si>
+    <t>Baseline E2E: 16 Playwright workflows passed against the throwaway stack (SQLite backend :8100, production build :3100). The brief's 24-workflow target is TEST-040; temp-dir leak logged as TEST-006.</t>
+  </si>
+  <si>
+    <t>Baseline database: alembic head 85211092fe4c, check reports no drift, full down/up cycle clean; PostgreSQL offline SQL builds 14 tables with RLS; Supabase has all 8 migrations and only INFO-level advisor notices.</t>
+  </si>
+  <si>
+    <t>Baseline dependency audit: pip-audit finds no known vulnerabilities in requirements.lock or requirements-dev.lock; npm audit reports 0 vulnerabilities (production and dev).</t>
+  </si>
+  <si>
+    <t>Baseline infrastructure inspected: compose file valid with 8 services, arq worker and in-process job backends, local and S3 storage providers. Docker images were not built (daemon not running) - left to INFRA-010.</t>
+  </si>
+  <si>
+    <t>Baseline fixtures: the repository's 12 golden DOCX are generated by python-docx (not Word-authored) plus one PDF; the audit's 17 Word-authored fixtures still live outside the repo and move in with TEST-020.</t>
+  </si>
+  <si>
+    <t>Wrote docs/architecture/current-baseline.md: stack versions, the 11 baseline checks with commands and results, the migration chain and live database state, fixture inventory, audit performance figures, and what the baseline could not verify (Docker images, real AI model, Stripe, e-mail, hosting).</t>
+  </si>
+  <si>
+    <t>INFRA-001, INFRA-002, INFRA-003, TEST-001, TEST-002, TEST-003, TEST-004, TEST-005, SEC-001, INFRA-004, DOCS-001</t>
+  </si>
+  <si>
+    <t>Phase 0 committed (4da4ecb, pushed to feature/smartdoc-production-hardening): tracker, checkpoint system and measured baseline. All 11 phase-0 tasks DONE; no production code changed.</t>
+  </si>
+  <si>
+    <t>see commit 4da4ecb</t>
+  </si>
+  <si>
+    <t>Model now holds blocks nested inside table cells, list items and quotes as Elements (authoritative when set; inline keeps plain text), plus list numbering start/format; nesting capped at 8 levels (422 beyond). schemaVersion stays 1: the fields are additive.</t>
+  </si>
+  <si>
+    <t>backend/app/models/document.py, backend/tests/test_document_nesting.py</t>
+  </si>
+  <si>
+    <t>Regenerated the OpenAPI schema and the frontend's generated types for the nested-block and numbering fields; the contract test and the type check pass.</t>
+  </si>
+  <si>
+    <t>frontend/types/generated/*, frontend/types/document.ts</t>
+  </si>
+  <si>
+    <t>Backend readers now see nested blocks: pasted pictures inside cells/list items/quotes are validated and moved to asset storage like top-level ones (security and quota), exports fetch their assets, and the links health check covers list items, cells and nested blocks.</t>
+  </si>
+  <si>
+    <t>backend/app/services/image_assets.py, backend/app/services/document_service.py, backend/app/formatting/health.py</t>
+  </si>
+  <si>
+    <t>Word export renders nested blocks in cells, list items and quotes in reading order (verified by text order), numbers lists from their start in their format, and writes pictures' alt text.</t>
+  </si>
+  <si>
+    <t>backend/app/export/docx_export.py</t>
+  </si>
+  <si>
+    <t>PDF export renders nested blocks and list numbering (start/format); nested numbered levels now use the same a./i. sequence as the Word export instead of 1. everywhere.</t>
+  </si>
+  <si>
+    <t>backend/app/export/pdf_export.py</t>
+  </si>
+  <si>
+    <t>The editor mapping is total over the schema (tested against getSchema(editorExtensions)); anything unknown stops the save with a visible 'Not saved' message instead of being dropped, and the last saved version stays untouched.</t>
+  </si>
+  <si>
+    <t>frontend/editor/*</t>
+  </si>
+  <si>
+    <t>frontend/editor/nestedBlocks.test.ts (7 refusal cases); frontend/editor/useAutoSave.test.tsx (3)</t>
+  </si>
+  <si>
+    <t>Playwright pastes rich HTML (lists, code and a picture in table cells; a list in a quote; code in a list item; a list starting at 3 in letters), waits for autosave and reloads: everything is still there and no 'Not saved' appears.</t>
+  </si>
+  <si>
+    <t>frontend/e2e/nested.spec.ts</t>
+  </si>
+  <si>
+    <t>CORE-001, CORE-002, CORE-003, EDIT-001, EDIT-002, EDIT-003, EDIT-004, EDIT-005, EDIT-006, DOCX-001, PDF-001</t>
+  </si>
+  <si>
+    <t>Committed phase-01a-editor-integrity (1fe27a9, pushed): nested blocks in cells, list items and quotes survive the editor, the backend and both exports; unknown content stops the save visibly. AUD-01 fix tasks all DONE.</t>
+  </si>
+  <si>
+    <t>Import now produces a Document Fidelity Report: the importer's notes as items (feature, policy, count, content lost) plus an independent content check - the source's words (DOCX XML read separately from the importer, Markdown by what it renders, PDF extracted text) against the document's, in order. 'Verified' only when identical; differences listed with context (missing/added/changed/moved).</t>
+  </si>
+  <si>
+    <t>backend/app/fidelity/*, backend/app/models/document.py, backend/app/services/ingestion_service.py</t>
+  </si>
+  <si>
+    <t>Every importer note now carries a stable feature key and a brief-§90 policy class; review count and content-loss count are derived from them.</t>
+  </si>
+  <si>
+    <t>The editor shows the import's verdict in the status bar and a Проверка panel: content verified / differs (with word-level differences) / body complete but some content left out, then each item by policy. Browser check with a05 caught and fixed a misleading 'No content changes' when header text had been left out.</t>
+  </si>
+  <si>
+    <t>frontend/editor/panels/FidelityPanel.tsx, frontend/editor/EditorStatusBar.tsx, frontend/editor/DocumentEditorShell.tsx</t>
+  </si>
+  <si>
+    <t>FID-001, FID-004, FID-005, INFRA-005</t>
+  </si>
+  <si>
+    <t>Committed phase-01b-fidelity-report (8a330be, pushed): import fidelity report with policy classes and an independent word-level content check, shown in the editor; throwaway preview scripts.</t>
+  </si>
+  <si>
+    <t>Exports now report what they approximate or leave out (missing pictures, WebP a Word file can't hold, tables restyled for Word-sourced documents, edited kept fragments, page breaks in PDF tables, PDF comments/equations/fields/internal links, scripts the PDF can't lay out, alt text) and re-read the file: a Word export must hold exactly the document's words, a PDF every word in order (its own list numbers and page headers allowed). Shown under the Download button; the job result carries it.</t>
+  </si>
+  <si>
+    <t>Committed phase-01c-export-report (e55412f, pushed): export fidelity report with read-back content check, shown in the Export menu.</t>
+  </si>
+  <si>
+    <t>Added the machine-readable capability matrix (brief §91): 67 document features with import/edit/export/round-trip support and the policy the fidelity report uses, served at GET /api/v1/capabilities. Tests tie it to the code both ways, require a test for every clean round trip and a task for every unreported gap; writing it exposed unreported gaps now tracked (EDIT-012, DOCX-027).</t>
+  </si>
+  <si>
+    <t>backend/app/capabilities.py, backend/app/api/capabilities.py, backend/app/main.py, backend/tests/test_capabilities.py, frontend/types/generated/*</t>
+  </si>
+  <si>
+    <t>Committed phase-01d-capability-matrix (fcf30d7, pushed).</t>
+  </si>
+  <si>
+    <t>FID-002: import report now names empty spacing paragraphs, unsafe link addresses and per-section differences (page setup, odd/even breaks, page numbering, borders, line numbers, vertical alignment); matrix rows docx.empty_paragraphs + docx.sections updated</t>
+  </si>
+  <si>
+    <t>backend/app/fidelity/docx_detect.py, backend/app/fidelity/imports.py, backend/app/parsers/docx.py, backend/app/parsers/docx_inline.py, backend/app/capabilities.py, backend/tests/test_docx_detect.py</t>
+  </si>
+  <si>
+    <t>DOCX-015: section breaks break the page only where Word does (next section's w:type decides); continuous breaks no longer become page breaks</t>
+  </si>
+  <si>
+    <t>tests/test_docx_detect.py::test_a_section_break_breaks_the_page_only_where_word_does</t>
+  </si>
+  <si>
+    <t>DOCX-016: list number formats, start values and continuation round-trip; custom and multi-level labels reported</t>
+  </si>
+  <si>
+    <t>DOCX-012: Word core properties round-trip; custom properties and sensitivity labels reported without values</t>
+  </si>
+  <si>
+    <t>tests/test_docx_detect.py::test_the_files_own_properties_go_back_into_word_not_the_templates, tests/test_docx_detect.py::test_metadata_that_is_not_kept_is_reported_without_its_values</t>
+  </si>
+  <si>
+    <t>DOCX-026: unsafe link addresses reported instead of silently dropped</t>
+  </si>
+  <si>
+    <t>Golden JSON export is deterministic (uuid5 ids by order, fixed timestamps) so a regenerated fixture only differs where the importer's output did</t>
+  </si>
+  <si>
+    <t>backend/scripts/export_golden_json.py, frontend/tests/fixtures/golden/*.json</t>
+  </si>
+  <si>
+    <t>two consecutive exports byte-identical; tests/test_golden_documents.py::test_the_frontend_golden_json_is_current</t>
+  </si>
+  <si>
+    <t>FID-002 committed and pushed (phase-01e-import-detections)</t>
+  </si>
+  <si>
+    <t>SEC-022: formatting rule values validated at every entry and at resolve; CSS break-out via element style/page settings/instructions closed</t>
+  </si>
+  <si>
+    <t>backend/app/formatting/values.py, backend/app/formatting/engine.py, backend/app/schemas/formatting.py, backend/app/schemas/document.py, backend/app/ai/instruction_extraction.py, backend/tests/test_rule_values.py</t>
+  </si>
+  <si>
+    <t>FMT-005: instruction-path rule values validated before reaching CSS/export (with SEC-022)</t>
+  </si>
+  <si>
+    <t>EDIT-008: pasted/shortcut alignment saved as the element's own style and kept on split; paste into an empty paragraph keeps the pasted paragraphs' attributes</t>
+  </si>
+  <si>
+    <t>frontend/editor/tiptapToDocument.ts, frontend/editor/documentToTiptap.ts, frontend/editor/useAutoSave.ts, frontend/editor/pasteIntoEmptyBlock.ts, frontend/editor/extensions.ts, frontend/services/api/documents.ts, backend/app/schemas/document.py, backend/app/formatting/engine.py, backend/app/services/document_service.py, backend/app/api/documents.py</t>
+  </si>
+  <si>
+    <t>EDIT-009: pasted picture size kept as the picture's width share</t>
+  </si>
+  <si>
+    <t>EDIT-012: values outside the model named in the status bar and the Проверка panel</t>
+  </si>
+  <si>
+    <t>EDIT-011: cell alignment from pasted cells kept per column; differing cells and column widths reported</t>
+  </si>
+  <si>
+    <t>EDIT-008, EDIT-009, EDIT-012, SEC-022, FMT-005</t>
+  </si>
+  <si>
+    <t>Committed and pushed phase-01f-editor-direct-formatting</t>
+  </si>
+  <si>
+    <t>EDIT-010: link titles kept from Word/Markdown through the editor back into Word</t>
+  </si>
+  <si>
+    <t>backend/app/models/document.py, backend/app/parsers/docx_inline.py, backend/app/parsers/docx.py, backend/app/export/docx_export.py, backend/app/parsers/markdown.py, frontend/editor/tiptapToDocument.ts, frontend/editor/documentToTiptap.ts</t>
+  </si>
+  <si>
+    <t>FID-006: Markdown pictures named as left out (content), thematic breaks kept as rules</t>
+  </si>
+  <si>
+    <t>backend/app/parsers/markdown.py, backend/app/capabilities.py, backend/tests/test_capabilities.py, backend/tests/test_markdown_parser.py</t>
+  </si>
+  <si>
+    <t>EDIT-011: cell alignment/widths the model can't hold are named; keeping them moves to DOCX-017</t>
+  </si>
+  <si>
+    <t>EDIT-007: marks in one canonical order (MarkType) on both sides; opening a document saves nothing</t>
+  </si>
+  <si>
+    <t>backend/app/models/document.py, frontend/editor/tiptapToDocument.ts</t>
+  </si>
+  <si>
+    <t>TEST-010: nested-structure regression suite consolidated and verified</t>
+  </si>
+  <si>
+    <t>EDIT-008, EDIT-010, FID-006</t>
+  </si>
+  <si>
+    <t>Phase 1 browser check in the throwaway stack: Markdown doc with a picture -&gt; 'Body text complete, some content left out · 1 to review' (picture named with its description), '---' imported as a rule; pasted centred line + 160px picture + hsl colour + titled link at the end -&gt; status 'Saved · 1 formatting change not kept', Проверка 'While editing' lists the colour; after reload: line centred, picture width 24.9%, link title kept, notice gone</t>
+  </si>
+  <si>
+    <t>manual browser check (throwaway stack, fresh SQLite)</t>
+  </si>
+  <si>
+    <t>DOCS-011: documentation tree started for Phase 1 (document model, fidelity, docx, formatting, security, testing)</t>
+  </si>
+  <si>
+    <t>EDIT-007, EDIT-010, EDIT-011, FID-006, TEST-010, DOCS-011</t>
+  </si>
+  <si>
+    <t>Committed and pushed phase-01g-phase-1-complete; Phase 1 complete</t>
+  </si>
+  <si>
+    <t>AI-001: order/count/token/numeric/punctuation-aware comparator for AI output, with classified differences</t>
+  </si>
+  <si>
+    <t>backend/app/fidelity/text_check.py, backend/tests/test_ai_fidelity.py</t>
+  </si>
+  <si>
+    <t>AI-002: numbers and units protected; changed_numbers for cross-language checks</t>
+  </si>
+  <si>
+    <t>AI-003: structure analysis refuses answers that alter the text, per piece, logging without content</t>
+  </si>
+  <si>
+    <t>backend/app/ai/structure_analysis.py</t>
+  </si>
+  <si>
+    <t>AI-004: adversarial fidelity tests for every alteration the brief names</t>
+  </si>
+  <si>
+    <t>AI-001, AI-002, AI-003, AI-004</t>
+  </si>
+  <si>
+    <t>Committed and pushed phase-02a-ai-fidelity-check</t>
+  </si>
+  <si>
+    <t>AI-005: AI operations classified FORMAT/STRUCTURE/CONTENT; per-element instruction styles no longer dropped by the formatting pass</t>
+  </si>
+  <si>
+    <t>backend/app/formatting/proposals.py, backend/app/services/document_service.py</t>
+  </si>
+  <si>
+    <t>REV-001: change model with categories, used for proposals</t>
+  </si>
+  <si>
+    <t>backend/app/models/document.py, frontend/types/document.ts</t>
+  </si>
+  <si>
+    <t>AI-006: PLAN-&gt;VALIDATE-&gt;PREVIEW-&gt;ACCEPT-&gt;APPLY for AI content changes</t>
+  </si>
+  <si>
+    <t>backend/app/formatting/proposals.py, backend/app/services/document_service.py, backend/app/api/documents.py, backend/app/jobs/runner.py, backend/app/schemas/document.py, backend/app/schemas/jobs.py</t>
+  </si>
+  <si>
+    <t>AI-007: proposal review UI with accept/reject, E2E verified</t>
+  </si>
+  <si>
+    <t>frontend/editor/panels/ProposalsList.tsx, frontend/editor/panels/InstructionsPanel.tsx, frontend/editor/EditorStatusBar.tsx, frontend/editor/useFormatting.ts, frontend/services/api/documents.ts, frontend/services/api/jobs.ts, backend/scripts/e2e_ai.py, backend/scripts/e2e_server.py</t>
+  </si>
+  <si>
+    <t>AI-005, REV-001, AI-006, AI-007</t>
+  </si>
+  <si>
+    <t>Committed and pushed phase-02b-ai-proposals</t>
+  </si>
+  <si>
+    <t>AI-008: per-job/per-request AI call and time budget; no unbounded retries</t>
+  </si>
+  <si>
+    <t>backend/app/ai/budget.py, backend/app/config.py, backend/app/jobs/runner.py, backend/app/api/deps.py, backend/app/ai/structure_analysis.py</t>
+  </si>
+  <si>
+    <t>Committed and pushed phase-02c-ai-budget</t>
+  </si>
+  <si>
+    <t>AI-009: prompt-injection review; AI answer fields bounded; hostile-document tests</t>
+  </si>
+  <si>
+    <t>backend/app/ai/schemas.py, backend/app/ai/structure_analysis.py, backend/tests/test_prompt_injection.py</t>
+  </si>
+  <si>
+    <t>SEC-018: prompt injection / AI output abuse covered by AI-009's tests</t>
+  </si>
+  <si>
+    <t>AI-001, AI-005, AI-007, AI-009</t>
+  </si>
+  <si>
+    <t>Phase 2 gate: backend 817 passed/1 skipped, Vitest 117, Playwright 20; browser check in the throwaway stack - 'make the title red and delete “This draft paragraph”': title red at once, the paragraph kept and shown under Changes to review (struck through, with the instruction), notice + '1 AI change to review'; Accept removed it, reload kept it removed with nothing pending</t>
+  </si>
+  <si>
+    <t>full suites + manual browser check</t>
+  </si>
+  <si>
+    <t>DOCX-010: original Word package kept as an immutable, checksummed asset</t>
+  </si>
+  <si>
+    <t>backend/app/models/document.py, backend/app/services/document_service.py</t>
+  </si>
+  <si>
+    <t>DOCX-011: Word exports written into the original package; import report reflects what they keep</t>
+  </si>
+  <si>
+    <t>backend/app/export/docx_export.py, backend/app/fidelity/imports.py, backend/app/fidelity/docx_source.py, backend/app/fidelity/docx_detect.py, backend/app/fidelity/exports.py, backend/app/jobs/runner.py, backend/app/api/documents.py, backend/app/capabilities.py</t>
+  </si>
+  <si>
+    <t>TEST-023: independent package validation of every Word export</t>
+  </si>
+  <si>
+    <t>backend/app/export/package_check.py, backend/tests/test_package_check.py</t>
+  </si>
+  <si>
+    <t>DOCX-012: metadata preserved (core in the model, app/custom/labels via the original package)</t>
+  </si>
+  <si>
+    <t>DOCX-028: unchanged blocks keep their original XML in Word exports; server-side provenance; earlier sections follow page setup, header and page-number changes; lost sections reported; golden 13-kept-blocks + E2E.</t>
+  </si>
+  <si>
+    <t>backend/app/export/provenance.py, backend/app/export/docx_export.py, backend/app/parsers/docx.py, backend/app/models/document.py, backend/app/services/document_service.py, backend/app/fidelity/imports.py, backend/app/fidelity/exports.py, backend/app/capabilities.py, frontend/editor/tiptapToDocument.ts, frontend/e2e/kept-blocks.spec.ts, docs/docx/README.md</t>
+  </si>
+  <si>
+    <t>DOCX-028 committed and pushed as c8c2d27 (phase-03b-original-blocks).</t>
+  </si>
+  <si>
+    <t>DOCX-025: Word's hidden text stays hidden - hidden mark with Word's style resolution, editor shows it only on request, vanish in Word exports, left out of PDF with a note, consistent content checks.</t>
+  </si>
+  <si>
+    <t>backend/app/models/document.py, backend/app/parsers/docx_inline.py, backend/app/parsers/docx_styles.py, backend/app/parsers/docx.py, backend/app/fidelity/docx_detect.py, backend/app/fidelity/content.py, backend/app/fidelity/exports.py, backend/app/export/docx_export.py, backend/app/export/pdf_export.py, frontend/editor/hiddenText.ts, frontend/editor/EditorStatusBar.tsx, frontend/editor/DocumentEditorShell.tsx, frontend/app/globals.css</t>
+  </si>
+  <si>
+    <t>DOCX-025 committed and pushed as 7d1af86 (phase-03c-hidden-text).</t>
+  </si>
+  <si>
+    <t>DOCX-013 part 1: underline and strike styles, capitals, small capitals, spacing and raised/lowered text kept through import, editor, Word and PDF; paragraph-style formatting turned off by a run fixed.</t>
+  </si>
+  <si>
+    <t>backend/app/models/document.py, backend/app/parsers/docx_inline.py, backend/app/parsers/docx_styles.py, backend/app/parsers/docx.py, backend/app/export/docx_export.py, backend/app/export/pdf_export.py, backend/app/fidelity/*, frontend/editor/characterFormatting.ts, frontend/editor/tiptapToDocument.ts</t>
+  </si>
+  <si>
+    <t>backend 888 passed/1 skipped (tests/test_character_formatting.py 12); Vitest 128 (editor/characterFormatting.test.ts 3, golden round trip of 02); Playwright 22; tsc + eslint clean</t>
+  </si>
+  <si>
+    <t>DOCX-013 part 1 committed and pushed as 6619159 (phase-03d-character-formatting); part 2 next.</t>
+  </si>
+  <si>
+    <t>6619159</t>
+  </si>
+  <si>
+    <t>FID-007: reports follow the Word copy - kept while unchanged at import, rewritten losses named at export, unsafe links never copied back.</t>
+  </si>
+  <si>
+    <t>backend/app/fidelity/imports.py, backend/app/export/docx_export.py, backend/tests/test_copy_reports.py</t>
+  </si>
+  <si>
+    <t>DOCX-013 part 2: language kept; scale and effects named and kept while unchanged; brief §22 list is now supported, preserved or explicitly named.</t>
+  </si>
+  <si>
+    <t>backend/app/models/document.py, backend/app/parsers/docx_inline.py, backend/app/fidelity/docx_detect.py, frontend/editor/characterFormatting.ts</t>
+  </si>
+  <si>
+    <t>DOCX-013 done: part 1 6619159, part 2 d32c6a6 (phase-03e-copy-reports).</t>
+  </si>
+  <si>
+    <t>FID-007 committed and pushed as d32c6a6.</t>
+  </si>
+  <si>
+    <t>DOCX-014 part 1: right indent, shading, pagination controls, contextual spacing and direction kept through import, CSS, Word and PDF.</t>
+  </si>
+  <si>
+    <t>backend/app/models/document.py, backend/app/formatting/*, backend/app/parsers/docx_styles.py, backend/app/parsers/docx.py, backend/app/export/docx_export.py, backend/app/export/pdf_export.py</t>
+  </si>
+  <si>
+    <t>backend 903 passed/1 skipped (tests/test_paragraph_formatting.py 9); Vitest 129; Playwright 22; tsc + eslint clean</t>
+  </si>
+  <si>
+    <t>DOCX-014 part 1 committed and pushed as eade93e (phase-03f-paragraph-formatting); part 2 next.</t>
+  </si>
+  <si>
+    <t>eade93e</t>
+  </si>
+  <si>
+    <t>DOCX-014 part 2: paragraph borders and tab stops kept through import, CSS, Word and PDF; what the PDF and editor can't draw is named.</t>
+  </si>
+  <si>
+    <t>backend/app/formatting/values.py, backend/app/parsers/docx_styles.py, backend/app/export/docx_export.py, backend/app/export/pdf_export.py, backend/tests/test_paragraph_formatting.py</t>
+  </si>
+  <si>
+    <t>DOCX-014 done: part 1 eade93e, part 2 c158722 (phase-03g-borders-tab-stops).</t>
+  </si>
+  <si>
+    <t>DOCX-015 part 1a: section breaks are elements with their section's settings - imported, shown and paginated in the editor, written back into Word from the model.</t>
+  </si>
+  <si>
+    <t>backend/app/models/document.py, backend/app/parsers/docx.py, backend/app/export/docx_export.py, frontend/editor/sectionBreak.ts, frontend/editor/pagination.ts</t>
+  </si>
+  <si>
+    <t>tests/test_docx_detect.py::test_a_section_break_breaks_the_page_only_where_word_does; tests/test_sections.py (6); frontend/editor/sectionBreak.test.ts (3); backend 919 passed/1 skipped; Vitest 132; Playwright 22</t>
+  </si>
+  <si>
+    <t>DOCX-015 part 1a committed and pushed as 047685d (phase-03h-section-breaks); part 1b next.</t>
+  </si>
+  <si>
     <t>047685d</t>
   </si>
   <si>
-    <t>Fixed: a section's w:type describes how THAT section starts (ECMA-376 17.6.22) - the importer used the ending section's own type, so a continuous break became a page break and continuous-&gt;new-page put the break between the wrong sections (probe confirmed). Now the next section's type decides. Per-section differences are reported (FID-002). Remaining: sections as a first-class model concept (orientation/margins/columns/headers per section, page-number restart) and export of several sections.; With DOCX-011 the last section's properties (columns, page numbering, borders, line numbers, vertical alignment, header/footer variants) are kept in Word exports; earlier sections' are still reported lost.; DOCX-028: earlier sections now survive in Word exports while their ending paragraph is unchanged; page setup/header/page-number changes apply to them; a lost one is reported (export.docx.section_lost). Modelling sections is still this task.</t>
-  </si>
-  <si>
-    <t>DOCX-016</t>
-  </si>
-  <si>
-    <t>Numbering engine</t>
-  </si>
-  <si>
-    <t>Decimal/roman/alpha/bullets, custom prefixes/suffixes, start, restart, continuation, multilevel, numId/abstractNum/ilvl, indentation.</t>
-  </si>
-  <si>
-    <t>tests/test_docx_numbering.py</t>
-  </si>
-  <si>
-    <t>Done so far: top-level list number format (decimal/roman/letters), start value (lvl start + lvlOverride/startOverride) and continuation across interrupting paragraphs imported into Element.numbering and written back to Word (per-level formats, startOverride) and PDF; empty numbered items keep counting. Reported, not kept: custom labels ('Чл. 1.', '(a)'), multi-level labels ('1.1'), numbered headings baked into text. Remaining: prefixes/suffixes, multilevel numbering model, restart semantics per level, indentation.</t>
-  </si>
-  <si>
-    <t>AUD-04</t>
-  </si>
-  <si>
-    <t>DOCX-017</t>
-  </si>
-  <si>
-    <t>Table engine</t>
-  </si>
-  <si>
-    <t>No forced header or Table Grid; widths, heights, margins, borders, shading, v-align, nested tables, repeated header rows, table styles.</t>
-  </si>
-  <si>
-    <t>From EDIT-011 (2026-09-27): add per-cell alignment and column widths to the model (the editor's cell align/colwidth, Word tcW/tblGrid, PDF colWidths); until then the editor names them as not kept.</t>
-  </si>
-  <si>
-    <t>DOCX-018</t>
-  </si>
-  <si>
-    <t>Images</t>
-  </si>
-  <si>
-    <t>Alt text exported; crop, rotation, anchor, wrap, position preserved; WEBP converted on export.</t>
-  </si>
-  <si>
-    <t>Alt text + title now exported (docPr descr/title) with DOCX-001; crop, rotation, WEBP still open.</t>
-  </si>
-  <si>
-    <t>DOCX-019</t>
-  </si>
-  <si>
-    <t>Drawings and text boxes preserved</t>
-  </si>
-  <si>
-    <t>Anchored drawings, text boxes, shapes kept even when not editable.</t>
-  </si>
-  <si>
-    <t>DOCX-028: text boxes and drawings in unchanged paragraphs are copied as they are (grouped with their anchor paragraph).</t>
-  </si>
-  <si>
-    <t>DOCX-020</t>
-  </si>
-  <si>
-    <t>Fields</t>
-  </si>
-  <si>
-    <t>Code/result/relationship; header STYLEREF/DATE live; TOC kept; CITATION/BIBLIOGRAPHY sources preserved; no 'Invalid source specified.'</t>
-  </si>
-  <si>
-    <t>backend/parsers, export</t>
-  </si>
-  <si>
-    <t>DOCX-028: field codes in unchanged blocks are copied as they are; a field spanning paragraphs is never copied half (self-contained check).</t>
-  </si>
-  <si>
-    <t>AUD-18</t>
-  </si>
-  <si>
-    <t>DOCX-021</t>
-  </si>
-  <si>
-    <t>Comment threads</t>
-  </si>
-  <si>
-    <t>Replies, resolved state, authors, ranges preserved (commentsExtended, people).</t>
-  </si>
-  <si>
-    <t>AUD-06</t>
-  </si>
-  <si>
-    <t>DOCX-022</t>
-  </si>
-  <si>
-    <t>Tracked changes preserved</t>
-  </si>
-  <si>
-    <t>Not silently accepted; explicit choice.</t>
-  </si>
-  <si>
-    <t>DOCX-028: blocks holding tracked changes are never copied (always written anew, accepted), so this task's explicit choice is still needed.</t>
-  </si>
-  <si>
-    <t>DOCX-023</t>
-  </si>
-  <si>
-    <t>Content controls preserved</t>
-  </si>
-  <si>
-    <t>w:sdt of every kind kept with its properties.</t>
-  </si>
-  <si>
-    <t>DOCX-028: content controls in unchanged blocks are copied with their properties (E2E proves it through the editor); written anew they are unwrapped (reported lossy at import).</t>
-  </si>
-  <si>
-    <t>DOCX-024</t>
-  </si>
-  <si>
-    <t>Real footnotes and endnotes</t>
-  </si>
-  <si>
-    <t>Notes stay notes on export.</t>
-  </si>
-  <si>
-    <t>DOCX-025</t>
-  </si>
-  <si>
-    <t>Hidden text stays hidden</t>
-  </si>
-  <si>
-    <t>Imported hidden text is kept hidden, shown only on request.</t>
-  </si>
-  <si>
-    <t>MarkType.HIDDEN (appended; no existing mark order changes). Importer resolves w:vanish as Word does: run, character style, paragraph style (the default paragraph style when none), docDefaults; webHidden stays visible; an explicit vanish=0 shows text in a hidden style. The detector uses the default paragraph style the same way and names hidden text as kept hidden (DETECTED_PRESERVED, not a content change). Editor: non-inclusive hidden mark (editor/hiddenText.ts; Word's display:none paste stays hidden), hidden by CSS unless .show-hidden; status bar 'Show hidden text (N words)' toggles it and re-paginates; the Structure panel leaves hidden text out of headings. Word export writes w:vanish (copied blocks keep theirs); PDF doesn't print hidden runs, export.pdf.hidden_text names the word count, and the PDF content check compares visible words (document_words(visible_only=True)); Word-side checks count hidden text on both sides. Golden 02-rich-text gained a hidden sentence (editor round trip in Vitest).</t>
-  </si>
-  <si>
-    <t>backend 876 passed/1 skipped (tests/test_hidden_text.py 7: import resolution, default paragraph style, report, upload + content check + editor save, Word export round trip, PDF text + note + check); Vitest 125 (editor/hiddenText.test.tsx 6, golden round trip of 02); Playwright 22 (e2e/hidden-text.spec.ts: hidden until asked, dotted line when shown, vanish in the Word export); tsc + eslint clean</t>
-  </si>
-  <si>
-    <t>backend/parsers, frontend</t>
-  </si>
-  <si>
-    <t>7d1af86</t>
-  </si>
-  <si>
-    <t>DOCX-028: vanish survives in unchanged blocks only; the model still shows hidden text as ordinary text - next task.</t>
-  </si>
-  <si>
-    <t>DOCX-026</t>
-  </si>
-  <si>
-    <t>Hyperlink policy and no silent autolink</t>
-  </si>
-  <si>
-    <t>Plain-text addresses not turned into links by default; file:/UNC reported.</t>
-  </si>
-  <si>
-    <t>tests/test_docx_detect.py::test_unsafe_links_and_spacing_paragraphs_are_reported</t>
-  </si>
-  <si>
-    <t>Done: links to unsafe addresses (javascript:, file:, UNC...) are kept as plain text and reported (docx.link.unsafe); plain-text addresses turned into links are reported (docx.autolink). Remaining: stop autolinking by default (a setting), per the task.</t>
-  </si>
-  <si>
-    <t>AUD-03,AUD-13</t>
-  </si>
-  <si>
-    <t>FMT-004</t>
-  </si>
-  <si>
-    <t>Render-spec defaults respect the source</t>
-  </si>
-  <si>
-    <t>Imported Word styles are not overridden by defaults (headings not forced bold).</t>
-  </si>
-  <si>
-    <t>backend/formatting</t>
-  </si>
-  <si>
-    <t>TEST-020</t>
-  </si>
-  <si>
-    <t>Word-authored fixtures in the repository</t>
-  </si>
-  <si>
-    <t>20 synthetic Word-authored fixtures, scrubbed of identifying metadata.</t>
-  </si>
-  <si>
-    <t>backend/tests/fixtures/word</t>
-  </si>
-  <si>
-    <t>TEST-021</t>
-  </si>
-  <si>
-    <t>Expected-loss manifests in CI</t>
-  </si>
-  <si>
-    <t>expected-loss.json per fixture; CI compares actual vs expected.</t>
-  </si>
-  <si>
-    <t>TEST-022</t>
-  </si>
-  <si>
-    <t>True fidelity test</t>
-  </si>
-  <si>
-    <t>SOURCE -&gt; import -&gt; format -&gt; editor save -&gt; export -&gt; reimport -&gt; compare SOURCE vs RESULT: content, formatting, metadata, structure separately.</t>
-  </si>
-  <si>
-    <t>TEST-023</t>
-  </si>
-  <si>
-    <t>Independent validation</t>
-  </si>
-  <si>
-    <t>OOXML schema validation, Word when available, docx2python; pdftotext/PyMuPDF for PDF.</t>
-  </si>
-  <si>
-    <t>app/export/package_check.py: an independent package check (zip read directly): well-formed parts, content types, relationships resolving, relationship ids used, defined styles/lists/comments. Found a real defect on first run (python-docx's add_comment refers to an undefined CommentReference style; exports now define it). Every golden export passes, fresh and into its original.</t>
-  </si>
-  <si>
-    <t>tests/test_package_check.py (13)</t>
-  </si>
-  <si>
-    <t>The docx skill's XSD validator needs defusedxml (not installed; installing needs a download) - schema-level validation remains open.</t>
-  </si>
-  <si>
-    <t>DOCX-027</t>
-  </si>
-  <si>
-    <t>Importer builds nested blocks</t>
-  </si>
-  <si>
-    <t>Use TableCell.blocks / ListItem.blocks on import: pictures, lists (with bullets) and nested tables inside cells, pictures inside list items - instead of dropping or flattening them.</t>
-  </si>
-  <si>
-    <t>AUD-01,AUD-03,AUD-08</t>
-  </si>
-  <si>
-    <t>DOCX-028</t>
-  </si>
-  <si>
-    <t>Unchanged blocks keep their original XML in Word exports</t>
-  </si>
-  <si>
-    <t>Blocks the user didn't change are written back as their original XML (fields, content controls, run-level formatting the model can't hold, bookmarks), changed ones regenerated; needs block provenance from the importer and fingerprints.</t>
-  </si>
-  <si>
-    <t>Importer records each top-level element's body children (Element.sourceBlocks: list items, drop caps, derived page breaks); an upload with a kept file stamps content+look fingerprints (Element.sourceHash, app/export/provenance.py: own/kind/body/nested resolved styles; page breaks have no look). docx_export._copy_plan groups elements with their children (uncovered children join the group before) and copies a group verbatim when every element is unchanged, together and in original order, children contiguous, XML self-contained (no tracked changes/note refs/altChunk; balanced fields, bookmarks, comment ranges); everything else is written anew. Provenance is server-side (keep_provenance on PUT /content). Page setup now runs after the body: changed size/margins reach every kept section (orientation kept, landscape turned), a changed main header is rewritten where Word shows it (link to previous), page numbers left out/asked for apply to every section. export.docx.section_lost (LOSSY) names sections lost with a changed paragraph; import report: earlier sections' setup/headers kept while unchanged; PDF names them Word-only. All 13 golden documents stamped + exported into their originals: sound packages, content verified (12-complex rewrites only the footnote paragraph and the note, by design).</t>
-  </si>
-  <si>
-    <t>backend 869 passed/1 skipped (tests/test_original_blocks.py 26 incl. 13 golden; test_source_package.py rewritten claims with export proof; test_golden_documents.py 13 files); Vitest 119 (editor round trip of 13-kept-blocks); Playwright 21 (e2e/kept-blocks.spec.ts: edit in the real editor, untouched paragraphs keep content control, double underline, landscape section); tsc + eslint clean</t>
-  </si>
-  <si>
-    <t>c8c2d27</t>
-  </si>
-  <si>
-    <t>Follow-up of DOCX-011 (package-level patch writer).; Known limit: any restyle (template, instruction) changes the body look, so every block but page breaks is written anew; follow-up DOCX-029. Sections survive only with their ending paragraph until DOCX-015 models them.</t>
-  </si>
-  <si>
-    <t>DOCX-029</t>
-  </si>
-  <si>
-    <t>Restyled blocks keep their original XML where nothing conflicts</t>
-  </si>
-  <si>
-    <t>After a template or instruction restyles a kind of block, copy a block's original XML when its paragraph style is the Word style the export rewrites for that kind and its direct formatting (pPr/rPr) sets none of the properties that changed; today any restyle writes every block anew (content controls, double underline etc. then lost, as the import report says).</t>
-  </si>
-  <si>
-    <t>Found while finishing DOCX-028: the look is part of the fingerprint so the export never shows a stale look.</t>
-  </si>
-  <si>
-    <t>FID-007</t>
-  </si>
-  <si>
-    <t>Reports follow the Word copy</t>
-  </si>
-  <si>
-    <t>With the original kept, the import report names what lives in blocks as kept in the Word export while the paragraph is unchanged, and an export that writes such a block anew names what it lost; a copy never brings back a link the app doesn't allow.</t>
-  </si>
-  <si>
-    <t>fidelity/imports.py KEPT_WHILE_UNCHANGED (content controls, text boxes, charts/shapes/SmartArt, objects, picture crop/rotation/floating, drop caps, empty paragraphs, approximated underlines, character scale, text effects, RTL) -&gt; detected_not_editable 'kept while the paragraph isn't changed or restyled'; docx_export._copy_plan returns rewritten groups, _lost_in/_rewritten_losses -&gt; export.docx.rewritten_blocks (LOSSY, count, kinds incl. proofing exclusions); _safe_links keeps groups with unsafe links (relationships or HYPERLINK fields) from being copied; the PDF's Word-only note covers the features.</t>
-  </si>
-  <si>
-    <t>tests/test_copy_reports.py (6): kept while unchanged at import, rewritten losses named (content controls, stretched text), unsafe javascript: link never copied back, PDF word-only; backend 894 passed/1 skipped; Playwright 22</t>
-  </si>
-  <si>
-    <t>Generalises DOCX-028's section handling (export.docx.section_lost) to everything the model doesn't hold inside blocks.</t>
-  </si>
-  <si>
-    <t>SEC-010</t>
-  </si>
-  <si>
-    <t>Malformed DOCX -&gt; safe 4xx</t>
-  </si>
-  <si>
-    <t>XML/zip/structure errors map to invalid_file; fuzz corpus shows no 500.</t>
-  </si>
-  <si>
-    <t>AUD-12</t>
-  </si>
-  <si>
-    <t>SEC-011</t>
-  </si>
-  <si>
-    <t>Malformed PDF -&gt; safe 4xx</t>
-  </si>
-  <si>
-    <t>Verified with a fuzz corpus.</t>
-  </si>
-  <si>
-    <t>SEC-012</t>
-  </si>
-  <si>
-    <t>Image resource limits</t>
-  </si>
-  <si>
-    <t>Compressed and decompressed size, pixel count, width, height, images per document, total bytes, format allowlist; rejected before rasterisation.</t>
-  </si>
-  <si>
-    <t>backend/security</t>
-  </si>
-  <si>
-    <t>AUD-09</t>
-  </si>
-  <si>
-    <t>SEC-013</t>
-  </si>
-  <si>
-    <t>PDF bombs, huge XML, decompression limits</t>
-  </si>
-  <si>
-    <t>Reviewed and tested limits.</t>
-  </si>
-  <si>
-    <t>SEC-014</t>
-  </si>
-  <si>
-    <t>Href policy</t>
-  </si>
-  <si>
-    <t>Server-side scheme allowlist; javascript:/data:/vbscript:/file: never exported as active links.</t>
-  </si>
-  <si>
-    <t>backend/models, export</t>
-  </si>
-  <si>
-    <t>AUD-13</t>
-  </si>
-  <si>
-    <t>SEC-015</t>
-  </si>
-  <si>
-    <t>Field instruction allowlist</t>
-  </si>
-  <si>
-    <t>No DDE/INCLUDETEXT/INCLUDEPICTURE/external fields accepted from clients or exported.</t>
-  </si>
-  <si>
-    <t>SEC-016</t>
-  </si>
-  <si>
-    <t>External relationships policy</t>
-  </si>
-  <si>
-    <t>No arbitrary external targets in exports.</t>
-  </si>
-  <si>
-    <t>SEC-017</t>
-  </si>
-  <si>
-    <t>Malicious SVG</t>
-  </si>
-  <si>
-    <t>Verified refused everywhere.</t>
-  </si>
-  <si>
-    <t>SEC-018</t>
-  </si>
-  <si>
-    <t>Prompt injection / AI output abuse</t>
-  </si>
-  <si>
-    <t>Tests with hostile documents; outputs validated.</t>
-  </si>
-  <si>
-    <t>Hostile-document tests: the document can't close its fence; out-of-bounds answers refused and fall back; an instruction steered by the document deletes nothing (proposals only) and a CSS break-out value is dropped; style-analysis flags on unknown elements dropped (see AI-009).</t>
-  </si>
-  <si>
-    <t>tests/test_prompt_injection.py</t>
-  </si>
-  <si>
-    <t>SEC-019</t>
-  </si>
-  <si>
-    <t>Error envelope audit</t>
-  </si>
-  <si>
-    <t>Every error {code, message, details, request_id}; no stack traces to users.</t>
-  </si>
-  <si>
-    <t>backend/api</t>
-  </si>
-  <si>
-    <t>SEC-020</t>
-  </si>
-  <si>
-    <t>CSP without 'unsafe-inline' scripts</t>
-  </si>
-  <si>
-    <t>Nonce-based CSP for the Next.js app.</t>
-  </si>
-  <si>
-    <t>TEST-030</t>
-  </si>
-  <si>
-    <t>Security regression suite</t>
-  </si>
-  <si>
-    <t>Fuzz corpus, pixel bombs, href/field policy, IDOR, CSRF.</t>
-  </si>
-  <si>
-    <t>SEC-010,SEC-012,SEC-014,SEC-015</t>
-  </si>
-  <si>
-    <t>AUD-09,AUD-12,AUD-13</t>
-  </si>
-  <si>
-    <t>SEC-021</t>
-  </si>
-  <si>
-    <t>Sensitivity-label metadata in the public repository</t>
-  </si>
-  <si>
-    <t>корекции.docx (committed in 5f2bf9e, pushed) carries 8 MSIP_Label_* custom properties incl. the organisation's tenant SiteId (label: Microsoft default 'General' family, no content marking). Options: leave; scrub the file in a new commit (HEAD only); purge from history (force-push).</t>
-  </si>
-  <si>
-    <t>repository history</t>
-  </si>
-  <si>
-    <t>Needs Boril: the choice involves his organisation's label and possibly rewriting pushed history. The tracker tools now strip MSIP labels on every write; the pre-push scan flags them.</t>
-  </si>
-  <si>
-    <t>SEC-022</t>
-  </si>
-  <si>
-    <t>Formatting rule values can't break out of a style</t>
-  </si>
-  <si>
-    <t>A rule value reaches the editor's style attribute, Word and PDF styles as text. The element-style and page-setting endpoints accepted any string (e.g. 'center;background-image:url(...)'), the AI instruction path too (FMT-005): CSS injection into every viewer's editor.</t>
-  </si>
-  <si>
-    <t>app/formatting/values.py: clean_rule_value per property (the StyleSystem's limits: choices, true/false, one safe font name, renderable colours, bounded numbers with known units, header/footer text &lt;=500). Refused with 422 by the element-style and page-setting endpoints (schemas RuleValue); instruction rules and set_style operations with such values dropped (FMT-005), validate_operations refuses them; stored rules no renderer can use are skipped at resolve (engine._usable) so old documents can't carry them either. All 177 default/template rules pass unchanged.</t>
-  </si>
-  <si>
-    <t>tests/test_rule_values.py (34 cases incl. API 422, stored-rule skip, instruction drop)</t>
-  </si>
-  <si>
-    <t>Found 2026-09-27 while mapping editor alignment (EDIT-008); probe confirmed the raw value in resolvedStyles.</t>
-  </si>
-  <si>
-    <t>PERF-001</t>
-  </si>
-  <si>
-    <t>Linear DOCX table export</t>
-  </si>
-  <si>
-    <t>500x8 table under a recorded threshold (baseline 321 s).</t>
-  </si>
-  <si>
-    <t>AUD-10</t>
-  </si>
-  <si>
-    <t>PERF-002</t>
-  </si>
-  <si>
-    <t>Benchmarks recorded</t>
-  </si>
-  <si>
-    <t>Baseline and current measurements in the PERFORMANCE sheet.</t>
-  </si>
-  <si>
-    <t>tests/perf</t>
-  </si>
-  <si>
-    <t>PERF-003</t>
-  </si>
-  <si>
-    <t>Delta autosave</t>
-  </si>
-  <si>
-    <t>Change-aware patches with a threshold strategy; whole document only when needed.</t>
-  </si>
-  <si>
-    <t>frontend/editor, backend/api</t>
-  </si>
-  <si>
-    <t>PERF-004</t>
-  </si>
-  <si>
-    <t>Bounded, compressed version history</t>
-  </si>
-  <si>
-    <t>Editor history separate from persisted versions; compression/deltas; asset references.</t>
-  </si>
-  <si>
-    <t>PERF-005</t>
-  </si>
-  <si>
-    <t>Editor at 5k-12k blocks</t>
-  </si>
-  <si>
-    <t>Typing latency measured and improved.</t>
-  </si>
-  <si>
-    <t>PERF-006</t>
-  </si>
-  <si>
-    <t>JSON without ASCII escaping</t>
-  </si>
-  <si>
-    <t>Document JSON stored and sent as UTF-8.</t>
-  </si>
-  <si>
-    <t>backend/db</t>
-  </si>
-  <si>
-    <t>PERF-007</t>
-  </si>
-  <si>
-    <t>Safe size limits recorded</t>
-  </si>
-  <si>
-    <t>User-facing maximum sizes, job timeouts, resource ceilings documented and enforced.</t>
-  </si>
-  <si>
-    <t>backend/config</t>
-  </si>
-  <si>
-    <t>AUD-09,AUD-10</t>
-  </si>
-  <si>
-    <t>ACCT-001</t>
-  </si>
-  <si>
-    <t>E-mail sender abstraction</t>
-  </si>
-  <si>
-    <t>SMTP provider + development outbox; no secrets in logs.</t>
-  </si>
-  <si>
-    <t>AUD-14</t>
-  </si>
-  <si>
-    <t>ACCT-002</t>
-  </si>
-  <si>
-    <t>Password reset</t>
-  </si>
-  <si>
-    <t>Single-use, expiring, hashed tokens; rate-limited; no account enumeration.</t>
-  </si>
-  <si>
-    <t>backend/api, frontend</t>
-  </si>
-  <si>
-    <t>ACCT-003</t>
-  </si>
-  <si>
-    <t>E-mail verification</t>
-  </si>
-  <si>
-    <t>Verification tokens and state.</t>
-  </si>
-  <si>
-    <t>ACCT-004</t>
-  </si>
-  <si>
-    <t>Password change</t>
-  </si>
-  <si>
-    <t>Current password required; other sessions revoked.</t>
-  </si>
-  <si>
-    <t>ACCT-005</t>
-  </si>
-  <si>
-    <t>Account deletion</t>
-  </si>
-  <si>
-    <t>Cascading policy: documents, versions, assets, exports, sessions, jobs, usage.</t>
-  </si>
-  <si>
-    <t>ACCT-006</t>
-  </si>
-  <si>
-    <t>Session revocation and cleanup</t>
-  </si>
-  <si>
-    <t>Sign out everywhere; expired/revoked session sweep.</t>
-  </si>
-  <si>
-    <t>ACCT-007</t>
-  </si>
-  <si>
-    <t>Suspicious login handling</t>
-  </si>
-  <si>
-    <t>Lockout and notification strategy.</t>
-  </si>
-  <si>
-    <t>PLAN-001</t>
-  </si>
-  <si>
-    <t>Usage units</t>
-  </si>
-  <si>
-    <t>Documents, exports, PDF pages, OCR pages, translation characters, AI operations, storage, batch jobs.</t>
-  </si>
-  <si>
-    <t>backend/billing</t>
-  </si>
-  <si>
-    <t>AUD-11</t>
-  </si>
-  <si>
-    <t>PLAN-002</t>
-  </si>
-  <si>
-    <t>Configurable plan defaults</t>
-  </si>
-  <si>
-    <t>Free/Pro/Business initial hypotheses as configuration, never hardcoded.</t>
-  </si>
-  <si>
-    <t>PLAN-003</t>
-  </si>
-  <si>
-    <t>Atomic entitlement checks</t>
-  </si>
-  <si>
-    <t>Reservation/locking; concurrency test proves limits hold.</t>
-  </si>
-  <si>
-    <t>PLAN-004</t>
-  </si>
-  <si>
-    <t>Stripe flows review</t>
-  </si>
-  <si>
-    <t>Checkout, portal, upgrade, downgrade, cancel, renewal, failed payment, webhook idempotency.</t>
-  </si>
-  <si>
-    <t>PLAN-005</t>
-  </si>
-  <si>
-    <t>Storage metering including history</t>
-  </si>
-  <si>
-    <t>History and autosave growth counted.</t>
-  </si>
-  <si>
-    <t>AUD-11,AUD-16</t>
-  </si>
-  <si>
-    <t>PDF-010</t>
-  </si>
-  <si>
-    <t>Geometry-aware PDF parser</t>
-  </si>
-  <si>
-    <t>Chars, fonts, sizes, colours, lines, rectangles, images, links, annotations, outlines, forms, metadata, rotation, page boxes.</t>
-  </si>
-  <si>
-    <t>backend/parsers/pdf</t>
-  </si>
-  <si>
-    <t>PDF-011</t>
-  </si>
-  <si>
-    <t>Page classifier</t>
-  </si>
-  <si>
-    <t>TEXT / SCANNED / HYBRID per page with evidence.</t>
-  </si>
-  <si>
-    <t>PDF-012</t>
-  </si>
-  <si>
-    <t>PDF inspection report</t>
-  </si>
-  <si>
-    <t>What the parser found, per page.</t>
-  </si>
-  <si>
-    <t>P2E-001</t>
-  </si>
-  <si>
-    <t>Layout primitives where PDF needs them</t>
-  </si>
-  <si>
-    <t>Page, block, bbox, rotation, confidence, provenance.</t>
-  </si>
-  <si>
-    <t>P2E-002</t>
-  </si>
-  <si>
-    <t>Structure reconstruction</t>
-  </si>
-  <si>
-    <t>Reading order, lines, paragraphs, headings, lists, captions, header/footer bands, columns.</t>
-  </si>
-  <si>
-    <t>backend/pdf</t>
-  </si>
-  <si>
-    <t>P2E-003</t>
-  </si>
-  <si>
-    <t>Images with position</t>
-  </si>
-  <si>
-    <t>Extracted images kept with bbox.</t>
-  </si>
-  <si>
-    <t>P2E-004</t>
-  </si>
-  <si>
-    <t>Tables from PDF</t>
-  </si>
-  <si>
-    <t>Ruling lines and alignment.</t>
-  </si>
-  <si>
-    <t>P2E-005</t>
-  </si>
-  <si>
-    <t>Confidence and conversion report</t>
-  </si>
-  <si>
-    <t>Per element confidence; issues reported; never silent removal.</t>
-  </si>
-  <si>
-    <t>P2E-006</t>
-  </si>
-  <si>
-    <t>OCR provider abstraction</t>
-  </si>
-  <si>
-    <t>Interface (text, confidence, bbox, page, language/script); implementation(s); OCR output untrusted.</t>
-  </si>
-  <si>
-    <t>backend/ocr</t>
-  </si>
-  <si>
-    <t>P2E-007</t>
-  </si>
-  <si>
-    <t>Imported-from-PDF version and UX</t>
-  </si>
-  <si>
-    <t>Editable document vs layout-focused choice; confidence shown.</t>
-  </si>
-  <si>
-    <t>frontend, backend</t>
-  </si>
-  <si>
-    <t>P2E-008</t>
-  </si>
-  <si>
-    <t>PDF fixtures and tests</t>
-  </si>
-  <si>
-    <t>Text, scanned, hybrid, tables, columns, multilingual.</t>
-  </si>
-  <si>
-    <t>P2E-020</t>
-  </si>
-  <si>
-    <t>Layout-preserving architecture</t>
-  </si>
-  <si>
-    <t>Frames/anchors model hooks and design doc.</t>
-  </si>
-  <si>
-    <t>docs, backend/models</t>
-  </si>
-  <si>
-    <t>PDF-020</t>
-  </si>
-  <si>
-    <t>PDF page operations service</t>
-  </si>
-  <si>
-    <t>Reorder, rotate, delete, duplicate, extract, split, merge as a separate service.</t>
-  </si>
-  <si>
-    <t>TRAN-001</t>
-  </si>
-  <si>
-    <t>Segments and tag protocol</t>
-  </si>
-  <si>
-    <t>Segments keep element/run ids, marks, placeholders; never one giant string.</t>
-  </si>
-  <si>
-    <t>backend/translation</t>
-  </si>
-  <si>
-    <t>TRAN-002</t>
-  </si>
-  <si>
-    <t>TranslationProvider abstraction</t>
-  </si>
-  <si>
-    <t>AI provider implementation + deterministic test provider.</t>
-  </si>
-  <si>
-    <t>TRAN-003</t>
-  </si>
-  <si>
-    <t>Translation validation</t>
-  </si>
-  <si>
-    <t>Tags, numbers, units, dates, percentages, identifiers, glossary terms.</t>
-  </si>
-  <si>
-    <t>TRAN-004</t>
-  </si>
-  <si>
-    <t>Glossary and terminology lock</t>
-  </si>
-  <si>
-    <t>Source/target term, domain, locked, case-sensitive.</t>
-  </si>
-  <si>
-    <t>backend/translation, db</t>
-  </si>
-  <si>
-    <t>TRAN-005</t>
-  </si>
-  <si>
-    <t>Selection/paragraph/block translation proposals</t>
-  </si>
-  <si>
-    <t>Preview; accept/reject; undo.</t>
-  </si>
-  <si>
-    <t>TRAN-003,REV-001</t>
-  </si>
-  <si>
-    <t>TRAN-006</t>
-  </si>
-  <si>
-    <t>Whole-document translated version</t>
-  </si>
-  <si>
-    <t>Source kept; translated copy linked.</t>
-  </si>
-  <si>
-    <t>TRAN-007</t>
-  </si>
-  <si>
-    <t>Language, script, direction metadata</t>
-  </si>
-  <si>
-    <t>Auto-detect + manual override.</t>
-  </si>
-  <si>
-    <t>TRAN-008</t>
-  </si>
-  <si>
-    <t>Translation UX</t>
-  </si>
-  <si>
-    <t>Toolbar/context Translate, target language, preview, accept/reject; 'AI-assisted translation - review required'.</t>
-  </si>
-  <si>
-    <t>TRAN-009</t>
-  </si>
-  <si>
-    <t>Translation metering</t>
-  </si>
-  <si>
-    <t>Translation characters as a usage unit.</t>
-  </si>
-  <si>
-    <t>TRAN-010</t>
-  </si>
-  <si>
-    <t>Translation tests</t>
-  </si>
-  <si>
-    <t>Formatting preservation, validation, versions.</t>
-  </si>
-  <si>
-    <t>FONT-001</t>
-  </si>
-  <si>
-    <t>Font catalogue with Unicode coverage</t>
-  </si>
-  <si>
-    <t>fontTools cmap coverage per script, metrics, embeddability.</t>
-  </si>
-  <si>
-    <t>backend/fonts</t>
-  </si>
-  <si>
-    <t>AUD-17</t>
-  </si>
-  <si>
-    <t>FONT-002</t>
-  </si>
-  <si>
-    <t>FontResolver</t>
-  </si>
-  <si>
-    <t>Script segmentation, coverage, fallback chain, embedding, RTL; deterministic first, AI suggestion validated.</t>
-  </si>
-  <si>
-    <t>FONT-003</t>
-  </si>
-  <si>
-    <t>Multilingual PDF rendering</t>
-  </si>
-  <si>
-    <t>Shaping for Arabic/Hebrew/Devanagari, bidi, CJK fonts, emoji handled gracefully.</t>
-  </si>
-  <si>
-    <t>FONT-004</t>
-  </si>
-  <si>
-    <t>DOCX per-script fonts</t>
-  </si>
-  <si>
-    <t>w:rFonts ascii/hAnsi/eastAsia/cs, w:lang, rtl/bidi.</t>
-  </si>
-  <si>
-    <t>FONT-005</t>
-  </si>
-  <si>
-    <t>Editor fallback stacks</t>
-  </si>
-  <si>
-    <t>CSS stacks from the resolver.</t>
-  </si>
-  <si>
-    <t>FONT-006</t>
-  </si>
-  <si>
-    <t>Multilingual tests</t>
-  </si>
-  <si>
-    <t>Script matrix x editor/DOCX/PDF with pdftotext and rendering.</t>
-  </si>
-  <si>
-    <t>FMT-001</t>
-  </si>
-  <si>
-    <t>Style extraction completeness</t>
-  </si>
-  <si>
-    <t>Page setup, margins, fonts, headings, lists, tables, captions, headers/footers, spacing, numbering, colours.</t>
-  </si>
-  <si>
-    <t>FMT-002</t>
-  </si>
-  <si>
-    <t>Semantic mapping validated</t>
-  </si>
-  <si>
-    <t>AI classifies/maps, engine applies; validation.</t>
-  </si>
-  <si>
-    <t>FMT-003</t>
-  </si>
-  <si>
-    <t>Before/after for Format by Example</t>
-  </si>
-  <si>
-    <t>Preview before saving a template.</t>
-  </si>
-  <si>
-    <t>FMT-005</t>
-  </si>
-  <si>
-    <t>Rule value validation</t>
-  </si>
-  <si>
-    <t>Instruction-path values validated before reaching CSS/export.</t>
-  </si>
-  <si>
-    <t>Instruction rules and set_style operations go through values.clean_rule_value: invalid ones dropped, normalised values stored (see SEC-022).</t>
-  </si>
-  <si>
-    <t>tests/test_rule_values.py::test_instructions_cannot_carry_such_values</t>
-  </si>
-  <si>
-    <t>HLTH-001</t>
-  </si>
-  <si>
-    <t>Health 2.0 checks</t>
-  </si>
-  <si>
-    <t>Alt text, hidden text, mixed language, unsupported features, section inconsistency, broken lists, empty paragraphs, layout anomalies, duplicated formatting, broken links.</t>
-  </si>
-  <si>
-    <t>HLTH-002</t>
-  </si>
-  <si>
-    <t>Deterministic fixes with preview</t>
-  </si>
-  <si>
-    <t>Fix proposals through the change model.</t>
-  </si>
-  <si>
-    <t>HLTH-003</t>
-  </si>
-  <si>
-    <t>AI explanations only</t>
-  </si>
-  <si>
-    <t>AI explains issues; never scores.</t>
-  </si>
-  <si>
-    <t>REV-002</t>
-  </si>
-  <si>
-    <t>Review Changes UI</t>
-  </si>
-  <si>
-    <t>Categories FORMAT/STRUCTURE/CONTENT/METADATA/PRESERVATION/TRANSLATION.</t>
-  </si>
-  <si>
-    <t>REV-003</t>
-  </si>
-  <si>
-    <t>Content changes need acceptance</t>
-  </si>
-  <si>
-    <t>Enforced server-side.</t>
-  </si>
-  <si>
-    <t>backend</t>
-  </si>
-  <si>
-    <t>REV-004</t>
-  </si>
-  <si>
-    <t>Repair</t>
-  </si>
-  <si>
-    <t>Detected issue, proposed fix, preview, apply.</t>
-  </si>
-  <si>
-    <t>REV-005</t>
-  </si>
-  <si>
-    <t>Clean copy</t>
-  </si>
-  <si>
-    <t>Explicit: remove comments, accept tracked changes, remove hidden text, remove metadata, normalise formatting.</t>
-  </si>
-  <si>
-    <t>FEAT-001</t>
-  </si>
-  <si>
-    <t>Batch formatting</t>
-  </si>
-  <si>
-    <t>One template/reference over many documents as jobs.</t>
-  </si>
-  <si>
-    <t>backend/jobs</t>
-  </si>
-  <si>
-    <t>FEAT-002</t>
-  </si>
-  <si>
-    <t>Batch export</t>
-  </si>
-  <si>
-    <t>Many documents to a zip.</t>
-  </si>
-  <si>
-    <t>FEAT-003</t>
-  </si>
-  <si>
-    <t>Batch translation</t>
-  </si>
-  <si>
-    <t>After the translation MVP.</t>
-  </si>
-  <si>
-    <t>FEAT-010</t>
-  </si>
-  <si>
-    <t>Accessibility checker</t>
-  </si>
-  <si>
-    <t>Heading hierarchy, alt text, link labels, table headers, reading order, language, contrast.</t>
-  </si>
-  <si>
-    <t>FEAT-011</t>
-  </si>
-  <si>
-    <t>App accessibility fixes</t>
-  </si>
-  <si>
-    <t>Zero serious axe violations on main pages and the editor.</t>
-  </si>
-  <si>
-    <t>JOB-001</t>
-  </si>
-  <si>
-    <t>Job safety</t>
-  </si>
-  <si>
-    <t>idempotency_key, retry_count, timeout, cancellation, stuck detection, backoff, dead-letter.</t>
-  </si>
-  <si>
-    <t>STOR-001</t>
-  </si>
-  <si>
-    <t>Storage retention and deletion</t>
-  </si>
-  <si>
-    <t>Source files, exports, OCR artifacts: retention, deletion, access control, content types, size limits.</t>
-  </si>
-  <si>
-    <t>OBS-001</t>
-  </si>
-  <si>
-    <t>Metrics</t>
-  </si>
-  <si>
-    <t>Latency, failure rate, job/AI/export metrics without content.</t>
-  </si>
-  <si>
-    <t>AUD-15</t>
-  </si>
-  <si>
-    <t>OBS-002</t>
-  </si>
-  <si>
-    <t>Operation and job IDs in logs</t>
-  </si>
-  <si>
-    <t>Request, operation and job IDs everywhere.</t>
-  </si>
-  <si>
-    <t>OBS-003</t>
-  </si>
-  <si>
-    <t>Operations data</t>
-  </si>
-  <si>
-    <t>Failed jobs, processing failures, usage spikes, AI/export failures, storage, abuse - minimal admin API.</t>
-  </si>
-  <si>
-    <t>INFRA-010</t>
-  </si>
-  <si>
-    <t>Deployment verified</t>
-  </si>
-  <si>
-    <t>Docker images build and start; Postgres, Redis, storage, worker, frontend, backend.</t>
-  </si>
-  <si>
-    <t>docker, CI</t>
-  </si>
-  <si>
-    <t>INFRA-011</t>
-  </si>
-  <si>
-    <t>CI gates</t>
-  </si>
-  <si>
-    <t>Backend, frontend, E2E, lint, typecheck, build, migrations, security audit, document fidelity tests.</t>
-  </si>
-  <si>
-    <t>.github/workflows</t>
-  </si>
-  <si>
-    <t>AUD-15,AUD-20</t>
-  </si>
-  <si>
-    <t>TEST-040</t>
-  </si>
-  <si>
-    <t>Playwright workflow coverage</t>
-  </si>
-  <si>
-    <t>The 24 workflows of the brief.</t>
-  </si>
-  <si>
-    <t>TEST-041</t>
-  </si>
-  <si>
-    <t>Performance gates</t>
-  </si>
-  <si>
-    <t>Regression thresholds relative to baseline.</t>
-  </si>
-  <si>
-    <t>TEST-043</t>
-  </si>
-  <si>
-    <t>Browser matrix</t>
-  </si>
-  <si>
-    <t>Chromium, Firefox, WebKit.</t>
-  </si>
-  <si>
-    <t>TEST-006</t>
-  </si>
-  <si>
-    <t>E2E backend removes its temp directory</t>
-  </si>
-  <si>
-    <t>scripts/e2e_server.py leaves %TEMP%/smartdoc-e2e-* behind after every Playwright run (10 found on 2026-09-27).</t>
-  </si>
-  <si>
-    <t>backend/scripts/e2e_server.py</t>
-  </si>
-  <si>
-    <t>DOCS-010</t>
-  </si>
-  <si>
-    <t>final-production-readiness.md</t>
-  </si>
-  <si>
-    <t>The 16-section final report.</t>
-  </si>
-  <si>
-    <t>DOCS-011</t>
-  </si>
-  <si>
-    <t>Documentation tree</t>
-  </si>
-  <si>
-    <t>docs/{architecture,document-model,docx,pdf,translation,ai,formatting,security,testing,deployment,billing,operations}.</t>
-  </si>
-  <si>
-    <t>Started with Phase 1: docs/document-model, docs/architecture/fidelity.md, docs/docx, docs/formatting, docs/security, docs/testing (each grounded in the code and tests of Phases 0-1). Remaining folders (pdf, translation, ai, deployment, billing, operations) as their phases land.; docs/ai/README.md added with Phase 2.</t>
-  </si>
-  <si>
-    <t>CRITICAL_FIXES — Audit findings and P0 tasks</t>
-  </si>
-  <si>
-    <t>The 20 findings of the 2026-09-26 audit (current known risks) with fix progress, then every P0 task. Report: https://claude.ai/artifact/WKskiyexTDLAHe1BfjvWR1 — a finding is RESOLVED when every linked fix task is DONE.</t>
-  </si>
-  <si>
-    <t>Findings</t>
-  </si>
-  <si>
-    <t>Resolved</t>
-  </si>
-  <si>
-    <t>Open</t>
-  </si>
-  <si>
-    <t>P0 tasks</t>
-  </si>
-  <si>
-    <t>P0 done</t>
-  </si>
-  <si>
-    <t>Audit findings (current known risks)</t>
-  </si>
-  <si>
-    <t>Finding ID</t>
-  </si>
-  <si>
-    <t>Progress</t>
-  </si>
-  <si>
-    <t>Finding</t>
-  </si>
-  <si>
-    <t>Fix Tasks</t>
-  </si>
-  <si>
-    <t>Active</t>
-  </si>
-  <si>
-    <t>Blocked/Failed</t>
-  </si>
-  <si>
-    <t>Editor save can discard nested blocks (lists, pictures, code, quotes inside cells/items)</t>
-  </si>
-  <si>
-    <t>EDIT-001,EDIT-002,EDIT-003,EDIT-005,EDIT-006</t>
-  </si>
-  <si>
-    <t>AI fidelity check misses omissions, negation removal, number changes, inserted text</t>
-  </si>
-  <si>
-    <t>AI-001,AI-002,AI-003,AI-004</t>
-  </si>
-  <si>
-    <t>Fixed in Phase 2 (AI-001..004): AI structure answers are checked token by token; any omission, negation removal, number/unit/date change, insertion, reordering, duplication or punctuation change is refused.</t>
-  </si>
-  <si>
-    <t>Import/export silently changes hidden text, numbering, section headers, metadata, alt text, structure</t>
-  </si>
-  <si>
-    <t>FID-002,DOCX-011,DOCX-013,DOCX-015,DOCX-025</t>
-  </si>
-  <si>
-    <t>List numbering changes ('Чл. 1.' -&gt; '1.', '(a)' -&gt; 'a.', start values)</t>
-  </si>
-  <si>
-    <t>Partly fixed in 622d9c1: list format/start/continuation kept; custom labels ('Чл. 1.', '(a)') and multi-level labels reported, not kept yet (DOCX-016).</t>
-  </si>
-  <si>
-    <t>AI instruction operations can delete/insert/move content without preview</t>
-  </si>
-  <si>
-    <t>AI-005,AI-006,AI-007,REV-003</t>
-  </si>
-  <si>
-    <t>Fixed in Phase 2 (AI-005..AI-007): an instruction's insert/delete/move is a proposal the user sees and accepts or rejects; nothing is deleted silently.</t>
-  </si>
-  <si>
-    <t>Content controls, metadata, comment threads, sensitivity information lost</t>
-  </si>
-  <si>
-    <t>DOCX-012,DOCX-021,DOCX-023</t>
-  </si>
-  <si>
-    <t>Image fidelity gaps: alt text, crop, rotation, formats</t>
-  </si>
-  <si>
-    <t>Table export changes header state, borders, alignment, widths, geometry</t>
-  </si>
-  <si>
-    <t>Large images cause huge memory consumption</t>
-  </si>
-  <si>
-    <t>SEC-012,SEC-013</t>
-  </si>
-  <si>
-    <t>Large tables have a performance problem</t>
-  </si>
-  <si>
-    <t>Plan limits have a concurrency race</t>
-  </si>
-  <si>
-    <t>Malformed DOCX leads to HTTP 500</t>
-  </si>
-  <si>
-    <t>SEC-010,SEC-019</t>
-  </si>
-  <si>
-    <t>Dangerous href/field instructions must be filtered</t>
-  </si>
-  <si>
-    <t>SEC-014,SEC-015,SEC-016</t>
-  </si>
-  <si>
-    <t>Account essentials missing: reset, verification, change, deletion</t>
-  </si>
-  <si>
-    <t>ACCT-002,ACCT-003,ACCT-004,ACCT-005</t>
-  </si>
-  <si>
-    <t>Operations/monitoring must be confirmed</t>
-  </si>
-  <si>
-    <t>OBS-001,OBS-002,INFRA-010</t>
-  </si>
-  <si>
-    <t>Whole-document autosave must be optimised</t>
-  </si>
-  <si>
-    <t>PERF-003,PERF-004</t>
-  </si>
-  <si>
-    <t>PDF multilingual rendering must be reliable</t>
-  </si>
-  <si>
-    <t>FONT-003,FONT-006</t>
-  </si>
-  <si>
-    <t>Export metadata must be correct</t>
-  </si>
-  <si>
-    <t>DOCX-012,DOCX-020</t>
-  </si>
-  <si>
-    <t>Partly fixed in 622d9c1: Word exports carry the source file's core properties (author, dates, subject...) instead of 'python-docx'/2013; fields remain (DOCX-020).</t>
-  </si>
-  <si>
-    <t>AUD-19</t>
-  </si>
-  <si>
-    <t>Canonical model must represent more than paragraphs + runs + simple tables</t>
-  </si>
-  <si>
-    <t>CORE-001,DOCX-015,DOCX-016,DOCX-017</t>
-  </si>
-  <si>
-    <t>Tests can miss import-side data loss (model-relative comparison)</t>
-  </si>
-  <si>
-    <t>TEST-020,TEST-021,TEST-022</t>
-  </si>
-  <si>
-    <t>P0 tasks (live from MASTER)</t>
-  </si>
-  <si>
-    <t>DOCUMENT_FIDELITY — Content preservation</t>
-  </si>
-  <si>
-    <t>Canonical model, fidelity reports, capability matrix, change/review model. Categories: CORE, FIDELITY, REVIEW. Rows are formulas over MASTER — change task data in MASTER or with tools/tracker/tracker.py.</t>
-  </si>
-  <si>
-    <t>Tasks (live from MASTER)</t>
-  </si>
-  <si>
-    <t>DOCX_OOXML — DOCX / OOXML preservation</t>
-  </si>
-  <si>
-    <t>Import and export fidelity for Word documents. Categories: DOCX. Rows are formulas over MASTER — change task data in MASTER or with tools/tracker/tracker.py.</t>
-  </si>
-  <si>
-    <t>PDF — PDF engine</t>
-  </si>
-  <si>
-    <t>PDF export and PDF parsing. Categories: PDF. Rows are formulas over MASTER — change task data in MASTER or with tools/tracker/tracker.py.</t>
-  </si>
-  <si>
-    <t>EDITOR — Editor integrity</t>
-  </si>
-  <si>
-    <t>Tiptap mapping and save integrity. Categories: EDITOR. Rows are formulas over MASTER — change task data in MASTER or with tools/tracker/tracker.py.</t>
-  </si>
-  <si>
-    <t>FORMATTING — Formatting and Document Health</t>
-  </si>
-  <si>
-    <t>Formatting engine, Format by Example, Document Health. Categories: FORMATTING, HEALTH. Rows are formulas over MASTER — change task data in MASTER or with tools/tracker/tracker.py.</t>
-  </si>
-  <si>
-    <t>AI — AI fidelity</t>
-  </si>
-  <si>
-    <t>Fidelity checks, proposals and review, budgets. Categories: AI. Rows are formulas over MASTER — change task data in MASTER or with tools/tracker/tracker.py.</t>
-  </si>
-  <si>
-    <t>SECURITY — Security and accounts</t>
-  </si>
-  <si>
-    <t>Security hardening and account essentials. Categories: SECURITY, ACCOUNT. Rows are formulas over MASTER — change task data in MASTER or with tools/tracker/tracker.py.</t>
-  </si>
-  <si>
-    <t>PERFORMANCE — Performance</t>
-  </si>
-  <si>
-    <t>Measured results — brief §80-81: measure, then set regression thresholds relative to the baseline (no invented SLOs)</t>
-  </si>
-  <si>
-    <t>Bench ID</t>
-  </si>
-  <si>
-    <t>Metric</t>
-  </si>
-  <si>
-    <t>Unit</t>
-  </si>
-  <si>
-    <t>Scenario</t>
-  </si>
-  <si>
-    <t>Baseline</t>
-  </si>
-  <si>
-    <t>Baseline Source</t>
-  </si>
-  <si>
-    <t>Current</t>
-  </si>
-  <si>
-    <t>Measured On</t>
-  </si>
-  <si>
-    <t>Threshold</t>
-  </si>
-  <si>
-    <t>BENCH-001</t>
-  </si>
-  <si>
-    <t>duration</t>
-  </si>
-  <si>
-    <t>s</t>
-  </si>
-  <si>
-    <t>DOCX export: table 500x8 (4,000 cells)</t>
-  </si>
-  <si>
-    <t>audit perf_table.py (400 cells 3.8 s; 1,600 cells 53.7 s; quadratic)</t>
-  </si>
-  <si>
-    <t>BENCH-002</t>
-  </si>
-  <si>
-    <t>PDF export: table 500x8</t>
-  </si>
-  <si>
-    <t>audit perf_table.py (linear)</t>
-  </si>
-  <si>
-    <t>BENCH-003</t>
-  </si>
-  <si>
-    <t>Import: 300-page text DOCX (1,650 elements)</t>
-  </si>
-  <si>
-    <t>audit perf_backend.py</t>
-  </si>
-  <si>
-    <t>BENCH-004</t>
-  </si>
-  <si>
-    <t>DOCX export: 300-page text document</t>
-  </si>
-  <si>
-    <t>BENCH-005</t>
-  </si>
-  <si>
-    <t>PDF export: 300-page text document</t>
-  </si>
-  <si>
-    <t>BENCH-006</t>
-  </si>
-  <si>
-    <t>memory growth</t>
-  </si>
-  <si>
-    <t>MB</t>
-  </si>
-  <si>
-    <t>PDF export: 39 KB DOCX holding a 12000x12000 PNG</t>
-  </si>
-  <si>
-    <t>audit pixel_bomb.py (14000x14000 crashes the export)</t>
-  </si>
-  <si>
-    <t>BENCH-007</t>
-  </si>
-  <si>
-    <t>PDF export: 4 JPEG images 2400x1800</t>
-  </si>
-  <si>
-    <t>audit perf_backend.py (6.3 s)</t>
-  </si>
-  <si>
-    <t>BENCH-008</t>
-  </si>
-  <si>
-    <t>Editor: type 20 characters at 12,196 elements (1M-character paste)</t>
-  </si>
-  <si>
-    <t>audit perf_browser.js (~470 ms per key)</t>
-  </si>
-  <si>
-    <t>BENCH-009</t>
-  </si>
-  <si>
-    <t>Editor: type 20 characters, 300-page document</t>
-  </si>
-  <si>
-    <t>audit perf_browser.js</t>
-  </si>
-  <si>
-    <t>BENCH-010</t>
-  </si>
-  <si>
-    <t>request size</t>
-  </si>
-  <si>
-    <t>Autosave request: 300-page document</t>
-  </si>
-  <si>
-    <t>audit perf_browser.js (whole elements list per save)</t>
-  </si>
-  <si>
-    <t>BENCH-011</t>
-  </si>
-  <si>
-    <t>Autosave request: 1M-character paste</t>
-  </si>
-  <si>
-    <t>BENCH-012</t>
-  </si>
-  <si>
-    <t>storage</t>
-  </si>
-  <si>
-    <t>Stored history: one 300-page document, 50 steps</t>
-  </si>
-  <si>
-    <t>audit (2.8 MB per full copy; 7.2 MB when the JSON is ASCII-escaped)</t>
-  </si>
-  <si>
-    <t>BENCH-013</t>
-  </si>
-  <si>
-    <t>Paste: 2M characters (the cap)</t>
-  </si>
-  <si>
-    <t>audit perf_backend.py (17.5k elements, 7.1 MB JSON)</t>
-  </si>
-  <si>
-    <t>Performance tasks (live from MASTER)</t>
-  </si>
-  <si>
-    <t>TESTING — Testing</t>
-  </si>
-  <si>
-    <t>Test runs (oldest first)</t>
-  </si>
-  <si>
-    <t>Run ID</t>
-  </si>
-  <si>
-    <t>Command</t>
-  </si>
-  <si>
-    <t>Passed</t>
-  </si>
-  <si>
-    <t>Skipped</t>
-  </si>
-  <si>
-    <t>Date</t>
-  </si>
-  <si>
-    <t>Duration (s)</t>
-  </si>
-  <si>
-    <t>RUN-0001</t>
-  </si>
-  <si>
-    <t>backend-pytest</t>
-  </si>
-  <si>
-    <t>PASS</t>
-  </si>
-  <si>
-    <t>cd backend &amp;&amp; venv/Scripts/python -m pytest -q -p no:cacheprovider</t>
-  </si>
-  <si>
-    <t>Skip: optional real-Word check (SMARTDOC_REAL_DOCX unset). 1 DeprecationWarning (starlette/anyio). Audit measured 93% line coverage on 2026-09-26.</t>
-  </si>
-  <si>
-    <t>ea69829</t>
-  </si>
-  <si>
-    <t>RUN-0002</t>
-  </si>
-  <si>
-    <t>frontend-lint</t>
-  </si>
-  <si>
-    <t>cd frontend &amp;&amp; npm run lint</t>
-  </si>
-  <si>
-    <t>eslint: 0 problems</t>
-  </si>
-  <si>
-    <t>RUN-0003</t>
-  </si>
-  <si>
-    <t>frontend-tsc</t>
-  </si>
-  <si>
-    <t>cd frontend &amp;&amp; npx tsc --noEmit</t>
-  </si>
-  <si>
-    <t>0 type errors</t>
-  </si>
-  <si>
-    <t>RUN-0004</t>
-  </si>
-  <si>
-    <t>frontend-vitest</t>
-  </si>
-  <si>
-    <t>cd frontend &amp;&amp; npm test</t>
-  </si>
-  <si>
-    <t>6 test files</t>
-  </si>
-  <si>
-    <t>RUN-0005</t>
-  </si>
-  <si>
-    <t>frontend-build</t>
-  </si>
-  <si>
-    <t>cd frontend &amp;&amp; npm run build</t>
-  </si>
-  <si>
-    <t>Next.js production build, 11 routes</t>
-  </si>
-  <si>
-    <t>RUN-0006</t>
-  </si>
-  <si>
-    <t>e2e-playwright</t>
-  </si>
-  <si>
-    <t>cd frontend &amp;&amp; npm run test:e2e</t>
-  </si>
-  <si>
-    <t>Edge; throwaway backend on SQLite (:8100) + production build (:3100). 16 workflows in 5 spec files; the brief asks for 24 (TEST-040). Leaves %TEMP%/smartdoc-e2e-* dirs behind (TEST-006).</t>
-  </si>
-  <si>
-    <t>RUN-0007</t>
-  </si>
-  <si>
-    <t>migrations</t>
-  </si>
-  <si>
-    <t>alembic upgrade head &amp;&amp; alembic check &amp;&amp; alembic downgrade base &amp;&amp; alembic upgrade head (scratch SQLite); alembic upgrade head --sql (PostgreSQL dialect)</t>
-  </si>
-  <si>
-    <t>head 85211092fe4c; 'No new upgrade operations detected'; offline SQL: 14 tables at head, RLS enabled on every table</t>
-  </si>
-  <si>
-    <t>RUN-0008</t>
-  </si>
-  <si>
-    <t>supabase</t>
-  </si>
-  <si>
-    <t>Supabase MCP: list_migrations, get_advisors security+performance, list_tables (project edmmjmsynjziahwtjuke)</t>
-  </si>
-  <si>
-    <t>8/8 migrations applied; 14 tables, RLS on all; advisors only INFO: 14x rls_enabled_no_policy (by design: the API connects as owner, PostgREST roles see nothing), 8x unused_index (low traffic)</t>
-  </si>
-  <si>
-    <t>RUN-0009</t>
-  </si>
-  <si>
-    <t>pip-audit</t>
-  </si>
-  <si>
-    <t>uvx pip-audit --disable-pip -r backend/requirements.lock; same for requirements-dev.lock</t>
-  </si>
-  <si>
-    <t>No known vulnerabilities in either lock file</t>
-  </si>
-  <si>
-    <t>RUN-0010</t>
-  </si>
-  <si>
-    <t>npm-audit</t>
-  </si>
-  <si>
-    <t>cd frontend &amp;&amp; npm audit; npm audit --omit=dev</t>
-  </si>
-  <si>
-    <t>0 vulnerabilities across 633 dependencies</t>
-  </si>
-  <si>
-    <t>RUN-0011</t>
-  </si>
-  <si>
-    <t>docker-compose</t>
-  </si>
-  <si>
-    <t>PARTIAL</t>
-  </si>
-  <si>
-    <t>docker compose config --quiet</t>
-  </si>
-  <si>
-    <t>compose file valid (8 services: postgres, redis, minio, minio-bucket, migrate, worker, backend, frontend); images NOT built: Docker daemon not running on this machine (CI builds them on main)</t>
-  </si>
-  <si>
-    <t>RUN-0012</t>
-  </si>
-  <si>
-    <t>Phase 1 editor integrity: +16 tests (nesting model, nested API/exports, health links)</t>
-  </si>
-  <si>
-    <t>RUN-0013</t>
-  </si>
-  <si>
-    <t>cd frontend &amp;&amp; npx vitest run</t>
-  </si>
-  <si>
-    <t>+31: nestedBlocks.test.ts (28), useAutoSave.test.tsx (3); tsc and eslint clean</t>
-  </si>
-  <si>
-    <t>RUN-0014</t>
-  </si>
-  <si>
-    <t>cd frontend &amp;&amp; npx playwright test</t>
-  </si>
-  <si>
-    <t>+1: e2e/nested.spec.ts (paste, autosave, reload)</t>
-  </si>
-  <si>
-    <t>RUN-0015</t>
-  </si>
-  <si>
-    <t>+29 test_fidelity_report.py</t>
-  </si>
-  <si>
-    <t>RUN-0016</t>
-  </si>
-  <si>
-    <t>+3 FidelityPanel.test.tsx</t>
-  </si>
-  <si>
-    <t>RUN-0017</t>
-  </si>
-  <si>
-    <t>+fidelity.spec.ts; nested.spec.ts made deterministic (focus check, Ctrl+End) after one run pasted at the document start</t>
-  </si>
-  <si>
-    <t>RUN-0018</t>
-  </si>
-  <si>
-    <t>+6 test_export_fidelity.py</t>
-  </si>
-  <si>
-    <t>RUN-0019</t>
-  </si>
-  <si>
-    <t>+4 ExportResult.test.tsx</t>
-  </si>
-  <si>
-    <t>RUN-0020</t>
-  </si>
-  <si>
-    <t>export test checks the export's content message</t>
-  </si>
-  <si>
-    <t>RUN-0021</t>
-  </si>
-  <si>
-    <t>+6 test_capabilities.py</t>
-  </si>
-  <si>
-    <t>RUN-0022</t>
-  </si>
-  <si>
-    <t>venv/Scripts/python -m pytest -q</t>
-  </si>
-  <si>
-    <t>after FID-002 detections + section break fix</t>
-  </si>
-  <si>
-    <t>RUN-0023</t>
-  </si>
-  <si>
-    <t>npx vitest run</t>
-  </si>
-  <si>
-    <t>tsc --noEmit and eslint clean too</t>
-  </si>
-  <si>
-    <t>RUN-0024</t>
-  </si>
-  <si>
-    <t>rule values (SEC-022) + editor direct styles</t>
-  </si>
-  <si>
-    <t>RUN-0025</t>
-  </si>
-  <si>
-    <t>tsc + eslint clean</t>
-  </si>
-  <si>
-    <t>RUN-0026</t>
-  </si>
-  <si>
-    <t>e2e</t>
-  </si>
-  <si>
-    <t>npx playwright test</t>
-  </si>
-  <si>
-    <t>incl. e2e/direct-formatting.spec.ts</t>
-  </si>
-  <si>
-    <t>RUN-0027</t>
-  </si>
-  <si>
-    <t>Phase 1 gate: link titles, mark order, Markdown pictures/rules</t>
-  </si>
-  <si>
-    <t>RUN-0028</t>
-  </si>
-  <si>
-    <t>Phase 1 gate; tsc + eslint clean</t>
-  </si>
-  <si>
-    <t>RUN-0029</t>
-  </si>
-  <si>
-    <t>Phase 1 gate</t>
-  </si>
-  <si>
-    <t>RUN-0030</t>
-  </si>
-  <si>
-    <t>AI fidelity check (AI-001..004)</t>
-  </si>
-  <si>
-    <t>RUN-0031</t>
-  </si>
-  <si>
-    <t>AI proposals</t>
-  </si>
-  <si>
-    <t>RUN-0032</t>
-  </si>
-  <si>
-    <t>RUN-0033</t>
-  </si>
-  <si>
-    <t>incl. e2e/proposals.spec.ts</t>
-  </si>
-  <si>
-    <t>RUN-0034</t>
-  </si>
-  <si>
-    <t>AI budget</t>
-  </si>
-  <si>
-    <t>RUN-0035</t>
-  </si>
-  <si>
-    <t>prompt-injection review</t>
-  </si>
-  <si>
-    <t>RUN-0036</t>
-  </si>
-  <si>
-    <t>Phase 2 gate</t>
-  </si>
-  <si>
-    <t>RUN-0037</t>
-  </si>
-  <si>
-    <t>RUN-0038</t>
-  </si>
-  <si>
-    <t>source package + patch writer</t>
-  </si>
-  <si>
-    <t>RUN-0039</t>
-  </si>
-  <si>
-    <t>after the patch writer</t>
-  </si>
-  <si>
-    <t>RUN-0040</t>
-  </si>
-  <si>
-    <t>backend pytest</t>
-  </si>
-  <si>
-    <t>DOCX-028: test_original_blocks.py (26), golden set of 13</t>
-  </si>
-  <si>
-    <t>7f22bf9</t>
-  </si>
-  <si>
-    <t>RUN-0041</t>
-  </si>
-  <si>
-    <t>frontend vitest</t>
-  </si>
-  <si>
-    <t>editor round trip includes 13-kept-blocks</t>
-  </si>
-  <si>
-    <t>RUN-0042</t>
-  </si>
-  <si>
-    <t>playwright</t>
-  </si>
-  <si>
-    <t>new e2e/kept-blocks.spec.ts</t>
-  </si>
-  <si>
-    <t>RUN-0043</t>
-  </si>
-  <si>
-    <t>tsc + eslint</t>
-  </si>
-  <si>
-    <t>cd frontend &amp;&amp; npx tsc --noEmit &amp;&amp; npx eslint .</t>
-  </si>
-  <si>
-    <t>0 type errors, 0 lint problems</t>
-  </si>
-  <si>
-    <t>RUN-0044</t>
-  </si>
-  <si>
-    <t>DOCX-025: tests/test_hidden_text.py (7)</t>
-  </si>
-  <si>
-    <t>fada4d7</t>
-  </si>
-  <si>
-    <t>RUN-0045</t>
-  </si>
-  <si>
-    <t>editor/hiddenText.test.tsx (6)</t>
-  </si>
-  <si>
-    <t>RUN-0046</t>
-  </si>
-  <si>
-    <t>new e2e/hidden-text.spec.ts</t>
-  </si>
-  <si>
-    <t>RUN-0047</t>
-  </si>
-  <si>
-    <t>RUN-0048</t>
-  </si>
-  <si>
-    <t>DOCX-013 part 1: tests/test_character_formatting.py (12)</t>
-  </si>
-  <si>
-    <t>c51b1bf</t>
-  </si>
-  <si>
-    <t>RUN-0049</t>
-  </si>
-  <si>
-    <t>editor/characterFormatting.test.ts (3)</t>
-  </si>
-  <si>
-    <t>RUN-0050</t>
-  </si>
-  <si>
-    <t>after DOCX-013 part 1</t>
-  </si>
-  <si>
-    <t>RUN-0051</t>
-  </si>
-  <si>
-    <t>RUN-0052</t>
-  </si>
-  <si>
-    <t>DOCX-013 part 2 + FID-007: tests/test_copy_reports.py (6)</t>
-  </si>
-  <si>
-    <t>309f9d6</t>
-  </si>
-  <si>
-    <t>RUN-0053</t>
-  </si>
-  <si>
-    <t>characterFormatting.test.ts (4)</t>
-  </si>
-  <si>
-    <t>RUN-0054</t>
-  </si>
-  <si>
-    <t>after DOCX-013 part 2</t>
-  </si>
-  <si>
-    <t>RUN-0055</t>
-  </si>
-  <si>
-    <t>RUN-0056</t>
-  </si>
-  <si>
-    <t>DOCX-014 part 1: tests/test_paragraph_formatting.py (9)</t>
-  </si>
-  <si>
-    <t>597275a</t>
-  </si>
-  <si>
-    <t>RUN-0057</t>
-  </si>
-  <si>
-    <t>after DOCX-014 part 1</t>
-  </si>
-  <si>
-    <t>RUN-0058</t>
-  </si>
-  <si>
-    <t>RUN-0059</t>
-  </si>
-  <si>
-    <t>RUN-0060</t>
-  </si>
-  <si>
-    <t>DOCX-014 part 2: tests/test_paragraph_formatting.py (19)</t>
-  </si>
-  <si>
-    <t>9f1c5b4</t>
-  </si>
-  <si>
-    <t>RUN-0061</t>
-  </si>
-  <si>
-    <t>after DOCX-014 part 2</t>
-  </si>
-  <si>
-    <t>RUN-0062</t>
-  </si>
-  <si>
-    <t>RUN-0063</t>
-  </si>
-  <si>
-    <t>RUN-0064</t>
-  </si>
-  <si>
-    <t>DOCX-015 part 1a: tests/test_sections.py (6)</t>
-  </si>
-  <si>
-    <t>49d54e5</t>
-  </si>
-  <si>
-    <t>RUN-0065</t>
-  </si>
-  <si>
-    <t>sectionBreak.test.ts (3)</t>
-  </si>
-  <si>
-    <t>RUN-0066</t>
-  </si>
-  <si>
-    <t>after DOCX-015 part 1a</t>
-  </si>
-  <si>
-    <t>RUN-0067</t>
-  </si>
-  <si>
-    <t>RUN-0068</t>
-  </si>
-  <si>
-    <t>DOCX-015 part 1b: tests/test_sections.py (7)</t>
-  </si>
-  <si>
-    <t>cb75ebd</t>
-  </si>
-  <si>
-    <t>RUN-0069</t>
-  </si>
-  <si>
-    <t>after DOCX-015 part 1b</t>
-  </si>
-  <si>
-    <t>RUN-0070</t>
-  </si>
-  <si>
-    <t>RUN-0071</t>
-  </si>
-  <si>
-    <t>Testing tasks (live from MASTER)</t>
-  </si>
-  <si>
-    <t>PRODUCT_FEATURES — Product features</t>
-  </si>
-  <si>
-    <t>Feature backlog — brief §61-62</t>
-  </si>
-  <si>
-    <t>Feature</t>
-  </si>
-  <si>
-    <t>Bucket</t>
-  </si>
-  <si>
-    <t>Linked Tasks</t>
-  </si>
-  <si>
-    <t>Linked Done</t>
-  </si>
-  <si>
-    <t>Linked Total</t>
-  </si>
-  <si>
-    <t>Document integrity</t>
-  </si>
-  <si>
-    <t>NOW</t>
-  </si>
-  <si>
-    <t>EDIT-001,EDIT-005,FID-002</t>
-  </si>
-  <si>
-    <t>Brief 62: NOW #1</t>
-  </si>
-  <si>
-    <t>Fidelity</t>
-  </si>
-  <si>
-    <t>DOCX-011,TEST-022</t>
-  </si>
-  <si>
-    <t>Brief 62: NOW #2</t>
-  </si>
-  <si>
-    <t>Security</t>
-  </si>
-  <si>
-    <t>SEC-010,SEC-012,SEC-014</t>
-  </si>
-  <si>
-    <t>Brief 62: NOW #3</t>
-  </si>
-  <si>
-    <t>Performance</t>
-  </si>
-  <si>
-    <t>PERF-001,PERF-003,PERF-004</t>
-  </si>
-  <si>
-    <t>Brief 62: NOW #4</t>
-  </si>
-  <si>
-    <t>PDF -&gt; editable</t>
-  </si>
-  <si>
-    <t>P2E-002,P2E-005</t>
-  </si>
-  <si>
-    <t>Brief 62: NOW #5</t>
-  </si>
-  <si>
-    <t>TRAN-001,TRAN-006</t>
-  </si>
-  <si>
-    <t>Brief 62: NOW #6</t>
-  </si>
-  <si>
-    <t>FONT-002,FONT-003</t>
-  </si>
-  <si>
-    <t>Brief 62: NOW #7</t>
-  </si>
-  <si>
-    <t>Review Changes</t>
-  </si>
-  <si>
-    <t>REV-001,REV-002</t>
-  </si>
-  <si>
-    <t>Brief 62: NOW #8</t>
-  </si>
-  <si>
-    <t>HLTH-001,HLTH-002</t>
-  </si>
-  <si>
-    <t>Brief 62: NOW #9</t>
-  </si>
-  <si>
-    <t>FMT-001,FMT-002,FMT-003</t>
-  </si>
-  <si>
-    <t>Brief 62: NOW #10</t>
-  </si>
-  <si>
-    <t>OCR</t>
-  </si>
-  <si>
-    <t>Part of PDF -&gt; editable (brief 43)</t>
-  </si>
-  <si>
-    <t>Multilingual support</t>
-  </si>
-  <si>
-    <t>TRAN-007,FONT-003</t>
-  </si>
-  <si>
-    <t>Part of translation + FontResolver</t>
-  </si>
-  <si>
-    <t>RTL</t>
-  </si>
-  <si>
-    <t>FONT-003,FONT-004</t>
-  </si>
-  <si>
-    <t>Part of FontResolver</t>
-  </si>
-  <si>
-    <t>CJK</t>
-  </si>
-  <si>
-    <t>Glossary</t>
-  </si>
-  <si>
-    <t>Part of translation MVP (brief 49)</t>
-  </si>
-  <si>
-    <t>Terminology lock</t>
-  </si>
-  <si>
-    <t>Citation preservation</t>
-  </si>
-  <si>
-    <t>Preservation is fidelity work; a citation editor is LATER</t>
-  </si>
-  <si>
-    <t>Bibliography preservation</t>
-  </si>
-  <si>
-    <t>Preservation is fidelity work</t>
-  </si>
-  <si>
-    <t>Content controls</t>
-  </si>
-  <si>
-    <t>Preserve now; editing content controls NEXT</t>
-  </si>
-  <si>
-    <t>Custom fields</t>
-  </si>
-  <si>
-    <t>Preserve custom properties and fields now; an editor NEXT</t>
-  </si>
-  <si>
-    <t>Document compare</t>
-  </si>
-  <si>
-    <t>NEXT</t>
-  </si>
-  <si>
-    <t>Brief 62: NEXT</t>
-  </si>
-  <si>
-    <t>Version compare</t>
-  </si>
-  <si>
-    <t>Brief 62: NEXT (batch processing)</t>
-  </si>
-  <si>
-    <t>After the translation MVP</t>
-  </si>
-  <si>
-    <t>Table repair</t>
-  </si>
-  <si>
-    <t>List repair</t>
-  </si>
-  <si>
-    <t>Brief 62: NEXT (accessibility)</t>
-  </si>
-  <si>
-    <t>Heading hierarchy checker</t>
-  </si>
-  <si>
-    <t>Link checker</t>
-  </si>
-  <si>
-    <t>Alt-text checker</t>
-  </si>
-  <si>
-    <t>HLTH-001,FEAT-010</t>
-  </si>
-  <si>
-    <t>Metadata editor</t>
-  </si>
-  <si>
-    <t>Global style replacement</t>
-  </si>
-  <si>
-    <t>Find/replace with formatting</t>
-  </si>
-  <si>
-    <t>Tracked change cleanup</t>
-  </si>
-  <si>
-    <t>Template extraction</t>
-  </si>
-  <si>
-    <t>Document-to-template</t>
-  </si>
-  <si>
-    <t>Template matching</t>
-  </si>
-  <si>
-    <t>Advanced template sharing</t>
-  </si>
-  <si>
-    <t>Teams</t>
-  </si>
-  <si>
-    <t>Translation memory</t>
-  </si>
-  <si>
-    <t>PDF merge/split</t>
-  </si>
-  <si>
-    <t>Page reorder</t>
-  </si>
-  <si>
-    <t>Page rotate</t>
-  </si>
-  <si>
-    <t>Page delete</t>
-  </si>
-  <si>
-    <t>Page extract</t>
-  </si>
-  <si>
-    <t>Merge documents</t>
-  </si>
-  <si>
-    <t>LATER</t>
-  </si>
-  <si>
-    <t>Split documents</t>
-  </si>
-  <si>
-    <t>Watermark</t>
-  </si>
-  <si>
-    <t>Forms (advanced)</t>
-  </si>
-  <si>
-    <t>Brief 62: LATER</t>
-  </si>
-  <si>
-    <t>SmartArt editing</t>
-  </si>
-  <si>
-    <t>Brief 62: LATER; SmartArt is preserved, not edited</t>
-  </si>
-  <si>
-    <t>OLE</t>
-  </si>
-  <si>
-    <t>Brief 62: LATER; OLE objects preserved, not edited</t>
-  </si>
-  <si>
-    <t>Full tracked-change editor</t>
-  </si>
-  <si>
-    <t>Advanced citation manager</t>
-  </si>
-  <si>
-    <t>Advanced drawing editor</t>
-  </si>
-  <si>
-    <t>Layout-preserving PDF editing (frames/anchors)</t>
-  </si>
-  <si>
-    <t>ARCHITECTURE_ONLY</t>
-  </si>
-  <si>
-    <t>Phase 9: architecture and hooks only</t>
-  </si>
-  <si>
-    <t>Product tasks (live from MASTER)</t>
-  </si>
-  <si>
-    <t>TRANSLATION — Translation and fonts</t>
-  </si>
-  <si>
-    <t>Translation MVP and FontResolver. Categories: TRANSLATION, FONT. Rows are formulas over MASTER — change task data in MASTER or with tools/tracker/tracker.py.</t>
-  </si>
-  <si>
-    <t>PDF_TO_EDITABLE — PDF to editable</t>
-  </si>
-  <si>
-    <t>PDF to editable document conversion. Categories: P2E. Rows are formulas over MASTER — change task data in MASTER or with tools/tracker/tracker.py.</t>
-  </si>
-  <si>
-    <t>BILLING_PLANS — Plans and billing</t>
-  </si>
-  <si>
-    <t>Initial plan hypothesis — brief §64: configurable defaults, not final prices; confirm against measured AI and infrastructure cost. Blue = input.</t>
-  </si>
-  <si>
-    <t>Usage unit / feature</t>
-  </si>
-  <si>
-    <t>FREE</t>
-  </si>
-  <si>
-    <t>PRO</t>
-  </si>
-  <si>
-    <t>BUSINESS</t>
-  </si>
-  <si>
-    <t>Documents / month</t>
-  </si>
-  <si>
-    <t>BUSINESS: per workspace</t>
-  </si>
-  <si>
-    <t>PDF conversion pages / month</t>
-  </si>
-  <si>
-    <t>OCR pages / month</t>
-  </si>
-  <si>
-    <t>Translation characters / month</t>
-  </si>
-  <si>
-    <t>AI operations / month</t>
-  </si>
-  <si>
-    <t>Exports / month</t>
-  </si>
-  <si>
-    <t>high</t>
-  </si>
-  <si>
-    <t>BUSINESS: 'high export limits', no number given</t>
-  </si>
-  <si>
-    <t>Templates</t>
-  </si>
-  <si>
-    <t>basic</t>
-  </si>
-  <si>
-    <t>custom</t>
-  </si>
-  <si>
-    <t>shared</t>
-  </si>
-  <si>
-    <t>Formatting</t>
-  </si>
-  <si>
-    <t>Format by Example</t>
-  </si>
-  <si>
-    <t>-</t>
-  </si>
-  <si>
-    <t>Advanced Document Health</t>
-  </si>
-  <si>
-    <t>yes</t>
-  </si>
-  <si>
-    <t>Version history</t>
-  </si>
-  <si>
-    <t>no</t>
-  </si>
-  <si>
-    <t>reasonable limits</t>
-  </si>
-  <si>
-    <t>Team workspace</t>
-  </si>
-  <si>
-    <t>Priority processing</t>
-  </si>
-  <si>
-    <t>Advanced controls</t>
-  </si>
-  <si>
-    <t>Billing and plan tasks (live from MASTER)</t>
-  </si>
-  <si>
-    <t>INFRA — Infrastructure</t>
-  </si>
-  <si>
-    <t>Tracker, jobs, storage, observability, deployment, documentation. Categories: INFRA, JOBS, STORAGE, OBSERVABILITY, DOCS. Rows are formulas over MASTER — change task data in MASTER or with tools/tracker/tracker.py.</t>
-  </si>
-  <si>
-    <t>Timestamp</t>
-  </si>
-  <si>
-    <t>Task ID</t>
-  </si>
-  <si>
-    <t>Change</t>
-  </si>
-  <si>
-    <t>Files</t>
-  </si>
-  <si>
-    <t>Created SmartDoc_Master_Implementation_Tracker.xlsx from the 2026-09-26 audit findings and the brief's phases: 151 tasks, 20 findings, 15 release gates.</t>
-  </si>
-  <si>
-    <t>tools/tracker/tracker.py, tools/tracker/seed.py</t>
-  </si>
-  <si>
-    <t>N/A</t>
-  </si>
-  <si>
-    <t>Built the Excel control centre: MASTER with 151 stable-ID tasks from the audit findings and the brief's 19 phases, CRITICAL_FIXES (20 findings -&gt; fix tasks, live status), 14 category views, DASHBOARD (totals, completion/verified %, phase %, category %, P0/P1 remaining), CHANGE_LOG, SESSION_STATE, RELEASE_GATES GATE-001..015. Formulas verified in Excel against independently computed values.</t>
-  </si>
-  <si>
-    <t>tools/tracker/*, SmartDoc_Master_Implementation_Tracker.xlsx, .gitignore</t>
-  </si>
-  <si>
-    <t>Resume reminder set with the platform scheduler; it fired and resumed the work. It only fires while this session is open and idle, which is recorded in AI-CONTINUATION.md.</t>
-  </si>
-  <si>
-    <t>Created the checkpoint system: AI-CONTINUATION.md with CURRENT STATE / LAST VERIFIED / WHAT WAS CHANGED / WHAT PASSED / WHAT FAILED / WHAT REMAINS / NEXT ACTION / IMPORTANT WARNINGS, session-state.json mirrored into SESSION_STATE by tracker.py state, and the brief saved verbatim for future sessions.</t>
-  </si>
-  <si>
-    <t>docs/AI-CONTINUATION.md, docs/session-state.json, docs/implementation-brief.md</t>
-  </si>
-  <si>
-    <t>Baseline backend suite: 643 passed, 1 skipped (optional real-Word check), 0 failed in 88 s on ea69829. Recorded as RUN-0001.</t>
-  </si>
-  <si>
-    <t>Baseline frontend: eslint clean, tsc clean, Vitest 46 passed in 6 files, production build succeeded. Recorded as RUN-0002..RUN-0005.</t>
-  </si>
-  <si>
-    <t>Baseline E2E: 16 Playwright workflows passed against the throwaway stack (SQLite backend :8100, production build :3100). The brief's 24-workflow target is TEST-040; temp-dir leak logged as TEST-006.</t>
-  </si>
-  <si>
-    <t>Baseline database: alembic head 85211092fe4c, check reports no drift, full down/up cycle clean; PostgreSQL offline SQL builds 14 tables with RLS; Supabase has all 8 migrations and only INFO-level advisor notices.</t>
-  </si>
-  <si>
-    <t>Baseline dependency audit: pip-audit finds no known vulnerabilities in requirements.lock or requirements-dev.lock; npm audit reports 0 vulnerabilities (production and dev).</t>
-  </si>
-  <si>
-    <t>Baseline infrastructure inspected: compose file valid with 8 services, arq worker and in-process job backends, local and S3 storage providers. Docker images were not built (daemon not running) - left to INFRA-010.</t>
-  </si>
-  <si>
-    <t>Baseline fixtures: the repository's 12 golden DOCX are generated by python-docx (not Word-authored) plus one PDF; the audit's 17 Word-authored fixtures still live outside the repo and move in with TEST-020.</t>
-  </si>
-  <si>
-    <t>Wrote docs/architecture/current-baseline.md: stack versions, the 11 baseline checks with commands and results, the migration chain and live database state, fixture inventory, audit performance figures, and what the baseline could not verify (Docker images, real AI model, Stripe, e-mail, hosting).</t>
-  </si>
-  <si>
-    <t>INFRA-001, INFRA-002, INFRA-003, TEST-001, TEST-002, TEST-003, TEST-004, TEST-005, SEC-001, INFRA-004, DOCS-001</t>
-  </si>
-  <si>
-    <t>Phase 0 committed (4da4ecb, pushed to feature/smartdoc-production-hardening): tracker, checkpoint system and measured baseline. All 11 phase-0 tasks DONE; no production code changed.</t>
-  </si>
-  <si>
-    <t>see commit 4da4ecb</t>
-  </si>
-  <si>
-    <t>Model now holds blocks nested inside table cells, list items and quotes as Elements (authoritative when set; inline keeps plain text), plus list numbering start/format; nesting capped at 8 levels (422 beyond). schemaVersion stays 1: the fields are additive.</t>
-  </si>
-  <si>
-    <t>backend/app/models/document.py, backend/tests/test_document_nesting.py</t>
-  </si>
-  <si>
-    <t>Regenerated the OpenAPI schema and the frontend's generated types for the nested-block and numbering fields; the contract test and the type check pass.</t>
-  </si>
-  <si>
-    <t>frontend/types/generated/*, frontend/types/document.ts</t>
-  </si>
-  <si>
-    <t>Backend readers now see nested blocks: pasted pictures inside cells/list items/quotes are validated and moved to asset storage like top-level ones (security and quota), exports fetch their assets, and the links health check covers list items, cells and nested blocks.</t>
-  </si>
-  <si>
-    <t>backend/app/services/image_assets.py, backend/app/services/document_service.py, backend/app/formatting/health.py</t>
-  </si>
-  <si>
-    <t>Word export renders nested blocks in cells, list items and quotes in reading order (verified by text order), numbers lists from their start in their format, and writes pictures' alt text.</t>
-  </si>
-  <si>
-    <t>backend/app/export/docx_export.py</t>
-  </si>
-  <si>
-    <t>PDF export renders nested blocks and list numbering (start/format); nested numbered levels now use the same a./i. sequence as the Word export instead of 1. everywhere.</t>
-  </si>
-  <si>
-    <t>backend/app/export/pdf_export.py</t>
-  </si>
-  <si>
-    <t>The editor mapping is total over the schema (tested against getSchema(editorExtensions)); anything unknown stops the save with a visible 'Not saved' message instead of being dropped, and the last saved version stays untouched.</t>
-  </si>
-  <si>
-    <t>frontend/editor/*</t>
-  </si>
-  <si>
-    <t>frontend/editor/nestedBlocks.test.ts (7 refusal cases); frontend/editor/useAutoSave.test.tsx (3)</t>
-  </si>
-  <si>
-    <t>Playwright pastes rich HTML (lists, code and a picture in table cells; a list in a quote; code in a list item; a list starting at 3 in letters), waits for autosave and reloads: everything is still there and no 'Not saved' appears.</t>
-  </si>
-  <si>
-    <t>frontend/e2e/nested.spec.ts</t>
-  </si>
-  <si>
-    <t>CORE-001, CORE-002, CORE-003, EDIT-001, EDIT-002, EDIT-003, EDIT-004, EDIT-005, EDIT-006, DOCX-001, PDF-001</t>
-  </si>
-  <si>
-    <t>Committed phase-01a-editor-integrity (1fe27a9, pushed): nested blocks in cells, list items and quotes survive the editor, the backend and both exports; unknown content stops the save visibly. AUD-01 fix tasks all DONE.</t>
-  </si>
-  <si>
-    <t>Import now produces a Document Fidelity Report: the importer's notes as items (feature, policy, count, content lost) plus an independent content check - the source's words (DOCX XML read separately from the importer, Markdown by what it renders, PDF extracted text) against the document's, in order. 'Verified' only when identical; differences listed with context (missing/added/changed/moved).</t>
-  </si>
-  <si>
-    <t>backend/app/fidelity/*, backend/app/models/document.py, backend/app/services/ingestion_service.py</t>
-  </si>
-  <si>
-    <t>Every importer note now carries a stable feature key and a brief-§90 policy class; review count and content-loss count are derived from them.</t>
-  </si>
-  <si>
-    <t>The editor shows the import's verdict in the status bar and a Проверка panel: content verified / differs (with word-level differences) / body complete but some content left out, then each item by policy. Browser check with a05 caught and fixed a misleading 'No content changes' when header text had been left out.</t>
-  </si>
-  <si>
-    <t>frontend/editor/panels/FidelityPanel.tsx, frontend/editor/EditorStatusBar.tsx, frontend/editor/DocumentEditorShell.tsx</t>
-  </si>
-  <si>
-    <t>FID-001, FID-004, FID-005, INFRA-005</t>
-  </si>
-  <si>
-    <t>Committed phase-01b-fidelity-report (8a330be, pushed): import fidelity report with policy classes and an independent word-level content check, shown in the editor; throwaway preview scripts.</t>
-  </si>
-  <si>
-    <t>Exports now report what they approximate or leave out (missing pictures, WebP a Word file can't hold, tables restyled for Word-sourced documents, edited kept fragments, page breaks in PDF tables, PDF comments/equations/fields/internal links, scripts the PDF can't lay out, alt text) and re-read the file: a Word export must hold exactly the document's words, a PDF every word in order (its own list numbers and page headers allowed). Shown under the Download button; the job result carries it.</t>
-  </si>
-  <si>
-    <t>Committed phase-01c-export-report (e55412f, pushed): export fidelity report with read-back content check, shown in the Export menu.</t>
-  </si>
-  <si>
-    <t>Added the machine-readable capability matrix (brief §91): 67 document features with import/edit/export/round-trip support and the policy the fidelity report uses, served at GET /api/v1/capabilities. Tests tie it to the code both ways, require a test for every clean round trip and a task for every unreported gap; writing it exposed unreported gaps now tracked (EDIT-012, DOCX-027).</t>
-  </si>
-  <si>
-    <t>backend/app/capabilities.py, backend/app/api/capabilities.py, backend/app/main.py, backend/tests/test_capabilities.py, frontend/types/generated/*</t>
-  </si>
-  <si>
-    <t>Committed phase-01d-capability-matrix (fcf30d7, pushed).</t>
-  </si>
-  <si>
-    <t>FID-002: import report now names empty spacing paragraphs, unsafe link addresses and per-section differences (page setup, odd/even breaks, page numbering, borders, line numbers, vertical alignment); matrix rows docx.empty_paragraphs + docx.sections updated</t>
-  </si>
-  <si>
-    <t>backend/app/fidelity/docx_detect.py, backend/app/fidelity/imports.py, backend/app/parsers/docx.py, backend/app/parsers/docx_inline.py, backend/app/capabilities.py, backend/tests/test_docx_detect.py</t>
-  </si>
-  <si>
-    <t>DOCX-015: section breaks break the page only where Word does (next section's w:type decides); continuous breaks no longer become page breaks</t>
-  </si>
-  <si>
-    <t>tests/test_docx_detect.py::test_a_section_break_breaks_the_page_only_where_word_does</t>
-  </si>
-  <si>
-    <t>DOCX-016: list number formats, start values and continuation round-trip; custom and multi-level labels reported</t>
-  </si>
-  <si>
-    <t>DOCX-012: Word core properties round-trip; custom properties and sensitivity labels reported without values</t>
-  </si>
-  <si>
-    <t>tests/test_docx_detect.py::test_the_files_own_properties_go_back_into_word_not_the_templates, tests/test_docx_detect.py::test_metadata_that_is_not_kept_is_reported_without_its_values</t>
-  </si>
-  <si>
-    <t>DOCX-026: unsafe link addresses reported instead of silently dropped</t>
-  </si>
-  <si>
-    <t>Golden JSON export is deterministic (uuid5 ids by order, fixed timestamps) so a regenerated fixture only differs where the importer's output did</t>
-  </si>
-  <si>
-    <t>backend/scripts/export_golden_json.py, frontend/tests/fixtures/golden/*.json</t>
-  </si>
-  <si>
-    <t>two consecutive exports byte-identical; tests/test_golden_documents.py::test_the_frontend_golden_json_is_current</t>
-  </si>
-  <si>
-    <t>FID-002 committed and pushed (phase-01e-import-detections)</t>
-  </si>
-  <si>
-    <t>SEC-022: formatting rule values validated at every entry and at resolve; CSS break-out via element style/page settings/instructions closed</t>
-  </si>
-  <si>
-    <t>backend/app/formatting/values.py, backend/app/formatting/engine.py, backend/app/schemas/formatting.py, backend/app/schemas/document.py, backend/app/ai/instruction_extraction.py, backend/tests/test_rule_values.py</t>
-  </si>
-  <si>
-    <t>FMT-005: instruction-path rule values validated before reaching CSS/export (with SEC-022)</t>
-  </si>
-  <si>
-    <t>EDIT-008: pasted/shortcut alignment saved as the element's own style and kept on split; paste into an empty paragraph keeps the pasted paragraphs' attributes</t>
-  </si>
-  <si>
-    <t>frontend/editor/tiptapToDocument.ts, frontend/editor/documentToTiptap.ts, frontend/editor/useAutoSave.ts, frontend/editor/pasteIntoEmptyBlock.ts, frontend/editor/extensions.ts, frontend/services/api/documents.ts, backend/app/schemas/document.py, backend/app/formatting/engine.py, backend/app/services/document_service.py, backend/app/api/documents.py</t>
-  </si>
-  <si>
-    <t>EDIT-009: pasted picture size kept as the picture's width share</t>
-  </si>
-  <si>
-    <t>EDIT-012: values outside the model named in the status bar and the Проверка panel</t>
-  </si>
-  <si>
-    <t>EDIT-011: cell alignment from pasted cells kept per column; differing cells and column widths reported</t>
-  </si>
-  <si>
-    <t>EDIT-008, EDIT-009, EDIT-012, SEC-022, FMT-005</t>
-  </si>
-  <si>
-    <t>Committed and pushed phase-01f-editor-direct-formatting</t>
-  </si>
-  <si>
-    <t>EDIT-010: link titles kept from Word/Markdown through the editor back into Word</t>
-  </si>
-  <si>
-    <t>backend/app/models/document.py, backend/app/parsers/docx_inline.py, backend/app/parsers/docx.py, backend/app/export/docx_export.py, backend/app/parsers/markdown.py, frontend/editor/tiptapToDocument.ts, frontend/editor/documentToTiptap.ts</t>
-  </si>
-  <si>
-    <t>FID-006: Markdown pictures named as left out (content), thematic breaks kept as rules</t>
-  </si>
-  <si>
-    <t>backend/app/parsers/markdown.py, backend/app/capabilities.py, backend/tests/test_capabilities.py, backend/tests/test_markdown_parser.py</t>
-  </si>
-  <si>
-    <t>EDIT-011: cell alignment/widths the model can't hold are named; keeping them moves to DOCX-017</t>
-  </si>
-  <si>
-    <t>EDIT-007: marks in one canonical order (MarkType) on both sides; opening a document saves nothing</t>
-  </si>
-  <si>
-    <t>backend/app/models/document.py, frontend/editor/tiptapToDocument.ts</t>
-  </si>
-  <si>
-    <t>TEST-010: nested-structure regression suite consolidated and verified</t>
-  </si>
-  <si>
-    <t>EDIT-008, EDIT-010, FID-006</t>
-  </si>
-  <si>
-    <t>Phase 1 browser check in the throwaway stack: Markdown doc with a picture -&gt; 'Body text complete, some content left out · 1 to review' (picture named with its description), '---' imported as a rule; pasted centred line + 160px picture + hsl colour + titled link at the end -&gt; status 'Saved · 1 formatting change not kept', Проверка 'While editing' lists the colour; after reload: line centred, picture width 24.9%, link title kept, notice gone</t>
-  </si>
-  <si>
-    <t>manual browser check (throwaway stack, fresh SQLite)</t>
-  </si>
-  <si>
-    <t>DOCS-011: documentation tree started for Phase 1 (document model, fidelity, docx, formatting, security, testing)</t>
-  </si>
-  <si>
-    <t>EDIT-007, EDIT-010, EDIT-011, FID-006, TEST-010, DOCS-011</t>
-  </si>
-  <si>
-    <t>Committed and pushed phase-01g-phase-1-complete; Phase 1 complete</t>
-  </si>
-  <si>
-    <t>AI-001: order/count/token/numeric/punctuation-aware comparator for AI output, with classified differences</t>
-  </si>
-  <si>
-    <t>backend/app/fidelity/text_check.py, backend/tests/test_ai_fidelity.py</t>
-  </si>
-  <si>
-    <t>AI-002: numbers and units protected; changed_numbers for cross-language checks</t>
-  </si>
-  <si>
-    <t>AI-003: structure analysis refuses answers that alter the text, per piece, logging without content</t>
-  </si>
-  <si>
-    <t>backend/app/ai/structure_analysis.py</t>
-  </si>
-  <si>
-    <t>AI-004: adversarial fidelity tests for every alteration the brief names</t>
-  </si>
-  <si>
-    <t>AI-001, AI-002, AI-003, AI-004</t>
-  </si>
-  <si>
-    <t>Committed and pushed phase-02a-ai-fidelity-check</t>
-  </si>
-  <si>
-    <t>AI-005: AI operations classified FORMAT/STRUCTURE/CONTENT; per-element instruction styles no longer dropped by the formatting pass</t>
-  </si>
-  <si>
-    <t>backend/app/formatting/proposals.py, backend/app/services/document_service.py</t>
-  </si>
-  <si>
-    <t>REV-001: change model with categories, used for proposals</t>
-  </si>
-  <si>
-    <t>backend/app/models/document.py, frontend/types/document.ts</t>
-  </si>
-  <si>
-    <t>AI-006: PLAN-&gt;VALIDATE-&gt;PREVIEW-&gt;ACCEPT-&gt;APPLY for AI content changes</t>
-  </si>
-  <si>
-    <t>backend/app/formatting/proposals.py, backend/app/services/document_service.py, backend/app/api/documents.py, backend/app/jobs/runner.py, backend/app/schemas/document.py, backend/app/schemas/jobs.py</t>
-  </si>
-  <si>
-    <t>AI-007: proposal review UI with accept/reject, E2E verified</t>
-  </si>
-  <si>
-    <t>frontend/editor/panels/ProposalsList.tsx, frontend/editor/panels/InstructionsPanel.tsx, frontend/editor/EditorStatusBar.tsx, frontend/editor/useFormatting.ts, frontend/services/api/documents.ts, frontend/services/api/jobs.ts, backend/scripts/e2e_ai.py, backend/scripts/e2e_server.py</t>
-  </si>
-  <si>
-    <t>AI-005, REV-001, AI-006, AI-007</t>
-  </si>
-  <si>
-    <t>Committed and pushed phase-02b-ai-proposals</t>
-  </si>
-  <si>
-    <t>AI-008: per-job/per-request AI call and time budget; no unbounded retries</t>
-  </si>
-  <si>
-    <t>backend/app/ai/budget.py, backend/app/config.py, backend/app/jobs/runner.py, backend/app/api/deps.py, backend/app/ai/structure_analysis.py</t>
-  </si>
-  <si>
-    <t>Committed and pushed phase-02c-ai-budget</t>
-  </si>
-  <si>
-    <t>AI-009: prompt-injection review; AI answer fields bounded; hostile-document tests</t>
-  </si>
-  <si>
-    <t>backend/app/ai/schemas.py, backend/app/ai/structure_analysis.py, backend/tests/test_prompt_injection.py</t>
-  </si>
-  <si>
-    <t>SEC-018: prompt injection / AI output abuse covered by AI-009's tests</t>
-  </si>
-  <si>
-    <t>AI-001, AI-005, AI-007, AI-009</t>
-  </si>
-  <si>
-    <t>Phase 2 gate: backend 817 passed/1 skipped, Vitest 117, Playwright 20; browser check in the throwaway stack - 'make the title red and delete “This draft paragraph”': title red at once, the paragraph kept and shown under Changes to review (struck through, with the instruction), notice + '1 AI change to review'; Accept removed it, reload kept it removed with nothing pending</t>
-  </si>
-  <si>
-    <t>full suites + manual browser check</t>
-  </si>
-  <si>
-    <t>DOCX-010: original Word package kept as an immutable, checksummed asset</t>
-  </si>
-  <si>
-    <t>backend/app/models/document.py, backend/app/services/document_service.py</t>
-  </si>
-  <si>
-    <t>DOCX-011: Word exports written into the original package; import report reflects what they keep</t>
-  </si>
-  <si>
-    <t>backend/app/export/docx_export.py, backend/app/fidelity/imports.py, backend/app/fidelity/docx_source.py, backend/app/fidelity/docx_detect.py, backend/app/fidelity/exports.py, backend/app/jobs/runner.py, backend/app/api/documents.py, backend/app/capabilities.py</t>
-  </si>
-  <si>
-    <t>TEST-023: independent package validation of every Word export</t>
-  </si>
-  <si>
-    <t>backend/app/export/package_check.py, backend/tests/test_package_check.py</t>
-  </si>
-  <si>
-    <t>DOCX-012: metadata preserved (core in the model, app/custom/labels via the original package)</t>
-  </si>
-  <si>
-    <t>DOCX-028: unchanged blocks keep their original XML in Word exports; server-side provenance; earlier sections follow page setup, header and page-number changes; lost sections reported; golden 13-kept-blocks + E2E.</t>
-  </si>
-  <si>
-    <t>backend/app/export/provenance.py, backend/app/export/docx_export.py, backend/app/parsers/docx.py, backend/app/models/document.py, backend/app/services/document_service.py, backend/app/fidelity/imports.py, backend/app/fidelity/exports.py, backend/app/capabilities.py, frontend/editor/tiptapToDocument.ts, frontend/e2e/kept-blocks.spec.ts, docs/docx/README.md</t>
-  </si>
-  <si>
-    <t>DOCX-028 committed and pushed as c8c2d27 (phase-03b-original-blocks).</t>
-  </si>
-  <si>
-    <t>DOCX-025: Word's hidden text stays hidden - hidden mark with Word's style resolution, editor shows it only on request, vanish in Word exports, left out of PDF with a note, consistent content checks.</t>
-  </si>
-  <si>
-    <t>backend/app/models/document.py, backend/app/parsers/docx_inline.py, backend/app/parsers/docx_styles.py, backend/app/parsers/docx.py, backend/app/fidelity/docx_detect.py, backend/app/fidelity/content.py, backend/app/fidelity/exports.py, backend/app/export/docx_export.py, backend/app/export/pdf_export.py, frontend/editor/hiddenText.ts, frontend/editor/EditorStatusBar.tsx, frontend/editor/DocumentEditorShell.tsx, frontend/app/globals.css</t>
-  </si>
-  <si>
-    <t>DOCX-025 committed and pushed as 7d1af86 (phase-03c-hidden-text).</t>
-  </si>
-  <si>
-    <t>DOCX-013 part 1: underline and strike styles, capitals, small capitals, spacing and raised/lowered text kept through import, editor, Word and PDF; paragraph-style formatting turned off by a run fixed.</t>
-  </si>
-  <si>
-    <t>backend/app/models/document.py, backend/app/parsers/docx_inline.py, backend/app/parsers/docx_styles.py, backend/app/parsers/docx.py, backend/app/export/docx_export.py, backend/app/export/pdf_export.py, backend/app/fidelity/*, frontend/editor/characterFormatting.ts, frontend/editor/tiptapToDocument.ts</t>
-  </si>
-  <si>
-    <t>backend 888 passed/1 skipped (tests/test_character_formatting.py 12); Vitest 128 (editor/characterFormatting.test.ts 3, golden round trip of 02); Playwright 22; tsc + eslint clean</t>
-  </si>
-  <si>
-    <t>DOCX-013 part 1 committed and pushed as 6619159 (phase-03d-character-formatting); part 2 next.</t>
-  </si>
-  <si>
-    <t>6619159</t>
-  </si>
-  <si>
-    <t>FID-007: reports follow the Word copy - kept while unchanged at import, rewritten losses named at export, unsafe links never copied back.</t>
-  </si>
-  <si>
-    <t>backend/app/fidelity/imports.py, backend/app/export/docx_export.py, backend/tests/test_copy_reports.py</t>
-  </si>
-  <si>
-    <t>DOCX-013 part 2: language kept; scale and effects named and kept while unchanged; brief §22 list is now supported, preserved or explicitly named.</t>
-  </si>
-  <si>
-    <t>backend/app/models/document.py, backend/app/parsers/docx_inline.py, backend/app/fidelity/docx_detect.py, frontend/editor/characterFormatting.ts</t>
-  </si>
-  <si>
-    <t>DOCX-013 done: part 1 6619159, part 2 d32c6a6 (phase-03e-copy-reports).</t>
-  </si>
-  <si>
-    <t>FID-007 committed and pushed as d32c6a6.</t>
-  </si>
-  <si>
-    <t>DOCX-014 part 1: right indent, shading, pagination controls, contextual spacing and direction kept through import, CSS, Word and PDF.</t>
-  </si>
-  <si>
-    <t>backend/app/models/document.py, backend/app/formatting/*, backend/app/parsers/docx_styles.py, backend/app/parsers/docx.py, backend/app/export/docx_export.py, backend/app/export/pdf_export.py</t>
-  </si>
-  <si>
-    <t>backend 903 passed/1 skipped (tests/test_paragraph_formatting.py 9); Vitest 129; Playwright 22; tsc + eslint clean</t>
-  </si>
-  <si>
-    <t>DOCX-014 part 1 committed and pushed as eade93e (phase-03f-paragraph-formatting); part 2 next.</t>
-  </si>
-  <si>
-    <t>eade93e</t>
-  </si>
-  <si>
-    <t>DOCX-014 part 2: paragraph borders and tab stops kept through import, CSS, Word and PDF; what the PDF and editor can't draw is named.</t>
-  </si>
-  <si>
-    <t>backend/app/formatting/values.py, backend/app/parsers/docx_styles.py, backend/app/export/docx_export.py, backend/app/export/pdf_export.py, backend/tests/test_paragraph_formatting.py</t>
-  </si>
-  <si>
-    <t>DOCX-014 done: part 1 eade93e, part 2 c158722 (phase-03g-borders-tab-stops).</t>
-  </si>
-  <si>
-    <t>DOCX-015 part 1a: section breaks are elements with their section's settings - imported, shown and paginated in the editor, written back into Word from the model.</t>
-  </si>
-  <si>
-    <t>backend/app/models/document.py, backend/app/parsers/docx.py, backend/app/export/docx_export.py, frontend/editor/sectionBreak.ts, frontend/editor/pagination.ts</t>
-  </si>
-  <si>
-    <t>tests/test_docx_detect.py::test_a_section_break_breaks_the_page_only_where_word_does; tests/test_sections.py (6); frontend/editor/sectionBreak.test.ts (3); backend 919 passed/1 skipped; Vitest 132; Playwright 22</t>
-  </si>
-  <si>
-    <t>DOCX-015 part 1a committed and pushed as 047685d (phase-03h-section-breaks); part 1b next.</t>
-  </si>
-  <si>
     <t>DOCX-015 part 1b: the PDF follows each section's page setup, even/odd starts and numbering.</t>
   </si>
   <si>
     <t>backend/app/export/pdf_export.py, backend/app/fidelity/exports.py, backend/tests/test_sections.py</t>
   </si>
   <si>
+    <t>DOCX-015 part 1b committed and pushed as 35c6771 (phase-03i-pdf-sections); part 2 next.</t>
+  </si>
+  <si>
     <t>SESSION_STATE — Where the work stands</t>
   </si>
   <si>
@@ -4687,7 +4693,7 @@
     <t>Current Commit</t>
   </si>
   <si>
-    <t>cb75ebd (+ uncommitted changes)</t>
+    <t>35c6771 (+ uncommitted changes)</t>
   </si>
   <si>
     <t>backend 920 passed, 1 skipped; vitest 132; e2e 22; tsc; eslint</t>
@@ -4708,7 +4714,7 @@
     <t>cd backend &amp;&amp; venv/Scripts/python -m pytest -q tests/test_sections.py tests/test_source_package.py</t>
   </si>
   <si>
-    <t>2026-09-27T23:32:40+03:00</t>
+    <t>2026-09-27T23:33:18+03:00</t>
   </si>
   <si>
     <t>Resume Instructions</t>
@@ -9415,7 +9421,7 @@
       </c>
       <c r="F15" s="1" t="str">
         <f>IF(SESSION_STATE!$B$17="","",SESSION_STATE!$B$17)</f>
-        <v>2026-09-27T23:32:40+03:00</v>
+        <v>2026-09-27T23:33:18+03:00</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
@@ -22283,7 +22289,7 @@
     <tabColor rgb="FF7F7F7F"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I88"/>
+  <dimension ref="A1:I89"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17" customWidth="1"/>
@@ -24420,7 +24426,7 @@
         <v>1065</v>
       </c>
       <c r="H87" s="12" t="s">
-        <v>516</v>
+        <v>1525</v>
       </c>
       <c r="I87" s="18"/>
     </row>
@@ -24435,10 +24441,10 @@
         <v>3</v>
       </c>
       <c r="D88" s="18" t="s">
-        <v>1525</v>
+        <v>1526</v>
       </c>
       <c r="E88" s="18" t="s">
-        <v>1526</v>
+        <v>1527</v>
       </c>
       <c r="F88" s="18" t="s">
         <v>514</v>
@@ -24447,12 +24453,37 @@
         <v>1065</v>
       </c>
       <c r="H88" s="12" t="s">
+        <v>1525</v>
+      </c>
+      <c r="I88" s="18"/>
+    </row>
+    <row r="89" spans="1:9" ht="114.75" x14ac:dyDescent="0.25">
+      <c r="A89" s="19">
+        <v>46292.981423611112</v>
+      </c>
+      <c r="B89" s="12" t="s">
+        <v>510</v>
+      </c>
+      <c r="C89" s="12">
+        <v>3</v>
+      </c>
+      <c r="D89" s="18" t="s">
+        <v>1528</v>
+      </c>
+      <c r="E89" s="18"/>
+      <c r="F89" s="18" t="s">
+        <v>514</v>
+      </c>
+      <c r="G89" s="12" t="s">
+        <v>1065</v>
+      </c>
+      <c r="H89" s="12" t="s">
         <v>516</v>
       </c>
-      <c r="I88" s="18"/>
+      <c r="I89" s="18"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I88" xr:uid="{00000000-0009-0000-0000-000011000000}"/>
+  <autoFilter ref="A1:I89" xr:uid="{00000000-0009-0000-0000-000011000000}"/>
   <conditionalFormatting sqref="G2:G5000">
     <cfRule type="cellIs" dxfId="4" priority="1" operator="equal">
       <formula>"PASS"</formula>
@@ -24489,7 +24520,7 @@
   <sheetData>
     <row r="1" spans="1:2" ht="20.25" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
-        <v>1527</v>
+        <v>1529</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -24499,15 +24530,15 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>1528</v>
+        <v>1530</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="10" t="s">
-        <v>1529</v>
+        <v>1531</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>1530</v>
+        <v>1532</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -24515,7 +24546,7 @@
         <v>6</v>
       </c>
       <c r="B5" s="18" t="s">
-        <v>1531</v>
+        <v>1533</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="25.5" x14ac:dyDescent="0.25">
@@ -24523,7 +24554,7 @@
         <v>9</v>
       </c>
       <c r="B6" s="18" t="s">
-        <v>1532</v>
+        <v>1534</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="25.5" x14ac:dyDescent="0.25">
@@ -24531,7 +24562,7 @@
         <v>12</v>
       </c>
       <c r="B7" s="18" t="s">
-        <v>1533</v>
+        <v>1535</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="25.5" x14ac:dyDescent="0.25">
@@ -24539,23 +24570,23 @@
         <v>15</v>
       </c>
       <c r="B8" s="18" t="s">
-        <v>1534</v>
+        <v>1536</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>1535</v>
+        <v>1537</v>
       </c>
       <c r="B9" s="18" t="s">
-        <v>1536</v>
+        <v>1538</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
-        <v>1537</v>
+        <v>1539</v>
       </c>
       <c r="B10" s="18" t="s">
-        <v>1538</v>
+        <v>1540</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
@@ -24563,7 +24594,7 @@
         <v>26</v>
       </c>
       <c r="B11" s="18" t="s">
-        <v>1539</v>
+        <v>1541</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
@@ -24571,7 +24602,7 @@
         <v>29</v>
       </c>
       <c r="B12" s="18" t="s">
-        <v>1540</v>
+        <v>1542</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="25.5" x14ac:dyDescent="0.25">
@@ -24579,7 +24610,7 @@
         <v>32</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>1541</v>
+        <v>1543</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="25.5" x14ac:dyDescent="0.25">
@@ -24587,7 +24618,7 @@
         <v>18</v>
       </c>
       <c r="B14" s="18" t="s">
-        <v>1542</v>
+        <v>1544</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
@@ -24595,7 +24626,7 @@
         <v>21</v>
       </c>
       <c r="B15" s="18" t="s">
-        <v>1543</v>
+        <v>1545</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
@@ -24603,7 +24634,7 @@
         <v>24</v>
       </c>
       <c r="B16" s="18" t="s">
-        <v>1544</v>
+        <v>1546</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
@@ -24611,20 +24642,20 @@
         <v>35</v>
       </c>
       <c r="B17" s="18" t="s">
-        <v>1545</v>
+        <v>1547</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
-        <v>1546</v>
+        <v>1548</v>
       </c>
       <c r="B18" s="18" t="s">
-        <v>1547</v>
+        <v>1549</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="6" t="s">
-        <v>1548</v>
+        <v>1550</v>
       </c>
       <c r="B19" s="18" t="str">
         <f>"Tasks "&amp;DASHBOARD!B5&amp;" · done "&amp;DASHBOARD!B6&amp;" · verified "&amp;DASHBOARD!B7&amp;" · in progress "&amp;DASHBOARD!B8&amp;" · blocked "&amp;DASHBOARD!B9&amp;" · failed "&amp;DASHBOARD!B10&amp;" · P0 open "&amp;DASHBOARD!B16&amp;" · P1 open "&amp;DASHBOARD!B17</f>
@@ -24633,7 +24664,7 @@
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
-        <v>1549</v>
+        <v>1551</v>
       </c>
       <c r="B20" s="18" t="s">
         <v>1364</v>
@@ -24641,7 +24672,7 @@
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" s="6" t="s">
-        <v>1550</v>
+        <v>1552</v>
       </c>
       <c r="B21" s="18" t="s">
         <v>1366</v>
@@ -32474,7 +32505,7 @@
   <sheetData>
     <row r="1" spans="1:9" ht="20.25" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
-        <v>1551</v>
+        <v>1553</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
@@ -32484,16 +32515,16 @@
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
-        <v>1552</v>
+        <v>1554</v>
       </c>
       <c r="B3" s="6" t="s">
         <v>1065</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>1553</v>
+        <v>1555</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>1554</v>
+        <v>1556</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
@@ -32516,10 +32547,10 @@
     </row>
     <row r="6" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>1555</v>
+        <v>1557</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>1556</v>
+        <v>1558</v>
       </c>
       <c r="C6" s="10" t="s">
         <v>57</v>
@@ -32545,16 +32576,16 @@
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="15" t="s">
-        <v>1557</v>
+        <v>1559</v>
       </c>
       <c r="B7" s="18" t="s">
-        <v>1558</v>
+        <v>1560</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>1554</v>
+        <v>1556</v>
       </c>
       <c r="D7" s="18" t="s">
-        <v>1559</v>
+        <v>1561</v>
       </c>
       <c r="E7" s="16">
         <f>SUMPRODUCT(ISNUMBER(SEARCH(","&amp;MASTER!$A$2:$A$2000&amp;",",","&amp;SUBSTITUTE($D7," ","")&amp;","))*((MASTER!$G$2:$G$2000="DONE")))</f>
@@ -32570,13 +32601,13 @@
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="15" t="s">
-        <v>1560</v>
+        <v>1562</v>
       </c>
       <c r="B8" s="18" t="s">
-        <v>1561</v>
+        <v>1563</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>1554</v>
+        <v>1556</v>
       </c>
       <c r="D8" s="18" t="s">
         <v>653</v>
@@ -32595,16 +32626,16 @@
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="15" t="s">
-        <v>1562</v>
+        <v>1564</v>
       </c>
       <c r="B9" s="18" t="s">
-        <v>1563</v>
+        <v>1565</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>1554</v>
+        <v>1556</v>
       </c>
       <c r="D9" s="18" t="s">
-        <v>1564</v>
+        <v>1566</v>
       </c>
       <c r="E9" s="16">
         <f>SUMPRODUCT(ISNUMBER(SEARCH(","&amp;MASTER!$A$2:$A$2000&amp;",",","&amp;SUBSTITUTE($D9," ","")&amp;","))*((MASTER!$G$2:$G$2000="DONE")))</f>
@@ -32620,13 +32651,13 @@
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="15" t="s">
-        <v>1565</v>
+        <v>1567</v>
       </c>
       <c r="B10" s="18" t="s">
-        <v>1566</v>
+        <v>1568</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>1554</v>
+        <v>1556</v>
       </c>
       <c r="D10" s="18" t="s">
         <v>727</v>
@@ -32645,16 +32676,16 @@
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="15" t="s">
-        <v>1567</v>
+        <v>1569</v>
       </c>
       <c r="B11" s="18" t="s">
-        <v>1568</v>
+        <v>1570</v>
       </c>
       <c r="C11" s="12" t="s">
-        <v>1554</v>
+        <v>1556</v>
       </c>
       <c r="D11" s="18" t="s">
-        <v>1569</v>
+        <v>1571</v>
       </c>
       <c r="E11" s="16">
         <f>SUMPRODUCT(ISNUMBER(SEARCH(","&amp;MASTER!$A$2:$A$2000&amp;",",","&amp;SUBSTITUTE($D11," ","")&amp;","))*((MASTER!$G$2:$G$2000="DONE")))</f>
@@ -32670,13 +32701,13 @@
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="15" t="s">
-        <v>1570</v>
+        <v>1572</v>
       </c>
       <c r="B12" s="18" t="s">
-        <v>1571</v>
+        <v>1573</v>
       </c>
       <c r="C12" s="12" t="s">
-        <v>1554</v>
+        <v>1556</v>
       </c>
       <c r="D12" s="18" t="s">
         <v>585</v>
@@ -32695,13 +32726,13 @@
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="15" t="s">
-        <v>1572</v>
+        <v>1574</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>1573</v>
+        <v>1575</v>
       </c>
       <c r="C13" s="12" t="s">
-        <v>1554</v>
+        <v>1556</v>
       </c>
       <c r="D13" s="18" t="s">
         <v>585</v>
@@ -32720,13 +32751,13 @@
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="15" t="s">
-        <v>1574</v>
+        <v>1576</v>
       </c>
       <c r="B14" s="18" t="s">
-        <v>1575</v>
+        <v>1577</v>
       </c>
       <c r="C14" s="12" t="s">
-        <v>1554</v>
+        <v>1556</v>
       </c>
       <c r="D14" s="18" t="s">
         <v>831</v>
@@ -32745,13 +32776,13 @@
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="15" t="s">
-        <v>1576</v>
+        <v>1578</v>
       </c>
       <c r="B15" s="18" t="s">
-        <v>1577</v>
+        <v>1579</v>
       </c>
       <c r="C15" s="12" t="s">
-        <v>1554</v>
+        <v>1556</v>
       </c>
       <c r="D15" s="18" t="s">
         <v>760</v>
@@ -32770,13 +32801,13 @@
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" s="15" t="s">
-        <v>1578</v>
+        <v>1580</v>
       </c>
       <c r="B16" s="18" t="s">
-        <v>1579</v>
+        <v>1581</v>
       </c>
       <c r="C16" s="12" t="s">
-        <v>1554</v>
+        <v>1556</v>
       </c>
       <c r="D16" s="18" t="s">
         <v>811</v>
@@ -32795,13 +32826,13 @@
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" s="15" t="s">
-        <v>1580</v>
+        <v>1582</v>
       </c>
       <c r="B17" s="18" t="s">
-        <v>1581</v>
+        <v>1583</v>
       </c>
       <c r="C17" s="12" t="s">
-        <v>1554</v>
+        <v>1556</v>
       </c>
       <c r="D17" s="18" t="s">
         <v>799</v>
@@ -32820,13 +32851,13 @@
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" s="15" t="s">
-        <v>1582</v>
+        <v>1584</v>
       </c>
       <c r="B18" s="18" t="s">
-        <v>1583</v>
+        <v>1585</v>
       </c>
       <c r="C18" s="12" t="s">
-        <v>1554</v>
+        <v>1556</v>
       </c>
       <c r="D18" s="18" t="s">
         <v>911</v>
@@ -32845,13 +32876,13 @@
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" s="15" t="s">
-        <v>1584</v>
+        <v>1586</v>
       </c>
       <c r="B19" s="18" t="s">
-        <v>1585</v>
+        <v>1587</v>
       </c>
       <c r="C19" s="12" t="s">
-        <v>1554</v>
+        <v>1556</v>
       </c>
       <c r="D19" s="18" t="s">
         <v>217</v>
@@ -32870,16 +32901,16 @@
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" s="15" t="s">
-        <v>1586</v>
+        <v>1588</v>
       </c>
       <c r="B20" s="18" t="s">
-        <v>1587</v>
+        <v>1589</v>
       </c>
       <c r="C20" s="12" t="s">
-        <v>1554</v>
+        <v>1556</v>
       </c>
       <c r="D20" s="18" t="s">
-        <v>1588</v>
+        <v>1590</v>
       </c>
       <c r="E20" s="16">
         <f>SUMPRODUCT(ISNUMBER(SEARCH(","&amp;MASTER!$A$2:$A$2000&amp;",",","&amp;SUBSTITUTE($D20," ","")&amp;","))*((MASTER!$G$2:$G$2000="DONE")))</f>
@@ -32895,13 +32926,13 @@
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" s="15" t="s">
-        <v>1589</v>
+        <v>1591</v>
       </c>
       <c r="B21" s="18" t="s">
-        <v>1590</v>
+        <v>1592</v>
       </c>
       <c r="C21" s="12" t="s">
-        <v>1554</v>
+        <v>1556</v>
       </c>
       <c r="D21" s="18" t="s">
         <v>892</v>
@@ -35639,7 +35670,7 @@
       </c>
       <c r="J68" s="12" t="str">
         <f>IFERROR(INDEX(MASTER!$P$2:$P$2000,MATCH($A68,MASTER!$A$2:$A$2000,0))&amp;"","")</f>
-        <v>047685d</v>
+        <v>35c6771</v>
       </c>
       <c r="K68" s="12" t="str">
         <f>IFERROR(INDEX(MASTER!$Q$2:$Q$2000,MATCH($A68,MASTER!$A$2:$A$2000,0))&amp;"","")</f>
@@ -39553,7 +39584,7 @@
       </c>
       <c r="J14" s="12" t="str">
         <f>IFERROR(INDEX(MASTER!$P$2:$P$2000,MATCH($A14,MASTER!$A$2:$A$2000,0))&amp;"","")</f>
-        <v>047685d</v>
+        <v>35c6771</v>
       </c>
       <c r="K14" s="12" t="str">
         <f>IFERROR(INDEX(MASTER!$Q$2:$Q$2000,MATCH($A14,MASTER!$A$2:$A$2000,0))&amp;"","")</f>

--- a/SmartDoc_Master_Implementation_Tracker.xlsx
+++ b/SmartDoc_Master_Implementation_Tracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\speed\Desktop\Claude - ПРОЕКТ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A66EAD5A-5483-4BD3-A366-91890D5DF73D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68173812-086B-4DB0-A8F4-FC6CDAE26A7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">AI!$A$7:$L$16</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="15" hidden="1">BILLING_PLANS!$A$25:$L$30</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="17" hidden="1">CHANGE_LOG!$A$1:$I$90</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="17" hidden="1">CHANGE_LOG!$A$1:$I$91</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">CRITICAL_FIXES!$A$31:$L$115</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">DOCUMENT_FIDELITY!$A$7:$L$24</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">DOCX_OOXML!$A$7:$L$28</definedName>
@@ -71,12 +71,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3956" uniqueCount="1598">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3961" uniqueCount="1600">
   <si>
     <t>SmartDoc — Master Implementation Tracker</t>
   </si>
   <si>
-    <t>Production-hardening brief. MASTER holds the task data; every number here is a formula. Updated with tools/tracker/tracker.py. Last written 2026-09-29 15:11 (local time).</t>
+    <t>Production-hardening brief. MASTER holds the task data; every number here is a formula. Updated with tools/tracker/tracker.py. Last written 2026-09-29 15:12 (local time).</t>
   </si>
   <si>
     <t>Overall</t>
@@ -1621,3066 +1621,3072 @@
     <t>backend/models, parsers, export</t>
   </si>
   <si>
+    <t>7bbf7f2</t>
+  </si>
+  <si>
+    <t>Fixed: a section's w:type describes how THAT section starts (ECMA-376 17.6.22) - the importer used the ending section's own type, so a continuous break became a page break and continuous-&gt;new-page put the break between the wrong sections (probe confirmed). Now the next section's type decides. Per-section differences are reported (FID-002). Remaining: sections as a first-class model concept (orientation/margins/columns/headers per section, page-number restart) and export of several sections.; With DOCX-011 the last section's properties (columns, page numbering, borders, line numbers, vertical alignment, header/footer variants) are kept in Word exports; earlier sections' are still reported lost.; DOCX-028: earlier sections now survive in Word exports while their ending paragraph is unchanged; page setup/header/page-number changes apply to them; a lost one is reported (export.docx.section_lost). Modelling sections is still this task.</t>
+  </si>
+  <si>
+    <t>DOCX-016</t>
+  </si>
+  <si>
+    <t>Numbering engine</t>
+  </si>
+  <si>
+    <t>Decimal/roman/alpha/bullets, custom prefixes/suffixes, start, restart, continuation, multilevel, numId/abstractNum/ilvl, indentation.</t>
+  </si>
+  <si>
+    <t>tests/test_docx_numbering.py</t>
+  </si>
+  <si>
+    <t>Done so far: top-level list number format (decimal/roman/letters), start value (lvl start + lvlOverride/startOverride) and continuation across interrupting paragraphs imported into Element.numbering and written back to Word (per-level formats, startOverride) and PDF; empty numbered items keep counting. Reported, not kept: custom labels ('Чл. 1.', '(a)'), multi-level labels ('1.1'), numbered headings baked into text. Remaining: prefixes/suffixes, multilevel numbering model, restart semantics per level, indentation.</t>
+  </si>
+  <si>
+    <t>AUD-04</t>
+  </si>
+  <si>
+    <t>DOCX-017</t>
+  </si>
+  <si>
+    <t>Table engine</t>
+  </si>
+  <si>
+    <t>No forced header or Table Grid; widths, heights, margins, borders, shading, v-align, nested tables, repeated header rows, table styles.</t>
+  </si>
+  <si>
+    <t>From EDIT-011 (2026-09-27): add per-cell alignment and column widths to the model (the editor's cell align/colwidth, Word tcW/tblGrid, PDF colWidths); until then the editor names them as not kept.</t>
+  </si>
+  <si>
+    <t>DOCX-018</t>
+  </si>
+  <si>
+    <t>Images</t>
+  </si>
+  <si>
+    <t>Alt text exported; crop, rotation, anchor, wrap, position preserved; WEBP converted on export.</t>
+  </si>
+  <si>
+    <t>Alt text + title now exported (docPr descr/title) with DOCX-001; crop, rotation, WEBP still open.</t>
+  </si>
+  <si>
+    <t>DOCX-019</t>
+  </si>
+  <si>
+    <t>Drawings and text boxes preserved</t>
+  </si>
+  <si>
+    <t>Anchored drawings, text boxes, shapes kept even when not editable.</t>
+  </si>
+  <si>
+    <t>DOCX-028: text boxes and drawings in unchanged paragraphs are copied as they are (grouped with their anchor paragraph).</t>
+  </si>
+  <si>
+    <t>DOCX-020</t>
+  </si>
+  <si>
+    <t>Fields</t>
+  </si>
+  <si>
+    <t>Code/result/relationship; header STYLEREF/DATE live; TOC kept; CITATION/BIBLIOGRAPHY sources preserved; no 'Invalid source specified.'</t>
+  </si>
+  <si>
+    <t>backend/parsers, export</t>
+  </si>
+  <si>
+    <t>DOCX-028: field codes in unchanged blocks are copied as they are; a field spanning paragraphs is never copied half (self-contained check).</t>
+  </si>
+  <si>
+    <t>AUD-18</t>
+  </si>
+  <si>
+    <t>DOCX-021</t>
+  </si>
+  <si>
+    <t>Comment threads</t>
+  </si>
+  <si>
+    <t>Replies, resolved state, authors, ranges preserved (commentsExtended, people).</t>
+  </si>
+  <si>
+    <t>AUD-06</t>
+  </si>
+  <si>
+    <t>DOCX-022</t>
+  </si>
+  <si>
+    <t>Tracked changes preserved</t>
+  </si>
+  <si>
+    <t>Not silently accepted; explicit choice.</t>
+  </si>
+  <si>
+    <t>DOCX-028: blocks holding tracked changes are never copied (always written anew, accepted), so this task's explicit choice is still needed.</t>
+  </si>
+  <si>
+    <t>DOCX-023</t>
+  </si>
+  <si>
+    <t>Content controls preserved</t>
+  </si>
+  <si>
+    <t>w:sdt of every kind kept with its properties.</t>
+  </si>
+  <si>
+    <t>DOCX-028: content controls in unchanged blocks are copied with their properties (E2E proves it through the editor); written anew they are unwrapped (reported lossy at import).</t>
+  </si>
+  <si>
+    <t>DOCX-024</t>
+  </si>
+  <si>
+    <t>Real footnotes and endnotes</t>
+  </si>
+  <si>
+    <t>Notes stay notes on export.</t>
+  </si>
+  <si>
+    <t>DOCX-025</t>
+  </si>
+  <si>
+    <t>Hidden text stays hidden</t>
+  </si>
+  <si>
+    <t>Imported hidden text is kept hidden, shown only on request.</t>
+  </si>
+  <si>
+    <t>MarkType.HIDDEN (appended; no existing mark order changes). Importer resolves w:vanish as Word does: run, character style, paragraph style (the default paragraph style when none), docDefaults; webHidden stays visible; an explicit vanish=0 shows text in a hidden style. The detector uses the default paragraph style the same way and names hidden text as kept hidden (DETECTED_PRESERVED, not a content change). Editor: non-inclusive hidden mark (editor/hiddenText.ts; Word's display:none paste stays hidden), hidden by CSS unless .show-hidden; status bar 'Show hidden text (N words)' toggles it and re-paginates; the Structure panel leaves hidden text out of headings. Word export writes w:vanish (copied blocks keep theirs); PDF doesn't print hidden runs, export.pdf.hidden_text names the word count, and the PDF content check compares visible words (document_words(visible_only=True)); Word-side checks count hidden text on both sides. Golden 02-rich-text gained a hidden sentence (editor round trip in Vitest).</t>
+  </si>
+  <si>
+    <t>backend 876 passed/1 skipped (tests/test_hidden_text.py 7: import resolution, default paragraph style, report, upload + content check + editor save, Word export round trip, PDF text + note + check); Vitest 125 (editor/hiddenText.test.tsx 6, golden round trip of 02); Playwright 22 (e2e/hidden-text.spec.ts: hidden until asked, dotted line when shown, vanish in the Word export); tsc + eslint clean</t>
+  </si>
+  <si>
+    <t>backend/parsers, frontend</t>
+  </si>
+  <si>
+    <t>7d1af86</t>
+  </si>
+  <si>
+    <t>DOCX-028: vanish survives in unchanged blocks only; the model still shows hidden text as ordinary text - next task.</t>
+  </si>
+  <si>
+    <t>DOCX-026</t>
+  </si>
+  <si>
+    <t>Hyperlink policy and no silent autolink</t>
+  </si>
+  <si>
+    <t>Plain-text addresses not turned into links by default; file:/UNC reported.</t>
+  </si>
+  <si>
+    <t>tests/test_docx_detect.py::test_unsafe_links_and_spacing_paragraphs_are_reported</t>
+  </si>
+  <si>
+    <t>Done: links to unsafe addresses (javascript:, file:, UNC...) are kept as plain text and reported (docx.link.unsafe); plain-text addresses turned into links are reported (docx.autolink). Remaining: stop autolinking by default (a setting), per the task.</t>
+  </si>
+  <si>
+    <t>AUD-03,AUD-13</t>
+  </si>
+  <si>
+    <t>FMT-004</t>
+  </si>
+  <si>
+    <t>Render-spec defaults respect the source</t>
+  </si>
+  <si>
+    <t>Imported Word styles are not overridden by defaults (headings not forced bold).</t>
+  </si>
+  <si>
+    <t>backend/formatting</t>
+  </si>
+  <si>
+    <t>TEST-020</t>
+  </si>
+  <si>
+    <t>Word-authored fixtures in the repository</t>
+  </si>
+  <si>
+    <t>20 synthetic Word-authored fixtures, scrubbed of identifying metadata.</t>
+  </si>
+  <si>
+    <t>backend/tests/fixtures/word</t>
+  </si>
+  <si>
+    <t>TEST-021</t>
+  </si>
+  <si>
+    <t>Expected-loss manifests in CI</t>
+  </si>
+  <si>
+    <t>expected-loss.json per fixture; CI compares actual vs expected.</t>
+  </si>
+  <si>
+    <t>TEST-022</t>
+  </si>
+  <si>
+    <t>True fidelity test</t>
+  </si>
+  <si>
+    <t>SOURCE -&gt; import -&gt; format -&gt; editor save -&gt; export -&gt; reimport -&gt; compare SOURCE vs RESULT: content, formatting, metadata, structure separately.</t>
+  </si>
+  <si>
+    <t>TEST-023</t>
+  </si>
+  <si>
+    <t>Independent validation</t>
+  </si>
+  <si>
+    <t>OOXML schema validation, Word when available, docx2python; pdftotext/PyMuPDF for PDF.</t>
+  </si>
+  <si>
+    <t>app/export/package_check.py: an independent package check (zip read directly): well-formed parts, content types, relationships resolving, relationship ids used, defined styles/lists/comments. Found a real defect on first run (python-docx's add_comment refers to an undefined CommentReference style; exports now define it). Every golden export passes, fresh and into its original.</t>
+  </si>
+  <si>
+    <t>tests/test_package_check.py (13)</t>
+  </si>
+  <si>
+    <t>The docx skill's XSD validator needs defusedxml (not installed; installing needs a download) - schema-level validation remains open.</t>
+  </si>
+  <si>
+    <t>DOCX-027</t>
+  </si>
+  <si>
+    <t>Importer builds nested blocks</t>
+  </si>
+  <si>
+    <t>Use TableCell.blocks / ListItem.blocks on import: pictures, lists (with bullets) and nested tables inside cells, pictures inside list items - instead of dropping or flattening them.</t>
+  </si>
+  <si>
+    <t>AUD-01,AUD-03,AUD-08</t>
+  </si>
+  <si>
+    <t>DOCX-028</t>
+  </si>
+  <si>
+    <t>Unchanged blocks keep their original XML in Word exports</t>
+  </si>
+  <si>
+    <t>Blocks the user didn't change are written back as their original XML (fields, content controls, run-level formatting the model can't hold, bookmarks), changed ones regenerated; needs block provenance from the importer and fingerprints.</t>
+  </si>
+  <si>
+    <t>Importer records each top-level element's body children (Element.sourceBlocks: list items, drop caps, derived page breaks); an upload with a kept file stamps content+look fingerprints (Element.sourceHash, app/export/provenance.py: own/kind/body/nested resolved styles; page breaks have no look). docx_export._copy_plan groups elements with their children (uncovered children join the group before) and copies a group verbatim when every element is unchanged, together and in original order, children contiguous, XML self-contained (no tracked changes/note refs/altChunk; balanced fields, bookmarks, comment ranges); everything else is written anew. Provenance is server-side (keep_provenance on PUT /content). Page setup now runs after the body: changed size/margins reach every kept section (orientation kept, landscape turned), a changed main header is rewritten where Word shows it (link to previous), page numbers left out/asked for apply to every section. export.docx.section_lost (LOSSY) names sections lost with a changed paragraph; import report: earlier sections' setup/headers kept while unchanged; PDF names them Word-only. All 13 golden documents stamped + exported into their originals: sound packages, content verified (12-complex rewrites only the footnote paragraph and the note, by design).</t>
+  </si>
+  <si>
+    <t>backend 869 passed/1 skipped (tests/test_original_blocks.py 26 incl. 13 golden; test_source_package.py rewritten claims with export proof; test_golden_documents.py 13 files); Vitest 119 (editor round trip of 13-kept-blocks); Playwright 21 (e2e/kept-blocks.spec.ts: edit in the real editor, untouched paragraphs keep content control, double underline, landscape section); tsc + eslint clean</t>
+  </si>
+  <si>
+    <t>c8c2d27</t>
+  </si>
+  <si>
+    <t>Follow-up of DOCX-011 (package-level patch writer).; Known limit: any restyle (template, instruction) changes the body look, so every block but page breaks is written anew; follow-up DOCX-029. Sections survive only with their ending paragraph until DOCX-015 models them.</t>
+  </si>
+  <si>
+    <t>DOCX-029</t>
+  </si>
+  <si>
+    <t>Restyled blocks keep their original XML where nothing conflicts</t>
+  </si>
+  <si>
+    <t>After a template or instruction restyles a kind of block, copy a block's original XML when its paragraph style is the Word style the export rewrites for that kind and its direct formatting (pPr/rPr) sets none of the properties that changed; today any restyle writes every block anew (content controls, double underline etc. then lost, as the import report says).</t>
+  </si>
+  <si>
+    <t>Found while finishing DOCX-028: the look is part of the fingerprint so the export never shows a stale look.</t>
+  </si>
+  <si>
+    <t>FID-007</t>
+  </si>
+  <si>
+    <t>Reports follow the Word copy</t>
+  </si>
+  <si>
+    <t>With the original kept, the import report names what lives in blocks as kept in the Word export while the paragraph is unchanged, and an export that writes such a block anew names what it lost; a copy never brings back a link the app doesn't allow.</t>
+  </si>
+  <si>
+    <t>fidelity/imports.py KEPT_WHILE_UNCHANGED (content controls, text boxes, charts/shapes/SmartArt, objects, picture crop/rotation/floating, drop caps, empty paragraphs, approximated underlines, character scale, text effects, RTL) -&gt; detected_not_editable 'kept while the paragraph isn't changed or restyled'; docx_export._copy_plan returns rewritten groups, _lost_in/_rewritten_losses -&gt; export.docx.rewritten_blocks (LOSSY, count, kinds incl. proofing exclusions); _safe_links keeps groups with unsafe links (relationships or HYPERLINK fields) from being copied; the PDF's Word-only note covers the features.</t>
+  </si>
+  <si>
+    <t>tests/test_copy_reports.py (6): kept while unchanged at import, rewritten losses named (content controls, stretched text), unsafe javascript: link never copied back, PDF word-only; backend 894 passed/1 skipped; Playwright 22</t>
+  </si>
+  <si>
+    <t>Generalises DOCX-028's section handling (export.docx.section_lost) to everything the model doesn't hold inside blocks.</t>
+  </si>
+  <si>
+    <t>SEC-010</t>
+  </si>
+  <si>
+    <t>Malformed DOCX -&gt; safe 4xx</t>
+  </si>
+  <si>
+    <t>XML/zip/structure errors map to invalid_file; fuzz corpus shows no 500.</t>
+  </si>
+  <si>
+    <t>AUD-12</t>
+  </si>
+  <si>
+    <t>SEC-011</t>
+  </si>
+  <si>
+    <t>Malformed PDF -&gt; safe 4xx</t>
+  </si>
+  <si>
+    <t>Verified with a fuzz corpus.</t>
+  </si>
+  <si>
+    <t>SEC-012</t>
+  </si>
+  <si>
+    <t>Image resource limits</t>
+  </si>
+  <si>
+    <t>Compressed and decompressed size, pixel count, width, height, images per document, total bytes, format allowlist; rejected before rasterisation.</t>
+  </si>
+  <si>
+    <t>backend/security</t>
+  </si>
+  <si>
+    <t>AUD-09</t>
+  </si>
+  <si>
+    <t>SEC-013</t>
+  </si>
+  <si>
+    <t>PDF bombs, huge XML, decompression limits</t>
+  </si>
+  <si>
+    <t>Reviewed and tested limits.</t>
+  </si>
+  <si>
+    <t>SEC-014</t>
+  </si>
+  <si>
+    <t>Href policy</t>
+  </si>
+  <si>
+    <t>Server-side scheme allowlist; javascript:/data:/vbscript:/file: never exported as active links.</t>
+  </si>
+  <si>
+    <t>backend/models, export</t>
+  </si>
+  <si>
+    <t>AUD-13</t>
+  </si>
+  <si>
+    <t>SEC-015</t>
+  </si>
+  <si>
+    <t>Field instruction allowlist</t>
+  </si>
+  <si>
+    <t>No DDE/INCLUDETEXT/INCLUDEPICTURE/external fields accepted from clients or exported.</t>
+  </si>
+  <si>
+    <t>SEC-016</t>
+  </si>
+  <si>
+    <t>External relationships policy</t>
+  </si>
+  <si>
+    <t>No arbitrary external targets in exports.</t>
+  </si>
+  <si>
+    <t>SEC-017</t>
+  </si>
+  <si>
+    <t>Malicious SVG</t>
+  </si>
+  <si>
+    <t>Verified refused everywhere.</t>
+  </si>
+  <si>
+    <t>SEC-018</t>
+  </si>
+  <si>
+    <t>Prompt injection / AI output abuse</t>
+  </si>
+  <si>
+    <t>Tests with hostile documents; outputs validated.</t>
+  </si>
+  <si>
+    <t>Hostile-document tests: the document can't close its fence; out-of-bounds answers refused and fall back; an instruction steered by the document deletes nothing (proposals only) and a CSS break-out value is dropped; style-analysis flags on unknown elements dropped (see AI-009).</t>
+  </si>
+  <si>
+    <t>tests/test_prompt_injection.py</t>
+  </si>
+  <si>
+    <t>SEC-019</t>
+  </si>
+  <si>
+    <t>Error envelope audit</t>
+  </si>
+  <si>
+    <t>Every error {code, message, details, request_id}; no stack traces to users.</t>
+  </si>
+  <si>
+    <t>backend/api</t>
+  </si>
+  <si>
+    <t>SEC-020</t>
+  </si>
+  <si>
+    <t>CSP without 'unsafe-inline' scripts</t>
+  </si>
+  <si>
+    <t>Nonce-based CSP for the Next.js app.</t>
+  </si>
+  <si>
+    <t>TEST-030</t>
+  </si>
+  <si>
+    <t>Security regression suite</t>
+  </si>
+  <si>
+    <t>Fuzz corpus, pixel bombs, href/field policy, IDOR, CSRF.</t>
+  </si>
+  <si>
+    <t>SEC-010,SEC-012,SEC-014,SEC-015</t>
+  </si>
+  <si>
+    <t>AUD-09,AUD-12,AUD-13</t>
+  </si>
+  <si>
+    <t>SEC-021</t>
+  </si>
+  <si>
+    <t>Sensitivity-label metadata in the public repository</t>
+  </si>
+  <si>
+    <t>корекции.docx (committed in 5f2bf9e, pushed) carries 8 MSIP_Label_* custom properties incl. the organisation's tenant SiteId (label: Microsoft default 'General' family, no content marking). Options: leave; scrub the file in a new commit (HEAD only); purge from history (force-push).</t>
+  </si>
+  <si>
+    <t>repository history</t>
+  </si>
+  <si>
+    <t>Needs Boril: the choice involves his organisation's label and possibly rewriting pushed history. The tracker tools now strip MSIP labels on every write; the pre-push scan flags them.</t>
+  </si>
+  <si>
+    <t>SEC-022</t>
+  </si>
+  <si>
+    <t>Formatting rule values can't break out of a style</t>
+  </si>
+  <si>
+    <t>A rule value reaches the editor's style attribute, Word and PDF styles as text. The element-style and page-setting endpoints accepted any string (e.g. 'center;background-image:url(...)'), the AI instruction path too (FMT-005): CSS injection into every viewer's editor.</t>
+  </si>
+  <si>
+    <t>app/formatting/values.py: clean_rule_value per property (the StyleSystem's limits: choices, true/false, one safe font name, renderable colours, bounded numbers with known units, header/footer text &lt;=500). Refused with 422 by the element-style and page-setting endpoints (schemas RuleValue); instruction rules and set_style operations with such values dropped (FMT-005), validate_operations refuses them; stored rules no renderer can use are skipped at resolve (engine._usable) so old documents can't carry them either. All 177 default/template rules pass unchanged.</t>
+  </si>
+  <si>
+    <t>tests/test_rule_values.py (34 cases incl. API 422, stored-rule skip, instruction drop)</t>
+  </si>
+  <si>
+    <t>Found 2026-09-27 while mapping editor alignment (EDIT-008); probe confirmed the raw value in resolvedStyles.</t>
+  </si>
+  <si>
+    <t>PERF-001</t>
+  </si>
+  <si>
+    <t>Linear DOCX table export</t>
+  </si>
+  <si>
+    <t>500x8 table under a recorded threshold (baseline 321 s).</t>
+  </si>
+  <si>
+    <t>AUD-10</t>
+  </si>
+  <si>
+    <t>PERF-002</t>
+  </si>
+  <si>
+    <t>Benchmarks recorded</t>
+  </si>
+  <si>
+    <t>Baseline and current measurements in the PERFORMANCE sheet.</t>
+  </si>
+  <si>
+    <t>tests/perf</t>
+  </si>
+  <si>
+    <t>PERF-003</t>
+  </si>
+  <si>
+    <t>Delta autosave</t>
+  </si>
+  <si>
+    <t>Change-aware patches with a threshold strategy; whole document only when needed.</t>
+  </si>
+  <si>
+    <t>frontend/editor, backend/api</t>
+  </si>
+  <si>
+    <t>PERF-004</t>
+  </si>
+  <si>
+    <t>Bounded, compressed version history</t>
+  </si>
+  <si>
+    <t>Editor history separate from persisted versions; compression/deltas; asset references.</t>
+  </si>
+  <si>
+    <t>PERF-005</t>
+  </si>
+  <si>
+    <t>Editor at 5k-12k blocks</t>
+  </si>
+  <si>
+    <t>Typing latency measured and improved.</t>
+  </si>
+  <si>
+    <t>PERF-006</t>
+  </si>
+  <si>
+    <t>JSON without ASCII escaping</t>
+  </si>
+  <si>
+    <t>Document JSON stored and sent as UTF-8.</t>
+  </si>
+  <si>
+    <t>backend/db</t>
+  </si>
+  <si>
+    <t>PERF-007</t>
+  </si>
+  <si>
+    <t>Safe size limits recorded</t>
+  </si>
+  <si>
+    <t>User-facing maximum sizes, job timeouts, resource ceilings documented and enforced.</t>
+  </si>
+  <si>
+    <t>backend/config</t>
+  </si>
+  <si>
+    <t>AUD-09,AUD-10</t>
+  </si>
+  <si>
+    <t>ACCT-001</t>
+  </si>
+  <si>
+    <t>E-mail sender abstraction</t>
+  </si>
+  <si>
+    <t>SMTP provider + development outbox; no secrets in logs.</t>
+  </si>
+  <si>
+    <t>AUD-14</t>
+  </si>
+  <si>
+    <t>ACCT-002</t>
+  </si>
+  <si>
+    <t>Password reset</t>
+  </si>
+  <si>
+    <t>Single-use, expiring, hashed tokens; rate-limited; no account enumeration.</t>
+  </si>
+  <si>
+    <t>backend/api, frontend</t>
+  </si>
+  <si>
+    <t>ACCT-003</t>
+  </si>
+  <si>
+    <t>E-mail verification</t>
+  </si>
+  <si>
+    <t>Verification tokens and state.</t>
+  </si>
+  <si>
+    <t>ACCT-004</t>
+  </si>
+  <si>
+    <t>Password change</t>
+  </si>
+  <si>
+    <t>Current password required; other sessions revoked.</t>
+  </si>
+  <si>
+    <t>ACCT-005</t>
+  </si>
+  <si>
+    <t>Account deletion</t>
+  </si>
+  <si>
+    <t>Cascading policy: documents, versions, assets, exports, sessions, jobs, usage.</t>
+  </si>
+  <si>
+    <t>ACCT-006</t>
+  </si>
+  <si>
+    <t>Session revocation and cleanup</t>
+  </si>
+  <si>
+    <t>Sign out everywhere; expired/revoked session sweep.</t>
+  </si>
+  <si>
+    <t>ACCT-007</t>
+  </si>
+  <si>
+    <t>Suspicious login handling</t>
+  </si>
+  <si>
+    <t>Lockout and notification strategy.</t>
+  </si>
+  <si>
+    <t>PLAN-001</t>
+  </si>
+  <si>
+    <t>Usage units</t>
+  </si>
+  <si>
+    <t>Documents, exports, PDF pages, OCR pages, translation characters, AI operations, storage, batch jobs.</t>
+  </si>
+  <si>
+    <t>backend/billing</t>
+  </si>
+  <si>
+    <t>AUD-11</t>
+  </si>
+  <si>
+    <t>PLAN-002</t>
+  </si>
+  <si>
+    <t>Configurable plan defaults</t>
+  </si>
+  <si>
+    <t>Free/Pro/Business initial hypotheses as configuration, never hardcoded.</t>
+  </si>
+  <si>
+    <t>PLAN-003</t>
+  </si>
+  <si>
+    <t>Atomic entitlement checks</t>
+  </si>
+  <si>
+    <t>Reservation/locking; concurrency test proves limits hold.</t>
+  </si>
+  <si>
+    <t>PLAN-004</t>
+  </si>
+  <si>
+    <t>Stripe flows review</t>
+  </si>
+  <si>
+    <t>Checkout, portal, upgrade, downgrade, cancel, renewal, failed payment, webhook idempotency.</t>
+  </si>
+  <si>
+    <t>PLAN-005</t>
+  </si>
+  <si>
+    <t>Storage metering including history</t>
+  </si>
+  <si>
+    <t>History and autosave growth counted.</t>
+  </si>
+  <si>
+    <t>AUD-11,AUD-16</t>
+  </si>
+  <si>
+    <t>PDF-010</t>
+  </si>
+  <si>
+    <t>Geometry-aware PDF parser</t>
+  </si>
+  <si>
+    <t>Chars, fonts, sizes, colours, lines, rectangles, images, links, annotations, outlines, forms, metadata, rotation, page boxes.</t>
+  </si>
+  <si>
+    <t>backend/parsers/pdf</t>
+  </si>
+  <si>
+    <t>PDF-011</t>
+  </si>
+  <si>
+    <t>Page classifier</t>
+  </si>
+  <si>
+    <t>TEXT / SCANNED / HYBRID per page with evidence.</t>
+  </si>
+  <si>
+    <t>PDF-012</t>
+  </si>
+  <si>
+    <t>PDF inspection report</t>
+  </si>
+  <si>
+    <t>What the parser found, per page.</t>
+  </si>
+  <si>
+    <t>P2E-001</t>
+  </si>
+  <si>
+    <t>Layout primitives where PDF needs them</t>
+  </si>
+  <si>
+    <t>Page, block, bbox, rotation, confidence, provenance.</t>
+  </si>
+  <si>
+    <t>P2E-002</t>
+  </si>
+  <si>
+    <t>Structure reconstruction</t>
+  </si>
+  <si>
+    <t>Reading order, lines, paragraphs, headings, lists, captions, header/footer bands, columns.</t>
+  </si>
+  <si>
+    <t>backend/pdf</t>
+  </si>
+  <si>
+    <t>P2E-003</t>
+  </si>
+  <si>
+    <t>Images with position</t>
+  </si>
+  <si>
+    <t>Extracted images kept with bbox.</t>
+  </si>
+  <si>
+    <t>P2E-004</t>
+  </si>
+  <si>
+    <t>Tables from PDF</t>
+  </si>
+  <si>
+    <t>Ruling lines and alignment.</t>
+  </si>
+  <si>
+    <t>P2E-005</t>
+  </si>
+  <si>
+    <t>Confidence and conversion report</t>
+  </si>
+  <si>
+    <t>Per element confidence; issues reported; never silent removal.</t>
+  </si>
+  <si>
+    <t>P2E-006</t>
+  </si>
+  <si>
+    <t>OCR provider abstraction</t>
+  </si>
+  <si>
+    <t>Interface (text, confidence, bbox, page, language/script); implementation(s); OCR output untrusted.</t>
+  </si>
+  <si>
+    <t>backend/ocr</t>
+  </si>
+  <si>
+    <t>P2E-007</t>
+  </si>
+  <si>
+    <t>Imported-from-PDF version and UX</t>
+  </si>
+  <si>
+    <t>Editable document vs layout-focused choice; confidence shown.</t>
+  </si>
+  <si>
+    <t>frontend, backend</t>
+  </si>
+  <si>
+    <t>P2E-008</t>
+  </si>
+  <si>
+    <t>PDF fixtures and tests</t>
+  </si>
+  <si>
+    <t>Text, scanned, hybrid, tables, columns, multilingual.</t>
+  </si>
+  <si>
+    <t>P2E-020</t>
+  </si>
+  <si>
+    <t>Layout-preserving architecture</t>
+  </si>
+  <si>
+    <t>Frames/anchors model hooks and design doc.</t>
+  </si>
+  <si>
+    <t>docs, backend/models</t>
+  </si>
+  <si>
+    <t>PDF-020</t>
+  </si>
+  <si>
+    <t>PDF page operations service</t>
+  </si>
+  <si>
+    <t>Reorder, rotate, delete, duplicate, extract, split, merge as a separate service.</t>
+  </si>
+  <si>
+    <t>TRAN-001</t>
+  </si>
+  <si>
+    <t>Segments and tag protocol</t>
+  </si>
+  <si>
+    <t>Segments keep element/run ids, marks, placeholders; never one giant string.</t>
+  </si>
+  <si>
+    <t>backend/translation</t>
+  </si>
+  <si>
+    <t>TRAN-002</t>
+  </si>
+  <si>
+    <t>TranslationProvider abstraction</t>
+  </si>
+  <si>
+    <t>AI provider implementation + deterministic test provider.</t>
+  </si>
+  <si>
+    <t>TRAN-003</t>
+  </si>
+  <si>
+    <t>Translation validation</t>
+  </si>
+  <si>
+    <t>Tags, numbers, units, dates, percentages, identifiers, glossary terms.</t>
+  </si>
+  <si>
+    <t>TRAN-004</t>
+  </si>
+  <si>
+    <t>Glossary and terminology lock</t>
+  </si>
+  <si>
+    <t>Source/target term, domain, locked, case-sensitive.</t>
+  </si>
+  <si>
+    <t>backend/translation, db</t>
+  </si>
+  <si>
+    <t>TRAN-005</t>
+  </si>
+  <si>
+    <t>Selection/paragraph/block translation proposals</t>
+  </si>
+  <si>
+    <t>Preview; accept/reject; undo.</t>
+  </si>
+  <si>
+    <t>TRAN-003,REV-001</t>
+  </si>
+  <si>
+    <t>TRAN-006</t>
+  </si>
+  <si>
+    <t>Whole-document translated version</t>
+  </si>
+  <si>
+    <t>Source kept; translated copy linked.</t>
+  </si>
+  <si>
+    <t>TRAN-007</t>
+  </si>
+  <si>
+    <t>Language, script, direction metadata</t>
+  </si>
+  <si>
+    <t>Auto-detect + manual override.</t>
+  </si>
+  <si>
+    <t>TRAN-008</t>
+  </si>
+  <si>
+    <t>Translation UX</t>
+  </si>
+  <si>
+    <t>Toolbar/context Translate, target language, preview, accept/reject; 'AI-assisted translation - review required'.</t>
+  </si>
+  <si>
+    <t>TRAN-009</t>
+  </si>
+  <si>
+    <t>Translation metering</t>
+  </si>
+  <si>
+    <t>Translation characters as a usage unit.</t>
+  </si>
+  <si>
+    <t>TRAN-010</t>
+  </si>
+  <si>
+    <t>Translation tests</t>
+  </si>
+  <si>
+    <t>Formatting preservation, validation, versions.</t>
+  </si>
+  <si>
+    <t>FONT-001</t>
+  </si>
+  <si>
+    <t>Font catalogue with Unicode coverage</t>
+  </si>
+  <si>
+    <t>fontTools cmap coverage per script, metrics, embeddability.</t>
+  </si>
+  <si>
+    <t>backend/fonts</t>
+  </si>
+  <si>
+    <t>AUD-17</t>
+  </si>
+  <si>
+    <t>FONT-002</t>
+  </si>
+  <si>
+    <t>FontResolver</t>
+  </si>
+  <si>
+    <t>Script segmentation, coverage, fallback chain, embedding, RTL; deterministic first, AI suggestion validated.</t>
+  </si>
+  <si>
+    <t>FONT-003</t>
+  </si>
+  <si>
+    <t>Multilingual PDF rendering</t>
+  </si>
+  <si>
+    <t>Shaping for Arabic/Hebrew/Devanagari, bidi, CJK fonts, emoji handled gracefully.</t>
+  </si>
+  <si>
+    <t>FONT-004</t>
+  </si>
+  <si>
+    <t>DOCX per-script fonts</t>
+  </si>
+  <si>
+    <t>w:rFonts ascii/hAnsi/eastAsia/cs, w:lang, rtl/bidi.</t>
+  </si>
+  <si>
+    <t>FONT-005</t>
+  </si>
+  <si>
+    <t>Editor fallback stacks</t>
+  </si>
+  <si>
+    <t>CSS stacks from the resolver.</t>
+  </si>
+  <si>
+    <t>FONT-006</t>
+  </si>
+  <si>
+    <t>Multilingual tests</t>
+  </si>
+  <si>
+    <t>Script matrix x editor/DOCX/PDF with pdftotext and rendering.</t>
+  </si>
+  <si>
+    <t>FMT-001</t>
+  </si>
+  <si>
+    <t>Style extraction completeness</t>
+  </si>
+  <si>
+    <t>Page setup, margins, fonts, headings, lists, tables, captions, headers/footers, spacing, numbering, colours.</t>
+  </si>
+  <si>
+    <t>FMT-002</t>
+  </si>
+  <si>
+    <t>Semantic mapping validated</t>
+  </si>
+  <si>
+    <t>AI classifies/maps, engine applies; validation.</t>
+  </si>
+  <si>
+    <t>FMT-003</t>
+  </si>
+  <si>
+    <t>Before/after for Format by Example</t>
+  </si>
+  <si>
+    <t>Preview before saving a template.</t>
+  </si>
+  <si>
+    <t>FMT-005</t>
+  </si>
+  <si>
+    <t>Rule value validation</t>
+  </si>
+  <si>
+    <t>Instruction-path values validated before reaching CSS/export.</t>
+  </si>
+  <si>
+    <t>Instruction rules and set_style operations go through values.clean_rule_value: invalid ones dropped, normalised values stored (see SEC-022).</t>
+  </si>
+  <si>
+    <t>tests/test_rule_values.py::test_instructions_cannot_carry_such_values</t>
+  </si>
+  <si>
+    <t>HLTH-001</t>
+  </si>
+  <si>
+    <t>Health 2.0 checks</t>
+  </si>
+  <si>
+    <t>Alt text, hidden text, mixed language, unsupported features, section inconsistency, broken lists, empty paragraphs, layout anomalies, duplicated formatting, broken links.</t>
+  </si>
+  <si>
+    <t>HLTH-002</t>
+  </si>
+  <si>
+    <t>Deterministic fixes with preview</t>
+  </si>
+  <si>
+    <t>Fix proposals through the change model.</t>
+  </si>
+  <si>
+    <t>HLTH-003</t>
+  </si>
+  <si>
+    <t>AI explanations only</t>
+  </si>
+  <si>
+    <t>AI explains issues; never scores.</t>
+  </si>
+  <si>
+    <t>REV-002</t>
+  </si>
+  <si>
+    <t>Review Changes UI</t>
+  </si>
+  <si>
+    <t>Categories FORMAT/STRUCTURE/CONTENT/METADATA/PRESERVATION/TRANSLATION.</t>
+  </si>
+  <si>
+    <t>REV-003</t>
+  </si>
+  <si>
+    <t>Content changes need acceptance</t>
+  </si>
+  <si>
+    <t>Enforced server-side.</t>
+  </si>
+  <si>
+    <t>backend</t>
+  </si>
+  <si>
+    <t>REV-004</t>
+  </si>
+  <si>
+    <t>Repair</t>
+  </si>
+  <si>
+    <t>Detected issue, proposed fix, preview, apply.</t>
+  </si>
+  <si>
+    <t>REV-005</t>
+  </si>
+  <si>
+    <t>Clean copy</t>
+  </si>
+  <si>
+    <t>Explicit: remove comments, accept tracked changes, remove hidden text, remove metadata, normalise formatting.</t>
+  </si>
+  <si>
+    <t>FEAT-001</t>
+  </si>
+  <si>
+    <t>Batch formatting</t>
+  </si>
+  <si>
+    <t>One template/reference over many documents as jobs.</t>
+  </si>
+  <si>
+    <t>backend/jobs</t>
+  </si>
+  <si>
+    <t>FEAT-002</t>
+  </si>
+  <si>
+    <t>Batch export</t>
+  </si>
+  <si>
+    <t>Many documents to a zip.</t>
+  </si>
+  <si>
+    <t>FEAT-003</t>
+  </si>
+  <si>
+    <t>Batch translation</t>
+  </si>
+  <si>
+    <t>After the translation MVP.</t>
+  </si>
+  <si>
+    <t>FEAT-010</t>
+  </si>
+  <si>
+    <t>Accessibility checker</t>
+  </si>
+  <si>
+    <t>Heading hierarchy, alt text, link labels, table headers, reading order, language, contrast.</t>
+  </si>
+  <si>
+    <t>FEAT-011</t>
+  </si>
+  <si>
+    <t>App accessibility fixes</t>
+  </si>
+  <si>
+    <t>Zero serious axe violations on main pages and the editor.</t>
+  </si>
+  <si>
+    <t>JOB-001</t>
+  </si>
+  <si>
+    <t>Job safety</t>
+  </si>
+  <si>
+    <t>idempotency_key, retry_count, timeout, cancellation, stuck detection, backoff, dead-letter.</t>
+  </si>
+  <si>
+    <t>STOR-001</t>
+  </si>
+  <si>
+    <t>Storage retention and deletion</t>
+  </si>
+  <si>
+    <t>Source files, exports, OCR artifacts: retention, deletion, access control, content types, size limits.</t>
+  </si>
+  <si>
+    <t>OBS-001</t>
+  </si>
+  <si>
+    <t>Metrics</t>
+  </si>
+  <si>
+    <t>Latency, failure rate, job/AI/export metrics without content.</t>
+  </si>
+  <si>
+    <t>AUD-15</t>
+  </si>
+  <si>
+    <t>OBS-002</t>
+  </si>
+  <si>
+    <t>Operation and job IDs in logs</t>
+  </si>
+  <si>
+    <t>Request, operation and job IDs everywhere.</t>
+  </si>
+  <si>
+    <t>OBS-003</t>
+  </si>
+  <si>
+    <t>Operations data</t>
+  </si>
+  <si>
+    <t>Failed jobs, processing failures, usage spikes, AI/export failures, storage, abuse - minimal admin API.</t>
+  </si>
+  <si>
+    <t>INFRA-010</t>
+  </si>
+  <si>
+    <t>Deployment verified</t>
+  </si>
+  <si>
+    <t>Docker images build and start; Postgres, Redis, storage, worker, frontend, backend.</t>
+  </si>
+  <si>
+    <t>docker, CI</t>
+  </si>
+  <si>
+    <t>INFRA-011</t>
+  </si>
+  <si>
+    <t>CI gates</t>
+  </si>
+  <si>
+    <t>Backend, frontend, E2E, lint, typecheck, build, migrations, security audit, document fidelity tests.</t>
+  </si>
+  <si>
+    <t>.github/workflows</t>
+  </si>
+  <si>
+    <t>AUD-15,AUD-20</t>
+  </si>
+  <si>
+    <t>TEST-040</t>
+  </si>
+  <si>
+    <t>Playwright workflow coverage</t>
+  </si>
+  <si>
+    <t>The 24 workflows of the brief.</t>
+  </si>
+  <si>
+    <t>TEST-041</t>
+  </si>
+  <si>
+    <t>Performance gates</t>
+  </si>
+  <si>
+    <t>Regression thresholds relative to baseline.</t>
+  </si>
+  <si>
+    <t>TEST-043</t>
+  </si>
+  <si>
+    <t>Browser matrix</t>
+  </si>
+  <si>
+    <t>Chromium, Firefox, WebKit.</t>
+  </si>
+  <si>
+    <t>TEST-006</t>
+  </si>
+  <si>
+    <t>E2E backend removes its temp directory</t>
+  </si>
+  <si>
+    <t>scripts/e2e_server.py leaves %TEMP%/smartdoc-e2e-* behind after every Playwright run (10 found on 2026-09-27).</t>
+  </si>
+  <si>
+    <t>backend/scripts/e2e_server.py</t>
+  </si>
+  <si>
+    <t>DOCS-010</t>
+  </si>
+  <si>
+    <t>final-production-readiness.md</t>
+  </si>
+  <si>
+    <t>The 16-section final report.</t>
+  </si>
+  <si>
+    <t>DOCS-011</t>
+  </si>
+  <si>
+    <t>Documentation tree</t>
+  </si>
+  <si>
+    <t>docs/{architecture,document-model,docx,pdf,translation,ai,formatting,security,testing,deployment,billing,operations}.</t>
+  </si>
+  <si>
+    <t>Started with Phase 1: docs/document-model, docs/architecture/fidelity.md, docs/docx, docs/formatting, docs/security, docs/testing (each grounded in the code and tests of Phases 0-1). Remaining folders (pdf, translation, ai, deployment, billing, operations) as their phases land.; docs/ai/README.md added with Phase 2.</t>
+  </si>
+  <si>
+    <t>CRITICAL_FIXES — Audit findings and P0 tasks</t>
+  </si>
+  <si>
+    <t>The 20 findings of the 2026-09-26 audit (current known risks) with fix progress, then every P0 task. Report: https://claude.ai/artifact/WKskiyexTDLAHe1BfjvWR1 — a finding is RESOLVED when every linked fix task is DONE.</t>
+  </si>
+  <si>
+    <t>Findings</t>
+  </si>
+  <si>
+    <t>Resolved</t>
+  </si>
+  <si>
+    <t>Open</t>
+  </si>
+  <si>
+    <t>P0 tasks</t>
+  </si>
+  <si>
+    <t>P0 done</t>
+  </si>
+  <si>
+    <t>Audit findings (current known risks)</t>
+  </si>
+  <si>
+    <t>Finding ID</t>
+  </si>
+  <si>
+    <t>Progress</t>
+  </si>
+  <si>
+    <t>Finding</t>
+  </si>
+  <si>
+    <t>Fix Tasks</t>
+  </si>
+  <si>
+    <t>Active</t>
+  </si>
+  <si>
+    <t>Blocked/Failed</t>
+  </si>
+  <si>
+    <t>Editor save can discard nested blocks (lists, pictures, code, quotes inside cells/items)</t>
+  </si>
+  <si>
+    <t>EDIT-001,EDIT-002,EDIT-003,EDIT-005,EDIT-006</t>
+  </si>
+  <si>
+    <t>AI fidelity check misses omissions, negation removal, number changes, inserted text</t>
+  </si>
+  <si>
+    <t>AI-001,AI-002,AI-003,AI-004</t>
+  </si>
+  <si>
+    <t>Fixed in Phase 2 (AI-001..004): AI structure answers are checked token by token; any omission, negation removal, number/unit/date change, insertion, reordering, duplication or punctuation change is refused.</t>
+  </si>
+  <si>
+    <t>Import/export silently changes hidden text, numbering, section headers, metadata, alt text, structure</t>
+  </si>
+  <si>
+    <t>FID-002,DOCX-011,DOCX-013,DOCX-015,DOCX-025</t>
+  </si>
+  <si>
+    <t>List numbering changes ('Чл. 1.' -&gt; '1.', '(a)' -&gt; 'a.', start values)</t>
+  </si>
+  <si>
+    <t>Partly fixed in 622d9c1: list format/start/continuation kept; custom labels ('Чл. 1.', '(a)') and multi-level labels reported, not kept yet (DOCX-016).</t>
+  </si>
+  <si>
+    <t>AI instruction operations can delete/insert/move content without preview</t>
+  </si>
+  <si>
+    <t>AI-005,AI-006,AI-007,REV-003</t>
+  </si>
+  <si>
+    <t>Fixed in Phase 2 (AI-005..AI-007): an instruction's insert/delete/move is a proposal the user sees and accepts or rejects; nothing is deleted silently.</t>
+  </si>
+  <si>
+    <t>Content controls, metadata, comment threads, sensitivity information lost</t>
+  </si>
+  <si>
+    <t>DOCX-012,DOCX-021,DOCX-023</t>
+  </si>
+  <si>
+    <t>Image fidelity gaps: alt text, crop, rotation, formats</t>
+  </si>
+  <si>
+    <t>Table export changes header state, borders, alignment, widths, geometry</t>
+  </si>
+  <si>
+    <t>Large images cause huge memory consumption</t>
+  </si>
+  <si>
+    <t>SEC-012,SEC-013</t>
+  </si>
+  <si>
+    <t>Large tables have a performance problem</t>
+  </si>
+  <si>
+    <t>Plan limits have a concurrency race</t>
+  </si>
+  <si>
+    <t>Malformed DOCX leads to HTTP 500</t>
+  </si>
+  <si>
+    <t>SEC-010,SEC-019</t>
+  </si>
+  <si>
+    <t>Dangerous href/field instructions must be filtered</t>
+  </si>
+  <si>
+    <t>SEC-014,SEC-015,SEC-016</t>
+  </si>
+  <si>
+    <t>Account essentials missing: reset, verification, change, deletion</t>
+  </si>
+  <si>
+    <t>ACCT-002,ACCT-003,ACCT-004,ACCT-005</t>
+  </si>
+  <si>
+    <t>Operations/monitoring must be confirmed</t>
+  </si>
+  <si>
+    <t>OBS-001,OBS-002,INFRA-010</t>
+  </si>
+  <si>
+    <t>Whole-document autosave must be optimised</t>
+  </si>
+  <si>
+    <t>PERF-003,PERF-004</t>
+  </si>
+  <si>
+    <t>PDF multilingual rendering must be reliable</t>
+  </si>
+  <si>
+    <t>FONT-003,FONT-006</t>
+  </si>
+  <si>
+    <t>Export metadata must be correct</t>
+  </si>
+  <si>
+    <t>DOCX-012,DOCX-020</t>
+  </si>
+  <si>
+    <t>Partly fixed in 622d9c1: Word exports carry the source file's core properties (author, dates, subject...) instead of 'python-docx'/2013; fields remain (DOCX-020).</t>
+  </si>
+  <si>
+    <t>AUD-19</t>
+  </si>
+  <si>
+    <t>Canonical model must represent more than paragraphs + runs + simple tables</t>
+  </si>
+  <si>
+    <t>CORE-001,DOCX-015,DOCX-016,DOCX-017</t>
+  </si>
+  <si>
+    <t>Tests can miss import-side data loss (model-relative comparison)</t>
+  </si>
+  <si>
+    <t>TEST-020,TEST-021,TEST-022</t>
+  </si>
+  <si>
+    <t>P0 tasks (live from MASTER)</t>
+  </si>
+  <si>
+    <t>DOCUMENT_FIDELITY — Content preservation</t>
+  </si>
+  <si>
+    <t>Canonical model, fidelity reports, capability matrix, change/review model. Categories: CORE, FIDELITY, REVIEW. Rows are formulas over MASTER — change task data in MASTER or with tools/tracker/tracker.py.</t>
+  </si>
+  <si>
+    <t>Tasks (live from MASTER)</t>
+  </si>
+  <si>
+    <t>DOCX_OOXML — DOCX / OOXML preservation</t>
+  </si>
+  <si>
+    <t>Import and export fidelity for Word documents. Categories: DOCX. Rows are formulas over MASTER — change task data in MASTER or with tools/tracker/tracker.py.</t>
+  </si>
+  <si>
+    <t>PDF — PDF engine</t>
+  </si>
+  <si>
+    <t>PDF export and PDF parsing. Categories: PDF. Rows are formulas over MASTER — change task data in MASTER or with tools/tracker/tracker.py.</t>
+  </si>
+  <si>
+    <t>EDITOR — Editor integrity</t>
+  </si>
+  <si>
+    <t>Tiptap mapping and save integrity. Categories: EDITOR. Rows are formulas over MASTER — change task data in MASTER or with tools/tracker/tracker.py.</t>
+  </si>
+  <si>
+    <t>FORMATTING — Formatting and Document Health</t>
+  </si>
+  <si>
+    <t>Formatting engine, Format by Example, Document Health. Categories: FORMATTING, HEALTH. Rows are formulas over MASTER — change task data in MASTER or with tools/tracker/tracker.py.</t>
+  </si>
+  <si>
+    <t>AI — AI fidelity</t>
+  </si>
+  <si>
+    <t>Fidelity checks, proposals and review, budgets. Categories: AI. Rows are formulas over MASTER — change task data in MASTER or with tools/tracker/tracker.py.</t>
+  </si>
+  <si>
+    <t>SECURITY — Security and accounts</t>
+  </si>
+  <si>
+    <t>Security hardening and account essentials. Categories: SECURITY, ACCOUNT. Rows are formulas over MASTER — change task data in MASTER or with tools/tracker/tracker.py.</t>
+  </si>
+  <si>
+    <t>PERFORMANCE — Performance</t>
+  </si>
+  <si>
+    <t>Measured results — brief §80-81: measure, then set regression thresholds relative to the baseline (no invented SLOs)</t>
+  </si>
+  <si>
+    <t>Bench ID</t>
+  </si>
+  <si>
+    <t>Metric</t>
+  </si>
+  <si>
+    <t>Unit</t>
+  </si>
+  <si>
+    <t>Scenario</t>
+  </si>
+  <si>
+    <t>Baseline</t>
+  </si>
+  <si>
+    <t>Baseline Source</t>
+  </si>
+  <si>
+    <t>Current</t>
+  </si>
+  <si>
+    <t>Measured On</t>
+  </si>
+  <si>
+    <t>Threshold</t>
+  </si>
+  <si>
+    <t>BENCH-001</t>
+  </si>
+  <si>
+    <t>duration</t>
+  </si>
+  <si>
+    <t>s</t>
+  </si>
+  <si>
+    <t>DOCX export: table 500x8 (4,000 cells)</t>
+  </si>
+  <si>
+    <t>audit perf_table.py (400 cells 3.8 s; 1,600 cells 53.7 s; quadratic)</t>
+  </si>
+  <si>
+    <t>BENCH-002</t>
+  </si>
+  <si>
+    <t>PDF export: table 500x8</t>
+  </si>
+  <si>
+    <t>audit perf_table.py (linear)</t>
+  </si>
+  <si>
+    <t>BENCH-003</t>
+  </si>
+  <si>
+    <t>Import: 300-page text DOCX (1,650 elements)</t>
+  </si>
+  <si>
+    <t>audit perf_backend.py</t>
+  </si>
+  <si>
+    <t>BENCH-004</t>
+  </si>
+  <si>
+    <t>DOCX export: 300-page text document</t>
+  </si>
+  <si>
+    <t>BENCH-005</t>
+  </si>
+  <si>
+    <t>PDF export: 300-page text document</t>
+  </si>
+  <si>
+    <t>BENCH-006</t>
+  </si>
+  <si>
+    <t>memory growth</t>
+  </si>
+  <si>
+    <t>MB</t>
+  </si>
+  <si>
+    <t>PDF export: 39 KB DOCX holding a 12000x12000 PNG</t>
+  </si>
+  <si>
+    <t>audit pixel_bomb.py (14000x14000 crashes the export)</t>
+  </si>
+  <si>
+    <t>BENCH-007</t>
+  </si>
+  <si>
+    <t>PDF export: 4 JPEG images 2400x1800</t>
+  </si>
+  <si>
+    <t>audit perf_backend.py (6.3 s)</t>
+  </si>
+  <si>
+    <t>BENCH-008</t>
+  </si>
+  <si>
+    <t>Editor: type 20 characters at 12,196 elements (1M-character paste)</t>
+  </si>
+  <si>
+    <t>audit perf_browser.js (~470 ms per key)</t>
+  </si>
+  <si>
+    <t>BENCH-009</t>
+  </si>
+  <si>
+    <t>Editor: type 20 characters, 300-page document</t>
+  </si>
+  <si>
+    <t>audit perf_browser.js</t>
+  </si>
+  <si>
+    <t>BENCH-010</t>
+  </si>
+  <si>
+    <t>request size</t>
+  </si>
+  <si>
+    <t>Autosave request: 300-page document</t>
+  </si>
+  <si>
+    <t>audit perf_browser.js (whole elements list per save)</t>
+  </si>
+  <si>
+    <t>BENCH-011</t>
+  </si>
+  <si>
+    <t>Autosave request: 1M-character paste</t>
+  </si>
+  <si>
+    <t>BENCH-012</t>
+  </si>
+  <si>
+    <t>storage</t>
+  </si>
+  <si>
+    <t>Stored history: one 300-page document, 50 steps</t>
+  </si>
+  <si>
+    <t>audit (2.8 MB per full copy; 7.2 MB when the JSON is ASCII-escaped)</t>
+  </si>
+  <si>
+    <t>BENCH-013</t>
+  </si>
+  <si>
+    <t>Paste: 2M characters (the cap)</t>
+  </si>
+  <si>
+    <t>audit perf_backend.py (17.5k elements, 7.1 MB JSON)</t>
+  </si>
+  <si>
+    <t>Performance tasks (live from MASTER)</t>
+  </si>
+  <si>
+    <t>TESTING — Testing</t>
+  </si>
+  <si>
+    <t>Test runs (oldest first)</t>
+  </si>
+  <si>
+    <t>Run ID</t>
+  </si>
+  <si>
+    <t>Command</t>
+  </si>
+  <si>
+    <t>Passed</t>
+  </si>
+  <si>
+    <t>Skipped</t>
+  </si>
+  <si>
+    <t>Date</t>
+  </si>
+  <si>
+    <t>Duration (s)</t>
+  </si>
+  <si>
+    <t>RUN-0001</t>
+  </si>
+  <si>
+    <t>backend-pytest</t>
+  </si>
+  <si>
+    <t>PASS</t>
+  </si>
+  <si>
+    <t>cd backend &amp;&amp; venv/Scripts/python -m pytest -q -p no:cacheprovider</t>
+  </si>
+  <si>
+    <t>Skip: optional real-Word check (SMARTDOC_REAL_DOCX unset). 1 DeprecationWarning (starlette/anyio). Audit measured 93% line coverage on 2026-09-26.</t>
+  </si>
+  <si>
+    <t>ea69829</t>
+  </si>
+  <si>
+    <t>RUN-0002</t>
+  </si>
+  <si>
+    <t>frontend-lint</t>
+  </si>
+  <si>
+    <t>cd frontend &amp;&amp; npm run lint</t>
+  </si>
+  <si>
+    <t>eslint: 0 problems</t>
+  </si>
+  <si>
+    <t>RUN-0003</t>
+  </si>
+  <si>
+    <t>frontend-tsc</t>
+  </si>
+  <si>
+    <t>cd frontend &amp;&amp; npx tsc --noEmit</t>
+  </si>
+  <si>
+    <t>0 type errors</t>
+  </si>
+  <si>
+    <t>RUN-0004</t>
+  </si>
+  <si>
+    <t>frontend-vitest</t>
+  </si>
+  <si>
+    <t>cd frontend &amp;&amp; npm test</t>
+  </si>
+  <si>
+    <t>6 test files</t>
+  </si>
+  <si>
+    <t>RUN-0005</t>
+  </si>
+  <si>
+    <t>frontend-build</t>
+  </si>
+  <si>
+    <t>cd frontend &amp;&amp; npm run build</t>
+  </si>
+  <si>
+    <t>Next.js production build, 11 routes</t>
+  </si>
+  <si>
+    <t>RUN-0006</t>
+  </si>
+  <si>
+    <t>e2e-playwright</t>
+  </si>
+  <si>
+    <t>cd frontend &amp;&amp; npm run test:e2e</t>
+  </si>
+  <si>
+    <t>Edge; throwaway backend on SQLite (:8100) + production build (:3100). 16 workflows in 5 spec files; the brief asks for 24 (TEST-040). Leaves %TEMP%/smartdoc-e2e-* dirs behind (TEST-006).</t>
+  </si>
+  <si>
+    <t>RUN-0007</t>
+  </si>
+  <si>
+    <t>migrations</t>
+  </si>
+  <si>
+    <t>alembic upgrade head &amp;&amp; alembic check &amp;&amp; alembic downgrade base &amp;&amp; alembic upgrade head (scratch SQLite); alembic upgrade head --sql (PostgreSQL dialect)</t>
+  </si>
+  <si>
+    <t>head 85211092fe4c; 'No new upgrade operations detected'; offline SQL: 14 tables at head, RLS enabled on every table</t>
+  </si>
+  <si>
+    <t>RUN-0008</t>
+  </si>
+  <si>
+    <t>supabase</t>
+  </si>
+  <si>
+    <t>Supabase MCP: list_migrations, get_advisors security+performance, list_tables (project edmmjmsynjziahwtjuke)</t>
+  </si>
+  <si>
+    <t>8/8 migrations applied; 14 tables, RLS on all; advisors only INFO: 14x rls_enabled_no_policy (by design: the API connects as owner, PostgREST roles see nothing), 8x unused_index (low traffic)</t>
+  </si>
+  <si>
+    <t>RUN-0009</t>
+  </si>
+  <si>
+    <t>pip-audit</t>
+  </si>
+  <si>
+    <t>uvx pip-audit --disable-pip -r backend/requirements.lock; same for requirements-dev.lock</t>
+  </si>
+  <si>
+    <t>No known vulnerabilities in either lock file</t>
+  </si>
+  <si>
+    <t>RUN-0010</t>
+  </si>
+  <si>
+    <t>npm-audit</t>
+  </si>
+  <si>
+    <t>cd frontend &amp;&amp; npm audit; npm audit --omit=dev</t>
+  </si>
+  <si>
+    <t>0 vulnerabilities across 633 dependencies</t>
+  </si>
+  <si>
+    <t>RUN-0011</t>
+  </si>
+  <si>
+    <t>docker-compose</t>
+  </si>
+  <si>
+    <t>PARTIAL</t>
+  </si>
+  <si>
+    <t>docker compose config --quiet</t>
+  </si>
+  <si>
+    <t>compose file valid (8 services: postgres, redis, minio, minio-bucket, migrate, worker, backend, frontend); images NOT built: Docker daemon not running on this machine (CI builds them on main)</t>
+  </si>
+  <si>
+    <t>RUN-0012</t>
+  </si>
+  <si>
+    <t>Phase 1 editor integrity: +16 tests (nesting model, nested API/exports, health links)</t>
+  </si>
+  <si>
+    <t>RUN-0013</t>
+  </si>
+  <si>
+    <t>cd frontend &amp;&amp; npx vitest run</t>
+  </si>
+  <si>
+    <t>+31: nestedBlocks.test.ts (28), useAutoSave.test.tsx (3); tsc and eslint clean</t>
+  </si>
+  <si>
+    <t>RUN-0014</t>
+  </si>
+  <si>
+    <t>cd frontend &amp;&amp; npx playwright test</t>
+  </si>
+  <si>
+    <t>+1: e2e/nested.spec.ts (paste, autosave, reload)</t>
+  </si>
+  <si>
+    <t>RUN-0015</t>
+  </si>
+  <si>
+    <t>+29 test_fidelity_report.py</t>
+  </si>
+  <si>
+    <t>RUN-0016</t>
+  </si>
+  <si>
+    <t>+3 FidelityPanel.test.tsx</t>
+  </si>
+  <si>
+    <t>RUN-0017</t>
+  </si>
+  <si>
+    <t>+fidelity.spec.ts; nested.spec.ts made deterministic (focus check, Ctrl+End) after one run pasted at the document start</t>
+  </si>
+  <si>
+    <t>RUN-0018</t>
+  </si>
+  <si>
+    <t>+6 test_export_fidelity.py</t>
+  </si>
+  <si>
+    <t>RUN-0019</t>
+  </si>
+  <si>
+    <t>+4 ExportResult.test.tsx</t>
+  </si>
+  <si>
+    <t>RUN-0020</t>
+  </si>
+  <si>
+    <t>export test checks the export's content message</t>
+  </si>
+  <si>
+    <t>RUN-0021</t>
+  </si>
+  <si>
+    <t>+6 test_capabilities.py</t>
+  </si>
+  <si>
+    <t>RUN-0022</t>
+  </si>
+  <si>
+    <t>venv/Scripts/python -m pytest -q</t>
+  </si>
+  <si>
+    <t>after FID-002 detections + section break fix</t>
+  </si>
+  <si>
+    <t>RUN-0023</t>
+  </si>
+  <si>
+    <t>npx vitest run</t>
+  </si>
+  <si>
+    <t>tsc --noEmit and eslint clean too</t>
+  </si>
+  <si>
+    <t>RUN-0024</t>
+  </si>
+  <si>
+    <t>rule values (SEC-022) + editor direct styles</t>
+  </si>
+  <si>
+    <t>RUN-0025</t>
+  </si>
+  <si>
+    <t>tsc + eslint clean</t>
+  </si>
+  <si>
+    <t>RUN-0026</t>
+  </si>
+  <si>
+    <t>e2e</t>
+  </si>
+  <si>
+    <t>npx playwright test</t>
+  </si>
+  <si>
+    <t>incl. e2e/direct-formatting.spec.ts</t>
+  </si>
+  <si>
+    <t>RUN-0027</t>
+  </si>
+  <si>
+    <t>Phase 1 gate: link titles, mark order, Markdown pictures/rules</t>
+  </si>
+  <si>
+    <t>RUN-0028</t>
+  </si>
+  <si>
+    <t>Phase 1 gate; tsc + eslint clean</t>
+  </si>
+  <si>
+    <t>RUN-0029</t>
+  </si>
+  <si>
+    <t>Phase 1 gate</t>
+  </si>
+  <si>
+    <t>RUN-0030</t>
+  </si>
+  <si>
+    <t>AI fidelity check (AI-001..004)</t>
+  </si>
+  <si>
+    <t>RUN-0031</t>
+  </si>
+  <si>
+    <t>AI proposals</t>
+  </si>
+  <si>
+    <t>RUN-0032</t>
+  </si>
+  <si>
+    <t>RUN-0033</t>
+  </si>
+  <si>
+    <t>incl. e2e/proposals.spec.ts</t>
+  </si>
+  <si>
+    <t>RUN-0034</t>
+  </si>
+  <si>
+    <t>AI budget</t>
+  </si>
+  <si>
+    <t>RUN-0035</t>
+  </si>
+  <si>
+    <t>prompt-injection review</t>
+  </si>
+  <si>
+    <t>RUN-0036</t>
+  </si>
+  <si>
+    <t>Phase 2 gate</t>
+  </si>
+  <si>
+    <t>RUN-0037</t>
+  </si>
+  <si>
+    <t>RUN-0038</t>
+  </si>
+  <si>
+    <t>source package + patch writer</t>
+  </si>
+  <si>
+    <t>RUN-0039</t>
+  </si>
+  <si>
+    <t>after the patch writer</t>
+  </si>
+  <si>
+    <t>RUN-0040</t>
+  </si>
+  <si>
+    <t>backend pytest</t>
+  </si>
+  <si>
+    <t>DOCX-028: test_original_blocks.py (26), golden set of 13</t>
+  </si>
+  <si>
+    <t>7f22bf9</t>
+  </si>
+  <si>
+    <t>RUN-0041</t>
+  </si>
+  <si>
+    <t>frontend vitest</t>
+  </si>
+  <si>
+    <t>editor round trip includes 13-kept-blocks</t>
+  </si>
+  <si>
+    <t>RUN-0042</t>
+  </si>
+  <si>
+    <t>playwright</t>
+  </si>
+  <si>
+    <t>new e2e/kept-blocks.spec.ts</t>
+  </si>
+  <si>
+    <t>RUN-0043</t>
+  </si>
+  <si>
+    <t>tsc + eslint</t>
+  </si>
+  <si>
+    <t>cd frontend &amp;&amp; npx tsc --noEmit &amp;&amp; npx eslint .</t>
+  </si>
+  <si>
+    <t>0 type errors, 0 lint problems</t>
+  </si>
+  <si>
+    <t>RUN-0044</t>
+  </si>
+  <si>
+    <t>DOCX-025: tests/test_hidden_text.py (7)</t>
+  </si>
+  <si>
+    <t>fada4d7</t>
+  </si>
+  <si>
+    <t>RUN-0045</t>
+  </si>
+  <si>
+    <t>editor/hiddenText.test.tsx (6)</t>
+  </si>
+  <si>
+    <t>RUN-0046</t>
+  </si>
+  <si>
+    <t>new e2e/hidden-text.spec.ts</t>
+  </si>
+  <si>
+    <t>RUN-0047</t>
+  </si>
+  <si>
+    <t>RUN-0048</t>
+  </si>
+  <si>
+    <t>DOCX-013 part 1: tests/test_character_formatting.py (12)</t>
+  </si>
+  <si>
+    <t>c51b1bf</t>
+  </si>
+  <si>
+    <t>RUN-0049</t>
+  </si>
+  <si>
+    <t>editor/characterFormatting.test.ts (3)</t>
+  </si>
+  <si>
+    <t>RUN-0050</t>
+  </si>
+  <si>
+    <t>after DOCX-013 part 1</t>
+  </si>
+  <si>
+    <t>RUN-0051</t>
+  </si>
+  <si>
+    <t>RUN-0052</t>
+  </si>
+  <si>
+    <t>DOCX-013 part 2 + FID-007: tests/test_copy_reports.py (6)</t>
+  </si>
+  <si>
+    <t>309f9d6</t>
+  </si>
+  <si>
+    <t>RUN-0053</t>
+  </si>
+  <si>
+    <t>characterFormatting.test.ts (4)</t>
+  </si>
+  <si>
+    <t>RUN-0054</t>
+  </si>
+  <si>
+    <t>after DOCX-013 part 2</t>
+  </si>
+  <si>
+    <t>RUN-0055</t>
+  </si>
+  <si>
+    <t>RUN-0056</t>
+  </si>
+  <si>
+    <t>DOCX-014 part 1: tests/test_paragraph_formatting.py (9)</t>
+  </si>
+  <si>
+    <t>597275a</t>
+  </si>
+  <si>
+    <t>RUN-0057</t>
+  </si>
+  <si>
+    <t>after DOCX-014 part 1</t>
+  </si>
+  <si>
+    <t>RUN-0058</t>
+  </si>
+  <si>
+    <t>RUN-0059</t>
+  </si>
+  <si>
+    <t>RUN-0060</t>
+  </si>
+  <si>
+    <t>DOCX-014 part 2: tests/test_paragraph_formatting.py (19)</t>
+  </si>
+  <si>
+    <t>9f1c5b4</t>
+  </si>
+  <si>
+    <t>RUN-0061</t>
+  </si>
+  <si>
+    <t>after DOCX-014 part 2</t>
+  </si>
+  <si>
+    <t>RUN-0062</t>
+  </si>
+  <si>
+    <t>RUN-0063</t>
+  </si>
+  <si>
+    <t>RUN-0064</t>
+  </si>
+  <si>
+    <t>DOCX-015 part 1a: tests/test_sections.py (6)</t>
+  </si>
+  <si>
+    <t>49d54e5</t>
+  </si>
+  <si>
+    <t>RUN-0065</t>
+  </si>
+  <si>
+    <t>sectionBreak.test.ts (3)</t>
+  </si>
+  <si>
+    <t>RUN-0066</t>
+  </si>
+  <si>
+    <t>after DOCX-015 part 1a</t>
+  </si>
+  <si>
+    <t>RUN-0067</t>
+  </si>
+  <si>
+    <t>RUN-0068</t>
+  </si>
+  <si>
+    <t>DOCX-015 part 1b: tests/test_sections.py (7)</t>
+  </si>
+  <si>
+    <t>cb75ebd</t>
+  </si>
+  <si>
+    <t>RUN-0069</t>
+  </si>
+  <si>
+    <t>after DOCX-015 part 1b</t>
+  </si>
+  <si>
+    <t>RUN-0070</t>
+  </si>
+  <si>
+    <t>RUN-0071</t>
+  </si>
+  <si>
+    <t>RUN-0072</t>
+  </si>
+  <si>
+    <t>bc138f5</t>
+  </si>
+  <si>
+    <t>RUN-0073</t>
+  </si>
+  <si>
+    <t>vitest</t>
+  </si>
+  <si>
+    <t>RUN-0074</t>
+  </si>
+  <si>
+    <t>Testing tasks (live from MASTER)</t>
+  </si>
+  <si>
+    <t>PRODUCT_FEATURES — Product features</t>
+  </si>
+  <si>
+    <t>Feature backlog — brief §61-62</t>
+  </si>
+  <si>
+    <t>Feature</t>
+  </si>
+  <si>
+    <t>Bucket</t>
+  </si>
+  <si>
+    <t>Linked Tasks</t>
+  </si>
+  <si>
+    <t>Linked Done</t>
+  </si>
+  <si>
+    <t>Linked Total</t>
+  </si>
+  <si>
+    <t>Document integrity</t>
+  </si>
+  <si>
+    <t>NOW</t>
+  </si>
+  <si>
+    <t>EDIT-001,EDIT-005,FID-002</t>
+  </si>
+  <si>
+    <t>Brief 62: NOW #1</t>
+  </si>
+  <si>
+    <t>Fidelity</t>
+  </si>
+  <si>
+    <t>DOCX-011,TEST-022</t>
+  </si>
+  <si>
+    <t>Brief 62: NOW #2</t>
+  </si>
+  <si>
+    <t>Security</t>
+  </si>
+  <si>
+    <t>SEC-010,SEC-012,SEC-014</t>
+  </si>
+  <si>
+    <t>Brief 62: NOW #3</t>
+  </si>
+  <si>
+    <t>Performance</t>
+  </si>
+  <si>
+    <t>PERF-001,PERF-003,PERF-004</t>
+  </si>
+  <si>
+    <t>Brief 62: NOW #4</t>
+  </si>
+  <si>
+    <t>PDF -&gt; editable</t>
+  </si>
+  <si>
+    <t>P2E-002,P2E-005</t>
+  </si>
+  <si>
+    <t>Brief 62: NOW #5</t>
+  </si>
+  <si>
+    <t>TRAN-001,TRAN-006</t>
+  </si>
+  <si>
+    <t>Brief 62: NOW #6</t>
+  </si>
+  <si>
+    <t>FONT-002,FONT-003</t>
+  </si>
+  <si>
+    <t>Brief 62: NOW #7</t>
+  </si>
+  <si>
+    <t>Review Changes</t>
+  </si>
+  <si>
+    <t>REV-001,REV-002</t>
+  </si>
+  <si>
+    <t>Brief 62: NOW #8</t>
+  </si>
+  <si>
+    <t>HLTH-001,HLTH-002</t>
+  </si>
+  <si>
+    <t>Brief 62: NOW #9</t>
+  </si>
+  <si>
+    <t>FMT-001,FMT-002,FMT-003</t>
+  </si>
+  <si>
+    <t>Brief 62: NOW #10</t>
+  </si>
+  <si>
+    <t>OCR</t>
+  </si>
+  <si>
+    <t>Part of PDF -&gt; editable (brief 43)</t>
+  </si>
+  <si>
+    <t>Multilingual support</t>
+  </si>
+  <si>
+    <t>TRAN-007,FONT-003</t>
+  </si>
+  <si>
+    <t>Part of translation + FontResolver</t>
+  </si>
+  <si>
+    <t>RTL</t>
+  </si>
+  <si>
+    <t>FONT-003,FONT-004</t>
+  </si>
+  <si>
+    <t>Part of FontResolver</t>
+  </si>
+  <si>
+    <t>CJK</t>
+  </si>
+  <si>
+    <t>Glossary</t>
+  </si>
+  <si>
+    <t>Part of translation MVP (brief 49)</t>
+  </si>
+  <si>
+    <t>Terminology lock</t>
+  </si>
+  <si>
+    <t>Citation preservation</t>
+  </si>
+  <si>
+    <t>Preservation is fidelity work; a citation editor is LATER</t>
+  </si>
+  <si>
+    <t>Bibliography preservation</t>
+  </si>
+  <si>
+    <t>Preservation is fidelity work</t>
+  </si>
+  <si>
+    <t>Content controls</t>
+  </si>
+  <si>
+    <t>Preserve now; editing content controls NEXT</t>
+  </si>
+  <si>
+    <t>Custom fields</t>
+  </si>
+  <si>
+    <t>Preserve custom properties and fields now; an editor NEXT</t>
+  </si>
+  <si>
+    <t>Document compare</t>
+  </si>
+  <si>
+    <t>NEXT</t>
+  </si>
+  <si>
+    <t>Brief 62: NEXT</t>
+  </si>
+  <si>
+    <t>Version compare</t>
+  </si>
+  <si>
+    <t>Brief 62: NEXT (batch processing)</t>
+  </si>
+  <si>
+    <t>After the translation MVP</t>
+  </si>
+  <si>
+    <t>Table repair</t>
+  </si>
+  <si>
+    <t>List repair</t>
+  </si>
+  <si>
+    <t>Brief 62: NEXT (accessibility)</t>
+  </si>
+  <si>
+    <t>Heading hierarchy checker</t>
+  </si>
+  <si>
+    <t>Link checker</t>
+  </si>
+  <si>
+    <t>Alt-text checker</t>
+  </si>
+  <si>
+    <t>HLTH-001,FEAT-010</t>
+  </si>
+  <si>
+    <t>Metadata editor</t>
+  </si>
+  <si>
+    <t>Global style replacement</t>
+  </si>
+  <si>
+    <t>Find/replace with formatting</t>
+  </si>
+  <si>
+    <t>Tracked change cleanup</t>
+  </si>
+  <si>
+    <t>Template extraction</t>
+  </si>
+  <si>
+    <t>Document-to-template</t>
+  </si>
+  <si>
+    <t>Template matching</t>
+  </si>
+  <si>
+    <t>Advanced template sharing</t>
+  </si>
+  <si>
+    <t>Teams</t>
+  </si>
+  <si>
+    <t>Translation memory</t>
+  </si>
+  <si>
+    <t>PDF merge/split</t>
+  </si>
+  <si>
+    <t>Page reorder</t>
+  </si>
+  <si>
+    <t>Page rotate</t>
+  </si>
+  <si>
+    <t>Page delete</t>
+  </si>
+  <si>
+    <t>Page extract</t>
+  </si>
+  <si>
+    <t>Merge documents</t>
+  </si>
+  <si>
+    <t>LATER</t>
+  </si>
+  <si>
+    <t>Split documents</t>
+  </si>
+  <si>
+    <t>Watermark</t>
+  </si>
+  <si>
+    <t>Forms (advanced)</t>
+  </si>
+  <si>
+    <t>Brief 62: LATER</t>
+  </si>
+  <si>
+    <t>SmartArt editing</t>
+  </si>
+  <si>
+    <t>Brief 62: LATER; SmartArt is preserved, not edited</t>
+  </si>
+  <si>
+    <t>OLE</t>
+  </si>
+  <si>
+    <t>Brief 62: LATER; OLE objects preserved, not edited</t>
+  </si>
+  <si>
+    <t>Full tracked-change editor</t>
+  </si>
+  <si>
+    <t>Advanced citation manager</t>
+  </si>
+  <si>
+    <t>Advanced drawing editor</t>
+  </si>
+  <si>
+    <t>Layout-preserving PDF editing (frames/anchors)</t>
+  </si>
+  <si>
+    <t>ARCHITECTURE_ONLY</t>
+  </si>
+  <si>
+    <t>Phase 9: architecture and hooks only</t>
+  </si>
+  <si>
+    <t>Product tasks (live from MASTER)</t>
+  </si>
+  <si>
+    <t>TRANSLATION — Translation and fonts</t>
+  </si>
+  <si>
+    <t>Translation MVP and FontResolver. Categories: TRANSLATION, FONT. Rows are formulas over MASTER — change task data in MASTER or with tools/tracker/tracker.py.</t>
+  </si>
+  <si>
+    <t>PDF_TO_EDITABLE — PDF to editable</t>
+  </si>
+  <si>
+    <t>PDF to editable document conversion. Categories: P2E. Rows are formulas over MASTER — change task data in MASTER or with tools/tracker/tracker.py.</t>
+  </si>
+  <si>
+    <t>BILLING_PLANS — Plans and billing</t>
+  </si>
+  <si>
+    <t>Initial plan hypothesis — brief §64: configurable defaults, not final prices; confirm against measured AI and infrastructure cost. Blue = input.</t>
+  </si>
+  <si>
+    <t>Usage unit / feature</t>
+  </si>
+  <si>
+    <t>FREE</t>
+  </si>
+  <si>
+    <t>PRO</t>
+  </si>
+  <si>
+    <t>BUSINESS</t>
+  </si>
+  <si>
+    <t>Documents / month</t>
+  </si>
+  <si>
+    <t>BUSINESS: per workspace</t>
+  </si>
+  <si>
+    <t>PDF conversion pages / month</t>
+  </si>
+  <si>
+    <t>OCR pages / month</t>
+  </si>
+  <si>
+    <t>Translation characters / month</t>
+  </si>
+  <si>
+    <t>AI operations / month</t>
+  </si>
+  <si>
+    <t>Exports / month</t>
+  </si>
+  <si>
+    <t>high</t>
+  </si>
+  <si>
+    <t>BUSINESS: 'high export limits', no number given</t>
+  </si>
+  <si>
+    <t>Templates</t>
+  </si>
+  <si>
+    <t>basic</t>
+  </si>
+  <si>
+    <t>custom</t>
+  </si>
+  <si>
+    <t>shared</t>
+  </si>
+  <si>
+    <t>Formatting</t>
+  </si>
+  <si>
+    <t>Format by Example</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>Advanced Document Health</t>
+  </si>
+  <si>
+    <t>yes</t>
+  </si>
+  <si>
+    <t>Version history</t>
+  </si>
+  <si>
+    <t>no</t>
+  </si>
+  <si>
+    <t>reasonable limits</t>
+  </si>
+  <si>
+    <t>Team workspace</t>
+  </si>
+  <si>
+    <t>Priority processing</t>
+  </si>
+  <si>
+    <t>Advanced controls</t>
+  </si>
+  <si>
+    <t>Billing and plan tasks (live from MASTER)</t>
+  </si>
+  <si>
+    <t>INFRA — Infrastructure</t>
+  </si>
+  <si>
+    <t>Tracker, jobs, storage, observability, deployment, documentation. Categories: INFRA, JOBS, STORAGE, OBSERVABILITY, DOCS. Rows are formulas over MASTER — change task data in MASTER or with tools/tracker/tracker.py.</t>
+  </si>
+  <si>
+    <t>Timestamp</t>
+  </si>
+  <si>
+    <t>Task ID</t>
+  </si>
+  <si>
+    <t>Change</t>
+  </si>
+  <si>
+    <t>Files</t>
+  </si>
+  <si>
+    <t>Created SmartDoc_Master_Implementation_Tracker.xlsx from the 2026-09-26 audit findings and the brief's phases: 151 tasks, 20 findings, 15 release gates.</t>
+  </si>
+  <si>
+    <t>tools/tracker/tracker.py, tools/tracker/seed.py</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>Built the Excel control centre: MASTER with 151 stable-ID tasks from the audit findings and the brief's 19 phases, CRITICAL_FIXES (20 findings -&gt; fix tasks, live status), 14 category views, DASHBOARD (totals, completion/verified %, phase %, category %, P0/P1 remaining), CHANGE_LOG, SESSION_STATE, RELEASE_GATES GATE-001..015. Formulas verified in Excel against independently computed values.</t>
+  </si>
+  <si>
+    <t>tools/tracker/*, SmartDoc_Master_Implementation_Tracker.xlsx, .gitignore</t>
+  </si>
+  <si>
+    <t>Resume reminder set with the platform scheduler; it fired and resumed the work. It only fires while this session is open and idle, which is recorded in AI-CONTINUATION.md.</t>
+  </si>
+  <si>
+    <t>Created the checkpoint system: AI-CONTINUATION.md with CURRENT STATE / LAST VERIFIED / WHAT WAS CHANGED / WHAT PASSED / WHAT FAILED / WHAT REMAINS / NEXT ACTION / IMPORTANT WARNINGS, session-state.json mirrored into SESSION_STATE by tracker.py state, and the brief saved verbatim for future sessions.</t>
+  </si>
+  <si>
+    <t>docs/AI-CONTINUATION.md, docs/session-state.json, docs/implementation-brief.md</t>
+  </si>
+  <si>
+    <t>Baseline backend suite: 643 passed, 1 skipped (optional real-Word check), 0 failed in 88 s on ea69829. Recorded as RUN-0001.</t>
+  </si>
+  <si>
+    <t>Baseline frontend: eslint clean, tsc clean, Vitest 46 passed in 6 files, production build succeeded. Recorded as RUN-0002..RUN-0005.</t>
+  </si>
+  <si>
+    <t>Baseline E2E: 16 Playwright workflows passed against the throwaway stack (SQLite backend :8100, production build :3100). The brief's 24-workflow target is TEST-040; temp-dir leak logged as TEST-006.</t>
+  </si>
+  <si>
+    <t>Baseline database: alembic head 85211092fe4c, check reports no drift, full down/up cycle clean; PostgreSQL offline SQL builds 14 tables with RLS; Supabase has all 8 migrations and only INFO-level advisor notices.</t>
+  </si>
+  <si>
+    <t>Baseline dependency audit: pip-audit finds no known vulnerabilities in requirements.lock or requirements-dev.lock; npm audit reports 0 vulnerabilities (production and dev).</t>
+  </si>
+  <si>
+    <t>Baseline infrastructure inspected: compose file valid with 8 services, arq worker and in-process job backends, local and S3 storage providers. Docker images were not built (daemon not running) - left to INFRA-010.</t>
+  </si>
+  <si>
+    <t>Baseline fixtures: the repository's 12 golden DOCX are generated by python-docx (not Word-authored) plus one PDF; the audit's 17 Word-authored fixtures still live outside the repo and move in with TEST-020.</t>
+  </si>
+  <si>
+    <t>Wrote docs/architecture/current-baseline.md: stack versions, the 11 baseline checks with commands and results, the migration chain and live database state, fixture inventory, audit performance figures, and what the baseline could not verify (Docker images, real AI model, Stripe, e-mail, hosting).</t>
+  </si>
+  <si>
+    <t>INFRA-001, INFRA-002, INFRA-003, TEST-001, TEST-002, TEST-003, TEST-004, TEST-005, SEC-001, INFRA-004, DOCS-001</t>
+  </si>
+  <si>
+    <t>Phase 0 committed (4da4ecb, pushed to feature/smartdoc-production-hardening): tracker, checkpoint system and measured baseline. All 11 phase-0 tasks DONE; no production code changed.</t>
+  </si>
+  <si>
+    <t>see commit 4da4ecb</t>
+  </si>
+  <si>
+    <t>Model now holds blocks nested inside table cells, list items and quotes as Elements (authoritative when set; inline keeps plain text), plus list numbering start/format; nesting capped at 8 levels (422 beyond). schemaVersion stays 1: the fields are additive.</t>
+  </si>
+  <si>
+    <t>backend/app/models/document.py, backend/tests/test_document_nesting.py</t>
+  </si>
+  <si>
+    <t>Regenerated the OpenAPI schema and the frontend's generated types for the nested-block and numbering fields; the contract test and the type check pass.</t>
+  </si>
+  <si>
+    <t>frontend/types/generated/*, frontend/types/document.ts</t>
+  </si>
+  <si>
+    <t>Backend readers now see nested blocks: pasted pictures inside cells/list items/quotes are validated and moved to asset storage like top-level ones (security and quota), exports fetch their assets, and the links health check covers list items, cells and nested blocks.</t>
+  </si>
+  <si>
+    <t>backend/app/services/image_assets.py, backend/app/services/document_service.py, backend/app/formatting/health.py</t>
+  </si>
+  <si>
+    <t>Word export renders nested blocks in cells, list items and quotes in reading order (verified by text order), numbers lists from their start in their format, and writes pictures' alt text.</t>
+  </si>
+  <si>
+    <t>backend/app/export/docx_export.py</t>
+  </si>
+  <si>
+    <t>PDF export renders nested blocks and list numbering (start/format); nested numbered levels now use the same a./i. sequence as the Word export instead of 1. everywhere.</t>
+  </si>
+  <si>
+    <t>backend/app/export/pdf_export.py</t>
+  </si>
+  <si>
+    <t>The editor mapping is total over the schema (tested against getSchema(editorExtensions)); anything unknown stops the save with a visible 'Not saved' message instead of being dropped, and the last saved version stays untouched.</t>
+  </si>
+  <si>
+    <t>frontend/editor/*</t>
+  </si>
+  <si>
+    <t>frontend/editor/nestedBlocks.test.ts (7 refusal cases); frontend/editor/useAutoSave.test.tsx (3)</t>
+  </si>
+  <si>
+    <t>Playwright pastes rich HTML (lists, code and a picture in table cells; a list in a quote; code in a list item; a list starting at 3 in letters), waits for autosave and reloads: everything is still there and no 'Not saved' appears.</t>
+  </si>
+  <si>
+    <t>frontend/e2e/nested.spec.ts</t>
+  </si>
+  <si>
+    <t>CORE-001, CORE-002, CORE-003, EDIT-001, EDIT-002, EDIT-003, EDIT-004, EDIT-005, EDIT-006, DOCX-001, PDF-001</t>
+  </si>
+  <si>
+    <t>Committed phase-01a-editor-integrity (1fe27a9, pushed): nested blocks in cells, list items and quotes survive the editor, the backend and both exports; unknown content stops the save visibly. AUD-01 fix tasks all DONE.</t>
+  </si>
+  <si>
+    <t>Import now produces a Document Fidelity Report: the importer's notes as items (feature, policy, count, content lost) plus an independent content check - the source's words (DOCX XML read separately from the importer, Markdown by what it renders, PDF extracted text) against the document's, in order. 'Verified' only when identical; differences listed with context (missing/added/changed/moved).</t>
+  </si>
+  <si>
+    <t>backend/app/fidelity/*, backend/app/models/document.py, backend/app/services/ingestion_service.py</t>
+  </si>
+  <si>
+    <t>Every importer note now carries a stable feature key and a brief-§90 policy class; review count and content-loss count are derived from them.</t>
+  </si>
+  <si>
+    <t>The editor shows the import's verdict in the status bar and a Проверка panel: content verified / differs (with word-level differences) / body complete but some content left out, then each item by policy. Browser check with a05 caught and fixed a misleading 'No content changes' when header text had been left out.</t>
+  </si>
+  <si>
+    <t>frontend/editor/panels/FidelityPanel.tsx, frontend/editor/EditorStatusBar.tsx, frontend/editor/DocumentEditorShell.tsx</t>
+  </si>
+  <si>
+    <t>FID-001, FID-004, FID-005, INFRA-005</t>
+  </si>
+  <si>
+    <t>Committed phase-01b-fidelity-report (8a330be, pushed): import fidelity report with policy classes and an independent word-level content check, shown in the editor; throwaway preview scripts.</t>
+  </si>
+  <si>
+    <t>Exports now report what they approximate or leave out (missing pictures, WebP a Word file can't hold, tables restyled for Word-sourced documents, edited kept fragments, page breaks in PDF tables, PDF comments/equations/fields/internal links, scripts the PDF can't lay out, alt text) and re-read the file: a Word export must hold exactly the document's words, a PDF every word in order (its own list numbers and page headers allowed). Shown under the Download button; the job result carries it.</t>
+  </si>
+  <si>
+    <t>Committed phase-01c-export-report (e55412f, pushed): export fidelity report with read-back content check, shown in the Export menu.</t>
+  </si>
+  <si>
+    <t>Added the machine-readable capability matrix (brief §91): 67 document features with import/edit/export/round-trip support and the policy the fidelity report uses, served at GET /api/v1/capabilities. Tests tie it to the code both ways, require a test for every clean round trip and a task for every unreported gap; writing it exposed unreported gaps now tracked (EDIT-012, DOCX-027).</t>
+  </si>
+  <si>
+    <t>backend/app/capabilities.py, backend/app/api/capabilities.py, backend/app/main.py, backend/tests/test_capabilities.py, frontend/types/generated/*</t>
+  </si>
+  <si>
+    <t>Committed phase-01d-capability-matrix (fcf30d7, pushed).</t>
+  </si>
+  <si>
+    <t>FID-002: import report now names empty spacing paragraphs, unsafe link addresses and per-section differences (page setup, odd/even breaks, page numbering, borders, line numbers, vertical alignment); matrix rows docx.empty_paragraphs + docx.sections updated</t>
+  </si>
+  <si>
+    <t>backend/app/fidelity/docx_detect.py, backend/app/fidelity/imports.py, backend/app/parsers/docx.py, backend/app/parsers/docx_inline.py, backend/app/capabilities.py, backend/tests/test_docx_detect.py</t>
+  </si>
+  <si>
+    <t>DOCX-015: section breaks break the page only where Word does (next section's w:type decides); continuous breaks no longer become page breaks</t>
+  </si>
+  <si>
+    <t>tests/test_docx_detect.py::test_a_section_break_breaks_the_page_only_where_word_does</t>
+  </si>
+  <si>
+    <t>DOCX-016: list number formats, start values and continuation round-trip; custom and multi-level labels reported</t>
+  </si>
+  <si>
+    <t>DOCX-012: Word core properties round-trip; custom properties and sensitivity labels reported without values</t>
+  </si>
+  <si>
+    <t>tests/test_docx_detect.py::test_the_files_own_properties_go_back_into_word_not_the_templates, tests/test_docx_detect.py::test_metadata_that_is_not_kept_is_reported_without_its_values</t>
+  </si>
+  <si>
+    <t>DOCX-026: unsafe link addresses reported instead of silently dropped</t>
+  </si>
+  <si>
+    <t>Golden JSON export is deterministic (uuid5 ids by order, fixed timestamps) so a regenerated fixture only differs where the importer's output did</t>
+  </si>
+  <si>
+    <t>backend/scripts/export_golden_json.py, frontend/tests/fixtures/golden/*.json</t>
+  </si>
+  <si>
+    <t>two consecutive exports byte-identical; tests/test_golden_documents.py::test_the_frontend_golden_json_is_current</t>
+  </si>
+  <si>
+    <t>FID-002 committed and pushed (phase-01e-import-detections)</t>
+  </si>
+  <si>
+    <t>SEC-022: formatting rule values validated at every entry and at resolve; CSS break-out via element style/page settings/instructions closed</t>
+  </si>
+  <si>
+    <t>backend/app/formatting/values.py, backend/app/formatting/engine.py, backend/app/schemas/formatting.py, backend/app/schemas/document.py, backend/app/ai/instruction_extraction.py, backend/tests/test_rule_values.py</t>
+  </si>
+  <si>
+    <t>FMT-005: instruction-path rule values validated before reaching CSS/export (with SEC-022)</t>
+  </si>
+  <si>
+    <t>EDIT-008: pasted/shortcut alignment saved as the element's own style and kept on split; paste into an empty paragraph keeps the pasted paragraphs' attributes</t>
+  </si>
+  <si>
+    <t>frontend/editor/tiptapToDocument.ts, frontend/editor/documentToTiptap.ts, frontend/editor/useAutoSave.ts, frontend/editor/pasteIntoEmptyBlock.ts, frontend/editor/extensions.ts, frontend/services/api/documents.ts, backend/app/schemas/document.py, backend/app/formatting/engine.py, backend/app/services/document_service.py, backend/app/api/documents.py</t>
+  </si>
+  <si>
+    <t>EDIT-009: pasted picture size kept as the picture's width share</t>
+  </si>
+  <si>
+    <t>EDIT-012: values outside the model named in the status bar and the Проверка panel</t>
+  </si>
+  <si>
+    <t>EDIT-011: cell alignment from pasted cells kept per column; differing cells and column widths reported</t>
+  </si>
+  <si>
+    <t>EDIT-008, EDIT-009, EDIT-012, SEC-022, FMT-005</t>
+  </si>
+  <si>
+    <t>Committed and pushed phase-01f-editor-direct-formatting</t>
+  </si>
+  <si>
+    <t>EDIT-010: link titles kept from Word/Markdown through the editor back into Word</t>
+  </si>
+  <si>
+    <t>backend/app/models/document.py, backend/app/parsers/docx_inline.py, backend/app/parsers/docx.py, backend/app/export/docx_export.py, backend/app/parsers/markdown.py, frontend/editor/tiptapToDocument.ts, frontend/editor/documentToTiptap.ts</t>
+  </si>
+  <si>
+    <t>FID-006: Markdown pictures named as left out (content), thematic breaks kept as rules</t>
+  </si>
+  <si>
+    <t>backend/app/parsers/markdown.py, backend/app/capabilities.py, backend/tests/test_capabilities.py, backend/tests/test_markdown_parser.py</t>
+  </si>
+  <si>
+    <t>EDIT-011: cell alignment/widths the model can't hold are named; keeping them moves to DOCX-017</t>
+  </si>
+  <si>
+    <t>EDIT-007: marks in one canonical order (MarkType) on both sides; opening a document saves nothing</t>
+  </si>
+  <si>
+    <t>backend/app/models/document.py, frontend/editor/tiptapToDocument.ts</t>
+  </si>
+  <si>
+    <t>TEST-010: nested-structure regression suite consolidated and verified</t>
+  </si>
+  <si>
+    <t>EDIT-008, EDIT-010, FID-006</t>
+  </si>
+  <si>
+    <t>Phase 1 browser check in the throwaway stack: Markdown doc with a picture -&gt; 'Body text complete, some content left out · 1 to review' (picture named with its description), '---' imported as a rule; pasted centred line + 160px picture + hsl colour + titled link at the end -&gt; status 'Saved · 1 formatting change not kept', Проверка 'While editing' lists the colour; after reload: line centred, picture width 24.9%, link title kept, notice gone</t>
+  </si>
+  <si>
+    <t>manual browser check (throwaway stack, fresh SQLite)</t>
+  </si>
+  <si>
+    <t>DOCS-011: documentation tree started for Phase 1 (document model, fidelity, docx, formatting, security, testing)</t>
+  </si>
+  <si>
+    <t>EDIT-007, EDIT-010, EDIT-011, FID-006, TEST-010, DOCS-011</t>
+  </si>
+  <si>
+    <t>Committed and pushed phase-01g-phase-1-complete; Phase 1 complete</t>
+  </si>
+  <si>
+    <t>AI-001: order/count/token/numeric/punctuation-aware comparator for AI output, with classified differences</t>
+  </si>
+  <si>
+    <t>backend/app/fidelity/text_check.py, backend/tests/test_ai_fidelity.py</t>
+  </si>
+  <si>
+    <t>AI-002: numbers and units protected; changed_numbers for cross-language checks</t>
+  </si>
+  <si>
+    <t>AI-003: structure analysis refuses answers that alter the text, per piece, logging without content</t>
+  </si>
+  <si>
+    <t>backend/app/ai/structure_analysis.py</t>
+  </si>
+  <si>
+    <t>AI-004: adversarial fidelity tests for every alteration the brief names</t>
+  </si>
+  <si>
+    <t>AI-001, AI-002, AI-003, AI-004</t>
+  </si>
+  <si>
+    <t>Committed and pushed phase-02a-ai-fidelity-check</t>
+  </si>
+  <si>
+    <t>AI-005: AI operations classified FORMAT/STRUCTURE/CONTENT; per-element instruction styles no longer dropped by the formatting pass</t>
+  </si>
+  <si>
+    <t>backend/app/formatting/proposals.py, backend/app/services/document_service.py</t>
+  </si>
+  <si>
+    <t>REV-001: change model with categories, used for proposals</t>
+  </si>
+  <si>
+    <t>backend/app/models/document.py, frontend/types/document.ts</t>
+  </si>
+  <si>
+    <t>AI-006: PLAN-&gt;VALIDATE-&gt;PREVIEW-&gt;ACCEPT-&gt;APPLY for AI content changes</t>
+  </si>
+  <si>
+    <t>backend/app/formatting/proposals.py, backend/app/services/document_service.py, backend/app/api/documents.py, backend/app/jobs/runner.py, backend/app/schemas/document.py, backend/app/schemas/jobs.py</t>
+  </si>
+  <si>
+    <t>AI-007: proposal review UI with accept/reject, E2E verified</t>
+  </si>
+  <si>
+    <t>frontend/editor/panels/ProposalsList.tsx, frontend/editor/panels/InstructionsPanel.tsx, frontend/editor/EditorStatusBar.tsx, frontend/editor/useFormatting.ts, frontend/services/api/documents.ts, frontend/services/api/jobs.ts, backend/scripts/e2e_ai.py, backend/scripts/e2e_server.py</t>
+  </si>
+  <si>
+    <t>AI-005, REV-001, AI-006, AI-007</t>
+  </si>
+  <si>
+    <t>Committed and pushed phase-02b-ai-proposals</t>
+  </si>
+  <si>
+    <t>AI-008: per-job/per-request AI call and time budget; no unbounded retries</t>
+  </si>
+  <si>
+    <t>backend/app/ai/budget.py, backend/app/config.py, backend/app/jobs/runner.py, backend/app/api/deps.py, backend/app/ai/structure_analysis.py</t>
+  </si>
+  <si>
+    <t>Committed and pushed phase-02c-ai-budget</t>
+  </si>
+  <si>
+    <t>AI-009: prompt-injection review; AI answer fields bounded; hostile-document tests</t>
+  </si>
+  <si>
+    <t>backend/app/ai/schemas.py, backend/app/ai/structure_analysis.py, backend/tests/test_prompt_injection.py</t>
+  </si>
+  <si>
+    <t>SEC-018: prompt injection / AI output abuse covered by AI-009's tests</t>
+  </si>
+  <si>
+    <t>AI-001, AI-005, AI-007, AI-009</t>
+  </si>
+  <si>
+    <t>Phase 2 gate: backend 817 passed/1 skipped, Vitest 117, Playwright 20; browser check in the throwaway stack - 'make the title red and delete “This draft paragraph”': title red at once, the paragraph kept and shown under Changes to review (struck through, with the instruction), notice + '1 AI change to review'; Accept removed it, reload kept it removed with nothing pending</t>
+  </si>
+  <si>
+    <t>full suites + manual browser check</t>
+  </si>
+  <si>
+    <t>DOCX-010: original Word package kept as an immutable, checksummed asset</t>
+  </si>
+  <si>
+    <t>backend/app/models/document.py, backend/app/services/document_service.py</t>
+  </si>
+  <si>
+    <t>DOCX-011: Word exports written into the original package; import report reflects what they keep</t>
+  </si>
+  <si>
+    <t>backend/app/export/docx_export.py, backend/app/fidelity/imports.py, backend/app/fidelity/docx_source.py, backend/app/fidelity/docx_detect.py, backend/app/fidelity/exports.py, backend/app/jobs/runner.py, backend/app/api/documents.py, backend/app/capabilities.py</t>
+  </si>
+  <si>
+    <t>TEST-023: independent package validation of every Word export</t>
+  </si>
+  <si>
+    <t>backend/app/export/package_check.py, backend/tests/test_package_check.py</t>
+  </si>
+  <si>
+    <t>DOCX-012: metadata preserved (core in the model, app/custom/labels via the original package)</t>
+  </si>
+  <si>
+    <t>DOCX-028: unchanged blocks keep their original XML in Word exports; server-side provenance; earlier sections follow page setup, header and page-number changes; lost sections reported; golden 13-kept-blocks + E2E.</t>
+  </si>
+  <si>
+    <t>backend/app/export/provenance.py, backend/app/export/docx_export.py, backend/app/parsers/docx.py, backend/app/models/document.py, backend/app/services/document_service.py, backend/app/fidelity/imports.py, backend/app/fidelity/exports.py, backend/app/capabilities.py, frontend/editor/tiptapToDocument.ts, frontend/e2e/kept-blocks.spec.ts, docs/docx/README.md</t>
+  </si>
+  <si>
+    <t>DOCX-028 committed and pushed as c8c2d27 (phase-03b-original-blocks).</t>
+  </si>
+  <si>
+    <t>DOCX-025: Word's hidden text stays hidden - hidden mark with Word's style resolution, editor shows it only on request, vanish in Word exports, left out of PDF with a note, consistent content checks.</t>
+  </si>
+  <si>
+    <t>backend/app/models/document.py, backend/app/parsers/docx_inline.py, backend/app/parsers/docx_styles.py, backend/app/parsers/docx.py, backend/app/fidelity/docx_detect.py, backend/app/fidelity/content.py, backend/app/fidelity/exports.py, backend/app/export/docx_export.py, backend/app/export/pdf_export.py, frontend/editor/hiddenText.ts, frontend/editor/EditorStatusBar.tsx, frontend/editor/DocumentEditorShell.tsx, frontend/app/globals.css</t>
+  </si>
+  <si>
+    <t>DOCX-025 committed and pushed as 7d1af86 (phase-03c-hidden-text).</t>
+  </si>
+  <si>
+    <t>DOCX-013 part 1: underline and strike styles, capitals, small capitals, spacing and raised/lowered text kept through import, editor, Word and PDF; paragraph-style formatting turned off by a run fixed.</t>
+  </si>
+  <si>
+    <t>backend/app/models/document.py, backend/app/parsers/docx_inline.py, backend/app/parsers/docx_styles.py, backend/app/parsers/docx.py, backend/app/export/docx_export.py, backend/app/export/pdf_export.py, backend/app/fidelity/*, frontend/editor/characterFormatting.ts, frontend/editor/tiptapToDocument.ts</t>
+  </si>
+  <si>
+    <t>backend 888 passed/1 skipped (tests/test_character_formatting.py 12); Vitest 128 (editor/characterFormatting.test.ts 3, golden round trip of 02); Playwright 22; tsc + eslint clean</t>
+  </si>
+  <si>
+    <t>DOCX-013 part 1 committed and pushed as 6619159 (phase-03d-character-formatting); part 2 next.</t>
+  </si>
+  <si>
+    <t>6619159</t>
+  </si>
+  <si>
+    <t>FID-007: reports follow the Word copy - kept while unchanged at import, rewritten losses named at export, unsafe links never copied back.</t>
+  </si>
+  <si>
+    <t>backend/app/fidelity/imports.py, backend/app/export/docx_export.py, backend/tests/test_copy_reports.py</t>
+  </si>
+  <si>
+    <t>DOCX-013 part 2: language kept; scale and effects named and kept while unchanged; brief §22 list is now supported, preserved or explicitly named.</t>
+  </si>
+  <si>
+    <t>backend/app/models/document.py, backend/app/parsers/docx_inline.py, backend/app/fidelity/docx_detect.py, frontend/editor/characterFormatting.ts</t>
+  </si>
+  <si>
+    <t>DOCX-013 done: part 1 6619159, part 2 d32c6a6 (phase-03e-copy-reports).</t>
+  </si>
+  <si>
+    <t>FID-007 committed and pushed as d32c6a6.</t>
+  </si>
+  <si>
+    <t>DOCX-014 part 1: right indent, shading, pagination controls, contextual spacing and direction kept through import, CSS, Word and PDF.</t>
+  </si>
+  <si>
+    <t>backend/app/models/document.py, backend/app/formatting/*, backend/app/parsers/docx_styles.py, backend/app/parsers/docx.py, backend/app/export/docx_export.py, backend/app/export/pdf_export.py</t>
+  </si>
+  <si>
+    <t>backend 903 passed/1 skipped (tests/test_paragraph_formatting.py 9); Vitest 129; Playwright 22; tsc + eslint clean</t>
+  </si>
+  <si>
+    <t>DOCX-014 part 1 committed and pushed as eade93e (phase-03f-paragraph-formatting); part 2 next.</t>
+  </si>
+  <si>
+    <t>eade93e</t>
+  </si>
+  <si>
+    <t>DOCX-014 part 2: paragraph borders and tab stops kept through import, CSS, Word and PDF; what the PDF and editor can't draw is named.</t>
+  </si>
+  <si>
+    <t>backend/app/formatting/values.py, backend/app/parsers/docx_styles.py, backend/app/export/docx_export.py, backend/app/export/pdf_export.py, backend/tests/test_paragraph_formatting.py</t>
+  </si>
+  <si>
+    <t>DOCX-014 done: part 1 eade93e, part 2 c158722 (phase-03g-borders-tab-stops).</t>
+  </si>
+  <si>
+    <t>DOCX-015 part 1a: section breaks are elements with their section's settings - imported, shown and paginated in the editor, written back into Word from the model.</t>
+  </si>
+  <si>
+    <t>backend/app/models/document.py, backend/app/parsers/docx.py, backend/app/export/docx_export.py, frontend/editor/sectionBreak.ts, frontend/editor/pagination.ts</t>
+  </si>
+  <si>
+    <t>tests/test_docx_detect.py::test_a_section_break_breaks_the_page_only_where_word_does; tests/test_sections.py (6); frontend/editor/sectionBreak.test.ts (3); backend 919 passed/1 skipped; Vitest 132; Playwright 22</t>
+  </si>
+  <si>
+    <t>DOCX-015 part 1a committed and pushed as 047685d (phase-03h-section-breaks); part 1b next.</t>
+  </si>
+  <si>
+    <t>047685d</t>
+  </si>
+  <si>
+    <t>DOCX-015 part 1b: the PDF follows each section's page setup, even/odd starts and numbering.</t>
+  </si>
+  <si>
+    <t>backend/app/export/pdf_export.py, backend/app/fidelity/exports.py, backend/tests/test_sections.py</t>
+  </si>
+  <si>
+    <t>tests/test_docx_detect.py::test_a_section_break_breaks_the_page_only_where_word_does; tests/test_sections.py (6); frontend/editor/sectionBreak.test.ts (3); backend 919 passed/1 skipped; Vitest 132; Playwright 22; tests/test_sections.py (7): per-page sizes, blank page, roman numbering, a picture fitting a narrow column; backend 920 passed/1 skipped</t>
+  </si>
+  <si>
+    <t>DOCX-015 part 1b committed and pushed as 35c6771 (phase-03i-pdf-sections); part 2 next.</t>
+  </si>
+  <si>
     <t>35c6771</t>
   </si>
   <si>
-    <t>Fixed: a section's w:type describes how THAT section starts (ECMA-376 17.6.22) - the importer used the ending section's own type, so a continuous break became a page break and continuous-&gt;new-page put the break between the wrong sections (probe confirmed). Now the next section's type decides. Per-section differences are reported (FID-002). Remaining: sections as a first-class model concept (orientation/margins/columns/headers per section, page-number restart) and export of several sections.; With DOCX-011 the last section's properties (columns, page numbering, borders, line numbers, vertical alignment, header/footer variants) are kept in Word exports; earlier sections' are still reported lost.; DOCX-028: earlier sections now survive in Word exports while their ending paragraph is unchanged; page setup/header/page-number changes apply to them; a lost one is reported (export.docx.section_lost). Modelling sections is still this task.</t>
-  </si>
-  <si>
-    <t>DOCX-016</t>
-  </si>
-  <si>
-    <t>Numbering engine</t>
-  </si>
-  <si>
-    <t>Decimal/roman/alpha/bullets, custom prefixes/suffixes, start, restart, continuation, multilevel, numId/abstractNum/ilvl, indentation.</t>
-  </si>
-  <si>
-    <t>tests/test_docx_numbering.py</t>
-  </si>
-  <si>
-    <t>Done so far: top-level list number format (decimal/roman/letters), start value (lvl start + lvlOverride/startOverride) and continuation across interrupting paragraphs imported into Element.numbering and written back to Word (per-level formats, startOverride) and PDF; empty numbered items keep counting. Reported, not kept: custom labels ('Чл. 1.', '(a)'), multi-level labels ('1.1'), numbered headings baked into text. Remaining: prefixes/suffixes, multilevel numbering model, restart semantics per level, indentation.</t>
-  </si>
-  <si>
-    <t>AUD-04</t>
-  </si>
-  <si>
-    <t>DOCX-017</t>
-  </si>
-  <si>
-    <t>Table engine</t>
-  </si>
-  <si>
-    <t>No forced header or Table Grid; widths, heights, margins, borders, shading, v-align, nested tables, repeated header rows, table styles.</t>
-  </si>
-  <si>
-    <t>From EDIT-011 (2026-09-27): add per-cell alignment and column widths to the model (the editor's cell align/colwidth, Word tcW/tblGrid, PDF colWidths); until then the editor names them as not kept.</t>
-  </si>
-  <si>
-    <t>DOCX-018</t>
-  </si>
-  <si>
-    <t>Images</t>
-  </si>
-  <si>
-    <t>Alt text exported; crop, rotation, anchor, wrap, position preserved; WEBP converted on export.</t>
-  </si>
-  <si>
-    <t>Alt text + title now exported (docPr descr/title) with DOCX-001; crop, rotation, WEBP still open.</t>
-  </si>
-  <si>
-    <t>DOCX-019</t>
-  </si>
-  <si>
-    <t>Drawings and text boxes preserved</t>
-  </si>
-  <si>
-    <t>Anchored drawings, text boxes, shapes kept even when not editable.</t>
-  </si>
-  <si>
-    <t>DOCX-028: text boxes and drawings in unchanged paragraphs are copied as they are (grouped with their anchor paragraph).</t>
-  </si>
-  <si>
-    <t>DOCX-020</t>
-  </si>
-  <si>
-    <t>Fields</t>
-  </si>
-  <si>
-    <t>Code/result/relationship; header STYLEREF/DATE live; TOC kept; CITATION/BIBLIOGRAPHY sources preserved; no 'Invalid source specified.'</t>
-  </si>
-  <si>
-    <t>backend/parsers, export</t>
-  </si>
-  <si>
-    <t>DOCX-028: field codes in unchanged blocks are copied as they are; a field spanning paragraphs is never copied half (self-contained check).</t>
-  </si>
-  <si>
-    <t>AUD-18</t>
-  </si>
-  <si>
-    <t>DOCX-021</t>
-  </si>
-  <si>
-    <t>Comment threads</t>
-  </si>
-  <si>
-    <t>Replies, resolved state, authors, ranges preserved (commentsExtended, people).</t>
-  </si>
-  <si>
-    <t>AUD-06</t>
-  </si>
-  <si>
-    <t>DOCX-022</t>
-  </si>
-  <si>
-    <t>Tracked changes preserved</t>
-  </si>
-  <si>
-    <t>Not silently accepted; explicit choice.</t>
-  </si>
-  <si>
-    <t>DOCX-028: blocks holding tracked changes are never copied (always written anew, accepted), so this task's explicit choice is still needed.</t>
-  </si>
-  <si>
-    <t>DOCX-023</t>
-  </si>
-  <si>
-    <t>Content controls preserved</t>
-  </si>
-  <si>
-    <t>w:sdt of every kind kept with its properties.</t>
-  </si>
-  <si>
-    <t>DOCX-028: content controls in unchanged blocks are copied with their properties (E2E proves it through the editor); written anew they are unwrapped (reported lossy at import).</t>
-  </si>
-  <si>
-    <t>DOCX-024</t>
-  </si>
-  <si>
-    <t>Real footnotes and endnotes</t>
-  </si>
-  <si>
-    <t>Notes stay notes on export.</t>
-  </si>
-  <si>
-    <t>DOCX-025</t>
-  </si>
-  <si>
-    <t>Hidden text stays hidden</t>
-  </si>
-  <si>
-    <t>Imported hidden text is kept hidden, shown only on request.</t>
-  </si>
-  <si>
-    <t>MarkType.HIDDEN (appended; no existing mark order changes). Importer resolves w:vanish as Word does: run, character style, paragraph style (the default paragraph style when none), docDefaults; webHidden stays visible; an explicit vanish=0 shows text in a hidden style. The detector uses the default paragraph style the same way and names hidden text as kept hidden (DETECTED_PRESERVED, not a content change). Editor: non-inclusive hidden mark (editor/hiddenText.ts; Word's display:none paste stays hidden), hidden by CSS unless .show-hidden; status bar 'Show hidden text (N words)' toggles it and re-paginates; the Structure panel leaves hidden text out of headings. Word export writes w:vanish (copied blocks keep theirs); PDF doesn't print hidden runs, export.pdf.hidden_text names the word count, and the PDF content check compares visible words (document_words(visible_only=True)); Word-side checks count hidden text on both sides. Golden 02-rich-text gained a hidden sentence (editor round trip in Vitest).</t>
-  </si>
-  <si>
-    <t>backend 876 passed/1 skipped (tests/test_hidden_text.py 7: import resolution, default paragraph style, report, upload + content check + editor save, Word export round trip, PDF text + note + check); Vitest 125 (editor/hiddenText.test.tsx 6, golden round trip of 02); Playwright 22 (e2e/hidden-text.spec.ts: hidden until asked, dotted line when shown, vanish in the Word export); tsc + eslint clean</t>
-  </si>
-  <si>
-    <t>backend/parsers, frontend</t>
-  </si>
-  <si>
-    <t>7d1af86</t>
-  </si>
-  <si>
-    <t>DOCX-028: vanish survives in unchanged blocks only; the model still shows hidden text as ordinary text - next task.</t>
-  </si>
-  <si>
-    <t>DOCX-026</t>
-  </si>
-  <si>
-    <t>Hyperlink policy and no silent autolink</t>
-  </si>
-  <si>
-    <t>Plain-text addresses not turned into links by default; file:/UNC reported.</t>
-  </si>
-  <si>
-    <t>tests/test_docx_detect.py::test_unsafe_links_and_spacing_paragraphs_are_reported</t>
-  </si>
-  <si>
-    <t>Done: links to unsafe addresses (javascript:, file:, UNC...) are kept as plain text and reported (docx.link.unsafe); plain-text addresses turned into links are reported (docx.autolink). Remaining: stop autolinking by default (a setting), per the task.</t>
-  </si>
-  <si>
-    <t>AUD-03,AUD-13</t>
-  </si>
-  <si>
-    <t>FMT-004</t>
-  </si>
-  <si>
-    <t>Render-spec defaults respect the source</t>
-  </si>
-  <si>
-    <t>Imported Word styles are not overridden by defaults (headings not forced bold).</t>
-  </si>
-  <si>
-    <t>backend/formatting</t>
-  </si>
-  <si>
-    <t>TEST-020</t>
-  </si>
-  <si>
-    <t>Word-authored fixtures in the repository</t>
-  </si>
-  <si>
-    <t>20 synthetic Word-authored fixtures, scrubbed of identifying metadata.</t>
-  </si>
-  <si>
-    <t>backend/tests/fixtures/word</t>
-  </si>
-  <si>
-    <t>TEST-021</t>
-  </si>
-  <si>
-    <t>Expected-loss manifests in CI</t>
-  </si>
-  <si>
-    <t>expected-loss.json per fixture; CI compares actual vs expected.</t>
-  </si>
-  <si>
-    <t>TEST-022</t>
-  </si>
-  <si>
-    <t>True fidelity test</t>
-  </si>
-  <si>
-    <t>SOURCE -&gt; import -&gt; format -&gt; editor save -&gt; export -&gt; reimport -&gt; compare SOURCE vs RESULT: content, formatting, metadata, structure separately.</t>
-  </si>
-  <si>
-    <t>TEST-023</t>
-  </si>
-  <si>
-    <t>Independent validation</t>
-  </si>
-  <si>
-    <t>OOXML schema validation, Word when available, docx2python; pdftotext/PyMuPDF for PDF.</t>
-  </si>
-  <si>
-    <t>app/export/package_check.py: an independent package check (zip read directly): well-formed parts, content types, relationships resolving, relationship ids used, defined styles/lists/comments. Found a real defect on first run (python-docx's add_comment refers to an undefined CommentReference style; exports now define it). Every golden export passes, fresh and into its original.</t>
-  </si>
-  <si>
-    <t>tests/test_package_check.py (13)</t>
-  </si>
-  <si>
-    <t>The docx skill's XSD validator needs defusedxml (not installed; installing needs a download) - schema-level validation remains open.</t>
-  </si>
-  <si>
-    <t>DOCX-027</t>
-  </si>
-  <si>
-    <t>Importer builds nested blocks</t>
-  </si>
-  <si>
-    <t>Use TableCell.blocks / ListItem.blocks on import: pictures, lists (with bullets) and nested tables inside cells, pictures inside list items - instead of dropping or flattening them.</t>
-  </si>
-  <si>
-    <t>AUD-01,AUD-03,AUD-08</t>
-  </si>
-  <si>
-    <t>DOCX-028</t>
-  </si>
-  <si>
-    <t>Unchanged blocks keep their original XML in Word exports</t>
-  </si>
-  <si>
-    <t>Blocks the user didn't change are written back as their original XML (fields, content controls, run-level formatting the model can't hold, bookmarks), changed ones regenerated; needs block provenance from the importer and fingerprints.</t>
-  </si>
-  <si>
-    <t>Importer records each top-level element's body children (Element.sourceBlocks: list items, drop caps, derived page breaks); an upload with a kept file stamps content+look fingerprints (Element.sourceHash, app/export/provenance.py: own/kind/body/nested resolved styles; page breaks have no look). docx_export._copy_plan groups elements with their children (uncovered children join the group before) and copies a group verbatim when every element is unchanged, together and in original order, children contiguous, XML self-contained (no tracked changes/note refs/altChunk; balanced fields, bookmarks, comment ranges); everything else is written anew. Provenance is server-side (keep_provenance on PUT /content). Page setup now runs after the body: changed size/margins reach every kept section (orientation kept, landscape turned), a changed main header is rewritten where Word shows it (link to previous), page numbers left out/asked for apply to every section. export.docx.section_lost (LOSSY) names sections lost with a changed paragraph; import report: earlier sections' setup/headers kept while unchanged; PDF names them Word-only. All 13 golden documents stamped + exported into their originals: sound packages, content verified (12-complex rewrites only the footnote paragraph and the note, by design).</t>
-  </si>
-  <si>
-    <t>backend 869 passed/1 skipped (tests/test_original_blocks.py 26 incl. 13 golden; test_source_package.py rewritten claims with export proof; test_golden_documents.py 13 files); Vitest 119 (editor round trip of 13-kept-blocks); Playwright 21 (e2e/kept-blocks.spec.ts: edit in the real editor, untouched paragraphs keep content control, double underline, landscape section); tsc + eslint clean</t>
-  </si>
-  <si>
-    <t>c8c2d27</t>
-  </si>
-  <si>
-    <t>Follow-up of DOCX-011 (package-level patch writer).; Known limit: any restyle (template, instruction) changes the body look, so every block but page breaks is written anew; follow-up DOCX-029. Sections survive only with their ending paragraph until DOCX-015 models them.</t>
-  </si>
-  <si>
-    <t>DOCX-029</t>
-  </si>
-  <si>
-    <t>Restyled blocks keep their original XML where nothing conflicts</t>
-  </si>
-  <si>
-    <t>After a template or instruction restyles a kind of block, copy a block's original XML when its paragraph style is the Word style the export rewrites for that kind and its direct formatting (pPr/rPr) sets none of the properties that changed; today any restyle writes every block anew (content controls, double underline etc. then lost, as the import report says).</t>
-  </si>
-  <si>
-    <t>Found while finishing DOCX-028: the look is part of the fingerprint so the export never shows a stale look.</t>
-  </si>
-  <si>
-    <t>FID-007</t>
-  </si>
-  <si>
-    <t>Reports follow the Word copy</t>
-  </si>
-  <si>
-    <t>With the original kept, the import report names what lives in blocks as kept in the Word export while the paragraph is unchanged, and an export that writes such a block anew names what it lost; a copy never brings back a link the app doesn't allow.</t>
-  </si>
-  <si>
-    <t>fidelity/imports.py KEPT_WHILE_UNCHANGED (content controls, text boxes, charts/shapes/SmartArt, objects, picture crop/rotation/floating, drop caps, empty paragraphs, approximated underlines, character scale, text effects, RTL) -&gt; detected_not_editable 'kept while the paragraph isn't changed or restyled'; docx_export._copy_plan returns rewritten groups, _lost_in/_rewritten_losses -&gt; export.docx.rewritten_blocks (LOSSY, count, kinds incl. proofing exclusions); _safe_links keeps groups with unsafe links (relationships or HYPERLINK fields) from being copied; the PDF's Word-only note covers the features.</t>
-  </si>
-  <si>
-    <t>tests/test_copy_reports.py (6): kept while unchanged at import, rewritten losses named (content controls, stretched text), unsafe javascript: link never copied back, PDF word-only; backend 894 passed/1 skipped; Playwright 22</t>
-  </si>
-  <si>
-    <t>Generalises DOCX-028's section handling (export.docx.section_lost) to everything the model doesn't hold inside blocks.</t>
-  </si>
-  <si>
-    <t>SEC-010</t>
-  </si>
-  <si>
-    <t>Malformed DOCX -&gt; safe 4xx</t>
-  </si>
-  <si>
-    <t>XML/zip/structure errors map to invalid_file; fuzz corpus shows no 500.</t>
-  </si>
-  <si>
-    <t>AUD-12</t>
-  </si>
-  <si>
-    <t>SEC-011</t>
-  </si>
-  <si>
-    <t>Malformed PDF -&gt; safe 4xx</t>
-  </si>
-  <si>
-    <t>Verified with a fuzz corpus.</t>
-  </si>
-  <si>
-    <t>SEC-012</t>
-  </si>
-  <si>
-    <t>Image resource limits</t>
-  </si>
-  <si>
-    <t>Compressed and decompressed size, pixel count, width, height, images per document, total bytes, format allowlist; rejected before rasterisation.</t>
-  </si>
-  <si>
-    <t>backend/security</t>
-  </si>
-  <si>
-    <t>AUD-09</t>
-  </si>
-  <si>
-    <t>SEC-013</t>
-  </si>
-  <si>
-    <t>PDF bombs, huge XML, decompression limits</t>
-  </si>
-  <si>
-    <t>Reviewed and tested limits.</t>
-  </si>
-  <si>
-    <t>SEC-014</t>
-  </si>
-  <si>
-    <t>Href policy</t>
-  </si>
-  <si>
-    <t>Server-side scheme allowlist; javascript:/data:/vbscript:/file: never exported as active links.</t>
-  </si>
-  <si>
-    <t>backend/models, export</t>
-  </si>
-  <si>
-    <t>AUD-13</t>
-  </si>
-  <si>
-    <t>SEC-015</t>
-  </si>
-  <si>
-    <t>Field instruction allowlist</t>
-  </si>
-  <si>
-    <t>No DDE/INCLUDETEXT/INCLUDEPICTURE/external fields accepted from clients or exported.</t>
-  </si>
-  <si>
-    <t>SEC-016</t>
-  </si>
-  <si>
-    <t>External relationships policy</t>
-  </si>
-  <si>
-    <t>No arbitrary external targets in exports.</t>
-  </si>
-  <si>
-    <t>SEC-017</t>
-  </si>
-  <si>
-    <t>Malicious SVG</t>
-  </si>
-  <si>
-    <t>Verified refused everywhere.</t>
-  </si>
-  <si>
-    <t>SEC-018</t>
-  </si>
-  <si>
-    <t>Prompt injection / AI output abuse</t>
-  </si>
-  <si>
-    <t>Tests with hostile documents; outputs validated.</t>
-  </si>
-  <si>
-    <t>Hostile-document tests: the document can't close its fence; out-of-bounds answers refused and fall back; an instruction steered by the document deletes nothing (proposals only) and a CSS break-out value is dropped; style-analysis flags on unknown elements dropped (see AI-009).</t>
-  </si>
-  <si>
-    <t>tests/test_prompt_injection.py</t>
-  </si>
-  <si>
-    <t>SEC-019</t>
-  </si>
-  <si>
-    <t>Error envelope audit</t>
-  </si>
-  <si>
-    <t>Every error {code, message, details, request_id}; no stack traces to users.</t>
-  </si>
-  <si>
-    <t>backend/api</t>
-  </si>
-  <si>
-    <t>SEC-020</t>
-  </si>
-  <si>
-    <t>CSP without 'unsafe-inline' scripts</t>
-  </si>
-  <si>
-    <t>Nonce-based CSP for the Next.js app.</t>
-  </si>
-  <si>
-    <t>TEST-030</t>
-  </si>
-  <si>
-    <t>Security regression suite</t>
-  </si>
-  <si>
-    <t>Fuzz corpus, pixel bombs, href/field policy, IDOR, CSRF.</t>
-  </si>
-  <si>
-    <t>SEC-010,SEC-012,SEC-014,SEC-015</t>
-  </si>
-  <si>
-    <t>AUD-09,AUD-12,AUD-13</t>
-  </si>
-  <si>
-    <t>SEC-021</t>
-  </si>
-  <si>
-    <t>Sensitivity-label metadata in the public repository</t>
-  </si>
-  <si>
-    <t>корекции.docx (committed in 5f2bf9e, pushed) carries 8 MSIP_Label_* custom properties incl. the organisation's tenant SiteId (label: Microsoft default 'General' family, no content marking). Options: leave; scrub the file in a new commit (HEAD only); purge from history (force-push).</t>
-  </si>
-  <si>
-    <t>repository history</t>
-  </si>
-  <si>
-    <t>Needs Boril: the choice involves his organisation's label and possibly rewriting pushed history. The tracker tools now strip MSIP labels on every write; the pre-push scan flags them.</t>
-  </si>
-  <si>
-    <t>SEC-022</t>
-  </si>
-  <si>
-    <t>Formatting rule values can't break out of a style</t>
-  </si>
-  <si>
-    <t>A rule value reaches the editor's style attribute, Word and PDF styles as text. The element-style and page-setting endpoints accepted any string (e.g. 'center;background-image:url(...)'), the AI instruction path too (FMT-005): CSS injection into every viewer's editor.</t>
-  </si>
-  <si>
-    <t>app/formatting/values.py: clean_rule_value per property (the StyleSystem's limits: choices, true/false, one safe font name, renderable colours, bounded numbers with known units, header/footer text &lt;=500). Refused with 422 by the element-style and page-setting endpoints (schemas RuleValue); instruction rules and set_style operations with such values dropped (FMT-005), validate_operations refuses them; stored rules no renderer can use are skipped at resolve (engine._usable) so old documents can't carry them either. All 177 default/template rules pass unchanged.</t>
-  </si>
-  <si>
-    <t>tests/test_rule_values.py (34 cases incl. API 422, stored-rule skip, instruction drop)</t>
-  </si>
-  <si>
-    <t>Found 2026-09-27 while mapping editor alignment (EDIT-008); probe confirmed the raw value in resolvedStyles.</t>
-  </si>
-  <si>
-    <t>PERF-001</t>
-  </si>
-  <si>
-    <t>Linear DOCX table export</t>
-  </si>
-  <si>
-    <t>500x8 table under a recorded threshold (baseline 321 s).</t>
-  </si>
-  <si>
-    <t>AUD-10</t>
-  </si>
-  <si>
-    <t>PERF-002</t>
-  </si>
-  <si>
-    <t>Benchmarks recorded</t>
-  </si>
-  <si>
-    <t>Baseline and current measurements in the PERFORMANCE sheet.</t>
-  </si>
-  <si>
-    <t>tests/perf</t>
-  </si>
-  <si>
-    <t>PERF-003</t>
-  </si>
-  <si>
-    <t>Delta autosave</t>
-  </si>
-  <si>
-    <t>Change-aware patches with a threshold strategy; whole document only when needed.</t>
-  </si>
-  <si>
-    <t>frontend/editor, backend/api</t>
-  </si>
-  <si>
-    <t>PERF-004</t>
-  </si>
-  <si>
-    <t>Bounded, compressed version history</t>
-  </si>
-  <si>
-    <t>Editor history separate from persisted versions; compression/deltas; asset references.</t>
-  </si>
-  <si>
-    <t>PERF-005</t>
-  </si>
-  <si>
-    <t>Editor at 5k-12k blocks</t>
-  </si>
-  <si>
-    <t>Typing latency measured and improved.</t>
-  </si>
-  <si>
-    <t>PERF-006</t>
-  </si>
-  <si>
-    <t>JSON without ASCII escaping</t>
-  </si>
-  <si>
-    <t>Document JSON stored and sent as UTF-8.</t>
-  </si>
-  <si>
-    <t>backend/db</t>
-  </si>
-  <si>
-    <t>PERF-007</t>
-  </si>
-  <si>
-    <t>Safe size limits recorded</t>
-  </si>
-  <si>
-    <t>User-facing maximum sizes, job timeouts, resource ceilings documented and enforced.</t>
-  </si>
-  <si>
-    <t>backend/config</t>
-  </si>
-  <si>
-    <t>AUD-09,AUD-10</t>
-  </si>
-  <si>
-    <t>ACCT-001</t>
-  </si>
-  <si>
-    <t>E-mail sender abstraction</t>
-  </si>
-  <si>
-    <t>SMTP provider + development outbox; no secrets in logs.</t>
-  </si>
-  <si>
-    <t>AUD-14</t>
-  </si>
-  <si>
-    <t>ACCT-002</t>
-  </si>
-  <si>
-    <t>Password reset</t>
-  </si>
-  <si>
-    <t>Single-use, expiring, hashed tokens; rate-limited; no account enumeration.</t>
-  </si>
-  <si>
-    <t>backend/api, frontend</t>
-  </si>
-  <si>
-    <t>ACCT-003</t>
-  </si>
-  <si>
-    <t>E-mail verification</t>
-  </si>
-  <si>
-    <t>Verification tokens and state.</t>
-  </si>
-  <si>
-    <t>ACCT-004</t>
-  </si>
-  <si>
-    <t>Password change</t>
-  </si>
-  <si>
-    <t>Current password required; other sessions revoked.</t>
-  </si>
-  <si>
-    <t>ACCT-005</t>
-  </si>
-  <si>
-    <t>Account deletion</t>
-  </si>
-  <si>
-    <t>Cascading policy: documents, versions, assets, exports, sessions, jobs, usage.</t>
-  </si>
-  <si>
-    <t>ACCT-006</t>
-  </si>
-  <si>
-    <t>Session revocation and cleanup</t>
-  </si>
-  <si>
-    <t>Sign out everywhere; expired/revoked session sweep.</t>
-  </si>
-  <si>
-    <t>ACCT-007</t>
-  </si>
-  <si>
-    <t>Suspicious login handling</t>
-  </si>
-  <si>
-    <t>Lockout and notification strategy.</t>
-  </si>
-  <si>
-    <t>PLAN-001</t>
-  </si>
-  <si>
-    <t>Usage units</t>
-  </si>
-  <si>
-    <t>Documents, exports, PDF pages, OCR pages, translation characters, AI operations, storage, batch jobs.</t>
-  </si>
-  <si>
-    <t>backend/billing</t>
-  </si>
-  <si>
-    <t>AUD-11</t>
-  </si>
-  <si>
-    <t>PLAN-002</t>
-  </si>
-  <si>
-    <t>Configurable plan defaults</t>
-  </si>
-  <si>
-    <t>Free/Pro/Business initial hypotheses as configuration, never hardcoded.</t>
-  </si>
-  <si>
-    <t>PLAN-003</t>
-  </si>
-  <si>
-    <t>Atomic entitlement checks</t>
-  </si>
-  <si>
-    <t>Reservation/locking; concurrency test proves limits hold.</t>
-  </si>
-  <si>
-    <t>PLAN-004</t>
-  </si>
-  <si>
-    <t>Stripe flows review</t>
-  </si>
-  <si>
-    <t>Checkout, portal, upgrade, downgrade, cancel, renewal, failed payment, webhook idempotency.</t>
-  </si>
-  <si>
-    <t>PLAN-005</t>
-  </si>
-  <si>
-    <t>Storage metering including history</t>
-  </si>
-  <si>
-    <t>History and autosave growth counted.</t>
-  </si>
-  <si>
-    <t>AUD-11,AUD-16</t>
-  </si>
-  <si>
-    <t>PDF-010</t>
-  </si>
-  <si>
-    <t>Geometry-aware PDF parser</t>
-  </si>
-  <si>
-    <t>Chars, fonts, sizes, colours, lines, rectangles, images, links, annotations, outlines, forms, metadata, rotation, page boxes.</t>
-  </si>
-  <si>
-    <t>backend/parsers/pdf</t>
-  </si>
-  <si>
-    <t>PDF-011</t>
-  </si>
-  <si>
-    <t>Page classifier</t>
-  </si>
-  <si>
-    <t>TEXT / SCANNED / HYBRID per page with evidence.</t>
-  </si>
-  <si>
-    <t>PDF-012</t>
-  </si>
-  <si>
-    <t>PDF inspection report</t>
-  </si>
-  <si>
-    <t>What the parser found, per page.</t>
-  </si>
-  <si>
-    <t>P2E-001</t>
-  </si>
-  <si>
-    <t>Layout primitives where PDF needs them</t>
-  </si>
-  <si>
-    <t>Page, block, bbox, rotation, confidence, provenance.</t>
-  </si>
-  <si>
-    <t>P2E-002</t>
-  </si>
-  <si>
-    <t>Structure reconstruction</t>
-  </si>
-  <si>
-    <t>Reading order, lines, paragraphs, headings, lists, captions, header/footer bands, columns.</t>
-  </si>
-  <si>
-    <t>backend/pdf</t>
-  </si>
-  <si>
-    <t>P2E-003</t>
-  </si>
-  <si>
-    <t>Images with position</t>
-  </si>
-  <si>
-    <t>Extracted images kept with bbox.</t>
-  </si>
-  <si>
-    <t>P2E-004</t>
-  </si>
-  <si>
-    <t>Tables from PDF</t>
-  </si>
-  <si>
-    <t>Ruling lines and alignment.</t>
-  </si>
-  <si>
-    <t>P2E-005</t>
-  </si>
-  <si>
-    <t>Confidence and conversion report</t>
-  </si>
-  <si>
-    <t>Per element confidence; issues reported; never silent removal.</t>
-  </si>
-  <si>
-    <t>P2E-006</t>
-  </si>
-  <si>
-    <t>OCR provider abstraction</t>
-  </si>
-  <si>
-    <t>Interface (text, confidence, bbox, page, language/script); implementation(s); OCR output untrusted.</t>
-  </si>
-  <si>
-    <t>backend/ocr</t>
-  </si>
-  <si>
-    <t>P2E-007</t>
-  </si>
-  <si>
-    <t>Imported-from-PDF version and UX</t>
-  </si>
-  <si>
-    <t>Editable document vs layout-focused choice; confidence shown.</t>
-  </si>
-  <si>
-    <t>frontend, backend</t>
-  </si>
-  <si>
-    <t>P2E-008</t>
-  </si>
-  <si>
-    <t>PDF fixtures and tests</t>
-  </si>
-  <si>
-    <t>Text, scanned, hybrid, tables, columns, multilingual.</t>
-  </si>
-  <si>
-    <t>P2E-020</t>
-  </si>
-  <si>
-    <t>Layout-preserving architecture</t>
-  </si>
-  <si>
-    <t>Frames/anchors model hooks and design doc.</t>
-  </si>
-  <si>
-    <t>docs, backend/models</t>
-  </si>
-  <si>
-    <t>PDF-020</t>
-  </si>
-  <si>
-    <t>PDF page operations service</t>
-  </si>
-  <si>
-    <t>Reorder, rotate, delete, duplicate, extract, split, merge as a separate service.</t>
-  </si>
-  <si>
-    <t>TRAN-001</t>
-  </si>
-  <si>
-    <t>Segments and tag protocol</t>
-  </si>
-  <si>
-    <t>Segments keep element/run ids, marks, placeholders; never one giant string.</t>
-  </si>
-  <si>
-    <t>backend/translation</t>
-  </si>
-  <si>
-    <t>TRAN-002</t>
-  </si>
-  <si>
-    <t>TranslationProvider abstraction</t>
-  </si>
-  <si>
-    <t>AI provider implementation + deterministic test provider.</t>
-  </si>
-  <si>
-    <t>TRAN-003</t>
-  </si>
-  <si>
-    <t>Translation validation</t>
-  </si>
-  <si>
-    <t>Tags, numbers, units, dates, percentages, identifiers, glossary terms.</t>
-  </si>
-  <si>
-    <t>TRAN-004</t>
-  </si>
-  <si>
-    <t>Glossary and terminology lock</t>
-  </si>
-  <si>
-    <t>Source/target term, domain, locked, case-sensitive.</t>
-  </si>
-  <si>
-    <t>backend/translation, db</t>
-  </si>
-  <si>
-    <t>TRAN-005</t>
-  </si>
-  <si>
-    <t>Selection/paragraph/block translation proposals</t>
-  </si>
-  <si>
-    <t>Preview; accept/reject; undo.</t>
-  </si>
-  <si>
-    <t>TRAN-003,REV-001</t>
-  </si>
-  <si>
-    <t>TRAN-006</t>
-  </si>
-  <si>
-    <t>Whole-document translated version</t>
-  </si>
-  <si>
-    <t>Source kept; translated copy linked.</t>
-  </si>
-  <si>
-    <t>TRAN-007</t>
-  </si>
-  <si>
-    <t>Language, script, direction metadata</t>
-  </si>
-  <si>
-    <t>Auto-detect + manual override.</t>
-  </si>
-  <si>
-    <t>TRAN-008</t>
-  </si>
-  <si>
-    <t>Translation UX</t>
-  </si>
-  <si>
-    <t>Toolbar/context Translate, target language, preview, accept/reject; 'AI-assisted translation - review required'.</t>
-  </si>
-  <si>
-    <t>TRAN-009</t>
-  </si>
-  <si>
-    <t>Translation metering</t>
-  </si>
-  <si>
-    <t>Translation characters as a usage unit.</t>
-  </si>
-  <si>
-    <t>TRAN-010</t>
-  </si>
-  <si>
-    <t>Translation tests</t>
-  </si>
-  <si>
-    <t>Formatting preservation, validation, versions.</t>
-  </si>
-  <si>
-    <t>FONT-001</t>
-  </si>
-  <si>
-    <t>Font catalogue with Unicode coverage</t>
-  </si>
-  <si>
-    <t>fontTools cmap coverage per script, metrics, embeddability.</t>
-  </si>
-  <si>
-    <t>backend/fonts</t>
-  </si>
-  <si>
-    <t>AUD-17</t>
-  </si>
-  <si>
-    <t>FONT-002</t>
-  </si>
-  <si>
-    <t>FontResolver</t>
-  </si>
-  <si>
-    <t>Script segmentation, coverage, fallback chain, embedding, RTL; deterministic first, AI suggestion validated.</t>
-  </si>
-  <si>
-    <t>FONT-003</t>
-  </si>
-  <si>
-    <t>Multilingual PDF rendering</t>
-  </si>
-  <si>
-    <t>Shaping for Arabic/Hebrew/Devanagari, bidi, CJK fonts, emoji handled gracefully.</t>
-  </si>
-  <si>
-    <t>FONT-004</t>
-  </si>
-  <si>
-    <t>DOCX per-script fonts</t>
-  </si>
-  <si>
-    <t>w:rFonts ascii/hAnsi/eastAsia/cs, w:lang, rtl/bidi.</t>
-  </si>
-  <si>
-    <t>FONT-005</t>
-  </si>
-  <si>
-    <t>Editor fallback stacks</t>
-  </si>
-  <si>
-    <t>CSS stacks from the resolver.</t>
-  </si>
-  <si>
-    <t>FONT-006</t>
-  </si>
-  <si>
-    <t>Multilingual tests</t>
-  </si>
-  <si>
-    <t>Script matrix x editor/DOCX/PDF with pdftotext and rendering.</t>
-  </si>
-  <si>
-    <t>FMT-001</t>
-  </si>
-  <si>
-    <t>Style extraction completeness</t>
-  </si>
-  <si>
-    <t>Page setup, margins, fonts, headings, lists, tables, captions, headers/footers, spacing, numbering, colours.</t>
-  </si>
-  <si>
-    <t>FMT-002</t>
-  </si>
-  <si>
-    <t>Semantic mapping validated</t>
-  </si>
-  <si>
-    <t>AI classifies/maps, engine applies; validation.</t>
-  </si>
-  <si>
-    <t>FMT-003</t>
-  </si>
-  <si>
-    <t>Before/after for Format by Example</t>
-  </si>
-  <si>
-    <t>Preview before saving a template.</t>
-  </si>
-  <si>
-    <t>FMT-005</t>
-  </si>
-  <si>
-    <t>Rule value validation</t>
-  </si>
-  <si>
-    <t>Instruction-path values validated before reaching CSS/export.</t>
-  </si>
-  <si>
-    <t>Instruction rules and set_style operations go through values.clean_rule_value: invalid ones dropped, normalised values stored (see SEC-022).</t>
-  </si>
-  <si>
-    <t>tests/test_rule_values.py::test_instructions_cannot_carry_such_values</t>
-  </si>
-  <si>
-    <t>HLTH-001</t>
-  </si>
-  <si>
-    <t>Health 2.0 checks</t>
-  </si>
-  <si>
-    <t>Alt text, hidden text, mixed language, unsupported features, section inconsistency, broken lists, empty paragraphs, layout anomalies, duplicated formatting, broken links.</t>
-  </si>
-  <si>
-    <t>HLTH-002</t>
-  </si>
-  <si>
-    <t>Deterministic fixes with preview</t>
-  </si>
-  <si>
-    <t>Fix proposals through the change model.</t>
-  </si>
-  <si>
-    <t>HLTH-003</t>
-  </si>
-  <si>
-    <t>AI explanations only</t>
-  </si>
-  <si>
-    <t>AI explains issues; never scores.</t>
-  </si>
-  <si>
-    <t>REV-002</t>
-  </si>
-  <si>
-    <t>Review Changes UI</t>
-  </si>
-  <si>
-    <t>Categories FORMAT/STRUCTURE/CONTENT/METADATA/PRESERVATION/TRANSLATION.</t>
-  </si>
-  <si>
-    <t>REV-003</t>
-  </si>
-  <si>
-    <t>Content changes need acceptance</t>
-  </si>
-  <si>
-    <t>Enforced server-side.</t>
-  </si>
-  <si>
-    <t>backend</t>
-  </si>
-  <si>
-    <t>REV-004</t>
-  </si>
-  <si>
-    <t>Repair</t>
-  </si>
-  <si>
-    <t>Detected issue, proposed fix, preview, apply.</t>
-  </si>
-  <si>
-    <t>REV-005</t>
-  </si>
-  <si>
-    <t>Clean copy</t>
-  </si>
-  <si>
-    <t>Explicit: remove comments, accept tracked changes, remove hidden text, remove metadata, normalise formatting.</t>
-  </si>
-  <si>
-    <t>FEAT-001</t>
-  </si>
-  <si>
-    <t>Batch formatting</t>
-  </si>
-  <si>
-    <t>One template/reference over many documents as jobs.</t>
-  </si>
-  <si>
-    <t>backend/jobs</t>
-  </si>
-  <si>
-    <t>FEAT-002</t>
-  </si>
-  <si>
-    <t>Batch export</t>
-  </si>
-  <si>
-    <t>Many documents to a zip.</t>
-  </si>
-  <si>
-    <t>FEAT-003</t>
-  </si>
-  <si>
-    <t>Batch translation</t>
-  </si>
-  <si>
-    <t>After the translation MVP.</t>
-  </si>
-  <si>
-    <t>FEAT-010</t>
-  </si>
-  <si>
-    <t>Accessibility checker</t>
-  </si>
-  <si>
-    <t>Heading hierarchy, alt text, link labels, table headers, reading order, language, contrast.</t>
-  </si>
-  <si>
-    <t>FEAT-011</t>
-  </si>
-  <si>
-    <t>App accessibility fixes</t>
-  </si>
-  <si>
-    <t>Zero serious axe violations on main pages and the editor.</t>
-  </si>
-  <si>
-    <t>JOB-001</t>
-  </si>
-  <si>
-    <t>Job safety</t>
-  </si>
-  <si>
-    <t>idempotency_key, retry_count, timeout, cancellation, stuck detection, backoff, dead-letter.</t>
-  </si>
-  <si>
-    <t>STOR-001</t>
-  </si>
-  <si>
-    <t>Storage retention and deletion</t>
-  </si>
-  <si>
-    <t>Source files, exports, OCR artifacts: retention, deletion, access control, content types, size limits.</t>
-  </si>
-  <si>
-    <t>OBS-001</t>
-  </si>
-  <si>
-    <t>Metrics</t>
-  </si>
-  <si>
-    <t>Latency, failure rate, job/AI/export metrics without content.</t>
-  </si>
-  <si>
-    <t>AUD-15</t>
-  </si>
-  <si>
-    <t>OBS-002</t>
-  </si>
-  <si>
-    <t>Operation and job IDs in logs</t>
-  </si>
-  <si>
-    <t>Request, operation and job IDs everywhere.</t>
-  </si>
-  <si>
-    <t>OBS-003</t>
-  </si>
-  <si>
-    <t>Operations data</t>
-  </si>
-  <si>
-    <t>Failed jobs, processing failures, usage spikes, AI/export failures, storage, abuse - minimal admin API.</t>
-  </si>
-  <si>
-    <t>INFRA-010</t>
-  </si>
-  <si>
-    <t>Deployment verified</t>
-  </si>
-  <si>
-    <t>Docker images build and start; Postgres, Redis, storage, worker, frontend, backend.</t>
-  </si>
-  <si>
-    <t>docker, CI</t>
-  </si>
-  <si>
-    <t>INFRA-011</t>
-  </si>
-  <si>
-    <t>CI gates</t>
-  </si>
-  <si>
-    <t>Backend, frontend, E2E, lint, typecheck, build, migrations, security audit, document fidelity tests.</t>
-  </si>
-  <si>
-    <t>.github/workflows</t>
-  </si>
-  <si>
-    <t>AUD-15,AUD-20</t>
-  </si>
-  <si>
-    <t>TEST-040</t>
-  </si>
-  <si>
-    <t>Playwright workflow coverage</t>
-  </si>
-  <si>
-    <t>The 24 workflows of the brief.</t>
-  </si>
-  <si>
-    <t>TEST-041</t>
-  </si>
-  <si>
-    <t>Performance gates</t>
-  </si>
-  <si>
-    <t>Regression thresholds relative to baseline.</t>
-  </si>
-  <si>
-    <t>TEST-043</t>
-  </si>
-  <si>
-    <t>Browser matrix</t>
-  </si>
-  <si>
-    <t>Chromium, Firefox, WebKit.</t>
-  </si>
-  <si>
-    <t>TEST-006</t>
-  </si>
-  <si>
-    <t>E2E backend removes its temp directory</t>
-  </si>
-  <si>
-    <t>scripts/e2e_server.py leaves %TEMP%/smartdoc-e2e-* behind after every Playwright run (10 found on 2026-09-27).</t>
-  </si>
-  <si>
-    <t>backend/scripts/e2e_server.py</t>
-  </si>
-  <si>
-    <t>DOCS-010</t>
-  </si>
-  <si>
-    <t>final-production-readiness.md</t>
-  </si>
-  <si>
-    <t>The 16-section final report.</t>
-  </si>
-  <si>
-    <t>DOCS-011</t>
-  </si>
-  <si>
-    <t>Documentation tree</t>
-  </si>
-  <si>
-    <t>docs/{architecture,document-model,docx,pdf,translation,ai,formatting,security,testing,deployment,billing,operations}.</t>
-  </si>
-  <si>
-    <t>Started with Phase 1: docs/document-model, docs/architecture/fidelity.md, docs/docx, docs/formatting, docs/security, docs/testing (each grounded in the code and tests of Phases 0-1). Remaining folders (pdf, translation, ai, deployment, billing, operations) as their phases land.; docs/ai/README.md added with Phase 2.</t>
-  </si>
-  <si>
-    <t>CRITICAL_FIXES — Audit findings and P0 tasks</t>
-  </si>
-  <si>
-    <t>The 20 findings of the 2026-09-26 audit (current known risks) with fix progress, then every P0 task. Report: https://claude.ai/artifact/WKskiyexTDLAHe1BfjvWR1 — a finding is RESOLVED when every linked fix task is DONE.</t>
-  </si>
-  <si>
-    <t>Findings</t>
-  </si>
-  <si>
-    <t>Resolved</t>
-  </si>
-  <si>
-    <t>Open</t>
-  </si>
-  <si>
-    <t>P0 tasks</t>
-  </si>
-  <si>
-    <t>P0 done</t>
-  </si>
-  <si>
-    <t>Audit findings (current known risks)</t>
-  </si>
-  <si>
-    <t>Finding ID</t>
-  </si>
-  <si>
-    <t>Progress</t>
-  </si>
-  <si>
-    <t>Finding</t>
-  </si>
-  <si>
-    <t>Fix Tasks</t>
-  </si>
-  <si>
-    <t>Active</t>
-  </si>
-  <si>
-    <t>Blocked/Failed</t>
-  </si>
-  <si>
-    <t>Editor save can discard nested blocks (lists, pictures, code, quotes inside cells/items)</t>
-  </si>
-  <si>
-    <t>EDIT-001,EDIT-002,EDIT-003,EDIT-005,EDIT-006</t>
-  </si>
-  <si>
-    <t>AI fidelity check misses omissions, negation removal, number changes, inserted text</t>
-  </si>
-  <si>
-    <t>AI-001,AI-002,AI-003,AI-004</t>
-  </si>
-  <si>
-    <t>Fixed in Phase 2 (AI-001..004): AI structure answers are checked token by token; any omission, negation removal, number/unit/date change, insertion, reordering, duplication or punctuation change is refused.</t>
-  </si>
-  <si>
-    <t>Import/export silently changes hidden text, numbering, section headers, metadata, alt text, structure</t>
-  </si>
-  <si>
-    <t>FID-002,DOCX-011,DOCX-013,DOCX-015,DOCX-025</t>
-  </si>
-  <si>
-    <t>List numbering changes ('Чл. 1.' -&gt; '1.', '(a)' -&gt; 'a.', start values)</t>
-  </si>
-  <si>
-    <t>Partly fixed in 622d9c1: list format/start/continuation kept; custom labels ('Чл. 1.', '(a)') and multi-level labels reported, not kept yet (DOCX-016).</t>
-  </si>
-  <si>
-    <t>AI instruction operations can delete/insert/move content without preview</t>
-  </si>
-  <si>
-    <t>AI-005,AI-006,AI-007,REV-003</t>
-  </si>
-  <si>
-    <t>Fixed in Phase 2 (AI-005..AI-007): an instruction's insert/delete/move is a proposal the user sees and accepts or rejects; nothing is deleted silently.</t>
-  </si>
-  <si>
-    <t>Content controls, metadata, comment threads, sensitivity information lost</t>
-  </si>
-  <si>
-    <t>DOCX-012,DOCX-021,DOCX-023</t>
-  </si>
-  <si>
-    <t>Image fidelity gaps: alt text, crop, rotation, formats</t>
-  </si>
-  <si>
-    <t>Table export changes header state, borders, alignment, widths, geometry</t>
-  </si>
-  <si>
-    <t>Large images cause huge memory consumption</t>
-  </si>
-  <si>
-    <t>SEC-012,SEC-013</t>
-  </si>
-  <si>
-    <t>Large tables have a performance problem</t>
-  </si>
-  <si>
-    <t>Plan limits have a concurrency race</t>
-  </si>
-  <si>
-    <t>Malformed DOCX leads to HTTP 500</t>
-  </si>
-  <si>
-    <t>SEC-010,SEC-019</t>
-  </si>
-  <si>
-    <t>Dangerous href/field instructions must be filtered</t>
-  </si>
-  <si>
-    <t>SEC-014,SEC-015,SEC-016</t>
-  </si>
-  <si>
-    <t>Account essentials missing: reset, verification, change, deletion</t>
-  </si>
-  <si>
-    <t>ACCT-002,ACCT-003,ACCT-004,ACCT-005</t>
-  </si>
-  <si>
-    <t>Operations/monitoring must be confirmed</t>
-  </si>
-  <si>
-    <t>OBS-001,OBS-002,INFRA-010</t>
-  </si>
-  <si>
-    <t>Whole-document autosave must be optimised</t>
-  </si>
-  <si>
-    <t>PERF-003,PERF-004</t>
-  </si>
-  <si>
-    <t>PDF multilingual rendering must be reliable</t>
-  </si>
-  <si>
-    <t>FONT-003,FONT-006</t>
-  </si>
-  <si>
-    <t>Export metadata must be correct</t>
-  </si>
-  <si>
-    <t>DOCX-012,DOCX-020</t>
-  </si>
-  <si>
-    <t>Partly fixed in 622d9c1: Word exports carry the source file's core properties (author, dates, subject...) instead of 'python-docx'/2013; fields remain (DOCX-020).</t>
-  </si>
-  <si>
-    <t>AUD-19</t>
-  </si>
-  <si>
-    <t>Canonical model must represent more than paragraphs + runs + simple tables</t>
-  </si>
-  <si>
-    <t>CORE-001,DOCX-015,DOCX-016,DOCX-017</t>
-  </si>
-  <si>
-    <t>Tests can miss import-side data loss (model-relative comparison)</t>
-  </si>
-  <si>
-    <t>TEST-020,TEST-021,TEST-022</t>
-  </si>
-  <si>
-    <t>P0 tasks (live from MASTER)</t>
-  </si>
-  <si>
-    <t>DOCUMENT_FIDELITY — Content preservation</t>
-  </si>
-  <si>
-    <t>Canonical model, fidelity reports, capability matrix, change/review model. Categories: CORE, FIDELITY, REVIEW. Rows are formulas over MASTER — change task data in MASTER or with tools/tracker/tracker.py.</t>
-  </si>
-  <si>
-    <t>Tasks (live from MASTER)</t>
-  </si>
-  <si>
-    <t>DOCX_OOXML — DOCX / OOXML preservation</t>
-  </si>
-  <si>
-    <t>Import and export fidelity for Word documents. Categories: DOCX. Rows are formulas over MASTER — change task data in MASTER or with tools/tracker/tracker.py.</t>
-  </si>
-  <si>
-    <t>PDF — PDF engine</t>
-  </si>
-  <si>
-    <t>PDF export and PDF parsing. Categories: PDF. Rows are formulas over MASTER — change task data in MASTER or with tools/tracker/tracker.py.</t>
-  </si>
-  <si>
-    <t>EDITOR — Editor integrity</t>
-  </si>
-  <si>
-    <t>Tiptap mapping and save integrity. Categories: EDITOR. Rows are formulas over MASTER — change task data in MASTER or with tools/tracker/tracker.py.</t>
-  </si>
-  <si>
-    <t>FORMATTING — Formatting and Document Health</t>
-  </si>
-  <si>
-    <t>Formatting engine, Format by Example, Document Health. Categories: FORMATTING, HEALTH. Rows are formulas over MASTER — change task data in MASTER or with tools/tracker/tracker.py.</t>
-  </si>
-  <si>
-    <t>AI — AI fidelity</t>
-  </si>
-  <si>
-    <t>Fidelity checks, proposals and review, budgets. Categories: AI. Rows are formulas over MASTER — change task data in MASTER or with tools/tracker/tracker.py.</t>
-  </si>
-  <si>
-    <t>SECURITY — Security and accounts</t>
-  </si>
-  <si>
-    <t>Security hardening and account essentials. Categories: SECURITY, ACCOUNT. Rows are formulas over MASTER — change task data in MASTER or with tools/tracker/tracker.py.</t>
-  </si>
-  <si>
-    <t>PERFORMANCE — Performance</t>
-  </si>
-  <si>
-    <t>Measured results — brief §80-81: measure, then set regression thresholds relative to the baseline (no invented SLOs)</t>
-  </si>
-  <si>
-    <t>Bench ID</t>
-  </si>
-  <si>
-    <t>Metric</t>
-  </si>
-  <si>
-    <t>Unit</t>
-  </si>
-  <si>
-    <t>Scenario</t>
-  </si>
-  <si>
-    <t>Baseline</t>
-  </si>
-  <si>
-    <t>Baseline Source</t>
-  </si>
-  <si>
-    <t>Current</t>
-  </si>
-  <si>
-    <t>Measured On</t>
-  </si>
-  <si>
-    <t>Threshold</t>
-  </si>
-  <si>
-    <t>BENCH-001</t>
-  </si>
-  <si>
-    <t>duration</t>
-  </si>
-  <si>
-    <t>s</t>
-  </si>
-  <si>
-    <t>DOCX export: table 500x8 (4,000 cells)</t>
-  </si>
-  <si>
-    <t>audit perf_table.py (400 cells 3.8 s; 1,600 cells 53.7 s; quadratic)</t>
-  </si>
-  <si>
-    <t>BENCH-002</t>
-  </si>
-  <si>
-    <t>PDF export: table 500x8</t>
-  </si>
-  <si>
-    <t>audit perf_table.py (linear)</t>
-  </si>
-  <si>
-    <t>BENCH-003</t>
-  </si>
-  <si>
-    <t>Import: 300-page text DOCX (1,650 elements)</t>
-  </si>
-  <si>
-    <t>audit perf_backend.py</t>
-  </si>
-  <si>
-    <t>BENCH-004</t>
-  </si>
-  <si>
-    <t>DOCX export: 300-page text document</t>
-  </si>
-  <si>
-    <t>BENCH-005</t>
-  </si>
-  <si>
-    <t>PDF export: 300-page text document</t>
-  </si>
-  <si>
-    <t>BENCH-006</t>
-  </si>
-  <si>
-    <t>memory growth</t>
-  </si>
-  <si>
-    <t>MB</t>
-  </si>
-  <si>
-    <t>PDF export: 39 KB DOCX holding a 12000x12000 PNG</t>
-  </si>
-  <si>
-    <t>audit pixel_bomb.py (14000x14000 crashes the export)</t>
-  </si>
-  <si>
-    <t>BENCH-007</t>
-  </si>
-  <si>
-    <t>PDF export: 4 JPEG images 2400x1800</t>
-  </si>
-  <si>
-    <t>audit perf_backend.py (6.3 s)</t>
-  </si>
-  <si>
-    <t>BENCH-008</t>
-  </si>
-  <si>
-    <t>Editor: type 20 characters at 12,196 elements (1M-character paste)</t>
-  </si>
-  <si>
-    <t>audit perf_browser.js (~470 ms per key)</t>
-  </si>
-  <si>
-    <t>BENCH-009</t>
-  </si>
-  <si>
-    <t>Editor: type 20 characters, 300-page document</t>
-  </si>
-  <si>
-    <t>audit perf_browser.js</t>
-  </si>
-  <si>
-    <t>BENCH-010</t>
-  </si>
-  <si>
-    <t>request size</t>
-  </si>
-  <si>
-    <t>Autosave request: 300-page document</t>
-  </si>
-  <si>
-    <t>audit perf_browser.js (whole elements list per save)</t>
-  </si>
-  <si>
-    <t>BENCH-011</t>
-  </si>
-  <si>
-    <t>Autosave request: 1M-character paste</t>
-  </si>
-  <si>
-    <t>BENCH-012</t>
-  </si>
-  <si>
-    <t>storage</t>
-  </si>
-  <si>
-    <t>Stored history: one 300-page document, 50 steps</t>
-  </si>
-  <si>
-    <t>audit (2.8 MB per full copy; 7.2 MB when the JSON is ASCII-escaped)</t>
-  </si>
-  <si>
-    <t>BENCH-013</t>
-  </si>
-  <si>
-    <t>Paste: 2M characters (the cap)</t>
-  </si>
-  <si>
-    <t>audit perf_backend.py (17.5k elements, 7.1 MB JSON)</t>
-  </si>
-  <si>
-    <t>Performance tasks (live from MASTER)</t>
-  </si>
-  <si>
-    <t>TESTING — Testing</t>
-  </si>
-  <si>
-    <t>Test runs (oldest first)</t>
-  </si>
-  <si>
-    <t>Run ID</t>
-  </si>
-  <si>
-    <t>Command</t>
-  </si>
-  <si>
-    <t>Passed</t>
-  </si>
-  <si>
-    <t>Skipped</t>
-  </si>
-  <si>
-    <t>Date</t>
-  </si>
-  <si>
-    <t>Duration (s)</t>
-  </si>
-  <si>
-    <t>RUN-0001</t>
-  </si>
-  <si>
-    <t>backend-pytest</t>
-  </si>
-  <si>
-    <t>PASS</t>
-  </si>
-  <si>
-    <t>cd backend &amp;&amp; venv/Scripts/python -m pytest -q -p no:cacheprovider</t>
-  </si>
-  <si>
-    <t>Skip: optional real-Word check (SMARTDOC_REAL_DOCX unset). 1 DeprecationWarning (starlette/anyio). Audit measured 93% line coverage on 2026-09-26.</t>
-  </si>
-  <si>
-    <t>ea69829</t>
-  </si>
-  <si>
-    <t>RUN-0002</t>
-  </si>
-  <si>
-    <t>frontend-lint</t>
-  </si>
-  <si>
-    <t>cd frontend &amp;&amp; npm run lint</t>
-  </si>
-  <si>
-    <t>eslint: 0 problems</t>
-  </si>
-  <si>
-    <t>RUN-0003</t>
-  </si>
-  <si>
-    <t>frontend-tsc</t>
-  </si>
-  <si>
-    <t>cd frontend &amp;&amp; npx tsc --noEmit</t>
-  </si>
-  <si>
-    <t>0 type errors</t>
-  </si>
-  <si>
-    <t>RUN-0004</t>
-  </si>
-  <si>
-    <t>frontend-vitest</t>
-  </si>
-  <si>
-    <t>cd frontend &amp;&amp; npm test</t>
-  </si>
-  <si>
-    <t>6 test files</t>
-  </si>
-  <si>
-    <t>RUN-0005</t>
-  </si>
-  <si>
-    <t>frontend-build</t>
-  </si>
-  <si>
-    <t>cd frontend &amp;&amp; npm run build</t>
-  </si>
-  <si>
-    <t>Next.js production build, 11 routes</t>
-  </si>
-  <si>
-    <t>RUN-0006</t>
-  </si>
-  <si>
-    <t>e2e-playwright</t>
-  </si>
-  <si>
-    <t>cd frontend &amp;&amp; npm run test:e2e</t>
-  </si>
-  <si>
-    <t>Edge; throwaway backend on SQLite (:8100) + production build (:3100). 16 workflows in 5 spec files; the brief asks for 24 (TEST-040). Leaves %TEMP%/smartdoc-e2e-* dirs behind (TEST-006).</t>
-  </si>
-  <si>
-    <t>RUN-0007</t>
-  </si>
-  <si>
-    <t>migrations</t>
-  </si>
-  <si>
-    <t>alembic upgrade head &amp;&amp; alembic check &amp;&amp; alembic downgrade base &amp;&amp; alembic upgrade head (scratch SQLite); alembic upgrade head --sql (PostgreSQL dialect)</t>
-  </si>
-  <si>
-    <t>head 85211092fe4c; 'No new upgrade operations detected'; offline SQL: 14 tables at head, RLS enabled on every table</t>
-  </si>
-  <si>
-    <t>RUN-0008</t>
-  </si>
-  <si>
-    <t>supabase</t>
-  </si>
-  <si>
-    <t>Supabase MCP: list_migrations, get_advisors security+performance, list_tables (project edmmjmsynjziahwtjuke)</t>
-  </si>
-  <si>
-    <t>8/8 migrations applied; 14 tables, RLS on all; advisors only INFO: 14x rls_enabled_no_policy (by design: the API connects as owner, PostgREST roles see nothing), 8x unused_index (low traffic)</t>
-  </si>
-  <si>
-    <t>RUN-0009</t>
-  </si>
-  <si>
-    <t>pip-audit</t>
-  </si>
-  <si>
-    <t>uvx pip-audit --disable-pip -r backend/requirements.lock; same for requirements-dev.lock</t>
-  </si>
-  <si>
-    <t>No known vulnerabilities in either lock file</t>
-  </si>
-  <si>
-    <t>RUN-0010</t>
-  </si>
-  <si>
-    <t>npm-audit</t>
-  </si>
-  <si>
-    <t>cd frontend &amp;&amp; npm audit; npm audit --omit=dev</t>
-  </si>
-  <si>
-    <t>0 vulnerabilities across 633 dependencies</t>
-  </si>
-  <si>
-    <t>RUN-0011</t>
-  </si>
-  <si>
-    <t>docker-compose</t>
-  </si>
-  <si>
-    <t>PARTIAL</t>
-  </si>
-  <si>
-    <t>docker compose config --quiet</t>
-  </si>
-  <si>
-    <t>compose file valid (8 services: postgres, redis, minio, minio-bucket, migrate, worker, backend, frontend); images NOT built: Docker daemon not running on this machine (CI builds them on main)</t>
-  </si>
-  <si>
-    <t>RUN-0012</t>
-  </si>
-  <si>
-    <t>Phase 1 editor integrity: +16 tests (nesting model, nested API/exports, health links)</t>
-  </si>
-  <si>
-    <t>RUN-0013</t>
-  </si>
-  <si>
-    <t>cd frontend &amp;&amp; npx vitest run</t>
-  </si>
-  <si>
-    <t>+31: nestedBlocks.test.ts (28), useAutoSave.test.tsx (3); tsc and eslint clean</t>
-  </si>
-  <si>
-    <t>RUN-0014</t>
-  </si>
-  <si>
-    <t>cd frontend &amp;&amp; npx playwright test</t>
-  </si>
-  <si>
-    <t>+1: e2e/nested.spec.ts (paste, autosave, reload)</t>
-  </si>
-  <si>
-    <t>RUN-0015</t>
-  </si>
-  <si>
-    <t>+29 test_fidelity_report.py</t>
-  </si>
-  <si>
-    <t>RUN-0016</t>
-  </si>
-  <si>
-    <t>+3 FidelityPanel.test.tsx</t>
-  </si>
-  <si>
-    <t>RUN-0017</t>
-  </si>
-  <si>
-    <t>+fidelity.spec.ts; nested.spec.ts made deterministic (focus check, Ctrl+End) after one run pasted at the document start</t>
-  </si>
-  <si>
-    <t>RUN-0018</t>
-  </si>
-  <si>
-    <t>+6 test_export_fidelity.py</t>
-  </si>
-  <si>
-    <t>RUN-0019</t>
-  </si>
-  <si>
-    <t>+4 ExportResult.test.tsx</t>
-  </si>
-  <si>
-    <t>RUN-0020</t>
-  </si>
-  <si>
-    <t>export test checks the export's content message</t>
-  </si>
-  <si>
-    <t>RUN-0021</t>
-  </si>
-  <si>
-    <t>+6 test_capabilities.py</t>
-  </si>
-  <si>
-    <t>RUN-0022</t>
-  </si>
-  <si>
-    <t>venv/Scripts/python -m pytest -q</t>
-  </si>
-  <si>
-    <t>after FID-002 detections + section break fix</t>
-  </si>
-  <si>
-    <t>RUN-0023</t>
-  </si>
-  <si>
-    <t>npx vitest run</t>
-  </si>
-  <si>
-    <t>tsc --noEmit and eslint clean too</t>
-  </si>
-  <si>
-    <t>RUN-0024</t>
-  </si>
-  <si>
-    <t>rule values (SEC-022) + editor direct styles</t>
-  </si>
-  <si>
-    <t>RUN-0025</t>
-  </si>
-  <si>
-    <t>tsc + eslint clean</t>
-  </si>
-  <si>
-    <t>RUN-0026</t>
-  </si>
-  <si>
-    <t>e2e</t>
-  </si>
-  <si>
-    <t>npx playwright test</t>
-  </si>
-  <si>
-    <t>incl. e2e/direct-formatting.spec.ts</t>
-  </si>
-  <si>
-    <t>RUN-0027</t>
-  </si>
-  <si>
-    <t>Phase 1 gate: link titles, mark order, Markdown pictures/rules</t>
-  </si>
-  <si>
-    <t>RUN-0028</t>
-  </si>
-  <si>
-    <t>Phase 1 gate; tsc + eslint clean</t>
-  </si>
-  <si>
-    <t>RUN-0029</t>
-  </si>
-  <si>
-    <t>Phase 1 gate</t>
-  </si>
-  <si>
-    <t>RUN-0030</t>
-  </si>
-  <si>
-    <t>AI fidelity check (AI-001..004)</t>
-  </si>
-  <si>
-    <t>RUN-0031</t>
-  </si>
-  <si>
-    <t>AI proposals</t>
-  </si>
-  <si>
-    <t>RUN-0032</t>
-  </si>
-  <si>
-    <t>RUN-0033</t>
-  </si>
-  <si>
-    <t>incl. e2e/proposals.spec.ts</t>
-  </si>
-  <si>
-    <t>RUN-0034</t>
-  </si>
-  <si>
-    <t>AI budget</t>
-  </si>
-  <si>
-    <t>RUN-0035</t>
-  </si>
-  <si>
-    <t>prompt-injection review</t>
-  </si>
-  <si>
-    <t>RUN-0036</t>
-  </si>
-  <si>
-    <t>Phase 2 gate</t>
-  </si>
-  <si>
-    <t>RUN-0037</t>
-  </si>
-  <si>
-    <t>RUN-0038</t>
-  </si>
-  <si>
-    <t>source package + patch writer</t>
-  </si>
-  <si>
-    <t>RUN-0039</t>
-  </si>
-  <si>
-    <t>after the patch writer</t>
-  </si>
-  <si>
-    <t>RUN-0040</t>
-  </si>
-  <si>
-    <t>backend pytest</t>
-  </si>
-  <si>
-    <t>DOCX-028: test_original_blocks.py (26), golden set of 13</t>
-  </si>
-  <si>
-    <t>7f22bf9</t>
-  </si>
-  <si>
-    <t>RUN-0041</t>
-  </si>
-  <si>
-    <t>frontend vitest</t>
-  </si>
-  <si>
-    <t>editor round trip includes 13-kept-blocks</t>
-  </si>
-  <si>
-    <t>RUN-0042</t>
-  </si>
-  <si>
-    <t>playwright</t>
-  </si>
-  <si>
-    <t>new e2e/kept-blocks.spec.ts</t>
-  </si>
-  <si>
-    <t>RUN-0043</t>
-  </si>
-  <si>
-    <t>tsc + eslint</t>
-  </si>
-  <si>
-    <t>cd frontend &amp;&amp; npx tsc --noEmit &amp;&amp; npx eslint .</t>
-  </si>
-  <si>
-    <t>0 type errors, 0 lint problems</t>
-  </si>
-  <si>
-    <t>RUN-0044</t>
-  </si>
-  <si>
-    <t>DOCX-025: tests/test_hidden_text.py (7)</t>
-  </si>
-  <si>
-    <t>fada4d7</t>
-  </si>
-  <si>
-    <t>RUN-0045</t>
-  </si>
-  <si>
-    <t>editor/hiddenText.test.tsx (6)</t>
-  </si>
-  <si>
-    <t>RUN-0046</t>
-  </si>
-  <si>
-    <t>new e2e/hidden-text.spec.ts</t>
-  </si>
-  <si>
-    <t>RUN-0047</t>
-  </si>
-  <si>
-    <t>RUN-0048</t>
-  </si>
-  <si>
-    <t>DOCX-013 part 1: tests/test_character_formatting.py (12)</t>
-  </si>
-  <si>
-    <t>c51b1bf</t>
-  </si>
-  <si>
-    <t>RUN-0049</t>
-  </si>
-  <si>
-    <t>editor/characterFormatting.test.ts (3)</t>
-  </si>
-  <si>
-    <t>RUN-0050</t>
-  </si>
-  <si>
-    <t>after DOCX-013 part 1</t>
-  </si>
-  <si>
-    <t>RUN-0051</t>
-  </si>
-  <si>
-    <t>RUN-0052</t>
-  </si>
-  <si>
-    <t>DOCX-013 part 2 + FID-007: tests/test_copy_reports.py (6)</t>
-  </si>
-  <si>
-    <t>309f9d6</t>
-  </si>
-  <si>
-    <t>RUN-0053</t>
-  </si>
-  <si>
-    <t>characterFormatting.test.ts (4)</t>
-  </si>
-  <si>
-    <t>RUN-0054</t>
-  </si>
-  <si>
-    <t>after DOCX-013 part 2</t>
-  </si>
-  <si>
-    <t>RUN-0055</t>
-  </si>
-  <si>
-    <t>RUN-0056</t>
-  </si>
-  <si>
-    <t>DOCX-014 part 1: tests/test_paragraph_formatting.py (9)</t>
-  </si>
-  <si>
-    <t>597275a</t>
-  </si>
-  <si>
-    <t>RUN-0057</t>
-  </si>
-  <si>
-    <t>after DOCX-014 part 1</t>
-  </si>
-  <si>
-    <t>RUN-0058</t>
-  </si>
-  <si>
-    <t>RUN-0059</t>
-  </si>
-  <si>
-    <t>RUN-0060</t>
-  </si>
-  <si>
-    <t>DOCX-014 part 2: tests/test_paragraph_formatting.py (19)</t>
-  </si>
-  <si>
-    <t>9f1c5b4</t>
-  </si>
-  <si>
-    <t>RUN-0061</t>
-  </si>
-  <si>
-    <t>after DOCX-014 part 2</t>
-  </si>
-  <si>
-    <t>RUN-0062</t>
-  </si>
-  <si>
-    <t>RUN-0063</t>
-  </si>
-  <si>
-    <t>RUN-0064</t>
-  </si>
-  <si>
-    <t>DOCX-015 part 1a: tests/test_sections.py (6)</t>
-  </si>
-  <si>
-    <t>49d54e5</t>
-  </si>
-  <si>
-    <t>RUN-0065</t>
-  </si>
-  <si>
-    <t>sectionBreak.test.ts (3)</t>
-  </si>
-  <si>
-    <t>RUN-0066</t>
-  </si>
-  <si>
-    <t>after DOCX-015 part 1a</t>
-  </si>
-  <si>
-    <t>RUN-0067</t>
-  </si>
-  <si>
-    <t>RUN-0068</t>
-  </si>
-  <si>
-    <t>DOCX-015 part 1b: tests/test_sections.py (7)</t>
-  </si>
-  <si>
-    <t>cb75ebd</t>
-  </si>
-  <si>
-    <t>RUN-0069</t>
-  </si>
-  <si>
-    <t>after DOCX-015 part 1b</t>
-  </si>
-  <si>
-    <t>RUN-0070</t>
-  </si>
-  <si>
-    <t>RUN-0071</t>
-  </si>
-  <si>
-    <t>RUN-0072</t>
-  </si>
-  <si>
-    <t>bc138f5</t>
-  </si>
-  <si>
-    <t>RUN-0073</t>
-  </si>
-  <si>
-    <t>vitest</t>
-  </si>
-  <si>
-    <t>RUN-0074</t>
-  </si>
-  <si>
-    <t>Testing tasks (live from MASTER)</t>
-  </si>
-  <si>
-    <t>PRODUCT_FEATURES — Product features</t>
-  </si>
-  <si>
-    <t>Feature backlog — brief §61-62</t>
-  </si>
-  <si>
-    <t>Feature</t>
-  </si>
-  <si>
-    <t>Bucket</t>
-  </si>
-  <si>
-    <t>Linked Tasks</t>
-  </si>
-  <si>
-    <t>Linked Done</t>
-  </si>
-  <si>
-    <t>Linked Total</t>
-  </si>
-  <si>
-    <t>Document integrity</t>
-  </si>
-  <si>
-    <t>NOW</t>
-  </si>
-  <si>
-    <t>EDIT-001,EDIT-005,FID-002</t>
-  </si>
-  <si>
-    <t>Brief 62: NOW #1</t>
-  </si>
-  <si>
-    <t>Fidelity</t>
-  </si>
-  <si>
-    <t>DOCX-011,TEST-022</t>
-  </si>
-  <si>
-    <t>Brief 62: NOW #2</t>
-  </si>
-  <si>
-    <t>Security</t>
-  </si>
-  <si>
-    <t>SEC-010,SEC-012,SEC-014</t>
-  </si>
-  <si>
-    <t>Brief 62: NOW #3</t>
-  </si>
-  <si>
-    <t>Performance</t>
-  </si>
-  <si>
-    <t>PERF-001,PERF-003,PERF-004</t>
-  </si>
-  <si>
-    <t>Brief 62: NOW #4</t>
-  </si>
-  <si>
-    <t>PDF -&gt; editable</t>
-  </si>
-  <si>
-    <t>P2E-002,P2E-005</t>
-  </si>
-  <si>
-    <t>Brief 62: NOW #5</t>
-  </si>
-  <si>
-    <t>TRAN-001,TRAN-006</t>
-  </si>
-  <si>
-    <t>Brief 62: NOW #6</t>
-  </si>
-  <si>
-    <t>FONT-002,FONT-003</t>
-  </si>
-  <si>
-    <t>Brief 62: NOW #7</t>
-  </si>
-  <si>
-    <t>Review Changes</t>
-  </si>
-  <si>
-    <t>REV-001,REV-002</t>
-  </si>
-  <si>
-    <t>Brief 62: NOW #8</t>
-  </si>
-  <si>
-    <t>HLTH-001,HLTH-002</t>
-  </si>
-  <si>
-    <t>Brief 62: NOW #9</t>
-  </si>
-  <si>
-    <t>FMT-001,FMT-002,FMT-003</t>
-  </si>
-  <si>
-    <t>Brief 62: NOW #10</t>
-  </si>
-  <si>
-    <t>OCR</t>
-  </si>
-  <si>
-    <t>Part of PDF -&gt; editable (brief 43)</t>
-  </si>
-  <si>
-    <t>Multilingual support</t>
-  </si>
-  <si>
-    <t>TRAN-007,FONT-003</t>
-  </si>
-  <si>
-    <t>Part of translation + FontResolver</t>
-  </si>
-  <si>
-    <t>RTL</t>
-  </si>
-  <si>
-    <t>FONT-003,FONT-004</t>
-  </si>
-  <si>
-    <t>Part of FontResolver</t>
-  </si>
-  <si>
-    <t>CJK</t>
-  </si>
-  <si>
-    <t>Glossary</t>
-  </si>
-  <si>
-    <t>Part of translation MVP (brief 49)</t>
-  </si>
-  <si>
-    <t>Terminology lock</t>
-  </si>
-  <si>
-    <t>Citation preservation</t>
-  </si>
-  <si>
-    <t>Preservation is fidelity work; a citation editor is LATER</t>
-  </si>
-  <si>
-    <t>Bibliography preservation</t>
-  </si>
-  <si>
-    <t>Preservation is fidelity work</t>
-  </si>
-  <si>
-    <t>Content controls</t>
-  </si>
-  <si>
-    <t>Preserve now; editing content controls NEXT</t>
-  </si>
-  <si>
-    <t>Custom fields</t>
-  </si>
-  <si>
-    <t>Preserve custom properties and fields now; an editor NEXT</t>
-  </si>
-  <si>
-    <t>Document compare</t>
-  </si>
-  <si>
-    <t>NEXT</t>
-  </si>
-  <si>
-    <t>Brief 62: NEXT</t>
-  </si>
-  <si>
-    <t>Version compare</t>
-  </si>
-  <si>
-    <t>Brief 62: NEXT (batch processing)</t>
-  </si>
-  <si>
-    <t>After the translation MVP</t>
-  </si>
-  <si>
-    <t>Table repair</t>
-  </si>
-  <si>
-    <t>List repair</t>
-  </si>
-  <si>
-    <t>Brief 62: NEXT (accessibility)</t>
-  </si>
-  <si>
-    <t>Heading hierarchy checker</t>
-  </si>
-  <si>
-    <t>Link checker</t>
-  </si>
-  <si>
-    <t>Alt-text checker</t>
-  </si>
-  <si>
-    <t>HLTH-001,FEAT-010</t>
-  </si>
-  <si>
-    <t>Metadata editor</t>
-  </si>
-  <si>
-    <t>Global style replacement</t>
-  </si>
-  <si>
-    <t>Find/replace with formatting</t>
-  </si>
-  <si>
-    <t>Tracked change cleanup</t>
-  </si>
-  <si>
-    <t>Template extraction</t>
-  </si>
-  <si>
-    <t>Document-to-template</t>
-  </si>
-  <si>
-    <t>Template matching</t>
-  </si>
-  <si>
-    <t>Advanced template sharing</t>
-  </si>
-  <si>
-    <t>Teams</t>
-  </si>
-  <si>
-    <t>Translation memory</t>
-  </si>
-  <si>
-    <t>PDF merge/split</t>
-  </si>
-  <si>
-    <t>Page reorder</t>
-  </si>
-  <si>
-    <t>Page rotate</t>
-  </si>
-  <si>
-    <t>Page delete</t>
-  </si>
-  <si>
-    <t>Page extract</t>
-  </si>
-  <si>
-    <t>Merge documents</t>
-  </si>
-  <si>
-    <t>LATER</t>
-  </si>
-  <si>
-    <t>Split documents</t>
-  </si>
-  <si>
-    <t>Watermark</t>
-  </si>
-  <si>
-    <t>Forms (advanced)</t>
-  </si>
-  <si>
-    <t>Brief 62: LATER</t>
-  </si>
-  <si>
-    <t>SmartArt editing</t>
-  </si>
-  <si>
-    <t>Brief 62: LATER; SmartArt is preserved, not edited</t>
-  </si>
-  <si>
-    <t>OLE</t>
-  </si>
-  <si>
-    <t>Brief 62: LATER; OLE objects preserved, not edited</t>
-  </si>
-  <si>
-    <t>Full tracked-change editor</t>
-  </si>
-  <si>
-    <t>Advanced citation manager</t>
-  </si>
-  <si>
-    <t>Advanced drawing editor</t>
-  </si>
-  <si>
-    <t>Layout-preserving PDF editing (frames/anchors)</t>
-  </si>
-  <si>
-    <t>ARCHITECTURE_ONLY</t>
-  </si>
-  <si>
-    <t>Phase 9: architecture and hooks only</t>
-  </si>
-  <si>
-    <t>Product tasks (live from MASTER)</t>
-  </si>
-  <si>
-    <t>TRANSLATION — Translation and fonts</t>
-  </si>
-  <si>
-    <t>Translation MVP and FontResolver. Categories: TRANSLATION, FONT. Rows are formulas over MASTER — change task data in MASTER or with tools/tracker/tracker.py.</t>
-  </si>
-  <si>
-    <t>PDF_TO_EDITABLE — PDF to editable</t>
-  </si>
-  <si>
-    <t>PDF to editable document conversion. Categories: P2E. Rows are formulas over MASTER — change task data in MASTER or with tools/tracker/tracker.py.</t>
-  </si>
-  <si>
-    <t>BILLING_PLANS — Plans and billing</t>
-  </si>
-  <si>
-    <t>Initial plan hypothesis — brief §64: configurable defaults, not final prices; confirm against measured AI and infrastructure cost. Blue = input.</t>
-  </si>
-  <si>
-    <t>Usage unit / feature</t>
-  </si>
-  <si>
-    <t>FREE</t>
-  </si>
-  <si>
-    <t>PRO</t>
-  </si>
-  <si>
-    <t>BUSINESS</t>
-  </si>
-  <si>
-    <t>Documents / month</t>
-  </si>
-  <si>
-    <t>BUSINESS: per workspace</t>
-  </si>
-  <si>
-    <t>PDF conversion pages / month</t>
-  </si>
-  <si>
-    <t>OCR pages / month</t>
-  </si>
-  <si>
-    <t>Translation characters / month</t>
-  </si>
-  <si>
-    <t>AI operations / month</t>
-  </si>
-  <si>
-    <t>Exports / month</t>
-  </si>
-  <si>
-    <t>high</t>
-  </si>
-  <si>
-    <t>BUSINESS: 'high export limits', no number given</t>
-  </si>
-  <si>
-    <t>Templates</t>
-  </si>
-  <si>
-    <t>basic</t>
-  </si>
-  <si>
-    <t>custom</t>
-  </si>
-  <si>
-    <t>shared</t>
-  </si>
-  <si>
-    <t>Formatting</t>
-  </si>
-  <si>
-    <t>Format by Example</t>
-  </si>
-  <si>
-    <t>-</t>
-  </si>
-  <si>
-    <t>Advanced Document Health</t>
-  </si>
-  <si>
-    <t>yes</t>
-  </si>
-  <si>
-    <t>Version history</t>
-  </si>
-  <si>
-    <t>no</t>
-  </si>
-  <si>
-    <t>reasonable limits</t>
-  </si>
-  <si>
-    <t>Team workspace</t>
-  </si>
-  <si>
-    <t>Priority processing</t>
-  </si>
-  <si>
-    <t>Advanced controls</t>
-  </si>
-  <si>
-    <t>Billing and plan tasks (live from MASTER)</t>
-  </si>
-  <si>
-    <t>INFRA — Infrastructure</t>
-  </si>
-  <si>
-    <t>Tracker, jobs, storage, observability, deployment, documentation. Categories: INFRA, JOBS, STORAGE, OBSERVABILITY, DOCS. Rows are formulas over MASTER — change task data in MASTER or with tools/tracker/tracker.py.</t>
-  </si>
-  <si>
-    <t>Timestamp</t>
-  </si>
-  <si>
-    <t>Task ID</t>
-  </si>
-  <si>
-    <t>Change</t>
-  </si>
-  <si>
-    <t>Files</t>
-  </si>
-  <si>
-    <t>Created SmartDoc_Master_Implementation_Tracker.xlsx from the 2026-09-26 audit findings and the brief's phases: 151 tasks, 20 findings, 15 release gates.</t>
-  </si>
-  <si>
-    <t>tools/tracker/tracker.py, tools/tracker/seed.py</t>
-  </si>
-  <si>
-    <t>N/A</t>
-  </si>
-  <si>
-    <t>Built the Excel control centre: MASTER with 151 stable-ID tasks from the audit findings and the brief's 19 phases, CRITICAL_FIXES (20 findings -&gt; fix tasks, live status), 14 category views, DASHBOARD (totals, completion/verified %, phase %, category %, P0/P1 remaining), CHANGE_LOG, SESSION_STATE, RELEASE_GATES GATE-001..015. Formulas verified in Excel against independently computed values.</t>
-  </si>
-  <si>
-    <t>tools/tracker/*, SmartDoc_Master_Implementation_Tracker.xlsx, .gitignore</t>
-  </si>
-  <si>
-    <t>Resume reminder set with the platform scheduler; it fired and resumed the work. It only fires while this session is open and idle, which is recorded in AI-CONTINUATION.md.</t>
-  </si>
-  <si>
-    <t>Created the checkpoint system: AI-CONTINUATION.md with CURRENT STATE / LAST VERIFIED / WHAT WAS CHANGED / WHAT PASSED / WHAT FAILED / WHAT REMAINS / NEXT ACTION / IMPORTANT WARNINGS, session-state.json mirrored into SESSION_STATE by tracker.py state, and the brief saved verbatim for future sessions.</t>
-  </si>
-  <si>
-    <t>docs/AI-CONTINUATION.md, docs/session-state.json, docs/implementation-brief.md</t>
-  </si>
-  <si>
-    <t>Baseline backend suite: 643 passed, 1 skipped (optional real-Word check), 0 failed in 88 s on ea69829. Recorded as RUN-0001.</t>
-  </si>
-  <si>
-    <t>Baseline frontend: eslint clean, tsc clean, Vitest 46 passed in 6 files, production build succeeded. Recorded as RUN-0002..RUN-0005.</t>
-  </si>
-  <si>
-    <t>Baseline E2E: 16 Playwright workflows passed against the throwaway stack (SQLite backend :8100, production build :3100). The brief's 24-workflow target is TEST-040; temp-dir leak logged as TEST-006.</t>
-  </si>
-  <si>
-    <t>Baseline database: alembic head 85211092fe4c, check reports no drift, full down/up cycle clean; PostgreSQL offline SQL builds 14 tables with RLS; Supabase has all 8 migrations and only INFO-level advisor notices.</t>
-  </si>
-  <si>
-    <t>Baseline dependency audit: pip-audit finds no known vulnerabilities in requirements.lock or requirements-dev.lock; npm audit reports 0 vulnerabilities (production and dev).</t>
-  </si>
-  <si>
-    <t>Baseline infrastructure inspected: compose file valid with 8 services, arq worker and in-process job backends, local and S3 storage providers. Docker images were not built (daemon not running) - left to INFRA-010.</t>
-  </si>
-  <si>
-    <t>Baseline fixtures: the repository's 12 golden DOCX are generated by python-docx (not Word-authored) plus one PDF; the audit's 17 Word-authored fixtures still live outside the repo and move in with TEST-020.</t>
-  </si>
-  <si>
-    <t>Wrote docs/architecture/current-baseline.md: stack versions, the 11 baseline checks with commands and results, the migration chain and live database state, fixture inventory, audit performance figures, and what the baseline could not verify (Docker images, real AI model, Stripe, e-mail, hosting).</t>
-  </si>
-  <si>
-    <t>INFRA-001, INFRA-002, INFRA-003, TEST-001, TEST-002, TEST-003, TEST-004, TEST-005, SEC-001, INFRA-004, DOCS-001</t>
-  </si>
-  <si>
-    <t>Phase 0 committed (4da4ecb, pushed to feature/smartdoc-production-hardening): tracker, checkpoint system and measured baseline. All 11 phase-0 tasks DONE; no production code changed.</t>
-  </si>
-  <si>
-    <t>see commit 4da4ecb</t>
-  </si>
-  <si>
-    <t>Model now holds blocks nested inside table cells, list items and quotes as Elements (authoritative when set; inline keeps plain text), plus list numbering start/format; nesting capped at 8 levels (422 beyond). schemaVersion stays 1: the fields are additive.</t>
-  </si>
-  <si>
-    <t>backend/app/models/document.py, backend/tests/test_document_nesting.py</t>
-  </si>
-  <si>
-    <t>Regenerated the OpenAPI schema and the frontend's generated types for the nested-block and numbering fields; the contract test and the type check pass.</t>
-  </si>
-  <si>
-    <t>frontend/types/generated/*, frontend/types/document.ts</t>
-  </si>
-  <si>
-    <t>Backend readers now see nested blocks: pasted pictures inside cells/list items/quotes are validated and moved to asset storage like top-level ones (security and quota), exports fetch their assets, and the links health check covers list items, cells and nested blocks.</t>
-  </si>
-  <si>
-    <t>backend/app/services/image_assets.py, backend/app/services/document_service.py, backend/app/formatting/health.py</t>
-  </si>
-  <si>
-    <t>Word export renders nested blocks in cells, list items and quotes in reading order (verified by text order), numbers lists from their start in their format, and writes pictures' alt text.</t>
-  </si>
-  <si>
-    <t>backend/app/export/docx_export.py</t>
-  </si>
-  <si>
-    <t>PDF export renders nested blocks and list numbering (start/format); nested numbered levels now use the same a./i. sequence as the Word export instead of 1. everywhere.</t>
-  </si>
-  <si>
-    <t>backend/app/export/pdf_export.py</t>
-  </si>
-  <si>
-    <t>The editor mapping is total over the schema (tested against getSchema(editorExtensions)); anything unknown stops the save with a visible 'Not saved' message instead of being dropped, and the last saved version stays untouched.</t>
-  </si>
-  <si>
-    <t>frontend/editor/*</t>
-  </si>
-  <si>
-    <t>frontend/editor/nestedBlocks.test.ts (7 refusal cases); frontend/editor/useAutoSave.test.tsx (3)</t>
-  </si>
-  <si>
-    <t>Playwright pastes rich HTML (lists, code and a picture in table cells; a list in a quote; code in a list item; a list starting at 3 in letters), waits for autosave and reloads: everything is still there and no 'Not saved' appears.</t>
-  </si>
-  <si>
-    <t>frontend/e2e/nested.spec.ts</t>
-  </si>
-  <si>
-    <t>CORE-001, CORE-002, CORE-003, EDIT-001, EDIT-002, EDIT-003, EDIT-004, EDIT-005, EDIT-006, DOCX-001, PDF-001</t>
-  </si>
-  <si>
-    <t>Committed phase-01a-editor-integrity (1fe27a9, pushed): nested blocks in cells, list items and quotes survive the editor, the backend and both exports; unknown content stops the save visibly. AUD-01 fix tasks all DONE.</t>
-  </si>
-  <si>
-    <t>Import now produces a Document Fidelity Report: the importer's notes as items (feature, policy, count, content lost) plus an independent content check - the source's words (DOCX XML read separately from the importer, Markdown by what it renders, PDF extracted text) against the document's, in order. 'Verified' only when identical; differences listed with context (missing/added/changed/moved).</t>
-  </si>
-  <si>
-    <t>backend/app/fidelity/*, backend/app/models/document.py, backend/app/services/ingestion_service.py</t>
-  </si>
-  <si>
-    <t>Every importer note now carries a stable feature key and a brief-§90 policy class; review count and content-loss count are derived from them.</t>
-  </si>
-  <si>
-    <t>The editor shows the import's verdict in the status bar and a Проверка panel: content verified / differs (with word-level differences) / body complete but some content left out, then each item by policy. Browser check with a05 caught and fixed a misleading 'No content changes' when header text had been left out.</t>
-  </si>
-  <si>
-    <t>frontend/editor/panels/FidelityPanel.tsx, frontend/editor/EditorStatusBar.tsx, frontend/editor/DocumentEditorShell.tsx</t>
-  </si>
-  <si>
-    <t>FID-001, FID-004, FID-005, INFRA-005</t>
-  </si>
-  <si>
-    <t>Committed phase-01b-fidelity-report (8a330be, pushed): import fidelity report with policy classes and an independent word-level content check, shown in the editor; throwaway preview scripts.</t>
-  </si>
-  <si>
-    <t>Exports now report what they approximate or leave out (missing pictures, WebP a Word file can't hold, tables restyled for Word-sourced documents, edited kept fragments, page breaks in PDF tables, PDF comments/equations/fields/internal links, scripts the PDF can't lay out, alt text) and re-read the file: a Word export must hold exactly the document's words, a PDF every word in order (its own list numbers and page headers allowed). Shown under the Download button; the job result carries it.</t>
-  </si>
-  <si>
-    <t>Committed phase-01c-export-report (e55412f, pushed): export fidelity report with read-back content check, shown in the Export menu.</t>
-  </si>
-  <si>
-    <t>Added the machine-readable capability matrix (brief §91): 67 document features with import/edit/export/round-trip support and the policy the fidelity report uses, served at GET /api/v1/capabilities. Tests tie it to the code both ways, require a test for every clean round trip and a task for every unreported gap; writing it exposed unreported gaps now tracked (EDIT-012, DOCX-027).</t>
-  </si>
-  <si>
-    <t>backend/app/capabilities.py, backend/app/api/capabilities.py, backend/app/main.py, backend/tests/test_capabilities.py, frontend/types/generated/*</t>
-  </si>
-  <si>
-    <t>Committed phase-01d-capability-matrix (fcf30d7, pushed).</t>
-  </si>
-  <si>
-    <t>FID-002: import report now names empty spacing paragraphs, unsafe link addresses and per-section differences (page setup, odd/even breaks, page numbering, borders, line numbers, vertical alignment); matrix rows docx.empty_paragraphs + docx.sections updated</t>
-  </si>
-  <si>
-    <t>backend/app/fidelity/docx_detect.py, backend/app/fidelity/imports.py, backend/app/parsers/docx.py, backend/app/parsers/docx_inline.py, backend/app/capabilities.py, backend/tests/test_docx_detect.py</t>
-  </si>
-  <si>
-    <t>DOCX-015: section breaks break the page only where Word does (next section's w:type decides); continuous breaks no longer become page breaks</t>
-  </si>
-  <si>
-    <t>tests/test_docx_detect.py::test_a_section_break_breaks_the_page_only_where_word_does</t>
-  </si>
-  <si>
-    <t>DOCX-016: list number formats, start values and continuation round-trip; custom and multi-level labels reported</t>
-  </si>
-  <si>
-    <t>DOCX-012: Word core properties round-trip; custom properties and sensitivity labels reported without values</t>
-  </si>
-  <si>
-    <t>tests/test_docx_detect.py::test_the_files_own_properties_go_back_into_word_not_the_templates, tests/test_docx_detect.py::test_metadata_that_is_not_kept_is_reported_without_its_values</t>
-  </si>
-  <si>
-    <t>DOCX-026: unsafe link addresses reported instead of silently dropped</t>
-  </si>
-  <si>
-    <t>Golden JSON export is deterministic (uuid5 ids by order, fixed timestamps) so a regenerated fixture only differs where the importer's output did</t>
-  </si>
-  <si>
-    <t>backend/scripts/export_golden_json.py, frontend/tests/fixtures/golden/*.json</t>
-  </si>
-  <si>
-    <t>two consecutive exports byte-identical; tests/test_golden_documents.py::test_the_frontend_golden_json_is_current</t>
-  </si>
-  <si>
-    <t>FID-002 committed and pushed (phase-01e-import-detections)</t>
-  </si>
-  <si>
-    <t>SEC-022: formatting rule values validated at every entry and at resolve; CSS break-out via element style/page settings/instructions closed</t>
-  </si>
-  <si>
-    <t>backend/app/formatting/values.py, backend/app/formatting/engine.py, backend/app/schemas/formatting.py, backend/app/schemas/document.py, backend/app/ai/instruction_extraction.py, backend/tests/test_rule_values.py</t>
-  </si>
-  <si>
-    <t>FMT-005: instruction-path rule values validated before reaching CSS/export (with SEC-022)</t>
-  </si>
-  <si>
-    <t>EDIT-008: pasted/shortcut alignment saved as the element's own style and kept on split; paste into an empty paragraph keeps the pasted paragraphs' attributes</t>
-  </si>
-  <si>
-    <t>frontend/editor/tiptapToDocument.ts, frontend/editor/documentToTiptap.ts, frontend/editor/useAutoSave.ts, frontend/editor/pasteIntoEmptyBlock.ts, frontend/editor/extensions.ts, frontend/services/api/documents.ts, backend/app/schemas/document.py, backend/app/formatting/engine.py, backend/app/services/document_service.py, backend/app/api/documents.py</t>
-  </si>
-  <si>
-    <t>EDIT-009: pasted picture size kept as the picture's width share</t>
-  </si>
-  <si>
-    <t>EDIT-012: values outside the model named in the status bar and the Проверка panel</t>
-  </si>
-  <si>
-    <t>EDIT-011: cell alignment from pasted cells kept per column; differing cells and column widths reported</t>
-  </si>
-  <si>
-    <t>EDIT-008, EDIT-009, EDIT-012, SEC-022, FMT-005</t>
-  </si>
-  <si>
-    <t>Committed and pushed phase-01f-editor-direct-formatting</t>
-  </si>
-  <si>
-    <t>EDIT-010: link titles kept from Word/Markdown through the editor back into Word</t>
-  </si>
-  <si>
-    <t>backend/app/models/document.py, backend/app/parsers/docx_inline.py, backend/app/parsers/docx.py, backend/app/export/docx_export.py, backend/app/parsers/markdown.py, frontend/editor/tiptapToDocument.ts, frontend/editor/documentToTiptap.ts</t>
-  </si>
-  <si>
-    <t>FID-006: Markdown pictures named as left out (content), thematic breaks kept as rules</t>
-  </si>
-  <si>
-    <t>backend/app/parsers/markdown.py, backend/app/capabilities.py, backend/tests/test_capabilities.py, backend/tests/test_markdown_parser.py</t>
-  </si>
-  <si>
-    <t>EDIT-011: cell alignment/widths the model can't hold are named; keeping them moves to DOCX-017</t>
-  </si>
-  <si>
-    <t>EDIT-007: marks in one canonical order (MarkType) on both sides; opening a document saves nothing</t>
-  </si>
-  <si>
-    <t>backend/app/models/document.py, frontend/editor/tiptapToDocument.ts</t>
-  </si>
-  <si>
-    <t>TEST-010: nested-structure regression suite consolidated and verified</t>
-  </si>
-  <si>
-    <t>EDIT-008, EDIT-010, FID-006</t>
-  </si>
-  <si>
-    <t>Phase 1 browser check in the throwaway stack: Markdown doc with a picture -&gt; 'Body text complete, some content left out · 1 to review' (picture named with its description), '---' imported as a rule; pasted centred line + 160px picture + hsl colour + titled link at the end -&gt; status 'Saved · 1 formatting change not kept', Проверка 'While editing' lists the colour; after reload: line centred, picture width 24.9%, link title kept, notice gone</t>
-  </si>
-  <si>
-    <t>manual browser check (throwaway stack, fresh SQLite)</t>
-  </si>
-  <si>
-    <t>DOCS-011: documentation tree started for Phase 1 (document model, fidelity, docx, formatting, security, testing)</t>
-  </si>
-  <si>
-    <t>EDIT-007, EDIT-010, EDIT-011, FID-006, TEST-010, DOCS-011</t>
-  </si>
-  <si>
-    <t>Committed and pushed phase-01g-phase-1-complete; Phase 1 complete</t>
-  </si>
-  <si>
-    <t>AI-001: order/count/token/numeric/punctuation-aware comparator for AI output, with classified differences</t>
-  </si>
-  <si>
-    <t>backend/app/fidelity/text_check.py, backend/tests/test_ai_fidelity.py</t>
-  </si>
-  <si>
-    <t>AI-002: numbers and units protected; changed_numbers for cross-language checks</t>
-  </si>
-  <si>
-    <t>AI-003: structure analysis refuses answers that alter the text, per piece, logging without content</t>
-  </si>
-  <si>
-    <t>backend/app/ai/structure_analysis.py</t>
-  </si>
-  <si>
-    <t>AI-004: adversarial fidelity tests for every alteration the brief names</t>
-  </si>
-  <si>
-    <t>AI-001, AI-002, AI-003, AI-004</t>
-  </si>
-  <si>
-    <t>Committed and pushed phase-02a-ai-fidelity-check</t>
-  </si>
-  <si>
-    <t>AI-005: AI operations classified FORMAT/STRUCTURE/CONTENT; per-element instruction styles no longer dropped by the formatting pass</t>
-  </si>
-  <si>
-    <t>backend/app/formatting/proposals.py, backend/app/services/document_service.py</t>
-  </si>
-  <si>
-    <t>REV-001: change model with categories, used for proposals</t>
-  </si>
-  <si>
-    <t>backend/app/models/document.py, frontend/types/document.ts</t>
-  </si>
-  <si>
-    <t>AI-006: PLAN-&gt;VALIDATE-&gt;PREVIEW-&gt;ACCEPT-&gt;APPLY for AI content changes</t>
-  </si>
-  <si>
-    <t>backend/app/formatting/proposals.py, backend/app/services/document_service.py, backend/app/api/documents.py, backend/app/jobs/runner.py, backend/app/schemas/document.py, backend/app/schemas/jobs.py</t>
-  </si>
-  <si>
-    <t>AI-007: proposal review UI with accept/reject, E2E verified</t>
-  </si>
-  <si>
-    <t>frontend/editor/panels/ProposalsList.tsx, frontend/editor/panels/InstructionsPanel.tsx, frontend/editor/EditorStatusBar.tsx, frontend/editor/useFormatting.ts, frontend/services/api/documents.ts, frontend/services/api/jobs.ts, backend/scripts/e2e_ai.py, backend/scripts/e2e_server.py</t>
-  </si>
-  <si>
-    <t>AI-005, REV-001, AI-006, AI-007</t>
-  </si>
-  <si>
-    <t>Committed and pushed phase-02b-ai-proposals</t>
-  </si>
-  <si>
-    <t>AI-008: per-job/per-request AI call and time budget; no unbounded retries</t>
-  </si>
-  <si>
-    <t>backend/app/ai/budget.py, backend/app/config.py, backend/app/jobs/runner.py, backend/app/api/deps.py, backend/app/ai/structure_analysis.py</t>
-  </si>
-  <si>
-    <t>Committed and pushed phase-02c-ai-budget</t>
-  </si>
-  <si>
-    <t>AI-009: prompt-injection review; AI answer fields bounded; hostile-document tests</t>
-  </si>
-  <si>
-    <t>backend/app/ai/schemas.py, backend/app/ai/structure_analysis.py, backend/tests/test_prompt_injection.py</t>
-  </si>
-  <si>
-    <t>SEC-018: prompt injection / AI output abuse covered by AI-009's tests</t>
-  </si>
-  <si>
-    <t>AI-001, AI-005, AI-007, AI-009</t>
-  </si>
-  <si>
-    <t>Phase 2 gate: backend 817 passed/1 skipped, Vitest 117, Playwright 20; browser check in the throwaway stack - 'make the title red and delete “This draft paragraph”': title red at once, the paragraph kept and shown under Changes to review (struck through, with the instruction), notice + '1 AI change to review'; Accept removed it, reload kept it removed with nothing pending</t>
-  </si>
-  <si>
-    <t>full suites + manual browser check</t>
-  </si>
-  <si>
-    <t>DOCX-010: original Word package kept as an immutable, checksummed asset</t>
-  </si>
-  <si>
-    <t>backend/app/models/document.py, backend/app/services/document_service.py</t>
-  </si>
-  <si>
-    <t>DOCX-011: Word exports written into the original package; import report reflects what they keep</t>
-  </si>
-  <si>
-    <t>backend/app/export/docx_export.py, backend/app/fidelity/imports.py, backend/app/fidelity/docx_source.py, backend/app/fidelity/docx_detect.py, backend/app/fidelity/exports.py, backend/app/jobs/runner.py, backend/app/api/documents.py, backend/app/capabilities.py</t>
-  </si>
-  <si>
-    <t>TEST-023: independent package validation of every Word export</t>
-  </si>
-  <si>
-    <t>backend/app/export/package_check.py, backend/tests/test_package_check.py</t>
-  </si>
-  <si>
-    <t>DOCX-012: metadata preserved (core in the model, app/custom/labels via the original package)</t>
-  </si>
-  <si>
-    <t>DOCX-028: unchanged blocks keep their original XML in Word exports; server-side provenance; earlier sections follow page setup, header and page-number changes; lost sections reported; golden 13-kept-blocks + E2E.</t>
-  </si>
-  <si>
-    <t>backend/app/export/provenance.py, backend/app/export/docx_export.py, backend/app/parsers/docx.py, backend/app/models/document.py, backend/app/services/document_service.py, backend/app/fidelity/imports.py, backend/app/fidelity/exports.py, backend/app/capabilities.py, frontend/editor/tiptapToDocument.ts, frontend/e2e/kept-blocks.spec.ts, docs/docx/README.md</t>
-  </si>
-  <si>
-    <t>DOCX-028 committed and pushed as c8c2d27 (phase-03b-original-blocks).</t>
-  </si>
-  <si>
-    <t>DOCX-025: Word's hidden text stays hidden - hidden mark with Word's style resolution, editor shows it only on request, vanish in Word exports, left out of PDF with a note, consistent content checks.</t>
-  </si>
-  <si>
-    <t>backend/app/models/document.py, backend/app/parsers/docx_inline.py, backend/app/parsers/docx_styles.py, backend/app/parsers/docx.py, backend/app/fidelity/docx_detect.py, backend/app/fidelity/content.py, backend/app/fidelity/exports.py, backend/app/export/docx_export.py, backend/app/export/pdf_export.py, frontend/editor/hiddenText.ts, frontend/editor/EditorStatusBar.tsx, frontend/editor/DocumentEditorShell.tsx, frontend/app/globals.css</t>
-  </si>
-  <si>
-    <t>DOCX-025 committed and pushed as 7d1af86 (phase-03c-hidden-text).</t>
-  </si>
-  <si>
-    <t>DOCX-013 part 1: underline and strike styles, capitals, small capitals, spacing and raised/lowered text kept through import, editor, Word and PDF; paragraph-style formatting turned off by a run fixed.</t>
-  </si>
-  <si>
-    <t>backend/app/models/document.py, backend/app/parsers/docx_inline.py, backend/app/parsers/docx_styles.py, backend/app/parsers/docx.py, backend/app/export/docx_export.py, backend/app/export/pdf_export.py, backend/app/fidelity/*, frontend/editor/characterFormatting.ts, frontend/editor/tiptapToDocument.ts</t>
-  </si>
-  <si>
-    <t>backend 888 passed/1 skipped (tests/test_character_formatting.py 12); Vitest 128 (editor/characterFormatting.test.ts 3, golden round trip of 02); Playwright 22; tsc + eslint clean</t>
-  </si>
-  <si>
-    <t>DOCX-013 part 1 committed and pushed as 6619159 (phase-03d-character-formatting); part 2 next.</t>
-  </si>
-  <si>
-    <t>6619159</t>
-  </si>
-  <si>
-    <t>FID-007: reports follow the Word copy - kept while unchanged at import, rewritten losses named at export, unsafe links never copied back.</t>
-  </si>
-  <si>
-    <t>backend/app/fidelity/imports.py, backend/app/export/docx_export.py, backend/tests/test_copy_reports.py</t>
-  </si>
-  <si>
-    <t>DOCX-013 part 2: language kept; scale and effects named and kept while unchanged; brief §22 list is now supported, preserved or explicitly named.</t>
-  </si>
-  <si>
-    <t>backend/app/models/document.py, backend/app/parsers/docx_inline.py, backend/app/fidelity/docx_detect.py, frontend/editor/characterFormatting.ts</t>
-  </si>
-  <si>
-    <t>DOCX-013 done: part 1 6619159, part 2 d32c6a6 (phase-03e-copy-reports).</t>
-  </si>
-  <si>
-    <t>FID-007 committed and pushed as d32c6a6.</t>
-  </si>
-  <si>
-    <t>DOCX-014 part 1: right indent, shading, pagination controls, contextual spacing and direction kept through import, CSS, Word and PDF.</t>
-  </si>
-  <si>
-    <t>backend/app/models/document.py, backend/app/formatting/*, backend/app/parsers/docx_styles.py, backend/app/parsers/docx.py, backend/app/export/docx_export.py, backend/app/export/pdf_export.py</t>
-  </si>
-  <si>
-    <t>backend 903 passed/1 skipped (tests/test_paragraph_formatting.py 9); Vitest 129; Playwright 22; tsc + eslint clean</t>
-  </si>
-  <si>
-    <t>DOCX-014 part 1 committed and pushed as eade93e (phase-03f-paragraph-formatting); part 2 next.</t>
-  </si>
-  <si>
-    <t>eade93e</t>
-  </si>
-  <si>
-    <t>DOCX-014 part 2: paragraph borders and tab stops kept through import, CSS, Word and PDF; what the PDF and editor can't draw is named.</t>
-  </si>
-  <si>
-    <t>backend/app/formatting/values.py, backend/app/parsers/docx_styles.py, backend/app/export/docx_export.py, backend/app/export/pdf_export.py, backend/tests/test_paragraph_formatting.py</t>
-  </si>
-  <si>
-    <t>DOCX-014 done: part 1 eade93e, part 2 c158722 (phase-03g-borders-tab-stops).</t>
-  </si>
-  <si>
-    <t>DOCX-015 part 1a: section breaks are elements with their section's settings - imported, shown and paginated in the editor, written back into Word from the model.</t>
-  </si>
-  <si>
-    <t>backend/app/models/document.py, backend/app/parsers/docx.py, backend/app/export/docx_export.py, frontend/editor/sectionBreak.ts, frontend/editor/pagination.ts</t>
-  </si>
-  <si>
-    <t>tests/test_docx_detect.py::test_a_section_break_breaks_the_page_only_where_word_does; tests/test_sections.py (6); frontend/editor/sectionBreak.test.ts (3); backend 919 passed/1 skipped; Vitest 132; Playwright 22</t>
-  </si>
-  <si>
-    <t>DOCX-015 part 1a committed and pushed as 047685d (phase-03h-section-breaks); part 1b next.</t>
-  </si>
-  <si>
-    <t>047685d</t>
-  </si>
-  <si>
-    <t>DOCX-015 part 1b: the PDF follows each section's page setup, even/odd starts and numbering.</t>
-  </si>
-  <si>
-    <t>backend/app/export/pdf_export.py, backend/app/fidelity/exports.py, backend/tests/test_sections.py</t>
-  </si>
-  <si>
-    <t>tests/test_docx_detect.py::test_a_section_break_breaks_the_page_only_where_word_does; tests/test_sections.py (6); frontend/editor/sectionBreak.test.ts (3); backend 919 passed/1 skipped; Vitest 132; Playwright 22; tests/test_sections.py (7): per-page sizes, blank page, roman numbering, a picture fitting a narrow column; backend 920 passed/1 skipped</t>
-  </si>
-  <si>
-    <t>DOCX-015 part 1b committed and pushed as 35c6771 (phase-03i-pdf-sections); part 2 next.</t>
-  </si>
-  <si>
     <t>DOCX-015 part 2: each page shows its own section's header, footer and number in the editor, a PDF and Word (brief 24: the last section's header is no longer every page's). Fixed on the way: continuous sections took the page they start on in the PDF; the last section's own numbering was ignored by both exports; header text boxes were read two or three times; the PDF had a shadowed duplicate number formatter; a header changed here overwrote earlier sections' in a Word export into the original; page numbers left out made a section show the previous one's footer.</t>
   </si>
   <si>
+    <t>DOCX-015 part 2 committed and pushed as 7bbf7f2 (phase-03j-section-headers); part 3 next (the editor's pages per section, the last section's columns and header/footer distances in both exports).</t>
+  </si>
+  <si>
     <t>SESSION_STATE — Where the work stands</t>
   </si>
   <si>
@@ -4714,7 +4720,7 @@
     <t>Current Commit</t>
   </si>
   <si>
-    <t>bc138f5 (+ uncommitted changes)</t>
+    <t>7bbf7f2 (+ uncommitted changes)</t>
   </si>
   <si>
     <t>backend 936 passed, 1 skipped; vitest 140; e2e 23; tsc; eslint</t>
@@ -4729,7 +4735,7 @@
     <t>DOCX-015 — Part 3: the editor's pages per section (size, orientation, margins; columns shown or named); the last section's columns, column spacing and header/footer distances in the PDF and a fresh Word export (lastSection); PDF headers/footers at their distances; then close DOCX-015.</t>
   </si>
   <si>
-    <t>2026-09-29T15:11:41+03:00</t>
+    <t>2026-09-29T15:12:48+03:00</t>
   </si>
   <si>
     <t>Resume Instructions</t>
@@ -9436,7 +9442,7 @@
       </c>
       <c r="F15" s="1" t="str">
         <f>IF(SESSION_STATE!$B$17="","",SESSION_STATE!$B$17)</f>
-        <v>2026-09-29T15:11:41+03:00</v>
+        <v>2026-09-29T15:12:48+03:00</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
@@ -22403,7 +22409,7 @@
     <tabColor rgb="FF7F7F7F"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I90"/>
+  <dimension ref="A1:I91"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17" customWidth="1"/>
@@ -24592,7 +24598,7 @@
         <v>1065</v>
       </c>
       <c r="H89" s="12" t="s">
-        <v>516</v>
+        <v>1535</v>
       </c>
       <c r="I89" s="18"/>
     </row>
@@ -24607,7 +24613,7 @@
         <v>3</v>
       </c>
       <c r="D90" s="18" t="s">
-        <v>1535</v>
+        <v>1536</v>
       </c>
       <c r="E90" s="18"/>
       <c r="F90" s="18" t="s">
@@ -24617,12 +24623,37 @@
         <v>1385</v>
       </c>
       <c r="H90" s="12" t="s">
+        <v>1535</v>
+      </c>
+      <c r="I90" s="18"/>
+    </row>
+    <row r="91" spans="1:9" ht="165.75" x14ac:dyDescent="0.25">
+      <c r="A91" s="19">
+        <v>46294.63385416667</v>
+      </c>
+      <c r="B91" s="12" t="s">
+        <v>510</v>
+      </c>
+      <c r="C91" s="12">
+        <v>3</v>
+      </c>
+      <c r="D91" s="18" t="s">
+        <v>1537</v>
+      </c>
+      <c r="E91" s="18"/>
+      <c r="F91" s="18" t="s">
+        <v>514</v>
+      </c>
+      <c r="G91" s="12" t="s">
+        <v>1385</v>
+      </c>
+      <c r="H91" s="12" t="s">
         <v>516</v>
       </c>
-      <c r="I90" s="18"/>
+      <c r="I91" s="18"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I90" xr:uid="{00000000-0009-0000-0000-000011000000}"/>
+  <autoFilter ref="A1:I91" xr:uid="{00000000-0009-0000-0000-000011000000}"/>
   <conditionalFormatting sqref="G2:G5000">
     <cfRule type="cellIs" dxfId="4" priority="1" operator="equal">
       <formula>"PASS"</formula>
@@ -24659,7 +24690,7 @@
   <sheetData>
     <row r="1" spans="1:2" ht="20.25" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
-        <v>1536</v>
+        <v>1538</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -24669,15 +24700,15 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>1537</v>
+        <v>1539</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="10" t="s">
-        <v>1538</v>
+        <v>1540</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>1539</v>
+        <v>1541</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -24685,7 +24716,7 @@
         <v>6</v>
       </c>
       <c r="B5" s="18" t="s">
-        <v>1540</v>
+        <v>1542</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="25.5" x14ac:dyDescent="0.25">
@@ -24693,7 +24724,7 @@
         <v>9</v>
       </c>
       <c r="B6" s="18" t="s">
-        <v>1541</v>
+        <v>1543</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="38.25" x14ac:dyDescent="0.25">
@@ -24701,7 +24732,7 @@
         <v>12</v>
       </c>
       <c r="B7" s="18" t="s">
-        <v>1542</v>
+        <v>1544</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="25.5" x14ac:dyDescent="0.25">
@@ -24709,23 +24740,23 @@
         <v>15</v>
       </c>
       <c r="B8" s="18" t="s">
-        <v>1543</v>
+        <v>1545</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>1544</v>
+        <v>1546</v>
       </c>
       <c r="B9" s="18" t="s">
-        <v>1545</v>
+        <v>1547</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
-        <v>1546</v>
+        <v>1548</v>
       </c>
       <c r="B10" s="18" t="s">
-        <v>1547</v>
+        <v>1549</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
@@ -24733,7 +24764,7 @@
         <v>26</v>
       </c>
       <c r="B11" s="18" t="s">
-        <v>1548</v>
+        <v>1550</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
@@ -24741,7 +24772,7 @@
         <v>29</v>
       </c>
       <c r="B12" s="18" t="s">
-        <v>1549</v>
+        <v>1551</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="25.5" x14ac:dyDescent="0.25">
@@ -24749,7 +24780,7 @@
         <v>32</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>1550</v>
+        <v>1552</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="38.25" x14ac:dyDescent="0.25">
@@ -24757,7 +24788,7 @@
         <v>18</v>
       </c>
       <c r="B14" s="18" t="s">
-        <v>1551</v>
+        <v>1553</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
@@ -24777,20 +24808,20 @@
         <v>35</v>
       </c>
       <c r="B17" s="18" t="s">
-        <v>1552</v>
+        <v>1554</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
-        <v>1553</v>
+        <v>1555</v>
       </c>
       <c r="B18" s="18" t="s">
-        <v>1554</v>
+        <v>1556</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="6" t="s">
-        <v>1555</v>
+        <v>1557</v>
       </c>
       <c r="B19" s="18" t="str">
         <f>"Tasks "&amp;DASHBOARD!B5&amp;" · done "&amp;DASHBOARD!B6&amp;" · verified "&amp;DASHBOARD!B7&amp;" · in progress "&amp;DASHBOARD!B8&amp;" · blocked "&amp;DASHBOARD!B9&amp;" · failed "&amp;DASHBOARD!B10&amp;" · P0 open "&amp;DASHBOARD!B16&amp;" · P1 open "&amp;DASHBOARD!B17</f>
@@ -24799,7 +24830,7 @@
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
-        <v>1556</v>
+        <v>1558</v>
       </c>
       <c r="B20" s="18" t="s">
         <v>1369</v>
@@ -24807,7 +24838,7 @@
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" s="6" t="s">
-        <v>1557</v>
+        <v>1559</v>
       </c>
       <c r="B21" s="18" t="s">
         <v>1371</v>
@@ -32640,7 +32671,7 @@
   <sheetData>
     <row r="1" spans="1:9" ht="20.25" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
-        <v>1558</v>
+        <v>1560</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
@@ -32650,16 +32681,16 @@
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
-        <v>1559</v>
+        <v>1561</v>
       </c>
       <c r="B3" s="6" t="s">
         <v>1065</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>1560</v>
+        <v>1562</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>1561</v>
+        <v>1563</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
@@ -32682,10 +32713,10 @@
     </row>
     <row r="6" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>1562</v>
+        <v>1564</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>1563</v>
+        <v>1565</v>
       </c>
       <c r="C6" s="10" t="s">
         <v>57</v>
@@ -32711,16 +32742,16 @@
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="15" t="s">
-        <v>1564</v>
+        <v>1566</v>
       </c>
       <c r="B7" s="18" t="s">
-        <v>1565</v>
+        <v>1567</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>1561</v>
+        <v>1563</v>
       </c>
       <c r="D7" s="18" t="s">
-        <v>1566</v>
+        <v>1568</v>
       </c>
       <c r="E7" s="16">
         <f>SUMPRODUCT(ISNUMBER(SEARCH(","&amp;MASTER!$A$2:$A$2000&amp;",",","&amp;SUBSTITUTE($D7," ","")&amp;","))*((MASTER!$G$2:$G$2000="DONE")))</f>
@@ -32736,13 +32767,13 @@
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="15" t="s">
-        <v>1567</v>
+        <v>1569</v>
       </c>
       <c r="B8" s="18" t="s">
-        <v>1568</v>
+        <v>1570</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>1561</v>
+        <v>1563</v>
       </c>
       <c r="D8" s="18" t="s">
         <v>653</v>
@@ -32761,16 +32792,16 @@
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="15" t="s">
-        <v>1569</v>
+        <v>1571</v>
       </c>
       <c r="B9" s="18" t="s">
-        <v>1570</v>
+        <v>1572</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>1561</v>
+        <v>1563</v>
       </c>
       <c r="D9" s="18" t="s">
-        <v>1571</v>
+        <v>1573</v>
       </c>
       <c r="E9" s="16">
         <f>SUMPRODUCT(ISNUMBER(SEARCH(","&amp;MASTER!$A$2:$A$2000&amp;",",","&amp;SUBSTITUTE($D9," ","")&amp;","))*((MASTER!$G$2:$G$2000="DONE")))</f>
@@ -32786,13 +32817,13 @@
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="15" t="s">
-        <v>1572</v>
+        <v>1574</v>
       </c>
       <c r="B10" s="18" t="s">
-        <v>1573</v>
+        <v>1575</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>1561</v>
+        <v>1563</v>
       </c>
       <c r="D10" s="18" t="s">
         <v>727</v>
@@ -32811,16 +32842,16 @@
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="15" t="s">
-        <v>1574</v>
+        <v>1576</v>
       </c>
       <c r="B11" s="18" t="s">
-        <v>1575</v>
+        <v>1577</v>
       </c>
       <c r="C11" s="12" t="s">
-        <v>1561</v>
+        <v>1563</v>
       </c>
       <c r="D11" s="18" t="s">
-        <v>1576</v>
+        <v>1578</v>
       </c>
       <c r="E11" s="16">
         <f>SUMPRODUCT(ISNUMBER(SEARCH(","&amp;MASTER!$A$2:$A$2000&amp;",",","&amp;SUBSTITUTE($D11," ","")&amp;","))*((MASTER!$G$2:$G$2000="DONE")))</f>
@@ -32836,13 +32867,13 @@
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="15" t="s">
-        <v>1577</v>
+        <v>1579</v>
       </c>
       <c r="B12" s="18" t="s">
-        <v>1578</v>
+        <v>1580</v>
       </c>
       <c r="C12" s="12" t="s">
-        <v>1561</v>
+        <v>1563</v>
       </c>
       <c r="D12" s="18" t="s">
         <v>585</v>
@@ -32861,13 +32892,13 @@
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="15" t="s">
-        <v>1579</v>
+        <v>1581</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>1580</v>
+        <v>1582</v>
       </c>
       <c r="C13" s="12" t="s">
-        <v>1561</v>
+        <v>1563</v>
       </c>
       <c r="D13" s="18" t="s">
         <v>585</v>
@@ -32886,13 +32917,13 @@
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="15" t="s">
-        <v>1581</v>
+        <v>1583</v>
       </c>
       <c r="B14" s="18" t="s">
-        <v>1582</v>
+        <v>1584</v>
       </c>
       <c r="C14" s="12" t="s">
-        <v>1561</v>
+        <v>1563</v>
       </c>
       <c r="D14" s="18" t="s">
         <v>831</v>
@@ -32911,13 +32942,13 @@
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="15" t="s">
-        <v>1583</v>
+        <v>1585</v>
       </c>
       <c r="B15" s="18" t="s">
-        <v>1584</v>
+        <v>1586</v>
       </c>
       <c r="C15" s="12" t="s">
-        <v>1561</v>
+        <v>1563</v>
       </c>
       <c r="D15" s="18" t="s">
         <v>760</v>
@@ -32936,13 +32967,13 @@
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" s="15" t="s">
-        <v>1585</v>
+        <v>1587</v>
       </c>
       <c r="B16" s="18" t="s">
-        <v>1586</v>
+        <v>1588</v>
       </c>
       <c r="C16" s="12" t="s">
-        <v>1561</v>
+        <v>1563</v>
       </c>
       <c r="D16" s="18" t="s">
         <v>811</v>
@@ -32961,13 +32992,13 @@
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" s="15" t="s">
-        <v>1587</v>
+        <v>1589</v>
       </c>
       <c r="B17" s="18" t="s">
-        <v>1588</v>
+        <v>1590</v>
       </c>
       <c r="C17" s="12" t="s">
-        <v>1561</v>
+        <v>1563</v>
       </c>
       <c r="D17" s="18" t="s">
         <v>799</v>
@@ -32986,13 +33017,13 @@
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" s="15" t="s">
-        <v>1589</v>
+        <v>1591</v>
       </c>
       <c r="B18" s="18" t="s">
-        <v>1590</v>
+        <v>1592</v>
       </c>
       <c r="C18" s="12" t="s">
-        <v>1561</v>
+        <v>1563</v>
       </c>
       <c r="D18" s="18" t="s">
         <v>911</v>
@@ -33011,13 +33042,13 @@
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" s="15" t="s">
-        <v>1591</v>
+        <v>1593</v>
       </c>
       <c r="B19" s="18" t="s">
-        <v>1592</v>
+        <v>1594</v>
       </c>
       <c r="C19" s="12" t="s">
-        <v>1561</v>
+        <v>1563</v>
       </c>
       <c r="D19" s="18" t="s">
         <v>217</v>
@@ -33036,16 +33067,16 @@
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" s="15" t="s">
-        <v>1593</v>
+        <v>1595</v>
       </c>
       <c r="B20" s="18" t="s">
-        <v>1594</v>
+        <v>1596</v>
       </c>
       <c r="C20" s="12" t="s">
-        <v>1561</v>
+        <v>1563</v>
       </c>
       <c r="D20" s="18" t="s">
-        <v>1595</v>
+        <v>1597</v>
       </c>
       <c r="E20" s="16">
         <f>SUMPRODUCT(ISNUMBER(SEARCH(","&amp;MASTER!$A$2:$A$2000&amp;",",","&amp;SUBSTITUTE($D20," ","")&amp;","))*((MASTER!$G$2:$G$2000="DONE")))</f>
@@ -33061,13 +33092,13 @@
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" s="15" t="s">
-        <v>1596</v>
+        <v>1598</v>
       </c>
       <c r="B21" s="18" t="s">
-        <v>1597</v>
+        <v>1599</v>
       </c>
       <c r="C21" s="12" t="s">
-        <v>1561</v>
+        <v>1563</v>
       </c>
       <c r="D21" s="18" t="s">
         <v>892</v>
@@ -35805,7 +35836,7 @@
       </c>
       <c r="J68" s="12" t="str">
         <f>IFERROR(INDEX(MASTER!$P$2:$P$2000,MATCH($A68,MASTER!$A$2:$A$2000,0))&amp;"","")</f>
-        <v>35c6771</v>
+        <v>7bbf7f2</v>
       </c>
       <c r="K68" s="12" t="str">
         <f>IFERROR(INDEX(MASTER!$Q$2:$Q$2000,MATCH($A68,MASTER!$A$2:$A$2000,0))&amp;"","")</f>
@@ -39719,7 +39750,7 @@
       </c>
       <c r="J14" s="12" t="str">
         <f>IFERROR(INDEX(MASTER!$P$2:$P$2000,MATCH($A14,MASTER!$A$2:$A$2000,0))&amp;"","")</f>
-        <v>35c6771</v>
+        <v>7bbf7f2</v>
       </c>
       <c r="K14" s="12" t="str">
         <f>IFERROR(INDEX(MASTER!$Q$2:$Q$2000,MATCH($A14,MASTER!$A$2:$A$2000,0))&amp;"","")</f>
